--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="112">
   <si>
     <t>Symbol</t>
   </si>
@@ -259,12 +259,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -274,13 +274,64 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.5 → 52.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>47.5</t>
+  </si>
+  <si>
+    <t>52.5</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>70.3 → 59.5</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>70.3</t>
+  </si>
+  <si>
+    <t>59.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -311,11 +362,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,8 +400,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,6 +438,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,27 +531,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -954,106 +1060,106 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>26724.4</v>
+        <v>29620.05</v>
       </c>
       <c r="E2">
-        <v>-0.62</v>
+        <v>-0.09</v>
       </c>
       <c r="F2">
-        <v>28922.35</v>
+        <v>29647.9</v>
       </c>
       <c r="G2">
-        <v>23227.3</v>
+        <v>23410.95</v>
       </c>
       <c r="H2">
-        <v>-7.6</v>
+        <v>-0.09</v>
       </c>
       <c r="I2">
-        <v>15.06</v>
+        <v>26.52</v>
       </c>
       <c r="J2">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="K2">
-        <v>2.51</v>
+        <v>10.27</v>
       </c>
       <c r="L2">
-        <v>3.08</v>
+        <v>10.72</v>
       </c>
       <c r="M2">
-        <v>12.95</v>
+        <v>24.74</v>
       </c>
       <c r="N2">
-        <v>20.49</v>
+        <v>23.87</v>
       </c>
       <c r="O2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="Q2">
-        <v>26306.74</v>
+        <v>29366.84</v>
       </c>
       <c r="R2">
-        <v>26168.92</v>
+        <v>27844.22</v>
       </c>
       <c r="S2">
-        <v>26104.41</v>
+        <v>27061.91</v>
       </c>
       <c r="T2">
-        <v>26790.18</v>
+        <v>26955.61</v>
       </c>
       <c r="U2">
-        <v>-0.25</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="s">
         <v>79</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z2">
-        <v>57.37</v>
+        <v>76.2</v>
       </c>
       <c r="AA2">
-        <v>74.09</v>
+        <v>728.61</v>
       </c>
       <c r="AB2">
-        <v>10.3</v>
+        <v>520.5700000000001</v>
       </c>
       <c r="AC2">
-        <v>63.79</v>
+        <v>208.04</v>
       </c>
       <c r="AD2">
-        <v>81.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="AE2">
-        <v>56.04</v>
+        <v>82.38</v>
       </c>
       <c r="AF2">
-        <v>521.71</v>
+        <v>448.79</v>
       </c>
       <c r="AG2">
         <v>-100</v>
       </c>
       <c r="AH2">
-        <v>26892.81</v>
+        <v>30088.64</v>
       </c>
       <c r="AI2">
-        <v>25445.02</v>
+        <v>25599.79</v>
       </c>
       <c r="AJ2">
-        <v>25455.24</v>
+        <v>28374.42</v>
       </c>
       <c r="AK2" t="s">
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>16.7</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1067,58 +1173,58 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>10044.45</v>
+        <v>10011.4</v>
       </c>
       <c r="E3">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
       </c>
       <c r="G3">
-        <v>8549.9</v>
+        <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-4.37</v>
+        <v>-4.68</v>
       </c>
       <c r="I3">
-        <v>17.48</v>
+        <v>16.79</v>
       </c>
       <c r="J3">
-        <v>0.71</v>
+        <v>0.08</v>
       </c>
       <c r="K3">
-        <v>-1.58</v>
+        <v>1.21</v>
       </c>
       <c r="L3">
-        <v>5.03</v>
+        <v>-2.18</v>
       </c>
       <c r="M3">
-        <v>15.65</v>
+        <v>13.18</v>
       </c>
       <c r="N3">
-        <v>14.15</v>
+        <v>13.65</v>
       </c>
       <c r="O3">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="Q3">
-        <v>9905.879999999999</v>
+        <v>9978.559999999999</v>
       </c>
       <c r="R3">
-        <v>10137.27</v>
+        <v>9878.860000000001</v>
       </c>
       <c r="S3">
-        <v>10087.73</v>
+        <v>9925.950000000001</v>
       </c>
       <c r="T3">
-        <v>9516.040000000001</v>
+        <v>9699.129999999999</v>
       </c>
       <c r="U3">
-        <v>5.55</v>
+        <v>3.22</v>
       </c>
       <c r="V3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
@@ -1127,43 +1233,43 @@
         <v>80</v>
       </c>
       <c r="Y3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z3">
-        <v>48.09</v>
+        <v>59.57</v>
       </c>
       <c r="AA3">
-        <v>-58.06</v>
+        <v>21.11</v>
       </c>
       <c r="AB3">
-        <v>-25.35</v>
+        <v>-3.66</v>
       </c>
       <c r="AC3">
-        <v>-32.71</v>
+        <v>24.77</v>
       </c>
       <c r="AD3">
-        <v>37.12</v>
+        <v>72.95</v>
       </c>
       <c r="AE3">
-        <v>22.28</v>
+        <v>71.66</v>
       </c>
       <c r="AF3">
-        <v>136.54</v>
+        <v>85.37</v>
       </c>
       <c r="AH3">
-        <v>10523.75</v>
+        <v>10023.77</v>
       </c>
       <c r="AI3">
-        <v>9750.790000000001</v>
+        <v>9733.959999999999</v>
       </c>
       <c r="AJ3">
-        <v>10198.38</v>
+        <v>10073.2</v>
       </c>
       <c r="AK3" t="s">
         <v>82</v>
       </c>
       <c r="AL3">
-        <v>31.64</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1177,10 +1283,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11555.25</v>
+        <v>12229.45</v>
       </c>
       <c r="E4">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1189,91 +1295,91 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-8.58</v>
+        <v>-3.24</v>
       </c>
       <c r="I4">
-        <v>11.81</v>
+        <v>18.34</v>
       </c>
       <c r="J4">
-        <v>3.67</v>
+        <v>-0.24</v>
       </c>
       <c r="K4">
-        <v>1.52</v>
+        <v>4.19</v>
       </c>
       <c r="L4">
-        <v>5.73</v>
+        <v>6.96</v>
       </c>
       <c r="M4">
-        <v>-0.53</v>
+        <v>4.52</v>
       </c>
       <c r="N4">
-        <v>12.84</v>
+        <v>13.43</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="Q4">
-        <v>11284.83</v>
+        <v>12206.09</v>
       </c>
       <c r="R4">
-        <v>11261.01</v>
+        <v>11885.33</v>
       </c>
       <c r="S4">
-        <v>11287.47</v>
+        <v>11635</v>
       </c>
       <c r="T4">
-        <v>11816.74</v>
+        <v>11720.48</v>
       </c>
       <c r="U4">
-        <v>-2.21</v>
+        <v>4.34</v>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z4">
-        <v>61.64</v>
+        <v>73.58</v>
       </c>
       <c r="AA4">
-        <v>4.01</v>
+        <v>167.63</v>
       </c>
       <c r="AB4">
-        <v>-27.08</v>
+        <v>134.92</v>
       </c>
       <c r="AC4">
-        <v>31.09</v>
+        <v>32.71</v>
       </c>
       <c r="AD4">
-        <v>86.33</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="AE4">
-        <v>55.64</v>
+        <v>71.92</v>
       </c>
       <c r="AF4">
-        <v>156.24</v>
+        <v>114.17</v>
       </c>
       <c r="AH4">
-        <v>11557.39</v>
+        <v>12391.13</v>
       </c>
       <c r="AI4">
-        <v>10964.63</v>
+        <v>11379.53</v>
       </c>
       <c r="AJ4">
-        <v>11057.92</v>
+        <v>11869.84</v>
       </c>
       <c r="AK4" t="s">
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>30.09</v>
+        <v>54.11</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1287,10 +1393,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>40238.45</v>
+        <v>38748.15</v>
       </c>
       <c r="E5">
-        <v>0.8100000000000001</v>
+        <v>-0</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1299,46 +1405,46 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-3.12</v>
+        <v>-6.71</v>
       </c>
       <c r="I5">
-        <v>21.57</v>
+        <v>17.07</v>
       </c>
       <c r="J5">
-        <v>1.22</v>
+        <v>-0.49</v>
       </c>
       <c r="K5">
-        <v>1.06</v>
+        <v>-1.26</v>
       </c>
       <c r="L5">
-        <v>11.35</v>
+        <v>-3.23</v>
       </c>
       <c r="M5">
-        <v>12.01</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="N5">
-        <v>14.37</v>
+        <v>15.16</v>
       </c>
       <c r="O5">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="Q5">
-        <v>39400.7</v>
+        <v>38763.95</v>
       </c>
       <c r="R5">
-        <v>40096.02</v>
+        <v>39061.15</v>
       </c>
       <c r="S5">
-        <v>39518.4</v>
+        <v>39459.18</v>
       </c>
       <c r="T5">
-        <v>36431.53</v>
+        <v>37270.71</v>
       </c>
       <c r="U5">
-        <v>10.45</v>
+        <v>3.96</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
@@ -1347,46 +1453,46 @@
         <v>80</v>
       </c>
       <c r="Y5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z5">
-        <v>54.22</v>
+        <v>41.4</v>
       </c>
       <c r="AA5">
-        <v>-17.97</v>
+        <v>-207.32</v>
       </c>
       <c r="AB5">
-        <v>93.69</v>
+        <v>-192.07</v>
       </c>
       <c r="AC5">
-        <v>-111.66</v>
+        <v>-15.25</v>
       </c>
       <c r="AD5">
-        <v>39.39</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="AE5">
-        <v>22.91</v>
+        <v>70.91</v>
       </c>
       <c r="AF5">
-        <v>619.1799999999999</v>
+        <v>394.73</v>
       </c>
       <c r="AG5">
         <v>-100</v>
       </c>
       <c r="AH5">
-        <v>41429.78</v>
+        <v>39670.62</v>
       </c>
       <c r="AI5">
-        <v>38762.27</v>
+        <v>38451.69</v>
       </c>
       <c r="AJ5">
-        <v>40694.03</v>
+        <v>39538.76</v>
       </c>
       <c r="AK5" t="s">
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>21.03</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1400,10 +1506,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>49556.05</v>
+        <v>49363.6</v>
       </c>
       <c r="E6">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1412,43 +1518,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-13.22</v>
+        <v>-13.55</v>
       </c>
       <c r="I6">
-        <v>8.82</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
-        <v>2.29</v>
+        <v>-1.2</v>
       </c>
       <c r="K6">
-        <v>-2.93</v>
+        <v>0.11</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>-3.6</v>
       </c>
       <c r="M6">
-        <v>-11.19</v>
+        <v>-10.28</v>
       </c>
       <c r="N6">
-        <v>6.49</v>
+        <v>6.2</v>
       </c>
       <c r="O6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>49100.97</v>
+        <v>49415.85</v>
       </c>
       <c r="R6">
-        <v>49269.07</v>
+        <v>48988.29</v>
       </c>
       <c r="S6">
-        <v>49648.67</v>
+        <v>49065.5</v>
       </c>
       <c r="T6">
-        <v>52625.1</v>
+        <v>51383.22</v>
       </c>
       <c r="U6">
-        <v>-5.83</v>
+        <v>-3.93</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -1457,49 +1563,49 @@
         <v>0</v>
       </c>
       <c r="X6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y6">
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>52.05</v>
+        <v>52.54</v>
       </c>
       <c r="AA6">
-        <v>-287.69</v>
+        <v>77.73</v>
       </c>
       <c r="AB6">
-        <v>-364.75</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AC6">
-        <v>77.06999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="AD6">
-        <v>91.56999999999999</v>
+        <v>50.18</v>
       </c>
       <c r="AE6">
-        <v>80.64</v>
+        <v>52.56</v>
       </c>
       <c r="AF6">
-        <v>687.16</v>
+        <v>626.4400000000001</v>
       </c>
       <c r="AG6">
         <v>-100</v>
       </c>
       <c r="AH6">
-        <v>51135.78</v>
+        <v>49893.65</v>
       </c>
       <c r="AI6">
-        <v>47402.36</v>
+        <v>48082.93</v>
       </c>
       <c r="AJ6">
-        <v>50222.13</v>
+        <v>50224.74</v>
       </c>
       <c r="AK6" t="s">
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>29.12</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1513,10 +1619,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26404.95</v>
+        <v>26545.3</v>
       </c>
       <c r="E7">
-        <v>-0.14</v>
+        <v>0.3</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1525,94 +1631,94 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-7.23</v>
+        <v>-6.74</v>
       </c>
       <c r="I7">
-        <v>12.26</v>
+        <v>12.85</v>
       </c>
       <c r="J7">
-        <v>4.98</v>
+        <v>-1.63</v>
       </c>
       <c r="K7">
-        <v>4.19</v>
+        <v>-1.06</v>
       </c>
       <c r="L7">
-        <v>1.87</v>
+        <v>3.47</v>
       </c>
       <c r="M7">
-        <v>-1.65</v>
+        <v>-0.59</v>
       </c>
       <c r="N7">
-        <v>9.98</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Q7">
-        <v>25829.77</v>
+        <v>26712.68</v>
       </c>
       <c r="R7">
-        <v>25425.35</v>
+        <v>26765.5</v>
       </c>
       <c r="S7">
-        <v>25673.66</v>
+        <v>26383.59</v>
       </c>
       <c r="T7">
-        <v>26669.89</v>
+        <v>26748.48</v>
       </c>
       <c r="U7">
-        <v>-0.99</v>
+        <v>-0.76</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
       </c>
       <c r="X7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7">
-        <v>63.34</v>
+        <v>47.14</v>
       </c>
       <c r="AA7">
-        <v>68.59</v>
+        <v>42.24</v>
       </c>
       <c r="AB7">
-        <v>-91.77</v>
+        <v>97.7</v>
       </c>
       <c r="AC7">
-        <v>160.36</v>
+        <v>-55.46</v>
       </c>
       <c r="AD7">
-        <v>99.08</v>
+        <v>47.84</v>
       </c>
       <c r="AE7">
-        <v>80.13</v>
+        <v>61.38</v>
       </c>
       <c r="AF7">
-        <v>418.31</v>
+        <v>359.55</v>
       </c>
       <c r="AG7">
         <v>-100</v>
       </c>
       <c r="AH7">
-        <v>26426.27</v>
+        <v>27169.22</v>
       </c>
       <c r="AI7">
-        <v>24424.43</v>
+        <v>26361.79</v>
       </c>
       <c r="AJ7">
-        <v>25173.54</v>
+        <v>26067.59</v>
       </c>
       <c r="AK7" t="s">
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>28.6</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1626,106 +1732,106 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>28809.55</v>
+        <v>31631.45</v>
       </c>
       <c r="E8">
-        <v>0.85</v>
+        <v>0.27</v>
       </c>
       <c r="F8">
         <v>39488</v>
       </c>
       <c r="G8">
-        <v>27360.35</v>
+        <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-27.04</v>
+        <v>-19.9</v>
       </c>
       <c r="I8">
-        <v>5.3</v>
+        <v>22.75</v>
       </c>
       <c r="J8">
-        <v>1.03</v>
+        <v>-0.26</v>
       </c>
       <c r="K8">
-        <v>3.94</v>
+        <v>12.93</v>
       </c>
       <c r="L8">
-        <v>-2.84</v>
+        <v>7.85</v>
       </c>
       <c r="M8">
-        <v>-22.75</v>
+        <v>-10.85</v>
       </c>
       <c r="N8">
-        <v>0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="Q8">
-        <v>28254.88</v>
+        <v>31448.22</v>
       </c>
       <c r="R8">
-        <v>28974.12</v>
+        <v>30052.35</v>
       </c>
       <c r="S8">
-        <v>29521.09</v>
+        <v>28848.74</v>
       </c>
       <c r="T8">
-        <v>33879.45</v>
+        <v>32647.53</v>
       </c>
       <c r="U8">
-        <v>-14.96</v>
+        <v>-3.11</v>
       </c>
       <c r="V8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8">
-        <v>48.75</v>
+        <v>67.25</v>
       </c>
       <c r="AA8">
-        <v>-263.44</v>
+        <v>890.14</v>
       </c>
       <c r="AB8">
-        <v>-222.14</v>
+        <v>746.3</v>
       </c>
       <c r="AC8">
-        <v>-41.3</v>
+        <v>143.84</v>
       </c>
       <c r="AD8">
-        <v>22.05</v>
+        <v>75.12</v>
       </c>
       <c r="AE8">
-        <v>10.58</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="AF8">
-        <v>697.6</v>
+        <v>687.86</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>30390.05</v>
+        <v>32593.47</v>
       </c>
       <c r="AI8">
-        <v>27558.18</v>
+        <v>27511.23</v>
       </c>
       <c r="AJ8">
-        <v>29945.6</v>
+        <v>29687.12</v>
       </c>
       <c r="AK8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL8">
-        <v>16.1</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1739,52 +1845,79 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15990.5</v>
+        <v>16655.5</v>
       </c>
       <c r="E9">
-        <v>0.71</v>
+        <v>-0.04</v>
       </c>
       <c r="F9">
-        <v>15990.5</v>
+        <v>16662.45</v>
       </c>
       <c r="G9">
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I9">
-        <v>2.09</v>
+        <v>6.34</v>
+      </c>
+      <c r="J9">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K9">
+        <v>4.5</v>
       </c>
       <c r="N9">
-        <v>353.22</v>
+        <v>46.27</v>
+      </c>
+      <c r="Q9">
+        <v>16599.04</v>
+      </c>
+      <c r="R9">
+        <v>16173.37</v>
       </c>
       <c r="X9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y9">
         <v>0</v>
       </c>
+      <c r="Z9">
+        <v>73.02</v>
+      </c>
       <c r="AA9">
-        <v>39.33</v>
+        <v>195.91</v>
       </c>
       <c r="AB9">
-        <v>10.6</v>
+        <v>134.96</v>
       </c>
       <c r="AC9">
-        <v>28.73</v>
+        <v>60.95</v>
+      </c>
+      <c r="AD9">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="AE9">
+        <v>98.98999999999999</v>
       </c>
       <c r="AF9">
-        <v>267.71</v>
+        <v>139.01</v>
+      </c>
+      <c r="AH9">
+        <v>16769.75</v>
+      </c>
+      <c r="AI9">
+        <v>15576.99</v>
       </c>
       <c r="AJ9">
-        <v>15124.16</v>
+        <v>16247.16</v>
       </c>
       <c r="AK9" t="s">
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>100</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1798,10 +1931,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9469.950000000001</v>
+        <v>9465.85</v>
       </c>
       <c r="E10">
-        <v>0.46</v>
+        <v>-0.4</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1810,94 +1943,94 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-3.03</v>
+        <v>-3.07</v>
       </c>
       <c r="I10">
-        <v>10.62</v>
+        <v>10.57</v>
       </c>
       <c r="J10">
-        <v>3.81</v>
+        <v>-0.44</v>
       </c>
       <c r="K10">
-        <v>1.52</v>
+        <v>0.39</v>
       </c>
       <c r="L10">
-        <v>4.76</v>
+        <v>1.61</v>
       </c>
       <c r="M10">
-        <v>4.28</v>
+        <v>3.44</v>
       </c>
       <c r="N10">
-        <v>16.62</v>
+        <v>16.22</v>
       </c>
       <c r="O10">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="Q10">
-        <v>9243.91</v>
+        <v>9459.120000000001</v>
       </c>
       <c r="R10">
-        <v>9280.360000000001</v>
+        <v>9398.68</v>
       </c>
       <c r="S10">
-        <v>9260.620000000001</v>
+        <v>9366.08</v>
       </c>
       <c r="T10">
-        <v>9298.700000000001</v>
+        <v>9362.68</v>
       </c>
       <c r="U10">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="s">
         <v>79</v>
       </c>
       <c r="Y10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z10">
-        <v>60.12</v>
+        <v>55.75</v>
       </c>
       <c r="AA10">
-        <v>-4.87</v>
+        <v>25.09</v>
       </c>
       <c r="AB10">
-        <v>-20.94</v>
+        <v>15.32</v>
       </c>
       <c r="AC10">
-        <v>16.07</v>
+        <v>9.77</v>
       </c>
       <c r="AD10">
-        <v>85.41</v>
+        <v>66.14</v>
       </c>
       <c r="AE10">
-        <v>52.43</v>
+        <v>61.45</v>
       </c>
       <c r="AF10">
-        <v>128.93</v>
+        <v>86.64</v>
       </c>
       <c r="AG10">
         <v>-100</v>
       </c>
       <c r="AH10">
-        <v>9564.860000000001</v>
+        <v>9502.82</v>
       </c>
       <c r="AI10">
-        <v>8995.870000000001</v>
+        <v>9294.549999999999</v>
       </c>
       <c r="AJ10">
-        <v>9050.57</v>
+        <v>9229.360000000001</v>
       </c>
       <c r="AK10" t="s">
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>36.97</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -1911,103 +2044,103 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1505.65</v>
+        <v>1559.45</v>
       </c>
       <c r="E11">
-        <v>-0.04</v>
+        <v>0.29</v>
       </c>
       <c r="F11">
-        <v>1773.9</v>
+        <v>1671.5</v>
       </c>
       <c r="G11">
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-15.12</v>
+        <v>-6.7</v>
       </c>
       <c r="I11">
-        <v>20.13</v>
+        <v>24.42</v>
       </c>
       <c r="J11">
-        <v>2.11</v>
+        <v>-0.59</v>
       </c>
       <c r="K11">
-        <v>4.84</v>
+        <v>5.06</v>
       </c>
       <c r="L11">
-        <v>11.97</v>
+        <v>8.59</v>
       </c>
       <c r="M11">
-        <v>-11.73</v>
+        <v>-4.02</v>
       </c>
       <c r="N11">
-        <v>-4.2</v>
+        <v>-1.63</v>
       </c>
       <c r="O11">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="Q11">
-        <v>1480.98</v>
+        <v>1570.7</v>
       </c>
       <c r="R11">
-        <v>1437.88</v>
+        <v>1542.75</v>
       </c>
       <c r="S11">
-        <v>1423.43</v>
+        <v>1509.34</v>
       </c>
       <c r="T11">
-        <v>1457.29</v>
+        <v>1442.26</v>
       </c>
       <c r="U11">
-        <v>3.32</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
       </c>
       <c r="W11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="s">
         <v>79</v>
       </c>
       <c r="Y11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z11">
-        <v>62.59</v>
+        <v>55.47</v>
       </c>
       <c r="AA11">
-        <v>21.66</v>
+        <v>19.96</v>
       </c>
       <c r="AB11">
-        <v>14.48</v>
+        <v>20.16</v>
       </c>
       <c r="AC11">
-        <v>7.18</v>
+        <v>-0.2</v>
       </c>
       <c r="AD11">
-        <v>77.31999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="AE11">
-        <v>69.27</v>
+        <v>6.91</v>
       </c>
       <c r="AF11">
-        <v>34.98</v>
+        <v>32.86</v>
       </c>
       <c r="AH11">
-        <v>1525.61</v>
+        <v>1608.59</v>
       </c>
       <c r="AI11">
-        <v>1350.15</v>
+        <v>1476.91</v>
       </c>
       <c r="AJ11">
-        <v>1406.86</v>
+        <v>1508.92</v>
       </c>
       <c r="AK11" t="s">
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>33.15</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2021,58 +2154,58 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13011.4</v>
+        <v>13226.7</v>
       </c>
       <c r="E12">
-        <v>1.01</v>
+        <v>0.28</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
       </c>
       <c r="G12">
-        <v>9040.450000000001</v>
+        <v>9102.35</v>
       </c>
       <c r="H12">
-        <v>-5.15</v>
+        <v>-3.58</v>
       </c>
       <c r="I12">
-        <v>43.92</v>
+        <v>45.31</v>
       </c>
       <c r="J12">
-        <v>0.19</v>
+        <v>2.42</v>
       </c>
       <c r="K12">
-        <v>-2.17</v>
+        <v>4.24</v>
       </c>
       <c r="L12">
-        <v>10.06</v>
+        <v>2.32</v>
       </c>
       <c r="M12">
-        <v>38.32</v>
+        <v>40.71</v>
       </c>
       <c r="N12">
-        <v>20.63</v>
+        <v>18.87</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>12849.49</v>
+        <v>13169.76</v>
       </c>
       <c r="R12">
-        <v>13211.9</v>
+        <v>12691.36</v>
       </c>
       <c r="S12">
-        <v>12934.09</v>
+        <v>12786.02</v>
       </c>
       <c r="T12">
-        <v>11334.94</v>
+        <v>11872.39</v>
       </c>
       <c r="U12">
-        <v>14.79</v>
+        <v>11.41</v>
       </c>
       <c r="V12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="b">
         <v>1</v>
@@ -2081,46 +2214,46 @@
         <v>80</v>
       </c>
       <c r="Y12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z12">
-        <v>48.42</v>
+        <v>69.39</v>
       </c>
       <c r="AA12">
-        <v>-26.91</v>
+        <v>134.92</v>
       </c>
       <c r="AB12">
-        <v>54.83</v>
+        <v>41.37</v>
       </c>
       <c r="AC12">
-        <v>-81.73999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="AD12">
-        <v>19.4</v>
+        <v>83.97</v>
       </c>
       <c r="AE12">
-        <v>11.1</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AF12">
-        <v>237.74</v>
+        <v>191.77</v>
       </c>
       <c r="AG12">
         <v>-100</v>
       </c>
       <c r="AH12">
-        <v>13795.37</v>
+        <v>13318.89</v>
       </c>
       <c r="AI12">
-        <v>12628.43</v>
+        <v>12063.83</v>
       </c>
       <c r="AJ12">
-        <v>13445.62</v>
+        <v>12652.05</v>
       </c>
       <c r="AK12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL12">
-        <v>30.12</v>
+        <v>51.42</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2134,10 +2267,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>10118.15</v>
+        <v>9850.75</v>
       </c>
       <c r="E13">
-        <v>1.01</v>
+        <v>-0.72</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2146,94 +2279,94 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-6.02</v>
+        <v>-8.5</v>
       </c>
       <c r="I13">
-        <v>9.949999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="J13">
-        <v>0.75</v>
+        <v>-1.55</v>
       </c>
       <c r="K13">
-        <v>-3.51</v>
+        <v>-0.61</v>
       </c>
       <c r="L13">
-        <v>-0.19</v>
+        <v>-6.77</v>
       </c>
       <c r="M13">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="N13">
-        <v>22.6</v>
+        <v>22.81</v>
       </c>
       <c r="O13">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="Q13">
-        <v>9939.93</v>
+        <v>9919.969999999999</v>
       </c>
       <c r="R13">
-        <v>10172.08</v>
+        <v>9931.780000000001</v>
       </c>
       <c r="S13">
-        <v>10342.97</v>
+        <v>9983.530000000001</v>
       </c>
       <c r="T13">
-        <v>9992.280000000001</v>
+        <v>10050.49</v>
       </c>
       <c r="U13">
-        <v>1.26</v>
+        <v>-1.99</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
       </c>
       <c r="W13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>46.65</v>
+        <v>38.34</v>
       </c>
       <c r="AA13">
-        <v>-122.73</v>
+        <v>-25.36</v>
       </c>
       <c r="AB13">
-        <v>-110.87</v>
+        <v>-27.15</v>
       </c>
       <c r="AC13">
-        <v>-11.86</v>
+        <v>1.79</v>
       </c>
       <c r="AD13">
-        <v>58.23</v>
+        <v>28.46</v>
       </c>
       <c r="AE13">
-        <v>33.21</v>
+        <v>42.79</v>
       </c>
       <c r="AF13">
-        <v>147.63</v>
+        <v>93.72</v>
       </c>
       <c r="AG13">
         <v>-100</v>
       </c>
       <c r="AH13">
-        <v>10589.49</v>
+        <v>9988.610000000001</v>
       </c>
       <c r="AI13">
-        <v>9754.66</v>
+        <v>9874.950000000001</v>
       </c>
       <c r="AJ13">
-        <v>10274.72</v>
+        <v>10154.68</v>
       </c>
       <c r="AK13" t="s">
         <v>82</v>
       </c>
       <c r="AL13">
-        <v>45.09</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2247,106 +2380,106 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8713.1</v>
+        <v>8639.799999999999</v>
       </c>
       <c r="E14">
-        <v>1.75</v>
+        <v>-1.67</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
       </c>
       <c r="G14">
-        <v>6734.3</v>
+        <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-11.81</v>
+        <v>-12.55</v>
       </c>
       <c r="I14">
-        <v>29.38</v>
+        <v>27.88</v>
       </c>
       <c r="J14">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="K14">
-        <v>8.539999999999999</v>
+        <v>2.23</v>
       </c>
       <c r="L14">
-        <v>-1.53</v>
+        <v>5.87</v>
       </c>
       <c r="M14">
-        <v>22.71</v>
+        <v>25.07</v>
       </c>
       <c r="N14">
-        <v>29.18</v>
+        <v>29.83</v>
       </c>
       <c r="O14">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="Q14">
-        <v>8497.540000000001</v>
+        <v>8635.290000000001</v>
       </c>
       <c r="R14">
-        <v>8231.219999999999</v>
+        <v>8441.82</v>
       </c>
       <c r="S14">
-        <v>8416.5</v>
+        <v>8436.34</v>
       </c>
       <c r="T14">
-        <v>8314.4</v>
+        <v>8549.74</v>
       </c>
       <c r="U14">
-        <v>4.8</v>
+        <v>1.05</v>
       </c>
       <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
         <v>0</v>
       </c>
-      <c r="W14" t="b">
-        <v>1</v>
-      </c>
       <c r="X14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y14">
         <v>2</v>
       </c>
       <c r="Z14">
-        <v>63.22</v>
+        <v>59.5</v>
       </c>
       <c r="AA14">
-        <v>55.13</v>
+        <v>64.08</v>
       </c>
       <c r="AB14">
-        <v>-18.8</v>
+        <v>24.15</v>
       </c>
       <c r="AC14">
-        <v>73.93000000000001</v>
+        <v>39.93</v>
       </c>
       <c r="AD14">
-        <v>99.14</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="AE14">
-        <v>88.69</v>
+        <v>94.66</v>
       </c>
       <c r="AF14">
-        <v>183.92</v>
+        <v>139.56</v>
       </c>
       <c r="AG14">
         <v>-100</v>
       </c>
       <c r="AH14">
-        <v>8663.469999999999</v>
+        <v>8707.24</v>
       </c>
       <c r="AI14">
-        <v>7798.98</v>
+        <v>8176.4</v>
       </c>
       <c r="AJ14">
-        <v>8078.11</v>
+        <v>8374.41</v>
       </c>
       <c r="AK14" t="s">
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>28.93</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2360,55 +2493,55 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>24146.55</v>
+        <v>26479.55</v>
       </c>
       <c r="E15">
-        <v>-0.05</v>
+        <v>-0.23</v>
       </c>
       <c r="F15">
-        <v>24890.9</v>
+        <v>26662.8</v>
       </c>
       <c r="G15">
         <v>21402.15</v>
       </c>
       <c r="H15">
-        <v>-2.99</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I15">
-        <v>12.82</v>
+        <v>23.72</v>
       </c>
       <c r="J15">
-        <v>-0.59</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K15">
-        <v>-1.98</v>
+        <v>3.14</v>
       </c>
       <c r="L15">
-        <v>3.42</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M15">
-        <v>11.35</v>
+        <v>14.76</v>
       </c>
       <c r="N15">
-        <v>11.39</v>
+        <v>12.8</v>
       </c>
       <c r="O15">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="Q15">
-        <v>24230.43</v>
+        <v>26549.44</v>
       </c>
       <c r="R15">
-        <v>24394.72</v>
+        <v>26161.13</v>
       </c>
       <c r="S15">
-        <v>23604.57</v>
+        <v>25339.76</v>
       </c>
       <c r="T15">
-        <v>22701.84</v>
+        <v>23400.93</v>
       </c>
       <c r="U15">
-        <v>6.36</v>
+        <v>13.16</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2417,49 +2550,49 @@
         <v>1</v>
       </c>
       <c r="X15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y15">
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>50.48</v>
+        <v>64.05</v>
       </c>
       <c r="AA15">
-        <v>104.15</v>
+        <v>345.75</v>
       </c>
       <c r="AB15">
-        <v>179.06</v>
+        <v>350.89</v>
       </c>
       <c r="AC15">
-        <v>-74.91</v>
+        <v>-5.14</v>
       </c>
       <c r="AD15">
-        <v>18.22</v>
+        <v>75.06</v>
       </c>
       <c r="AE15">
-        <v>24.11</v>
+        <v>79.53</v>
       </c>
       <c r="AF15">
-        <v>336.57</v>
+        <v>322.44</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>24967.06</v>
+        <v>26888.66</v>
       </c>
       <c r="AI15">
-        <v>23822.38</v>
+        <v>25433.59</v>
       </c>
       <c r="AJ15">
-        <v>23827.01</v>
+        <v>25649.77</v>
       </c>
       <c r="AK15" t="s">
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>22.24</v>
+        <v>46.27</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2473,106 +2606,106 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>814.6</v>
+        <v>897.95</v>
       </c>
       <c r="E16">
-        <v>-0.43</v>
+        <v>1.35</v>
       </c>
       <c r="F16">
-        <v>1038.15</v>
+        <v>968.65</v>
       </c>
       <c r="G16">
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-21.53</v>
+        <v>-7.3</v>
       </c>
       <c r="I16">
-        <v>25.1</v>
+        <v>37.9</v>
       </c>
       <c r="J16">
-        <v>6.99</v>
+        <v>-1.65</v>
       </c>
       <c r="K16">
-        <v>7.71</v>
+        <v>-4.33</v>
       </c>
       <c r="L16">
-        <v>11.38</v>
+        <v>12.45</v>
       </c>
       <c r="M16">
-        <v>-21.64</v>
+        <v>-2.15</v>
       </c>
       <c r="N16">
-        <v>18.63</v>
+        <v>18.01</v>
       </c>
       <c r="O16">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="Q16">
-        <v>778.76</v>
+        <v>892.13</v>
       </c>
       <c r="R16">
-        <v>772.8200000000001</v>
+        <v>909.15</v>
       </c>
       <c r="S16">
-        <v>773.97</v>
+        <v>857.13</v>
       </c>
       <c r="T16">
-        <v>836.78</v>
+        <v>835.45</v>
       </c>
       <c r="U16">
-        <v>-2.65</v>
+        <v>7.48</v>
       </c>
       <c r="V16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="s">
         <v>79</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z16">
-        <v>62.18</v>
+        <v>52.54</v>
       </c>
       <c r="AA16">
-        <v>3.13</v>
+        <v>7.03</v>
       </c>
       <c r="AB16">
-        <v>-1.45</v>
+        <v>13.83</v>
       </c>
       <c r="AC16">
-        <v>4.58</v>
+        <v>-6.8</v>
       </c>
       <c r="AD16">
-        <v>90.39</v>
+        <v>9.48</v>
       </c>
       <c r="AE16">
-        <v>59.08</v>
+        <v>7.4</v>
       </c>
       <c r="AF16">
-        <v>20.24</v>
+        <v>19.35</v>
       </c>
       <c r="AG16">
         <v>-100</v>
       </c>
       <c r="AH16">
-        <v>810.7</v>
+        <v>933.0599999999999</v>
       </c>
       <c r="AI16">
-        <v>734.9400000000001</v>
+        <v>885.23</v>
       </c>
       <c r="AJ16">
-        <v>752.83</v>
+        <v>864.8</v>
       </c>
       <c r="AK16" t="s">
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>29.35</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2586,10 +2719,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30668.35</v>
+        <v>31310.15</v>
       </c>
       <c r="E17">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2598,94 +2731,94 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-10.07</v>
+        <v>-8.18</v>
       </c>
       <c r="I17">
-        <v>8.130000000000001</v>
+        <v>10.39</v>
       </c>
       <c r="J17">
-        <v>4.04</v>
+        <v>-1.46</v>
       </c>
       <c r="K17">
-        <v>3.25</v>
+        <v>0.45</v>
       </c>
       <c r="L17">
-        <v>0.67</v>
+        <v>4.66</v>
       </c>
       <c r="M17">
-        <v>-7.04</v>
+        <v>-4.6</v>
       </c>
       <c r="N17">
-        <v>7.18</v>
+        <v>6.43</v>
       </c>
       <c r="O17">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q17">
-        <v>30049.52</v>
+        <v>31449.63</v>
       </c>
       <c r="R17">
-        <v>29830.94</v>
+        <v>31386.66</v>
       </c>
       <c r="S17">
-        <v>30166.44</v>
+        <v>30782.22</v>
       </c>
       <c r="T17">
-        <v>32121.33</v>
+        <v>31868.41</v>
       </c>
       <c r="U17">
-        <v>-4.52</v>
+        <v>-1.75</v>
       </c>
       <c r="V17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="b">
         <v>0</v>
       </c>
       <c r="X17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17">
-        <v>62.68</v>
+        <v>52.1</v>
       </c>
       <c r="AA17">
-        <v>3.11</v>
+        <v>154.42</v>
       </c>
       <c r="AB17">
-        <v>-131.2</v>
+        <v>203.92</v>
       </c>
       <c r="AC17">
-        <v>134.31</v>
+        <v>-49.5</v>
       </c>
       <c r="AD17">
-        <v>100</v>
+        <v>14.38</v>
       </c>
       <c r="AE17">
-        <v>74.20999999999999</v>
+        <v>30.2</v>
       </c>
       <c r="AF17">
-        <v>408.6</v>
+        <v>319.94</v>
       </c>
       <c r="AG17">
         <v>-100</v>
       </c>
       <c r="AH17">
-        <v>30616.68</v>
+        <v>31740.2</v>
       </c>
       <c r="AI17">
-        <v>29045.2</v>
+        <v>31033.13</v>
       </c>
       <c r="AJ17">
-        <v>29434.93</v>
+        <v>30549.87</v>
       </c>
       <c r="AK17" t="s">
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>28.16</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2699,55 +2832,79 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15403.15</v>
+        <v>16650.95</v>
       </c>
       <c r="E18">
-        <v>-0.19</v>
+        <v>-0.35</v>
       </c>
       <c r="F18">
-        <v>15551.7</v>
+        <v>16783.35</v>
       </c>
       <c r="G18">
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-0.96</v>
+        <v>-0.79</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>8.1</v>
+      </c>
+      <c r="J18">
+        <v>-0.79</v>
+      </c>
+      <c r="K18">
+        <v>1.92</v>
       </c>
       <c r="N18">
-        <v>-50.4</v>
+        <v>52.62</v>
+      </c>
+      <c r="Q18">
+        <v>16706.68</v>
+      </c>
+      <c r="R18">
+        <v>16554.23</v>
       </c>
       <c r="X18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y18">
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>60.12</v>
       </c>
       <c r="AA18">
-        <v>-19.16</v>
+        <v>159.78</v>
       </c>
       <c r="AB18">
-        <v>-5.35</v>
+        <v>170.78</v>
       </c>
       <c r="AC18">
-        <v>-13.81</v>
+        <v>-11</v>
+      </c>
+      <c r="AD18">
+        <v>65.73999999999999</v>
+      </c>
+      <c r="AE18">
+        <v>71.36</v>
       </c>
       <c r="AF18">
-        <v>198.49</v>
+        <v>188.67</v>
+      </c>
+      <c r="AH18">
+        <v>16900.9</v>
+      </c>
+      <c r="AI18">
+        <v>16207.55</v>
       </c>
       <c r="AJ18">
-        <v>14834.12</v>
+        <v>16199.38</v>
       </c>
       <c r="AK18" t="s">
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>100</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2761,52 +2918,79 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9487.35</v>
+        <v>9635.65</v>
       </c>
       <c r="E19">
-        <v>3.91</v>
+        <v>-0.99</v>
       </c>
       <c r="F19">
-        <v>9487.35</v>
+        <v>9732.15</v>
       </c>
       <c r="G19">
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>-0.99</v>
       </c>
       <c r="I19">
-        <v>5.47</v>
+        <v>7.12</v>
+      </c>
+      <c r="J19">
+        <v>2.09</v>
+      </c>
+      <c r="K19">
+        <v>1.58</v>
       </c>
       <c r="N19">
-        <v>4791.22</v>
+        <v>53.06</v>
+      </c>
+      <c r="Q19">
+        <v>9570.030000000001</v>
+      </c>
+      <c r="R19">
+        <v>9395.76</v>
       </c>
       <c r="X19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y19">
         <v>0</v>
       </c>
+      <c r="Z19">
+        <v>60.72</v>
+      </c>
       <c r="AA19">
-        <v>47.59</v>
+        <v>63.82</v>
       </c>
       <c r="AB19">
-        <v>11.25</v>
+        <v>27.82</v>
       </c>
       <c r="AC19">
-        <v>36.34</v>
+        <v>36</v>
+      </c>
+      <c r="AD19">
+        <v>92.45</v>
+      </c>
+      <c r="AE19">
+        <v>92.76000000000001</v>
       </c>
       <c r="AF19">
-        <v>195.22</v>
+        <v>148.79</v>
+      </c>
+      <c r="AH19">
+        <v>9680.719999999999</v>
+      </c>
+      <c r="AI19">
+        <v>9110.790000000001</v>
       </c>
       <c r="AJ19">
-        <v>8752.93</v>
+        <v>9264.24</v>
       </c>
       <c r="AK19" t="s">
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>100</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2820,52 +3004,79 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11303.95</v>
+        <v>11270.45</v>
       </c>
       <c r="E20">
-        <v>0.08</v>
+        <v>-0.37</v>
       </c>
       <c r="F20">
-        <v>11303.95</v>
+        <v>11369.05</v>
       </c>
       <c r="G20">
-        <v>11012.3</v>
+        <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="I20">
-        <v>2.65</v>
+        <v>2.47</v>
+      </c>
+      <c r="J20">
+        <v>-0.77</v>
+      </c>
+      <c r="K20">
+        <v>0.83</v>
       </c>
       <c r="N20">
-        <v>574.96</v>
+        <v>15.42</v>
+      </c>
+      <c r="Q20">
+        <v>11265.86</v>
+      </c>
+      <c r="R20">
+        <v>11209.16</v>
       </c>
       <c r="X20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y20">
         <v>0</v>
       </c>
+      <c r="Z20">
+        <v>54.74</v>
+      </c>
       <c r="AA20">
-        <v>40.65</v>
+        <v>36.19</v>
       </c>
       <c r="AB20">
-        <v>11.73</v>
+        <v>25.65</v>
       </c>
       <c r="AC20">
-        <v>28.92</v>
+        <v>10.54</v>
+      </c>
+      <c r="AD20">
+        <v>67.56999999999999</v>
+      </c>
+      <c r="AE20">
+        <v>61.02</v>
       </c>
       <c r="AF20">
-        <v>284.08</v>
+        <v>135.93</v>
+      </c>
+      <c r="AH20">
+        <v>11409.37</v>
+      </c>
+      <c r="AI20">
+        <v>11008.94</v>
       </c>
       <c r="AJ20">
-        <v>10462.64</v>
+        <v>10895.17</v>
       </c>
       <c r="AK20" t="s">
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>100</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -2879,10 +3090,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27893.3</v>
+        <v>27534.3</v>
       </c>
       <c r="E21">
-        <v>-0.08</v>
+        <v>0.52</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -2891,49 +3102,49 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-4.44</v>
+        <v>-5.67</v>
       </c>
       <c r="I21">
-        <v>15.52</v>
+        <v>14.04</v>
       </c>
       <c r="J21">
-        <v>5.06</v>
+        <v>-1.82</v>
       </c>
       <c r="K21">
-        <v>6.87</v>
+        <v>-1.96</v>
       </c>
       <c r="L21">
-        <v>5.34</v>
+        <v>4.47</v>
       </c>
       <c r="M21">
-        <v>0.22</v>
+        <v>1.53</v>
       </c>
       <c r="N21">
-        <v>8.92</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="Q21">
-        <v>27417.3</v>
+        <v>27642.25</v>
       </c>
       <c r="R21">
-        <v>26579.18</v>
+        <v>28085.23</v>
       </c>
       <c r="S21">
-        <v>26483.93</v>
+        <v>27743.64</v>
       </c>
       <c r="T21">
-        <v>27460.15</v>
+        <v>27695.98</v>
       </c>
       <c r="U21">
-        <v>1.58</v>
+        <v>-0.58</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
       </c>
       <c r="W21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="s">
         <v>79</v>
@@ -2942,40 +3153,40 @@
         <v>2</v>
       </c>
       <c r="Z21">
-        <v>69.94</v>
+        <v>42.21</v>
       </c>
       <c r="AA21">
-        <v>305.27</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="AB21">
-        <v>112.44</v>
+        <v>44.07</v>
       </c>
       <c r="AC21">
-        <v>192.82</v>
+        <v>-122.37</v>
       </c>
       <c r="AD21">
-        <v>99.34999999999999</v>
+        <v>13.55</v>
       </c>
       <c r="AE21">
-        <v>98.23999999999999</v>
+        <v>19.55</v>
       </c>
       <c r="AF21">
-        <v>435.75</v>
+        <v>452.85</v>
       </c>
       <c r="AH21">
-        <v>27811.01</v>
+        <v>28935.57</v>
       </c>
       <c r="AI21">
-        <v>25347.34</v>
+        <v>27234.89</v>
       </c>
       <c r="AJ21">
-        <v>26627.32</v>
+        <v>27330.14</v>
       </c>
       <c r="AK21" t="s">
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>35.55</v>
+        <v>23.16</v>
       </c>
     </row>
   </sheetData>
@@ -3116,7 +3327,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3136,27 +3347,2423 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>86</v>
+      <c r="A6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7">
+        <v>11.14</v>
+      </c>
+      <c r="D8" s="7">
+        <v>10.27</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2.23</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.21</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="7">
+        <v>4.25</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4.19</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-0.23</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-1.26</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-0.06</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-1.06</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7">
+        <v>14.84</v>
+      </c>
+      <c r="D14" s="7">
+        <v>12.93</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="D15" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0.39</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="7">
+        <v>4.87</v>
+      </c>
+      <c r="D17" s="7">
+        <v>5.06</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="7">
+        <v>5.49</v>
+      </c>
+      <c r="D18" s="7">
+        <v>4.24</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.19</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-0.61</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="7">
+        <v>7.11</v>
+      </c>
+      <c r="D20" s="7">
+        <v>2.23</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-4.88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="7">
+        <v>3.45</v>
+      </c>
+      <c r="D21" s="7">
+        <v>3.14</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-2.32</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-4.33</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2.46</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.92</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="7">
+        <v>4.54</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1.58</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2.53</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-1.33</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-1.96</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="7">
+        <v>3.14</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="7">
+        <v>1.32</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.96</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-0.24</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-0.49</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.64</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-1.2</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-0.48</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-1.63</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="7">
+        <v>2.73</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-0.26</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="7">
+        <v>2.04</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="7">
+        <v>1.01</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-0.44</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-3.93</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-0.59</v>
+      </c>
+      <c r="E37" s="9">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="7">
+        <v>3.7</v>
+      </c>
+      <c r="D38" s="7">
+        <v>2.42</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-0.2</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-1.55</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="7">
+        <v>5.01</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-1.72</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-1.65</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-0.01</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-1.46</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-0.28</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-0.79</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="7">
+        <v>4.3</v>
+      </c>
+      <c r="D45" s="7">
+        <v>2.09</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.57</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-0.77</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-0.47</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-1.82</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="7">
+        <v>24.11</v>
+      </c>
+      <c r="D48" s="7">
+        <v>24.74</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="7">
+        <v>13.13</v>
+      </c>
+      <c r="D49" s="7">
+        <v>13.18</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="7">
+        <v>4.46</v>
+      </c>
+      <c r="D50" s="7">
+        <v>4.52</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="7">
+        <v>9.43</v>
+      </c>
+      <c r="D51" s="7">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-9.94</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-10.28</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-0.88</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-0.59</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-10.81</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-10.85</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="7">
+        <v>4.38</v>
+      </c>
+      <c r="D55" s="7">
+        <v>3.44</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="7">
+        <v>-5.05</v>
+      </c>
+      <c r="D56" s="7">
+        <v>-4.02</v>
+      </c>
+      <c r="E56" s="9">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="7">
+        <v>40.17</v>
+      </c>
+      <c r="D57" s="7">
+        <v>40.71</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="7">
+        <v>1.46</v>
+      </c>
+      <c r="D58" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="7">
+        <v>26.36</v>
+      </c>
+      <c r="D59" s="7">
+        <v>25.07</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="7">
+        <v>15.04</v>
+      </c>
+      <c r="D60" s="7">
+        <v>14.76</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-4.38</v>
+      </c>
+      <c r="D61" s="7">
+        <v>-2.15</v>
+      </c>
+      <c r="E61" s="9">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-4.65</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-4.6</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="D63" s="7">
+        <v>1.53</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="7">
+        <v>8.76</v>
+      </c>
+      <c r="D64" s="7">
+        <v>10.72</v>
+      </c>
+      <c r="E64" s="9">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-3.42</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-2.18</v>
+      </c>
+      <c r="E65" s="9">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="7">
+        <v>4.8</v>
+      </c>
+      <c r="D66" s="7">
+        <v>6.96</v>
+      </c>
+      <c r="E66" s="9">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="7">
+        <v>-5.02</v>
+      </c>
+      <c r="D67" s="7">
+        <v>-3.23</v>
+      </c>
+      <c r="E67" s="9">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="7">
+        <v>-3.38</v>
+      </c>
+      <c r="D68" s="7">
+        <v>-3.6</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="D69" s="7">
+        <v>3.47</v>
+      </c>
+      <c r="E69" s="9">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="7">
+        <v>7.33</v>
+      </c>
+      <c r="D70" s="7">
+        <v>7.85</v>
+      </c>
+      <c r="E70" s="9">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D71" s="7">
+        <v>1.61</v>
+      </c>
+      <c r="E71" s="9">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="7">
+        <v>5.58</v>
+      </c>
+      <c r="D72" s="7">
+        <v>8.59</v>
+      </c>
+      <c r="E72" s="9">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="7">
+        <v>1.06</v>
+      </c>
+      <c r="D73" s="7">
+        <v>2.32</v>
+      </c>
+      <c r="E73" s="9">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-7.36</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-6.77</v>
+      </c>
+      <c r="E74" s="9">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="7">
+        <v>4.95</v>
+      </c>
+      <c r="D75" s="7">
+        <v>5.87</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="7">
+        <v>10.08</v>
+      </c>
+      <c r="D76" s="7">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="7">
+        <v>7.57</v>
+      </c>
+      <c r="D77" s="7">
+        <v>12.45</v>
+      </c>
+      <c r="E77" s="9">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="7">
+        <v>2.94</v>
+      </c>
+      <c r="D78" s="7">
+        <v>4.66</v>
+      </c>
+      <c r="E78" s="9">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="7">
+        <v>3.13</v>
+      </c>
+      <c r="D79" s="7">
+        <v>4.47</v>
+      </c>
+      <c r="E79" s="9">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="7">
+        <v>0</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-0.09</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-4.87</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-4.68</v>
+      </c>
+      <c r="E81" s="9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-3.49</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-3.24</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="7">
+        <v>-13.43</v>
+      </c>
+      <c r="D83" s="7">
+        <v>-13.55</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="7">
+        <v>-7.02</v>
+      </c>
+      <c r="D84" s="7">
+        <v>-6.74</v>
+      </c>
+      <c r="E84" s="9">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="7">
+        <v>-20.11</v>
+      </c>
+      <c r="D85" s="7">
+        <v>-19.9</v>
+      </c>
+      <c r="E85" s="9">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="7">
+        <v>0</v>
+      </c>
+      <c r="D86" s="7">
+        <v>-0.04</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="7">
+        <v>-2.68</v>
+      </c>
+      <c r="D87" s="7">
+        <v>-3.07</v>
+      </c>
+      <c r="E87" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="7">
+        <v>-6.97</v>
+      </c>
+      <c r="D88" s="7">
+        <v>-6.7</v>
+      </c>
+      <c r="E88" s="9">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="7">
+        <v>-3.85</v>
+      </c>
+      <c r="D89" s="7">
+        <v>-3.58</v>
+      </c>
+      <c r="E89" s="9">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="7">
+        <v>-7.84</v>
+      </c>
+      <c r="D90" s="7">
+        <v>-8.5</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="7">
+        <v>-11.07</v>
+      </c>
+      <c r="D91" s="7">
+        <v>-12.55</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="7">
+        <v>-0.45</v>
+      </c>
+      <c r="D92" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="7">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="D93" s="7">
+        <v>-7.3</v>
+      </c>
+      <c r="E93" s="9">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="7">
+        <v>-8.32</v>
+      </c>
+      <c r="D94" s="7">
+        <v>-8.18</v>
+      </c>
+      <c r="E94" s="9">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="7">
+        <v>-0.44</v>
+      </c>
+      <c r="D95" s="7">
+        <v>-0.79</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="7">
+        <v>0</v>
+      </c>
+      <c r="D96" s="7">
+        <v>-0.99</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="7">
+        <v>-0.5</v>
+      </c>
+      <c r="D97" s="7">
+        <v>-0.87</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="7">
+        <v>-6.15</v>
+      </c>
+      <c r="D98" s="7">
+        <v>-5.67</v>
+      </c>
+      <c r="E98" s="9">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="7">
+        <v>29647.9</v>
+      </c>
+      <c r="D99" s="7">
+        <v>29620.05</v>
+      </c>
+      <c r="E99" s="8">
+        <v>-27.85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="7">
+        <v>9991.65</v>
+      </c>
+      <c r="D100" s="7">
+        <v>10011.4</v>
+      </c>
+      <c r="E100" s="9">
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="7">
+        <v>12197.35</v>
+      </c>
+      <c r="D101" s="7">
+        <v>12229.45</v>
+      </c>
+      <c r="E101" s="9">
+        <v>32.1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="7">
+        <v>38749.85</v>
+      </c>
+      <c r="D102" s="7">
+        <v>38748.15</v>
+      </c>
+      <c r="E102" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="7">
+        <v>49435.2</v>
+      </c>
+      <c r="D103" s="7">
+        <v>49363.6</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-71.59999999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="7">
+        <v>26466</v>
+      </c>
+      <c r="D104" s="7">
+        <v>26545.3</v>
+      </c>
+      <c r="E104" s="9">
+        <v>79.3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="7">
+        <v>31547.7</v>
+      </c>
+      <c r="D105" s="7">
+        <v>31631.45</v>
+      </c>
+      <c r="E105" s="9">
+        <v>83.75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="7">
+        <v>16662.45</v>
+      </c>
+      <c r="D106" s="7">
+        <v>16655.5</v>
+      </c>
+      <c r="E106" s="8">
+        <v>-6.95</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="7">
+        <v>9504.15</v>
+      </c>
+      <c r="D107" s="7">
+        <v>9465.85</v>
+      </c>
+      <c r="E107" s="8">
+        <v>-38.3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="7">
+        <v>1555</v>
+      </c>
+      <c r="D108" s="7">
+        <v>1559.45</v>
+      </c>
+      <c r="E108" s="9">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" s="7">
+        <v>13189.85</v>
+      </c>
+      <c r="D109" s="7">
+        <v>13226.7</v>
+      </c>
+      <c r="E109" s="9">
+        <v>36.85</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="7">
+        <v>9922.35</v>
+      </c>
+      <c r="D110" s="7">
+        <v>9850.75</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-71.59999999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="7">
+        <v>8786.200000000001</v>
+      </c>
+      <c r="D111" s="7">
+        <v>8639.799999999999</v>
+      </c>
+      <c r="E111" s="8">
+        <v>-146.4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" s="7">
+        <v>26541.8</v>
+      </c>
+      <c r="D112" s="7">
+        <v>26479.55</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-62.25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="7">
+        <v>885.95</v>
+      </c>
+      <c r="D113" s="7">
+        <v>897.95</v>
+      </c>
+      <c r="E113" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="7">
+        <v>31265.2</v>
+      </c>
+      <c r="D114" s="7">
+        <v>31310.15</v>
+      </c>
+      <c r="E114" s="9">
+        <v>44.95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" s="7">
+        <v>16708.9</v>
+      </c>
+      <c r="D115" s="7">
+        <v>16650.95</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-57.95</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" s="7">
+        <v>9732.15</v>
+      </c>
+      <c r="D116" s="7">
+        <v>9635.65</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-96.5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="7">
+        <v>11312.2</v>
+      </c>
+      <c r="D117" s="7">
+        <v>11270.45</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-41.75</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="7">
+        <v>27392.35</v>
+      </c>
+      <c r="D118" s="7">
+        <v>27534.3</v>
+      </c>
+      <c r="E118" s="9">
+        <v>141.95</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119" s="7">
+        <v>56</v>
+      </c>
+      <c r="D119" s="7">
+        <v>50</v>
+      </c>
+      <c r="E119" s="8">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120" s="7">
+        <v>50</v>
+      </c>
+      <c r="D120" s="7">
+        <v>32</v>
+      </c>
+      <c r="E120" s="8">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" s="7">
+        <v>62</v>
+      </c>
+      <c r="D121" s="7">
+        <v>44</v>
+      </c>
+      <c r="E121" s="8">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="7">
+        <v>38</v>
+      </c>
+      <c r="D122" s="7">
+        <v>56</v>
+      </c>
+      <c r="E122" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123" s="7">
+        <v>32</v>
+      </c>
+      <c r="D123" s="7">
+        <v>62</v>
+      </c>
+      <c r="E123" s="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" s="7">
+        <v>44</v>
+      </c>
+      <c r="D124" s="7">
+        <v>38</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C125" s="7">
+        <v>76.81</v>
+      </c>
+      <c r="D125" s="7">
+        <v>76.2</v>
+      </c>
+      <c r="E125" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C126" s="7">
+        <v>58.1</v>
+      </c>
+      <c r="D126" s="7">
+        <v>59.57</v>
+      </c>
+      <c r="E126" s="9">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C127" s="7">
+        <v>72.45</v>
+      </c>
+      <c r="D127" s="7">
+        <v>73.58</v>
+      </c>
+      <c r="E127" s="9">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C128" s="7">
+        <v>41.43</v>
+      </c>
+      <c r="D128" s="7">
+        <v>41.4</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C129" s="7">
+        <v>53.68</v>
+      </c>
+      <c r="D129" s="7">
+        <v>52.54</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C130" s="7">
+        <v>45.27</v>
+      </c>
+      <c r="D130" s="7">
+        <v>47.14</v>
+      </c>
+      <c r="E130" s="9">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C131" s="7">
+        <v>66.73</v>
+      </c>
+      <c r="D131" s="7">
+        <v>67.25</v>
+      </c>
+      <c r="E131" s="9">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C132" s="7">
+        <v>73.48999999999999</v>
+      </c>
+      <c r="D132" s="7">
+        <v>73.02</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C133" s="7">
+        <v>60.04</v>
+      </c>
+      <c r="D133" s="7">
+        <v>55.75</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C134" s="7">
+        <v>54.56</v>
+      </c>
+      <c r="D134" s="7">
+        <v>55.47</v>
+      </c>
+      <c r="E134" s="9">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C135" s="7">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="D135" s="7">
+        <v>69.39</v>
+      </c>
+      <c r="E135" s="9">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C136" s="7">
+        <v>45.08</v>
+      </c>
+      <c r="D136" s="7">
+        <v>38.34</v>
+      </c>
+      <c r="E136" s="8">
+        <v>-6.74</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C137" s="7">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="D137" s="7">
+        <v>59.5</v>
+      </c>
+      <c r="E137" s="8">
+        <v>-10.85</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C138" s="7">
+        <v>66.27</v>
+      </c>
+      <c r="D138" s="7">
+        <v>64.05</v>
+      </c>
+      <c r="E138" s="8">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C139" s="7">
+        <v>47.45</v>
+      </c>
+      <c r="D139" s="7">
+        <v>52.54</v>
+      </c>
+      <c r="E139" s="9">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C140" s="7">
+        <v>50.94</v>
+      </c>
+      <c r="D140" s="7">
+        <v>52.1</v>
+      </c>
+      <c r="E140" s="9">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141" s="7">
+        <v>63.88</v>
+      </c>
+      <c r="D141" s="7">
+        <v>60.12</v>
+      </c>
+      <c r="E141" s="8">
+        <v>-3.76</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C142" s="7">
+        <v>66.54000000000001</v>
+      </c>
+      <c r="D142" s="7">
+        <v>60.72</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-5.82</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C143" s="7">
+        <v>57.62</v>
+      </c>
+      <c r="D143" s="7">
+        <v>54.74</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C144" s="7">
+        <v>38.86</v>
+      </c>
+      <c r="D144" s="7">
+        <v>42.21</v>
+      </c>
+      <c r="E144" s="9">
+        <v>3.35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3176,61 +5783,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>94</v>
+      <c r="B1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="6">
-        <v>47.24</v>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="12">
+        <v>51.24</v>
+      </c>
+      <c r="C2" s="13">
         <v>20</v>
       </c>
-      <c r="D2" s="6">
-        <v>53.6</v>
-      </c>
-      <c r="E2" s="6">
-        <v>40</v>
-      </c>
-      <c r="F2" s="6">
-        <v>2.1</v>
-      </c>
-      <c r="G2" s="6">
-        <v>4.4</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="D2" s="12">
+        <v>57.8</v>
+      </c>
+      <c r="E2" s="12">
+        <v>50</v>
+      </c>
+      <c r="F2" s="12">
+        <v>2.2</v>
+      </c>
+      <c r="G2" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="H2" s="12">
         <v>53.1</v>
       </c>
-      <c r="I2" s="6">
-        <v>20</v>
+      <c r="I2" s="12">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3331,131 +5938,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="15">
+        <v>0.5306000000000001</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.5262</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.4627000000000001</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2983</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.2387</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.2281</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.1887</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0.1801</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0.1622</v>
+      </c>
+      <c r="J2" s="15">
+        <v>0.1542</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="14" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="9">
-        <v>47.91220000000001</v>
-      </c>
-      <c r="B2" s="9">
-        <v>5.7496</v>
-      </c>
-      <c r="C2" s="9">
-        <v>3.5322</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.2918</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.226</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.2063</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0.2049</v>
-      </c>
-      <c r="H2" s="9">
-        <v>0.1863</v>
-      </c>
-      <c r="I2" s="9">
-        <v>0.1662</v>
-      </c>
-      <c r="J2" s="9">
-        <v>0.1437</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="8" t="s">
+      <c r="B3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="8" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="9">
-        <v>0.1415</v>
-      </c>
-      <c r="B4" s="9">
-        <v>0.1284</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0.1139</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0.0998</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.0892</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.0718</v>
-      </c>
-      <c r="G4" s="9">
-        <v>0.0649</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0.0014</v>
-      </c>
-      <c r="I4" s="9">
-        <v>-0.042</v>
-      </c>
-      <c r="J4" s="9">
-        <v>-0.504</v>
+      <c r="A4" s="15">
+        <v>0.1516</v>
+      </c>
+      <c r="B4" s="15">
+        <v>0.1365</v>
+      </c>
+      <c r="C4" s="15">
+        <v>0.1343</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0.128</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0.09</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.08</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.0643</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0.062</v>
+      </c>
+      <c r="I4" s="15">
+        <v>-0.0005</v>
+      </c>
+      <c r="J4" s="15">
+        <v>-0.0163</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="123">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,34 +289,67 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>73.6 → 66.6</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>73.6</t>
+  </si>
+  <si>
+    <t>66.6</t>
+  </si>
+  <si>
+    <t>73.0 → 69.8</t>
+  </si>
+  <si>
+    <t>73.0</t>
+  </si>
+  <si>
+    <t>69.8</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.5 → 52.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.5</t>
+    <t>52.5 → 44.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>52.5</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>70.3 → 59.5</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>70.3</t>
-  </si>
-  <si>
-    <t>59.5</t>
+    <t>44.4</t>
+  </si>
+  <si>
+    <t>55.8 → 47.9</t>
+  </si>
+  <si>
+    <t>55.8</t>
+  </si>
+  <si>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>52.5 → 48.8</t>
+  </si>
+  <si>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>52.1 → 49.7</t>
+  </si>
+  <si>
+    <t>52.1</t>
+  </si>
+  <si>
+    <t>49.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -402,13 +435,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -417,6 +443,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -449,12 +482,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -462,6 +489,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,8 +575,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1060,10 +1093,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>29620.05</v>
+        <v>29458.55</v>
       </c>
       <c r="E2">
-        <v>-0.09</v>
+        <v>-0.55</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1072,43 +1105,43 @@
         <v>23410.95</v>
       </c>
       <c r="H2">
-        <v>-0.09</v>
+        <v>-0.64</v>
       </c>
       <c r="I2">
-        <v>26.52</v>
+        <v>25.83</v>
       </c>
       <c r="J2">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="K2">
-        <v>10.27</v>
+        <v>9.18</v>
       </c>
       <c r="L2">
-        <v>10.72</v>
+        <v>12.68</v>
       </c>
       <c r="M2">
-        <v>24.74</v>
+        <v>24.53</v>
       </c>
       <c r="N2">
-        <v>23.87</v>
+        <v>23.78</v>
       </c>
       <c r="O2">
         <v>93</v>
       </c>
       <c r="Q2">
-        <v>29366.84</v>
+        <v>29450.29</v>
       </c>
       <c r="R2">
-        <v>27844.22</v>
+        <v>27989.77</v>
       </c>
       <c r="S2">
-        <v>27061.91</v>
+        <v>27133.24</v>
       </c>
       <c r="T2">
-        <v>26955.61</v>
+        <v>26967.66</v>
       </c>
       <c r="U2">
-        <v>9.880000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -1123,34 +1156,34 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>76.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="AA2">
-        <v>728.61</v>
+        <v>736.88</v>
       </c>
       <c r="AB2">
-        <v>520.5700000000001</v>
+        <v>563.83</v>
       </c>
       <c r="AC2">
-        <v>208.04</v>
+        <v>173.05</v>
       </c>
       <c r="AD2">
-        <v>78.56</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="AE2">
-        <v>82.38</v>
+        <v>80.06</v>
       </c>
       <c r="AF2">
-        <v>448.79</v>
+        <v>437.5</v>
       </c>
       <c r="AG2">
         <v>-100</v>
       </c>
       <c r="AH2">
-        <v>30088.64</v>
+        <v>30257.56</v>
       </c>
       <c r="AI2">
-        <v>25599.79</v>
+        <v>25721.98</v>
       </c>
       <c r="AJ2">
         <v>28374.42</v>
@@ -1159,7 +1192,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>61.95</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1173,10 +1206,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>10011.4</v>
+        <v>9927.25</v>
       </c>
       <c r="E3">
-        <v>0.2</v>
+        <v>-0.84</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1185,43 +1218,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-4.68</v>
+        <v>-5.48</v>
       </c>
       <c r="I3">
-        <v>16.79</v>
+        <v>15.81</v>
       </c>
       <c r="J3">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="K3">
-        <v>1.21</v>
+        <v>0.87</v>
       </c>
       <c r="L3">
-        <v>-2.18</v>
+        <v>-1.8</v>
       </c>
       <c r="M3">
-        <v>13.18</v>
+        <v>13.52</v>
       </c>
       <c r="N3">
-        <v>13.65</v>
+        <v>13.14</v>
       </c>
       <c r="O3">
         <v>68</v>
       </c>
       <c r="Q3">
-        <v>9978.559999999999</v>
+        <v>9978.26</v>
       </c>
       <c r="R3">
-        <v>9878.860000000001</v>
+        <v>9882.139999999999</v>
       </c>
       <c r="S3">
-        <v>9925.950000000001</v>
+        <v>9919.65</v>
       </c>
       <c r="T3">
-        <v>9699.129999999999</v>
+        <v>9702.709999999999</v>
       </c>
       <c r="U3">
-        <v>3.22</v>
+        <v>2.31</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -1236,31 +1269,31 @@
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>59.57</v>
+        <v>51.32</v>
       </c>
       <c r="AA3">
-        <v>21.11</v>
+        <v>19.17</v>
       </c>
       <c r="AB3">
-        <v>-3.66</v>
+        <v>0.9</v>
       </c>
       <c r="AC3">
-        <v>24.77</v>
+        <v>18.27</v>
       </c>
       <c r="AD3">
-        <v>72.95</v>
+        <v>65.73</v>
       </c>
       <c r="AE3">
-        <v>71.66</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="AF3">
-        <v>85.37</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="AH3">
-        <v>10023.77</v>
+        <v>10028.37</v>
       </c>
       <c r="AI3">
-        <v>9733.959999999999</v>
+        <v>9735.91</v>
       </c>
       <c r="AJ3">
         <v>10073.2</v>
@@ -1269,7 +1302,7 @@
         <v>82</v>
       </c>
       <c r="AL3">
-        <v>33.54</v>
+        <v>31.34</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1283,10 +1316,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>12229.45</v>
+        <v>12152.9</v>
       </c>
       <c r="E4">
-        <v>0.26</v>
+        <v>-0.63</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1295,43 +1328,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-3.24</v>
+        <v>-3.85</v>
       </c>
       <c r="I4">
-        <v>18.34</v>
+        <v>17.6</v>
       </c>
       <c r="J4">
-        <v>-0.24</v>
+        <v>-0.46</v>
       </c>
       <c r="K4">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="L4">
-        <v>6.96</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M4">
-        <v>4.52</v>
+        <v>3.52</v>
       </c>
       <c r="N4">
-        <v>13.43</v>
+        <v>13.37</v>
       </c>
       <c r="O4">
         <v>74</v>
       </c>
       <c r="Q4">
-        <v>12206.09</v>
+        <v>12194.81</v>
       </c>
       <c r="R4">
-        <v>11885.33</v>
+        <v>11912.41</v>
       </c>
       <c r="S4">
-        <v>11635</v>
+        <v>11656.38</v>
       </c>
       <c r="T4">
-        <v>11720.48</v>
+        <v>11718.82</v>
       </c>
       <c r="U4">
-        <v>4.34</v>
+        <v>3.7</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -1346,31 +1379,31 @@
         <v>2</v>
       </c>
       <c r="Z4">
-        <v>73.58</v>
+        <v>66.58</v>
       </c>
       <c r="AA4">
-        <v>167.63</v>
+        <v>162.38</v>
       </c>
       <c r="AB4">
-        <v>134.92</v>
+        <v>140.42</v>
       </c>
       <c r="AC4">
-        <v>32.71</v>
+        <v>21.97</v>
       </c>
       <c r="AD4">
-        <v>67.76000000000001</v>
+        <v>60.75</v>
       </c>
       <c r="AE4">
-        <v>71.92</v>
+        <v>66.64</v>
       </c>
       <c r="AF4">
-        <v>114.17</v>
+        <v>112.33</v>
       </c>
       <c r="AH4">
-        <v>12391.13</v>
+        <v>12414.42</v>
       </c>
       <c r="AI4">
-        <v>11379.53</v>
+        <v>11410.39</v>
       </c>
       <c r="AJ4">
         <v>11869.84</v>
@@ -1379,7 +1412,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>54.11</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1393,10 +1426,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38748.15</v>
+        <v>38707.75</v>
       </c>
       <c r="E5">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1405,43 +1438,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-6.71</v>
+        <v>-6.81</v>
       </c>
       <c r="I5">
-        <v>17.07</v>
+        <v>16.95</v>
       </c>
       <c r="J5">
-        <v>-0.49</v>
+        <v>-0.28</v>
       </c>
       <c r="K5">
-        <v>-1.26</v>
+        <v>-1.31</v>
       </c>
       <c r="L5">
-        <v>-3.23</v>
+        <v>-2.11</v>
       </c>
       <c r="M5">
-        <v>9.390000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="N5">
-        <v>15.16</v>
+        <v>14.82</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Q5">
-        <v>38763.95</v>
+        <v>38742.17</v>
       </c>
       <c r="R5">
-        <v>39061.15</v>
+        <v>39036.38</v>
       </c>
       <c r="S5">
-        <v>39459.18</v>
+        <v>39428.27</v>
       </c>
       <c r="T5">
-        <v>37270.71</v>
+        <v>37286.91</v>
       </c>
       <c r="U5">
-        <v>3.96</v>
+        <v>3.81</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1456,34 +1489,34 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>41.4</v>
+        <v>40.61</v>
       </c>
       <c r="AA5">
-        <v>-207.32</v>
+        <v>-206.24</v>
       </c>
       <c r="AB5">
-        <v>-192.07</v>
+        <v>-194.91</v>
       </c>
       <c r="AC5">
-        <v>-15.25</v>
+        <v>-11.33</v>
       </c>
       <c r="AD5">
-        <v>70.15000000000001</v>
+        <v>72.19</v>
       </c>
       <c r="AE5">
-        <v>70.91</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="AF5">
-        <v>394.73</v>
+        <v>386.31</v>
       </c>
       <c r="AG5">
         <v>-100</v>
       </c>
       <c r="AH5">
-        <v>39670.62</v>
+        <v>39661.61</v>
       </c>
       <c r="AI5">
-        <v>38451.69</v>
+        <v>38411.15</v>
       </c>
       <c r="AJ5">
         <v>39538.76</v>
@@ -1492,7 +1525,7 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>13.21</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1506,10 +1539,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>49363.6</v>
+        <v>48787.85</v>
       </c>
       <c r="E6">
-        <v>-0.14</v>
+        <v>-1.17</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1518,43 +1551,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-13.55</v>
+        <v>-14.56</v>
       </c>
       <c r="I6">
-        <v>8.4</v>
+        <v>7.14</v>
       </c>
       <c r="J6">
-        <v>-1.2</v>
+        <v>-1.49</v>
       </c>
       <c r="K6">
-        <v>0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="L6">
-        <v>-3.6</v>
+        <v>-3.3</v>
       </c>
       <c r="M6">
-        <v>-10.28</v>
+        <v>-12.59</v>
       </c>
       <c r="N6">
-        <v>6.2</v>
+        <v>6.02</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>49415.85</v>
+        <v>49268</v>
       </c>
       <c r="R6">
-        <v>48988.29</v>
+        <v>49001.44</v>
       </c>
       <c r="S6">
-        <v>49065.5</v>
+        <v>49076.3</v>
       </c>
       <c r="T6">
-        <v>51383.22</v>
+        <v>51347.89</v>
       </c>
       <c r="U6">
-        <v>-3.93</v>
+        <v>-4.99</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -1569,34 +1602,34 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>52.54</v>
+        <v>44.39</v>
       </c>
       <c r="AA6">
-        <v>77.73</v>
+        <v>32.57</v>
       </c>
       <c r="AB6">
-        <v>8.359999999999999</v>
+        <v>13.21</v>
       </c>
       <c r="AC6">
-        <v>69.37</v>
+        <v>19.37</v>
       </c>
       <c r="AD6">
-        <v>50.18</v>
+        <v>33.85</v>
       </c>
       <c r="AE6">
-        <v>52.56</v>
+        <v>45.04</v>
       </c>
       <c r="AF6">
-        <v>626.4400000000001</v>
+        <v>626.3099999999999</v>
       </c>
       <c r="AG6">
         <v>-100</v>
       </c>
       <c r="AH6">
-        <v>49893.65</v>
+        <v>49885.86</v>
       </c>
       <c r="AI6">
-        <v>48082.93</v>
+        <v>48117.01</v>
       </c>
       <c r="AJ6">
         <v>50224.74</v>
@@ -1605,7 +1638,7 @@
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>24.95</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1619,10 +1652,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26545.3</v>
+        <v>26432.4</v>
       </c>
       <c r="E7">
-        <v>0.3</v>
+        <v>-0.43</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1631,43 +1664,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-6.74</v>
+        <v>-7.13</v>
       </c>
       <c r="I7">
-        <v>12.85</v>
+        <v>12.37</v>
       </c>
       <c r="J7">
-        <v>-1.63</v>
+        <v>-1.54</v>
       </c>
       <c r="K7">
-        <v>-1.06</v>
+        <v>-1.5</v>
       </c>
       <c r="L7">
-        <v>3.47</v>
+        <v>5.15</v>
       </c>
       <c r="M7">
-        <v>-0.59</v>
+        <v>-0.82</v>
       </c>
       <c r="N7">
-        <v>9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="O7">
         <v>26</v>
       </c>
       <c r="Q7">
-        <v>26712.68</v>
+        <v>26630.22</v>
       </c>
       <c r="R7">
-        <v>26765.5</v>
+        <v>26760.29</v>
       </c>
       <c r="S7">
-        <v>26383.59</v>
+        <v>26412.07</v>
       </c>
       <c r="T7">
-        <v>26748.48</v>
+        <v>26743.73</v>
       </c>
       <c r="U7">
-        <v>-0.76</v>
+        <v>-1.16</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
@@ -1682,34 +1715,34 @@
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>47.14</v>
+        <v>44.8</v>
       </c>
       <c r="AA7">
-        <v>42.24</v>
+        <v>16.32</v>
       </c>
       <c r="AB7">
-        <v>97.7</v>
+        <v>81.42</v>
       </c>
       <c r="AC7">
-        <v>-55.46</v>
+        <v>-65.11</v>
       </c>
       <c r="AD7">
-        <v>47.84</v>
+        <v>30.32</v>
       </c>
       <c r="AE7">
-        <v>61.38</v>
+        <v>46.12</v>
       </c>
       <c r="AF7">
-        <v>359.55</v>
+        <v>349.63</v>
       </c>
       <c r="AG7">
         <v>-100</v>
       </c>
       <c r="AH7">
-        <v>27169.22</v>
+        <v>27178.87</v>
       </c>
       <c r="AI7">
-        <v>26361.79</v>
+        <v>26341.71</v>
       </c>
       <c r="AJ7">
         <v>26067.59</v>
@@ -1718,7 +1751,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>19.54</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1732,10 +1765,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31631.45</v>
+        <v>31823.15</v>
       </c>
       <c r="E8">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1744,43 +1777,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-19.9</v>
+        <v>-19.41</v>
       </c>
       <c r="I8">
-        <v>22.75</v>
+        <v>23.49</v>
       </c>
       <c r="J8">
-        <v>-0.26</v>
+        <v>1.17</v>
       </c>
       <c r="K8">
-        <v>12.93</v>
+        <v>9.68</v>
       </c>
       <c r="L8">
-        <v>7.85</v>
+        <v>12.71</v>
       </c>
       <c r="M8">
-        <v>-10.85</v>
+        <v>-9.85</v>
       </c>
       <c r="N8">
-        <v>-0.05</v>
+        <v>0.1</v>
       </c>
       <c r="O8">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q8">
-        <v>31448.22</v>
+        <v>31522.02</v>
       </c>
       <c r="R8">
-        <v>30052.35</v>
+        <v>30207.27</v>
       </c>
       <c r="S8">
-        <v>28848.74</v>
+        <v>28888.11</v>
       </c>
       <c r="T8">
-        <v>32647.53</v>
+        <v>32628.99</v>
       </c>
       <c r="U8">
-        <v>-3.11</v>
+        <v>-2.47</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -1795,43 +1828,43 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>67.25</v>
+        <v>68.47</v>
       </c>
       <c r="AA8">
-        <v>890.14</v>
+        <v>901.45</v>
       </c>
       <c r="AB8">
-        <v>746.3</v>
+        <v>777.33</v>
       </c>
       <c r="AC8">
-        <v>143.84</v>
+        <v>124.12</v>
       </c>
       <c r="AD8">
-        <v>75.12</v>
+        <v>82.19</v>
       </c>
       <c r="AE8">
-        <v>75.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="AF8">
-        <v>687.86</v>
+        <v>661.77</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32593.47</v>
+        <v>32785.13</v>
       </c>
       <c r="AI8">
-        <v>27511.23</v>
+        <v>27629.41</v>
       </c>
       <c r="AJ8">
-        <v>29687.12</v>
+        <v>29811.25</v>
       </c>
       <c r="AK8" t="s">
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>31.99</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1845,10 +1878,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16655.5</v>
+        <v>16608.9</v>
       </c>
       <c r="E9">
-        <v>-0.04</v>
+        <v>-0.28</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1857,25 +1890,25 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="I9">
-        <v>6.34</v>
+        <v>6.04</v>
       </c>
       <c r="J9">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="K9">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="N9">
-        <v>46.27</v>
+        <v>42.89</v>
       </c>
       <c r="Q9">
-        <v>16599.04</v>
+        <v>16621.61</v>
       </c>
       <c r="R9">
-        <v>16173.37</v>
+        <v>16211.29</v>
       </c>
       <c r="X9" t="s">
         <v>80</v>
@@ -1884,31 +1917,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>73.02</v>
+        <v>69.8</v>
       </c>
       <c r="AA9">
-        <v>195.91</v>
+        <v>198.37</v>
       </c>
       <c r="AB9">
-        <v>134.96</v>
+        <v>147.64</v>
       </c>
       <c r="AC9">
-        <v>60.95</v>
+        <v>50.73</v>
       </c>
       <c r="AD9">
-        <v>99.26000000000001</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="AE9">
-        <v>98.98999999999999</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="AF9">
-        <v>139.01</v>
+        <v>136.48</v>
       </c>
       <c r="AH9">
-        <v>16769.75</v>
+        <v>16817.58</v>
       </c>
       <c r="AI9">
-        <v>15576.99</v>
+        <v>15605</v>
       </c>
       <c r="AJ9">
         <v>16247.16</v>
@@ -1917,7 +1950,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>45.33</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1931,10 +1964,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9465.85</v>
+        <v>9384.5</v>
       </c>
       <c r="E10">
-        <v>-0.4</v>
+        <v>-0.86</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1943,43 +1976,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-3.07</v>
+        <v>-3.9</v>
       </c>
       <c r="I10">
-        <v>10.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J10">
-        <v>-0.44</v>
+        <v>-0.37</v>
       </c>
       <c r="K10">
-        <v>0.39</v>
+        <v>0.04</v>
       </c>
       <c r="L10">
-        <v>1.61</v>
+        <v>2.52</v>
       </c>
       <c r="M10">
-        <v>3.44</v>
+        <v>3.51</v>
       </c>
       <c r="N10">
-        <v>16.22</v>
+        <v>15.89</v>
       </c>
       <c r="O10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q10">
-        <v>9459.120000000001</v>
+        <v>9452.110000000001</v>
       </c>
       <c r="R10">
-        <v>9398.68</v>
+        <v>9400.370000000001</v>
       </c>
       <c r="S10">
-        <v>9366.08</v>
+        <v>9369.02</v>
       </c>
       <c r="T10">
-        <v>9362.68</v>
+        <v>9363.08</v>
       </c>
       <c r="U10">
-        <v>1.1</v>
+        <v>0.23</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -1994,34 +2027,34 @@
         <v>3</v>
       </c>
       <c r="Z10">
-        <v>55.75</v>
+        <v>47.91</v>
       </c>
       <c r="AA10">
-        <v>25.09</v>
+        <v>19.2</v>
       </c>
       <c r="AB10">
-        <v>15.32</v>
+        <v>16.09</v>
       </c>
       <c r="AC10">
-        <v>9.77</v>
+        <v>3.1</v>
       </c>
       <c r="AD10">
-        <v>66.14</v>
+        <v>49.98</v>
       </c>
       <c r="AE10">
-        <v>61.45</v>
+        <v>60.79</v>
       </c>
       <c r="AF10">
-        <v>86.64</v>
+        <v>87.17</v>
       </c>
       <c r="AG10">
         <v>-100</v>
       </c>
       <c r="AH10">
-        <v>9502.82</v>
+        <v>9502.309999999999</v>
       </c>
       <c r="AI10">
-        <v>9294.549999999999</v>
+        <v>9298.440000000001</v>
       </c>
       <c r="AJ10">
         <v>9229.360000000001</v>
@@ -2030,7 +2063,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>26.85</v>
+        <v>24.98</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2044,10 +2077,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1559.45</v>
+        <v>1552.75</v>
       </c>
       <c r="E11">
-        <v>0.29</v>
+        <v>-0.43</v>
       </c>
       <c r="F11">
         <v>1671.5</v>
@@ -2056,43 +2089,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-6.7</v>
+        <v>-7.1</v>
       </c>
       <c r="I11">
-        <v>24.42</v>
+        <v>23.89</v>
       </c>
       <c r="J11">
-        <v>-0.59</v>
+        <v>-2.98</v>
       </c>
       <c r="K11">
-        <v>5.06</v>
+        <v>2.47</v>
       </c>
       <c r="L11">
-        <v>8.59</v>
+        <v>11.2</v>
       </c>
       <c r="M11">
-        <v>-4.02</v>
+        <v>-4.53</v>
       </c>
       <c r="N11">
-        <v>-1.63</v>
+        <v>-1.6</v>
       </c>
       <c r="O11">
         <v>56</v>
       </c>
       <c r="Q11">
-        <v>1570.7</v>
+        <v>1561.15</v>
       </c>
       <c r="R11">
-        <v>1542.75</v>
+        <v>1544.86</v>
       </c>
       <c r="S11">
-        <v>1509.34</v>
+        <v>1511.84</v>
       </c>
       <c r="T11">
-        <v>1442.26</v>
+        <v>1442.31</v>
       </c>
       <c r="U11">
-        <v>8.130000000000001</v>
+        <v>7.66</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -2107,31 +2140,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>55.47</v>
+        <v>53.73</v>
       </c>
       <c r="AA11">
-        <v>19.96</v>
+        <v>18.06</v>
       </c>
       <c r="AB11">
-        <v>20.16</v>
+        <v>19.74</v>
       </c>
       <c r="AC11">
-        <v>-0.2</v>
+        <v>-1.68</v>
       </c>
       <c r="AD11">
         <v>1.28</v>
       </c>
       <c r="AE11">
-        <v>6.91</v>
+        <v>1.81</v>
       </c>
       <c r="AF11">
-        <v>32.86</v>
+        <v>31.75</v>
       </c>
       <c r="AH11">
-        <v>1608.59</v>
+        <v>1609.05</v>
       </c>
       <c r="AI11">
-        <v>1476.91</v>
+        <v>1480.67</v>
       </c>
       <c r="AJ11">
         <v>1508.92</v>
@@ -2140,7 +2173,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>37.76</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2154,10 +2187,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13226.7</v>
+        <v>13100.8</v>
       </c>
       <c r="E12">
-        <v>0.28</v>
+        <v>-0.95</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2166,43 +2199,43 @@
         <v>9102.35</v>
       </c>
       <c r="H12">
-        <v>-3.58</v>
+        <v>-4.5</v>
       </c>
       <c r="I12">
-        <v>45.31</v>
+        <v>43.93</v>
       </c>
       <c r="J12">
-        <v>2.42</v>
+        <v>0.53</v>
       </c>
       <c r="K12">
-        <v>4.24</v>
+        <v>3.96</v>
       </c>
       <c r="L12">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="M12">
-        <v>40.71</v>
+        <v>41.09</v>
       </c>
       <c r="N12">
-        <v>18.87</v>
+        <v>17.91</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13169.76</v>
+        <v>13183.46</v>
       </c>
       <c r="R12">
-        <v>12691.36</v>
+        <v>12712.51</v>
       </c>
       <c r="S12">
-        <v>12786.02</v>
+        <v>12777.9</v>
       </c>
       <c r="T12">
-        <v>11872.39</v>
+        <v>11886.46</v>
       </c>
       <c r="U12">
-        <v>11.41</v>
+        <v>10.22</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
@@ -2217,34 +2250,34 @@
         <v>2</v>
       </c>
       <c r="Z12">
-        <v>69.39</v>
+        <v>62.42</v>
       </c>
       <c r="AA12">
-        <v>134.92</v>
+        <v>138.77</v>
       </c>
       <c r="AB12">
-        <v>41.37</v>
+        <v>60.85</v>
       </c>
       <c r="AC12">
-        <v>93.55</v>
+        <v>77.91</v>
       </c>
       <c r="AD12">
-        <v>83.97</v>
+        <v>79</v>
       </c>
       <c r="AE12">
-        <v>88.56999999999999</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="AF12">
-        <v>191.77</v>
+        <v>193.51</v>
       </c>
       <c r="AG12">
         <v>-100</v>
       </c>
       <c r="AH12">
-        <v>13318.89</v>
+        <v>13366.09</v>
       </c>
       <c r="AI12">
-        <v>12063.83</v>
+        <v>12058.94</v>
       </c>
       <c r="AJ12">
         <v>12652.05</v>
@@ -2253,7 +2286,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>51.42</v>
+        <v>50.94</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2267,10 +2300,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9850.75</v>
+        <v>9831.4</v>
       </c>
       <c r="E13">
-        <v>-0.72</v>
+        <v>-0.2</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2279,43 +2312,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-8.5</v>
+        <v>-8.68</v>
       </c>
       <c r="I13">
-        <v>7.04</v>
+        <v>6.83</v>
       </c>
       <c r="J13">
-        <v>-1.55</v>
+        <v>-1.07</v>
       </c>
       <c r="K13">
-        <v>-0.61</v>
+        <v>-1.27</v>
       </c>
       <c r="L13">
-        <v>-6.77</v>
+        <v>-5.87</v>
       </c>
       <c r="M13">
-        <v>0.72</v>
+        <v>1.54</v>
       </c>
       <c r="N13">
-        <v>22.81</v>
+        <v>22.38</v>
       </c>
       <c r="O13">
         <v>13</v>
       </c>
       <c r="Q13">
-        <v>9919.969999999999</v>
+        <v>9898.67</v>
       </c>
       <c r="R13">
-        <v>9931.780000000001</v>
+        <v>9927.219999999999</v>
       </c>
       <c r="S13">
-        <v>9983.530000000001</v>
+        <v>9977.129999999999</v>
       </c>
       <c r="T13">
-        <v>10050.49</v>
+        <v>10050</v>
       </c>
       <c r="U13">
-        <v>-1.99</v>
+        <v>-2.18</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -2330,43 +2363,43 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>38.34</v>
+        <v>36.74</v>
       </c>
       <c r="AA13">
-        <v>-25.36</v>
+        <v>-31.07</v>
       </c>
       <c r="AB13">
-        <v>-27.15</v>
+        <v>-27.93</v>
       </c>
       <c r="AC13">
-        <v>1.79</v>
+        <v>-3.14</v>
       </c>
       <c r="AD13">
-        <v>28.46</v>
+        <v>12.34</v>
       </c>
       <c r="AE13">
-        <v>42.79</v>
+        <v>29.63</v>
       </c>
       <c r="AF13">
-        <v>93.72</v>
+        <v>92.17</v>
       </c>
       <c r="AG13">
         <v>-100</v>
       </c>
       <c r="AH13">
-        <v>9988.610000000001</v>
+        <v>9999.65</v>
       </c>
       <c r="AI13">
-        <v>9874.950000000001</v>
+        <v>9854.799999999999</v>
       </c>
       <c r="AJ13">
-        <v>10154.68</v>
+        <v>10104.9</v>
       </c>
       <c r="AK13" t="s">
         <v>82</v>
       </c>
       <c r="AL13">
-        <v>16.63</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2380,10 +2413,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8639.799999999999</v>
+        <v>8640.25</v>
       </c>
       <c r="E14">
-        <v>-1.67</v>
+        <v>0.01</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2395,40 +2428,40 @@
         <v>-12.55</v>
       </c>
       <c r="I14">
-        <v>27.88</v>
+        <v>27.89</v>
       </c>
       <c r="J14">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="K14">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="L14">
-        <v>5.87</v>
+        <v>7.05</v>
       </c>
       <c r="M14">
-        <v>25.07</v>
+        <v>26.12</v>
       </c>
       <c r="N14">
-        <v>29.83</v>
+        <v>29.71</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8635.290000000001</v>
+        <v>8667.360000000001</v>
       </c>
       <c r="R14">
-        <v>8441.82</v>
+        <v>8458.440000000001</v>
       </c>
       <c r="S14">
-        <v>8436.34</v>
+        <v>8449.030000000001</v>
       </c>
       <c r="T14">
-        <v>8549.74</v>
+        <v>8554.5</v>
       </c>
       <c r="U14">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -2443,34 +2476,34 @@
         <v>2</v>
       </c>
       <c r="Z14">
-        <v>59.5</v>
+        <v>59.52</v>
       </c>
       <c r="AA14">
-        <v>64.08</v>
+        <v>67.44</v>
       </c>
       <c r="AB14">
-        <v>24.15</v>
+        <v>32.81</v>
       </c>
       <c r="AC14">
-        <v>39.93</v>
+        <v>34.63</v>
       </c>
       <c r="AD14">
-        <v>85.56999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="AE14">
-        <v>94.66</v>
+        <v>85.58</v>
       </c>
       <c r="AF14">
-        <v>139.56</v>
+        <v>137.53</v>
       </c>
       <c r="AG14">
         <v>-100</v>
       </c>
       <c r="AH14">
-        <v>8707.24</v>
+        <v>8730.1</v>
       </c>
       <c r="AI14">
-        <v>8176.4</v>
+        <v>8186.78</v>
       </c>
       <c r="AJ14">
         <v>8374.41</v>
@@ -2479,7 +2512,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>38.7</v>
+        <v>38.53</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2493,55 +2526,55 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26479.55</v>
+        <v>26750.45</v>
       </c>
       <c r="E15">
-        <v>-0.23</v>
+        <v>1.02</v>
       </c>
       <c r="F15">
-        <v>26662.8</v>
+        <v>26750.45</v>
       </c>
       <c r="G15">
         <v>21402.15</v>
       </c>
       <c r="H15">
-        <v>-0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>23.72</v>
+        <v>24.99</v>
       </c>
       <c r="J15">
-        <v>-0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="K15">
-        <v>3.14</v>
+        <v>4.32</v>
       </c>
       <c r="L15">
-        <v>9.550000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="M15">
-        <v>14.76</v>
+        <v>17.48</v>
       </c>
       <c r="N15">
-        <v>12.8</v>
+        <v>13.36</v>
       </c>
       <c r="O15">
         <v>81</v>
       </c>
       <c r="Q15">
-        <v>26549.44</v>
+        <v>26580.03</v>
       </c>
       <c r="R15">
-        <v>26161.13</v>
+        <v>26203.29</v>
       </c>
       <c r="S15">
-        <v>25339.76</v>
+        <v>25390.49</v>
       </c>
       <c r="T15">
-        <v>23400.93</v>
+        <v>23424.17</v>
       </c>
       <c r="U15">
-        <v>13.16</v>
+        <v>14.2</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2556,34 +2589,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>64.05</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="AA15">
-        <v>345.75</v>
+        <v>350.89</v>
       </c>
       <c r="AB15">
         <v>350.89</v>
       </c>
       <c r="AC15">
-        <v>-5.14</v>
+        <v>-0</v>
       </c>
       <c r="AD15">
-        <v>75.06</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="AE15">
-        <v>79.53</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="AF15">
-        <v>322.44</v>
+        <v>323.36</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>26888.66</v>
+        <v>26965.76</v>
       </c>
       <c r="AI15">
-        <v>25433.59</v>
+        <v>25440.83</v>
       </c>
       <c r="AJ15">
         <v>25649.77</v>
@@ -2592,7 +2625,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>46.27</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2606,10 +2639,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>897.95</v>
+        <v>889.1</v>
       </c>
       <c r="E16">
-        <v>1.35</v>
+        <v>-0.99</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2618,43 +2651,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-7.3</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="I16">
-        <v>37.9</v>
+        <v>36.54</v>
       </c>
       <c r="J16">
-        <v>-1.65</v>
+        <v>-0.24</v>
       </c>
       <c r="K16">
-        <v>-4.33</v>
+        <v>-5.13</v>
       </c>
       <c r="L16">
-        <v>12.45</v>
+        <v>16.12</v>
       </c>
       <c r="M16">
-        <v>-2.15</v>
+        <v>-2.55</v>
       </c>
       <c r="N16">
-        <v>18.01</v>
+        <v>17.71</v>
       </c>
       <c r="O16">
         <v>62</v>
       </c>
       <c r="Q16">
-        <v>892.13</v>
+        <v>891.71</v>
       </c>
       <c r="R16">
-        <v>909.15</v>
+        <v>907.67</v>
       </c>
       <c r="S16">
-        <v>857.13</v>
+        <v>859.55</v>
       </c>
       <c r="T16">
-        <v>835.45</v>
+        <v>835.23</v>
       </c>
       <c r="U16">
-        <v>7.48</v>
+        <v>6.45</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
@@ -2669,34 +2702,34 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>52.54</v>
+        <v>48.78</v>
       </c>
       <c r="AA16">
-        <v>7.03</v>
+        <v>5.63</v>
       </c>
       <c r="AB16">
-        <v>13.83</v>
+        <v>12.19</v>
       </c>
       <c r="AC16">
-        <v>-6.8</v>
+        <v>-6.56</v>
       </c>
       <c r="AD16">
-        <v>9.48</v>
+        <v>11.97</v>
       </c>
       <c r="AE16">
-        <v>7.4</v>
+        <v>9.27</v>
       </c>
       <c r="AF16">
-        <v>19.35</v>
+        <v>19.07</v>
       </c>
       <c r="AG16">
         <v>-100</v>
       </c>
       <c r="AH16">
-        <v>933.0599999999999</v>
+        <v>932.73</v>
       </c>
       <c r="AI16">
-        <v>885.23</v>
+        <v>882.6</v>
       </c>
       <c r="AJ16">
         <v>864.8</v>
@@ -2705,7 +2738,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>20.28</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2719,10 +2752,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>31310.15</v>
+        <v>31223.65</v>
       </c>
       <c r="E17">
-        <v>0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2731,22 +2764,22 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-8.18</v>
+        <v>-8.44</v>
       </c>
       <c r="I17">
-        <v>10.39</v>
+        <v>10.08</v>
       </c>
       <c r="J17">
-        <v>-1.46</v>
+        <v>-1.22</v>
       </c>
       <c r="K17">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
       <c r="L17">
-        <v>4.66</v>
+        <v>6.48</v>
       </c>
       <c r="M17">
-        <v>-4.6</v>
+        <v>-4.63</v>
       </c>
       <c r="N17">
         <v>6.43</v>
@@ -2755,19 +2788,19 @@
         <v>19</v>
       </c>
       <c r="Q17">
-        <v>31449.63</v>
+        <v>31372.66</v>
       </c>
       <c r="R17">
-        <v>31386.66</v>
+        <v>31395.16</v>
       </c>
       <c r="S17">
-        <v>30782.22</v>
+        <v>30816.32</v>
       </c>
       <c r="T17">
-        <v>31868.41</v>
+        <v>31857.61</v>
       </c>
       <c r="U17">
-        <v>-1.75</v>
+        <v>-1.99</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
@@ -2782,34 +2815,34 @@
         <v>1</v>
       </c>
       <c r="Z17">
-        <v>52.1</v>
+        <v>49.67</v>
       </c>
       <c r="AA17">
-        <v>154.42</v>
+        <v>128.65</v>
       </c>
       <c r="AB17">
-        <v>203.92</v>
+        <v>188.87</v>
       </c>
       <c r="AC17">
-        <v>-49.5</v>
+        <v>-60.21</v>
       </c>
       <c r="AD17">
-        <v>14.38</v>
+        <v>2.5</v>
       </c>
       <c r="AE17">
-        <v>30.2</v>
+        <v>15</v>
       </c>
       <c r="AF17">
-        <v>319.94</v>
+        <v>311.59</v>
       </c>
       <c r="AG17">
         <v>-100</v>
       </c>
       <c r="AH17">
-        <v>31740.2</v>
+        <v>31722.17</v>
       </c>
       <c r="AI17">
-        <v>31033.13</v>
+        <v>31068.15</v>
       </c>
       <c r="AJ17">
         <v>30549.87</v>
@@ -2818,7 +2851,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>23.9</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2832,10 +2865,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16650.95</v>
+        <v>16705.05</v>
       </c>
       <c r="E18">
-        <v>-0.35</v>
+        <v>0.32</v>
       </c>
       <c r="F18">
         <v>16783.35</v>
@@ -2844,25 +2877,25 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-0.79</v>
+        <v>-0.47</v>
       </c>
       <c r="I18">
-        <v>8.1</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J18">
-        <v>-0.79</v>
+        <v>-0.25</v>
       </c>
       <c r="K18">
-        <v>1.92</v>
+        <v>2.51</v>
       </c>
       <c r="N18">
-        <v>52.62</v>
+        <v>54.57</v>
       </c>
       <c r="Q18">
-        <v>16706.68</v>
+        <v>16698.35</v>
       </c>
       <c r="R18">
-        <v>16554.23</v>
+        <v>16567.41</v>
       </c>
       <c r="X18" t="s">
         <v>80</v>
@@ -2871,31 +2904,31 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>60.12</v>
+        <v>62.35</v>
       </c>
       <c r="AA18">
-        <v>159.78</v>
+        <v>153.36</v>
       </c>
       <c r="AB18">
-        <v>170.78</v>
+        <v>167.3</v>
       </c>
       <c r="AC18">
-        <v>-11</v>
+        <v>-13.94</v>
       </c>
       <c r="AD18">
-        <v>65.73999999999999</v>
+        <v>61.56</v>
       </c>
       <c r="AE18">
-        <v>71.36</v>
+        <v>67.09</v>
       </c>
       <c r="AF18">
-        <v>188.67</v>
+        <v>188.78</v>
       </c>
       <c r="AH18">
-        <v>16900.9</v>
+        <v>16916.07</v>
       </c>
       <c r="AI18">
-        <v>16207.55</v>
+        <v>16218.75</v>
       </c>
       <c r="AJ18">
         <v>16199.38</v>
@@ -2904,7 +2937,7 @@
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>25.1</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2918,10 +2951,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9635.65</v>
+        <v>9593.4</v>
       </c>
       <c r="E19">
-        <v>-0.99</v>
+        <v>-0.44</v>
       </c>
       <c r="F19">
         <v>9732.15</v>
@@ -2930,25 +2963,25 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-0.99</v>
+        <v>-1.43</v>
       </c>
       <c r="I19">
-        <v>7.12</v>
+        <v>6.65</v>
       </c>
       <c r="J19">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="K19">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="N19">
-        <v>53.06</v>
+        <v>47.97</v>
       </c>
       <c r="Q19">
-        <v>9570.030000000001</v>
+        <v>9604.700000000001</v>
       </c>
       <c r="R19">
-        <v>9395.76</v>
+        <v>9409.15</v>
       </c>
       <c r="X19" t="s">
         <v>80</v>
@@ -2957,31 +2990,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>60.72</v>
+        <v>58.31</v>
       </c>
       <c r="AA19">
-        <v>63.82</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="AB19">
-        <v>27.82</v>
+        <v>35.82</v>
       </c>
       <c r="AC19">
-        <v>36</v>
+        <v>32.02</v>
       </c>
       <c r="AD19">
-        <v>92.45</v>
+        <v>81.78</v>
       </c>
       <c r="AE19">
-        <v>92.76000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="AF19">
-        <v>148.79</v>
+        <v>149.68</v>
       </c>
       <c r="AH19">
-        <v>9680.719999999999</v>
+        <v>9705.18</v>
       </c>
       <c r="AI19">
-        <v>9110.790000000001</v>
+        <v>9113.120000000001</v>
       </c>
       <c r="AJ19">
         <v>9264.24</v>
@@ -2990,7 +3023,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>25.59</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3004,10 +3037,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11270.45</v>
+        <v>11279.1</v>
       </c>
       <c r="E20">
-        <v>-0.37</v>
+        <v>0.08</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3016,25 +3049,25 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-0.87</v>
+        <v>-0.79</v>
       </c>
       <c r="I20">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="J20">
-        <v>-0.77</v>
+        <v>0.47</v>
       </c>
       <c r="K20">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="N20">
-        <v>15.42</v>
+        <v>15.69</v>
       </c>
       <c r="Q20">
-        <v>11265.86</v>
+        <v>11276.42</v>
       </c>
       <c r="R20">
-        <v>11209.16</v>
+        <v>11217.99</v>
       </c>
       <c r="X20" t="s">
         <v>80</v>
@@ -3043,31 +3076,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>54.74</v>
+        <v>55.24</v>
       </c>
       <c r="AA20">
-        <v>36.19</v>
+        <v>37.02</v>
       </c>
       <c r="AB20">
-        <v>25.65</v>
+        <v>27.92</v>
       </c>
       <c r="AC20">
-        <v>10.54</v>
+        <v>9.1</v>
       </c>
       <c r="AD20">
-        <v>67.56999999999999</v>
+        <v>65.27</v>
       </c>
       <c r="AE20">
-        <v>61.02</v>
+        <v>65.12</v>
       </c>
       <c r="AF20">
-        <v>135.93</v>
+        <v>132.06</v>
       </c>
       <c r="AH20">
-        <v>11409.37</v>
+        <v>11413.92</v>
       </c>
       <c r="AI20">
-        <v>11008.94</v>
+        <v>11022.06</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3076,7 +3109,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>15.66</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3090,10 +3123,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27534.3</v>
+        <v>27380.35</v>
       </c>
       <c r="E21">
-        <v>0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3102,43 +3135,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-5.67</v>
+        <v>-6.19</v>
       </c>
       <c r="I21">
-        <v>14.04</v>
+        <v>13.4</v>
       </c>
       <c r="J21">
-        <v>-1.82</v>
+        <v>-1.72</v>
       </c>
       <c r="K21">
-        <v>-1.96</v>
+        <v>-2.75</v>
       </c>
       <c r="L21">
-        <v>4.47</v>
+        <v>5.75</v>
       </c>
       <c r="M21">
-        <v>1.53</v>
+        <v>1.09</v>
       </c>
       <c r="N21">
-        <v>8</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O21">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q21">
-        <v>27642.25</v>
+        <v>27546.23</v>
       </c>
       <c r="R21">
-        <v>28085.23</v>
+        <v>28058.45</v>
       </c>
       <c r="S21">
-        <v>27743.64</v>
+        <v>27769.88</v>
       </c>
       <c r="T21">
-        <v>27695.98</v>
+        <v>27692.2</v>
       </c>
       <c r="U21">
-        <v>-0.58</v>
+        <v>-1.13</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
@@ -3153,31 +3186,31 @@
         <v>2</v>
       </c>
       <c r="Z21">
-        <v>42.21</v>
+        <v>39.67</v>
       </c>
       <c r="AA21">
-        <v>-78.29000000000001</v>
+        <v>-108.75</v>
       </c>
       <c r="AB21">
-        <v>44.07</v>
+        <v>13.51</v>
       </c>
       <c r="AC21">
-        <v>-122.37</v>
+        <v>-122.26</v>
       </c>
       <c r="AD21">
-        <v>13.55</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AE21">
-        <v>19.55</v>
+        <v>12.91</v>
       </c>
       <c r="AF21">
-        <v>452.85</v>
+        <v>441.73</v>
       </c>
       <c r="AH21">
-        <v>28935.57</v>
+        <v>28963.23</v>
       </c>
       <c r="AI21">
-        <v>27234.89</v>
+        <v>27153.67</v>
       </c>
       <c r="AJ21">
         <v>27330.14</v>
@@ -3186,7 +3219,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>23.16</v>
+        <v>24.53</v>
       </c>
     </row>
   </sheetData>
@@ -3327,7 +3360,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3367,7 +3400,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3386,2324 +3419,2336 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="5" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>98</v>
       </c>
+      <c r="D5" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7">
-        <v>11.14</v>
-      </c>
-      <c r="D8" s="7">
-        <v>10.27</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2.23</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.21</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7">
-        <v>4.25</v>
-      </c>
-      <c r="D10" s="7">
-        <v>4.19</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-0.23</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-1.26</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.03</v>
+      <c r="B11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="7">
-        <v>0.17</v>
+        <v>10.27</v>
       </c>
       <c r="D12" s="7">
-        <v>0.11</v>
+        <v>9.18</v>
       </c>
       <c r="E12" s="8">
-        <v>-0.06</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="7">
-        <v>-0.06</v>
+        <v>1.21</v>
       </c>
       <c r="D13" s="7">
-        <v>-1.06</v>
+        <v>0.87</v>
       </c>
       <c r="E13" s="8">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="7">
-        <v>14.84</v>
+        <v>4.19</v>
       </c>
       <c r="D14" s="7">
-        <v>12.93</v>
+        <v>4.16</v>
       </c>
       <c r="E14" s="8">
-        <v>-1.91</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="7">
-        <v>5.5</v>
+        <v>-1.26</v>
       </c>
       <c r="D15" s="7">
-        <v>4.5</v>
+        <v>-1.31</v>
       </c>
       <c r="E15" s="8">
-        <v>-1</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="7">
-        <v>1.91</v>
+        <v>0.11</v>
       </c>
       <c r="D16" s="7">
-        <v>0.39</v>
+        <v>-0.05</v>
       </c>
       <c r="E16" s="8">
-        <v>-1.52</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="7">
-        <v>4.87</v>
+        <v>-1.06</v>
       </c>
       <c r="D17" s="7">
-        <v>5.06</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.19</v>
+        <v>-1.5</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="7">
-        <v>5.49</v>
+        <v>12.93</v>
       </c>
       <c r="D18" s="7">
-        <v>4.24</v>
+        <v>9.68</v>
       </c>
       <c r="E18" s="8">
-        <v>-1.25</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="7">
-        <v>1.19</v>
+        <v>4.5</v>
       </c>
       <c r="D19" s="7">
-        <v>-0.61</v>
+        <v>4.46</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.8</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="7">
-        <v>7.11</v>
+        <v>0.39</v>
       </c>
       <c r="D20" s="7">
-        <v>2.23</v>
+        <v>0.04</v>
       </c>
       <c r="E20" s="8">
-        <v>-4.88</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="7">
-        <v>3.45</v>
+        <v>5.06</v>
       </c>
       <c r="D21" s="7">
-        <v>3.14</v>
+        <v>2.47</v>
       </c>
       <c r="E21" s="8">
-        <v>-0.31</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="7">
-        <v>-2.32</v>
+        <v>4.24</v>
       </c>
       <c r="D22" s="7">
-        <v>-4.33</v>
+        <v>3.96</v>
       </c>
       <c r="E22" s="8">
-        <v>-2.01</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="7">
-        <v>1.31</v>
+        <v>-0.61</v>
       </c>
       <c r="D23" s="7">
-        <v>0.45</v>
+        <v>-1.27</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.86</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="7">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="D24" s="7">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="E24" s="8">
-        <v>-0.54</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="7">
-        <v>4.54</v>
+        <v>3.14</v>
       </c>
       <c r="D25" s="7">
-        <v>1.58</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.96</v>
+        <v>4.32</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1.18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="7">
-        <v>2.53</v>
+        <v>-4.33</v>
       </c>
       <c r="D26" s="7">
-        <v>0.83</v>
+        <v>-5.13</v>
       </c>
       <c r="E26" s="8">
-        <v>-1.7</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="7">
-        <v>-1.33</v>
+        <v>0.45</v>
       </c>
       <c r="D27" s="7">
-        <v>-1.96</v>
+        <v>-0.15</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.63</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="7">
-        <v>3.14</v>
+        <v>1.92</v>
       </c>
       <c r="D28" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.59</v>
+        <v>2.51</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.59</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="7">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="D29" s="7">
-        <v>0.08</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.24</v>
+        <v>1.9</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.32</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" s="7">
-        <v>0.96</v>
+        <v>0.83</v>
       </c>
       <c r="D30" s="7">
-        <v>-0.24</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.2</v>
+        <v>0.92</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.09</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="7">
-        <v>0.05</v>
+        <v>-1.96</v>
       </c>
       <c r="D31" s="7">
-        <v>-0.49</v>
+        <v>-2.75</v>
       </c>
       <c r="E31" s="8">
-        <v>-0.54</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="7">
-        <v>0.64</v>
+        <v>1.55</v>
       </c>
       <c r="D32" s="7">
-        <v>-1.2</v>
+        <v>1.44</v>
       </c>
       <c r="E32" s="8">
-        <v>-1.84</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="7">
-        <v>-0.48</v>
+        <v>0.08</v>
       </c>
       <c r="D33" s="7">
-        <v>-1.63</v>
+        <v>-0.02</v>
       </c>
       <c r="E33" s="8">
-        <v>-1.15</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="7">
-        <v>2.73</v>
+        <v>-0.24</v>
       </c>
       <c r="D34" s="7">
-        <v>-0.26</v>
+        <v>-0.46</v>
       </c>
       <c r="E34" s="8">
-        <v>-2.99</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="7">
-        <v>2.04</v>
+        <v>-0.49</v>
       </c>
       <c r="D35" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.23</v>
+        <v>-0.28</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.21</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="7">
-        <v>1.01</v>
+        <v>-1.2</v>
       </c>
       <c r="D36" s="7">
-        <v>-0.44</v>
+        <v>-1.49</v>
       </c>
       <c r="E36" s="8">
-        <v>-1.45</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="7">
-        <v>-3.93</v>
+        <v>-1.63</v>
       </c>
       <c r="D37" s="7">
-        <v>-0.59</v>
+        <v>-1.54</v>
       </c>
       <c r="E37" s="9">
-        <v>3.34</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="7">
-        <v>3.7</v>
+        <v>-0.26</v>
       </c>
       <c r="D38" s="7">
-        <v>2.42</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.28</v>
+        <v>1.17</v>
+      </c>
+      <c r="E38" s="9">
+        <v>1.43</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="7">
-        <v>-0.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D39" s="7">
-        <v>-1.55</v>
+        <v>0.68</v>
       </c>
       <c r="E39" s="8">
-        <v>-1.35</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="7">
-        <v>5.01</v>
+        <v>-0.44</v>
       </c>
       <c r="D40" s="7">
-        <v>1.8</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-3.21</v>
+        <v>-0.37</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="7">
-        <v>0.03</v>
+        <v>-0.59</v>
       </c>
       <c r="D41" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-2.98</v>
       </c>
       <c r="E41" s="8">
-        <v>-0.72</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="7">
-        <v>-1.72</v>
+        <v>2.42</v>
       </c>
       <c r="D42" s="7">
-        <v>-1.65</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.07000000000000001</v>
+        <v>0.53</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="7">
-        <v>-0.01</v>
+        <v>-1.55</v>
       </c>
       <c r="D43" s="7">
-        <v>-1.46</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-1.45</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.48</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="7">
-        <v>-0.28</v>
+        <v>1.8</v>
       </c>
       <c r="D44" s="7">
-        <v>-0.79</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.51</v>
+        <v>1.89</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.09</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="7">
-        <v>4.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D45" s="7">
-        <v>2.09</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-2.21</v>
+        <v>0.58</v>
+      </c>
+      <c r="E45" s="9">
+        <v>1.27</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="7">
-        <v>0.57</v>
+        <v>-1.65</v>
       </c>
       <c r="D46" s="7">
-        <v>-0.77</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-1.34</v>
+        <v>-0.24</v>
+      </c>
+      <c r="E46" s="9">
+        <v>1.41</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="7">
-        <v>-0.47</v>
+        <v>-1.46</v>
       </c>
       <c r="D47" s="7">
-        <v>-1.82</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-1.35</v>
+        <v>-1.22</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.24</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C48" s="7">
-        <v>24.11</v>
+        <v>-0.79</v>
       </c>
       <c r="D48" s="7">
-        <v>24.74</v>
+        <v>-0.25</v>
       </c>
       <c r="E48" s="9">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="7">
-        <v>13.13</v>
+        <v>2.09</v>
       </c>
       <c r="D49" s="7">
-        <v>13.18</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.05</v>
+        <v>1.84</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="7">
-        <v>4.46</v>
+        <v>-0.77</v>
       </c>
       <c r="D50" s="7">
-        <v>4.52</v>
+        <v>0.47</v>
       </c>
       <c r="E50" s="9">
-        <v>0.06</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C51" s="7">
-        <v>9.43</v>
+        <v>-1.82</v>
       </c>
       <c r="D51" s="7">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.04</v>
+        <v>-1.72</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.1</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="7">
-        <v>-9.94</v>
+        <v>24.74</v>
       </c>
       <c r="D52" s="7">
-        <v>-10.28</v>
+        <v>24.53</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="7">
-        <v>-0.88</v>
+        <v>13.18</v>
       </c>
       <c r="D53" s="7">
-        <v>-0.59</v>
+        <v>13.52</v>
       </c>
       <c r="E53" s="9">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="7">
-        <v>-10.81</v>
+        <v>4.52</v>
       </c>
       <c r="D54" s="7">
-        <v>-10.85</v>
+        <v>3.52</v>
       </c>
       <c r="E54" s="8">
-        <v>-0.04</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="7">
-        <v>4.38</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="D55" s="7">
-        <v>3.44</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.9399999999999999</v>
+        <v>10.23</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.84</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="7">
-        <v>-5.05</v>
+        <v>-10.28</v>
       </c>
       <c r="D56" s="7">
-        <v>-4.02</v>
-      </c>
-      <c r="E56" s="9">
-        <v>1.03</v>
+        <v>-12.59</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="7">
-        <v>40.17</v>
+        <v>-0.59</v>
       </c>
       <c r="D57" s="7">
-        <v>40.71</v>
-      </c>
-      <c r="E57" s="9">
-        <v>0.54</v>
+        <v>-0.82</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="7">
-        <v>1.46</v>
+        <v>-10.85</v>
       </c>
       <c r="D58" s="7">
-        <v>0.72</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.74</v>
+        <v>-9.85</v>
+      </c>
+      <c r="E58" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="7">
-        <v>26.36</v>
+        <v>3.44</v>
       </c>
       <c r="D59" s="7">
-        <v>25.07</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-1.29</v>
+        <v>3.51</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="7">
-        <v>15.04</v>
+        <v>-4.02</v>
       </c>
       <c r="D60" s="7">
-        <v>14.76</v>
+        <v>-4.53</v>
       </c>
       <c r="E60" s="8">
-        <v>-0.28</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="7">
-        <v>-4.38</v>
+        <v>40.71</v>
       </c>
       <c r="D61" s="7">
-        <v>-2.15</v>
+        <v>41.09</v>
       </c>
       <c r="E61" s="9">
-        <v>2.23</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="7">
-        <v>-4.65</v>
+        <v>0.72</v>
       </c>
       <c r="D62" s="7">
-        <v>-4.6</v>
+        <v>1.54</v>
       </c>
       <c r="E62" s="9">
-        <v>0.05</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="7">
-        <v>0.88</v>
+        <v>25.07</v>
       </c>
       <c r="D63" s="7">
-        <v>1.53</v>
+        <v>26.12</v>
       </c>
       <c r="E63" s="9">
-        <v>0.65</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" s="7">
-        <v>8.76</v>
+        <v>14.76</v>
       </c>
       <c r="D64" s="7">
-        <v>10.72</v>
+        <v>17.48</v>
       </c>
       <c r="E64" s="9">
-        <v>1.96</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" s="7">
-        <v>-3.42</v>
+        <v>-2.15</v>
       </c>
       <c r="D65" s="7">
-        <v>-2.18</v>
-      </c>
-      <c r="E65" s="9">
-        <v>1.24</v>
+        <v>-2.55</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="7">
-        <v>4.8</v>
+        <v>-4.6</v>
       </c>
       <c r="D66" s="7">
-        <v>6.96</v>
-      </c>
-      <c r="E66" s="9">
-        <v>2.16</v>
+        <v>-4.63</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67" s="7">
-        <v>-5.02</v>
+        <v>1.53</v>
       </c>
       <c r="D67" s="7">
-        <v>-3.23</v>
-      </c>
-      <c r="E67" s="9">
-        <v>1.79</v>
+        <v>1.09</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>-3.38</v>
+        <v>10.72</v>
       </c>
       <c r="D68" s="7">
-        <v>-3.6</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-0.22</v>
+        <v>12.68</v>
+      </c>
+      <c r="E68" s="9">
+        <v>1.96</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="7">
-        <v>1.75</v>
+        <v>-2.18</v>
       </c>
       <c r="D69" s="7">
-        <v>3.47</v>
+        <v>-1.8</v>
       </c>
       <c r="E69" s="9">
-        <v>1.72</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>7.33</v>
+        <v>6.96</v>
       </c>
       <c r="D70" s="7">
-        <v>7.85</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E70" s="9">
-        <v>0.52</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="7">
-        <v>0.07000000000000001</v>
+        <v>-3.23</v>
       </c>
       <c r="D71" s="7">
-        <v>1.61</v>
+        <v>-2.11</v>
       </c>
       <c r="E71" s="9">
-        <v>1.54</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="7">
-        <v>5.58</v>
+        <v>-3.6</v>
       </c>
       <c r="D72" s="7">
-        <v>8.59</v>
+        <v>-3.3</v>
       </c>
       <c r="E72" s="9">
-        <v>3.01</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="7">
-        <v>1.06</v>
+        <v>3.47</v>
       </c>
       <c r="D73" s="7">
-        <v>2.32</v>
+        <v>5.15</v>
       </c>
       <c r="E73" s="9">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="7">
-        <v>-7.36</v>
+        <v>7.85</v>
       </c>
       <c r="D74" s="7">
-        <v>-6.77</v>
+        <v>12.71</v>
       </c>
       <c r="E74" s="9">
-        <v>0.59</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="7">
-        <v>4.95</v>
+        <v>1.61</v>
       </c>
       <c r="D75" s="7">
-        <v>5.87</v>
+        <v>2.52</v>
       </c>
       <c r="E75" s="9">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="7">
-        <v>10.08</v>
+        <v>8.59</v>
       </c>
       <c r="D76" s="7">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.53</v>
+        <v>11.2</v>
+      </c>
+      <c r="E76" s="9">
+        <v>2.61</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="7">
-        <v>7.57</v>
+        <v>2.32</v>
       </c>
       <c r="D77" s="7">
-        <v>12.45</v>
-      </c>
-      <c r="E77" s="9">
-        <v>4.88</v>
+        <v>1.7</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="7">
-        <v>2.94</v>
+        <v>-6.77</v>
       </c>
       <c r="D78" s="7">
-        <v>4.66</v>
+        <v>-5.87</v>
       </c>
       <c r="E78" s="9">
-        <v>1.72</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="7">
-        <v>3.13</v>
+        <v>5.87</v>
       </c>
       <c r="D79" s="7">
-        <v>4.47</v>
+        <v>7.05</v>
       </c>
       <c r="E79" s="9">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C80" s="7">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="D80" s="7">
-        <v>-0.09</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-0.09</v>
+        <v>12.2</v>
+      </c>
+      <c r="E80" s="9">
+        <v>2.65</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C81" s="7">
-        <v>-4.87</v>
+        <v>12.45</v>
       </c>
       <c r="D81" s="7">
-        <v>-4.68</v>
+        <v>16.12</v>
       </c>
       <c r="E81" s="9">
-        <v>0.19</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C82" s="7">
-        <v>-3.49</v>
+        <v>4.66</v>
       </c>
       <c r="D82" s="7">
-        <v>-3.24</v>
+        <v>6.48</v>
       </c>
       <c r="E82" s="9">
-        <v>0.25</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C83" s="7">
-        <v>-13.43</v>
+        <v>4.47</v>
       </c>
       <c r="D83" s="7">
-        <v>-13.55</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.12</v>
+        <v>5.75</v>
+      </c>
+      <c r="E83" s="9">
+        <v>1.28</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="7">
-        <v>-7.02</v>
+        <v>-0.09</v>
       </c>
       <c r="D84" s="7">
-        <v>-6.74</v>
-      </c>
-      <c r="E84" s="9">
-        <v>0.28</v>
+        <v>-0.64</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="7">
-        <v>-20.11</v>
+        <v>-4.68</v>
       </c>
       <c r="D85" s="7">
-        <v>-19.9</v>
-      </c>
-      <c r="E85" s="9">
-        <v>0.21</v>
+        <v>-5.48</v>
+      </c>
+      <c r="E85" s="8">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="7">
-        <v>0</v>
+        <v>-3.24</v>
       </c>
       <c r="D86" s="7">
-        <v>-0.04</v>
+        <v>-3.85</v>
       </c>
       <c r="E86" s="8">
-        <v>-0.04</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="7">
-        <v>-2.68</v>
+        <v>-6.71</v>
       </c>
       <c r="D87" s="7">
-        <v>-3.07</v>
+        <v>-6.81</v>
       </c>
       <c r="E87" s="8">
-        <v>-0.39</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="7">
-        <v>-6.97</v>
+        <v>-13.55</v>
       </c>
       <c r="D88" s="7">
-        <v>-6.7</v>
-      </c>
-      <c r="E88" s="9">
-        <v>0.27</v>
+        <v>-14.56</v>
+      </c>
+      <c r="E88" s="8">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="7">
-        <v>-3.85</v>
+        <v>-6.74</v>
       </c>
       <c r="D89" s="7">
-        <v>-3.58</v>
-      </c>
-      <c r="E89" s="9">
-        <v>0.27</v>
+        <v>-7.13</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="7">
-        <v>-7.84</v>
+        <v>-19.9</v>
       </c>
       <c r="D90" s="7">
-        <v>-8.5</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-0.66</v>
+        <v>-19.41</v>
+      </c>
+      <c r="E90" s="9">
+        <v>0.49</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="7">
-        <v>-11.07</v>
+        <v>-0.04</v>
       </c>
       <c r="D91" s="7">
-        <v>-12.55</v>
+        <v>-0.32</v>
       </c>
       <c r="E91" s="8">
-        <v>-1.48</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="7">
-        <v>-0.45</v>
+        <v>-3.07</v>
       </c>
       <c r="D92" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-3.9</v>
       </c>
       <c r="E92" s="8">
-        <v>-0.24</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="7">
-        <v>-8.539999999999999</v>
+        <v>-6.7</v>
       </c>
       <c r="D93" s="7">
-        <v>-7.3</v>
-      </c>
-      <c r="E93" s="9">
-        <v>1.24</v>
+        <v>-7.1</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="7">
-        <v>-8.32</v>
+        <v>-3.58</v>
       </c>
       <c r="D94" s="7">
-        <v>-8.18</v>
-      </c>
-      <c r="E94" s="9">
-        <v>0.14</v>
+        <v>-4.5</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="7">
-        <v>-0.44</v>
+        <v>-8.5</v>
       </c>
       <c r="D95" s="7">
-        <v>-0.79</v>
+        <v>-8.68</v>
       </c>
       <c r="E95" s="8">
-        <v>-0.35</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="D96" s="7">
         <v>0</v>
       </c>
-      <c r="D96" s="7">
-        <v>-0.99</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-0.99</v>
+      <c r="E96" s="9">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="7">
-        <v>-0.5</v>
+        <v>-7.3</v>
       </c>
       <c r="D97" s="7">
-        <v>-0.87</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="E97" s="8">
-        <v>-0.37</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="7">
-        <v>-6.15</v>
+        <v>-8.18</v>
       </c>
       <c r="D98" s="7">
-        <v>-5.67</v>
-      </c>
-      <c r="E98" s="9">
-        <v>0.48</v>
+        <v>-8.44</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C99" s="7">
-        <v>29647.9</v>
+        <v>-0.79</v>
       </c>
       <c r="D99" s="7">
-        <v>29620.05</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-27.85</v>
+        <v>-0.47</v>
+      </c>
+      <c r="E99" s="9">
+        <v>0.32</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C100" s="7">
-        <v>9991.65</v>
+        <v>-0.99</v>
       </c>
       <c r="D100" s="7">
-        <v>10011.4</v>
-      </c>
-      <c r="E100" s="9">
-        <v>19.75</v>
+        <v>-1.43</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C101" s="7">
-        <v>12197.35</v>
+        <v>-0.87</v>
       </c>
       <c r="D101" s="7">
-        <v>12229.45</v>
+        <v>-0.79</v>
       </c>
       <c r="E101" s="9">
-        <v>32.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C102" s="7">
-        <v>38749.85</v>
+        <v>-5.67</v>
       </c>
       <c r="D102" s="7">
-        <v>38748.15</v>
+        <v>-6.19</v>
       </c>
       <c r="E102" s="8">
-        <v>-1.7</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C103" s="7">
-        <v>49435.2</v>
+        <v>29620.05</v>
       </c>
       <c r="D103" s="7">
-        <v>49363.6</v>
+        <v>29458.55</v>
       </c>
       <c r="E103" s="8">
-        <v>-71.59999999999999</v>
+        <v>-161.5</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C104" s="7">
-        <v>26466</v>
+        <v>10011.4</v>
       </c>
       <c r="D104" s="7">
-        <v>26545.3</v>
-      </c>
-      <c r="E104" s="9">
-        <v>79.3</v>
+        <v>9927.25</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-84.15000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="7">
-        <v>31547.7</v>
+        <v>12229.45</v>
       </c>
       <c r="D105" s="7">
-        <v>31631.45</v>
-      </c>
-      <c r="E105" s="9">
-        <v>83.75</v>
+        <v>12152.9</v>
+      </c>
+      <c r="E105" s="8">
+        <v>-76.55</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="7">
-        <v>16662.45</v>
+        <v>38748.15</v>
       </c>
       <c r="D106" s="7">
-        <v>16655.5</v>
+        <v>38707.75</v>
       </c>
       <c r="E106" s="8">
-        <v>-6.95</v>
+        <v>-40.4</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="7">
-        <v>9504.15</v>
+        <v>49363.6</v>
       </c>
       <c r="D107" s="7">
-        <v>9465.85</v>
+        <v>48787.85</v>
       </c>
       <c r="E107" s="8">
-        <v>-38.3</v>
+        <v>-575.75</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="7">
-        <v>1555</v>
+        <v>26545.3</v>
       </c>
       <c r="D108" s="7">
-        <v>1559.45</v>
-      </c>
-      <c r="E108" s="9">
-        <v>4.45</v>
+        <v>26432.4</v>
+      </c>
+      <c r="E108" s="8">
+        <v>-112.9</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="7">
-        <v>13189.85</v>
+        <v>31631.45</v>
       </c>
       <c r="D109" s="7">
-        <v>13226.7</v>
+        <v>31823.15</v>
       </c>
       <c r="E109" s="9">
-        <v>36.85</v>
+        <v>191.7</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="7">
-        <v>9922.35</v>
+        <v>16655.5</v>
       </c>
       <c r="D110" s="7">
-        <v>9850.75</v>
+        <v>16608.9</v>
       </c>
       <c r="E110" s="8">
-        <v>-71.59999999999999</v>
+        <v>-46.6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="7">
-        <v>8786.200000000001</v>
+        <v>9465.85</v>
       </c>
       <c r="D111" s="7">
-        <v>8639.799999999999</v>
+        <v>9384.5</v>
       </c>
       <c r="E111" s="8">
-        <v>-146.4</v>
+        <v>-81.34999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="7">
-        <v>26541.8</v>
+        <v>1559.45</v>
       </c>
       <c r="D112" s="7">
-        <v>26479.55</v>
+        <v>1552.75</v>
       </c>
       <c r="E112" s="8">
-        <v>-62.25</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="7">
-        <v>885.95</v>
+        <v>13226.7</v>
       </c>
       <c r="D113" s="7">
-        <v>897.95</v>
-      </c>
-      <c r="E113" s="9">
-        <v>12</v>
+        <v>13100.8</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-125.9</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="7">
-        <v>31265.2</v>
+        <v>9850.75</v>
       </c>
       <c r="D114" s="7">
-        <v>31310.15</v>
-      </c>
-      <c r="E114" s="9">
-        <v>44.95</v>
+        <v>9831.4</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-19.35</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="7">
-        <v>16708.9</v>
+        <v>8639.799999999999</v>
       </c>
       <c r="D115" s="7">
-        <v>16650.95</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-57.95</v>
+        <v>8640.25</v>
+      </c>
+      <c r="E115" s="9">
+        <v>0.45</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="7">
-        <v>9732.15</v>
+        <v>26479.55</v>
       </c>
       <c r="D116" s="7">
-        <v>9635.65</v>
-      </c>
-      <c r="E116" s="8">
-        <v>-96.5</v>
+        <v>26750.45</v>
+      </c>
+      <c r="E116" s="9">
+        <v>270.9</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="7">
-        <v>11312.2</v>
+        <v>897.95</v>
       </c>
       <c r="D117" s="7">
-        <v>11270.45</v>
+        <v>889.1</v>
       </c>
       <c r="E117" s="8">
-        <v>-41.75</v>
+        <v>-8.85</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="7">
-        <v>27392.35</v>
+        <v>31310.15</v>
       </c>
       <c r="D118" s="7">
-        <v>27534.3</v>
-      </c>
-      <c r="E118" s="9">
-        <v>141.95</v>
+        <v>31223.65</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-86.5</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C119" s="7">
-        <v>56</v>
+        <v>16650.95</v>
       </c>
       <c r="D119" s="7">
-        <v>50</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-6</v>
+        <v>16705.05</v>
+      </c>
+      <c r="E119" s="9">
+        <v>54.1</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C120" s="7">
-        <v>50</v>
+        <v>9635.65</v>
       </c>
       <c r="D120" s="7">
-        <v>32</v>
+        <v>9593.4</v>
       </c>
       <c r="E120" s="8">
-        <v>-18</v>
+        <v>-42.25</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C121" s="7">
-        <v>62</v>
+        <v>11270.45</v>
       </c>
       <c r="D121" s="7">
-        <v>44</v>
-      </c>
-      <c r="E121" s="8">
-        <v>-18</v>
+        <v>11279.1</v>
+      </c>
+      <c r="E121" s="9">
+        <v>8.65</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C122" s="7">
-        <v>38</v>
+        <v>27534.3</v>
       </c>
       <c r="D122" s="7">
-        <v>56</v>
-      </c>
-      <c r="E122" s="9">
-        <v>18</v>
+        <v>27380.35</v>
+      </c>
+      <c r="E122" s="8">
+        <v>-153.95</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C123" s="7">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D123" s="7">
-        <v>62</v>
-      </c>
-      <c r="E123" s="9">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C124" s="7">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D124" s="7">
-        <v>38</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-6</v>
+        <v>50</v>
+      </c>
+      <c r="E124" s="9">
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" s="7">
+        <v>44</v>
+      </c>
+      <c r="D125" s="7">
         <v>38</v>
       </c>
-      <c r="B125" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C125" s="7">
-        <v>76.81</v>
-      </c>
-      <c r="D125" s="7">
-        <v>76.2</v>
-      </c>
       <c r="E125" s="8">
-        <v>-0.61</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C126" s="7">
-        <v>58.1</v>
+        <v>38</v>
       </c>
       <c r="D126" s="7">
-        <v>59.57</v>
-      </c>
-      <c r="E126" s="9">
-        <v>1.47</v>
+        <v>32</v>
+      </c>
+      <c r="E126" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C127" s="7">
-        <v>72.45</v>
+        <v>76.2</v>
       </c>
       <c r="D127" s="7">
-        <v>73.58</v>
-      </c>
-      <c r="E127" s="9">
-        <v>1.13</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="E127" s="8">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C128" s="7">
-        <v>41.43</v>
+        <v>59.57</v>
       </c>
       <c r="D128" s="7">
-        <v>41.4</v>
+        <v>51.32</v>
       </c>
       <c r="E128" s="8">
-        <v>-0.03</v>
+        <v>-8.25</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C129" s="7">
-        <v>53.68</v>
+        <v>73.58</v>
       </c>
       <c r="D129" s="7">
-        <v>52.54</v>
+        <v>66.58</v>
       </c>
       <c r="E129" s="8">
-        <v>-1.14</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C130" s="7">
-        <v>45.27</v>
+        <v>41.4</v>
       </c>
       <c r="D130" s="7">
-        <v>47.14</v>
-      </c>
-      <c r="E130" s="9">
-        <v>1.87</v>
+        <v>40.61</v>
+      </c>
+      <c r="E130" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C131" s="7">
-        <v>66.73</v>
+        <v>52.54</v>
       </c>
       <c r="D131" s="7">
-        <v>67.25</v>
-      </c>
-      <c r="E131" s="9">
-        <v>0.52</v>
+        <v>44.39</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-8.15</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="7">
-        <v>73.48999999999999</v>
+        <v>47.14</v>
       </c>
       <c r="D132" s="7">
-        <v>73.02</v>
+        <v>44.8</v>
       </c>
       <c r="E132" s="8">
-        <v>-0.47</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="7">
-        <v>60.04</v>
+        <v>67.25</v>
       </c>
       <c r="D133" s="7">
-        <v>55.75</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-4.29</v>
+        <v>68.47</v>
+      </c>
+      <c r="E133" s="9">
+        <v>1.22</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="7">
-        <v>54.56</v>
+        <v>73.02</v>
       </c>
       <c r="D134" s="7">
-        <v>55.47</v>
-      </c>
-      <c r="E134" s="9">
-        <v>0.91</v>
+        <v>69.8</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-3.22</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="7">
-        <v>68.43000000000001</v>
+        <v>55.75</v>
       </c>
       <c r="D135" s="7">
-        <v>69.39</v>
-      </c>
-      <c r="E135" s="9">
-        <v>0.96</v>
+        <v>47.91</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-7.84</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="7">
-        <v>45.08</v>
+        <v>55.47</v>
       </c>
       <c r="D136" s="7">
-        <v>38.34</v>
+        <v>53.73</v>
       </c>
       <c r="E136" s="8">
-        <v>-6.74</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="7">
-        <v>70.34999999999999</v>
+        <v>69.39</v>
       </c>
       <c r="D137" s="7">
-        <v>59.5</v>
+        <v>62.42</v>
       </c>
       <c r="E137" s="8">
-        <v>-10.85</v>
+        <v>-6.97</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="7">
-        <v>66.27</v>
+        <v>38.34</v>
       </c>
       <c r="D138" s="7">
-        <v>64.05</v>
+        <v>36.74</v>
       </c>
       <c r="E138" s="8">
-        <v>-2.22</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="7">
-        <v>47.45</v>
+        <v>59.5</v>
       </c>
       <c r="D139" s="7">
-        <v>52.54</v>
+        <v>59.52</v>
       </c>
       <c r="E139" s="9">
-        <v>5.09</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="7">
-        <v>50.94</v>
+        <v>64.05</v>
       </c>
       <c r="D140" s="7">
-        <v>52.1</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="E140" s="9">
-        <v>1.16</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="7">
-        <v>63.88</v>
+        <v>52.54</v>
       </c>
       <c r="D141" s="7">
-        <v>60.12</v>
+        <v>48.78</v>
       </c>
       <c r="E141" s="8">
         <v>-3.76</v>
@@ -5711,59 +5756,93 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="7">
-        <v>66.54000000000001</v>
+        <v>52.1</v>
       </c>
       <c r="D142" s="7">
-        <v>60.72</v>
+        <v>49.67</v>
       </c>
       <c r="E142" s="8">
-        <v>-5.82</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="7">
-        <v>57.62</v>
+        <v>60.12</v>
       </c>
       <c r="D143" s="7">
-        <v>54.74</v>
-      </c>
-      <c r="E143" s="8">
-        <v>-2.88</v>
+        <v>62.35</v>
+      </c>
+      <c r="E143" s="9">
+        <v>2.23</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="7">
-        <v>38.86</v>
+        <v>60.72</v>
       </c>
       <c r="D144" s="7">
+        <v>58.31</v>
+      </c>
+      <c r="E144" s="8">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C145" s="7">
+        <v>54.74</v>
+      </c>
+      <c r="D145" s="7">
+        <v>55.24</v>
+      </c>
+      <c r="E145" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C146" s="7">
         <v>42.21</v>
       </c>
-      <c r="E144" s="9">
-        <v>3.35</v>
+      <c r="D146" s="7">
+        <v>39.67</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-2.54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5787,28 +5866,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5822,16 +5901,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>57.8</v>
+        <v>55.1</v>
       </c>
       <c r="E2" s="12">
         <v>50</v>
       </c>
       <c r="F2" s="12">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="G2" s="12">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -5939,10 +6018,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>55</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>45</v>
@@ -5971,34 +6050,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5306000000000001</v>
+        <v>0.5457</v>
       </c>
       <c r="B2" s="15">
-        <v>0.5262</v>
+        <v>0.4797</v>
       </c>
       <c r="C2" s="15">
-        <v>0.4627000000000001</v>
+        <v>0.4289</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2983</v>
+        <v>0.2971</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2387</v>
+        <v>0.2378</v>
       </c>
       <c r="F2" s="15">
-        <v>0.2281</v>
+        <v>0.2238</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1887</v>
+        <v>0.1791</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1801</v>
+        <v>0.1771</v>
       </c>
       <c r="I2" s="15">
-        <v>0.1622</v>
+        <v>0.1589</v>
       </c>
       <c r="J2" s="15">
-        <v>0.1542</v>
+        <v>0.1569</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6006,13 +6085,13 @@
         <v>41</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>51</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>43</v>
@@ -6035,34 +6114,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.1516</v>
+        <v>0.1482</v>
       </c>
       <c r="B4" s="15">
-        <v>0.1365</v>
+        <v>0.1337</v>
       </c>
       <c r="C4" s="15">
-        <v>0.1343</v>
+        <v>0.1336</v>
       </c>
       <c r="D4" s="15">
-        <v>0.128</v>
+        <v>0.1314</v>
       </c>
       <c r="E4" s="15">
-        <v>0.09</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="F4" s="15">
-        <v>0.08</v>
+        <v>0.0803</v>
       </c>
       <c r="G4" s="15">
         <v>0.0643</v>
       </c>
       <c r="H4" s="15">
-        <v>0.062</v>
+        <v>0.0602</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.0163</v>
+        <v>-0.016</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="112">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,67 +289,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>73.6 → 66.6</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>73.6</t>
-  </si>
-  <si>
-    <t>66.6</t>
-  </si>
-  <si>
-    <t>73.0 → 69.8</t>
-  </si>
-  <si>
-    <t>73.0</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.9 → 50.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>50.2</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>69.8 → 70.4</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
   </si>
   <si>
     <t>69.8</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.5 → 44.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.5</t>
-  </si>
-  <si>
-    <t>44.4</t>
-  </si>
-  <si>
-    <t>55.8 → 47.9</t>
-  </si>
-  <si>
-    <t>55.8</t>
-  </si>
-  <si>
-    <t>47.9</t>
-  </si>
-  <si>
-    <t>52.5 → 48.8</t>
-  </si>
-  <si>
-    <t>48.8</t>
-  </si>
-  <si>
-    <t>52.1 → 49.7</t>
-  </si>
-  <si>
-    <t>52.1</t>
-  </si>
-  <si>
-    <t>49.7</t>
+    <t>70.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -435,7 +402,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -443,13 +417,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -482,19 +449,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +542,7 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1093,55 +1060,55 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>29458.55</v>
+        <v>29363.05</v>
       </c>
       <c r="E2">
-        <v>-0.55</v>
+        <v>-0.32</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
       </c>
       <c r="G2">
-        <v>23410.95</v>
+        <v>23474.65</v>
       </c>
       <c r="H2">
-        <v>-0.64</v>
+        <v>-0.96</v>
       </c>
       <c r="I2">
-        <v>25.83</v>
+        <v>25.08</v>
       </c>
       <c r="J2">
-        <v>1.44</v>
+        <v>-0.16</v>
       </c>
       <c r="K2">
-        <v>9.18</v>
+        <v>10.61</v>
       </c>
       <c r="L2">
-        <v>12.68</v>
+        <v>13.42</v>
       </c>
       <c r="M2">
-        <v>24.53</v>
+        <v>25.42</v>
       </c>
       <c r="N2">
-        <v>23.78</v>
+        <v>23.6</v>
       </c>
       <c r="O2">
         <v>93</v>
       </c>
       <c r="Q2">
-        <v>29450.29</v>
+        <v>29440.59</v>
       </c>
       <c r="R2">
-        <v>27989.77</v>
+        <v>28125.67</v>
       </c>
       <c r="S2">
-        <v>27133.24</v>
+        <v>27198.92</v>
       </c>
       <c r="T2">
-        <v>26967.66</v>
+        <v>26978.33</v>
       </c>
       <c r="U2">
-        <v>9.24</v>
+        <v>8.84</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -1156,34 +1123,34 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>72.59999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="AA2">
-        <v>736.88</v>
+        <v>727.34</v>
       </c>
       <c r="AB2">
-        <v>563.83</v>
+        <v>596.53</v>
       </c>
       <c r="AC2">
-        <v>173.05</v>
+        <v>130.81</v>
       </c>
       <c r="AD2">
-        <v>78.06999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="AE2">
-        <v>80.06</v>
+        <v>75.33</v>
       </c>
       <c r="AF2">
-        <v>437.5</v>
+        <v>427.49</v>
       </c>
       <c r="AG2">
         <v>-100</v>
       </c>
       <c r="AH2">
-        <v>30257.56</v>
+        <v>30379.88</v>
       </c>
       <c r="AI2">
-        <v>25721.98</v>
+        <v>25871.45</v>
       </c>
       <c r="AJ2">
         <v>28374.42</v>
@@ -1192,7 +1159,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>63</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1206,10 +1173,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9927.25</v>
+        <v>9920.15</v>
       </c>
       <c r="E3">
-        <v>-0.84</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1218,43 +1185,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-5.48</v>
+        <v>-5.55</v>
       </c>
       <c r="I3">
-        <v>15.81</v>
+        <v>15.73</v>
       </c>
       <c r="J3">
-        <v>-0.02</v>
+        <v>-0.84</v>
       </c>
       <c r="K3">
-        <v>0.87</v>
+        <v>0.59</v>
       </c>
       <c r="L3">
-        <v>-1.8</v>
+        <v>-3.05</v>
       </c>
       <c r="M3">
-        <v>13.52</v>
+        <v>15.09</v>
       </c>
       <c r="N3">
-        <v>13.14</v>
+        <v>13.07</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="Q3">
-        <v>9978.26</v>
+        <v>9961.49</v>
       </c>
       <c r="R3">
-        <v>9882.139999999999</v>
+        <v>9886.860000000001</v>
       </c>
       <c r="S3">
-        <v>9919.65</v>
+        <v>9913.6</v>
       </c>
       <c r="T3">
-        <v>9702.709999999999</v>
+        <v>9706.34</v>
       </c>
       <c r="U3">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -1269,31 +1236,31 @@
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>51.32</v>
+        <v>50.68</v>
       </c>
       <c r="AA3">
-        <v>19.17</v>
+        <v>16.87</v>
       </c>
       <c r="AB3">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="AC3">
-        <v>18.27</v>
+        <v>12.77</v>
       </c>
       <c r="AD3">
-        <v>65.73</v>
+        <v>52.81</v>
       </c>
       <c r="AE3">
-        <v>70.93000000000001</v>
+        <v>63.83</v>
       </c>
       <c r="AF3">
-        <v>87.54000000000001</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="AH3">
-        <v>10028.37</v>
+        <v>10031.52</v>
       </c>
       <c r="AI3">
-        <v>9735.91</v>
+        <v>9742.190000000001</v>
       </c>
       <c r="AJ3">
         <v>10073.2</v>
@@ -1302,7 +1269,7 @@
         <v>82</v>
       </c>
       <c r="AL3">
-        <v>31.34</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1316,10 +1283,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>12152.9</v>
+        <v>12092.2</v>
       </c>
       <c r="E4">
-        <v>-0.63</v>
+        <v>-0.5</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1328,43 +1295,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-3.85</v>
+        <v>-4.33</v>
       </c>
       <c r="I4">
-        <v>17.6</v>
+        <v>17.01</v>
       </c>
       <c r="J4">
-        <v>-0.46</v>
+        <v>-1.07</v>
       </c>
       <c r="K4">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="L4">
-        <v>8.539999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="M4">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="N4">
-        <v>13.37</v>
+        <v>13.21</v>
       </c>
       <c r="O4">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="Q4">
-        <v>12194.81</v>
+        <v>12168.71</v>
       </c>
       <c r="R4">
-        <v>11912.41</v>
+        <v>11935.27</v>
       </c>
       <c r="S4">
-        <v>11656.38</v>
+        <v>11674.89</v>
       </c>
       <c r="T4">
-        <v>11718.82</v>
+        <v>11716.18</v>
       </c>
       <c r="U4">
-        <v>3.7</v>
+        <v>3.21</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -1379,31 +1346,31 @@
         <v>2</v>
       </c>
       <c r="Z4">
-        <v>66.58</v>
+        <v>61.57</v>
       </c>
       <c r="AA4">
-        <v>162.38</v>
+        <v>151.58</v>
       </c>
       <c r="AB4">
-        <v>140.42</v>
+        <v>142.65</v>
       </c>
       <c r="AC4">
-        <v>21.97</v>
+        <v>8.93</v>
       </c>
       <c r="AD4">
-        <v>60.75</v>
+        <v>45.42</v>
       </c>
       <c r="AE4">
-        <v>66.64</v>
+        <v>57.98</v>
       </c>
       <c r="AF4">
-        <v>112.33</v>
+        <v>113.22</v>
       </c>
       <c r="AH4">
-        <v>12414.42</v>
+        <v>12425.59</v>
       </c>
       <c r="AI4">
-        <v>11410.39</v>
+        <v>11444.94</v>
       </c>
       <c r="AJ4">
         <v>11869.84</v>
@@ -1412,7 +1379,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>53.6</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1426,10 +1393,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38707.75</v>
+        <v>38776.9</v>
       </c>
       <c r="E5">
-        <v>-0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1438,43 +1405,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-6.81</v>
+        <v>-6.64</v>
       </c>
       <c r="I5">
-        <v>16.95</v>
+        <v>17.16</v>
       </c>
       <c r="J5">
-        <v>-0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="K5">
-        <v>-1.31</v>
+        <v>-1.09</v>
       </c>
       <c r="L5">
-        <v>-2.11</v>
+        <v>-2.62</v>
       </c>
       <c r="M5">
-        <v>10.23</v>
+        <v>11.14</v>
       </c>
       <c r="N5">
-        <v>14.82</v>
+        <v>14.62</v>
       </c>
       <c r="O5">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q5">
-        <v>38742.17</v>
+        <v>38731.54</v>
       </c>
       <c r="R5">
-        <v>39036.38</v>
+        <v>39006.16</v>
       </c>
       <c r="S5">
-        <v>39428.27</v>
+        <v>39400.01</v>
       </c>
       <c r="T5">
-        <v>37286.91</v>
+        <v>37303.81</v>
       </c>
       <c r="U5">
-        <v>3.81</v>
+        <v>3.95</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1489,34 +1456,34 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>40.61</v>
+        <v>42.63</v>
       </c>
       <c r="AA5">
-        <v>-206.24</v>
+        <v>-197.53</v>
       </c>
       <c r="AB5">
-        <v>-194.91</v>
+        <v>-195.43</v>
       </c>
       <c r="AC5">
-        <v>-11.33</v>
+        <v>-2.1</v>
       </c>
       <c r="AD5">
-        <v>72.19</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AE5">
-        <v>71.31999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="AF5">
-        <v>386.31</v>
+        <v>382.28</v>
       </c>
       <c r="AG5">
         <v>-100</v>
       </c>
       <c r="AH5">
-        <v>39661.61</v>
+        <v>39619.52</v>
       </c>
       <c r="AI5">
-        <v>38411.15</v>
+        <v>38392.81</v>
       </c>
       <c r="AJ5">
         <v>39538.76</v>
@@ -1525,7 +1492,7 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>12.06</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1539,10 +1506,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>48787.85</v>
+        <v>48429.35</v>
       </c>
       <c r="E6">
-        <v>-1.17</v>
+        <v>-0.73</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1551,43 +1518,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-14.56</v>
+        <v>-15.19</v>
       </c>
       <c r="I6">
-        <v>7.14</v>
+        <v>6.35</v>
       </c>
       <c r="J6">
-        <v>-1.49</v>
+        <v>-1.93</v>
       </c>
       <c r="K6">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="L6">
-        <v>-3.3</v>
+        <v>-4.3</v>
       </c>
       <c r="M6">
-        <v>-12.59</v>
+        <v>-13.82</v>
       </c>
       <c r="N6">
-        <v>6.02</v>
+        <v>5.81</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>49268</v>
+        <v>49077.17</v>
       </c>
       <c r="R6">
-        <v>49001.44</v>
+        <v>49008.58</v>
       </c>
       <c r="S6">
-        <v>49076.3</v>
+        <v>49072.63</v>
       </c>
       <c r="T6">
-        <v>51347.89</v>
+        <v>51306.95</v>
       </c>
       <c r="U6">
-        <v>-4.99</v>
+        <v>-5.61</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -1602,34 +1569,34 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>44.39</v>
+        <v>40.21</v>
       </c>
       <c r="AA6">
-        <v>32.57</v>
+        <v>-31.78</v>
       </c>
       <c r="AB6">
-        <v>13.21</v>
+        <v>4.21</v>
       </c>
       <c r="AC6">
-        <v>19.37</v>
+        <v>-35.99</v>
       </c>
       <c r="AD6">
-        <v>33.85</v>
+        <v>15.79</v>
       </c>
       <c r="AE6">
-        <v>45.04</v>
+        <v>33.27</v>
       </c>
       <c r="AF6">
-        <v>626.3099999999999</v>
+        <v>623.89</v>
       </c>
       <c r="AG6">
         <v>-100</v>
       </c>
       <c r="AH6">
-        <v>49885.86</v>
+        <v>49870.72</v>
       </c>
       <c r="AI6">
-        <v>48117.01</v>
+        <v>48146.44</v>
       </c>
       <c r="AJ6">
         <v>50224.74</v>
@@ -1638,7 +1605,7 @@
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>23.49</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1652,10 +1619,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26432.4</v>
+        <v>26426.75</v>
       </c>
       <c r="E7">
-        <v>-0.43</v>
+        <v>-0.02</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1664,40 +1631,40 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-7.13</v>
+        <v>-7.15</v>
       </c>
       <c r="I7">
-        <v>12.37</v>
+        <v>12.35</v>
       </c>
       <c r="J7">
-        <v>-1.54</v>
+        <v>-1.55</v>
       </c>
       <c r="K7">
-        <v>-1.5</v>
+        <v>-0.41</v>
       </c>
       <c r="L7">
-        <v>5.15</v>
+        <v>5.22</v>
       </c>
       <c r="M7">
-        <v>-0.82</v>
+        <v>-0.25</v>
       </c>
       <c r="N7">
-        <v>9.039999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="O7">
         <v>26</v>
       </c>
       <c r="Q7">
-        <v>26630.22</v>
+        <v>26546.79</v>
       </c>
       <c r="R7">
-        <v>26760.29</v>
+        <v>26746.96</v>
       </c>
       <c r="S7">
-        <v>26412.07</v>
+        <v>26443.38</v>
       </c>
       <c r="T7">
-        <v>26743.73</v>
+        <v>26738.17</v>
       </c>
       <c r="U7">
         <v>-1.16</v>
@@ -1715,34 +1682,34 @@
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>44.8</v>
+        <v>44.68</v>
       </c>
       <c r="AA7">
-        <v>16.32</v>
+        <v>-4.63</v>
       </c>
       <c r="AB7">
-        <v>81.42</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="AC7">
-        <v>-65.11</v>
+        <v>-68.84</v>
       </c>
       <c r="AD7">
-        <v>30.32</v>
+        <v>29.2</v>
       </c>
       <c r="AE7">
-        <v>46.12</v>
+        <v>35.79</v>
       </c>
       <c r="AF7">
-        <v>349.63</v>
+        <v>338.31</v>
       </c>
       <c r="AG7">
         <v>-100</v>
       </c>
       <c r="AH7">
-        <v>27178.87</v>
+        <v>27190.73</v>
       </c>
       <c r="AI7">
-        <v>26341.71</v>
+        <v>26303.18</v>
       </c>
       <c r="AJ7">
         <v>26067.59</v>
@@ -1751,7 +1718,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>21.18</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1765,10 +1732,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31823.15</v>
+        <v>31332.55</v>
       </c>
       <c r="E8">
-        <v>0.61</v>
+        <v>-1.54</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1777,43 +1744,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-19.41</v>
+        <v>-20.65</v>
       </c>
       <c r="I8">
-        <v>23.49</v>
+        <v>21.59</v>
       </c>
       <c r="J8">
-        <v>1.17</v>
+        <v>-0.23</v>
       </c>
       <c r="K8">
-        <v>9.68</v>
+        <v>9.08</v>
       </c>
       <c r="L8">
-        <v>12.71</v>
+        <v>12.24</v>
       </c>
       <c r="M8">
-        <v>-9.85</v>
+        <v>-9.57</v>
       </c>
       <c r="N8">
-        <v>0.1</v>
+        <v>-0.57</v>
       </c>
       <c r="O8">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Q8">
-        <v>31522.02</v>
+        <v>31507.72</v>
       </c>
       <c r="R8">
-        <v>30207.27</v>
+        <v>30347.29</v>
       </c>
       <c r="S8">
-        <v>28888.11</v>
+        <v>28892.43</v>
       </c>
       <c r="T8">
-        <v>32628.99</v>
+        <v>32610.9</v>
       </c>
       <c r="U8">
-        <v>-2.47</v>
+        <v>-3.92</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -1828,34 +1795,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>68.47</v>
+        <v>62.09</v>
       </c>
       <c r="AA8">
-        <v>901.45</v>
+        <v>860.9</v>
       </c>
       <c r="AB8">
-        <v>777.33</v>
+        <v>794.04</v>
       </c>
       <c r="AC8">
-        <v>124.12</v>
+        <v>66.86</v>
       </c>
       <c r="AD8">
-        <v>82.19</v>
+        <v>71.67</v>
       </c>
       <c r="AE8">
-        <v>77.27</v>
+        <v>76.33</v>
       </c>
       <c r="AF8">
-        <v>661.77</v>
+        <v>673.4400000000001</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32785.13</v>
+        <v>32845.03</v>
       </c>
       <c r="AI8">
-        <v>27629.41</v>
+        <v>27849.54</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1864,7 +1831,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>32.18</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1878,10 +1845,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16608.9</v>
+        <v>16630.45</v>
       </c>
       <c r="E9">
-        <v>-0.28</v>
+        <v>0.13</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1890,25 +1857,25 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-0.32</v>
+        <v>-0.19</v>
       </c>
       <c r="I9">
-        <v>6.04</v>
+        <v>6.18</v>
       </c>
       <c r="J9">
-        <v>0.68</v>
+        <v>0.23</v>
       </c>
       <c r="K9">
-        <v>4.46</v>
+        <v>4.92</v>
       </c>
       <c r="N9">
-        <v>42.89</v>
+        <v>43.17</v>
       </c>
       <c r="Q9">
-        <v>16621.61</v>
+        <v>16629.39</v>
       </c>
       <c r="R9">
-        <v>16211.29</v>
+        <v>16247.22</v>
       </c>
       <c r="X9" t="s">
         <v>80</v>
@@ -1917,31 +1884,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>69.8</v>
+        <v>70.44</v>
       </c>
       <c r="AA9">
-        <v>198.37</v>
+        <v>199.76</v>
       </c>
       <c r="AB9">
-        <v>147.64</v>
+        <v>158.07</v>
       </c>
       <c r="AC9">
-        <v>50.73</v>
+        <v>41.69</v>
       </c>
       <c r="AD9">
-        <v>94.79000000000001</v>
+        <v>90.98</v>
       </c>
       <c r="AE9">
-        <v>97.95999999999999</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="AF9">
-        <v>136.48</v>
+        <v>134.78</v>
       </c>
       <c r="AH9">
-        <v>16817.58</v>
+        <v>16863.89</v>
       </c>
       <c r="AI9">
-        <v>15605</v>
+        <v>15630.55</v>
       </c>
       <c r="AJ9">
         <v>16247.16</v>
@@ -1950,7 +1917,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>46.15</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1964,10 +1931,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9384.5</v>
+        <v>9409.799999999999</v>
       </c>
       <c r="E10">
-        <v>-0.86</v>
+        <v>0.27</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1976,43 +1943,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-3.9</v>
+        <v>-3.64</v>
       </c>
       <c r="I10">
-        <v>9.619999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="J10">
-        <v>-0.37</v>
+        <v>-0.45</v>
       </c>
       <c r="K10">
-        <v>0.04</v>
+        <v>0.63</v>
       </c>
       <c r="L10">
-        <v>2.52</v>
+        <v>1.86</v>
       </c>
       <c r="M10">
-        <v>3.51</v>
+        <v>4.91</v>
       </c>
       <c r="N10">
-        <v>15.89</v>
+        <v>15.75</v>
       </c>
       <c r="O10">
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>9452.110000000001</v>
+        <v>9443.52</v>
       </c>
       <c r="R10">
-        <v>9400.370000000001</v>
+        <v>9403.969999999999</v>
       </c>
       <c r="S10">
-        <v>9369.02</v>
+        <v>9372.690000000001</v>
       </c>
       <c r="T10">
-        <v>9363.08</v>
+        <v>9363.440000000001</v>
       </c>
       <c r="U10">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -2027,34 +1994,34 @@
         <v>3</v>
       </c>
       <c r="Z10">
-        <v>47.91</v>
+        <v>50.25</v>
       </c>
       <c r="AA10">
-        <v>19.2</v>
+        <v>16.38</v>
       </c>
       <c r="AB10">
-        <v>16.09</v>
+        <v>16.15</v>
       </c>
       <c r="AC10">
-        <v>3.1</v>
+        <v>0.23</v>
       </c>
       <c r="AD10">
-        <v>49.98</v>
+        <v>30.06</v>
       </c>
       <c r="AE10">
-        <v>60.79</v>
+        <v>48.73</v>
       </c>
       <c r="AF10">
-        <v>87.17</v>
+        <v>88.62</v>
       </c>
       <c r="AG10">
         <v>-100</v>
       </c>
       <c r="AH10">
-        <v>9502.309999999999</v>
+        <v>9501.6</v>
       </c>
       <c r="AI10">
-        <v>9298.440000000001</v>
+        <v>9306.35</v>
       </c>
       <c r="AJ10">
         <v>9229.360000000001</v>
@@ -2063,7 +2030,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>24.98</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2077,10 +2044,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1552.75</v>
+        <v>1569.1</v>
       </c>
       <c r="E11">
-        <v>-0.43</v>
+        <v>1.05</v>
       </c>
       <c r="F11">
         <v>1671.5</v>
@@ -2089,43 +2056,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-7.1</v>
+        <v>-6.13</v>
       </c>
       <c r="I11">
-        <v>23.89</v>
+        <v>25.19</v>
       </c>
       <c r="J11">
-        <v>-2.98</v>
+        <v>-0.38</v>
       </c>
       <c r="K11">
-        <v>2.47</v>
+        <v>3.87</v>
       </c>
       <c r="L11">
-        <v>11.2</v>
+        <v>12.42</v>
       </c>
       <c r="M11">
-        <v>-4.53</v>
+        <v>-2.95</v>
       </c>
       <c r="N11">
-        <v>-1.6</v>
+        <v>-1.84</v>
       </c>
       <c r="O11">
         <v>56</v>
       </c>
       <c r="Q11">
-        <v>1561.15</v>
+        <v>1559.94</v>
       </c>
       <c r="R11">
-        <v>1544.86</v>
+        <v>1548.13</v>
       </c>
       <c r="S11">
-        <v>1511.84</v>
+        <v>1514.64</v>
       </c>
       <c r="T11">
-        <v>1442.31</v>
+        <v>1442.55</v>
       </c>
       <c r="U11">
-        <v>7.66</v>
+        <v>8.77</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -2140,31 +2107,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>53.73</v>
+        <v>57.25</v>
       </c>
       <c r="AA11">
-        <v>18.06</v>
+        <v>17.67</v>
       </c>
       <c r="AB11">
-        <v>19.74</v>
+        <v>19.33</v>
       </c>
       <c r="AC11">
-        <v>-1.68</v>
+        <v>-1.66</v>
       </c>
       <c r="AD11">
-        <v>1.28</v>
+        <v>6.07</v>
       </c>
       <c r="AE11">
-        <v>1.81</v>
+        <v>2.87</v>
       </c>
       <c r="AF11">
-        <v>31.75</v>
+        <v>32</v>
       </c>
       <c r="AH11">
-        <v>1609.05</v>
+        <v>1610.11</v>
       </c>
       <c r="AI11">
-        <v>1480.67</v>
+        <v>1486.14</v>
       </c>
       <c r="AJ11">
         <v>1508.92</v>
@@ -2173,7 +2140,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>35.4</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2187,55 +2154,55 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13100.8</v>
+        <v>13171.45</v>
       </c>
       <c r="E12">
-        <v>-0.95</v>
+        <v>0.54</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
       </c>
       <c r="G12">
-        <v>9102.35</v>
+        <v>9147.1</v>
       </c>
       <c r="H12">
-        <v>-4.5</v>
+        <v>-3.99</v>
       </c>
       <c r="I12">
-        <v>43.93</v>
+        <v>44</v>
       </c>
       <c r="J12">
-        <v>0.53</v>
+        <v>-0.64</v>
       </c>
       <c r="K12">
-        <v>3.96</v>
+        <v>3.89</v>
       </c>
       <c r="L12">
-        <v>1.7</v>
+        <v>-0.9</v>
       </c>
       <c r="M12">
-        <v>41.09</v>
+        <v>44.7</v>
       </c>
       <c r="N12">
-        <v>17.91</v>
+        <v>17.95</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13183.46</v>
+        <v>13166.48</v>
       </c>
       <c r="R12">
-        <v>12712.51</v>
+        <v>12744.24</v>
       </c>
       <c r="S12">
-        <v>12777.9</v>
+        <v>12770.18</v>
       </c>
       <c r="T12">
-        <v>11886.46</v>
+        <v>11901.32</v>
       </c>
       <c r="U12">
-        <v>10.22</v>
+        <v>10.67</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
@@ -2250,34 +2217,34 @@
         <v>2</v>
       </c>
       <c r="Z12">
-        <v>62.42</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="AA12">
-        <v>138.77</v>
+        <v>145.83</v>
       </c>
       <c r="AB12">
-        <v>60.85</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="AC12">
-        <v>77.91</v>
+        <v>67.98</v>
       </c>
       <c r="AD12">
-        <v>79</v>
+        <v>75.02</v>
       </c>
       <c r="AE12">
-        <v>83.73999999999999</v>
+        <v>79.33</v>
       </c>
       <c r="AF12">
-        <v>193.51</v>
+        <v>191.3</v>
       </c>
       <c r="AG12">
         <v>-100</v>
       </c>
       <c r="AH12">
-        <v>13366.09</v>
+        <v>13423.04</v>
       </c>
       <c r="AI12">
-        <v>12058.94</v>
+        <v>12065.44</v>
       </c>
       <c r="AJ12">
         <v>12652.05</v>
@@ -2286,7 +2253,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>50.94</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2300,10 +2267,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9831.4</v>
+        <v>9869.25</v>
       </c>
       <c r="E13">
-        <v>-0.2</v>
+        <v>0.38</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2312,43 +2279,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-8.68</v>
+        <v>-8.33</v>
       </c>
       <c r="I13">
-        <v>6.83</v>
+        <v>7.25</v>
       </c>
       <c r="J13">
-        <v>-1.07</v>
+        <v>-0.83</v>
       </c>
       <c r="K13">
-        <v>-1.27</v>
+        <v>-0.54</v>
       </c>
       <c r="L13">
-        <v>-5.87</v>
+        <v>-6.62</v>
       </c>
       <c r="M13">
-        <v>1.54</v>
+        <v>3.48</v>
       </c>
       <c r="N13">
-        <v>22.38</v>
+        <v>22.11</v>
       </c>
       <c r="O13">
         <v>13</v>
       </c>
       <c r="Q13">
-        <v>9898.67</v>
+        <v>9882.23</v>
       </c>
       <c r="R13">
-        <v>9927.219999999999</v>
+        <v>9924.940000000001</v>
       </c>
       <c r="S13">
-        <v>9977.129999999999</v>
+        <v>9972.870000000001</v>
       </c>
       <c r="T13">
-        <v>10050</v>
+        <v>10049.87</v>
       </c>
       <c r="U13">
-        <v>-2.18</v>
+        <v>-1.8</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -2363,43 +2330,43 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>36.74</v>
+        <v>41.85</v>
       </c>
       <c r="AA13">
-        <v>-31.07</v>
+        <v>-32.17</v>
       </c>
       <c r="AB13">
-        <v>-27.93</v>
+        <v>-28.78</v>
       </c>
       <c r="AC13">
-        <v>-3.14</v>
+        <v>-3.39</v>
       </c>
       <c r="AD13">
-        <v>12.34</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AE13">
-        <v>29.63</v>
+        <v>16.9</v>
       </c>
       <c r="AF13">
-        <v>92.17</v>
+        <v>93.78</v>
       </c>
       <c r="AG13">
         <v>-100</v>
       </c>
       <c r="AH13">
-        <v>9999.65</v>
+        <v>10001.75</v>
       </c>
       <c r="AI13">
-        <v>9854.799999999999</v>
+        <v>9848.139999999999</v>
       </c>
       <c r="AJ13">
-        <v>10104.9</v>
+        <v>10093.21</v>
       </c>
       <c r="AK13" t="s">
         <v>82</v>
       </c>
       <c r="AL13">
-        <v>20.93</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2413,10 +2380,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8640.25</v>
+        <v>8817.5</v>
       </c>
       <c r="E14">
-        <v>0.01</v>
+        <v>2.05</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2425,43 +2392,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-12.55</v>
+        <v>-10.75</v>
       </c>
       <c r="I14">
-        <v>27.89</v>
+        <v>30.51</v>
       </c>
       <c r="J14">
-        <v>1.89</v>
+        <v>3.23</v>
       </c>
       <c r="K14">
-        <v>2.12</v>
+        <v>6.13</v>
       </c>
       <c r="L14">
-        <v>7.05</v>
+        <v>9.34</v>
       </c>
       <c r="M14">
-        <v>26.12</v>
+        <v>30.18</v>
       </c>
       <c r="N14">
-        <v>29.71</v>
+        <v>29.91</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8667.360000000001</v>
+        <v>8722.6</v>
       </c>
       <c r="R14">
-        <v>8458.440000000001</v>
+        <v>8479.969999999999</v>
       </c>
       <c r="S14">
-        <v>8449.030000000001</v>
+        <v>8464.4</v>
       </c>
       <c r="T14">
-        <v>8554.5</v>
+        <v>8560.4</v>
       </c>
       <c r="U14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -2476,34 +2443,34 @@
         <v>2</v>
       </c>
       <c r="Z14">
-        <v>59.52</v>
+        <v>66.72</v>
       </c>
       <c r="AA14">
-        <v>67.44</v>
+        <v>83.45</v>
       </c>
       <c r="AB14">
-        <v>32.81</v>
+        <v>42.94</v>
       </c>
       <c r="AC14">
-        <v>34.63</v>
+        <v>40.51</v>
       </c>
       <c r="AD14">
-        <v>71.16</v>
+        <v>66.34</v>
       </c>
       <c r="AE14">
-        <v>85.58</v>
+        <v>74.36</v>
       </c>
       <c r="AF14">
-        <v>137.53</v>
+        <v>142.56</v>
       </c>
       <c r="AG14">
         <v>-100</v>
       </c>
       <c r="AH14">
-        <v>8730.1</v>
+        <v>8792.879999999999</v>
       </c>
       <c r="AI14">
-        <v>8186.78</v>
+        <v>8167.06</v>
       </c>
       <c r="AJ14">
         <v>8374.41</v>
@@ -2512,7 +2479,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>38.53</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2526,13 +2493,13 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26750.45</v>
+        <v>26762.5</v>
       </c>
       <c r="E15">
-        <v>1.02</v>
+        <v>0.05</v>
       </c>
       <c r="F15">
-        <v>26750.45</v>
+        <v>26762.5</v>
       </c>
       <c r="G15">
         <v>21402.15</v>
@@ -2541,40 +2508,40 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>24.99</v>
+        <v>25.05</v>
       </c>
       <c r="J15">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="K15">
-        <v>4.32</v>
+        <v>3.3</v>
       </c>
       <c r="L15">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="M15">
-        <v>17.48</v>
+        <v>21.58</v>
       </c>
       <c r="N15">
-        <v>13.36</v>
+        <v>13.62</v>
       </c>
       <c r="O15">
         <v>81</v>
       </c>
       <c r="Q15">
-        <v>26580.03</v>
+        <v>26619.82</v>
       </c>
       <c r="R15">
-        <v>26203.29</v>
+        <v>26241.24</v>
       </c>
       <c r="S15">
-        <v>25390.49</v>
+        <v>25445.61</v>
       </c>
       <c r="T15">
-        <v>23424.17</v>
+        <v>23446.71</v>
       </c>
       <c r="U15">
-        <v>14.2</v>
+        <v>14.14</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2589,43 +2556,43 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>68.93000000000001</v>
+        <v>69.13</v>
       </c>
       <c r="AA15">
-        <v>350.89</v>
+        <v>351.87</v>
       </c>
       <c r="AB15">
-        <v>350.89</v>
+        <v>351.08</v>
       </c>
       <c r="AC15">
-        <v>-0</v>
+        <v>0.79</v>
       </c>
       <c r="AD15">
-        <v>78.70999999999999</v>
+        <v>84.31</v>
       </c>
       <c r="AE15">
-        <v>78.23999999999999</v>
+        <v>79.36</v>
       </c>
       <c r="AF15">
-        <v>323.36</v>
+        <v>314.27</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>26965.76</v>
+        <v>27036.68</v>
       </c>
       <c r="AI15">
-        <v>25440.83</v>
+        <v>25445.79</v>
       </c>
       <c r="AJ15">
-        <v>25649.77</v>
+        <v>25756.98</v>
       </c>
       <c r="AK15" t="s">
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>47.28</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2639,10 +2606,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>889.1</v>
+        <v>889.8</v>
       </c>
       <c r="E16">
-        <v>-0.99</v>
+        <v>0.08</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2651,43 +2618,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-8.210000000000001</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="I16">
-        <v>36.54</v>
+        <v>36.65</v>
       </c>
       <c r="J16">
-        <v>-0.24</v>
+        <v>-0.99</v>
       </c>
       <c r="K16">
-        <v>-5.13</v>
+        <v>-3.14</v>
       </c>
       <c r="L16">
-        <v>16.12</v>
+        <v>16.43</v>
       </c>
       <c r="M16">
-        <v>-2.55</v>
+        <v>-0.71</v>
       </c>
       <c r="N16">
-        <v>17.71</v>
+        <v>17.45</v>
       </c>
       <c r="O16">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="Q16">
-        <v>891.71</v>
+        <v>889.9299999999999</v>
       </c>
       <c r="R16">
-        <v>907.67</v>
+        <v>906.4</v>
       </c>
       <c r="S16">
-        <v>859.55</v>
+        <v>861.88</v>
       </c>
       <c r="T16">
-        <v>835.23</v>
+        <v>835.01</v>
       </c>
       <c r="U16">
-        <v>6.45</v>
+        <v>6.56</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
@@ -2702,34 +2669,34 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>48.78</v>
+        <v>49.09</v>
       </c>
       <c r="AA16">
-        <v>5.63</v>
+        <v>4.52</v>
       </c>
       <c r="AB16">
-        <v>12.19</v>
+        <v>10.65</v>
       </c>
       <c r="AC16">
-        <v>-6.56</v>
+        <v>-6.13</v>
       </c>
       <c r="AD16">
-        <v>11.97</v>
+        <v>15.04</v>
       </c>
       <c r="AE16">
-        <v>9.27</v>
+        <v>12.16</v>
       </c>
       <c r="AF16">
-        <v>19.07</v>
+        <v>18.79</v>
       </c>
       <c r="AG16">
         <v>-100</v>
       </c>
       <c r="AH16">
-        <v>932.73</v>
+        <v>932.42</v>
       </c>
       <c r="AI16">
-        <v>882.6</v>
+        <v>880.38</v>
       </c>
       <c r="AJ16">
         <v>864.8</v>
@@ -2738,7 +2705,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>18.01</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2752,10 +2719,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>31223.65</v>
+        <v>31178.55</v>
       </c>
       <c r="E17">
-        <v>-0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2764,43 +2731,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-8.44</v>
+        <v>-8.57</v>
       </c>
       <c r="I17">
-        <v>10.08</v>
+        <v>9.92</v>
       </c>
       <c r="J17">
-        <v>-1.22</v>
+        <v>-1.21</v>
       </c>
       <c r="K17">
-        <v>-0.15</v>
+        <v>0.4</v>
       </c>
       <c r="L17">
-        <v>6.48</v>
+        <v>6.51</v>
       </c>
       <c r="M17">
-        <v>-4.63</v>
+        <v>-3.86</v>
       </c>
       <c r="N17">
-        <v>6.43</v>
+        <v>6.24</v>
       </c>
       <c r="O17">
         <v>19</v>
       </c>
       <c r="Q17">
-        <v>31372.66</v>
+        <v>31296.43</v>
       </c>
       <c r="R17">
-        <v>31395.16</v>
+        <v>31396.6</v>
       </c>
       <c r="S17">
-        <v>30816.32</v>
+        <v>30846.71</v>
       </c>
       <c r="T17">
-        <v>31857.61</v>
+        <v>31846.2</v>
       </c>
       <c r="U17">
-        <v>-1.99</v>
+        <v>-2.1</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
@@ -2815,34 +2782,34 @@
         <v>1</v>
       </c>
       <c r="Z17">
-        <v>49.67</v>
+        <v>48.41</v>
       </c>
       <c r="AA17">
-        <v>128.65</v>
+        <v>103.4</v>
       </c>
       <c r="AB17">
-        <v>188.87</v>
+        <v>171.77</v>
       </c>
       <c r="AC17">
-        <v>-60.21</v>
+        <v>-68.37</v>
       </c>
       <c r="AD17">
         <v>2.5</v>
       </c>
       <c r="AE17">
-        <v>15</v>
+        <v>6.46</v>
       </c>
       <c r="AF17">
-        <v>311.59</v>
+        <v>310.44</v>
       </c>
       <c r="AG17">
         <v>-100</v>
       </c>
       <c r="AH17">
-        <v>31722.17</v>
+        <v>31719.3</v>
       </c>
       <c r="AI17">
-        <v>31068.15</v>
+        <v>31073.9</v>
       </c>
       <c r="AJ17">
         <v>30549.87</v>
@@ -2851,7 +2818,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>23.26</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2865,10 +2832,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16705.05</v>
+        <v>16632.35</v>
       </c>
       <c r="E18">
-        <v>0.32</v>
+        <v>-0.44</v>
       </c>
       <c r="F18">
         <v>16783.35</v>
@@ -2877,25 +2844,25 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-0.47</v>
+        <v>-0.9</v>
       </c>
       <c r="I18">
-        <v>8.449999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="J18">
-        <v>-0.25</v>
+        <v>-0.46</v>
       </c>
       <c r="K18">
-        <v>2.51</v>
+        <v>1.16</v>
       </c>
       <c r="N18">
-        <v>54.57</v>
+        <v>49.52</v>
       </c>
       <c r="Q18">
-        <v>16698.35</v>
+        <v>16682.84</v>
       </c>
       <c r="R18">
-        <v>16567.41</v>
+        <v>16573.63</v>
       </c>
       <c r="X18" t="s">
         <v>80</v>
@@ -2904,31 +2871,31 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>62.35</v>
+        <v>57.68</v>
       </c>
       <c r="AA18">
-        <v>153.36</v>
+        <v>140.78</v>
       </c>
       <c r="AB18">
-        <v>167.3</v>
+        <v>161.99</v>
       </c>
       <c r="AC18">
-        <v>-13.94</v>
+        <v>-21.21</v>
       </c>
       <c r="AD18">
-        <v>61.56</v>
+        <v>48.95</v>
       </c>
       <c r="AE18">
-        <v>67.09</v>
+        <v>58.75</v>
       </c>
       <c r="AF18">
-        <v>188.78</v>
+        <v>189.41</v>
       </c>
       <c r="AH18">
-        <v>16916.07</v>
+        <v>16922.26</v>
       </c>
       <c r="AI18">
-        <v>16218.75</v>
+        <v>16225.01</v>
       </c>
       <c r="AJ18">
         <v>16199.38</v>
@@ -2937,7 +2904,7 @@
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>22.15</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2951,10 +2918,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9593.4</v>
+        <v>9660.700000000001</v>
       </c>
       <c r="E19">
-        <v>-0.44</v>
+        <v>0.7</v>
       </c>
       <c r="F19">
         <v>9732.15</v>
@@ -2963,25 +2930,25 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-1.43</v>
+        <v>-0.73</v>
       </c>
       <c r="I19">
-        <v>6.65</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>1.84</v>
+        <v>2.81</v>
       </c>
       <c r="K19">
-        <v>1.9</v>
+        <v>3.59</v>
       </c>
       <c r="N19">
-        <v>47.97</v>
+        <v>53.31</v>
       </c>
       <c r="Q19">
-        <v>9604.700000000001</v>
+        <v>9657.6</v>
       </c>
       <c r="R19">
-        <v>9409.15</v>
+        <v>9425.629999999999</v>
       </c>
       <c r="X19" t="s">
         <v>80</v>
@@ -2990,31 +2957,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>58.31</v>
+        <v>60.96</v>
       </c>
       <c r="AA19">
-        <v>67.84999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AB19">
-        <v>35.82</v>
+        <v>43.78</v>
       </c>
       <c r="AC19">
-        <v>32.02</v>
+        <v>31.82</v>
       </c>
       <c r="AD19">
-        <v>81.78</v>
+        <v>74.55</v>
       </c>
       <c r="AE19">
-        <v>89.45999999999999</v>
+        <v>82.92</v>
       </c>
       <c r="AF19">
-        <v>149.68</v>
+        <v>151.37</v>
       </c>
       <c r="AH19">
-        <v>9705.18</v>
+        <v>9739.52</v>
       </c>
       <c r="AI19">
-        <v>9113.120000000001</v>
+        <v>9111.74</v>
       </c>
       <c r="AJ19">
         <v>9264.24</v>
@@ -3023,7 +2990,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>24.11</v>
+        <v>23.22</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3037,10 +3004,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11279.1</v>
+        <v>11293.9</v>
       </c>
       <c r="E20">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3049,25 +3016,25 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-0.79</v>
+        <v>-0.66</v>
       </c>
       <c r="I20">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="J20">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K20">
-        <v>0.92</v>
+        <v>1.72</v>
       </c>
       <c r="N20">
-        <v>15.69</v>
+        <v>16.32</v>
       </c>
       <c r="Q20">
-        <v>11276.42</v>
+        <v>11291.99</v>
       </c>
       <c r="R20">
-        <v>11217.99</v>
+        <v>11223.74</v>
       </c>
       <c r="X20" t="s">
         <v>80</v>
@@ -3076,31 +3043,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>55.24</v>
+        <v>56.13</v>
       </c>
       <c r="AA20">
-        <v>37.02</v>
+        <v>38.43</v>
       </c>
       <c r="AB20">
-        <v>27.92</v>
+        <v>30.02</v>
       </c>
       <c r="AC20">
-        <v>9.1</v>
+        <v>8.41</v>
       </c>
       <c r="AD20">
-        <v>65.27</v>
+        <v>62.38</v>
       </c>
       <c r="AE20">
-        <v>65.12</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="AF20">
-        <v>132.06</v>
+        <v>131.11</v>
       </c>
       <c r="AH20">
-        <v>11413.92</v>
+        <v>11421.58</v>
       </c>
       <c r="AI20">
-        <v>11022.06</v>
+        <v>11025.9</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3109,7 +3076,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>14.35</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3123,10 +3090,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27380.35</v>
+        <v>27408.4</v>
       </c>
       <c r="E21">
-        <v>-0.5600000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3135,43 +3102,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.19</v>
+        <v>-6.1</v>
       </c>
       <c r="I21">
-        <v>13.4</v>
+        <v>13.52</v>
       </c>
       <c r="J21">
-        <v>-1.72</v>
+        <v>-1.21</v>
       </c>
       <c r="K21">
-        <v>-2.75</v>
+        <v>-1.82</v>
       </c>
       <c r="L21">
-        <v>5.75</v>
+        <v>6.01</v>
       </c>
       <c r="M21">
-        <v>1.09</v>
+        <v>1.81</v>
       </c>
       <c r="N21">
-        <v>8.029999999999999</v>
+        <v>7.99</v>
       </c>
       <c r="O21">
         <v>32</v>
       </c>
       <c r="Q21">
-        <v>27546.23</v>
+        <v>27479.06</v>
       </c>
       <c r="R21">
-        <v>28058.45</v>
+        <v>28028.75</v>
       </c>
       <c r="S21">
-        <v>27769.88</v>
+        <v>27797.82</v>
       </c>
       <c r="T21">
-        <v>27692.2</v>
+        <v>27688.04</v>
       </c>
       <c r="U21">
-        <v>-1.13</v>
+        <v>-1.01</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
@@ -3186,31 +3153,31 @@
         <v>2</v>
       </c>
       <c r="Z21">
-        <v>39.67</v>
+        <v>40.37</v>
       </c>
       <c r="AA21">
-        <v>-108.75</v>
+        <v>-129.13</v>
       </c>
       <c r="AB21">
-        <v>13.51</v>
+        <v>-15.02</v>
       </c>
       <c r="AC21">
-        <v>-122.26</v>
+        <v>-114.11</v>
       </c>
       <c r="AD21">
-        <v>8.109999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="AE21">
-        <v>12.91</v>
+        <v>10.62</v>
       </c>
       <c r="AF21">
-        <v>441.73</v>
+        <v>424.93</v>
       </c>
       <c r="AH21">
-        <v>28963.23</v>
+        <v>28979.12</v>
       </c>
       <c r="AI21">
-        <v>27153.67</v>
+        <v>27078.37</v>
       </c>
       <c r="AJ21">
         <v>27330.14</v>
@@ -3219,7 +3186,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>24.53</v>
+        <v>25.85</v>
       </c>
     </row>
   </sheetData>
@@ -3360,7 +3327,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3400,7 +3367,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3419,2430 +3386,2367 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>109</v>
+      <c r="A8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7">
+        <v>9.18</v>
+      </c>
+      <c r="D8" s="7">
+        <v>10.61</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.59</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="7">
+        <v>4.16</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4.14</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>114</v>
+      <c r="A11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-1.31</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-1.09</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.22</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="7">
-        <v>10.27</v>
+        <v>-0.05</v>
       </c>
       <c r="D12" s="7">
-        <v>9.18</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.09</v>
+        <v>-0.2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="7">
-        <v>1.21</v>
+        <v>-1.5</v>
       </c>
       <c r="D13" s="7">
-        <v>0.87</v>
+        <v>-0.41</v>
       </c>
       <c r="E13" s="8">
-        <v>-0.34</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="7">
-        <v>4.19</v>
+        <v>9.68</v>
       </c>
       <c r="D14" s="7">
-        <v>4.16</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.03</v>
+        <v>9.08</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="7">
-        <v>-1.26</v>
+        <v>4.46</v>
       </c>
       <c r="D15" s="7">
-        <v>-1.31</v>
+        <v>4.92</v>
       </c>
       <c r="E15" s="8">
-        <v>-0.05</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="7">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="D16" s="7">
-        <v>-0.05</v>
+        <v>0.63</v>
       </c>
       <c r="E16" s="8">
-        <v>-0.16</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="7">
-        <v>-1.06</v>
+        <v>2.47</v>
       </c>
       <c r="D17" s="7">
-        <v>-1.5</v>
+        <v>3.87</v>
       </c>
       <c r="E17" s="8">
-        <v>-0.44</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="7">
-        <v>12.93</v>
+        <v>3.96</v>
       </c>
       <c r="D18" s="7">
-        <v>9.68</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-3.25</v>
+        <v>3.89</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="7">
-        <v>4.5</v>
+        <v>-1.27</v>
       </c>
       <c r="D19" s="7">
-        <v>4.46</v>
+        <v>-0.54</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.04</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="7">
-        <v>0.39</v>
+        <v>2.12</v>
       </c>
       <c r="D20" s="7">
-        <v>0.04</v>
+        <v>6.13</v>
       </c>
       <c r="E20" s="8">
-        <v>-0.35</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="7">
-        <v>5.06</v>
+        <v>4.32</v>
       </c>
       <c r="D21" s="7">
-        <v>2.47</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.59</v>
+        <v>3.3</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="7">
-        <v>4.24</v>
+        <v>-5.13</v>
       </c>
       <c r="D22" s="7">
-        <v>3.96</v>
+        <v>-3.14</v>
       </c>
       <c r="E22" s="8">
-        <v>-0.28</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="7">
-        <v>-0.61</v>
+        <v>-0.15</v>
       </c>
       <c r="D23" s="7">
-        <v>-1.27</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.66</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="7">
-        <v>2.23</v>
+        <v>2.51</v>
       </c>
       <c r="D24" s="7">
-        <v>2.12</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.11</v>
+        <v>1.16</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="7">
-        <v>3.14</v>
+        <v>1.9</v>
       </c>
       <c r="D25" s="7">
-        <v>4.32</v>
-      </c>
-      <c r="E25" s="9">
-        <v>1.18</v>
+        <v>3.59</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.69</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="7">
-        <v>-4.33</v>
+        <v>0.92</v>
       </c>
       <c r="D26" s="7">
-        <v>-5.13</v>
+        <v>1.72</v>
       </c>
       <c r="E26" s="8">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="7">
-        <v>0.45</v>
+        <v>-2.75</v>
       </c>
       <c r="D27" s="7">
-        <v>-0.15</v>
+        <v>-1.82</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.6</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="7">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="D28" s="7">
-        <v>2.51</v>
+        <v>-0.16</v>
       </c>
       <c r="E28" s="9">
-        <v>0.59</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="7">
-        <v>1.58</v>
+        <v>-0.02</v>
       </c>
       <c r="D29" s="7">
-        <v>1.9</v>
+        <v>-0.84</v>
       </c>
       <c r="E29" s="9">
-        <v>0.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="7">
-        <v>0.83</v>
+        <v>-0.46</v>
       </c>
       <c r="D30" s="7">
-        <v>0.92</v>
+        <v>-1.07</v>
       </c>
       <c r="E30" s="9">
-        <v>0.09</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="7">
-        <v>-1.96</v>
+        <v>-0.28</v>
       </c>
       <c r="D31" s="7">
-        <v>-2.75</v>
+        <v>-0.14</v>
       </c>
       <c r="E31" s="8">
-        <v>-0.79</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="7">
-        <v>1.55</v>
+        <v>-1.49</v>
       </c>
       <c r="D32" s="7">
-        <v>1.44</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.11</v>
+        <v>-1.93</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="7">
-        <v>0.08</v>
+        <v>-1.54</v>
       </c>
       <c r="D33" s="7">
-        <v>-0.02</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.1</v>
+        <v>-1.55</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="7">
-        <v>-0.24</v>
+        <v>1.17</v>
       </c>
       <c r="D34" s="7">
-        <v>-0.46</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.22</v>
+        <v>-0.23</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="7">
-        <v>-0.49</v>
+        <v>0.68</v>
       </c>
       <c r="D35" s="7">
-        <v>-0.28</v>
+        <v>0.23</v>
       </c>
       <c r="E35" s="9">
-        <v>0.21</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="7">
-        <v>-1.2</v>
+        <v>-0.37</v>
       </c>
       <c r="D36" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.29</v>
+        <v>-0.45</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="7">
-        <v>-1.63</v>
+        <v>-2.98</v>
       </c>
       <c r="D37" s="7">
-        <v>-1.54</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.09</v>
+        <v>-0.38</v>
+      </c>
+      <c r="E37" s="8">
+        <v>2.6</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="7">
-        <v>-0.26</v>
+        <v>0.53</v>
       </c>
       <c r="D38" s="7">
-        <v>1.17</v>
+        <v>-0.64</v>
       </c>
       <c r="E38" s="9">
-        <v>1.43</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="7">
-        <v>0.8100000000000001</v>
+        <v>-1.07</v>
       </c>
       <c r="D39" s="7">
-        <v>0.68</v>
+        <v>-0.83</v>
       </c>
       <c r="E39" s="8">
-        <v>-0.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="7">
-        <v>-0.44</v>
+        <v>1.89</v>
       </c>
       <c r="D40" s="7">
-        <v>-0.37</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.07000000000000001</v>
+        <v>3.23</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.34</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="7">
-        <v>-0.59</v>
+        <v>0.58</v>
       </c>
       <c r="D41" s="7">
-        <v>-2.98</v>
+        <v>0.75</v>
       </c>
       <c r="E41" s="8">
-        <v>-2.39</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="7">
-        <v>2.42</v>
+        <v>-0.24</v>
       </c>
       <c r="D42" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.89</v>
+        <v>-0.99</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="7">
-        <v>-1.55</v>
+        <v>-1.22</v>
       </c>
       <c r="D43" s="7">
-        <v>-1.07</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.48</v>
+        <v>-1.21</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.01</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="7">
-        <v>1.8</v>
+        <v>-0.25</v>
       </c>
       <c r="D44" s="7">
-        <v>1.89</v>
+        <v>-0.46</v>
       </c>
       <c r="E44" s="9">
-        <v>0.09</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="7">
-        <v>-0.6899999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="D45" s="7">
-        <v>0.58</v>
-      </c>
-      <c r="E45" s="9">
-        <v>1.27</v>
+        <v>2.81</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.97</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="7">
-        <v>-1.65</v>
+        <v>0.47</v>
       </c>
       <c r="D46" s="7">
-        <v>-0.24</v>
-      </c>
-      <c r="E46" s="9">
-        <v>1.41</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.22</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="7">
-        <v>-1.46</v>
+        <v>-1.72</v>
       </c>
       <c r="D47" s="7">
-        <v>-1.22</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.24</v>
+        <v>-1.21</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" s="7">
-        <v>-0.79</v>
+        <v>24.53</v>
       </c>
       <c r="D48" s="7">
-        <v>-0.25</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.54</v>
+        <v>25.42</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.89</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" s="7">
-        <v>2.09</v>
+        <v>13.52</v>
       </c>
       <c r="D49" s="7">
-        <v>1.84</v>
+        <v>15.09</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.25</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="7">
-        <v>-0.77</v>
+        <v>3.52</v>
       </c>
       <c r="D50" s="7">
-        <v>0.47</v>
+        <v>3.38</v>
       </c>
       <c r="E50" s="9">
-        <v>1.24</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="7">
-        <v>-1.82</v>
+        <v>10.23</v>
       </c>
       <c r="D51" s="7">
-        <v>-1.72</v>
-      </c>
-      <c r="E51" s="9">
-        <v>0.1</v>
+        <v>11.14</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.91</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="7">
-        <v>24.74</v>
+        <v>-12.59</v>
       </c>
       <c r="D52" s="7">
-        <v>24.53</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.21</v>
+        <v>-13.82</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="7">
-        <v>13.18</v>
+        <v>-0.82</v>
       </c>
       <c r="D53" s="7">
-        <v>13.52</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.34</v>
+        <v>-0.25</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.57</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="7">
-        <v>4.52</v>
+        <v>-9.85</v>
       </c>
       <c r="D54" s="7">
-        <v>3.52</v>
+        <v>-9.57</v>
       </c>
       <c r="E54" s="8">
-        <v>-1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="7">
-        <v>9.390000000000001</v>
+        <v>3.51</v>
       </c>
       <c r="D55" s="7">
-        <v>10.23</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.84</v>
+        <v>4.91</v>
+      </c>
+      <c r="E55" s="8">
+        <v>1.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="7">
-        <v>-10.28</v>
+        <v>-4.53</v>
       </c>
       <c r="D56" s="7">
-        <v>-12.59</v>
+        <v>-2.95</v>
       </c>
       <c r="E56" s="8">
-        <v>-2.31</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="7">
-        <v>-0.59</v>
+        <v>41.09</v>
       </c>
       <c r="D57" s="7">
-        <v>-0.82</v>
+        <v>44.7</v>
       </c>
       <c r="E57" s="8">
-        <v>-0.23</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="7">
-        <v>-10.85</v>
+        <v>1.54</v>
       </c>
       <c r="D58" s="7">
-        <v>-9.85</v>
-      </c>
-      <c r="E58" s="9">
-        <v>1</v>
+        <v>3.48</v>
+      </c>
+      <c r="E58" s="8">
+        <v>1.94</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="7">
-        <v>3.44</v>
+        <v>26.12</v>
       </c>
       <c r="D59" s="7">
-        <v>3.51</v>
-      </c>
-      <c r="E59" s="9">
-        <v>0.07000000000000001</v>
+        <v>30.18</v>
+      </c>
+      <c r="E59" s="8">
+        <v>4.06</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="7">
-        <v>-4.02</v>
+        <v>17.48</v>
       </c>
       <c r="D60" s="7">
-        <v>-4.53</v>
+        <v>21.58</v>
       </c>
       <c r="E60" s="8">
-        <v>-0.51</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="7">
-        <v>40.71</v>
+        <v>-2.55</v>
       </c>
       <c r="D61" s="7">
-        <v>41.09</v>
-      </c>
-      <c r="E61" s="9">
-        <v>0.38</v>
+        <v>-0.71</v>
+      </c>
+      <c r="E61" s="8">
+        <v>1.84</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="7">
-        <v>0.72</v>
+        <v>-4.63</v>
       </c>
       <c r="D62" s="7">
-        <v>1.54</v>
-      </c>
-      <c r="E62" s="9">
-        <v>0.82</v>
+        <v>-3.86</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.77</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="7">
-        <v>25.07</v>
+        <v>1.09</v>
       </c>
       <c r="D63" s="7">
-        <v>26.12</v>
-      </c>
-      <c r="E63" s="9">
-        <v>1.05</v>
+        <v>1.81</v>
+      </c>
+      <c r="E63" s="8">
+        <v>0.72</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" s="7">
-        <v>14.76</v>
+        <v>12.68</v>
       </c>
       <c r="D64" s="7">
-        <v>17.48</v>
-      </c>
-      <c r="E64" s="9">
-        <v>2.72</v>
+        <v>13.42</v>
+      </c>
+      <c r="E64" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" s="7">
-        <v>-2.15</v>
+        <v>-1.8</v>
       </c>
       <c r="D65" s="7">
-        <v>-2.55</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.4</v>
+        <v>-3.05</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>-4.6</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D66" s="7">
-        <v>-4.63</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.03</v>
+        <v>7.72</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>1.53</v>
+        <v>-2.11</v>
       </c>
       <c r="D67" s="7">
-        <v>1.09</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-0.44</v>
+        <v>-2.62</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>10.72</v>
+        <v>-3.3</v>
       </c>
       <c r="D68" s="7">
-        <v>12.68</v>
+        <v>-4.3</v>
       </c>
       <c r="E68" s="9">
-        <v>1.96</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="7">
-        <v>-2.18</v>
+        <v>5.15</v>
       </c>
       <c r="D69" s="7">
-        <v>-1.8</v>
-      </c>
-      <c r="E69" s="9">
-        <v>0.38</v>
+        <v>5.22</v>
+      </c>
+      <c r="E69" s="8">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>6.96</v>
+        <v>12.71</v>
       </c>
       <c r="D70" s="7">
-        <v>8.539999999999999</v>
+        <v>12.24</v>
       </c>
       <c r="E70" s="9">
-        <v>1.58</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="7">
-        <v>-3.23</v>
+        <v>2.52</v>
       </c>
       <c r="D71" s="7">
-        <v>-2.11</v>
+        <v>1.86</v>
       </c>
       <c r="E71" s="9">
-        <v>1.12</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="7">
-        <v>-3.6</v>
+        <v>11.2</v>
       </c>
       <c r="D72" s="7">
-        <v>-3.3</v>
-      </c>
-      <c r="E72" s="9">
-        <v>0.3</v>
+        <v>12.42</v>
+      </c>
+      <c r="E72" s="8">
+        <v>1.22</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="7">
-        <v>3.47</v>
+        <v>1.7</v>
       </c>
       <c r="D73" s="7">
-        <v>5.15</v>
+        <v>-0.9</v>
       </c>
       <c r="E73" s="9">
-        <v>1.68</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="7">
-        <v>7.85</v>
+        <v>-5.87</v>
       </c>
       <c r="D74" s="7">
-        <v>12.71</v>
+        <v>-6.62</v>
       </c>
       <c r="E74" s="9">
-        <v>4.86</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="7">
-        <v>1.61</v>
+        <v>7.05</v>
       </c>
       <c r="D75" s="7">
-        <v>2.52</v>
-      </c>
-      <c r="E75" s="9">
-        <v>0.91</v>
+        <v>9.34</v>
+      </c>
+      <c r="E75" s="8">
+        <v>2.29</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="7">
-        <v>8.59</v>
+        <v>12.2</v>
       </c>
       <c r="D76" s="7">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="E76" s="9">
-        <v>2.61</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="7">
-        <v>2.32</v>
+        <v>16.12</v>
       </c>
       <c r="D77" s="7">
-        <v>1.7</v>
+        <v>16.43</v>
       </c>
       <c r="E77" s="8">
-        <v>-0.62</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="7">
-        <v>-6.77</v>
+        <v>6.48</v>
       </c>
       <c r="D78" s="7">
-        <v>-5.87</v>
-      </c>
-      <c r="E78" s="9">
-        <v>0.9</v>
+        <v>6.51</v>
+      </c>
+      <c r="E78" s="8">
+        <v>0.03</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="7">
-        <v>5.87</v>
+        <v>5.75</v>
       </c>
       <c r="D79" s="7">
-        <v>7.05</v>
-      </c>
-      <c r="E79" s="9">
-        <v>1.18</v>
+        <v>6.01</v>
+      </c>
+      <c r="E79" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C80" s="7">
-        <v>9.550000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="D80" s="7">
-        <v>12.2</v>
+        <v>-0.96</v>
       </c>
       <c r="E80" s="9">
-        <v>2.65</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C81" s="7">
-        <v>12.45</v>
+        <v>-5.48</v>
       </c>
       <c r="D81" s="7">
-        <v>16.12</v>
+        <v>-5.55</v>
       </c>
       <c r="E81" s="9">
-        <v>3.67</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C82" s="7">
-        <v>4.66</v>
+        <v>-3.85</v>
       </c>
       <c r="D82" s="7">
-        <v>6.48</v>
+        <v>-4.33</v>
       </c>
       <c r="E82" s="9">
-        <v>1.82</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C83" s="7">
-        <v>4.47</v>
+        <v>-6.81</v>
       </c>
       <c r="D83" s="7">
-        <v>5.75</v>
-      </c>
-      <c r="E83" s="9">
-        <v>1.28</v>
+        <v>-6.64</v>
+      </c>
+      <c r="E83" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="7">
-        <v>-0.09</v>
+        <v>-14.56</v>
       </c>
       <c r="D84" s="7">
-        <v>-0.64</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.55</v>
+        <v>-15.19</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="7">
-        <v>-4.68</v>
+        <v>-7.13</v>
       </c>
       <c r="D85" s="7">
-        <v>-5.48</v>
-      </c>
-      <c r="E85" s="8">
-        <v>-0.8</v>
+        <v>-7.15</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="7">
-        <v>-3.24</v>
+        <v>-19.41</v>
       </c>
       <c r="D86" s="7">
-        <v>-3.85</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-0.61</v>
+        <v>-20.65</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="7">
-        <v>-6.71</v>
+        <v>-0.32</v>
       </c>
       <c r="D87" s="7">
-        <v>-6.81</v>
+        <v>-0.19</v>
       </c>
       <c r="E87" s="8">
-        <v>-0.1</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="7">
-        <v>-13.55</v>
+        <v>-3.9</v>
       </c>
       <c r="D88" s="7">
-        <v>-14.56</v>
+        <v>-3.64</v>
       </c>
       <c r="E88" s="8">
-        <v>-1.01</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="7">
-        <v>-6.74</v>
+        <v>-7.1</v>
       </c>
       <c r="D89" s="7">
-        <v>-7.13</v>
+        <v>-6.13</v>
       </c>
       <c r="E89" s="8">
-        <v>-0.39</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="7">
-        <v>-19.9</v>
+        <v>-4.5</v>
       </c>
       <c r="D90" s="7">
-        <v>-19.41</v>
-      </c>
-      <c r="E90" s="9">
-        <v>0.49</v>
+        <v>-3.99</v>
+      </c>
+      <c r="E90" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="7">
-        <v>-0.04</v>
+        <v>-8.68</v>
       </c>
       <c r="D91" s="7">
-        <v>-0.32</v>
+        <v>-8.33</v>
       </c>
       <c r="E91" s="8">
-        <v>-0.28</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="7">
-        <v>-3.07</v>
+        <v>-12.55</v>
       </c>
       <c r="D92" s="7">
-        <v>-3.9</v>
+        <v>-10.75</v>
       </c>
       <c r="E92" s="8">
-        <v>-0.83</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="7">
-        <v>-6.7</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="D93" s="7">
-        <v>-7.1</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="E93" s="8">
-        <v>-0.4</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="7">
-        <v>-3.58</v>
+        <v>-8.44</v>
       </c>
       <c r="D94" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="E94" s="8">
-        <v>-0.92</v>
+        <v>-8.57</v>
+      </c>
+      <c r="E94" s="9">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="7">
-        <v>-8.5</v>
+        <v>-0.47</v>
       </c>
       <c r="D95" s="7">
-        <v>-8.68</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-0.18</v>
+        <v>-0.9</v>
+      </c>
+      <c r="E95" s="9">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-1.43</v>
       </c>
       <c r="D96" s="7">
-        <v>0</v>
-      </c>
-      <c r="E96" s="9">
-        <v>0.6899999999999999</v>
+        <v>-0.73</v>
+      </c>
+      <c r="E96" s="8">
+        <v>0.7</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="7">
-        <v>-7.3</v>
+        <v>-0.79</v>
       </c>
       <c r="D97" s="7">
-        <v>-8.210000000000001</v>
+        <v>-0.66</v>
       </c>
       <c r="E97" s="8">
-        <v>-0.91</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="7">
-        <v>-8.18</v>
+        <v>-6.19</v>
       </c>
       <c r="D98" s="7">
-        <v>-8.44</v>
+        <v>-6.1</v>
       </c>
       <c r="E98" s="8">
-        <v>-0.26</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C99" s="7">
-        <v>-0.79</v>
+        <v>29458.55</v>
       </c>
       <c r="D99" s="7">
-        <v>-0.47</v>
+        <v>29363.05</v>
       </c>
       <c r="E99" s="9">
-        <v>0.32</v>
+        <v>-95.5</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C100" s="7">
-        <v>-0.99</v>
+        <v>9927.25</v>
       </c>
       <c r="D100" s="7">
-        <v>-1.43</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-0.44</v>
+        <v>9920.15</v>
+      </c>
+      <c r="E100" s="9">
+        <v>-7.1</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C101" s="7">
-        <v>-0.87</v>
+        <v>12152.9</v>
       </c>
       <c r="D101" s="7">
-        <v>-0.79</v>
+        <v>12092.2</v>
       </c>
       <c r="E101" s="9">
-        <v>0.08</v>
+        <v>-60.7</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C102" s="7">
-        <v>-5.67</v>
+        <v>38707.75</v>
       </c>
       <c r="D102" s="7">
-        <v>-6.19</v>
+        <v>38776.9</v>
       </c>
       <c r="E102" s="8">
-        <v>-0.52</v>
+        <v>69.15000000000001</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C103" s="7">
-        <v>29620.05</v>
+        <v>48787.85</v>
       </c>
       <c r="D103" s="7">
-        <v>29458.55</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-161.5</v>
+        <v>48429.35</v>
+      </c>
+      <c r="E103" s="9">
+        <v>-358.5</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C104" s="7">
-        <v>10011.4</v>
+        <v>26432.4</v>
       </c>
       <c r="D104" s="7">
-        <v>9927.25</v>
-      </c>
-      <c r="E104" s="8">
-        <v>-84.15000000000001</v>
+        <v>26426.75</v>
+      </c>
+      <c r="E104" s="9">
+        <v>-5.65</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="7">
-        <v>12229.45</v>
+        <v>31823.15</v>
       </c>
       <c r="D105" s="7">
-        <v>12152.9</v>
-      </c>
-      <c r="E105" s="8">
-        <v>-76.55</v>
+        <v>31332.55</v>
+      </c>
+      <c r="E105" s="9">
+        <v>-490.6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="7">
-        <v>38748.15</v>
+        <v>16608.9</v>
       </c>
       <c r="D106" s="7">
-        <v>38707.75</v>
+        <v>16630.45</v>
       </c>
       <c r="E106" s="8">
-        <v>-40.4</v>
+        <v>21.55</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="7">
-        <v>49363.6</v>
+        <v>9384.5</v>
       </c>
       <c r="D107" s="7">
-        <v>48787.85</v>
+        <v>9409.799999999999</v>
       </c>
       <c r="E107" s="8">
-        <v>-575.75</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="7">
-        <v>26545.3</v>
+        <v>1552.75</v>
       </c>
       <c r="D108" s="7">
-        <v>26432.4</v>
+        <v>1569.1</v>
       </c>
       <c r="E108" s="8">
-        <v>-112.9</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="7">
-        <v>31631.45</v>
+        <v>13100.8</v>
       </c>
       <c r="D109" s="7">
-        <v>31823.15</v>
-      </c>
-      <c r="E109" s="9">
-        <v>191.7</v>
+        <v>13171.45</v>
+      </c>
+      <c r="E109" s="8">
+        <v>70.65000000000001</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="7">
-        <v>16655.5</v>
+        <v>9831.4</v>
       </c>
       <c r="D110" s="7">
-        <v>16608.9</v>
+        <v>9869.25</v>
       </c>
       <c r="E110" s="8">
-        <v>-46.6</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="7">
-        <v>9465.85</v>
+        <v>8640.25</v>
       </c>
       <c r="D111" s="7">
-        <v>9384.5</v>
+        <v>8817.5</v>
       </c>
       <c r="E111" s="8">
-        <v>-81.34999999999999</v>
+        <v>177.25</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="7">
-        <v>1559.45</v>
+        <v>26750.45</v>
       </c>
       <c r="D112" s="7">
-        <v>1552.75</v>
+        <v>26762.5</v>
       </c>
       <c r="E112" s="8">
-        <v>-6.7</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="7">
-        <v>13226.7</v>
+        <v>889.1</v>
       </c>
       <c r="D113" s="7">
-        <v>13100.8</v>
+        <v>889.8</v>
       </c>
       <c r="E113" s="8">
-        <v>-125.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="7">
-        <v>9850.75</v>
+        <v>31223.65</v>
       </c>
       <c r="D114" s="7">
-        <v>9831.4</v>
-      </c>
-      <c r="E114" s="8">
-        <v>-19.35</v>
+        <v>31178.55</v>
+      </c>
+      <c r="E114" s="9">
+        <v>-45.1</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="7">
-        <v>8639.799999999999</v>
+        <v>16705.05</v>
       </c>
       <c r="D115" s="7">
-        <v>8640.25</v>
+        <v>16632.35</v>
       </c>
       <c r="E115" s="9">
-        <v>0.45</v>
+        <v>-72.7</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="7">
-        <v>26479.55</v>
+        <v>9593.4</v>
       </c>
       <c r="D116" s="7">
-        <v>26750.45</v>
-      </c>
-      <c r="E116" s="9">
-        <v>270.9</v>
+        <v>9660.700000000001</v>
+      </c>
+      <c r="E116" s="8">
+        <v>67.3</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="7">
-        <v>897.95</v>
+        <v>11279.1</v>
       </c>
       <c r="D117" s="7">
-        <v>889.1</v>
+        <v>11293.9</v>
       </c>
       <c r="E117" s="8">
-        <v>-8.85</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="7">
-        <v>31310.15</v>
+        <v>27380.35</v>
       </c>
       <c r="D118" s="7">
-        <v>31223.65</v>
+        <v>27408.4</v>
       </c>
       <c r="E118" s="8">
-        <v>-86.5</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C119" s="7">
-        <v>16650.95</v>
+        <v>68</v>
       </c>
       <c r="D119" s="7">
-        <v>16705.05</v>
+        <v>62</v>
       </c>
       <c r="E119" s="9">
-        <v>54.1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C120" s="7">
-        <v>9635.65</v>
+        <v>74</v>
       </c>
       <c r="D120" s="7">
-        <v>9593.4</v>
-      </c>
-      <c r="E120" s="8">
-        <v>-42.25</v>
+        <v>68</v>
+      </c>
+      <c r="E120" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C121" s="7">
-        <v>11270.45</v>
+        <v>44</v>
       </c>
       <c r="D121" s="7">
-        <v>11279.1</v>
-      </c>
-      <c r="E121" s="9">
-        <v>8.65</v>
+        <v>50</v>
+      </c>
+      <c r="E121" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C122" s="7">
-        <v>27534.3</v>
+        <v>50</v>
       </c>
       <c r="D122" s="7">
-        <v>27380.35</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-153.95</v>
+        <v>44</v>
+      </c>
+      <c r="E122" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C123" s="7">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D123" s="7">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="E123" s="8">
-        <v>-6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C124" s="7">
-        <v>32</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D124" s="7">
-        <v>50</v>
+        <v>70.48</v>
       </c>
       <c r="E124" s="9">
-        <v>18</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C125" s="7">
-        <v>44</v>
+        <v>51.32</v>
       </c>
       <c r="D125" s="7">
-        <v>38</v>
-      </c>
-      <c r="E125" s="8">
-        <v>-6</v>
+        <v>50.68</v>
+      </c>
+      <c r="E125" s="9">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C126" s="7">
-        <v>38</v>
+        <v>66.58</v>
       </c>
       <c r="D126" s="7">
-        <v>32</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-6</v>
+        <v>61.57</v>
+      </c>
+      <c r="E126" s="9">
+        <v>-5.01</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C127" s="7">
-        <v>76.2</v>
+        <v>40.61</v>
       </c>
       <c r="D127" s="7">
-        <v>72.59999999999999</v>
+        <v>42.63</v>
       </c>
       <c r="E127" s="8">
-        <v>-3.6</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C128" s="7">
-        <v>59.57</v>
+        <v>44.39</v>
       </c>
       <c r="D128" s="7">
-        <v>51.32</v>
-      </c>
-      <c r="E128" s="8">
-        <v>-8.25</v>
+        <v>40.21</v>
+      </c>
+      <c r="E128" s="9">
+        <v>-4.18</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C129" s="7">
-        <v>73.58</v>
+        <v>44.8</v>
       </c>
       <c r="D129" s="7">
-        <v>66.58</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-7</v>
+        <v>44.68</v>
+      </c>
+      <c r="E129" s="9">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C130" s="7">
-        <v>41.4</v>
+        <v>68.47</v>
       </c>
       <c r="D130" s="7">
-        <v>40.61</v>
-      </c>
-      <c r="E130" s="8">
-        <v>-0.79</v>
+        <v>62.09</v>
+      </c>
+      <c r="E130" s="9">
+        <v>-6.38</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C131" s="7">
-        <v>52.54</v>
+        <v>69.8</v>
       </c>
       <c r="D131" s="7">
-        <v>44.39</v>
+        <v>70.44</v>
       </c>
       <c r="E131" s="8">
-        <v>-8.15</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="7">
-        <v>47.14</v>
+        <v>47.91</v>
       </c>
       <c r="D132" s="7">
-        <v>44.8</v>
+        <v>50.25</v>
       </c>
       <c r="E132" s="8">
-        <v>-2.34</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="7">
-        <v>67.25</v>
+        <v>53.73</v>
       </c>
       <c r="D133" s="7">
-        <v>68.47</v>
-      </c>
-      <c r="E133" s="9">
-        <v>1.22</v>
+        <v>57.25</v>
+      </c>
+      <c r="E133" s="8">
+        <v>3.52</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="7">
-        <v>73.02</v>
+        <v>62.42</v>
       </c>
       <c r="D134" s="7">
-        <v>69.8</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E134" s="8">
-        <v>-3.22</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="7">
-        <v>55.75</v>
+        <v>36.74</v>
       </c>
       <c r="D135" s="7">
-        <v>47.91</v>
+        <v>41.85</v>
       </c>
       <c r="E135" s="8">
-        <v>-7.84</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="7">
-        <v>55.47</v>
+        <v>59.52</v>
       </c>
       <c r="D136" s="7">
-        <v>53.73</v>
+        <v>66.72</v>
       </c>
       <c r="E136" s="8">
-        <v>-1.74</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="7">
-        <v>69.39</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="D137" s="7">
-        <v>62.42</v>
+        <v>69.13</v>
       </c>
       <c r="E137" s="8">
-        <v>-6.97</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="7">
-        <v>38.34</v>
+        <v>48.78</v>
       </c>
       <c r="D138" s="7">
-        <v>36.74</v>
+        <v>49.09</v>
       </c>
       <c r="E138" s="8">
-        <v>-1.6</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="7">
-        <v>59.5</v>
+        <v>49.67</v>
       </c>
       <c r="D139" s="7">
-        <v>59.52</v>
+        <v>48.41</v>
       </c>
       <c r="E139" s="9">
-        <v>0.02</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="7">
-        <v>64.05</v>
+        <v>62.35</v>
       </c>
       <c r="D140" s="7">
-        <v>68.93000000000001</v>
+        <v>57.68</v>
       </c>
       <c r="E140" s="9">
-        <v>4.88</v>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="7">
-        <v>52.54</v>
+        <v>58.31</v>
       </c>
       <c r="D141" s="7">
-        <v>48.78</v>
+        <v>60.96</v>
       </c>
       <c r="E141" s="8">
-        <v>-3.76</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="7">
-        <v>52.1</v>
+        <v>55.24</v>
       </c>
       <c r="D142" s="7">
-        <v>49.67</v>
+        <v>56.13</v>
       </c>
       <c r="E142" s="8">
-        <v>-2.43</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="7">
-        <v>60.12</v>
+        <v>39.67</v>
       </c>
       <c r="D143" s="7">
-        <v>62.35</v>
-      </c>
-      <c r="E143" s="9">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C144" s="7">
-        <v>60.72</v>
-      </c>
-      <c r="D144" s="7">
-        <v>58.31</v>
-      </c>
-      <c r="E144" s="8">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C145" s="7">
-        <v>54.74</v>
-      </c>
-      <c r="D145" s="7">
-        <v>55.24</v>
-      </c>
-      <c r="E145" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C146" s="7">
-        <v>42.21</v>
-      </c>
-      <c r="D146" s="7">
-        <v>39.67</v>
-      </c>
-      <c r="E146" s="8">
-        <v>-2.54</v>
+        <v>40.37</v>
+      </c>
+      <c r="E143" s="8">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5866,28 +5770,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5901,16 +5805,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>55.1</v>
+        <v>55.3</v>
       </c>
       <c r="E2" s="12">
         <v>50</v>
       </c>
       <c r="F2" s="12">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="G2" s="12">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -6018,10 +5922,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>45</v>
@@ -6042,42 +5946,42 @@
         <v>52</v>
       </c>
       <c r="I1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="14" t="s">
         <v>46</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.5457</v>
+        <v>0.5331</v>
       </c>
       <c r="B2" s="15">
-        <v>0.4797</v>
+        <v>0.4952</v>
       </c>
       <c r="C2" s="15">
-        <v>0.4289</v>
+        <v>0.4317</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2971</v>
+        <v>0.2991</v>
       </c>
       <c r="E2" s="15">
-        <v>0.2378</v>
+        <v>0.236</v>
       </c>
       <c r="F2" s="15">
-        <v>0.2238</v>
+        <v>0.2211</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1791</v>
+        <v>0.1795</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1771</v>
+        <v>0.1745</v>
       </c>
       <c r="I2" s="15">
-        <v>0.1589</v>
+        <v>0.1632</v>
       </c>
       <c r="J2" s="15">
-        <v>0.1569</v>
+        <v>0.1575</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6085,10 +5989,10 @@
         <v>41</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>51</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>39</v>
@@ -6114,34 +6018,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.1482</v>
+        <v>0.1462</v>
       </c>
       <c r="B4" s="15">
-        <v>0.1337</v>
+        <v>0.1362</v>
       </c>
       <c r="C4" s="15">
-        <v>0.1336</v>
+        <v>0.1321</v>
       </c>
       <c r="D4" s="15">
-        <v>0.1314</v>
+        <v>0.1307</v>
       </c>
       <c r="E4" s="15">
-        <v>0.09039999999999999</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="F4" s="15">
-        <v>0.0803</v>
+        <v>0.0799</v>
       </c>
       <c r="G4" s="15">
-        <v>0.0643</v>
+        <v>0.0624</v>
       </c>
       <c r="H4" s="15">
-        <v>0.0602</v>
+        <v>0.0581</v>
       </c>
       <c r="I4" s="15">
-        <v>0.001</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.016</v>
+        <v>-0.0184</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="119">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,61 +289,55 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
     <t>No → Yes</t>
   </si>
   <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.1 → 52.9</t>
-  </si>
-  <si>
-    <t>49.1</t>
-  </si>
-  <si>
-    <t>52.9</t>
+    <t>48.7 → 51.2</t>
+  </si>
+  <si>
+    <t>48.7</t>
+  </si>
+  <si>
+    <t>51.2</t>
   </si>
   <si>
     <t>RSI Overbought Exit</t>
   </si>
   <si>
-    <t>70.4 → 69.7</t>
+    <t>70.8 → 66.5</t>
   </si>
   <si>
     <t>🔵 COOLING</t>
   </si>
   <si>
-    <t>70.4</t>
-  </si>
-  <si>
-    <t>69.7</t>
-  </si>
-  <si>
-    <t>50.7 → 47.0</t>
+    <t>70.8</t>
+  </si>
+  <si>
+    <t>66.5</t>
+  </si>
+  <si>
+    <t>53.0 → 49.2</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.7</t>
-  </si>
-  <si>
-    <t>47.0</t>
-  </si>
-  <si>
-    <t>50.2 → 48.7</t>
-  </si>
-  <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>48.7</t>
+    <t>53.0</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1088,10 +1082,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>29392.15</v>
+        <v>29207.9</v>
       </c>
       <c r="E2">
-        <v>0.1</v>
+        <v>-0.63</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1100,43 +1094,43 @@
         <v>23474.65</v>
       </c>
       <c r="H2">
-        <v>-0.86</v>
+        <v>-1.48</v>
       </c>
       <c r="I2">
-        <v>25.21</v>
+        <v>24.42</v>
       </c>
       <c r="J2">
-        <v>0.96</v>
+        <v>-1.48</v>
       </c>
       <c r="K2">
-        <v>10.31</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L2">
-        <v>12.83</v>
+        <v>12.03</v>
       </c>
       <c r="M2">
-        <v>23.56</v>
+        <v>22.33</v>
       </c>
       <c r="N2">
-        <v>23.63</v>
+        <v>23.72</v>
       </c>
       <c r="O2">
         <v>99</v>
       </c>
       <c r="Q2">
-        <v>29496.34</v>
+        <v>29408.34</v>
       </c>
       <c r="R2">
-        <v>28256.9</v>
+        <v>28362.3</v>
       </c>
       <c r="S2">
-        <v>27264.9</v>
+        <v>27326.17</v>
       </c>
       <c r="T2">
-        <v>26989.36</v>
+        <v>26999.26</v>
       </c>
       <c r="U2">
-        <v>8.9</v>
+        <v>8.18</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -1151,34 +1145,34 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>70.76000000000001</v>
+        <v>66.45</v>
       </c>
       <c r="AA2">
-        <v>713.9</v>
+        <v>680.53</v>
       </c>
       <c r="AB2">
-        <v>620.01</v>
+        <v>632.11</v>
       </c>
       <c r="AC2">
-        <v>93.89</v>
+        <v>48.42</v>
       </c>
       <c r="AD2">
-        <v>61.88</v>
+        <v>53.43</v>
       </c>
       <c r="AE2">
-        <v>69.77</v>
+        <v>61.56</v>
       </c>
       <c r="AF2">
-        <v>413.48</v>
+        <v>403.34</v>
       </c>
       <c r="AG2">
         <v>-100</v>
       </c>
       <c r="AH2">
-        <v>30483.63</v>
+        <v>30557.77</v>
       </c>
       <c r="AI2">
-        <v>26030.16</v>
+        <v>26166.83</v>
       </c>
       <c r="AJ2">
         <v>28374.42</v>
@@ -1187,7 +1181,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>60.99</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1201,10 +1195,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9878.049999999999</v>
+        <v>9822.75</v>
       </c>
       <c r="E3">
-        <v>-0.42</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1213,43 +1207,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-5.95</v>
+        <v>-6.48</v>
       </c>
       <c r="I3">
-        <v>15.24</v>
+        <v>14.59</v>
       </c>
       <c r="J3">
-        <v>-0.79</v>
+        <v>-1.69</v>
       </c>
       <c r="K3">
-        <v>0.53</v>
+        <v>0.05</v>
       </c>
       <c r="L3">
-        <v>-4.45</v>
+        <v>-3.75</v>
       </c>
       <c r="M3">
-        <v>12.92</v>
+        <v>12.28</v>
       </c>
       <c r="N3">
-        <v>12.85</v>
+        <v>12.61</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q3">
-        <v>9945.700000000001</v>
+        <v>9911.92</v>
       </c>
       <c r="R3">
-        <v>9889.879999999999</v>
+        <v>9889.41</v>
       </c>
       <c r="S3">
-        <v>9907.09</v>
+        <v>9899.91</v>
       </c>
       <c r="T3">
-        <v>9709.540000000001</v>
+        <v>9712.389999999999</v>
       </c>
       <c r="U3">
-        <v>1.74</v>
+        <v>1.14</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -1264,31 +1258,31 @@
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>46.96</v>
+        <v>42.54</v>
       </c>
       <c r="AA3">
-        <v>11.51</v>
+        <v>2.77</v>
       </c>
       <c r="AB3">
-        <v>5.58</v>
+        <v>5.02</v>
       </c>
       <c r="AC3">
-        <v>5.93</v>
+        <v>-2.25</v>
       </c>
       <c r="AD3">
-        <v>30.85</v>
+        <v>17.67</v>
       </c>
       <c r="AE3">
-        <v>49.8</v>
+        <v>33.78</v>
       </c>
       <c r="AF3">
-        <v>89.36</v>
+        <v>89.22</v>
       </c>
       <c r="AH3">
-        <v>10030.92</v>
+        <v>10031.32</v>
       </c>
       <c r="AI3">
-        <v>9748.84</v>
+        <v>9747.5</v>
       </c>
       <c r="AJ3">
         <v>10073.2</v>
@@ -1297,7 +1291,7 @@
         <v>82</v>
       </c>
       <c r="AL3">
-        <v>27.46</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1311,10 +1305,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>12138</v>
+        <v>12142.85</v>
       </c>
       <c r="E4">
-        <v>0.38</v>
+        <v>0.04</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1323,82 +1317,82 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-3.96</v>
+        <v>-3.93</v>
       </c>
       <c r="I4">
-        <v>17.45</v>
+        <v>17.5</v>
       </c>
       <c r="J4">
-        <v>-0.28</v>
+        <v>-0.45</v>
       </c>
       <c r="K4">
-        <v>4.32</v>
+        <v>4.14</v>
       </c>
       <c r="L4">
-        <v>6.6</v>
+        <v>6.68</v>
       </c>
       <c r="M4">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="N4">
-        <v>13.16</v>
+        <v>13.2</v>
       </c>
       <c r="O4">
         <v>68</v>
       </c>
       <c r="Q4">
-        <v>12161.98</v>
+        <v>12151.08</v>
       </c>
       <c r="R4">
-        <v>11959.16</v>
+        <v>11981.06</v>
       </c>
       <c r="S4">
-        <v>11694.94</v>
+        <v>11714.08</v>
       </c>
       <c r="T4">
-        <v>11713.68</v>
+        <v>11711.22</v>
       </c>
       <c r="U4">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z4">
-        <v>63.78</v>
+        <v>64.02</v>
       </c>
       <c r="AA4">
-        <v>145.04</v>
+        <v>138.65</v>
       </c>
       <c r="AB4">
-        <v>143.13</v>
+        <v>142.23</v>
       </c>
       <c r="AC4">
-        <v>1.91</v>
+        <v>-3.58</v>
       </c>
       <c r="AD4">
-        <v>31.61</v>
+        <v>28</v>
       </c>
       <c r="AE4">
-        <v>45.93</v>
+        <v>35.01</v>
       </c>
       <c r="AF4">
-        <v>110.01</v>
+        <v>108.04</v>
       </c>
       <c r="AH4">
-        <v>12439.5</v>
+        <v>12452.45</v>
       </c>
       <c r="AI4">
-        <v>11478.82</v>
+        <v>11509.66</v>
       </c>
       <c r="AJ4">
         <v>11869.84</v>
@@ -1407,7 +1401,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>42.2</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1421,10 +1415,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38690.25</v>
+        <v>38554.2</v>
       </c>
       <c r="E5">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1433,43 +1427,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-6.85</v>
+        <v>-7.18</v>
       </c>
       <c r="I5">
-        <v>16.89</v>
+        <v>16.48</v>
       </c>
       <c r="J5">
-        <v>0.04</v>
+        <v>-0.5</v>
       </c>
       <c r="K5">
-        <v>-1.75</v>
+        <v>-2.01</v>
       </c>
       <c r="L5">
-        <v>-3.47</v>
+        <v>-3.17</v>
       </c>
       <c r="M5">
-        <v>10.79</v>
+        <v>10.42</v>
       </c>
       <c r="N5">
-        <v>14.48</v>
+        <v>14.29</v>
       </c>
       <c r="O5">
         <v>44</v>
       </c>
       <c r="Q5">
-        <v>38734.58</v>
+        <v>38695.45</v>
       </c>
       <c r="R5">
-        <v>38973.39</v>
+        <v>38937.25</v>
       </c>
       <c r="S5">
-        <v>39369.88</v>
+        <v>39332.05</v>
       </c>
       <c r="T5">
-        <v>37319.44</v>
+        <v>37333.99</v>
       </c>
       <c r="U5">
-        <v>3.67</v>
+        <v>3.27</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1484,34 +1478,34 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>40.76</v>
+        <v>37.95</v>
       </c>
       <c r="AA5">
-        <v>-195.36</v>
+        <v>-202.29</v>
       </c>
       <c r="AB5">
-        <v>-195.42</v>
+        <v>-196.79</v>
       </c>
       <c r="AC5">
-        <v>0.06</v>
+        <v>-5.5</v>
       </c>
       <c r="AD5">
-        <v>73.26000000000001</v>
+        <v>68.13</v>
       </c>
       <c r="AE5">
-        <v>73.31</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="AF5">
-        <v>374.91</v>
+        <v>365.2</v>
       </c>
       <c r="AG5">
         <v>-100</v>
       </c>
       <c r="AH5">
-        <v>39580.36</v>
+        <v>39554.09</v>
       </c>
       <c r="AI5">
-        <v>38366.42</v>
+        <v>38320.4</v>
       </c>
       <c r="AJ5">
         <v>39538.76</v>
@@ -1520,7 +1514,7 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>13.11</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1534,10 +1528,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>48837.3</v>
+        <v>48615.05</v>
       </c>
       <c r="E6">
-        <v>0.84</v>
+        <v>-0.46</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1546,43 +1540,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-14.48</v>
+        <v>-14.87</v>
       </c>
       <c r="I6">
-        <v>7.24</v>
+        <v>6.76</v>
       </c>
       <c r="J6">
-        <v>-1.08</v>
+        <v>-1.66</v>
       </c>
       <c r="K6">
-        <v>1.14</v>
+        <v>0.43</v>
       </c>
       <c r="L6">
-        <v>-3.82</v>
+        <v>-4.77</v>
       </c>
       <c r="M6">
-        <v>-13.01</v>
+        <v>-12.77</v>
       </c>
       <c r="N6">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>48970.66</v>
+        <v>48806.63</v>
       </c>
       <c r="R6">
-        <v>49030.05</v>
+        <v>49023.36</v>
       </c>
       <c r="S6">
-        <v>49086.9</v>
+        <v>49094.88</v>
       </c>
       <c r="T6">
-        <v>51268.15</v>
+        <v>51228.18</v>
       </c>
       <c r="U6">
-        <v>-4.74</v>
+        <v>-5.1</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -1597,34 +1591,34 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>46.4</v>
+        <v>43.74</v>
       </c>
       <c r="AA6">
-        <v>-49.29</v>
+        <v>-80.17</v>
       </c>
       <c r="AB6">
-        <v>-6.49</v>
+        <v>-21.23</v>
       </c>
       <c r="AC6">
-        <v>-42.8</v>
+        <v>-58.95</v>
       </c>
       <c r="AD6">
-        <v>9.75</v>
+        <v>15.31</v>
       </c>
       <c r="AE6">
-        <v>19.79</v>
+        <v>13.62</v>
       </c>
       <c r="AF6">
-        <v>617.65</v>
+        <v>596.3</v>
       </c>
       <c r="AG6">
         <v>-100</v>
       </c>
       <c r="AH6">
-        <v>49849.55</v>
+        <v>49854.62</v>
       </c>
       <c r="AI6">
-        <v>48210.54</v>
+        <v>48192.1</v>
       </c>
       <c r="AJ6">
         <v>50224.74</v>
@@ -1633,7 +1627,7 @@
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>25.34</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1647,10 +1641,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26327.95</v>
+        <v>26213.65</v>
       </c>
       <c r="E7">
-        <v>-0.37</v>
+        <v>-0.43</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1659,43 +1653,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-7.5</v>
+        <v>-7.9</v>
       </c>
       <c r="I7">
-        <v>11.93</v>
+        <v>11.44</v>
       </c>
       <c r="J7">
-        <v>-1.99</v>
+        <v>-0.95</v>
       </c>
       <c r="K7">
-        <v>-1.37</v>
+        <v>-1.29</v>
       </c>
       <c r="L7">
-        <v>3.36</v>
+        <v>3.43</v>
       </c>
       <c r="M7">
-        <v>-0.5600000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="N7">
-        <v>8.699999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="O7">
         <v>26</v>
       </c>
       <c r="Q7">
-        <v>26439.68</v>
+        <v>26389.21</v>
       </c>
       <c r="R7">
-        <v>26735.52</v>
+        <v>26701.04</v>
       </c>
       <c r="S7">
-        <v>26470.82</v>
+        <v>26494.47</v>
       </c>
       <c r="T7">
-        <v>26732.28</v>
+        <v>26725.67</v>
       </c>
       <c r="U7">
-        <v>-1.51</v>
+        <v>-1.92</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
@@ -1710,34 +1704,34 @@
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>42.54</v>
+        <v>40.14</v>
       </c>
       <c r="AA7">
-        <v>-28.87</v>
+        <v>-56.65</v>
       </c>
       <c r="AB7">
-        <v>45.6</v>
+        <v>25.15</v>
       </c>
       <c r="AC7">
-        <v>-74.47</v>
+        <v>-81.8</v>
       </c>
       <c r="AD7">
-        <v>20.61</v>
+        <v>12.26</v>
       </c>
       <c r="AE7">
-        <v>26.71</v>
+        <v>20.69</v>
       </c>
       <c r="AF7">
-        <v>324.57</v>
+        <v>312.31</v>
       </c>
       <c r="AG7">
         <v>-100</v>
       </c>
       <c r="AH7">
-        <v>27210.63</v>
+        <v>27222.69</v>
       </c>
       <c r="AI7">
-        <v>26260.41</v>
+        <v>26179.38</v>
       </c>
       <c r="AJ7">
         <v>26067.59</v>
@@ -1746,7 +1740,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>25.21</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1760,10 +1754,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31453.9</v>
+        <v>31357.75</v>
       </c>
       <c r="E8">
-        <v>0.39</v>
+        <v>-0.31</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1772,43 +1766,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-20.35</v>
+        <v>-20.59</v>
       </c>
       <c r="I8">
-        <v>22.06</v>
+        <v>21.68</v>
       </c>
       <c r="J8">
-        <v>0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="K8">
-        <v>10.24</v>
+        <v>9.17</v>
       </c>
       <c r="L8">
-        <v>14.96</v>
+        <v>13.14</v>
       </c>
       <c r="M8">
-        <v>-10.65</v>
+        <v>-10.49</v>
       </c>
       <c r="N8">
         <v>-0.76</v>
       </c>
       <c r="O8">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="Q8">
-        <v>31557.75</v>
+        <v>31519.76</v>
       </c>
       <c r="R8">
-        <v>30483.85</v>
+        <v>30590.41</v>
       </c>
       <c r="S8">
-        <v>28933.82</v>
+        <v>28974.97</v>
       </c>
       <c r="T8">
-        <v>32591.71</v>
+        <v>32572</v>
       </c>
       <c r="U8">
-        <v>-3.49</v>
+        <v>-3.73</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -1823,34 +1817,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>63.01</v>
+        <v>61.73</v>
       </c>
       <c r="AA8">
-        <v>829.01</v>
+        <v>786.9</v>
       </c>
       <c r="AB8">
-        <v>801.04</v>
+        <v>798.21</v>
       </c>
       <c r="AC8">
-        <v>27.97</v>
+        <v>-11.31</v>
       </c>
       <c r="AD8">
-        <v>53.58</v>
+        <v>24.39</v>
       </c>
       <c r="AE8">
-        <v>69.15000000000001</v>
+        <v>49.88</v>
       </c>
       <c r="AF8">
-        <v>651.1</v>
+        <v>638.66</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32905.07</v>
+        <v>32965.8</v>
       </c>
       <c r="AI8">
-        <v>28062.63</v>
+        <v>28215.02</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1859,7 +1853,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>24.3</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1873,10 +1867,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16620.6</v>
+        <v>16545.3</v>
       </c>
       <c r="E9">
-        <v>-0.06</v>
+        <v>-0.45</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1885,25 +1879,25 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-0.25</v>
+        <v>-0.7</v>
       </c>
       <c r="I9">
-        <v>6.11</v>
+        <v>5.63</v>
       </c>
       <c r="J9">
-        <v>0.19</v>
+        <v>-0.7</v>
       </c>
       <c r="K9">
-        <v>4.45</v>
+        <v>3.71</v>
       </c>
       <c r="N9">
-        <v>41.84</v>
+        <v>37.39</v>
       </c>
       <c r="Q9">
-        <v>16635.58</v>
+        <v>16612.15</v>
       </c>
       <c r="R9">
-        <v>16280.54</v>
+        <v>16311.53</v>
       </c>
       <c r="X9" t="s">
         <v>80</v>
@@ -1912,31 +1906,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>69.70999999999999</v>
+        <v>64.17</v>
       </c>
       <c r="AA9">
-        <v>197.79</v>
+        <v>187.98</v>
       </c>
       <c r="AB9">
-        <v>166.01</v>
+        <v>170.4</v>
       </c>
       <c r="AC9">
-        <v>31.78</v>
+        <v>17.57</v>
       </c>
       <c r="AD9">
-        <v>85.84999999999999</v>
+        <v>76.37</v>
       </c>
       <c r="AE9">
-        <v>90.54000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AF9">
-        <v>130.74</v>
+        <v>129.52</v>
       </c>
       <c r="AH9">
-        <v>16902.53</v>
+        <v>16920.68</v>
       </c>
       <c r="AI9">
-        <v>15658.56</v>
+        <v>15702.37</v>
       </c>
       <c r="AJ9">
         <v>16247.16</v>
@@ -1945,7 +1939,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>44.74</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1959,10 +1953,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9393.15</v>
+        <v>9419.1</v>
       </c>
       <c r="E10">
-        <v>-0.18</v>
+        <v>0.28</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1971,43 +1965,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-3.82</v>
+        <v>-3.55</v>
       </c>
       <c r="I10">
-        <v>9.720000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="J10">
-        <v>-0.64</v>
+        <v>-0.89</v>
       </c>
       <c r="K10">
-        <v>0.59</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L10">
-        <v>0.26</v>
+        <v>0.98</v>
       </c>
       <c r="M10">
-        <v>3.69</v>
+        <v>4.16</v>
       </c>
       <c r="N10">
-        <v>15.52</v>
+        <v>15.58</v>
       </c>
       <c r="O10">
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>9431.49</v>
+        <v>9414.48</v>
       </c>
       <c r="R10">
-        <v>9407.059999999999</v>
+        <v>9409.15</v>
       </c>
       <c r="S10">
-        <v>9376.17</v>
+        <v>9380.370000000001</v>
       </c>
       <c r="T10">
-        <v>9363.09</v>
+        <v>9362.860000000001</v>
       </c>
       <c r="U10">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -2022,34 +2016,34 @@
         <v>3</v>
       </c>
       <c r="Z10">
-        <v>48.7</v>
+        <v>51.23</v>
       </c>
       <c r="AA10">
-        <v>12.65</v>
+        <v>11.66</v>
       </c>
       <c r="AB10">
-        <v>15.45</v>
+        <v>14.69</v>
       </c>
       <c r="AC10">
-        <v>-2.8</v>
+        <v>-3.03</v>
       </c>
       <c r="AD10">
-        <v>15.72</v>
+        <v>22.48</v>
       </c>
       <c r="AE10">
-        <v>31.92</v>
+        <v>22.76</v>
       </c>
       <c r="AF10">
-        <v>87.70999999999999</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="AG10">
         <v>-100</v>
       </c>
       <c r="AH10">
-        <v>9498.74</v>
+        <v>9499.870000000001</v>
       </c>
       <c r="AI10">
-        <v>9315.389999999999</v>
+        <v>9318.43</v>
       </c>
       <c r="AJ10">
         <v>9229.360000000001</v>
@@ -2058,7 +2052,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>26.76</v>
+        <v>25.83</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2072,10 +2066,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1574.95</v>
+        <v>1590.1</v>
       </c>
       <c r="E11">
-        <v>0.37</v>
+        <v>0.96</v>
       </c>
       <c r="F11">
         <v>1671.5</v>
@@ -2084,43 +2078,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-5.78</v>
+        <v>-4.87</v>
       </c>
       <c r="I11">
-        <v>25.66</v>
+        <v>26.87</v>
       </c>
       <c r="J11">
-        <v>0.74</v>
+        <v>2.26</v>
       </c>
       <c r="K11">
-        <v>4.74</v>
+        <v>4.52</v>
       </c>
       <c r="L11">
-        <v>11.84</v>
+        <v>10.72</v>
       </c>
       <c r="M11">
-        <v>-4.03</v>
+        <v>-3.05</v>
       </c>
       <c r="N11">
-        <v>-1.58</v>
+        <v>-1.11</v>
       </c>
       <c r="O11">
         <v>62</v>
       </c>
       <c r="Q11">
-        <v>1562.25</v>
+        <v>1569.27</v>
       </c>
       <c r="R11">
-        <v>1550.8</v>
+        <v>1554.24</v>
       </c>
       <c r="S11">
-        <v>1517.72</v>
+        <v>1520.49</v>
       </c>
       <c r="T11">
-        <v>1442.76</v>
+        <v>1443.01</v>
       </c>
       <c r="U11">
-        <v>9.16</v>
+        <v>10.19</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -2135,31 +2129,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>58.47</v>
+        <v>61.52</v>
       </c>
       <c r="AA11">
-        <v>17.63</v>
+        <v>18.6</v>
       </c>
       <c r="AB11">
-        <v>18.99</v>
+        <v>18.91</v>
       </c>
       <c r="AC11">
-        <v>-1.36</v>
+        <v>-0.31</v>
       </c>
       <c r="AD11">
-        <v>11.23</v>
+        <v>21.84</v>
       </c>
       <c r="AE11">
-        <v>6.19</v>
+        <v>13.05</v>
       </c>
       <c r="AF11">
-        <v>31.29</v>
+        <v>31.66</v>
       </c>
       <c r="AH11">
-        <v>1612.55</v>
+        <v>1616.74</v>
       </c>
       <c r="AI11">
-        <v>1489.06</v>
+        <v>1491.73</v>
       </c>
       <c r="AJ11">
         <v>1508.92</v>
@@ -2168,7 +2162,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>36.44</v>
+        <v>38.41</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2182,10 +2176,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13033.75</v>
+        <v>12941.7</v>
       </c>
       <c r="E12">
-        <v>-1.05</v>
+        <v>-0.71</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2194,43 +2188,43 @@
         <v>9147.1</v>
       </c>
       <c r="H12">
-        <v>-4.99</v>
+        <v>-5.66</v>
       </c>
       <c r="I12">
-        <v>42.49</v>
+        <v>41.48</v>
       </c>
       <c r="J12">
-        <v>-0.84</v>
+        <v>-1.88</v>
       </c>
       <c r="K12">
-        <v>3.96</v>
+        <v>3.57</v>
       </c>
       <c r="L12">
-        <v>-3.9</v>
+        <v>-2.7</v>
       </c>
       <c r="M12">
-        <v>39.73</v>
+        <v>38.62</v>
       </c>
       <c r="N12">
-        <v>17.58</v>
+        <v>17.09</v>
       </c>
       <c r="O12">
         <v>87</v>
       </c>
       <c r="Q12">
-        <v>13144.51</v>
+        <v>13094.88</v>
       </c>
       <c r="R12">
-        <v>12771.13</v>
+        <v>12796.37</v>
       </c>
       <c r="S12">
-        <v>12760.15</v>
+        <v>12750.27</v>
       </c>
       <c r="T12">
-        <v>11915.53</v>
+        <v>11929.08</v>
       </c>
       <c r="U12">
-        <v>9.380000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -2245,34 +2239,34 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>57.65</v>
+        <v>53.52</v>
       </c>
       <c r="AA12">
-        <v>138.72</v>
+        <v>124.22</v>
       </c>
       <c r="AB12">
-        <v>90.02</v>
+        <v>96.86</v>
       </c>
       <c r="AC12">
-        <v>48.7</v>
+        <v>27.36</v>
       </c>
       <c r="AD12">
-        <v>62.92</v>
+        <v>53.74</v>
       </c>
       <c r="AE12">
-        <v>72.31</v>
+        <v>63.89</v>
       </c>
       <c r="AF12">
-        <v>191.28</v>
+        <v>193.4</v>
       </c>
       <c r="AG12">
         <v>-100</v>
       </c>
       <c r="AH12">
-        <v>13451.13</v>
+        <v>13461.44</v>
       </c>
       <c r="AI12">
-        <v>12091.14</v>
+        <v>12131.3</v>
       </c>
       <c r="AJ12">
         <v>12652.05</v>
@@ -2281,7 +2275,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>46.2</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2295,10 +2289,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9894.950000000001</v>
+        <v>9844.950000000001</v>
       </c>
       <c r="E13">
-        <v>0.26</v>
+        <v>-0.51</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2307,43 +2301,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-8.09</v>
+        <v>-8.56</v>
       </c>
       <c r="I13">
-        <v>7.53</v>
+        <v>6.98</v>
       </c>
       <c r="J13">
-        <v>-0.43</v>
+        <v>-0.78</v>
       </c>
       <c r="K13">
-        <v>-0.2</v>
+        <v>-0.67</v>
       </c>
       <c r="L13">
-        <v>-6.66</v>
+        <v>-6.11</v>
       </c>
       <c r="M13">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="N13">
-        <v>22.29</v>
+        <v>22.16</v>
       </c>
       <c r="O13">
         <v>13</v>
       </c>
       <c r="Q13">
-        <v>9873.74</v>
+        <v>9858.26</v>
       </c>
       <c r="R13">
-        <v>9924.15</v>
+        <v>9919.469999999999</v>
       </c>
       <c r="S13">
-        <v>9968.98</v>
+        <v>9963.43</v>
       </c>
       <c r="T13">
-        <v>10049.73</v>
+        <v>10049.27</v>
       </c>
       <c r="U13">
-        <v>-1.54</v>
+        <v>-2.03</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -2358,34 +2352,34 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>45.09</v>
+        <v>40.38</v>
       </c>
       <c r="AA13">
-        <v>-30.62</v>
+        <v>-33.04</v>
       </c>
       <c r="AB13">
-        <v>-29.15</v>
+        <v>-29.93</v>
       </c>
       <c r="AC13">
-        <v>-1.47</v>
+        <v>-3.11</v>
       </c>
       <c r="AD13">
-        <v>26.05</v>
+        <v>33.08</v>
       </c>
       <c r="AE13">
-        <v>16.09</v>
+        <v>23</v>
       </c>
       <c r="AF13">
-        <v>92.37</v>
+        <v>91.31</v>
       </c>
       <c r="AG13">
         <v>-100</v>
       </c>
       <c r="AH13">
-        <v>10001.89</v>
+        <v>10004.49</v>
       </c>
       <c r="AI13">
-        <v>9846.4</v>
+        <v>9834.440000000001</v>
       </c>
       <c r="AJ13">
         <v>10093.21</v>
@@ -2394,7 +2388,7 @@
         <v>82</v>
       </c>
       <c r="AL13">
-        <v>27.51</v>
+        <v>29.07</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2408,10 +2402,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8788.950000000001</v>
+        <v>8738.799999999999</v>
       </c>
       <c r="E14">
-        <v>-0.32</v>
+        <v>-0.57</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2420,43 +2414,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-11.04</v>
+        <v>-11.55</v>
       </c>
       <c r="I14">
-        <v>30.09</v>
+        <v>29.35</v>
       </c>
       <c r="J14">
-        <v>0.68</v>
+        <v>-0.54</v>
       </c>
       <c r="K14">
-        <v>4.79</v>
+        <v>4.68</v>
       </c>
       <c r="L14">
-        <v>7.52</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M14">
-        <v>28.14</v>
+        <v>27.6</v>
       </c>
       <c r="N14">
-        <v>29.77</v>
+        <v>29.92</v>
       </c>
       <c r="O14">
         <v>93</v>
       </c>
       <c r="Q14">
-        <v>8734.540000000001</v>
+        <v>8725.059999999999</v>
       </c>
       <c r="R14">
-        <v>8502.02</v>
+        <v>8519.879999999999</v>
       </c>
       <c r="S14">
-        <v>8476.459999999999</v>
+        <v>8486.85</v>
       </c>
       <c r="T14">
-        <v>8565.049999999999</v>
+        <v>8569.48</v>
       </c>
       <c r="U14">
-        <v>2.61</v>
+        <v>1.98</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -2471,34 +2465,34 @@
         <v>2</v>
       </c>
       <c r="Z14">
-        <v>64.72</v>
+        <v>61.26</v>
       </c>
       <c r="AA14">
-        <v>92.76000000000001</v>
+        <v>95</v>
       </c>
       <c r="AB14">
-        <v>52.9</v>
+        <v>61.32</v>
       </c>
       <c r="AC14">
-        <v>39.86</v>
+        <v>33.68</v>
       </c>
       <c r="AD14">
-        <v>73.29000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="AE14">
-        <v>70.27</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="AF14">
-        <v>139.48</v>
+        <v>135.94</v>
       </c>
       <c r="AG14">
         <v>-100</v>
       </c>
       <c r="AH14">
-        <v>8837.120000000001</v>
+        <v>8865.860000000001</v>
       </c>
       <c r="AI14">
-        <v>8166.93</v>
+        <v>8173.89</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
@@ -2507,7 +2501,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>42.87</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2521,10 +2515,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26686.8</v>
+        <v>26445.55</v>
       </c>
       <c r="E15">
-        <v>-0.28</v>
+        <v>-0.9</v>
       </c>
       <c r="F15">
         <v>26762.5</v>
@@ -2533,43 +2527,43 @@
         <v>21402.15</v>
       </c>
       <c r="H15">
-        <v>-0.28</v>
+        <v>-1.18</v>
       </c>
       <c r="I15">
-        <v>24.69</v>
+        <v>23.56</v>
       </c>
       <c r="J15">
-        <v>0.46</v>
+        <v>-0.36</v>
       </c>
       <c r="K15">
-        <v>2.63</v>
+        <v>1.68</v>
       </c>
       <c r="L15">
-        <v>8.699999999999999</v>
+        <v>7.35</v>
       </c>
       <c r="M15">
-        <v>20.46</v>
+        <v>20.37</v>
       </c>
       <c r="N15">
-        <v>13.69</v>
+        <v>13.64</v>
       </c>
       <c r="O15">
         <v>81</v>
       </c>
       <c r="Q15">
-        <v>26644.22</v>
+        <v>26624.97</v>
       </c>
       <c r="R15">
-        <v>26275.18</v>
+        <v>26315.2</v>
       </c>
       <c r="S15">
-        <v>25497.62</v>
+        <v>25542.97</v>
       </c>
       <c r="T15">
-        <v>23467.95</v>
+        <v>23487.6</v>
       </c>
       <c r="U15">
-        <v>13.72</v>
+        <v>12.59</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2584,34 +2578,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>66.23999999999999</v>
+        <v>57.91</v>
       </c>
       <c r="AA15">
-        <v>342.6</v>
+        <v>312.19</v>
       </c>
       <c r="AB15">
-        <v>349.39</v>
+        <v>341.95</v>
       </c>
       <c r="AC15">
-        <v>-6.79</v>
+        <v>-29.76</v>
       </c>
       <c r="AD15">
-        <v>83.13</v>
+        <v>51.97</v>
       </c>
       <c r="AE15">
-        <v>82.05</v>
+        <v>73.13</v>
       </c>
       <c r="AF15">
-        <v>307.9</v>
+        <v>308.79</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27086.49</v>
+        <v>27072.82</v>
       </c>
       <c r="AI15">
-        <v>25463.86</v>
+        <v>25557.58</v>
       </c>
       <c r="AJ15">
         <v>25756.98</v>
@@ -2620,7 +2614,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>47.69</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2634,10 +2628,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>898.4</v>
+        <v>895.65</v>
       </c>
       <c r="E16">
-        <v>0.97</v>
+        <v>-0.31</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2646,43 +2640,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-7.25</v>
+        <v>-7.54</v>
       </c>
       <c r="I16">
-        <v>37.97</v>
+        <v>37.55</v>
       </c>
       <c r="J16">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="K16">
-        <v>-1.83</v>
+        <v>-1.16</v>
       </c>
       <c r="L16">
-        <v>16.66</v>
+        <v>18.43</v>
       </c>
       <c r="M16">
-        <v>-1.5</v>
+        <v>-1.34</v>
       </c>
       <c r="N16">
-        <v>17.89</v>
+        <v>17.93</v>
       </c>
       <c r="O16">
         <v>74</v>
       </c>
       <c r="Q16">
-        <v>892.24</v>
+        <v>894.1799999999999</v>
       </c>
       <c r="R16">
-        <v>906.01</v>
+        <v>904.86</v>
       </c>
       <c r="S16">
-        <v>864.59</v>
+        <v>867.21</v>
       </c>
       <c r="T16">
-        <v>834.8099999999999</v>
+        <v>834.6</v>
       </c>
       <c r="U16">
-        <v>7.62</v>
+        <v>7.31</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
@@ -2697,34 +2691,34 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>52.87</v>
+        <v>51.55</v>
       </c>
       <c r="AA16">
-        <v>4.29</v>
+        <v>3.84</v>
       </c>
       <c r="AB16">
-        <v>9.380000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="AC16">
-        <v>-5.09</v>
+        <v>-4.43</v>
       </c>
       <c r="AD16">
-        <v>15.65</v>
+        <v>20.79</v>
       </c>
       <c r="AE16">
-        <v>14.22</v>
+        <v>17.16</v>
       </c>
       <c r="AF16">
-        <v>18.67</v>
+        <v>18.06</v>
       </c>
       <c r="AG16">
         <v>-100</v>
       </c>
       <c r="AH16">
-        <v>932.27</v>
+        <v>930.8</v>
       </c>
       <c r="AI16">
-        <v>879.75</v>
+        <v>878.92</v>
       </c>
       <c r="AJ16">
         <v>864.8</v>
@@ -2733,7 +2727,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>16.41</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2747,10 +2741,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>31101.75</v>
+        <v>31128.25</v>
       </c>
       <c r="E17">
-        <v>-0.25</v>
+        <v>0.09</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2759,43 +2753,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-8.800000000000001</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="I17">
-        <v>9.65</v>
+        <v>9.75</v>
       </c>
       <c r="J17">
-        <v>-1.28</v>
+        <v>-0.44</v>
       </c>
       <c r="K17">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L17">
-        <v>4.77</v>
+        <v>4.8</v>
       </c>
       <c r="M17">
-        <v>-4.35</v>
+        <v>-3.96</v>
       </c>
       <c r="N17">
-        <v>5.98</v>
+        <v>5.97</v>
       </c>
       <c r="O17">
         <v>19</v>
       </c>
       <c r="Q17">
-        <v>31215.86</v>
+        <v>31188.47</v>
       </c>
       <c r="R17">
-        <v>31396.78</v>
+        <v>31381.22</v>
       </c>
       <c r="S17">
-        <v>30877.62</v>
+        <v>30908.46</v>
       </c>
       <c r="T17">
-        <v>31834.03</v>
+        <v>31821.86</v>
       </c>
       <c r="U17">
-        <v>-2.3</v>
+        <v>-2.18</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
@@ -2810,34 +2804,34 @@
         <v>1</v>
       </c>
       <c r="Z17">
-        <v>46.25</v>
+        <v>47.13</v>
       </c>
       <c r="AA17">
-        <v>76.31999999999999</v>
+        <v>56.34</v>
       </c>
       <c r="AB17">
-        <v>152.68</v>
+        <v>133.41</v>
       </c>
       <c r="AC17">
-        <v>-76.37</v>
+        <v>-77.06999999999999</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AF17">
-        <v>298.4</v>
+        <v>287.98</v>
       </c>
       <c r="AG17">
         <v>-100</v>
       </c>
       <c r="AH17">
-        <v>31718.77</v>
+        <v>31723.94</v>
       </c>
       <c r="AI17">
-        <v>31074.8</v>
+        <v>31038.51</v>
       </c>
       <c r="AJ17">
         <v>30549.87</v>
@@ -2846,7 +2840,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>26.71</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2860,10 +2854,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16581.85</v>
+        <v>16505.3</v>
       </c>
       <c r="E18">
-        <v>-0.3</v>
+        <v>-0.46</v>
       </c>
       <c r="F18">
         <v>16783.35</v>
@@ -2872,25 +2866,25 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-1.2</v>
+        <v>-1.66</v>
       </c>
       <c r="I18">
-        <v>7.65</v>
+        <v>7.16</v>
       </c>
       <c r="J18">
-        <v>-0.8100000000000001</v>
+        <v>-1.22</v>
       </c>
       <c r="K18">
-        <v>0.45</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N18">
-        <v>45.91</v>
+        <v>41.2</v>
       </c>
       <c r="Q18">
-        <v>16655.82</v>
+        <v>16615.1</v>
       </c>
       <c r="R18">
-        <v>16578.04</v>
+        <v>16589.16</v>
       </c>
       <c r="X18" t="s">
         <v>80</v>
@@ -2899,31 +2893,31 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>54.62</v>
+        <v>50.27</v>
       </c>
       <c r="AA18">
-        <v>125.29</v>
+        <v>105.62</v>
       </c>
       <c r="AB18">
-        <v>154.65</v>
+        <v>144.85</v>
       </c>
       <c r="AC18">
-        <v>-29.36</v>
+        <v>-39.23</v>
       </c>
       <c r="AD18">
-        <v>32.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE18">
-        <v>47.67</v>
+        <v>30.98</v>
       </c>
       <c r="AF18">
-        <v>183.28</v>
+        <v>178.82</v>
       </c>
       <c r="AH18">
-        <v>16924.64</v>
+        <v>16909.14</v>
       </c>
       <c r="AI18">
-        <v>16231.44</v>
+        <v>16269.18</v>
       </c>
       <c r="AJ18">
         <v>16199.38</v>
@@ -2932,7 +2926,7 @@
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>17.69</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2946,13 +2940,13 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9810.799999999999</v>
+        <v>9811.75</v>
       </c>
       <c r="E19">
-        <v>1.55</v>
+        <v>0.01</v>
       </c>
       <c r="F19">
-        <v>9810.799999999999</v>
+        <v>9811.75</v>
       </c>
       <c r="G19">
         <v>8995.35</v>
@@ -2961,22 +2955,22 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>9.07</v>
+        <v>9.08</v>
       </c>
       <c r="J19">
-        <v>1.5</v>
+        <v>0.82</v>
       </c>
       <c r="K19">
-        <v>5.14</v>
+        <v>5.66</v>
       </c>
       <c r="N19">
-        <v>66.73</v>
+        <v>65.48</v>
       </c>
       <c r="Q19">
-        <v>9686.540000000001</v>
+        <v>9702.459999999999</v>
       </c>
       <c r="R19">
-        <v>9451.860000000001</v>
+        <v>9475.18</v>
       </c>
       <c r="X19" t="s">
         <v>80</v>
@@ -2985,40 +2979,40 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>66.14</v>
+        <v>66.17</v>
       </c>
       <c r="AA19">
-        <v>92.79000000000001</v>
+        <v>105.28</v>
       </c>
       <c r="AB19">
-        <v>53.58</v>
+        <v>63.92</v>
       </c>
       <c r="AC19">
-        <v>39.21</v>
+        <v>41.35</v>
       </c>
       <c r="AD19">
-        <v>81.58</v>
+        <v>91.77</v>
       </c>
       <c r="AE19">
-        <v>79.3</v>
+        <v>82.63</v>
       </c>
       <c r="AF19">
-        <v>153.88</v>
+        <v>150.55</v>
       </c>
       <c r="AH19">
-        <v>9802.25</v>
+        <v>9856.450000000001</v>
       </c>
       <c r="AI19">
-        <v>9101.459999999999</v>
+        <v>9093.91</v>
       </c>
       <c r="AJ19">
-        <v>9264.24</v>
+        <v>9339.17</v>
       </c>
       <c r="AK19" t="s">
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>24.71</v>
+        <v>26.49</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3032,10 +3026,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11252.55</v>
+        <v>11200.05</v>
       </c>
       <c r="E20">
-        <v>-0.37</v>
+        <v>-0.47</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3044,25 +3038,25 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-1.02</v>
+        <v>-1.49</v>
       </c>
       <c r="I20">
-        <v>2.31</v>
+        <v>1.83</v>
       </c>
       <c r="J20">
-        <v>-0.46</v>
+        <v>-0.99</v>
       </c>
       <c r="K20">
-        <v>0.66</v>
+        <v>0.11</v>
       </c>
       <c r="N20">
-        <v>13.56</v>
+        <v>10.3</v>
       </c>
       <c r="Q20">
-        <v>11281.64</v>
+        <v>11259.21</v>
       </c>
       <c r="R20">
-        <v>11226.96</v>
+        <v>11222.03</v>
       </c>
       <c r="X20" t="s">
         <v>80</v>
@@ -3071,31 +3065,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>52.96</v>
+        <v>49.16</v>
       </c>
       <c r="AA20">
-        <v>35.79</v>
+        <v>29.14</v>
       </c>
       <c r="AB20">
-        <v>31.18</v>
+        <v>30.77</v>
       </c>
       <c r="AC20">
-        <v>4.62</v>
+        <v>-1.63</v>
       </c>
       <c r="AD20">
-        <v>58.93</v>
+        <v>47.14</v>
       </c>
       <c r="AE20">
-        <v>62.19</v>
+        <v>56.15</v>
       </c>
       <c r="AF20">
-        <v>129.29</v>
+        <v>126.52</v>
       </c>
       <c r="AH20">
-        <v>11424.46</v>
+        <v>11416.9</v>
       </c>
       <c r="AI20">
-        <v>11029.47</v>
+        <v>11027.17</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3104,7 +3098,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>12.21</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3118,10 +3112,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27260.55</v>
+        <v>27247.25</v>
       </c>
       <c r="E21">
-        <v>-0.54</v>
+        <v>-0.05</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3130,43 +3124,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.6</v>
+        <v>-6.65</v>
       </c>
       <c r="I21">
-        <v>12.9</v>
+        <v>12.85</v>
       </c>
       <c r="J21">
-        <v>-1.51</v>
+        <v>-0.53</v>
       </c>
       <c r="K21">
-        <v>-2.65</v>
+        <v>-2.39</v>
       </c>
       <c r="L21">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="M21">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="N21">
-        <v>7.79</v>
+        <v>7.82</v>
       </c>
       <c r="O21">
         <v>32</v>
       </c>
       <c r="Q21">
-        <v>27395.19</v>
+        <v>27366.17</v>
       </c>
       <c r="R21">
-        <v>27995.99</v>
+        <v>27932.93</v>
       </c>
       <c r="S21">
-        <v>27819.17</v>
+        <v>27839.34</v>
       </c>
       <c r="T21">
-        <v>27682.21</v>
+        <v>27676.31</v>
       </c>
       <c r="U21">
-        <v>-1.52</v>
+        <v>-1.55</v>
       </c>
       <c r="V21" t="b">
         <v>1</v>
@@ -3181,40 +3175,40 @@
         <v>2</v>
       </c>
       <c r="Z21">
-        <v>37.86</v>
+        <v>37.64</v>
       </c>
       <c r="AA21">
-        <v>-155.42</v>
+        <v>-175.31</v>
       </c>
       <c r="AB21">
-        <v>-43.1</v>
+        <v>-69.54000000000001</v>
       </c>
       <c r="AC21">
-        <v>-112.32</v>
+        <v>-105.77</v>
       </c>
       <c r="AD21">
-        <v>4.79</v>
+        <v>2.88</v>
       </c>
       <c r="AE21">
-        <v>7.7</v>
+        <v>5.96</v>
       </c>
       <c r="AF21">
-        <v>408.5</v>
+        <v>388.97</v>
       </c>
       <c r="AH21">
-        <v>29006.06</v>
+        <v>28965.51</v>
       </c>
       <c r="AI21">
-        <v>26985.92</v>
+        <v>26900.35</v>
       </c>
       <c r="AJ21">
-        <v>28507.71</v>
+        <v>28395.64</v>
       </c>
       <c r="AK21" t="s">
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>27.15</v>
+        <v>28.98</v>
       </c>
     </row>
   </sheetData>
@@ -3355,7 +3349,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3395,16 +3389,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>80</v>
@@ -3415,16 +3409,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>80</v>
@@ -3435,2012 +3429,2009 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="D10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>112</v>
+      <c r="A11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>10.31</v>
+      </c>
+      <c r="D11" s="8">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="8">
-        <v>10.61</v>
+        <v>0.53</v>
       </c>
       <c r="D12" s="8">
-        <v>10.31</v>
+        <v>0.05</v>
       </c>
       <c r="E12" s="9">
-        <v>-0.3</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="8">
-        <v>0.59</v>
+        <v>4.32</v>
       </c>
       <c r="D13" s="8">
-        <v>0.53</v>
+        <v>4.14</v>
       </c>
       <c r="E13" s="9">
-        <v>-0.06</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="8">
-        <v>4.14</v>
+        <v>-1.75</v>
       </c>
       <c r="D14" s="8">
-        <v>4.32</v>
-      </c>
-      <c r="E14" s="10">
-        <v>0.18</v>
+        <v>-2.01</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="8">
-        <v>-1.09</v>
+        <v>1.14</v>
       </c>
       <c r="D15" s="8">
-        <v>-1.75</v>
+        <v>0.43</v>
       </c>
       <c r="E15" s="9">
-        <v>-0.66</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="8">
-        <v>-0.2</v>
+        <v>-1.37</v>
       </c>
       <c r="D16" s="8">
-        <v>1.14</v>
+        <v>-1.29</v>
       </c>
       <c r="E16" s="10">
-        <v>1.34</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="8">
-        <v>-0.41</v>
+        <v>10.24</v>
       </c>
       <c r="D17" s="8">
-        <v>-1.37</v>
+        <v>9.17</v>
       </c>
       <c r="E17" s="9">
-        <v>-0.96</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="8">
-        <v>9.08</v>
+        <v>4.45</v>
       </c>
       <c r="D18" s="8">
-        <v>10.24</v>
-      </c>
-      <c r="E18" s="10">
-        <v>1.16</v>
+        <v>3.71</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="8">
-        <v>4.92</v>
+        <v>0.59</v>
       </c>
       <c r="D19" s="8">
-        <v>4.45</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.47</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0.35</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="8">
-        <v>0.63</v>
+        <v>4.74</v>
       </c>
       <c r="D20" s="8">
-        <v>0.59</v>
+        <v>4.52</v>
       </c>
       <c r="E20" s="9">
-        <v>-0.04</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="8">
-        <v>3.87</v>
+        <v>3.96</v>
       </c>
       <c r="D21" s="8">
-        <v>4.74</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0.87</v>
+        <v>3.57</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="8">
-        <v>3.89</v>
+        <v>-0.2</v>
       </c>
       <c r="D22" s="8">
-        <v>3.96</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0.07000000000000001</v>
+        <v>-0.67</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="8">
-        <v>-0.54</v>
+        <v>4.79</v>
       </c>
       <c r="D23" s="8">
-        <v>-0.2</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0.34</v>
+        <v>4.68</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="8">
-        <v>6.13</v>
+        <v>2.63</v>
       </c>
       <c r="D24" s="8">
-        <v>4.79</v>
+        <v>1.68</v>
       </c>
       <c r="E24" s="9">
-        <v>-1.34</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="8">
-        <v>3.3</v>
+        <v>-1.83</v>
       </c>
       <c r="D25" s="8">
-        <v>2.63</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.67</v>
+        <v>-1.16</v>
+      </c>
+      <c r="E25" s="10">
+        <v>0.67</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="8">
-        <v>-3.14</v>
+        <v>-0.15</v>
       </c>
       <c r="D26" s="8">
-        <v>-1.83</v>
+        <v>0.1</v>
       </c>
       <c r="E26" s="10">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="8">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="D27" s="8">
-        <v>-0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E27" s="9">
-        <v>-0.55</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="8">
-        <v>1.16</v>
+        <v>5.14</v>
       </c>
       <c r="D28" s="8">
-        <v>0.45</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.71</v>
+        <v>5.66</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0.52</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="8">
-        <v>3.59</v>
+        <v>0.66</v>
       </c>
       <c r="D29" s="8">
-        <v>5.14</v>
-      </c>
-      <c r="E29" s="10">
-        <v>1.55</v>
+        <v>0.11</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="8">
-        <v>1.72</v>
+        <v>-2.65</v>
       </c>
       <c r="D30" s="8">
-        <v>0.66</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-1.06</v>
+        <v>-2.39</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0.26</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="8">
-        <v>-1.82</v>
+        <v>0.96</v>
       </c>
       <c r="D31" s="8">
-        <v>-2.65</v>
+        <v>-1.48</v>
       </c>
       <c r="E31" s="9">
-        <v>-0.83</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="8">
-        <v>-0.16</v>
+        <v>-0.79</v>
       </c>
       <c r="D32" s="8">
-        <v>0.96</v>
-      </c>
-      <c r="E32" s="10">
-        <v>1.12</v>
+        <v>-1.69</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="8">
-        <v>-0.84</v>
+        <v>-0.28</v>
       </c>
       <c r="D33" s="8">
-        <v>-0.79</v>
-      </c>
-      <c r="E33" s="10">
-        <v>0.05</v>
+        <v>-0.45</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="8">
-        <v>-1.07</v>
+        <v>0.04</v>
       </c>
       <c r="D34" s="8">
-        <v>-0.28</v>
-      </c>
-      <c r="E34" s="10">
-        <v>0.79</v>
+        <v>-0.5</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="8">
-        <v>-0.14</v>
+        <v>-1.08</v>
       </c>
       <c r="D35" s="8">
-        <v>0.04</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0.18</v>
+        <v>-1.66</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="8">
-        <v>-1.93</v>
+        <v>-1.99</v>
       </c>
       <c r="D36" s="8">
-        <v>-1.08</v>
+        <v>-0.95</v>
       </c>
       <c r="E36" s="10">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="8">
-        <v>-1.55</v>
+        <v>0.8</v>
       </c>
       <c r="D37" s="8">
-        <v>-1.99</v>
+        <v>-0.6</v>
       </c>
       <c r="E37" s="9">
-        <v>-0.44</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="8">
-        <v>-0.23</v>
+        <v>0.19</v>
       </c>
       <c r="D38" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="E38" s="10">
-        <v>1.03</v>
+        <v>-0.7</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="8">
-        <v>0.23</v>
+        <v>-0.64</v>
       </c>
       <c r="D39" s="8">
-        <v>0.19</v>
+        <v>-0.89</v>
       </c>
       <c r="E39" s="9">
-        <v>-0.04</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="8">
-        <v>-0.45</v>
+        <v>0.74</v>
       </c>
       <c r="D40" s="8">
-        <v>-0.64</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.19</v>
+        <v>2.26</v>
+      </c>
+      <c r="E40" s="10">
+        <v>1.52</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="8">
-        <v>-0.38</v>
+        <v>-0.84</v>
       </c>
       <c r="D41" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="E41" s="10">
-        <v>1.12</v>
+        <v>-1.88</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="8">
-        <v>-0.64</v>
+        <v>-0.43</v>
       </c>
       <c r="D42" s="8">
-        <v>-0.84</v>
+        <v>-0.78</v>
       </c>
       <c r="E42" s="9">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="8">
-        <v>-0.83</v>
+        <v>0.68</v>
       </c>
       <c r="D43" s="8">
-        <v>-0.43</v>
-      </c>
-      <c r="E43" s="10">
-        <v>0.4</v>
+        <v>-0.54</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="8">
-        <v>3.23</v>
+        <v>0.46</v>
       </c>
       <c r="D44" s="8">
-        <v>0.68</v>
+        <v>-0.36</v>
       </c>
       <c r="E44" s="9">
-        <v>-2.55</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="8">
-        <v>0.75</v>
+        <v>1.3</v>
       </c>
       <c r="D45" s="8">
-        <v>0.46</v>
+        <v>1.09</v>
       </c>
       <c r="E45" s="9">
-        <v>-0.29</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="8">
-        <v>-0.99</v>
+        <v>-1.28</v>
       </c>
       <c r="D46" s="8">
-        <v>1.3</v>
+        <v>-0.44</v>
       </c>
       <c r="E46" s="10">
-        <v>2.29</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="8">
-        <v>-1.21</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D47" s="8">
-        <v>-1.28</v>
+        <v>-1.22</v>
       </c>
       <c r="E47" s="9">
-        <v>-0.07000000000000001</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>-0.46</v>
+        <v>1.5</v>
       </c>
       <c r="D48" s="8">
-        <v>-0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="E48" s="9">
-        <v>-0.35</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="8">
-        <v>2.81</v>
+        <v>-0.46</v>
       </c>
       <c r="D49" s="8">
-        <v>1.5</v>
+        <v>-0.99</v>
       </c>
       <c r="E49" s="9">
-        <v>-1.31</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="8">
-        <v>0.6899999999999999</v>
+        <v>-1.51</v>
       </c>
       <c r="D50" s="8">
-        <v>-0.46</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-1.15</v>
+        <v>-0.53</v>
+      </c>
+      <c r="E50" s="10">
+        <v>0.98</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="8">
-        <v>-1.21</v>
+        <v>23.56</v>
       </c>
       <c r="D51" s="8">
-        <v>-1.51</v>
+        <v>22.33</v>
       </c>
       <c r="E51" s="9">
-        <v>-0.3</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="8">
-        <v>25.42</v>
+        <v>12.92</v>
       </c>
       <c r="D52" s="8">
-        <v>23.56</v>
+        <v>12.28</v>
       </c>
       <c r="E52" s="9">
-        <v>-1.86</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="8">
-        <v>15.09</v>
+        <v>3.02</v>
       </c>
       <c r="D53" s="8">
-        <v>12.92</v>
+        <v>2.99</v>
       </c>
       <c r="E53" s="9">
-        <v>-2.17</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="8">
-        <v>3.38</v>
+        <v>10.79</v>
       </c>
       <c r="D54" s="8">
-        <v>3.02</v>
+        <v>10.42</v>
       </c>
       <c r="E54" s="9">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="8">
-        <v>11.14</v>
+        <v>-13.01</v>
       </c>
       <c r="D55" s="8">
-        <v>10.79</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.35</v>
+        <v>-12.77</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.24</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="8">
-        <v>-13.82</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D56" s="8">
-        <v>-13.01</v>
-      </c>
-      <c r="E56" s="10">
-        <v>0.8100000000000001</v>
+        <v>-0.61</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="8">
-        <v>-0.25</v>
+        <v>-10.65</v>
       </c>
       <c r="D57" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.31</v>
+        <v>-10.49</v>
+      </c>
+      <c r="E57" s="10">
+        <v>0.16</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="8">
-        <v>-9.57</v>
+        <v>3.69</v>
       </c>
       <c r="D58" s="8">
-        <v>-10.65</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-1.08</v>
+        <v>4.16</v>
+      </c>
+      <c r="E58" s="10">
+        <v>0.47</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="8">
-        <v>4.91</v>
+        <v>-4.03</v>
       </c>
       <c r="D59" s="8">
-        <v>3.69</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-1.22</v>
+        <v>-3.05</v>
+      </c>
+      <c r="E59" s="10">
+        <v>0.98</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="8">
-        <v>-2.95</v>
+        <v>39.73</v>
       </c>
       <c r="D60" s="8">
-        <v>-4.03</v>
+        <v>38.62</v>
       </c>
       <c r="E60" s="9">
-        <v>-1.08</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="8">
-        <v>44.7</v>
+        <v>2.77</v>
       </c>
       <c r="D61" s="8">
-        <v>39.73</v>
+        <v>2.3</v>
       </c>
       <c r="E61" s="9">
-        <v>-4.97</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="8">
-        <v>3.48</v>
+        <v>28.14</v>
       </c>
       <c r="D62" s="8">
-        <v>2.77</v>
+        <v>27.6</v>
       </c>
       <c r="E62" s="9">
-        <v>-0.71</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="8">
-        <v>30.18</v>
+        <v>20.46</v>
       </c>
       <c r="D63" s="8">
-        <v>28.14</v>
+        <v>20.37</v>
       </c>
       <c r="E63" s="9">
-        <v>-2.04</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="8">
-        <v>21.58</v>
+        <v>-1.5</v>
       </c>
       <c r="D64" s="8">
-        <v>20.46</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-1.12</v>
+        <v>-1.34</v>
+      </c>
+      <c r="E64" s="10">
+        <v>0.16</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="8">
-        <v>-0.71</v>
+        <v>-4.35</v>
       </c>
       <c r="D65" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-0.79</v>
+        <v>-3.96</v>
+      </c>
+      <c r="E65" s="10">
+        <v>0.39</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="8">
-        <v>-3.86</v>
+        <v>1.13</v>
       </c>
       <c r="D66" s="8">
-        <v>-4.35</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-0.49</v>
+        <v>1.39</v>
+      </c>
+      <c r="E66" s="10">
+        <v>0.26</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="8">
-        <v>1.81</v>
+        <v>12.83</v>
       </c>
       <c r="D67" s="8">
-        <v>1.13</v>
+        <v>12.03</v>
       </c>
       <c r="E67" s="9">
-        <v>-0.68</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="8">
-        <v>13.42</v>
+        <v>-4.45</v>
       </c>
       <c r="D68" s="8">
-        <v>12.83</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-0.59</v>
+        <v>-3.75</v>
+      </c>
+      <c r="E68" s="10">
+        <v>0.7</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="8">
-        <v>-3.05</v>
+        <v>6.6</v>
       </c>
       <c r="D69" s="8">
-        <v>-4.45</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-1.4</v>
+        <v>6.68</v>
+      </c>
+      <c r="E69" s="10">
+        <v>0.08</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="8">
-        <v>7.72</v>
+        <v>-3.47</v>
       </c>
       <c r="D70" s="8">
-        <v>6.6</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-1.12</v>
+        <v>-3.17</v>
+      </c>
+      <c r="E70" s="10">
+        <v>0.3</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="8">
-        <v>-2.62</v>
+        <v>-3.82</v>
       </c>
       <c r="D71" s="8">
-        <v>-3.47</v>
+        <v>-4.77</v>
       </c>
       <c r="E71" s="9">
-        <v>-0.85</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="8">
-        <v>-4.3</v>
+        <v>3.36</v>
       </c>
       <c r="D72" s="8">
-        <v>-3.82</v>
+        <v>3.43</v>
       </c>
       <c r="E72" s="10">
-        <v>0.48</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="8">
-        <v>5.22</v>
+        <v>14.96</v>
       </c>
       <c r="D73" s="8">
-        <v>3.36</v>
+        <v>13.14</v>
       </c>
       <c r="E73" s="9">
-        <v>-1.86</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="8">
-        <v>12.24</v>
+        <v>0.26</v>
       </c>
       <c r="D74" s="8">
-        <v>14.96</v>
+        <v>0.98</v>
       </c>
       <c r="E74" s="10">
-        <v>2.72</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="8">
-        <v>1.86</v>
+        <v>11.84</v>
       </c>
       <c r="D75" s="8">
-        <v>0.26</v>
+        <v>10.72</v>
       </c>
       <c r="E75" s="9">
-        <v>-1.6</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="8">
-        <v>12.42</v>
+        <v>-3.9</v>
       </c>
       <c r="D76" s="8">
-        <v>11.84</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-0.58</v>
+        <v>-2.7</v>
+      </c>
+      <c r="E76" s="10">
+        <v>1.2</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="8">
-        <v>-0.9</v>
+        <v>-6.66</v>
       </c>
       <c r="D77" s="8">
-        <v>-3.9</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-3</v>
+        <v>-6.11</v>
+      </c>
+      <c r="E77" s="10">
+        <v>0.55</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="8">
-        <v>-6.62</v>
+        <v>7.52</v>
       </c>
       <c r="D78" s="8">
-        <v>-6.66</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-0.04</v>
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E78" s="10">
+        <v>1.34</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="8">
-        <v>9.34</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D79" s="8">
-        <v>7.52</v>
+        <v>7.35</v>
       </c>
       <c r="E79" s="9">
-        <v>-1.82</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="8">
-        <v>12</v>
+        <v>16.66</v>
       </c>
       <c r="D80" s="8">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-3.3</v>
+        <v>18.43</v>
+      </c>
+      <c r="E80" s="10">
+        <v>1.77</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="8">
-        <v>16.43</v>
+        <v>4.77</v>
       </c>
       <c r="D81" s="8">
-        <v>16.66</v>
+        <v>4.8</v>
       </c>
       <c r="E81" s="10">
-        <v>0.23</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="8">
-        <v>6.51</v>
+        <v>4.22</v>
       </c>
       <c r="D82" s="8">
-        <v>4.77</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-1.74</v>
+        <v>4.4</v>
+      </c>
+      <c r="E82" s="10">
+        <v>0.18</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C83" s="8">
-        <v>6.01</v>
+        <v>-0.86</v>
       </c>
       <c r="D83" s="8">
-        <v>4.22</v>
+        <v>-1.48</v>
       </c>
       <c r="E83" s="9">
-        <v>-1.79</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="8">
-        <v>-0.96</v>
+        <v>-5.95</v>
       </c>
       <c r="D84" s="8">
-        <v>-0.86</v>
-      </c>
-      <c r="E84" s="10">
-        <v>0.1</v>
+        <v>-6.48</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="8">
-        <v>-5.55</v>
+        <v>-3.96</v>
       </c>
       <c r="D85" s="8">
-        <v>-5.95</v>
-      </c>
-      <c r="E85" s="9">
-        <v>-0.4</v>
+        <v>-3.93</v>
+      </c>
+      <c r="E85" s="10">
+        <v>0.03</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="8">
-        <v>-4.33</v>
+        <v>-6.85</v>
       </c>
       <c r="D86" s="8">
-        <v>-3.96</v>
-      </c>
-      <c r="E86" s="10">
-        <v>0.37</v>
+        <v>-7.18</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="8">
-        <v>-6.64</v>
+        <v>-14.48</v>
       </c>
       <c r="D87" s="8">
-        <v>-6.85</v>
+        <v>-14.87</v>
       </c>
       <c r="E87" s="9">
-        <v>-0.21</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="8">
-        <v>-15.19</v>
+        <v>-7.5</v>
       </c>
       <c r="D88" s="8">
-        <v>-14.48</v>
-      </c>
-      <c r="E88" s="10">
-        <v>0.71</v>
+        <v>-7.9</v>
+      </c>
+      <c r="E88" s="9">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="8">
-        <v>-7.15</v>
+        <v>-20.35</v>
       </c>
       <c r="D89" s="8">
-        <v>-7.5</v>
+        <v>-20.59</v>
       </c>
       <c r="E89" s="9">
-        <v>-0.35</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="8">
-        <v>-20.65</v>
+        <v>-0.25</v>
       </c>
       <c r="D90" s="8">
-        <v>-20.35</v>
-      </c>
-      <c r="E90" s="10">
-        <v>0.3</v>
+        <v>-0.7</v>
+      </c>
+      <c r="E90" s="9">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="8">
-        <v>-0.19</v>
+        <v>-3.82</v>
       </c>
       <c r="D91" s="8">
-        <v>-0.25</v>
-      </c>
-      <c r="E91" s="9">
-        <v>-0.06</v>
+        <v>-3.55</v>
+      </c>
+      <c r="E91" s="10">
+        <v>0.27</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="8">
-        <v>-3.64</v>
+        <v>-5.78</v>
       </c>
       <c r="D92" s="8">
-        <v>-3.82</v>
-      </c>
-      <c r="E92" s="9">
-        <v>-0.18</v>
+        <v>-4.87</v>
+      </c>
+      <c r="E92" s="10">
+        <v>0.91</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="8">
-        <v>-6.13</v>
+        <v>-4.99</v>
       </c>
       <c r="D93" s="8">
-        <v>-5.78</v>
-      </c>
-      <c r="E93" s="10">
-        <v>0.35</v>
+        <v>-5.66</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="8">
-        <v>-3.99</v>
+        <v>-8.09</v>
       </c>
       <c r="D94" s="8">
-        <v>-4.99</v>
+        <v>-8.56</v>
       </c>
       <c r="E94" s="9">
-        <v>-1</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="8">
-        <v>-8.33</v>
+        <v>-11.04</v>
       </c>
       <c r="D95" s="8">
-        <v>-8.09</v>
-      </c>
-      <c r="E95" s="10">
-        <v>0.24</v>
+        <v>-11.55</v>
+      </c>
+      <c r="E95" s="9">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="8">
-        <v>-10.75</v>
+        <v>-0.28</v>
       </c>
       <c r="D96" s="8">
-        <v>-11.04</v>
+        <v>-1.18</v>
       </c>
       <c r="E96" s="9">
-        <v>-0.29</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="8">
-        <v>0</v>
+        <v>-7.25</v>
       </c>
       <c r="D97" s="8">
-        <v>-0.28</v>
+        <v>-7.54</v>
       </c>
       <c r="E97" s="9">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="8">
-        <v>-8.140000000000001</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="D98" s="8">
-        <v>-7.25</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="E98" s="10">
-        <v>0.89</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="8">
-        <v>-8.57</v>
+        <v>-1.2</v>
       </c>
       <c r="D99" s="8">
-        <v>-8.800000000000001</v>
+        <v>-1.66</v>
       </c>
       <c r="E99" s="9">
-        <v>-0.23</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="8">
-        <v>-0.9</v>
+        <v>-1.02</v>
       </c>
       <c r="D100" s="8">
-        <v>-1.2</v>
+        <v>-1.49</v>
       </c>
       <c r="E100" s="9">
-        <v>-0.3</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="8">
-        <v>-0.73</v>
+        <v>-6.6</v>
       </c>
       <c r="D101" s="8">
-        <v>0</v>
-      </c>
-      <c r="E101" s="10">
-        <v>0.73</v>
+        <v>-6.65</v>
+      </c>
+      <c r="E101" s="9">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C102" s="8">
-        <v>-0.66</v>
+        <v>29392.15</v>
       </c>
       <c r="D102" s="8">
-        <v>-1.02</v>
+        <v>29207.9</v>
       </c>
       <c r="E102" s="9">
-        <v>-0.36</v>
+        <v>-184.25</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C103" s="8">
-        <v>-6.1</v>
+        <v>9878.049999999999</v>
       </c>
       <c r="D103" s="8">
-        <v>-6.6</v>
+        <v>9822.75</v>
       </c>
       <c r="E103" s="9">
-        <v>-0.5</v>
+        <v>-55.3</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C104" s="8">
-        <v>29363.05</v>
+        <v>12138</v>
       </c>
       <c r="D104" s="8">
-        <v>29392.15</v>
+        <v>12142.85</v>
       </c>
       <c r="E104" s="10">
-        <v>29.1</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="8">
-        <v>9920.15</v>
+        <v>38690.25</v>
       </c>
       <c r="D105" s="8">
-        <v>9878.049999999999</v>
+        <v>38554.2</v>
       </c>
       <c r="E105" s="9">
-        <v>-42.1</v>
+        <v>-136.05</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="8">
-        <v>12092.2</v>
+        <v>48837.3</v>
       </c>
       <c r="D106" s="8">
-        <v>12138</v>
-      </c>
-      <c r="E106" s="10">
-        <v>45.8</v>
+        <v>48615.05</v>
+      </c>
+      <c r="E106" s="9">
+        <v>-222.25</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="8">
-        <v>38776.9</v>
+        <v>26327.95</v>
       </c>
       <c r="D107" s="8">
-        <v>38690.25</v>
+        <v>26213.65</v>
       </c>
       <c r="E107" s="9">
-        <v>-86.65000000000001</v>
+        <v>-114.3</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="8">
-        <v>48429.35</v>
+        <v>31453.9</v>
       </c>
       <c r="D108" s="8">
-        <v>48837.3</v>
-      </c>
-      <c r="E108" s="10">
-        <v>407.95</v>
+        <v>31357.75</v>
+      </c>
+      <c r="E108" s="9">
+        <v>-96.15000000000001</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="8">
-        <v>26426.75</v>
+        <v>16620.6</v>
       </c>
       <c r="D109" s="8">
-        <v>26327.95</v>
+        <v>16545.3</v>
       </c>
       <c r="E109" s="9">
-        <v>-98.8</v>
+        <v>-75.3</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="8">
-        <v>31332.55</v>
+        <v>9393.15</v>
       </c>
       <c r="D110" s="8">
-        <v>31453.9</v>
+        <v>9419.1</v>
       </c>
       <c r="E110" s="10">
-        <v>121.35</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="8">
-        <v>16630.45</v>
+        <v>1574.95</v>
       </c>
       <c r="D111" s="8">
-        <v>16620.6</v>
-      </c>
-      <c r="E111" s="9">
-        <v>-9.85</v>
+        <v>1590.1</v>
+      </c>
+      <c r="E111" s="10">
+        <v>15.15</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="8">
-        <v>9409.799999999999</v>
+        <v>13033.75</v>
       </c>
       <c r="D112" s="8">
-        <v>9393.15</v>
+        <v>12941.7</v>
       </c>
       <c r="E112" s="9">
-        <v>-16.65</v>
+        <v>-92.05</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="8">
-        <v>1569.1</v>
+        <v>9894.950000000001</v>
       </c>
       <c r="D113" s="8">
-        <v>1574.95</v>
-      </c>
-      <c r="E113" s="10">
-        <v>5.85</v>
+        <v>9844.950000000001</v>
+      </c>
+      <c r="E113" s="9">
+        <v>-50</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="8">
-        <v>13171.45</v>
+        <v>8788.950000000001</v>
       </c>
       <c r="D114" s="8">
-        <v>13033.75</v>
+        <v>8738.799999999999</v>
       </c>
       <c r="E114" s="9">
-        <v>-137.7</v>
+        <v>-50.15</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="8">
-        <v>9869.25</v>
+        <v>26686.8</v>
       </c>
       <c r="D115" s="8">
-        <v>9894.950000000001</v>
-      </c>
-      <c r="E115" s="10">
-        <v>25.7</v>
+        <v>26445.55</v>
+      </c>
+      <c r="E115" s="9">
+        <v>-241.25</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="8">
-        <v>8817.5</v>
+        <v>898.4</v>
       </c>
       <c r="D116" s="8">
-        <v>8788.950000000001</v>
+        <v>895.65</v>
       </c>
       <c r="E116" s="9">
-        <v>-28.55</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="8">
-        <v>26762.5</v>
+        <v>31101.75</v>
       </c>
       <c r="D117" s="8">
-        <v>26686.8</v>
-      </c>
-      <c r="E117" s="9">
-        <v>-75.7</v>
+        <v>31128.25</v>
+      </c>
+      <c r="E117" s="10">
+        <v>26.5</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="8">
-        <v>889.8</v>
+        <v>16581.85</v>
       </c>
       <c r="D118" s="8">
-        <v>898.4</v>
-      </c>
-      <c r="E118" s="10">
-        <v>8.6</v>
+        <v>16505.3</v>
+      </c>
+      <c r="E118" s="9">
+        <v>-76.55</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="8">
-        <v>31178.55</v>
+        <v>9810.799999999999</v>
       </c>
       <c r="D119" s="8">
-        <v>31101.75</v>
-      </c>
-      <c r="E119" s="9">
-        <v>-76.8</v>
+        <v>9811.75</v>
+      </c>
+      <c r="E119" s="10">
+        <v>0.95</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="8">
-        <v>16632.35</v>
+        <v>11252.55</v>
       </c>
       <c r="D120" s="8">
-        <v>16581.85</v>
+        <v>11200.05</v>
       </c>
       <c r="E120" s="9">
-        <v>-50.5</v>
+        <v>-52.5</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="8">
-        <v>9660.700000000001</v>
+        <v>27260.55</v>
       </c>
       <c r="D121" s="8">
-        <v>9810.799999999999</v>
-      </c>
-      <c r="E121" s="10">
-        <v>150.1</v>
+        <v>27247.25</v>
+      </c>
+      <c r="E121" s="9">
+        <v>-13.3</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="8">
+        <v>50</v>
+      </c>
+      <c r="D122" s="8">
         <v>56</v>
       </c>
-      <c r="B122" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C122" s="8">
-        <v>11293.9</v>
-      </c>
-      <c r="D122" s="8">
-        <v>11252.55</v>
-      </c>
-      <c r="E122" s="9">
-        <v>-41.35</v>
+      <c r="E122" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C123" s="8">
-        <v>27408.4</v>
+        <v>56</v>
       </c>
       <c r="D123" s="8">
-        <v>27260.55</v>
+        <v>50</v>
       </c>
       <c r="E123" s="9">
-        <v>-147.85</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5448,16 +5439,16 @@
         <v>38</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C124" s="8">
-        <v>93</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="D124" s="8">
-        <v>99</v>
-      </c>
-      <c r="E124" s="10">
-        <v>6</v>
+        <v>66.45</v>
+      </c>
+      <c r="E124" s="9">
+        <v>-4.31</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -5465,447 +5456,328 @@
         <v>39</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C125" s="8">
-        <v>62</v>
+        <v>46.96</v>
       </c>
       <c r="D125" s="8">
-        <v>50</v>
+        <v>42.54</v>
       </c>
       <c r="E125" s="9">
-        <v>-12</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C126" s="8">
-        <v>50</v>
+        <v>63.78</v>
       </c>
       <c r="D126" s="8">
-        <v>44</v>
-      </c>
-      <c r="E126" s="9">
-        <v>-6</v>
+        <v>64.02</v>
+      </c>
+      <c r="E126" s="10">
+        <v>0.24</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C127" s="8">
-        <v>44</v>
+        <v>40.76</v>
       </c>
       <c r="D127" s="8">
-        <v>56</v>
-      </c>
-      <c r="E127" s="10">
-        <v>12</v>
+        <v>37.95</v>
+      </c>
+      <c r="E127" s="9">
+        <v>-2.81</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C128" s="8">
-        <v>56</v>
+        <v>46.4</v>
       </c>
       <c r="D128" s="8">
-        <v>62</v>
-      </c>
-      <c r="E128" s="10">
-        <v>6</v>
+        <v>43.74</v>
+      </c>
+      <c r="E128" s="9">
+        <v>-2.66</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C129" s="8">
-        <v>99</v>
+        <v>42.54</v>
       </c>
       <c r="D129" s="8">
-        <v>87</v>
+        <v>40.14</v>
       </c>
       <c r="E129" s="9">
-        <v>-12</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C130" s="8">
-        <v>87</v>
+        <v>63.01</v>
       </c>
       <c r="D130" s="8">
-        <v>93</v>
-      </c>
-      <c r="E130" s="10">
-        <v>6</v>
+        <v>61.73</v>
+      </c>
+      <c r="E130" s="9">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C131" s="8">
-        <v>70.48</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="D131" s="8">
-        <v>70.76000000000001</v>
-      </c>
-      <c r="E131" s="10">
-        <v>0.28</v>
+        <v>64.17</v>
+      </c>
+      <c r="E131" s="9">
+        <v>-5.54</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="8">
-        <v>50.68</v>
+        <v>48.7</v>
       </c>
       <c r="D132" s="8">
-        <v>46.96</v>
-      </c>
-      <c r="E132" s="9">
-        <v>-3.72</v>
+        <v>51.23</v>
+      </c>
+      <c r="E132" s="10">
+        <v>2.53</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="8">
-        <v>61.57</v>
+        <v>58.47</v>
       </c>
       <c r="D133" s="8">
-        <v>63.78</v>
+        <v>61.52</v>
       </c>
       <c r="E133" s="10">
-        <v>2.21</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="8">
-        <v>42.63</v>
+        <v>57.65</v>
       </c>
       <c r="D134" s="8">
-        <v>40.76</v>
+        <v>53.52</v>
       </c>
       <c r="E134" s="9">
-        <v>-1.87</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="8">
-        <v>40.21</v>
+        <v>45.09</v>
       </c>
       <c r="D135" s="8">
-        <v>46.4</v>
-      </c>
-      <c r="E135" s="10">
-        <v>6.19</v>
+        <v>40.38</v>
+      </c>
+      <c r="E135" s="9">
+        <v>-4.71</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="8">
-        <v>44.68</v>
+        <v>64.72</v>
       </c>
       <c r="D136" s="8">
-        <v>42.54</v>
+        <v>61.26</v>
       </c>
       <c r="E136" s="9">
-        <v>-2.14</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="8">
-        <v>62.09</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="D137" s="8">
-        <v>63.01</v>
-      </c>
-      <c r="E137" s="10">
-        <v>0.92</v>
+        <v>57.91</v>
+      </c>
+      <c r="E137" s="9">
+        <v>-8.33</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="8">
-        <v>70.44</v>
+        <v>52.87</v>
       </c>
       <c r="D138" s="8">
-        <v>69.70999999999999</v>
+        <v>51.55</v>
       </c>
       <c r="E138" s="9">
-        <v>-0.73</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="8">
-        <v>50.25</v>
+        <v>46.25</v>
       </c>
       <c r="D139" s="8">
-        <v>48.7</v>
-      </c>
-      <c r="E139" s="9">
-        <v>-1.55</v>
+        <v>47.13</v>
+      </c>
+      <c r="E139" s="10">
+        <v>0.88</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="8">
-        <v>57.25</v>
+        <v>54.62</v>
       </c>
       <c r="D140" s="8">
-        <v>58.47</v>
-      </c>
-      <c r="E140" s="10">
-        <v>1.22</v>
+        <v>50.27</v>
+      </c>
+      <c r="E140" s="9">
+        <v>-4.35</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="8">
-        <v>64.56999999999999</v>
+        <v>66.14</v>
       </c>
       <c r="D141" s="8">
-        <v>57.65</v>
-      </c>
-      <c r="E141" s="9">
-        <v>-6.92</v>
+        <v>66.17</v>
+      </c>
+      <c r="E141" s="10">
+        <v>0.03</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="8">
-        <v>41.85</v>
+        <v>52.96</v>
       </c>
       <c r="D142" s="8">
-        <v>45.09</v>
-      </c>
-      <c r="E142" s="10">
-        <v>3.24</v>
+        <v>49.16</v>
+      </c>
+      <c r="E142" s="9">
+        <v>-3.8</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="8">
-        <v>66.72</v>
+        <v>37.86</v>
       </c>
       <c r="D143" s="8">
-        <v>64.72</v>
+        <v>37.64</v>
       </c>
       <c r="E143" s="9">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C144" s="8">
-        <v>69.13</v>
-      </c>
-      <c r="D144" s="8">
-        <v>66.23999999999999</v>
-      </c>
-      <c r="E144" s="9">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C145" s="8">
-        <v>49.09</v>
-      </c>
-      <c r="D145" s="8">
-        <v>52.87</v>
-      </c>
-      <c r="E145" s="10">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C146" s="8">
-        <v>48.41</v>
-      </c>
-      <c r="D146" s="8">
-        <v>46.25</v>
-      </c>
-      <c r="E146" s="9">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C147" s="8">
-        <v>57.68</v>
-      </c>
-      <c r="D147" s="8">
-        <v>54.62</v>
-      </c>
-      <c r="E147" s="9">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C148" s="8">
-        <v>60.96</v>
-      </c>
-      <c r="D148" s="8">
-        <v>66.14</v>
-      </c>
-      <c r="E148" s="10">
-        <v>5.18</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C149" s="8">
-        <v>56.13</v>
-      </c>
-      <c r="D149" s="8">
-        <v>52.96</v>
-      </c>
-      <c r="E149" s="9">
-        <v>-3.17</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C150" s="8">
-        <v>40.37</v>
-      </c>
-      <c r="D150" s="8">
-        <v>37.86</v>
-      </c>
-      <c r="E150" s="9">
-        <v>-2.51</v>
+        <v>-0.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5929,28 +5801,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5964,16 +5836,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="13">
-        <v>54.8</v>
+        <v>52.4</v>
       </c>
       <c r="E2" s="13">
         <v>50</v>
       </c>
       <c r="F2" s="13">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
@@ -6113,34 +5985,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.6673</v>
+        <v>0.6548</v>
       </c>
       <c r="B2" s="16">
-        <v>0.4591</v>
+        <v>0.412</v>
       </c>
       <c r="C2" s="16">
-        <v>0.4184</v>
+        <v>0.3739</v>
       </c>
       <c r="D2" s="16">
-        <v>0.2977</v>
+        <v>0.2992</v>
       </c>
       <c r="E2" s="16">
-        <v>0.2363</v>
+        <v>0.2372</v>
       </c>
       <c r="F2" s="16">
-        <v>0.2229</v>
+        <v>0.2216</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1789</v>
+        <v>0.1793</v>
       </c>
       <c r="H2" s="16">
-        <v>0.1758</v>
+        <v>0.1709</v>
       </c>
       <c r="I2" s="16">
-        <v>0.1552</v>
+        <v>0.1558</v>
       </c>
       <c r="J2" s="16">
-        <v>0.1448</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6148,13 +6020,13 @@
         <v>51</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>43</v>
@@ -6177,34 +6049,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.1369</v>
+        <v>0.1364</v>
       </c>
       <c r="B4" s="16">
-        <v>0.1356</v>
+        <v>0.132</v>
       </c>
       <c r="C4" s="16">
-        <v>0.1316</v>
+        <v>0.1261</v>
       </c>
       <c r="D4" s="16">
-        <v>0.1285</v>
+        <v>0.103</v>
       </c>
       <c r="E4" s="16">
-        <v>0.08699999999999999</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="F4" s="16">
-        <v>0.0779</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G4" s="16">
-        <v>0.05980000000000001</v>
+        <v>0.0597</v>
       </c>
       <c r="H4" s="16">
-        <v>0.058</v>
+        <v>0.0565</v>
       </c>
       <c r="I4" s="16">
         <v>-0.0076</v>
       </c>
       <c r="J4" s="16">
-        <v>-0.0158</v>
+        <v>-0.0111</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="124">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,34 +289,70 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.7% → -2.1%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.7%</t>
-  </si>
-  <si>
-    <t>-2.1%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.3 → 46.3</t>
+    <t>49.2 → 51.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>49.2</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>66.2 → 71.1</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>66.2</t>
+  </si>
+  <si>
+    <t>71.1</t>
+  </si>
+  <si>
+    <t>61.7 → 48.2</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
+    <t>61.7</t>
+  </si>
+  <si>
+    <t>48.2</t>
+  </si>
+  <si>
+    <t>51.2 → 46.9</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>46.9</t>
+  </si>
+  <si>
+    <t>50.3 → 48.3</t>
+  </si>
+  <si>
     <t>50.3</t>
   </si>
   <si>
-    <t>46.3</t>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -402,7 +438,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -410,13 +453,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -449,19 +485,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -540,10 +576,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1060,10 +1097,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>29178.1</v>
+        <v>29264.55</v>
       </c>
       <c r="E2">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1072,43 +1109,43 @@
         <v>23474.65</v>
       </c>
       <c r="H2">
-        <v>-1.58</v>
+        <v>-1.29</v>
       </c>
       <c r="I2">
-        <v>24.3</v>
+        <v>24.66</v>
       </c>
       <c r="J2">
-        <v>-1.49</v>
+        <v>-0.66</v>
       </c>
       <c r="K2">
-        <v>7.67</v>
+        <v>7.99</v>
       </c>
       <c r="L2">
-        <v>13.87</v>
+        <v>13.88</v>
       </c>
       <c r="M2">
-        <v>22.86</v>
+        <v>22.92</v>
       </c>
       <c r="N2">
-        <v>23.67</v>
+        <v>23.79</v>
       </c>
       <c r="O2">
         <v>93</v>
       </c>
       <c r="Q2">
-        <v>29319.95</v>
+        <v>29281.15</v>
       </c>
       <c r="R2">
-        <v>28466.22</v>
+        <v>28574.46</v>
       </c>
       <c r="S2">
-        <v>27386.42</v>
+        <v>27458.07</v>
       </c>
       <c r="T2">
-        <v>27009.05</v>
+        <v>27019.83</v>
       </c>
       <c r="U2">
-        <v>8.029999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -1123,34 +1160,34 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>65.76000000000001</v>
+        <v>66.84</v>
       </c>
       <c r="AA2">
-        <v>644.26</v>
+        <v>615.4</v>
       </c>
       <c r="AB2">
-        <v>634.54</v>
+        <v>630.71</v>
       </c>
       <c r="AC2">
-        <v>9.720000000000001</v>
+        <v>-15.32</v>
       </c>
       <c r="AD2">
-        <v>46.95</v>
+        <v>29.49</v>
       </c>
       <c r="AE2">
-        <v>54.09</v>
+        <v>43.29</v>
       </c>
       <c r="AF2">
-        <v>390.08</v>
+        <v>377.37</v>
       </c>
       <c r="AG2">
         <v>-100</v>
       </c>
       <c r="AH2">
-        <v>30606.11</v>
+        <v>30641.07</v>
       </c>
       <c r="AI2">
-        <v>26326.33</v>
+        <v>26507.85</v>
       </c>
       <c r="AJ2">
         <v>28374.42</v>
@@ -1159,7 +1196,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>55.04</v>
+        <v>52.91</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1173,10 +1210,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9843.299999999999</v>
+        <v>9814.950000000001</v>
       </c>
       <c r="E3">
-        <v>0.21</v>
+        <v>-0.29</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1185,43 +1222,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-6.28</v>
+        <v>-6.55</v>
       </c>
       <c r="I3">
-        <v>14.83</v>
+        <v>14.5</v>
       </c>
       <c r="J3">
-        <v>-1.68</v>
+        <v>-1.13</v>
       </c>
       <c r="K3">
-        <v>0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="L3">
-        <v>-2.91</v>
+        <v>-3.15</v>
       </c>
       <c r="M3">
-        <v>13.05</v>
+        <v>12.71</v>
       </c>
       <c r="N3">
-        <v>12.85</v>
+        <v>12.76</v>
       </c>
       <c r="O3">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q3">
-        <v>9878.299999999999</v>
+        <v>9855.84</v>
       </c>
       <c r="R3">
-        <v>9889.969999999999</v>
+        <v>9889.120000000001</v>
       </c>
       <c r="S3">
-        <v>9894.700000000001</v>
+        <v>9892.16</v>
       </c>
       <c r="T3">
-        <v>9715.52</v>
+        <v>9718.459999999999</v>
       </c>
       <c r="U3">
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -1236,31 +1273,31 @@
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>44.62</v>
+        <v>42.34</v>
       </c>
       <c r="AA3">
-        <v>-2.47</v>
+        <v>-8.81</v>
       </c>
       <c r="AB3">
-        <v>3.52</v>
+        <v>1.05</v>
       </c>
       <c r="AC3">
-        <v>-5.99</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="AD3">
-        <v>9.01</v>
+        <v>3.42</v>
       </c>
       <c r="AE3">
-        <v>19.18</v>
+        <v>10.03</v>
       </c>
       <c r="AF3">
-        <v>89.23999999999999</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="AH3">
-        <v>10031.02</v>
+        <v>10031.84</v>
       </c>
       <c r="AI3">
-        <v>9748.93</v>
+        <v>9746.389999999999</v>
       </c>
       <c r="AJ3">
         <v>10073.2</v>
@@ -1269,7 +1306,7 @@
         <v>82</v>
       </c>
       <c r="AL3">
-        <v>29.3</v>
+        <v>30.03</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1283,10 +1320,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>12064.55</v>
+        <v>12004.7</v>
       </c>
       <c r="E4">
-        <v>-0.64</v>
+        <v>-0.5</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1295,43 +1332,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-4.55</v>
+        <v>-5.02</v>
       </c>
       <c r="I4">
-        <v>16.74</v>
+        <v>16.16</v>
       </c>
       <c r="J4">
-        <v>-1.35</v>
+        <v>-1.22</v>
       </c>
       <c r="K4">
-        <v>3.07</v>
+        <v>2.56</v>
       </c>
       <c r="L4">
-        <v>6.53</v>
+        <v>6.06</v>
       </c>
       <c r="M4">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="N4">
-        <v>12.78</v>
+        <v>12.62</v>
       </c>
       <c r="O4">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Q4">
-        <v>12118.1</v>
+        <v>12088.46</v>
       </c>
       <c r="R4">
-        <v>11999.03</v>
+        <v>12014.02</v>
       </c>
       <c r="S4">
-        <v>11731.51</v>
+        <v>11749.93</v>
       </c>
       <c r="T4">
-        <v>11708.71</v>
+        <v>11706.13</v>
       </c>
       <c r="U4">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -1346,31 +1383,31 @@
         <v>3</v>
       </c>
       <c r="Z4">
-        <v>57.5</v>
+        <v>53.05</v>
       </c>
       <c r="AA4">
-        <v>125.81</v>
+        <v>109.55</v>
       </c>
       <c r="AB4">
-        <v>138.95</v>
+        <v>133.07</v>
       </c>
       <c r="AC4">
-        <v>-13.13</v>
+        <v>-23.52</v>
       </c>
       <c r="AD4">
-        <v>22.26</v>
+        <v>12</v>
       </c>
       <c r="AE4">
-        <v>27.29</v>
+        <v>20.76</v>
       </c>
       <c r="AF4">
-        <v>106.69</v>
+        <v>103.78</v>
       </c>
       <c r="AH4">
-        <v>12453.21</v>
+        <v>12446.61</v>
       </c>
       <c r="AI4">
-        <v>11544.85</v>
+        <v>11581.42</v>
       </c>
       <c r="AJ4">
         <v>11869.84</v>
@@ -1379,7 +1416,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>34.78</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1393,10 +1430,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38652.65</v>
+        <v>38578.85</v>
       </c>
       <c r="E5">
-        <v>0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1405,22 +1442,22 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-6.94</v>
+        <v>-7.12</v>
       </c>
       <c r="I5">
-        <v>16.78</v>
+        <v>16.56</v>
       </c>
       <c r="J5">
-        <v>-0.25</v>
+        <v>-0.33</v>
       </c>
       <c r="K5">
-        <v>-1.59</v>
+        <v>-1.78</v>
       </c>
       <c r="L5">
-        <v>-2.19</v>
+        <v>-2.5</v>
       </c>
       <c r="M5">
-        <v>11.44</v>
+        <v>11.46</v>
       </c>
       <c r="N5">
         <v>14.41</v>
@@ -1429,19 +1466,19 @@
         <v>50</v>
       </c>
       <c r="Q5">
-        <v>38676.35</v>
+        <v>38650.57</v>
       </c>
       <c r="R5">
-        <v>38906.03</v>
+        <v>38871.12</v>
       </c>
       <c r="S5">
-        <v>39298.18</v>
+        <v>39276.05</v>
       </c>
       <c r="T5">
-        <v>37349.16</v>
+        <v>37363.92</v>
       </c>
       <c r="U5">
-        <v>3.49</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1456,34 +1493,34 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>41.11</v>
+        <v>39.49</v>
       </c>
       <c r="AA5">
-        <v>-197.56</v>
+        <v>-197.49</v>
       </c>
       <c r="AB5">
-        <v>-196.95</v>
+        <v>-197.05</v>
       </c>
       <c r="AC5">
-        <v>-0.61</v>
+        <v>-0.43</v>
       </c>
       <c r="AD5">
-        <v>65.22</v>
+        <v>65.77</v>
       </c>
       <c r="AE5">
-        <v>68.87</v>
+        <v>66.37</v>
       </c>
       <c r="AF5">
-        <v>358.1</v>
+        <v>352.37</v>
       </c>
       <c r="AG5">
         <v>-100</v>
       </c>
       <c r="AH5">
-        <v>39513.6</v>
+        <v>39469.1</v>
       </c>
       <c r="AI5">
-        <v>38298.46</v>
+        <v>38273.14</v>
       </c>
       <c r="AJ5">
         <v>39538.76</v>
@@ -1492,7 +1529,7 @@
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>14.77</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1506,10 +1543,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>48105.05</v>
+        <v>47734.8</v>
       </c>
       <c r="E6">
-        <v>-1.05</v>
+        <v>-0.77</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1518,43 +1555,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-15.76</v>
+        <v>-16.41</v>
       </c>
       <c r="I6">
-        <v>5.64</v>
+        <v>4.82</v>
       </c>
       <c r="J6">
-        <v>-2.55</v>
+        <v>-2.16</v>
       </c>
       <c r="K6">
-        <v>-1.32</v>
+        <v>-2.08</v>
       </c>
       <c r="L6">
-        <v>-5.49</v>
+        <v>-6.19</v>
       </c>
       <c r="M6">
-        <v>-12.9</v>
+        <v>-13.68</v>
       </c>
       <c r="N6">
-        <v>5.12</v>
+        <v>4.81</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>48554.92</v>
+        <v>48344.31</v>
       </c>
       <c r="R6">
-        <v>48991.18</v>
+        <v>48940.49</v>
       </c>
       <c r="S6">
-        <v>49090.93</v>
+        <v>49083.65</v>
       </c>
       <c r="T6">
-        <v>51184.85</v>
+        <v>51141.78</v>
       </c>
       <c r="U6">
-        <v>-6.02</v>
+        <v>-6.66</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -1569,43 +1606,43 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>38.32</v>
+        <v>34.93</v>
       </c>
       <c r="AA6">
-        <v>-144.14</v>
+        <v>-222.16</v>
       </c>
       <c r="AB6">
-        <v>-45.81</v>
+        <v>-81.08</v>
       </c>
       <c r="AC6">
-        <v>-98.33</v>
+        <v>-141.08</v>
       </c>
       <c r="AD6">
-        <v>15.31</v>
+        <v>5.56</v>
       </c>
       <c r="AE6">
-        <v>13.45</v>
+        <v>12.06</v>
       </c>
       <c r="AF6">
-        <v>590.98</v>
+        <v>581.95</v>
       </c>
       <c r="AG6">
         <v>-100</v>
       </c>
       <c r="AH6">
-        <v>49912.2</v>
+        <v>50016.31</v>
       </c>
       <c r="AI6">
-        <v>48070.16</v>
+        <v>47864.66</v>
       </c>
       <c r="AJ6">
-        <v>50137.57</v>
+        <v>49687.24</v>
       </c>
       <c r="AK6" t="s">
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>27.46</v>
+        <v>30.95</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1619,10 +1656,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26217.15</v>
+        <v>26108</v>
       </c>
       <c r="E7">
-        <v>0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1631,43 +1668,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-7.89</v>
+        <v>-8.27</v>
       </c>
       <c r="I7">
-        <v>11.46</v>
+        <v>10.99</v>
       </c>
       <c r="J7">
-        <v>-1.24</v>
+        <v>-1.23</v>
       </c>
       <c r="K7">
-        <v>-2.55</v>
+        <v>-2.96</v>
       </c>
       <c r="L7">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="M7">
-        <v>-0.58</v>
+        <v>-1.12</v>
       </c>
       <c r="N7">
-        <v>8.58</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q7">
-        <v>26323.58</v>
+        <v>26258.7</v>
       </c>
       <c r="R7">
-        <v>26666.73</v>
+        <v>26626.96</v>
       </c>
       <c r="S7">
-        <v>26517.68</v>
+        <v>26543.74</v>
       </c>
       <c r="T7">
-        <v>26718.97</v>
+        <v>26712.54</v>
       </c>
       <c r="U7">
-        <v>-1.88</v>
+        <v>-2.26</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
@@ -1682,34 +1719,34 @@
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>40.25</v>
+        <v>37.89</v>
       </c>
       <c r="AA7">
-        <v>-77.48999999999999</v>
+        <v>-101.64</v>
       </c>
       <c r="AB7">
-        <v>4.62</v>
+        <v>-16.63</v>
       </c>
       <c r="AC7">
-        <v>-82.11</v>
+        <v>-85.01000000000001</v>
       </c>
       <c r="AD7">
-        <v>4.34</v>
+        <v>0.21</v>
       </c>
       <c r="AE7">
-        <v>12.4</v>
+        <v>5.6</v>
       </c>
       <c r="AF7">
-        <v>309.35</v>
+        <v>296.68</v>
       </c>
       <c r="AG7">
         <v>-100</v>
       </c>
       <c r="AH7">
-        <v>27221.56</v>
+        <v>27222.88</v>
       </c>
       <c r="AI7">
-        <v>26111.89</v>
+        <v>26031.04</v>
       </c>
       <c r="AJ7">
         <v>26067.59</v>
@@ -1718,7 +1755,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>31.43</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1732,10 +1769,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31357.75</v>
+        <v>30213.45</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>-3.65</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1744,43 +1781,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-20.59</v>
+        <v>-23.49</v>
       </c>
       <c r="I8">
-        <v>21.68</v>
+        <v>17.24</v>
       </c>
       <c r="J8">
-        <v>-0.87</v>
+        <v>-5.06</v>
       </c>
       <c r="K8">
-        <v>7.29</v>
+        <v>3.61</v>
       </c>
       <c r="L8">
-        <v>10.45</v>
+        <v>3.09</v>
       </c>
       <c r="M8">
-        <v>-8.91</v>
+        <v>-13</v>
       </c>
       <c r="N8">
-        <v>-1.26</v>
+        <v>-2.01</v>
       </c>
       <c r="O8">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="Q8">
-        <v>31465.02</v>
+        <v>31143.08</v>
       </c>
       <c r="R8">
-        <v>30700.2</v>
+        <v>30761.65</v>
       </c>
       <c r="S8">
-        <v>29021.92</v>
+        <v>29053.11</v>
       </c>
       <c r="T8">
-        <v>32548.39</v>
+        <v>32519.53</v>
       </c>
       <c r="U8">
-        <v>-3.66</v>
+        <v>-7.09</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -1795,34 +1832,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>61.73</v>
+        <v>48.25</v>
       </c>
       <c r="AA8">
-        <v>744.9400000000001</v>
+        <v>612.29</v>
       </c>
       <c r="AB8">
-        <v>787.55</v>
+        <v>752.5</v>
       </c>
       <c r="AC8">
-        <v>-42.62</v>
+        <v>-140.21</v>
       </c>
       <c r="AD8">
-        <v>8.880000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>28.95</v>
+        <v>11.09</v>
       </c>
       <c r="AF8">
-        <v>627.1</v>
+        <v>664.08</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32999.35</v>
+        <v>32929.67</v>
       </c>
       <c r="AI8">
-        <v>28401.05</v>
+        <v>28593.64</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1831,7 +1868,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>19.24</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1845,10 +1882,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16583.6</v>
+        <v>16553.4</v>
       </c>
       <c r="E9">
-        <v>0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1857,25 +1894,25 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-0.47</v>
+        <v>-0.65</v>
       </c>
       <c r="I9">
-        <v>5.88</v>
+        <v>5.68</v>
       </c>
       <c r="J9">
-        <v>-0.43</v>
+        <v>-0.33</v>
       </c>
       <c r="K9">
-        <v>4.13</v>
+        <v>3.47</v>
       </c>
       <c r="N9">
-        <v>37.17</v>
+        <v>35.17</v>
       </c>
       <c r="Q9">
-        <v>16597.77</v>
+        <v>16586.67</v>
       </c>
       <c r="R9">
-        <v>16340.76</v>
+        <v>16364.75</v>
       </c>
       <c r="X9" t="s">
         <v>80</v>
@@ -1884,31 +1921,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>65.67</v>
+        <v>63.42</v>
       </c>
       <c r="AA9">
-        <v>181.21</v>
+        <v>171.43</v>
       </c>
       <c r="AB9">
-        <v>172.57</v>
+        <v>172.34</v>
       </c>
       <c r="AC9">
-        <v>8.640000000000001</v>
+        <v>-0.91</v>
       </c>
       <c r="AD9">
-        <v>64.84999999999999</v>
+        <v>46.35</v>
       </c>
       <c r="AE9">
-        <v>75.69</v>
+        <v>62.52</v>
       </c>
       <c r="AF9">
-        <v>125.5</v>
+        <v>123.19</v>
       </c>
       <c r="AH9">
-        <v>16942.83</v>
+        <v>16960.19</v>
       </c>
       <c r="AI9">
-        <v>15738.68</v>
+        <v>15769.31</v>
       </c>
       <c r="AJ9">
         <v>16247.16</v>
@@ -1917,7 +1954,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>38.8</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1931,10 +1968,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9416.5</v>
+        <v>9376.549999999999</v>
       </c>
       <c r="E10">
-        <v>-0.03</v>
+        <v>-0.42</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1943,43 +1980,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-3.58</v>
+        <v>-3.99</v>
       </c>
       <c r="I10">
-        <v>9.99</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="J10">
-        <v>-0.52</v>
+        <v>-0.08</v>
       </c>
       <c r="K10">
-        <v>0.42</v>
+        <v>-0.01</v>
       </c>
       <c r="L10">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="M10">
-        <v>4.41</v>
+        <v>4.23</v>
       </c>
       <c r="N10">
-        <v>15.56</v>
+        <v>15.44</v>
       </c>
       <c r="O10">
         <v>44</v>
       </c>
       <c r="Q10">
-        <v>9404.610000000001</v>
+        <v>9403.02</v>
       </c>
       <c r="R10">
-        <v>9411.110000000001</v>
+        <v>9411.07</v>
       </c>
       <c r="S10">
-        <v>9385.049999999999</v>
+        <v>9390.83</v>
       </c>
       <c r="T10">
-        <v>9362.870000000001</v>
+        <v>9362.77</v>
       </c>
       <c r="U10">
-        <v>0.57</v>
+        <v>0.15</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -1994,34 +2031,34 @@
         <v>3</v>
       </c>
       <c r="Z10">
-        <v>50.96</v>
+        <v>46.86</v>
       </c>
       <c r="AA10">
-        <v>10.55</v>
+        <v>6.36</v>
       </c>
       <c r="AB10">
-        <v>13.86</v>
+        <v>12.36</v>
       </c>
       <c r="AC10">
-        <v>-3.32</v>
+        <v>-6</v>
       </c>
       <c r="AD10">
-        <v>23.91</v>
+        <v>20.16</v>
       </c>
       <c r="AE10">
-        <v>20.7</v>
+        <v>22.18</v>
       </c>
       <c r="AF10">
-        <v>85.62</v>
+        <v>83.08</v>
       </c>
       <c r="AG10">
         <v>-100</v>
       </c>
       <c r="AH10">
-        <v>9500.620000000001</v>
+        <v>9500.639999999999</v>
       </c>
       <c r="AI10">
-        <v>9321.6</v>
+        <v>9321.5</v>
       </c>
       <c r="AJ10">
         <v>9229.360000000001</v>
@@ -2030,7 +2067,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>25.02</v>
+        <v>24.79</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2044,10 +2081,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1595.75</v>
+        <v>1602.2</v>
       </c>
       <c r="E11">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
         <v>1671.5</v>
@@ -2056,43 +2093,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-4.53</v>
+        <v>-4.15</v>
       </c>
       <c r="I11">
-        <v>27.32</v>
+        <v>27.83</v>
       </c>
       <c r="J11">
-        <v>2.33</v>
+        <v>3.18</v>
       </c>
       <c r="K11">
-        <v>4.88</v>
+        <v>5.31</v>
       </c>
       <c r="L11">
-        <v>13.66</v>
+        <v>12.78</v>
       </c>
       <c r="M11">
-        <v>-1.54</v>
+        <v>-2.11</v>
       </c>
       <c r="N11">
-        <v>-0.92</v>
+        <v>-0.79</v>
       </c>
       <c r="O11">
         <v>68</v>
       </c>
       <c r="Q11">
-        <v>1576.53</v>
+        <v>1586.42</v>
       </c>
       <c r="R11">
-        <v>1557.95</v>
+        <v>1561.99</v>
       </c>
       <c r="S11">
-        <v>1522.35</v>
+        <v>1524.86</v>
       </c>
       <c r="T11">
-        <v>1443.25</v>
+        <v>1443.56</v>
       </c>
       <c r="U11">
-        <v>10.57</v>
+        <v>10.99</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -2107,40 +2144,40 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>62.63</v>
+        <v>63.9</v>
       </c>
       <c r="AA11">
-        <v>19.61</v>
+        <v>20.68</v>
       </c>
       <c r="AB11">
-        <v>19.05</v>
+        <v>19.38</v>
       </c>
       <c r="AC11">
-        <v>0.5600000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="AD11">
-        <v>29.16</v>
+        <v>36.55</v>
       </c>
       <c r="AE11">
-        <v>20.74</v>
+        <v>29.18</v>
       </c>
       <c r="AF11">
-        <v>31.07</v>
+        <v>30.07</v>
       </c>
       <c r="AH11">
-        <v>1621.08</v>
+        <v>1625.62</v>
       </c>
       <c r="AI11">
-        <v>1494.82</v>
+        <v>1498.36</v>
       </c>
       <c r="AJ11">
-        <v>1508.92</v>
+        <v>1509.79</v>
       </c>
       <c r="AK11" t="s">
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>40.58</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2154,10 +2191,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13104.6</v>
+        <v>13025.3</v>
       </c>
       <c r="E12">
-        <v>1.26</v>
+        <v>-0.61</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2166,43 +2203,43 @@
         <v>9147.1</v>
       </c>
       <c r="H12">
-        <v>-4.47</v>
+        <v>-5.05</v>
       </c>
       <c r="I12">
-        <v>43.27</v>
+        <v>42.4</v>
       </c>
       <c r="J12">
-        <v>-0.92</v>
+        <v>-0.58</v>
       </c>
       <c r="K12">
-        <v>5.37</v>
+        <v>4.73</v>
       </c>
       <c r="L12">
-        <v>-0.5</v>
+        <v>-1.05</v>
       </c>
       <c r="M12">
-        <v>40.93</v>
+        <v>39.9</v>
       </c>
       <c r="N12">
-        <v>17.92</v>
+        <v>17.96</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13070.46</v>
+        <v>13055.36</v>
       </c>
       <c r="R12">
-        <v>12829.75</v>
+        <v>12859.17</v>
       </c>
       <c r="S12">
-        <v>12747.92</v>
+        <v>12750.16</v>
       </c>
       <c r="T12">
-        <v>11943.39</v>
+        <v>11956.78</v>
       </c>
       <c r="U12">
-        <v>9.720000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -2217,34 +2254,34 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>59.1</v>
+        <v>55.6</v>
       </c>
       <c r="AA12">
-        <v>124.44</v>
+        <v>116.87</v>
       </c>
       <c r="AB12">
-        <v>102.38</v>
+        <v>105.28</v>
       </c>
       <c r="AC12">
-        <v>22.07</v>
+        <v>11.6</v>
       </c>
       <c r="AD12">
-        <v>48.1</v>
+        <v>34.62</v>
       </c>
       <c r="AE12">
-        <v>54.92</v>
+        <v>45.48</v>
       </c>
       <c r="AF12">
-        <v>196.25</v>
+        <v>189.94</v>
       </c>
       <c r="AG12">
         <v>-100</v>
       </c>
       <c r="AH12">
-        <v>13485.83</v>
+        <v>13493.49</v>
       </c>
       <c r="AI12">
-        <v>12173.68</v>
+        <v>12224.86</v>
       </c>
       <c r="AJ12">
         <v>12652.05</v>
@@ -2253,7 +2290,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>37.61</v>
+        <v>34.36</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2267,10 +2304,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9861.6</v>
+        <v>9838.5</v>
       </c>
       <c r="E13">
-        <v>0.17</v>
+        <v>-0.23</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2279,43 +2316,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-8.4</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="I13">
-        <v>7.16</v>
+        <v>6.91</v>
       </c>
       <c r="J13">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K13">
-        <v>-0.77</v>
+        <v>-1.01</v>
       </c>
       <c r="L13">
-        <v>-4.64</v>
+        <v>-5</v>
       </c>
       <c r="M13">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="N13">
-        <v>22.39</v>
+        <v>22.42</v>
       </c>
       <c r="O13">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q13">
-        <v>9860.43</v>
+        <v>9861.85</v>
       </c>
       <c r="R13">
-        <v>9915.620000000001</v>
+        <v>9910.620000000001</v>
       </c>
       <c r="S13">
-        <v>9959.059999999999</v>
+        <v>9954.99</v>
       </c>
       <c r="T13">
-        <v>10049</v>
+        <v>10048.65</v>
       </c>
       <c r="U13">
-        <v>-1.86</v>
+        <v>-2.09</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -2330,34 +2367,34 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>42.53</v>
+        <v>40.35</v>
       </c>
       <c r="AA13">
-        <v>-33.23</v>
+        <v>-34.85</v>
       </c>
       <c r="AB13">
-        <v>-30.59</v>
+        <v>-31.44</v>
       </c>
       <c r="AC13">
-        <v>-2.64</v>
+        <v>-3.41</v>
       </c>
       <c r="AD13">
-        <v>34.4</v>
+        <v>25.22</v>
       </c>
       <c r="AE13">
-        <v>31.17</v>
+        <v>30.9</v>
       </c>
       <c r="AF13">
-        <v>89.2</v>
+        <v>87.53</v>
       </c>
       <c r="AG13">
         <v>-100</v>
       </c>
       <c r="AH13">
-        <v>10003.91</v>
+        <v>10004.59</v>
       </c>
       <c r="AI13">
-        <v>9827.33</v>
+        <v>9816.639999999999</v>
       </c>
       <c r="AJ13">
         <v>10093.21</v>
@@ -2366,7 +2403,7 @@
         <v>82</v>
       </c>
       <c r="AL13">
-        <v>30.83</v>
+        <v>29.49</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2380,10 +2417,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8706.200000000001</v>
+        <v>8618.5</v>
       </c>
       <c r="E14">
-        <v>-0.37</v>
+        <v>-1.01</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2392,43 +2429,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-11.88</v>
+        <v>-12.77</v>
       </c>
       <c r="I14">
-        <v>28.87</v>
+        <v>27.57</v>
       </c>
       <c r="J14">
-        <v>0.77</v>
+        <v>-0.25</v>
       </c>
       <c r="K14">
-        <v>3.87</v>
+        <v>2.82</v>
       </c>
       <c r="L14">
-        <v>10.58</v>
+        <v>8.59</v>
       </c>
       <c r="M14">
-        <v>26.38</v>
+        <v>24.74</v>
       </c>
       <c r="N14">
-        <v>30.26</v>
+        <v>29.92</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8738.34</v>
+        <v>8733.99</v>
       </c>
       <c r="R14">
-        <v>8536.1</v>
+        <v>8547.940000000001</v>
       </c>
       <c r="S14">
-        <v>8495.790000000001</v>
+        <v>8504.17</v>
       </c>
       <c r="T14">
-        <v>8573.629999999999</v>
+        <v>8577.639999999999</v>
       </c>
       <c r="U14">
-        <v>1.55</v>
+        <v>0.48</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -2443,34 +2480,34 @@
         <v>2</v>
       </c>
       <c r="Z14">
-        <v>59.04</v>
+        <v>53.44</v>
       </c>
       <c r="AA14">
-        <v>93.06999999999999</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="AB14">
-        <v>67.67</v>
+        <v>70.84</v>
       </c>
       <c r="AC14">
-        <v>25.4</v>
+        <v>12.67</v>
       </c>
       <c r="AD14">
-        <v>65.38</v>
+        <v>50.37</v>
       </c>
       <c r="AE14">
-        <v>71.42</v>
+        <v>63.78</v>
       </c>
       <c r="AF14">
-        <v>136.35</v>
+        <v>135.68</v>
       </c>
       <c r="AG14">
         <v>-100</v>
       </c>
       <c r="AH14">
-        <v>8885.219999999999</v>
+        <v>8891.030000000001</v>
       </c>
       <c r="AI14">
-        <v>8186.97</v>
+        <v>8204.84</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
@@ -2479,7 +2516,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>39.08</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2493,10 +2530,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26445.55</v>
+        <v>26361.9</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="F15">
         <v>26762.5</v>
@@ -2505,43 +2542,43 @@
         <v>21402.15</v>
       </c>
       <c r="H15">
-        <v>-1.18</v>
+        <v>-1.5</v>
       </c>
       <c r="I15">
-        <v>23.56</v>
+        <v>23.17</v>
       </c>
       <c r="J15">
-        <v>-0.13</v>
+        <v>-1.45</v>
       </c>
       <c r="K15">
-        <v>3.12</v>
+        <v>1.38</v>
       </c>
       <c r="L15">
-        <v>6.8</v>
+        <v>6.01</v>
       </c>
       <c r="M15">
-        <v>22.87</v>
+        <v>21.57</v>
       </c>
       <c r="N15">
-        <v>13.5</v>
+        <v>13.38</v>
       </c>
       <c r="O15">
         <v>81</v>
       </c>
       <c r="Q15">
-        <v>26618.17</v>
+        <v>26540.46</v>
       </c>
       <c r="R15">
-        <v>26337.32</v>
+        <v>26350.78</v>
       </c>
       <c r="S15">
-        <v>25586.92</v>
+        <v>25631.2</v>
       </c>
       <c r="T15">
-        <v>23507.42</v>
+        <v>23527.44</v>
       </c>
       <c r="U15">
-        <v>12.5</v>
+        <v>12.05</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2556,34 +2593,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>57.91</v>
+        <v>55.12</v>
       </c>
       <c r="AA15">
-        <v>284.8</v>
+        <v>253.42</v>
       </c>
       <c r="AB15">
-        <v>330.52</v>
+        <v>315.1</v>
       </c>
       <c r="AC15">
-        <v>-45.72</v>
+        <v>-61.68</v>
       </c>
       <c r="AD15">
-        <v>20.42</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>51.84</v>
+        <v>24.13</v>
       </c>
       <c r="AF15">
-        <v>309.61</v>
+        <v>300.82</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27082.31</v>
+        <v>27086.84</v>
       </c>
       <c r="AI15">
-        <v>25592.33</v>
+        <v>25614.71</v>
       </c>
       <c r="AJ15">
         <v>25756.98</v>
@@ -2592,7 +2629,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>39.88</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2606,10 +2643,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>908.7</v>
+        <v>895.8</v>
       </c>
       <c r="E16">
-        <v>1.46</v>
+        <v>-1.42</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2618,43 +2655,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-6.19</v>
+        <v>-7.52</v>
       </c>
       <c r="I16">
-        <v>39.55</v>
+        <v>37.57</v>
       </c>
       <c r="J16">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="K16">
-        <v>-1.09</v>
+        <v>-2.49</v>
       </c>
       <c r="L16">
-        <v>20.85</v>
+        <v>17.45</v>
       </c>
       <c r="M16">
-        <v>1.63</v>
+        <v>0.31</v>
       </c>
       <c r="N16">
-        <v>18.42</v>
+        <v>18.26</v>
       </c>
       <c r="O16">
         <v>74</v>
       </c>
       <c r="Q16">
-        <v>896.33</v>
+        <v>897.67</v>
       </c>
       <c r="R16">
-        <v>904.36</v>
+        <v>903.22</v>
       </c>
       <c r="S16">
-        <v>870.01</v>
+        <v>872.9400000000001</v>
       </c>
       <c r="T16">
-        <v>834.45</v>
+        <v>834.22</v>
       </c>
       <c r="U16">
-        <v>8.9</v>
+        <v>7.38</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
@@ -2669,34 +2706,34 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>57.02</v>
+        <v>50.9</v>
       </c>
       <c r="AA16">
-        <v>4.49</v>
+        <v>3.91</v>
       </c>
       <c r="AB16">
-        <v>7.52</v>
+        <v>6.8</v>
       </c>
       <c r="AC16">
-        <v>-3.03</v>
+        <v>-2.88</v>
       </c>
       <c r="AD16">
-        <v>35.54</v>
+        <v>34.69</v>
       </c>
       <c r="AE16">
-        <v>23.99</v>
+        <v>30.34</v>
       </c>
       <c r="AF16">
-        <v>18.44</v>
+        <v>18.4</v>
       </c>
       <c r="AG16">
         <v>-100</v>
       </c>
       <c r="AH16">
-        <v>929.55</v>
+        <v>927.73</v>
       </c>
       <c r="AI16">
-        <v>879.17</v>
+        <v>878.7</v>
       </c>
       <c r="AJ16">
         <v>864.8</v>
@@ -2705,7 +2742,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>16.01</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2719,10 +2756,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30971.65</v>
+        <v>30759.75</v>
       </c>
       <c r="E17">
-        <v>-0.5</v>
+        <v>-0.68</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2731,43 +2768,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-9.18</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I17">
-        <v>9.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J17">
-        <v>-1.08</v>
+        <v>-1.49</v>
       </c>
       <c r="K17">
-        <v>-1.49</v>
+        <v>-2.16</v>
       </c>
       <c r="L17">
-        <v>3.93</v>
+        <v>3.05</v>
       </c>
       <c r="M17">
-        <v>-4.15</v>
+        <v>-4.92</v>
       </c>
       <c r="N17">
-        <v>5.77</v>
+        <v>5.72</v>
       </c>
       <c r="O17">
         <v>19</v>
       </c>
       <c r="Q17">
-        <v>31120.77</v>
+        <v>31027.99</v>
       </c>
       <c r="R17">
-        <v>31357.83</v>
+        <v>31323.85</v>
       </c>
       <c r="S17">
-        <v>30937.54</v>
+        <v>30966.77</v>
       </c>
       <c r="T17">
-        <v>31808.44</v>
+        <v>31794.79</v>
       </c>
       <c r="U17">
-        <v>-2.63</v>
+        <v>-3.26</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
@@ -2782,34 +2819,34 @@
         <v>1</v>
       </c>
       <c r="Z17">
-        <v>42.7</v>
+        <v>37.55</v>
       </c>
       <c r="AA17">
-        <v>27.55</v>
+        <v>-12.22</v>
       </c>
       <c r="AB17">
-        <v>112.24</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="AC17">
-        <v>-84.69</v>
+        <v>-99.56999999999999</v>
       </c>
       <c r="AD17">
         <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>0.97</v>
+        <v>1.46</v>
       </c>
       <c r="AF17">
-        <v>283.27</v>
+        <v>278.66</v>
       </c>
       <c r="AG17">
         <v>-100</v>
       </c>
       <c r="AH17">
-        <v>31744.81</v>
+        <v>31791.6</v>
       </c>
       <c r="AI17">
-        <v>30970.86</v>
+        <v>30856.1</v>
       </c>
       <c r="AJ17">
         <v>30549.87</v>
@@ -2818,7 +2855,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>31.26</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2832,10 +2869,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16429.35</v>
+        <v>16463.7</v>
       </c>
       <c r="E18">
-        <v>-0.46</v>
+        <v>0.21</v>
       </c>
       <c r="F18">
         <v>16783.35</v>
@@ -2844,25 +2881,25 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-2.11</v>
+        <v>-1.9</v>
       </c>
       <c r="I18">
-        <v>6.66</v>
+        <v>6.89</v>
       </c>
       <c r="J18">
-        <v>-1.33</v>
+        <v>-1.44</v>
       </c>
       <c r="K18">
-        <v>0.9</v>
+        <v>-0.16</v>
       </c>
       <c r="N18">
-        <v>35.5</v>
+        <v>36.43</v>
       </c>
       <c r="Q18">
-        <v>16570.78</v>
+        <v>16522.51</v>
       </c>
       <c r="R18">
-        <v>16586.14</v>
+        <v>16581.95</v>
       </c>
       <c r="X18" t="s">
         <v>80</v>
@@ -2871,31 +2908,31 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>46.33</v>
+        <v>48.3</v>
       </c>
       <c r="AA18">
-        <v>82.95</v>
+        <v>66.98</v>
       </c>
       <c r="AB18">
-        <v>132.47</v>
+        <v>119.37</v>
       </c>
       <c r="AC18">
-        <v>-49.52</v>
+        <v>-52.39</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AE18">
-        <v>14.67</v>
+        <v>4.83</v>
       </c>
       <c r="AF18">
-        <v>175.69</v>
+        <v>173.35</v>
       </c>
       <c r="AH18">
-        <v>16911.17</v>
+        <v>16911.21</v>
       </c>
       <c r="AI18">
-        <v>16261.11</v>
+        <v>16252.69</v>
       </c>
       <c r="AJ18">
         <v>16199.38</v>
@@ -2904,7 +2941,7 @@
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>17.24</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2918,13 +2955,13 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9841.5</v>
+        <v>9968.25</v>
       </c>
       <c r="E19">
-        <v>0.3</v>
+        <v>1.29</v>
       </c>
       <c r="F19">
-        <v>9841.5</v>
+        <v>9968.25</v>
       </c>
       <c r="G19">
         <v>8995.35</v>
@@ -2933,22 +2970,22 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>9.41</v>
+        <v>10.82</v>
       </c>
       <c r="J19">
-        <v>2.14</v>
+        <v>3.91</v>
       </c>
       <c r="K19">
-        <v>5.31</v>
+        <v>6.45</v>
       </c>
       <c r="N19">
-        <v>64.45999999999999</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="Q19">
-        <v>9743.629999999999</v>
+        <v>9818.6</v>
       </c>
       <c r="R19">
-        <v>9499.049999999999</v>
+        <v>9525.700000000001</v>
       </c>
       <c r="X19" t="s">
         <v>80</v>
@@ -2957,40 +2994,40 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>67.17</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="AA19">
-        <v>116.23</v>
+        <v>133.6</v>
       </c>
       <c r="AB19">
-        <v>74.38</v>
+        <v>86.23</v>
       </c>
       <c r="AC19">
-        <v>41.85</v>
+        <v>47.37</v>
       </c>
       <c r="AD19">
-        <v>99</v>
+        <v>99.52</v>
       </c>
       <c r="AE19">
-        <v>90.78</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="AF19">
-        <v>147.01</v>
+        <v>146.7</v>
       </c>
       <c r="AH19">
-        <v>9909.68</v>
+        <v>9985.18</v>
       </c>
       <c r="AI19">
-        <v>9088.42</v>
+        <v>9066.23</v>
       </c>
       <c r="AJ19">
-        <v>9423.91</v>
+        <v>9466.209999999999</v>
       </c>
       <c r="AK19" t="s">
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>29.1</v>
+        <v>32.27</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3004,10 +3041,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11208.5</v>
+        <v>11231.15</v>
       </c>
       <c r="E20">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3016,25 +3053,25 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-1.41</v>
+        <v>-1.21</v>
       </c>
       <c r="I20">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="J20">
-        <v>-0.55</v>
+        <v>-0.43</v>
       </c>
       <c r="K20">
-        <v>-0.8</v>
+        <v>-1.21</v>
       </c>
       <c r="N20">
-        <v>10.27</v>
+        <v>11.32</v>
       </c>
       <c r="Q20">
-        <v>11246.82</v>
+        <v>11237.23</v>
       </c>
       <c r="R20">
-        <v>11214</v>
+        <v>11209.97</v>
       </c>
       <c r="X20" t="s">
         <v>80</v>
@@ -3043,31 +3080,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>49.78</v>
+        <v>51.5</v>
       </c>
       <c r="AA20">
-        <v>24.26</v>
+        <v>21.97</v>
       </c>
       <c r="AB20">
-        <v>29.47</v>
+        <v>27.97</v>
       </c>
       <c r="AC20">
-        <v>-5.2</v>
+        <v>-5.99</v>
       </c>
       <c r="AD20">
-        <v>33.97</v>
+        <v>24.43</v>
       </c>
       <c r="AE20">
-        <v>46.68</v>
+        <v>35.18</v>
       </c>
       <c r="AF20">
-        <v>125.53</v>
+        <v>123.99</v>
       </c>
       <c r="AH20">
-        <v>11396.19</v>
+        <v>11386.5</v>
       </c>
       <c r="AI20">
-        <v>11031.82</v>
+        <v>11033.43</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3076,7 +3113,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>14.55</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3090,10 +3127,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27311.05</v>
+        <v>27247.9</v>
       </c>
       <c r="E21">
-        <v>0.23</v>
+        <v>-0.23</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3102,91 +3139,91 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.43</v>
+        <v>-6.65</v>
       </c>
       <c r="I21">
-        <v>13.11</v>
+        <v>12.85</v>
       </c>
       <c r="J21">
-        <v>-0.8100000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="K21">
-        <v>-4.2</v>
+        <v>-4.42</v>
       </c>
       <c r="L21">
-        <v>4.4</v>
+        <v>4.94</v>
       </c>
       <c r="M21">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="N21">
-        <v>8.039999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="O21">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q21">
-        <v>27321.52</v>
+        <v>27295.03</v>
       </c>
       <c r="R21">
-        <v>27873.06</v>
+        <v>27810.03</v>
       </c>
       <c r="S21">
-        <v>27859.58</v>
+        <v>27882.09</v>
       </c>
       <c r="T21">
-        <v>27670.03</v>
+        <v>27664.59</v>
       </c>
       <c r="U21">
-        <v>-1.3</v>
+        <v>-1.51</v>
       </c>
       <c r="V21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="b">
         <v>1</v>
       </c>
       <c r="X21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21">
-        <v>39.51</v>
+        <v>38.28</v>
       </c>
       <c r="AA21">
-        <v>-183.8</v>
+        <v>-193.4</v>
       </c>
       <c r="AB21">
-        <v>-92.39</v>
+        <v>-112.59</v>
       </c>
       <c r="AC21">
-        <v>-91.41</v>
+        <v>-80.81</v>
       </c>
       <c r="AD21">
-        <v>2.51</v>
+        <v>4.23</v>
       </c>
       <c r="AE21">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="AF21">
-        <v>382.94</v>
+        <v>365.55</v>
       </c>
       <c r="AH21">
-        <v>28903.98</v>
+        <v>28831.47</v>
       </c>
       <c r="AI21">
-        <v>26842.13</v>
+        <v>26788.58</v>
       </c>
       <c r="AJ21">
-        <v>28395.64</v>
+        <v>28369.85</v>
       </c>
       <c r="AK21" t="s">
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>26.29</v>
+        <v>23.95</v>
       </c>
     </row>
   </sheetData>
@@ -3327,7 +3364,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3367,7 +3404,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3387,7 +3424,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>94</v>
@@ -3405,2280 +3442,2550 @@
         <v>98</v>
       </c>
     </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>103</v>
+      <c r="E7" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="D8" s="7">
-        <v>7.67</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-1.45</v>
+        <v>23</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="D13" s="8">
+        <v>7.99</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C14" s="8">
         <v>0.05</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D14" s="8">
+        <v>-0.17</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8">
+        <v>4.14</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2.56</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-2.01</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-1.78</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="D17" s="8">
+        <v>-2.08</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-1.29</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-2.96</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="8">
+        <v>9.17</v>
+      </c>
+      <c r="D19" s="8">
+        <v>3.61</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-5.56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="D20" s="8">
+        <v>3.47</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-0.01</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="8">
+        <v>4.52</v>
+      </c>
+      <c r="D22" s="8">
+        <v>5.31</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="D23" s="8">
+        <v>4.73</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="8">
+        <v>-0.67</v>
+      </c>
+      <c r="D24" s="8">
+        <v>-1.01</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="8">
+        <v>4.68</v>
+      </c>
+      <c r="D25" s="8">
+        <v>2.82</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="8">
+        <v>1.68</v>
+      </c>
+      <c r="D26" s="8">
+        <v>1.38</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-1.16</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-2.49</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="8">
+        <v>-2.16</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D29" s="8">
+        <v>-0.16</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="8">
+        <v>5.66</v>
+      </c>
+      <c r="D30" s="8">
+        <v>6.45</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="8">
         <v>0.11</v>
       </c>
-      <c r="E9" s="9">
+      <c r="D31" s="8">
+        <v>-1.21</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="8">
+        <v>-2.39</v>
+      </c>
+      <c r="D32" s="8">
+        <v>-4.42</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="8">
+        <v>-1.48</v>
+      </c>
+      <c r="D33" s="8">
+        <v>-0.66</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="8">
+        <v>-1.69</v>
+      </c>
+      <c r="D34" s="8">
+        <v>-1.13</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="8">
+        <v>-0.45</v>
+      </c>
+      <c r="D35" s="8">
+        <v>-1.22</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-0.5</v>
+      </c>
+      <c r="D36" s="8">
+        <v>-0.33</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="8">
+        <v>-1.66</v>
+      </c>
+      <c r="D37" s="8">
+        <v>-2.16</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="8">
+        <v>-0.95</v>
+      </c>
+      <c r="D38" s="8">
+        <v>-1.23</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-0.6</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-5.06</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-4.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-0.7</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-0.33</v>
+      </c>
+      <c r="E40" s="10">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="8">
+        <v>-0.89</v>
+      </c>
+      <c r="D41" s="8">
+        <v>-0.08</v>
+      </c>
+      <c r="E41" s="10">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="8">
+        <v>2.26</v>
+      </c>
+      <c r="D42" s="8">
+        <v>3.18</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-1.88</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-0.58</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="8">
+        <v>-0.78</v>
+      </c>
+      <c r="D44" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E44" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-0.54</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-0.25</v>
+      </c>
+      <c r="E45" s="10">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="8">
+        <v>-0.36</v>
+      </c>
+      <c r="D46" s="8">
+        <v>-1.45</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1.09</v>
+      </c>
+      <c r="D47" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-0.44</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-1.49</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-1.22</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-1.44</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="D50" s="8">
+        <v>3.91</v>
+      </c>
+      <c r="E50" s="10">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="8">
+        <v>-0.99</v>
+      </c>
+      <c r="D51" s="8">
+        <v>-0.43</v>
+      </c>
+      <c r="E51" s="10">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="8">
+        <v>-0.53</v>
+      </c>
+      <c r="D52" s="8">
+        <v>-0.48</v>
+      </c>
+      <c r="E52" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="8">
+        <v>22.33</v>
+      </c>
+      <c r="D53" s="8">
+        <v>22.92</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="8">
+        <v>12.28</v>
+      </c>
+      <c r="D54" s="8">
+        <v>12.71</v>
+      </c>
+      <c r="E54" s="10">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="8">
+        <v>2.99</v>
+      </c>
+      <c r="D55" s="8">
+        <v>1.97</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="8">
+        <v>10.42</v>
+      </c>
+      <c r="D56" s="8">
+        <v>11.46</v>
+      </c>
+      <c r="E56" s="10">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="8">
+        <v>-12.77</v>
+      </c>
+      <c r="D57" s="8">
+        <v>-13.68</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="8">
+        <v>-0.61</v>
+      </c>
+      <c r="D58" s="8">
+        <v>-1.12</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="8">
+        <v>-10.49</v>
+      </c>
+      <c r="D59" s="8">
+        <v>-13</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="8">
+        <v>4.16</v>
+      </c>
+      <c r="D60" s="8">
+        <v>4.23</v>
+      </c>
+      <c r="E60" s="10">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="8">
+        <v>-3.05</v>
+      </c>
+      <c r="D61" s="8">
+        <v>-2.11</v>
+      </c>
+      <c r="E61" s="10">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="8">
+        <v>38.62</v>
+      </c>
+      <c r="D62" s="8">
+        <v>39.9</v>
+      </c>
+      <c r="E62" s="10">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="8">
+        <v>2.3</v>
+      </c>
+      <c r="D63" s="8">
+        <v>3.12</v>
+      </c>
+      <c r="E63" s="10">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="8">
+        <v>27.6</v>
+      </c>
+      <c r="D64" s="8">
+        <v>24.74</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="8">
+        <v>20.37</v>
+      </c>
+      <c r="D65" s="8">
+        <v>21.57</v>
+      </c>
+      <c r="E65" s="10">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="8">
+        <v>-1.34</v>
+      </c>
+      <c r="D66" s="8">
+        <v>0.31</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="8">
+        <v>-3.96</v>
+      </c>
+      <c r="D67" s="8">
+        <v>-4.92</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="8">
+        <v>1.39</v>
+      </c>
+      <c r="D68" s="8">
+        <v>1.29</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="8">
+        <v>12.03</v>
+      </c>
+      <c r="D69" s="8">
+        <v>13.88</v>
+      </c>
+      <c r="E69" s="10">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="8">
+        <v>-3.75</v>
+      </c>
+      <c r="D70" s="8">
+        <v>-3.15</v>
+      </c>
+      <c r="E70" s="10">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="8">
+        <v>6.68</v>
+      </c>
+      <c r="D71" s="8">
+        <v>6.06</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="8">
+        <v>-3.17</v>
+      </c>
+      <c r="D72" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="E72" s="10">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="8">
+        <v>-4.77</v>
+      </c>
+      <c r="D73" s="8">
+        <v>-6.19</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="8">
+        <v>3.43</v>
+      </c>
+      <c r="D74" s="8">
+        <v>3.26</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="8">
+        <v>13.14</v>
+      </c>
+      <c r="D75" s="8">
+        <v>3.09</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-10.05</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="8">
+        <v>0.98</v>
+      </c>
+      <c r="D76" s="8">
+        <v>1.08</v>
+      </c>
+      <c r="E76" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="8">
+        <v>10.72</v>
+      </c>
+      <c r="D77" s="8">
+        <v>12.78</v>
+      </c>
+      <c r="E77" s="10">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="8">
+        <v>-2.7</v>
+      </c>
+      <c r="D78" s="8">
+        <v>-1.05</v>
+      </c>
+      <c r="E78" s="10">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="8">
+        <v>-6.11</v>
+      </c>
+      <c r="D79" s="8">
+        <v>-5</v>
+      </c>
+      <c r="E79" s="10">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="8">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="D80" s="8">
+        <v>8.59</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="8">
+        <v>7.35</v>
+      </c>
+      <c r="D81" s="8">
+        <v>6.01</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="8">
+        <v>18.43</v>
+      </c>
+      <c r="D82" s="8">
+        <v>17.45</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="8">
+        <v>4.8</v>
+      </c>
+      <c r="D83" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="8">
+        <v>4.4</v>
+      </c>
+      <c r="D84" s="8">
+        <v>4.94</v>
+      </c>
+      <c r="E84" s="10">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="8">
+        <v>-1.48</v>
+      </c>
+      <c r="D85" s="8">
+        <v>-1.29</v>
+      </c>
+      <c r="E85" s="10">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="8">
+        <v>-6.48</v>
+      </c>
+      <c r="D86" s="8">
+        <v>-6.55</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="8">
+        <v>-3.93</v>
+      </c>
+      <c r="D87" s="8">
+        <v>-5.02</v>
+      </c>
+      <c r="E87" s="9">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="8">
+        <v>-7.18</v>
+      </c>
+      <c r="D88" s="8">
+        <v>-7.12</v>
+      </c>
+      <c r="E88" s="10">
         <v>0.06</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+    <row r="89" spans="1:5">
+      <c r="A89" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="8">
+        <v>-14.87</v>
+      </c>
+      <c r="D89" s="8">
+        <v>-16.41</v>
+      </c>
+      <c r="E89" s="9">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="8">
+        <v>-7.9</v>
+      </c>
+      <c r="D90" s="8">
+        <v>-8.27</v>
+      </c>
+      <c r="E90" s="9">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="8">
+        <v>-20.59</v>
+      </c>
+      <c r="D91" s="8">
+        <v>-23.49</v>
+      </c>
+      <c r="E91" s="9">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="8">
+        <v>-0.7</v>
+      </c>
+      <c r="D92" s="8">
+        <v>-0.65</v>
+      </c>
+      <c r="E92" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="8">
+        <v>-3.55</v>
+      </c>
+      <c r="D93" s="8">
+        <v>-3.99</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="8">
+        <v>-4.87</v>
+      </c>
+      <c r="D94" s="8">
+        <v>-4.15</v>
+      </c>
+      <c r="E94" s="10">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="8">
+        <v>-5.66</v>
+      </c>
+      <c r="D95" s="8">
+        <v>-5.05</v>
+      </c>
+      <c r="E95" s="10">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="8">
+        <v>-8.56</v>
+      </c>
+      <c r="D96" s="8">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="E96" s="9">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="8">
+        <v>-11.55</v>
+      </c>
+      <c r="D97" s="8">
+        <v>-12.77</v>
+      </c>
+      <c r="E97" s="9">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="8">
+        <v>-1.18</v>
+      </c>
+      <c r="D98" s="8">
+        <v>-1.5</v>
+      </c>
+      <c r="E98" s="9">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="8">
+        <v>-7.54</v>
+      </c>
+      <c r="D99" s="8">
+        <v>-7.52</v>
+      </c>
+      <c r="E99" s="10">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="8">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="D100" s="8">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E100" s="9">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="8">
+        <v>-1.66</v>
+      </c>
+      <c r="D101" s="8">
+        <v>-1.9</v>
+      </c>
+      <c r="E101" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="8">
+        <v>-1.49</v>
+      </c>
+      <c r="D102" s="8">
+        <v>-1.21</v>
+      </c>
+      <c r="E102" s="10">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="8">
+        <v>29207.9</v>
+      </c>
+      <c r="D103" s="8">
+        <v>29264.55</v>
+      </c>
+      <c r="E103" s="10">
+        <v>56.65</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="8">
+        <v>9822.75</v>
+      </c>
+      <c r="D104" s="8">
+        <v>9814.950000000001</v>
+      </c>
+      <c r="E104" s="9">
+        <v>-7.8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7">
-        <v>4.14</v>
-      </c>
-      <c r="D10" s="7">
-        <v>3.07</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B105" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="8">
+        <v>12142.85</v>
+      </c>
+      <c r="D105" s="8">
+        <v>12004.7</v>
+      </c>
+      <c r="E105" s="9">
+        <v>-138.15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-2.01</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-1.59</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B106" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="8">
+        <v>38554.2</v>
+      </c>
+      <c r="D106" s="8">
+        <v>38578.85</v>
+      </c>
+      <c r="E106" s="10">
+        <v>24.65</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.43</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-1.32</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B107" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="8">
+        <v>48615.05</v>
+      </c>
+      <c r="D107" s="8">
+        <v>47734.8</v>
+      </c>
+      <c r="E107" s="9">
+        <v>-880.25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-1.29</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-2.55</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B108" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="8">
+        <v>26213.65</v>
+      </c>
+      <c r="D108" s="8">
+        <v>26108</v>
+      </c>
+      <c r="E108" s="9">
+        <v>-105.65</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7">
-        <v>9.17</v>
-      </c>
-      <c r="D14" s="7">
-        <v>7.29</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B109" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" s="8">
+        <v>31357.75</v>
+      </c>
+      <c r="D109" s="8">
+        <v>30213.45</v>
+      </c>
+      <c r="E109" s="9">
+        <v>-1144.3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="7">
-        <v>3.71</v>
-      </c>
-      <c r="D15" s="7">
-        <v>4.13</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B110" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="8">
+        <v>16545.3</v>
+      </c>
+      <c r="D110" s="8">
+        <v>16553.4</v>
+      </c>
+      <c r="E110" s="10">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0.42</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B111" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="8">
+        <v>9419.1</v>
+      </c>
+      <c r="D111" s="8">
+        <v>9376.549999999999</v>
+      </c>
+      <c r="E111" s="9">
+        <v>-42.55</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7">
-        <v>4.52</v>
-      </c>
-      <c r="D17" s="7">
-        <v>4.88</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B112" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" s="8">
+        <v>1590.1</v>
+      </c>
+      <c r="D112" s="8">
+        <v>1602.2</v>
+      </c>
+      <c r="E112" s="10">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="7">
-        <v>3.57</v>
-      </c>
-      <c r="D18" s="7">
-        <v>5.37</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B113" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="8">
+        <v>12941.7</v>
+      </c>
+      <c r="D113" s="8">
+        <v>13025.3</v>
+      </c>
+      <c r="E113" s="10">
+        <v>83.59999999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.67</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-0.77</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B114" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="8">
+        <v>9844.950000000001</v>
+      </c>
+      <c r="D114" s="8">
+        <v>9838.5</v>
+      </c>
+      <c r="E114" s="9">
+        <v>-6.45</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="7">
-        <v>4.68</v>
-      </c>
-      <c r="D20" s="7">
-        <v>3.87</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B115" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" s="8">
+        <v>8738.799999999999</v>
+      </c>
+      <c r="D115" s="8">
+        <v>8618.5</v>
+      </c>
+      <c r="E115" s="9">
+        <v>-120.3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1.68</v>
-      </c>
-      <c r="D21" s="7">
-        <v>3.12</v>
-      </c>
-      <c r="E21" s="9">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B116" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" s="8">
+        <v>26445.55</v>
+      </c>
+      <c r="D116" s="8">
+        <v>26361.9</v>
+      </c>
+      <c r="E116" s="9">
+        <v>-83.65000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-1.16</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-1.09</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B117" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="8">
+        <v>895.65</v>
+      </c>
+      <c r="D117" s="8">
+        <v>895.8</v>
+      </c>
+      <c r="E117" s="10">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B118" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="8">
+        <v>31128.25</v>
+      </c>
+      <c r="D118" s="8">
+        <v>30759.75</v>
+      </c>
+      <c r="E118" s="9">
+        <v>-368.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B119" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="8">
+        <v>16505.3</v>
+      </c>
+      <c r="D119" s="8">
+        <v>16463.7</v>
+      </c>
+      <c r="E119" s="9">
+        <v>-41.6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>5.66</v>
-      </c>
-      <c r="D25" s="7">
-        <v>5.31</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B120" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="8">
+        <v>9811.75</v>
+      </c>
+      <c r="D120" s="8">
+        <v>9968.25</v>
+      </c>
+      <c r="E120" s="10">
+        <v>156.5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0.11</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.8</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B121" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" s="8">
+        <v>11200.05</v>
+      </c>
+      <c r="D121" s="8">
+        <v>11231.15</v>
+      </c>
+      <c r="E121" s="10">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-2.39</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-4.2</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B122" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="8">
+        <v>27247.25</v>
+      </c>
+      <c r="D122" s="8">
+        <v>27247.9</v>
+      </c>
+      <c r="E122" s="10">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-1.48</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B123" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123" s="8">
+        <v>99</v>
+      </c>
+      <c r="D123" s="8">
+        <v>93</v>
+      </c>
+      <c r="E123" s="9">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-1.69</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-1.68</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B124" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" s="8">
+        <v>56</v>
+      </c>
+      <c r="D124" s="8">
+        <v>62</v>
+      </c>
+      <c r="E124" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-1.35</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B125" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" s="8">
+        <v>68</v>
+      </c>
+      <c r="D125" s="8">
+        <v>56</v>
+      </c>
+      <c r="E125" s="9">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-0.5</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-0.25</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B126" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" s="8">
+        <v>44</v>
+      </c>
+      <c r="D126" s="8">
+        <v>50</v>
+      </c>
+      <c r="E126" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" s="8">
+        <v>26</v>
+      </c>
+      <c r="D127" s="8">
+        <v>32</v>
+      </c>
+      <c r="E127" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C128" s="8">
+        <v>50</v>
+      </c>
+      <c r="D128" s="8">
+        <v>13</v>
+      </c>
+      <c r="E128" s="9">
+        <v>-37</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C129" s="8">
+        <v>38</v>
+      </c>
+      <c r="D129" s="8">
+        <v>44</v>
+      </c>
+      <c r="E129" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130" s="8">
+        <v>62</v>
+      </c>
+      <c r="D130" s="8">
+        <v>68</v>
+      </c>
+      <c r="E130" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C131" s="8">
+        <v>87</v>
+      </c>
+      <c r="D131" s="8">
+        <v>99</v>
+      </c>
+      <c r="E131" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C132" s="8">
+        <v>13</v>
+      </c>
+      <c r="D132" s="8">
+        <v>26</v>
+      </c>
+      <c r="E132" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133" s="8">
+        <v>93</v>
+      </c>
+      <c r="D133" s="8">
+        <v>87</v>
+      </c>
+      <c r="E133" s="9">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134" s="8">
+        <v>32</v>
+      </c>
+      <c r="D134" s="8">
+        <v>38</v>
+      </c>
+      <c r="E134" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C135" s="8">
+        <v>66.45</v>
+      </c>
+      <c r="D135" s="8">
+        <v>66.84</v>
+      </c>
+      <c r="E135" s="10">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C136" s="8">
+        <v>42.54</v>
+      </c>
+      <c r="D136" s="8">
+        <v>42.34</v>
+      </c>
+      <c r="E136" s="9">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C137" s="8">
+        <v>64.02</v>
+      </c>
+      <c r="D137" s="8">
+        <v>53.05</v>
+      </c>
+      <c r="E137" s="9">
+        <v>-10.97</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C138" s="8">
+        <v>37.95</v>
+      </c>
+      <c r="D138" s="8">
+        <v>39.49</v>
+      </c>
+      <c r="E138" s="10">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-1.66</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-2.55</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B139" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C139" s="8">
+        <v>43.74</v>
+      </c>
+      <c r="D139" s="8">
+        <v>34.93</v>
+      </c>
+      <c r="E139" s="9">
+        <v>-8.81</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-0.95</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-1.24</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B140" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C140" s="8">
+        <v>40.14</v>
+      </c>
+      <c r="D140" s="8">
+        <v>37.89</v>
+      </c>
+      <c r="E140" s="9">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-0.6</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-0.87</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B141" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141" s="8">
+        <v>61.73</v>
+      </c>
+      <c r="D141" s="8">
+        <v>48.25</v>
+      </c>
+      <c r="E141" s="9">
+        <v>-13.48</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-0.7</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-0.43</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B142" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C142" s="8">
+        <v>64.17</v>
+      </c>
+      <c r="D142" s="8">
+        <v>63.42</v>
+      </c>
+      <c r="E142" s="9">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-0.89</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-0.52</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B143" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C143" s="8">
+        <v>51.23</v>
+      </c>
+      <c r="D143" s="8">
+        <v>46.86</v>
+      </c>
+      <c r="E143" s="9">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="7">
-        <v>2.26</v>
-      </c>
-      <c r="D37" s="7">
-        <v>2.33</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B144" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C144" s="8">
+        <v>61.52</v>
+      </c>
+      <c r="D144" s="8">
+        <v>63.9</v>
+      </c>
+      <c r="E144" s="10">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-1.88</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-0.92</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B145" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C145" s="8">
+        <v>53.52</v>
+      </c>
+      <c r="D145" s="8">
+        <v>55.6</v>
+      </c>
+      <c r="E145" s="10">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="D39" s="7">
-        <v>0.11</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B146" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C146" s="8">
+        <v>40.38</v>
+      </c>
+      <c r="D146" s="8">
+        <v>40.35</v>
+      </c>
+      <c r="E146" s="9">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-0.54</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.77</v>
-      </c>
-      <c r="E40" s="9">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B147" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C147" s="8">
+        <v>61.26</v>
+      </c>
+      <c r="D147" s="8">
+        <v>53.44</v>
+      </c>
+      <c r="E147" s="9">
+        <v>-7.82</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-0.13</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B148" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C148" s="8">
+        <v>57.91</v>
+      </c>
+      <c r="D148" s="8">
+        <v>55.12</v>
+      </c>
+      <c r="E148" s="9">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="7">
-        <v>1.09</v>
-      </c>
-      <c r="D42" s="7">
-        <v>1.2</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B149" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C149" s="8">
+        <v>51.55</v>
+      </c>
+      <c r="D149" s="8">
+        <v>50.9</v>
+      </c>
+      <c r="E149" s="9">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-0.44</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-1.08</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B150" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C150" s="8">
+        <v>47.13</v>
+      </c>
+      <c r="D150" s="8">
+        <v>37.55</v>
+      </c>
+      <c r="E150" s="9">
+        <v>-9.58</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-1.22</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-1.33</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
+      <c r="B151" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C151" s="8">
+        <v>50.27</v>
+      </c>
+      <c r="D151" s="8">
+        <v>48.3</v>
+      </c>
+      <c r="E151" s="9">
+        <v>-1.97</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="7">
-        <v>0.82</v>
-      </c>
-      <c r="D45" s="7">
-        <v>2.14</v>
-      </c>
-      <c r="E45" s="9">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="B152" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C152" s="8">
+        <v>66.17</v>
+      </c>
+      <c r="D152" s="8">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="E152" s="10">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-0.99</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-0.55</v>
-      </c>
-      <c r="E46" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="B153" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C153" s="8">
+        <v>49.16</v>
+      </c>
+      <c r="D153" s="8">
+        <v>51.5</v>
+      </c>
+      <c r="E153" s="10">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-0.53</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="7">
-        <v>22.33</v>
-      </c>
-      <c r="D48" s="7">
-        <v>22.86</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="7">
-        <v>12.28</v>
-      </c>
-      <c r="D49" s="7">
-        <v>13.05</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="7">
-        <v>2.99</v>
-      </c>
-      <c r="D50" s="7">
-        <v>2.7</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="7">
-        <v>10.42</v>
-      </c>
-      <c r="D51" s="7">
-        <v>11.44</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-12.77</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-12.9</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-0.61</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-0.58</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-10.49</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-8.91</v>
-      </c>
-      <c r="E54" s="9">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="7">
-        <v>4.16</v>
-      </c>
-      <c r="D55" s="7">
-        <v>4.41</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="7">
-        <v>-3.05</v>
-      </c>
-      <c r="D56" s="7">
-        <v>-1.54</v>
-      </c>
-      <c r="E56" s="9">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="7">
-        <v>38.62</v>
-      </c>
-      <c r="D57" s="7">
-        <v>40.93</v>
-      </c>
-      <c r="E57" s="9">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="7">
-        <v>2.3</v>
-      </c>
-      <c r="D58" s="7">
-        <v>2.89</v>
-      </c>
-      <c r="E58" s="9">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="7">
-        <v>27.6</v>
-      </c>
-      <c r="D59" s="7">
-        <v>26.38</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="7">
-        <v>20.37</v>
-      </c>
-      <c r="D60" s="7">
-        <v>22.87</v>
-      </c>
-      <c r="E60" s="9">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-1.34</v>
-      </c>
-      <c r="D61" s="7">
-        <v>1.63</v>
-      </c>
-      <c r="E61" s="9">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-3.96</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-4.15</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="7">
-        <v>1.39</v>
-      </c>
-      <c r="D63" s="7">
-        <v>1.71</v>
-      </c>
-      <c r="E63" s="9">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="7">
-        <v>12.03</v>
-      </c>
-      <c r="D64" s="7">
-        <v>13.87</v>
-      </c>
-      <c r="E64" s="9">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-3.75</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-2.91</v>
-      </c>
-      <c r="E65" s="9">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66" s="7">
-        <v>6.68</v>
-      </c>
-      <c r="D66" s="7">
-        <v>6.53</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-3.17</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-2.19</v>
-      </c>
-      <c r="E67" s="9">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" s="7">
-        <v>-4.77</v>
-      </c>
-      <c r="D68" s="7">
-        <v>-5.49</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="7">
-        <v>3.43</v>
-      </c>
-      <c r="D69" s="7">
-        <v>3.42</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="7">
-        <v>13.14</v>
-      </c>
-      <c r="D70" s="7">
-        <v>10.45</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="7">
-        <v>0.98</v>
-      </c>
-      <c r="D71" s="7">
-        <v>1.18</v>
-      </c>
-      <c r="E71" s="9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="7">
-        <v>10.72</v>
-      </c>
-      <c r="D72" s="7">
-        <v>13.66</v>
-      </c>
-      <c r="E72" s="9">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-2.7</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-0.5</v>
-      </c>
-      <c r="E73" s="9">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-6.11</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-4.64</v>
-      </c>
-      <c r="E74" s="9">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="7">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="D75" s="7">
-        <v>10.58</v>
-      </c>
-      <c r="E75" s="9">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="7">
-        <v>7.35</v>
-      </c>
-      <c r="D76" s="7">
-        <v>6.8</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="7">
-        <v>18.43</v>
-      </c>
-      <c r="D77" s="7">
-        <v>20.85</v>
-      </c>
-      <c r="E77" s="9">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="7">
-        <v>4.8</v>
-      </c>
-      <c r="D78" s="7">
-        <v>3.93</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-1.48</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-1.58</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-6.48</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-6.28</v>
-      </c>
-      <c r="E80" s="9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-4.55</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-7.18</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-6.94</v>
-      </c>
-      <c r="E82" s="9">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-14.87</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-15.76</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-7.9</v>
-      </c>
-      <c r="D84" s="7">
-        <v>-7.89</v>
-      </c>
-      <c r="E84" s="9">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="7">
-        <v>-0.7</v>
-      </c>
-      <c r="D85" s="7">
-        <v>-0.47</v>
-      </c>
-      <c r="E85" s="9">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="7">
-        <v>-3.55</v>
-      </c>
-      <c r="D86" s="7">
-        <v>-3.58</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="7">
-        <v>-4.87</v>
-      </c>
-      <c r="D87" s="7">
-        <v>-4.53</v>
-      </c>
-      <c r="E87" s="9">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="7">
-        <v>-5.66</v>
-      </c>
-      <c r="D88" s="7">
-        <v>-4.47</v>
-      </c>
-      <c r="E88" s="9">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C89" s="7">
-        <v>-8.56</v>
-      </c>
-      <c r="D89" s="7">
-        <v>-8.4</v>
-      </c>
-      <c r="E89" s="9">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="7">
-        <v>-11.55</v>
-      </c>
-      <c r="D90" s="7">
-        <v>-11.88</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="7">
-        <v>-7.54</v>
-      </c>
-      <c r="D91" s="7">
-        <v>-6.19</v>
-      </c>
-      <c r="E91" s="9">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="7">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="D92" s="7">
-        <v>-9.18</v>
-      </c>
-      <c r="E92" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="7">
-        <v>-1.66</v>
-      </c>
-      <c r="D93" s="7">
-        <v>-2.11</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="D94" s="7">
-        <v>-1.41</v>
-      </c>
-      <c r="E94" s="9">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="7">
-        <v>-6.65</v>
-      </c>
-      <c r="D95" s="7">
-        <v>-6.43</v>
-      </c>
-      <c r="E95" s="9">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C96" s="7">
-        <v>29207.9</v>
-      </c>
-      <c r="D96" s="7">
-        <v>29178.1</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-29.8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C97" s="7">
-        <v>9822.75</v>
-      </c>
-      <c r="D97" s="7">
-        <v>9843.299999999999</v>
-      </c>
-      <c r="E97" s="9">
-        <v>20.55</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98" s="7">
-        <v>12142.85</v>
-      </c>
-      <c r="D98" s="7">
-        <v>12064.55</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-78.3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C99" s="7">
-        <v>38554.2</v>
-      </c>
-      <c r="D99" s="7">
-        <v>38652.65</v>
-      </c>
-      <c r="E99" s="9">
-        <v>98.45</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C100" s="7">
-        <v>48615.05</v>
-      </c>
-      <c r="D100" s="7">
-        <v>48105.05</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-510</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C101" s="7">
-        <v>26213.65</v>
-      </c>
-      <c r="D101" s="7">
-        <v>26217.15</v>
-      </c>
-      <c r="E101" s="9">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C102" s="7">
-        <v>16545.3</v>
-      </c>
-      <c r="D102" s="7">
-        <v>16583.6</v>
-      </c>
-      <c r="E102" s="9">
-        <v>38.3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C103" s="7">
-        <v>9419.1</v>
-      </c>
-      <c r="D103" s="7">
-        <v>9416.5</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C104" s="7">
-        <v>1590.1</v>
-      </c>
-      <c r="D104" s="7">
-        <v>1595.75</v>
-      </c>
-      <c r="E104" s="9">
-        <v>5.65</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C105" s="7">
-        <v>12941.7</v>
-      </c>
-      <c r="D105" s="7">
-        <v>13104.6</v>
-      </c>
-      <c r="E105" s="9">
-        <v>162.9</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="7">
-        <v>9844.950000000001</v>
-      </c>
-      <c r="D106" s="7">
-        <v>9861.6</v>
-      </c>
-      <c r="E106" s="9">
-        <v>16.65</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C107" s="7">
-        <v>8738.799999999999</v>
-      </c>
-      <c r="D107" s="7">
-        <v>8706.200000000001</v>
-      </c>
-      <c r="E107" s="8">
-        <v>-32.6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C108" s="7">
-        <v>895.65</v>
-      </c>
-      <c r="D108" s="7">
-        <v>908.7</v>
-      </c>
-      <c r="E108" s="9">
-        <v>13.05</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C109" s="7">
-        <v>31128.25</v>
-      </c>
-      <c r="D109" s="7">
-        <v>30971.65</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-156.6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C110" s="7">
-        <v>16505.3</v>
-      </c>
-      <c r="D110" s="7">
-        <v>16429.35</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-75.95</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C111" s="7">
-        <v>9811.75</v>
-      </c>
-      <c r="D111" s="7">
-        <v>9841.5</v>
-      </c>
-      <c r="E111" s="9">
-        <v>29.75</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C112" s="7">
-        <v>11200.05</v>
-      </c>
-      <c r="D112" s="7">
-        <v>11208.5</v>
-      </c>
-      <c r="E112" s="9">
-        <v>8.449999999999999</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" s="7">
-        <v>27247.25</v>
-      </c>
-      <c r="D113" s="7">
-        <v>27311.05</v>
-      </c>
-      <c r="E113" s="9">
-        <v>63.8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C114" s="7">
-        <v>99</v>
-      </c>
-      <c r="D114" s="7">
-        <v>93</v>
-      </c>
-      <c r="E114" s="8">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C115" s="7">
-        <v>68</v>
-      </c>
-      <c r="D115" s="7">
-        <v>62</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C116" s="7">
-        <v>44</v>
-      </c>
-      <c r="D116" s="7">
-        <v>50</v>
-      </c>
-      <c r="E116" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C117" s="7">
-        <v>50</v>
-      </c>
-      <c r="D117" s="7">
-        <v>38</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C118" s="7">
-        <v>38</v>
-      </c>
-      <c r="D118" s="7">
-        <v>44</v>
-      </c>
-      <c r="E118" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C119" s="7">
-        <v>62</v>
-      </c>
-      <c r="D119" s="7">
-        <v>68</v>
-      </c>
-      <c r="E119" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C120" s="7">
-        <v>87</v>
-      </c>
-      <c r="D120" s="7">
-        <v>99</v>
-      </c>
-      <c r="E120" s="9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C121" s="7">
-        <v>93</v>
-      </c>
-      <c r="D121" s="7">
-        <v>87</v>
-      </c>
-      <c r="E121" s="8">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B122" s="6" t="s">
+      <c r="B154" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C122" s="7">
-        <v>66.45</v>
-      </c>
-      <c r="D122" s="7">
-        <v>65.76000000000001</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C123" s="7">
-        <v>42.54</v>
-      </c>
-      <c r="D123" s="7">
-        <v>44.62</v>
-      </c>
-      <c r="E123" s="9">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C124" s="7">
-        <v>64.02</v>
-      </c>
-      <c r="D124" s="7">
-        <v>57.5</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-6.52</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C125" s="7">
-        <v>37.95</v>
-      </c>
-      <c r="D125" s="7">
-        <v>41.11</v>
-      </c>
-      <c r="E125" s="9">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C126" s="7">
-        <v>43.74</v>
-      </c>
-      <c r="D126" s="7">
-        <v>38.32</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-5.42</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C127" s="7">
-        <v>40.14</v>
-      </c>
-      <c r="D127" s="7">
-        <v>40.25</v>
-      </c>
-      <c r="E127" s="9">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C128" s="7">
-        <v>64.17</v>
-      </c>
-      <c r="D128" s="7">
-        <v>65.67</v>
-      </c>
-      <c r="E128" s="9">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C129" s="7">
-        <v>51.23</v>
-      </c>
-      <c r="D129" s="7">
-        <v>50.96</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C130" s="7">
-        <v>61.52</v>
-      </c>
-      <c r="D130" s="7">
-        <v>62.63</v>
-      </c>
-      <c r="E130" s="9">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C131" s="7">
-        <v>53.52</v>
-      </c>
-      <c r="D131" s="7">
-        <v>59.1</v>
-      </c>
-      <c r="E131" s="9">
-        <v>5.58</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C132" s="7">
-        <v>40.38</v>
-      </c>
-      <c r="D132" s="7">
-        <v>42.53</v>
-      </c>
-      <c r="E132" s="9">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C133" s="7">
-        <v>61.26</v>
-      </c>
-      <c r="D133" s="7">
-        <v>59.04</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C134" s="7">
-        <v>51.55</v>
-      </c>
-      <c r="D134" s="7">
-        <v>57.02</v>
-      </c>
-      <c r="E134" s="9">
-        <v>5.47</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C135" s="7">
-        <v>47.13</v>
-      </c>
-      <c r="D135" s="7">
-        <v>42.7</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-4.43</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C136" s="7">
-        <v>50.27</v>
-      </c>
-      <c r="D136" s="7">
-        <v>46.33</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-3.94</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C137" s="7">
-        <v>66.17</v>
-      </c>
-      <c r="D137" s="7">
-        <v>67.17</v>
-      </c>
-      <c r="E137" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C138" s="7">
-        <v>49.16</v>
-      </c>
-      <c r="D138" s="7">
-        <v>49.78</v>
-      </c>
-      <c r="E138" s="9">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C139" s="7">
+      <c r="C154" s="8">
         <v>37.64</v>
       </c>
-      <c r="D139" s="7">
-        <v>39.51</v>
-      </c>
-      <c r="E139" s="9">
-        <v>1.87</v>
+      <c r="D154" s="8">
+        <v>38.28</v>
+      </c>
+      <c r="E154" s="10">
+        <v>0.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5698,60 +6005,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>111</v>
+      <c r="B1" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="13">
         <v>51.24</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="14">
         <v>20</v>
       </c>
-      <c r="D2" s="12">
-        <v>52.5</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="13">
         <v>50</v>
       </c>
-      <c r="F2" s="12">
-        <v>1.6</v>
-      </c>
-      <c r="G2" s="12">
-        <v>5</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="E2" s="13">
+        <v>50</v>
+      </c>
+      <c r="F2" s="13">
+        <v>1</v>
+      </c>
+      <c r="G2" s="13">
+        <v>3.9</v>
+      </c>
+      <c r="H2" s="13">
         <v>53.1</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>40</v>
       </c>
     </row>
@@ -5853,131 +6160,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="15">
-        <v>0.6446</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3717</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.355</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.3026</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.2367</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.2239</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.1842</v>
-      </c>
-      <c r="H2" s="15">
-        <v>0.1792</v>
-      </c>
-      <c r="I2" s="15">
-        <v>0.1556</v>
-      </c>
-      <c r="J2" s="15">
+      <c r="A2" s="16">
+        <v>0.7504000000000001</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.3643</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.3517</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.2992</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.2379</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.2242</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.1826</v>
+      </c>
+      <c r="H2" s="16">
+        <v>0.1796</v>
+      </c>
+      <c r="I2" s="16">
+        <v>0.1544</v>
+      </c>
+      <c r="J2" s="16">
         <v>0.1441</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="15">
-        <v>0.135</v>
-      </c>
-      <c r="B4" s="15">
-        <v>0.1285</v>
-      </c>
-      <c r="C4" s="15">
-        <v>0.1278</v>
-      </c>
-      <c r="D4" s="15">
-        <v>0.1027</v>
-      </c>
-      <c r="E4" s="15">
-        <v>0.0858</v>
-      </c>
-      <c r="F4" s="15">
-        <v>0.08039999999999999</v>
-      </c>
-      <c r="G4" s="15">
-        <v>0.05769999999999999</v>
-      </c>
-      <c r="H4" s="15">
-        <v>0.0512</v>
-      </c>
-      <c r="I4" s="15">
-        <v>-0.0092</v>
-      </c>
-      <c r="J4" s="15">
-        <v>-0.0126</v>
+      <c r="A4" s="16">
+        <v>0.1338</v>
+      </c>
+      <c r="B4" s="16">
+        <v>0.1276</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.1262</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0.1132</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0.0861</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0.0819</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.0572</v>
+      </c>
+      <c r="H4" s="16">
+        <v>0.0481</v>
+      </c>
+      <c r="I4" s="16">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="J4" s="16">
+        <v>-0.0201</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="121">
   <si>
     <t>Symbol</t>
   </si>
@@ -292,67 +292,58 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.2 → 51.5</t>
+    <t>48.2 → 50.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.2</t>
+    <t>48.2</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>71.1 → 61.8</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>71.1</t>
+  </si>
+  <si>
+    <t>61.8</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.9% → -2.2%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.9%</t>
+  </si>
+  <si>
+    <t>-2.2%</t>
+  </si>
+  <si>
+    <t>51.5 → 47.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.5</t>
   </si>
   <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>66.2 → 71.1</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>66.2</t>
-  </si>
-  <si>
-    <t>71.1</t>
-  </si>
-  <si>
-    <t>61.7 → 48.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>61.7</t>
-  </si>
-  <si>
-    <t>48.2</t>
-  </si>
-  <si>
-    <t>51.2 → 46.9</t>
-  </si>
-  <si>
-    <t>51.2</t>
-  </si>
-  <si>
-    <t>46.9</t>
-  </si>
-  <si>
-    <t>50.3 → 48.3</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>48.3</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>47.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -445,7 +436,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -491,7 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1097,55 +1088,55 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>29264.55</v>
+        <v>29185.4</v>
       </c>
       <c r="E2">
-        <v>0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
       </c>
       <c r="G2">
-        <v>23474.65</v>
+        <v>23723.75</v>
       </c>
       <c r="H2">
-        <v>-1.29</v>
+        <v>-1.56</v>
       </c>
       <c r="I2">
-        <v>24.66</v>
+        <v>23.02</v>
       </c>
       <c r="J2">
-        <v>-0.66</v>
+        <v>-0.61</v>
       </c>
       <c r="K2">
-        <v>7.99</v>
+        <v>7.7</v>
       </c>
       <c r="L2">
-        <v>13.88</v>
+        <v>12.62</v>
       </c>
       <c r="M2">
-        <v>22.92</v>
+        <v>24.33</v>
       </c>
       <c r="N2">
-        <v>23.79</v>
+        <v>24.14</v>
       </c>
       <c r="O2">
         <v>93</v>
       </c>
       <c r="Q2">
-        <v>29281.15</v>
+        <v>29245.62</v>
       </c>
       <c r="R2">
-        <v>28574.46</v>
+        <v>28678.74</v>
       </c>
       <c r="S2">
-        <v>27458.07</v>
+        <v>27521.27</v>
       </c>
       <c r="T2">
-        <v>27019.83</v>
+        <v>27029.44</v>
       </c>
       <c r="U2">
-        <v>8.31</v>
+        <v>7.98</v>
       </c>
       <c r="V2" t="b">
         <v>1</v>
@@ -1160,34 +1151,34 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>66.84</v>
+        <v>64.81</v>
       </c>
       <c r="AA2">
-        <v>615.4</v>
+        <v>579.46</v>
       </c>
       <c r="AB2">
-        <v>630.71</v>
+        <v>620.46</v>
       </c>
       <c r="AC2">
-        <v>-15.32</v>
+        <v>-41.01</v>
       </c>
       <c r="AD2">
-        <v>29.49</v>
+        <v>15.49</v>
       </c>
       <c r="AE2">
-        <v>43.29</v>
+        <v>30.64</v>
       </c>
       <c r="AF2">
-        <v>377.37</v>
+        <v>367.58</v>
       </c>
       <c r="AG2">
         <v>-100</v>
       </c>
       <c r="AH2">
-        <v>30641.07</v>
+        <v>30639.82</v>
       </c>
       <c r="AI2">
-        <v>26507.85</v>
+        <v>26717.67</v>
       </c>
       <c r="AJ2">
         <v>28374.42</v>
@@ -1196,7 +1187,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>52.91</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1210,10 +1201,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9814.950000000001</v>
+        <v>9755.15</v>
       </c>
       <c r="E3">
-        <v>-0.29</v>
+        <v>-0.61</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1222,43 +1213,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-6.55</v>
+        <v>-7.12</v>
       </c>
       <c r="I3">
-        <v>14.5</v>
+        <v>13.81</v>
       </c>
       <c r="J3">
-        <v>-1.13</v>
+        <v>-1.66</v>
       </c>
       <c r="K3">
-        <v>-0.17</v>
+        <v>-0.78</v>
       </c>
       <c r="L3">
-        <v>-3.15</v>
+        <v>-4.38</v>
       </c>
       <c r="M3">
-        <v>12.71</v>
+        <v>12.92</v>
       </c>
       <c r="N3">
-        <v>12.76</v>
+        <v>13.4</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Q3">
-        <v>9855.84</v>
+        <v>9822.84</v>
       </c>
       <c r="R3">
-        <v>9889.120000000001</v>
+        <v>9885.27</v>
       </c>
       <c r="S3">
-        <v>9892.16</v>
+        <v>9887.799999999999</v>
       </c>
       <c r="T3">
-        <v>9718.459999999999</v>
+        <v>9720.610000000001</v>
       </c>
       <c r="U3">
-        <v>0.99</v>
+        <v>0.36</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -1273,40 +1264,40 @@
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>42.34</v>
+        <v>37.93</v>
       </c>
       <c r="AA3">
-        <v>-8.81</v>
+        <v>-18.44</v>
       </c>
       <c r="AB3">
-        <v>1.05</v>
+        <v>-2.84</v>
       </c>
       <c r="AC3">
-        <v>-9.859999999999999</v>
+        <v>-15.6</v>
       </c>
       <c r="AD3">
         <v>3.42</v>
       </c>
       <c r="AE3">
-        <v>10.03</v>
+        <v>5.28</v>
       </c>
       <c r="AF3">
-        <v>86.79000000000001</v>
+        <v>86.92</v>
       </c>
       <c r="AH3">
-        <v>10031.84</v>
+        <v>10038.24</v>
       </c>
       <c r="AI3">
-        <v>9746.389999999999</v>
+        <v>9732.290000000001</v>
       </c>
       <c r="AJ3">
-        <v>10073.2</v>
+        <v>10027.74</v>
       </c>
       <c r="AK3" t="s">
         <v>82</v>
       </c>
       <c r="AL3">
-        <v>30.03</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1320,10 +1311,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>12004.7</v>
+        <v>11986.85</v>
       </c>
       <c r="E4">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1332,43 +1323,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-5.02</v>
+        <v>-5.16</v>
       </c>
       <c r="I4">
-        <v>16.16</v>
+        <v>15.99</v>
       </c>
       <c r="J4">
-        <v>-1.22</v>
+        <v>-0.87</v>
       </c>
       <c r="K4">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="L4">
-        <v>6.06</v>
+        <v>5.96</v>
       </c>
       <c r="M4">
-        <v>1.97</v>
+        <v>2.92</v>
       </c>
       <c r="N4">
-        <v>12.62</v>
+        <v>12.42</v>
       </c>
       <c r="O4">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q4">
-        <v>12088.46</v>
+        <v>12067.39</v>
       </c>
       <c r="R4">
-        <v>12014.02</v>
+        <v>12028.11</v>
       </c>
       <c r="S4">
-        <v>11749.93</v>
+        <v>11766.74</v>
       </c>
       <c r="T4">
-        <v>11706.13</v>
+        <v>11703.06</v>
       </c>
       <c r="U4">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="V4" t="b">
         <v>1</v>
@@ -1383,31 +1374,31 @@
         <v>3</v>
       </c>
       <c r="Z4">
-        <v>53.05</v>
+        <v>51.77</v>
       </c>
       <c r="AA4">
-        <v>109.55</v>
+        <v>94.14</v>
       </c>
       <c r="AB4">
-        <v>133.07</v>
+        <v>125.28</v>
       </c>
       <c r="AC4">
-        <v>-23.52</v>
+        <v>-31.14</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>20.76</v>
+        <v>11.89</v>
       </c>
       <c r="AF4">
-        <v>103.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="AH4">
-        <v>12446.61</v>
+        <v>12435.97</v>
       </c>
       <c r="AI4">
-        <v>11581.42</v>
+        <v>11620.25</v>
       </c>
       <c r="AJ4">
         <v>11869.84</v>
@@ -1416,7 +1407,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>31.62</v>
+        <v>30.12</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1430,10 +1421,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38578.85</v>
+        <v>38124.45</v>
       </c>
       <c r="E5">
-        <v>-0.19</v>
+        <v>-1.18</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1442,43 +1433,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-7.12</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="I5">
-        <v>16.56</v>
+        <v>15.19</v>
       </c>
       <c r="J5">
-        <v>-0.33</v>
+        <v>-1.68</v>
       </c>
       <c r="K5">
-        <v>-1.78</v>
+        <v>-2.93</v>
       </c>
       <c r="L5">
-        <v>-2.5</v>
+        <v>-5.06</v>
       </c>
       <c r="M5">
-        <v>11.46</v>
+        <v>10.85</v>
       </c>
       <c r="N5">
-        <v>14.41</v>
+        <v>14.54</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Q5">
-        <v>38650.57</v>
+        <v>38520.08</v>
       </c>
       <c r="R5">
-        <v>38871.12</v>
+        <v>38813.49</v>
       </c>
       <c r="S5">
-        <v>39276.05</v>
+        <v>39243.48</v>
       </c>
       <c r="T5">
-        <v>37363.92</v>
+        <v>37375.64</v>
       </c>
       <c r="U5">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
@@ -1493,43 +1484,43 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>39.49</v>
+        <v>31.28</v>
       </c>
       <c r="AA5">
-        <v>-197.49</v>
+        <v>-231.43</v>
       </c>
       <c r="AB5">
-        <v>-197.05</v>
+        <v>-203.93</v>
       </c>
       <c r="AC5">
-        <v>-0.43</v>
+        <v>-27.5</v>
       </c>
       <c r="AD5">
-        <v>65.77</v>
+        <v>47.87</v>
       </c>
       <c r="AE5">
-        <v>66.37</v>
+        <v>59.62</v>
       </c>
       <c r="AF5">
-        <v>352.37</v>
+        <v>367.57</v>
       </c>
       <c r="AG5">
         <v>-100</v>
       </c>
       <c r="AH5">
-        <v>39469.1</v>
+        <v>39466.4</v>
       </c>
       <c r="AI5">
-        <v>38273.14</v>
+        <v>38160.59</v>
       </c>
       <c r="AJ5">
-        <v>39538.76</v>
+        <v>39408.4</v>
       </c>
       <c r="AK5" t="s">
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>13.42</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1543,10 +1534,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>47734.8</v>
+        <v>47473.9</v>
       </c>
       <c r="E6">
-        <v>-0.77</v>
+        <v>-0.55</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1555,43 +1546,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-16.41</v>
+        <v>-16.86</v>
       </c>
       <c r="I6">
-        <v>4.82</v>
+        <v>4.25</v>
       </c>
       <c r="J6">
-        <v>-2.16</v>
+        <v>-1.97</v>
       </c>
       <c r="K6">
-        <v>-2.08</v>
+        <v>-2.62</v>
       </c>
       <c r="L6">
-        <v>-6.19</v>
+        <v>-6.03</v>
       </c>
       <c r="M6">
-        <v>-13.68</v>
+        <v>-13.53</v>
       </c>
       <c r="N6">
-        <v>4.81</v>
+        <v>4.23</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>48344.31</v>
+        <v>48153.22</v>
       </c>
       <c r="R6">
-        <v>48940.49</v>
+        <v>48876.75</v>
       </c>
       <c r="S6">
-        <v>49083.65</v>
+        <v>49064.18</v>
       </c>
       <c r="T6">
-        <v>51141.78</v>
+        <v>51097</v>
       </c>
       <c r="U6">
-        <v>-6.66</v>
+        <v>-7.09</v>
       </c>
       <c r="V6" t="b">
         <v>0</v>
@@ -1606,43 +1597,43 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>34.93</v>
+        <v>32.74</v>
       </c>
       <c r="AA6">
-        <v>-222.16</v>
+        <v>-301.56</v>
       </c>
       <c r="AB6">
-        <v>-81.08</v>
+        <v>-125.17</v>
       </c>
       <c r="AC6">
-        <v>-141.08</v>
+        <v>-176.38</v>
       </c>
       <c r="AD6">
-        <v>5.56</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>12.06</v>
+        <v>6.96</v>
       </c>
       <c r="AF6">
-        <v>581.95</v>
+        <v>583.66</v>
       </c>
       <c r="AG6">
         <v>-100</v>
       </c>
       <c r="AH6">
-        <v>50016.31</v>
+        <v>50135.86</v>
       </c>
       <c r="AI6">
-        <v>47864.66</v>
+        <v>47617.63</v>
       </c>
       <c r="AJ6">
-        <v>49687.24</v>
+        <v>49398.71</v>
       </c>
       <c r="AK6" t="s">
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>30.95</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1656,10 +1647,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26108</v>
+        <v>26013</v>
       </c>
       <c r="E7">
-        <v>-0.42</v>
+        <v>-0.36</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1668,43 +1659,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-8.27</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="I7">
-        <v>10.99</v>
+        <v>10.59</v>
       </c>
       <c r="J7">
-        <v>-1.23</v>
+        <v>-1.57</v>
       </c>
       <c r="K7">
-        <v>-2.96</v>
+        <v>-3.31</v>
       </c>
       <c r="L7">
-        <v>3.26</v>
+        <v>2.84</v>
       </c>
       <c r="M7">
-        <v>-1.12</v>
+        <v>-0.59</v>
       </c>
       <c r="N7">
-        <v>8.609999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="O7">
         <v>32</v>
       </c>
       <c r="Q7">
-        <v>26258.7</v>
+        <v>26175.95</v>
       </c>
       <c r="R7">
-        <v>26626.96</v>
+        <v>26582.44</v>
       </c>
       <c r="S7">
-        <v>26543.74</v>
+        <v>26560.95</v>
       </c>
       <c r="T7">
-        <v>26712.54</v>
+        <v>26705.01</v>
       </c>
       <c r="U7">
-        <v>-2.26</v>
+        <v>-2.59</v>
       </c>
       <c r="V7" t="b">
         <v>1</v>
@@ -1719,43 +1710,43 @@
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>37.89</v>
+        <v>35.92</v>
       </c>
       <c r="AA7">
-        <v>-101.64</v>
+        <v>-126.99</v>
       </c>
       <c r="AB7">
-        <v>-16.63</v>
+        <v>-38.7</v>
       </c>
       <c r="AC7">
-        <v>-85.01000000000001</v>
+        <v>-88.28</v>
       </c>
       <c r="AD7">
         <v>0.21</v>
       </c>
       <c r="AE7">
-        <v>5.6</v>
+        <v>1.58</v>
       </c>
       <c r="AF7">
-        <v>296.68</v>
+        <v>289.3</v>
       </c>
       <c r="AG7">
         <v>-100</v>
       </c>
       <c r="AH7">
-        <v>27222.88</v>
+        <v>27222.79</v>
       </c>
       <c r="AI7">
-        <v>26031.04</v>
+        <v>25942.09</v>
       </c>
       <c r="AJ7">
-        <v>26067.59</v>
+        <v>26900.75</v>
       </c>
       <c r="AK7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL7">
-        <v>34.44</v>
+        <v>38.27</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1769,10 +1760,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>30213.45</v>
+        <v>30433.05</v>
       </c>
       <c r="E8">
-        <v>-3.65</v>
+        <v>0.73</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1781,43 +1772,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-23.49</v>
+        <v>-22.93</v>
       </c>
       <c r="I8">
-        <v>17.24</v>
+        <v>18.1</v>
       </c>
       <c r="J8">
-        <v>-5.06</v>
+        <v>-2.87</v>
       </c>
       <c r="K8">
-        <v>3.61</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>3.09</v>
+        <v>4.28</v>
       </c>
       <c r="M8">
-        <v>-13</v>
+        <v>-11.53</v>
       </c>
       <c r="N8">
-        <v>-2.01</v>
+        <v>-1.82</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>31143.08</v>
+        <v>30963.18</v>
       </c>
       <c r="R8">
-        <v>30761.65</v>
+        <v>30855.81</v>
       </c>
       <c r="S8">
-        <v>29053.11</v>
+        <v>29091.45</v>
       </c>
       <c r="T8">
-        <v>32519.53</v>
+        <v>32491.05</v>
       </c>
       <c r="U8">
-        <v>-7.09</v>
+        <v>-6.33</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
@@ -1832,34 +1823,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>48.25</v>
+        <v>50.49</v>
       </c>
       <c r="AA8">
-        <v>612.29</v>
+        <v>518.91</v>
       </c>
       <c r="AB8">
-        <v>752.5</v>
+        <v>705.78</v>
       </c>
       <c r="AC8">
-        <v>-140.21</v>
+        <v>-186.87</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AE8">
-        <v>11.09</v>
+        <v>4.08</v>
       </c>
       <c r="AF8">
-        <v>664.08</v>
+        <v>651.99</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32929.67</v>
+        <v>32767.82</v>
       </c>
       <c r="AI8">
-        <v>28593.64</v>
+        <v>28943.81</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1868,7 +1859,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>21.08</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1882,10 +1873,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16553.4</v>
+        <v>16474.4</v>
       </c>
       <c r="E9">
-        <v>-0.18</v>
+        <v>-0.48</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1894,25 +1885,25 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-0.65</v>
+        <v>-1.13</v>
       </c>
       <c r="I9">
-        <v>5.68</v>
+        <v>5.18</v>
       </c>
       <c r="J9">
-        <v>-0.33</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K9">
-        <v>3.47</v>
+        <v>2.49</v>
       </c>
       <c r="N9">
-        <v>35.17</v>
+        <v>31.16</v>
       </c>
       <c r="Q9">
-        <v>16586.67</v>
+        <v>16555.46</v>
       </c>
       <c r="R9">
-        <v>16364.75</v>
+        <v>16388.82</v>
       </c>
       <c r="X9" t="s">
         <v>80</v>
@@ -1921,31 +1912,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>63.42</v>
+        <v>57.85</v>
       </c>
       <c r="AA9">
-        <v>171.43</v>
+        <v>155.51</v>
       </c>
       <c r="AB9">
-        <v>172.34</v>
+        <v>168.97</v>
       </c>
       <c r="AC9">
-        <v>-0.91</v>
+        <v>-13.46</v>
       </c>
       <c r="AD9">
-        <v>46.35</v>
+        <v>27.11</v>
       </c>
       <c r="AE9">
-        <v>62.52</v>
+        <v>46.1</v>
       </c>
       <c r="AF9">
-        <v>123.19</v>
+        <v>124.14</v>
       </c>
       <c r="AH9">
-        <v>16960.19</v>
+        <v>16959.38</v>
       </c>
       <c r="AI9">
-        <v>15769.31</v>
+        <v>15818.26</v>
       </c>
       <c r="AJ9">
         <v>16247.16</v>
@@ -1954,7 +1945,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>37.46</v>
+        <v>33.78</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1968,10 +1959,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9376.549999999999</v>
+        <v>9305.549999999999</v>
       </c>
       <c r="E10">
-        <v>-0.42</v>
+        <v>-0.76</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1980,43 +1971,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-3.99</v>
+        <v>-4.71</v>
       </c>
       <c r="I10">
-        <v>9.529999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
-        <v>-0.08</v>
+        <v>-1.11</v>
       </c>
       <c r="K10">
-        <v>-0.01</v>
+        <v>-0.77</v>
       </c>
       <c r="L10">
-        <v>1.08</v>
+        <v>-0.53</v>
       </c>
       <c r="M10">
-        <v>4.23</v>
+        <v>4.8</v>
       </c>
       <c r="N10">
-        <v>15.44</v>
+        <v>15.7</v>
       </c>
       <c r="O10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q10">
-        <v>9403.02</v>
+        <v>9382.17</v>
       </c>
       <c r="R10">
-        <v>9411.07</v>
+        <v>9407.48</v>
       </c>
       <c r="S10">
-        <v>9390.83</v>
+        <v>9394.49</v>
       </c>
       <c r="T10">
-        <v>9362.77</v>
+        <v>9361.639999999999</v>
       </c>
       <c r="U10">
-        <v>0.15</v>
+        <v>-0.6</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
@@ -2028,37 +2019,37 @@
         <v>79</v>
       </c>
       <c r="Y10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z10">
-        <v>46.86</v>
+        <v>40.6</v>
       </c>
       <c r="AA10">
-        <v>6.36</v>
+        <v>-2.65</v>
       </c>
       <c r="AB10">
-        <v>12.36</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AC10">
-        <v>-6</v>
+        <v>-12.01</v>
       </c>
       <c r="AD10">
-        <v>20.16</v>
+        <v>10.29</v>
       </c>
       <c r="AE10">
-        <v>22.18</v>
+        <v>18.12</v>
       </c>
       <c r="AF10">
-        <v>83.08</v>
+        <v>83.59</v>
       </c>
       <c r="AG10">
         <v>-100</v>
       </c>
       <c r="AH10">
-        <v>9500.639999999999</v>
+        <v>9507.85</v>
       </c>
       <c r="AI10">
-        <v>9321.5</v>
+        <v>9307.110000000001</v>
       </c>
       <c r="AJ10">
         <v>9229.360000000001</v>
@@ -2067,7 +2058,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>24.79</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2081,10 +2072,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1602.2</v>
+        <v>1587.65</v>
       </c>
       <c r="E11">
-        <v>0.4</v>
+        <v>-0.91</v>
       </c>
       <c r="F11">
         <v>1671.5</v>
@@ -2093,43 +2084,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-4.15</v>
+        <v>-5.02</v>
       </c>
       <c r="I11">
-        <v>27.83</v>
+        <v>26.67</v>
       </c>
       <c r="J11">
-        <v>3.18</v>
+        <v>1.18</v>
       </c>
       <c r="K11">
-        <v>5.31</v>
+        <v>4.35</v>
       </c>
       <c r="L11">
-        <v>12.78</v>
+        <v>13.4</v>
       </c>
       <c r="M11">
-        <v>-2.11</v>
+        <v>-2.9</v>
       </c>
       <c r="N11">
-        <v>-0.79</v>
+        <v>-0.21</v>
       </c>
       <c r="O11">
         <v>68</v>
       </c>
       <c r="Q11">
-        <v>1586.42</v>
+        <v>1590.13</v>
       </c>
       <c r="R11">
-        <v>1561.99</v>
+        <v>1565.3</v>
       </c>
       <c r="S11">
-        <v>1524.86</v>
+        <v>1527.12</v>
       </c>
       <c r="T11">
-        <v>1443.56</v>
+        <v>1443.82</v>
       </c>
       <c r="U11">
-        <v>10.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -2144,31 +2135,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>63.9</v>
+        <v>59.01</v>
       </c>
       <c r="AA11">
-        <v>20.68</v>
+        <v>20.13</v>
       </c>
       <c r="AB11">
-        <v>19.38</v>
+        <v>19.53</v>
       </c>
       <c r="AC11">
-        <v>1.31</v>
+        <v>0.6</v>
       </c>
       <c r="AD11">
-        <v>36.55</v>
+        <v>33.14</v>
       </c>
       <c r="AE11">
-        <v>29.18</v>
+        <v>32.95</v>
       </c>
       <c r="AF11">
-        <v>30.07</v>
+        <v>29.74</v>
       </c>
       <c r="AH11">
-        <v>1625.62</v>
+        <v>1626.9</v>
       </c>
       <c r="AI11">
-        <v>1498.36</v>
+        <v>1503.7</v>
       </c>
       <c r="AJ11">
         <v>1509.79</v>
@@ -2177,7 +2168,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>42.62</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2191,55 +2182,55 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13025.3</v>
+        <v>13023.25</v>
       </c>
       <c r="E12">
-        <v>-0.61</v>
+        <v>-0.02</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
       </c>
       <c r="G12">
-        <v>9147.1</v>
+        <v>9154.799999999999</v>
       </c>
       <c r="H12">
-        <v>-5.05</v>
+        <v>-5.07</v>
       </c>
       <c r="I12">
-        <v>42.4</v>
+        <v>42.26</v>
       </c>
       <c r="J12">
-        <v>-0.58</v>
+        <v>-1.13</v>
       </c>
       <c r="K12">
-        <v>4.73</v>
+        <v>4.71</v>
       </c>
       <c r="L12">
-        <v>-1.05</v>
+        <v>-1.24</v>
       </c>
       <c r="M12">
-        <v>39.9</v>
+        <v>42.38</v>
       </c>
       <c r="N12">
-        <v>17.96</v>
+        <v>19.55</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13055.36</v>
+        <v>13025.72</v>
       </c>
       <c r="R12">
-        <v>12859.17</v>
+        <v>12888.49</v>
       </c>
       <c r="S12">
-        <v>12750.16</v>
+        <v>12750.88</v>
       </c>
       <c r="T12">
-        <v>11956.78</v>
+        <v>11969.56</v>
       </c>
       <c r="U12">
-        <v>8.94</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V12" t="b">
         <v>1</v>
@@ -2254,34 +2245,34 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>55.6</v>
+        <v>55.51</v>
       </c>
       <c r="AA12">
-        <v>116.87</v>
+        <v>109.45</v>
       </c>
       <c r="AB12">
-        <v>105.28</v>
+        <v>106.11</v>
       </c>
       <c r="AC12">
-        <v>11.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD12">
-        <v>34.62</v>
+        <v>25.24</v>
       </c>
       <c r="AE12">
-        <v>45.48</v>
+        <v>35.98</v>
       </c>
       <c r="AF12">
-        <v>189.94</v>
+        <v>184.76</v>
       </c>
       <c r="AG12">
         <v>-100</v>
       </c>
       <c r="AH12">
-        <v>13493.49</v>
+        <v>13494.19</v>
       </c>
       <c r="AI12">
-        <v>12224.86</v>
+        <v>12282.79</v>
       </c>
       <c r="AJ12">
         <v>12652.05</v>
@@ -2290,7 +2281,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>34.36</v>
+        <v>30.52</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2304,10 +2295,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9838.5</v>
+        <v>9750.85</v>
       </c>
       <c r="E13">
-        <v>-0.23</v>
+        <v>-0.89</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2316,43 +2307,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-8.619999999999999</v>
+        <v>-9.43</v>
       </c>
       <c r="I13">
-        <v>6.91</v>
+        <v>5.96</v>
       </c>
       <c r="J13">
-        <v>0.07000000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="K13">
-        <v>-1.01</v>
+        <v>-1.89</v>
       </c>
       <c r="L13">
-        <v>-5</v>
+        <v>-6.11</v>
       </c>
       <c r="M13">
-        <v>3.12</v>
+        <v>2.32</v>
       </c>
       <c r="N13">
-        <v>22.42</v>
+        <v>22.89</v>
       </c>
       <c r="O13">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q13">
-        <v>9861.85</v>
+        <v>9838.17</v>
       </c>
       <c r="R13">
-        <v>9910.620000000001</v>
+        <v>9901.23</v>
       </c>
       <c r="S13">
-        <v>9954.99</v>
+        <v>9949.15</v>
       </c>
       <c r="T13">
-        <v>10048.65</v>
+        <v>10047.63</v>
       </c>
       <c r="U13">
-        <v>-2.09</v>
+        <v>-2.95</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
@@ -2367,43 +2358,43 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>40.35</v>
+        <v>33.36</v>
       </c>
       <c r="AA13">
-        <v>-34.85</v>
+        <v>-42.71</v>
       </c>
       <c r="AB13">
-        <v>-31.44</v>
+        <v>-33.69</v>
       </c>
       <c r="AC13">
-        <v>-3.41</v>
+        <v>-9.01</v>
       </c>
       <c r="AD13">
-        <v>25.22</v>
+        <v>18.19</v>
       </c>
       <c r="AE13">
-        <v>30.9</v>
+        <v>25.94</v>
       </c>
       <c r="AF13">
-        <v>87.53</v>
+        <v>89.66</v>
       </c>
       <c r="AG13">
         <v>-100</v>
       </c>
       <c r="AH13">
-        <v>10004.59</v>
+        <v>10018.15</v>
       </c>
       <c r="AI13">
-        <v>9816.639999999999</v>
+        <v>9784.309999999999</v>
       </c>
       <c r="AJ13">
-        <v>10093.21</v>
+        <v>10052.04</v>
       </c>
       <c r="AK13" t="s">
         <v>82</v>
       </c>
       <c r="AL13">
-        <v>29.49</v>
+        <v>32.78</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2417,10 +2408,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8618.5</v>
+        <v>8617.65</v>
       </c>
       <c r="E14">
-        <v>-1.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2429,43 +2420,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-12.77</v>
+        <v>-12.78</v>
       </c>
       <c r="I14">
-        <v>27.57</v>
+        <v>27.55</v>
       </c>
       <c r="J14">
-        <v>-0.25</v>
+        <v>-2.27</v>
       </c>
       <c r="K14">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="L14">
-        <v>8.59</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M14">
-        <v>24.74</v>
+        <v>25.23</v>
       </c>
       <c r="N14">
-        <v>29.92</v>
+        <v>30.85</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8733.99</v>
+        <v>8694.02</v>
       </c>
       <c r="R14">
-        <v>8547.940000000001</v>
+        <v>8559.73</v>
       </c>
       <c r="S14">
-        <v>8504.17</v>
+        <v>8506.59</v>
       </c>
       <c r="T14">
-        <v>8577.639999999999</v>
+        <v>8580.77</v>
       </c>
       <c r="U14">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="V14" t="b">
         <v>1</v>
@@ -2480,34 +2471,34 @@
         <v>2</v>
       </c>
       <c r="Z14">
-        <v>53.44</v>
+        <v>53.39</v>
       </c>
       <c r="AA14">
-        <v>83.51000000000001</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="AB14">
-        <v>70.84</v>
+        <v>71.67</v>
       </c>
       <c r="AC14">
-        <v>12.67</v>
+        <v>3.32</v>
       </c>
       <c r="AD14">
-        <v>50.37</v>
+        <v>36.75</v>
       </c>
       <c r="AE14">
-        <v>63.78</v>
+        <v>50.83</v>
       </c>
       <c r="AF14">
-        <v>135.68</v>
+        <v>131.12</v>
       </c>
       <c r="AG14">
         <v>-100</v>
       </c>
       <c r="AH14">
-        <v>8891.030000000001</v>
+        <v>8894.9</v>
       </c>
       <c r="AI14">
-        <v>8204.84</v>
+        <v>8224.559999999999</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
@@ -2516,7 +2507,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>35.82</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2530,55 +2521,55 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26361.9</v>
+        <v>26313.8</v>
       </c>
       <c r="E15">
-        <v>-0.32</v>
+        <v>-0.18</v>
       </c>
       <c r="F15">
         <v>26762.5</v>
       </c>
       <c r="G15">
-        <v>21402.15</v>
+        <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-1.5</v>
+        <v>-1.68</v>
       </c>
       <c r="I15">
-        <v>23.17</v>
+        <v>22.65</v>
       </c>
       <c r="J15">
-        <v>-1.45</v>
+        <v>-1.68</v>
       </c>
       <c r="K15">
-        <v>1.38</v>
+        <v>0.85</v>
       </c>
       <c r="L15">
-        <v>6.01</v>
+        <v>5.92</v>
       </c>
       <c r="M15">
-        <v>21.57</v>
+        <v>22.95</v>
       </c>
       <c r="N15">
-        <v>13.38</v>
+        <v>13.94</v>
       </c>
       <c r="O15">
         <v>81</v>
       </c>
       <c r="Q15">
-        <v>26540.46</v>
+        <v>26450.72</v>
       </c>
       <c r="R15">
-        <v>26350.78</v>
+        <v>26378.85</v>
       </c>
       <c r="S15">
-        <v>25631.2</v>
+        <v>25671.67</v>
       </c>
       <c r="T15">
-        <v>23527.44</v>
+        <v>23547.46</v>
       </c>
       <c r="U15">
-        <v>12.05</v>
+        <v>11.75</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
@@ -2593,34 +2584,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>55.12</v>
+        <v>53.53</v>
       </c>
       <c r="AA15">
-        <v>253.42</v>
+        <v>222.12</v>
       </c>
       <c r="AB15">
-        <v>315.1</v>
+        <v>296.5</v>
       </c>
       <c r="AC15">
-        <v>-61.68</v>
+        <v>-74.39</v>
       </c>
       <c r="AD15">
         <v>0</v>
       </c>
       <c r="AE15">
-        <v>24.13</v>
+        <v>6.81</v>
       </c>
       <c r="AF15">
-        <v>300.82</v>
+        <v>295.68</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27086.84</v>
+        <v>27059.54</v>
       </c>
       <c r="AI15">
-        <v>25614.71</v>
+        <v>25698.16</v>
       </c>
       <c r="AJ15">
         <v>25756.98</v>
@@ -2629,7 +2620,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>35.46</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2643,10 +2634,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>895.8</v>
+        <v>895.35</v>
       </c>
       <c r="E16">
-        <v>-1.42</v>
+        <v>-0.05</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2655,43 +2646,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-7.52</v>
+        <v>-7.57</v>
       </c>
       <c r="I16">
-        <v>37.57</v>
+        <v>37.5</v>
       </c>
       <c r="J16">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="K16">
-        <v>-2.49</v>
+        <v>-2.54</v>
       </c>
       <c r="L16">
-        <v>17.45</v>
+        <v>16.73</v>
       </c>
       <c r="M16">
-        <v>0.31</v>
+        <v>2.43</v>
       </c>
       <c r="N16">
-        <v>18.26</v>
+        <v>19.13</v>
       </c>
       <c r="O16">
         <v>74</v>
       </c>
       <c r="Q16">
-        <v>897.67</v>
+        <v>898.78</v>
       </c>
       <c r="R16">
-        <v>903.22</v>
+        <v>902.05</v>
       </c>
       <c r="S16">
-        <v>872.9400000000001</v>
+        <v>875.62</v>
       </c>
       <c r="T16">
-        <v>834.22</v>
+        <v>833.9299999999999</v>
       </c>
       <c r="U16">
-        <v>7.38</v>
+        <v>7.37</v>
       </c>
       <c r="V16" t="b">
         <v>1</v>
@@ -2706,34 +2697,34 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="AA16">
-        <v>3.91</v>
+        <v>3.38</v>
       </c>
       <c r="AB16">
-        <v>6.8</v>
+        <v>6.11</v>
       </c>
       <c r="AC16">
-        <v>-2.88</v>
+        <v>-2.73</v>
       </c>
       <c r="AD16">
-        <v>34.69</v>
+        <v>35.74</v>
       </c>
       <c r="AE16">
-        <v>30.34</v>
+        <v>35.32</v>
       </c>
       <c r="AF16">
-        <v>18.4</v>
+        <v>17.96</v>
       </c>
       <c r="AG16">
         <v>-100</v>
       </c>
       <c r="AH16">
-        <v>927.73</v>
+        <v>925.67</v>
       </c>
       <c r="AI16">
-        <v>878.7</v>
+        <v>878.4299999999999</v>
       </c>
       <c r="AJ16">
         <v>864.8</v>
@@ -2742,7 +2733,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>17.22</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2756,10 +2747,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30759.75</v>
+        <v>30682.9</v>
       </c>
       <c r="E17">
-        <v>-0.68</v>
+        <v>-0.25</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2768,43 +2759,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-9.800000000000001</v>
+        <v>-10.02</v>
       </c>
       <c r="I17">
-        <v>8.449999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="J17">
-        <v>-1.49</v>
+        <v>-1.59</v>
       </c>
       <c r="K17">
-        <v>-2.16</v>
+        <v>-2.41</v>
       </c>
       <c r="L17">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="M17">
-        <v>-4.92</v>
+        <v>-4.22</v>
       </c>
       <c r="N17">
-        <v>5.72</v>
+        <v>5.81</v>
       </c>
       <c r="O17">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q17">
-        <v>31027.99</v>
+        <v>30928.86</v>
       </c>
       <c r="R17">
-        <v>31323.85</v>
+        <v>31286.02</v>
       </c>
       <c r="S17">
-        <v>30966.77</v>
+        <v>30990.87</v>
       </c>
       <c r="T17">
-        <v>31794.79</v>
+        <v>31779.8</v>
       </c>
       <c r="U17">
-        <v>-3.26</v>
+        <v>-3.45</v>
       </c>
       <c r="V17" t="b">
         <v>1</v>
@@ -2819,34 +2810,34 @@
         <v>1</v>
       </c>
       <c r="Z17">
-        <v>37.55</v>
+        <v>35.87</v>
       </c>
       <c r="AA17">
-        <v>-12.22</v>
+        <v>-49.37</v>
       </c>
       <c r="AB17">
-        <v>87.34999999999999</v>
+        <v>60</v>
       </c>
       <c r="AC17">
-        <v>-99.56999999999999</v>
+        <v>-109.38</v>
       </c>
       <c r="AD17">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.46</v>
+        <v>0.97</v>
       </c>
       <c r="AF17">
-        <v>278.66</v>
+        <v>274.34</v>
       </c>
       <c r="AG17">
         <v>-100</v>
       </c>
       <c r="AH17">
-        <v>31791.6</v>
+        <v>31830.48</v>
       </c>
       <c r="AI17">
-        <v>30856.1</v>
+        <v>30741.56</v>
       </c>
       <c r="AJ17">
         <v>30549.87</v>
@@ -2855,7 +2846,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>35.2</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2869,10 +2860,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16463.7</v>
+        <v>16412.8</v>
       </c>
       <c r="E18">
-        <v>0.21</v>
+        <v>-0.31</v>
       </c>
       <c r="F18">
         <v>16783.35</v>
@@ -2881,25 +2872,25 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-1.9</v>
+        <v>-2.21</v>
       </c>
       <c r="I18">
-        <v>6.89</v>
+        <v>6.55</v>
       </c>
       <c r="J18">
-        <v>-1.44</v>
+        <v>-1.32</v>
       </c>
       <c r="K18">
-        <v>-0.16</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N18">
-        <v>36.43</v>
+        <v>33.57</v>
       </c>
       <c r="Q18">
-        <v>16522.51</v>
+        <v>16478.6</v>
       </c>
       <c r="R18">
-        <v>16581.95</v>
+        <v>16585.04</v>
       </c>
       <c r="X18" t="s">
         <v>80</v>
@@ -2908,31 +2899,31 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>48.3</v>
+        <v>45.62</v>
       </c>
       <c r="AA18">
-        <v>66.98</v>
+        <v>49.64</v>
       </c>
       <c r="AB18">
-        <v>119.37</v>
+        <v>105.42</v>
       </c>
       <c r="AC18">
-        <v>-52.39</v>
+        <v>-55.78</v>
       </c>
       <c r="AD18">
         <v>2.98</v>
       </c>
       <c r="AE18">
-        <v>4.83</v>
+        <v>1.99</v>
       </c>
       <c r="AF18">
-        <v>173.35</v>
+        <v>170.75</v>
       </c>
       <c r="AH18">
-        <v>16911.21</v>
+        <v>16906.23</v>
       </c>
       <c r="AI18">
-        <v>16252.69</v>
+        <v>16263.86</v>
       </c>
       <c r="AJ18">
         <v>16199.38</v>
@@ -2941,7 +2932,7 @@
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>18.23</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2955,10 +2946,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9968.25</v>
+        <v>9819.450000000001</v>
       </c>
       <c r="E19">
-        <v>1.29</v>
+        <v>-1.49</v>
       </c>
       <c r="F19">
         <v>9968.25</v>
@@ -2967,25 +2958,25 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>-1.49</v>
       </c>
       <c r="I19">
-        <v>10.82</v>
+        <v>9.16</v>
       </c>
       <c r="J19">
-        <v>3.91</v>
+        <v>1.64</v>
       </c>
       <c r="K19">
-        <v>6.45</v>
+        <v>4.07</v>
       </c>
       <c r="N19">
-        <v>75.04000000000001</v>
+        <v>60.13</v>
       </c>
       <c r="Q19">
-        <v>9818.6</v>
+        <v>9850.35</v>
       </c>
       <c r="R19">
-        <v>9525.700000000001</v>
+        <v>9545.559999999999</v>
       </c>
       <c r="X19" t="s">
         <v>80</v>
@@ -2994,31 +2985,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>71.09999999999999</v>
+        <v>61.77</v>
       </c>
       <c r="AA19">
-        <v>133.6</v>
+        <v>133.82</v>
       </c>
       <c r="AB19">
-        <v>86.23</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="AC19">
-        <v>47.37</v>
+        <v>38.07</v>
       </c>
       <c r="AD19">
-        <v>99.52</v>
+        <v>85.41</v>
       </c>
       <c r="AE19">
-        <v>96.76000000000001</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="AF19">
-        <v>146.7</v>
+        <v>149.43</v>
       </c>
       <c r="AH19">
-        <v>9985.18</v>
+        <v>10020.29</v>
       </c>
       <c r="AI19">
-        <v>9066.23</v>
+        <v>9070.82</v>
       </c>
       <c r="AJ19">
         <v>9466.209999999999</v>
@@ -3027,7 +3018,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>32.27</v>
+        <v>33.08</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3041,10 +3032,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11231.15</v>
+        <v>11176.9</v>
       </c>
       <c r="E20">
-        <v>0.2</v>
+        <v>-0.48</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3053,25 +3044,25 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-1.21</v>
+        <v>-1.69</v>
       </c>
       <c r="I20">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="J20">
-        <v>-0.43</v>
+        <v>-1.04</v>
       </c>
       <c r="K20">
-        <v>-1.21</v>
+        <v>-1.19</v>
       </c>
       <c r="N20">
-        <v>11.32</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q20">
-        <v>11237.23</v>
+        <v>11213.83</v>
       </c>
       <c r="R20">
-        <v>11209.97</v>
+        <v>11206.65</v>
       </c>
       <c r="X20" t="s">
         <v>80</v>
@@ -3080,31 +3071,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>51.5</v>
+        <v>47.33</v>
       </c>
       <c r="AA20">
-        <v>21.97</v>
+        <v>15.6</v>
       </c>
       <c r="AB20">
-        <v>27.97</v>
+        <v>25.49</v>
       </c>
       <c r="AC20">
-        <v>-5.99</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="AD20">
-        <v>24.43</v>
+        <v>15.68</v>
       </c>
       <c r="AE20">
-        <v>35.18</v>
+        <v>24.69</v>
       </c>
       <c r="AF20">
-        <v>123.99</v>
+        <v>124.46</v>
       </c>
       <c r="AH20">
-        <v>11386.5</v>
+        <v>11383.05</v>
       </c>
       <c r="AI20">
-        <v>11033.43</v>
+        <v>11030.26</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3113,7 +3104,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>12.64</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3127,10 +3118,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27247.9</v>
+        <v>27207.7</v>
       </c>
       <c r="E21">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3139,43 +3130,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.65</v>
+        <v>-6.78</v>
       </c>
       <c r="I21">
-        <v>12.85</v>
+        <v>12.69</v>
       </c>
       <c r="J21">
-        <v>-0.48</v>
+        <v>-0.73</v>
       </c>
       <c r="K21">
-        <v>-4.42</v>
+        <v>-4.56</v>
       </c>
       <c r="L21">
-        <v>4.94</v>
+        <v>4.53</v>
       </c>
       <c r="M21">
-        <v>1.29</v>
+        <v>2.42</v>
       </c>
       <c r="N21">
-        <v>8.19</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="O21">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q21">
-        <v>27295.03</v>
+        <v>27254.89</v>
       </c>
       <c r="R21">
-        <v>27810.03</v>
+        <v>27744.99</v>
       </c>
       <c r="S21">
-        <v>27882.09</v>
+        <v>27895.25</v>
       </c>
       <c r="T21">
-        <v>27664.59</v>
+        <v>27658.57</v>
       </c>
       <c r="U21">
-        <v>-1.51</v>
+        <v>-1.63</v>
       </c>
       <c r="V21" t="b">
         <v>0</v>
@@ -3190,40 +3181,40 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>38.28</v>
+        <v>37.49</v>
       </c>
       <c r="AA21">
-        <v>-193.4</v>
+        <v>-201.92</v>
       </c>
       <c r="AB21">
-        <v>-112.59</v>
+        <v>-130.46</v>
       </c>
       <c r="AC21">
-        <v>-80.81</v>
+        <v>-71.45999999999999</v>
       </c>
       <c r="AD21">
         <v>4.23</v>
       </c>
       <c r="AE21">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="AF21">
-        <v>365.55</v>
+        <v>354.95</v>
       </c>
       <c r="AH21">
-        <v>28831.47</v>
+        <v>28744.59</v>
       </c>
       <c r="AI21">
-        <v>26788.58</v>
+        <v>26745.38</v>
       </c>
       <c r="AJ21">
-        <v>28369.85</v>
+        <v>28265.67</v>
       </c>
       <c r="AK21" t="s">
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>23.95</v>
+        <v>24.02</v>
       </c>
     </row>
   </sheetData>
@@ -3364,7 +3355,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3404,7 +3395,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3443,1078 +3434,1069 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>102</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>89</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="6" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>80</v>
+      <c r="D9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>7.99</v>
+      </c>
+      <c r="D10" s="8">
+        <v>7.7</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="A11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>-0.17</v>
+      </c>
+      <c r="D11" s="8">
+        <v>-0.78</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-0.61</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>115</v>
+      <c r="A12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8">
+        <v>2.56</v>
+      </c>
+      <c r="D12" s="8">
+        <v>2.41</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="8">
-        <v>9.119999999999999</v>
+        <v>-1.78</v>
       </c>
       <c r="D13" s="8">
-        <v>7.99</v>
+        <v>-2.93</v>
       </c>
       <c r="E13" s="9">
-        <v>-1.13</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="8">
-        <v>0.05</v>
+        <v>-2.08</v>
       </c>
       <c r="D14" s="8">
-        <v>-0.17</v>
+        <v>-2.62</v>
       </c>
       <c r="E14" s="9">
-        <v>-0.22</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="8">
-        <v>4.14</v>
+        <v>-2.96</v>
       </c>
       <c r="D15" s="8">
-        <v>2.56</v>
+        <v>-3.31</v>
       </c>
       <c r="E15" s="9">
-        <v>-1.58</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="8">
-        <v>-2.01</v>
+        <v>3.61</v>
       </c>
       <c r="D16" s="8">
-        <v>-1.78</v>
+        <v>5</v>
       </c>
       <c r="E16" s="10">
-        <v>0.23</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="8">
-        <v>0.43</v>
+        <v>3.47</v>
       </c>
       <c r="D17" s="8">
-        <v>-2.08</v>
+        <v>2.49</v>
       </c>
       <c r="E17" s="9">
-        <v>-2.51</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="8">
-        <v>-1.29</v>
+        <v>-0.01</v>
       </c>
       <c r="D18" s="8">
-        <v>-2.96</v>
+        <v>-0.77</v>
       </c>
       <c r="E18" s="9">
-        <v>-1.67</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="8">
-        <v>9.17</v>
+        <v>5.31</v>
       </c>
       <c r="D19" s="8">
-        <v>3.61</v>
+        <v>4.35</v>
       </c>
       <c r="E19" s="9">
-        <v>-5.56</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="8">
-        <v>3.71</v>
+        <v>4.73</v>
       </c>
       <c r="D20" s="8">
-        <v>3.47</v>
+        <v>4.71</v>
       </c>
       <c r="E20" s="9">
-        <v>-0.24</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="8">
-        <v>0.9399999999999999</v>
+        <v>-1.01</v>
       </c>
       <c r="D21" s="8">
-        <v>-0.01</v>
+        <v>-1.89</v>
       </c>
       <c r="E21" s="9">
-        <v>-0.95</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="8">
-        <v>4.52</v>
+        <v>2.82</v>
       </c>
       <c r="D22" s="8">
-        <v>5.31</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0.79</v>
+        <v>2.81</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="8">
-        <v>3.57</v>
+        <v>1.38</v>
       </c>
       <c r="D23" s="8">
-        <v>4.73</v>
-      </c>
-      <c r="E23" s="10">
-        <v>1.16</v>
+        <v>0.85</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="8">
-        <v>-0.67</v>
+        <v>-2.49</v>
       </c>
       <c r="D24" s="8">
-        <v>-1.01</v>
+        <v>-2.54</v>
       </c>
       <c r="E24" s="9">
-        <v>-0.34</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="8">
-        <v>4.68</v>
+        <v>-2.16</v>
       </c>
       <c r="D25" s="8">
-        <v>2.82</v>
+        <v>-2.41</v>
       </c>
       <c r="E25" s="9">
-        <v>-1.86</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="8">
-        <v>1.68</v>
+        <v>-0.16</v>
       </c>
       <c r="D26" s="8">
-        <v>1.38</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E26" s="9">
-        <v>-0.3</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="8">
-        <v>-1.16</v>
+        <v>6.45</v>
       </c>
       <c r="D27" s="8">
-        <v>-2.49</v>
+        <v>4.07</v>
       </c>
       <c r="E27" s="9">
-        <v>-1.33</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="8">
-        <v>0.1</v>
+        <v>-1.21</v>
       </c>
       <c r="D28" s="8">
-        <v>-2.16</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-2.26</v>
+        <v>-1.19</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0.02</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="8">
-        <v>0.07000000000000001</v>
+        <v>-4.42</v>
       </c>
       <c r="D29" s="8">
-        <v>-0.16</v>
+        <v>-4.56</v>
       </c>
       <c r="E29" s="9">
-        <v>-0.23</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="8">
-        <v>5.66</v>
+        <v>-0.66</v>
       </c>
       <c r="D30" s="8">
-        <v>6.45</v>
+        <v>-0.61</v>
       </c>
       <c r="E30" s="10">
-        <v>0.79</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="8">
-        <v>0.11</v>
+        <v>-1.13</v>
       </c>
       <c r="D31" s="8">
-        <v>-1.21</v>
+        <v>-1.66</v>
       </c>
       <c r="E31" s="9">
-        <v>-1.32</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="8">
-        <v>-2.39</v>
+        <v>-1.22</v>
       </c>
       <c r="D32" s="8">
-        <v>-4.42</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-2.03</v>
+        <v>-0.87</v>
+      </c>
+      <c r="E32" s="10">
+        <v>0.35</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="8">
-        <v>-1.48</v>
+        <v>-0.33</v>
       </c>
       <c r="D33" s="8">
-        <v>-0.66</v>
-      </c>
-      <c r="E33" s="10">
-        <v>0.82</v>
+        <v>-1.68</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="8">
-        <v>-1.69</v>
+        <v>-2.16</v>
       </c>
       <c r="D34" s="8">
-        <v>-1.13</v>
+        <v>-1.97</v>
       </c>
       <c r="E34" s="10">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="8">
-        <v>-0.45</v>
+        <v>-1.23</v>
       </c>
       <c r="D35" s="8">
-        <v>-1.22</v>
+        <v>-1.57</v>
       </c>
       <c r="E35" s="9">
-        <v>-0.77</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="8">
-        <v>-0.5</v>
+        <v>-5.06</v>
       </c>
       <c r="D36" s="8">
-        <v>-0.33</v>
+        <v>-2.87</v>
       </c>
       <c r="E36" s="10">
-        <v>0.17</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="8">
-        <v>-1.66</v>
+        <v>-0.33</v>
       </c>
       <c r="D37" s="8">
-        <v>-2.16</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E37" s="9">
-        <v>-0.5</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="8">
-        <v>-0.95</v>
+        <v>-0.08</v>
       </c>
       <c r="D38" s="8">
-        <v>-1.23</v>
+        <v>-1.11</v>
       </c>
       <c r="E38" s="9">
-        <v>-0.28</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="8">
-        <v>-0.6</v>
+        <v>3.18</v>
       </c>
       <c r="D39" s="8">
-        <v>-5.06</v>
+        <v>1.18</v>
       </c>
       <c r="E39" s="9">
-        <v>-4.46</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="8">
-        <v>-0.7</v>
+        <v>-0.58</v>
       </c>
       <c r="D40" s="8">
-        <v>-0.33</v>
-      </c>
-      <c r="E40" s="10">
-        <v>0.37</v>
+        <v>-1.13</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="8">
-        <v>-0.89</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D41" s="8">
-        <v>-0.08</v>
-      </c>
-      <c r="E41" s="10">
-        <v>0.8100000000000001</v>
+        <v>-1.2</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="8">
-        <v>2.26</v>
+        <v>-0.25</v>
       </c>
       <c r="D42" s="8">
-        <v>3.18</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0.92</v>
+        <v>-2.27</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="8">
-        <v>-1.88</v>
+        <v>-1.45</v>
       </c>
       <c r="D43" s="8">
-        <v>-0.58</v>
-      </c>
-      <c r="E43" s="10">
-        <v>1.3</v>
+        <v>-1.68</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="8">
-        <v>-0.78</v>
+        <v>0.75</v>
       </c>
       <c r="D44" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E44" s="10">
-        <v>0.85</v>
+        <v>0.62</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="8">
-        <v>-0.54</v>
+        <v>-1.49</v>
       </c>
       <c r="D45" s="8">
-        <v>-0.25</v>
-      </c>
-      <c r="E45" s="10">
-        <v>0.29</v>
+        <v>-1.59</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="8">
-        <v>-0.36</v>
+        <v>-1.44</v>
       </c>
       <c r="D46" s="8">
-        <v>-1.45</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-1.09</v>
+        <v>-1.32</v>
+      </c>
+      <c r="E46" s="10">
+        <v>0.12</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="8">
-        <v>1.09</v>
+        <v>3.91</v>
       </c>
       <c r="D47" s="8">
-        <v>0.75</v>
+        <v>1.64</v>
       </c>
       <c r="E47" s="9">
-        <v>-0.34</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>-0.44</v>
+        <v>-0.43</v>
       </c>
       <c r="D48" s="8">
-        <v>-1.49</v>
+        <v>-1.04</v>
       </c>
       <c r="E48" s="9">
-        <v>-1.05</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="8">
-        <v>-1.22</v>
+        <v>-0.48</v>
       </c>
       <c r="D49" s="8">
-        <v>-1.44</v>
+        <v>-0.73</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.22</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="8">
-        <v>0.82</v>
+        <v>22.92</v>
       </c>
       <c r="D50" s="8">
-        <v>3.91</v>
+        <v>24.33</v>
       </c>
       <c r="E50" s="10">
-        <v>3.09</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="8">
-        <v>-0.99</v>
+        <v>12.71</v>
       </c>
       <c r="D51" s="8">
-        <v>-0.43</v>
+        <v>12.92</v>
       </c>
       <c r="E51" s="10">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" s="8">
-        <v>-0.53</v>
+        <v>1.97</v>
       </c>
       <c r="D52" s="8">
-        <v>-0.48</v>
+        <v>2.92</v>
       </c>
       <c r="E52" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="8">
-        <v>22.33</v>
+        <v>11.46</v>
       </c>
       <c r="D53" s="8">
-        <v>22.92</v>
-      </c>
-      <c r="E53" s="10">
-        <v>0.59</v>
+        <v>10.85</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="8">
-        <v>12.28</v>
+        <v>-13.68</v>
       </c>
       <c r="D54" s="8">
-        <v>12.71</v>
+        <v>-13.53</v>
       </c>
       <c r="E54" s="10">
-        <v>0.43</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="8">
-        <v>2.99</v>
+        <v>-1.12</v>
       </c>
       <c r="D55" s="8">
-        <v>1.97</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-1.02</v>
+        <v>-0.59</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.53</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="8">
-        <v>10.42</v>
+        <v>-13</v>
       </c>
       <c r="D56" s="8">
-        <v>11.46</v>
+        <v>-11.53</v>
       </c>
       <c r="E56" s="10">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="8">
-        <v>-12.77</v>
+        <v>4.23</v>
       </c>
       <c r="D57" s="8">
-        <v>-13.68</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.91</v>
+        <v>4.8</v>
+      </c>
+      <c r="E57" s="10">
+        <v>0.57</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="8">
-        <v>-0.61</v>
+        <v>-2.11</v>
       </c>
       <c r="D58" s="8">
-        <v>-1.12</v>
+        <v>-2.9</v>
       </c>
       <c r="E58" s="9">
-        <v>-0.51</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="8">
-        <v>-10.49</v>
+        <v>39.9</v>
       </c>
       <c r="D59" s="8">
-        <v>-13</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-2.51</v>
+        <v>42.38</v>
+      </c>
+      <c r="E59" s="10">
+        <v>2.48</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="8">
-        <v>4.16</v>
+        <v>3.12</v>
       </c>
       <c r="D60" s="8">
-        <v>4.23</v>
-      </c>
-      <c r="E60" s="10">
-        <v>0.07000000000000001</v>
+        <v>2.32</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="8">
-        <v>-3.05</v>
+        <v>24.74</v>
       </c>
       <c r="D61" s="8">
-        <v>-2.11</v>
+        <v>25.23</v>
       </c>
       <c r="E61" s="10">
-        <v>0.9399999999999999</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="8">
-        <v>38.62</v>
+        <v>21.57</v>
       </c>
       <c r="D62" s="8">
-        <v>39.9</v>
+        <v>22.95</v>
       </c>
       <c r="E62" s="10">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="8">
-        <v>2.3</v>
+        <v>0.31</v>
       </c>
       <c r="D63" s="8">
-        <v>3.12</v>
+        <v>2.43</v>
       </c>
       <c r="E63" s="10">
-        <v>0.82</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="8">
-        <v>27.6</v>
+        <v>-4.92</v>
       </c>
       <c r="D64" s="8">
-        <v>24.74</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-2.86</v>
+        <v>-4.22</v>
+      </c>
+      <c r="E64" s="10">
+        <v>0.7</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="8">
-        <v>20.37</v>
+        <v>1.29</v>
       </c>
       <c r="D65" s="8">
-        <v>21.57</v>
+        <v>2.42</v>
       </c>
       <c r="E65" s="10">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" s="8">
-        <v>-1.34</v>
+        <v>13.88</v>
       </c>
       <c r="D66" s="8">
-        <v>0.31</v>
-      </c>
-      <c r="E66" s="10">
-        <v>1.65</v>
+        <v>12.62</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="8">
-        <v>-3.96</v>
+        <v>-3.15</v>
       </c>
       <c r="D67" s="8">
-        <v>-4.92</v>
+        <v>-4.38</v>
       </c>
       <c r="E67" s="9">
-        <v>-0.96</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" s="8">
-        <v>1.39</v>
+        <v>6.06</v>
       </c>
       <c r="D68" s="8">
-        <v>1.29</v>
+        <v>5.96</v>
       </c>
       <c r="E68" s="9">
         <v>-0.1</v>
@@ -4522,1470 +4504,1368 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="8">
-        <v>12.03</v>
+        <v>-2.5</v>
       </c>
       <c r="D69" s="8">
-        <v>13.88</v>
-      </c>
-      <c r="E69" s="10">
-        <v>1.85</v>
+        <v>-5.06</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="8">
-        <v>-3.75</v>
+        <v>-6.19</v>
       </c>
       <c r="D70" s="8">
-        <v>-3.15</v>
+        <v>-6.03</v>
       </c>
       <c r="E70" s="10">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="8">
-        <v>6.68</v>
+        <v>3.26</v>
       </c>
       <c r="D71" s="8">
-        <v>6.06</v>
+        <v>2.84</v>
       </c>
       <c r="E71" s="9">
-        <v>-0.62</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="8">
-        <v>-3.17</v>
+        <v>3.09</v>
       </c>
       <c r="D72" s="8">
-        <v>-2.5</v>
+        <v>4.28</v>
       </c>
       <c r="E72" s="10">
-        <v>0.67</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="8">
-        <v>-4.77</v>
+        <v>1.08</v>
       </c>
       <c r="D73" s="8">
-        <v>-6.19</v>
+        <v>-0.53</v>
       </c>
       <c r="E73" s="9">
-        <v>-1.42</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="8">
-        <v>3.43</v>
+        <v>12.78</v>
       </c>
       <c r="D74" s="8">
-        <v>3.26</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-0.17</v>
+        <v>13.4</v>
+      </c>
+      <c r="E74" s="10">
+        <v>0.62</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="8">
-        <v>13.14</v>
+        <v>-1.05</v>
       </c>
       <c r="D75" s="8">
-        <v>3.09</v>
+        <v>-1.24</v>
       </c>
       <c r="E75" s="9">
-        <v>-10.05</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="8">
-        <v>0.98</v>
+        <v>-5</v>
       </c>
       <c r="D76" s="8">
-        <v>1.08</v>
-      </c>
-      <c r="E76" s="10">
-        <v>0.1</v>
+        <v>-6.11</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="8">
-        <v>10.72</v>
+        <v>8.59</v>
       </c>
       <c r="D77" s="8">
-        <v>12.78</v>
-      </c>
-      <c r="E77" s="10">
-        <v>2.06</v>
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="8">
-        <v>-2.7</v>
+        <v>6.01</v>
       </c>
       <c r="D78" s="8">
-        <v>-1.05</v>
-      </c>
-      <c r="E78" s="10">
-        <v>1.65</v>
+        <v>5.92</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="8">
-        <v>-6.11</v>
+        <v>17.45</v>
       </c>
       <c r="D79" s="8">
-        <v>-5</v>
-      </c>
-      <c r="E79" s="10">
-        <v>1.11</v>
+        <v>16.73</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="8">
-        <v>8.859999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="D80" s="8">
-        <v>8.59</v>
+        <v>2.9</v>
       </c>
       <c r="E80" s="9">
-        <v>-0.27</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="8">
-        <v>7.35</v>
+        <v>4.94</v>
       </c>
       <c r="D81" s="8">
-        <v>6.01</v>
+        <v>4.53</v>
       </c>
       <c r="E81" s="9">
-        <v>-1.34</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C82" s="8">
-        <v>18.43</v>
+        <v>-1.29</v>
       </c>
       <c r="D82" s="8">
-        <v>17.45</v>
+        <v>-1.56</v>
       </c>
       <c r="E82" s="9">
-        <v>-0.98</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C83" s="8">
-        <v>4.8</v>
+        <v>-6.55</v>
       </c>
       <c r="D83" s="8">
-        <v>3.05</v>
+        <v>-7.12</v>
       </c>
       <c r="E83" s="9">
-        <v>-1.75</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C84" s="8">
-        <v>4.4</v>
+        <v>-5.02</v>
       </c>
       <c r="D84" s="8">
-        <v>4.94</v>
-      </c>
-      <c r="E84" s="10">
-        <v>0.54</v>
+        <v>-5.16</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="8">
-        <v>-1.48</v>
+        <v>-7.12</v>
       </c>
       <c r="D85" s="8">
-        <v>-1.29</v>
-      </c>
-      <c r="E85" s="10">
-        <v>0.19</v>
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="8">
-        <v>-6.48</v>
+        <v>-16.41</v>
       </c>
       <c r="D86" s="8">
-        <v>-6.55</v>
+        <v>-16.86</v>
       </c>
       <c r="E86" s="9">
-        <v>-0.07000000000000001</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="8">
-        <v>-3.93</v>
+        <v>-8.27</v>
       </c>
       <c r="D87" s="8">
-        <v>-5.02</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="E87" s="9">
-        <v>-1.09</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="8">
-        <v>-7.18</v>
+        <v>-23.49</v>
       </c>
       <c r="D88" s="8">
-        <v>-7.12</v>
+        <v>-22.93</v>
       </c>
       <c r="E88" s="10">
-        <v>0.06</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="8">
-        <v>-14.87</v>
+        <v>-0.65</v>
       </c>
       <c r="D89" s="8">
-        <v>-16.41</v>
+        <v>-1.13</v>
       </c>
       <c r="E89" s="9">
-        <v>-1.54</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="8">
-        <v>-7.9</v>
+        <v>-3.99</v>
       </c>
       <c r="D90" s="8">
-        <v>-8.27</v>
+        <v>-4.71</v>
       </c>
       <c r="E90" s="9">
-        <v>-0.37</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="8">
-        <v>-20.59</v>
+        <v>-4.15</v>
       </c>
       <c r="D91" s="8">
-        <v>-23.49</v>
+        <v>-5.02</v>
       </c>
       <c r="E91" s="9">
-        <v>-2.9</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="8">
-        <v>-0.7</v>
+        <v>-5.05</v>
       </c>
       <c r="D92" s="8">
-        <v>-0.65</v>
-      </c>
-      <c r="E92" s="10">
-        <v>0.05</v>
+        <v>-5.07</v>
+      </c>
+      <c r="E92" s="9">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="8">
-        <v>-3.55</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="D93" s="8">
-        <v>-3.99</v>
+        <v>-9.43</v>
       </c>
       <c r="E93" s="9">
-        <v>-0.44</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="8">
-        <v>-4.87</v>
+        <v>-12.77</v>
       </c>
       <c r="D94" s="8">
-        <v>-4.15</v>
-      </c>
-      <c r="E94" s="10">
-        <v>0.72</v>
+        <v>-12.78</v>
+      </c>
+      <c r="E94" s="9">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="8">
-        <v>-5.66</v>
+        <v>-1.5</v>
       </c>
       <c r="D95" s="8">
-        <v>-5.05</v>
-      </c>
-      <c r="E95" s="10">
-        <v>0.61</v>
+        <v>-1.68</v>
+      </c>
+      <c r="E95" s="9">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="8">
-        <v>-8.56</v>
+        <v>-7.52</v>
       </c>
       <c r="D96" s="8">
-        <v>-8.619999999999999</v>
+        <v>-7.57</v>
       </c>
       <c r="E96" s="9">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="8">
-        <v>-11.55</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="D97" s="8">
-        <v>-12.77</v>
+        <v>-10.02</v>
       </c>
       <c r="E97" s="9">
-        <v>-1.22</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="8">
-        <v>-1.18</v>
+        <v>-1.9</v>
       </c>
       <c r="D98" s="8">
-        <v>-1.5</v>
+        <v>-2.21</v>
       </c>
       <c r="E98" s="9">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="8">
-        <v>-7.54</v>
+        <v>0</v>
       </c>
       <c r="D99" s="8">
-        <v>-7.52</v>
-      </c>
-      <c r="E99" s="10">
-        <v>0.02</v>
+        <v>-1.49</v>
+      </c>
+      <c r="E99" s="9">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="8">
-        <v>-8.720000000000001</v>
+        <v>-1.21</v>
       </c>
       <c r="D100" s="8">
-        <v>-9.800000000000001</v>
+        <v>-1.69</v>
       </c>
       <c r="E100" s="9">
-        <v>-1.08</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="8">
-        <v>-1.66</v>
+        <v>-6.65</v>
       </c>
       <c r="D101" s="8">
-        <v>-1.9</v>
+        <v>-6.78</v>
       </c>
       <c r="E101" s="9">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C102" s="8">
-        <v>-1.49</v>
+        <v>29264.55</v>
       </c>
       <c r="D102" s="8">
-        <v>-1.21</v>
-      </c>
-      <c r="E102" s="10">
-        <v>0.28</v>
+        <v>29185.4</v>
+      </c>
+      <c r="E102" s="9">
+        <v>-79.15000000000001</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C103" s="8">
-        <v>29207.9</v>
+        <v>9814.950000000001</v>
       </c>
       <c r="D103" s="8">
-        <v>29264.55</v>
-      </c>
-      <c r="E103" s="10">
-        <v>56.65</v>
+        <v>9755.15</v>
+      </c>
+      <c r="E103" s="9">
+        <v>-59.8</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C104" s="8">
-        <v>9822.75</v>
+        <v>12004.7</v>
       </c>
       <c r="D104" s="8">
-        <v>9814.950000000001</v>
+        <v>11986.85</v>
       </c>
       <c r="E104" s="9">
-        <v>-7.8</v>
+        <v>-17.85</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="8">
-        <v>12142.85</v>
+        <v>38578.85</v>
       </c>
       <c r="D105" s="8">
-        <v>12004.7</v>
+        <v>38124.45</v>
       </c>
       <c r="E105" s="9">
-        <v>-138.15</v>
+        <v>-454.4</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="8">
-        <v>38554.2</v>
+        <v>47734.8</v>
       </c>
       <c r="D106" s="8">
-        <v>38578.85</v>
-      </c>
-      <c r="E106" s="10">
-        <v>24.65</v>
+        <v>47473.9</v>
+      </c>
+      <c r="E106" s="9">
+        <v>-260.9</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="8">
-        <v>48615.05</v>
+        <v>26108</v>
       </c>
       <c r="D107" s="8">
-        <v>47734.8</v>
+        <v>26013</v>
       </c>
       <c r="E107" s="9">
-        <v>-880.25</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="8">
-        <v>26213.65</v>
+        <v>30213.45</v>
       </c>
       <c r="D108" s="8">
-        <v>26108</v>
-      </c>
-      <c r="E108" s="9">
-        <v>-105.65</v>
+        <v>30433.05</v>
+      </c>
+      <c r="E108" s="10">
+        <v>219.6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="8">
-        <v>31357.75</v>
+        <v>16553.4</v>
       </c>
       <c r="D109" s="8">
-        <v>30213.45</v>
+        <v>16474.4</v>
       </c>
       <c r="E109" s="9">
-        <v>-1144.3</v>
+        <v>-79</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="8">
-        <v>16545.3</v>
+        <v>9376.549999999999</v>
       </c>
       <c r="D110" s="8">
-        <v>16553.4</v>
-      </c>
-      <c r="E110" s="10">
-        <v>8.1</v>
+        <v>9305.549999999999</v>
+      </c>
+      <c r="E110" s="9">
+        <v>-71</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="8">
-        <v>9419.1</v>
+        <v>1602.2</v>
       </c>
       <c r="D111" s="8">
-        <v>9376.549999999999</v>
+        <v>1587.65</v>
       </c>
       <c r="E111" s="9">
-        <v>-42.55</v>
+        <v>-14.55</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="8">
-        <v>1590.1</v>
+        <v>13025.3</v>
       </c>
       <c r="D112" s="8">
-        <v>1602.2</v>
-      </c>
-      <c r="E112" s="10">
-        <v>12.1</v>
+        <v>13023.25</v>
+      </c>
+      <c r="E112" s="9">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="8">
-        <v>12941.7</v>
+        <v>9838.5</v>
       </c>
       <c r="D113" s="8">
-        <v>13025.3</v>
-      </c>
-      <c r="E113" s="10">
-        <v>83.59999999999999</v>
+        <v>9750.85</v>
+      </c>
+      <c r="E113" s="9">
+        <v>-87.65000000000001</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="8">
-        <v>9844.950000000001</v>
+        <v>8618.5</v>
       </c>
       <c r="D114" s="8">
-        <v>9838.5</v>
+        <v>8617.65</v>
       </c>
       <c r="E114" s="9">
-        <v>-6.45</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="8">
-        <v>8738.799999999999</v>
+        <v>26361.9</v>
       </c>
       <c r="D115" s="8">
-        <v>8618.5</v>
+        <v>26313.8</v>
       </c>
       <c r="E115" s="9">
-        <v>-120.3</v>
+        <v>-48.1</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="8">
-        <v>26445.55</v>
+        <v>895.8</v>
       </c>
       <c r="D116" s="8">
-        <v>26361.9</v>
+        <v>895.35</v>
       </c>
       <c r="E116" s="9">
-        <v>-83.65000000000001</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="8">
-        <v>895.65</v>
+        <v>30759.75</v>
       </c>
       <c r="D117" s="8">
-        <v>895.8</v>
-      </c>
-      <c r="E117" s="10">
-        <v>0.15</v>
+        <v>30682.9</v>
+      </c>
+      <c r="E117" s="9">
+        <v>-76.84999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="8">
-        <v>31128.25</v>
+        <v>16463.7</v>
       </c>
       <c r="D118" s="8">
-        <v>30759.75</v>
+        <v>16412.8</v>
       </c>
       <c r="E118" s="9">
-        <v>-368.5</v>
+        <v>-50.9</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="8">
-        <v>16505.3</v>
+        <v>9968.25</v>
       </c>
       <c r="D119" s="8">
-        <v>16463.7</v>
+        <v>9819.450000000001</v>
       </c>
       <c r="E119" s="9">
-        <v>-41.6</v>
+        <v>-148.8</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="8">
-        <v>9811.75</v>
+        <v>11231.15</v>
       </c>
       <c r="D120" s="8">
-        <v>9968.25</v>
-      </c>
-      <c r="E120" s="10">
-        <v>156.5</v>
+        <v>11176.9</v>
+      </c>
+      <c r="E120" s="9">
+        <v>-54.25</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="8">
-        <v>11200.05</v>
+        <v>27247.9</v>
       </c>
       <c r="D121" s="8">
-        <v>11231.15</v>
-      </c>
-      <c r="E121" s="10">
-        <v>31.1</v>
+        <v>27207.7</v>
+      </c>
+      <c r="E121" s="9">
+        <v>-40.2</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C122" s="8">
-        <v>27247.25</v>
+        <v>62</v>
       </c>
       <c r="D122" s="8">
-        <v>27247.9</v>
-      </c>
-      <c r="E122" s="10">
-        <v>0.65</v>
+        <v>56</v>
+      </c>
+      <c r="E122" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C123" s="8">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="D123" s="8">
-        <v>93</v>
-      </c>
-      <c r="E123" s="9">
-        <v>-6</v>
+        <v>62</v>
+      </c>
+      <c r="E123" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C124" s="8">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D124" s="8">
-        <v>62</v>
-      </c>
-      <c r="E124" s="10">
-        <v>6</v>
+        <v>44</v>
+      </c>
+      <c r="E124" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C125" s="8">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D125" s="8">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E125" s="9">
-        <v>-12</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="8">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D126" s="8">
-        <v>50</v>
-      </c>
-      <c r="E126" s="10">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="E126" s="9">
+        <v>-7</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="8">
+        <v>19</v>
+      </c>
+      <c r="D127" s="8">
         <v>26</v>
       </c>
-      <c r="D127" s="8">
-        <v>32</v>
-      </c>
       <c r="E127" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="8">
+        <v>38</v>
+      </c>
+      <c r="D128" s="8">
         <v>50</v>
       </c>
-      <c r="D128" s="8">
-        <v>13</v>
-      </c>
-      <c r="E128" s="9">
-        <v>-37</v>
+      <c r="E128" s="10">
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C129" s="8">
-        <v>38</v>
+        <v>66.84</v>
       </c>
       <c r="D129" s="8">
-        <v>44</v>
-      </c>
-      <c r="E129" s="10">
-        <v>6</v>
+        <v>64.81</v>
+      </c>
+      <c r="E129" s="9">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C130" s="8">
-        <v>62</v>
+        <v>42.34</v>
       </c>
       <c r="D130" s="8">
-        <v>68</v>
-      </c>
-      <c r="E130" s="10">
-        <v>6</v>
+        <v>37.93</v>
+      </c>
+      <c r="E130" s="9">
+        <v>-4.41</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C131" s="8">
-        <v>87</v>
+        <v>53.05</v>
       </c>
       <c r="D131" s="8">
-        <v>99</v>
-      </c>
-      <c r="E131" s="10">
-        <v>12</v>
+        <v>51.77</v>
+      </c>
+      <c r="E131" s="9">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C132" s="8">
-        <v>13</v>
+        <v>39.49</v>
       </c>
       <c r="D132" s="8">
-        <v>26</v>
-      </c>
-      <c r="E132" s="10">
-        <v>13</v>
+        <v>31.28</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-8.210000000000001</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C133" s="8">
-        <v>93</v>
+        <v>34.93</v>
       </c>
       <c r="D133" s="8">
-        <v>87</v>
+        <v>32.74</v>
       </c>
       <c r="E133" s="9">
-        <v>-6</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C134" s="8">
-        <v>32</v>
+        <v>37.89</v>
       </c>
       <c r="D134" s="8">
-        <v>38</v>
-      </c>
-      <c r="E134" s="10">
-        <v>6</v>
+        <v>35.92</v>
+      </c>
+      <c r="E134" s="9">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="8">
-        <v>66.45</v>
+        <v>48.25</v>
       </c>
       <c r="D135" s="8">
-        <v>66.84</v>
+        <v>50.49</v>
       </c>
       <c r="E135" s="10">
-        <v>0.39</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="8">
-        <v>42.54</v>
+        <v>63.42</v>
       </c>
       <c r="D136" s="8">
-        <v>42.34</v>
+        <v>57.85</v>
       </c>
       <c r="E136" s="9">
-        <v>-0.2</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="8">
-        <v>64.02</v>
+        <v>46.86</v>
       </c>
       <c r="D137" s="8">
-        <v>53.05</v>
+        <v>40.6</v>
       </c>
       <c r="E137" s="9">
-        <v>-10.97</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="8">
-        <v>37.95</v>
+        <v>63.9</v>
       </c>
       <c r="D138" s="8">
-        <v>39.49</v>
-      </c>
-      <c r="E138" s="10">
-        <v>1.54</v>
+        <v>59.01</v>
+      </c>
+      <c r="E138" s="9">
+        <v>-4.89</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="8">
-        <v>43.74</v>
+        <v>55.6</v>
       </c>
       <c r="D139" s="8">
-        <v>34.93</v>
+        <v>55.51</v>
       </c>
       <c r="E139" s="9">
-        <v>-8.81</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="8">
-        <v>40.14</v>
+        <v>40.35</v>
       </c>
       <c r="D140" s="8">
-        <v>37.89</v>
+        <v>33.36</v>
       </c>
       <c r="E140" s="9">
-        <v>-2.25</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="8">
-        <v>61.73</v>
+        <v>53.44</v>
       </c>
       <c r="D141" s="8">
-        <v>48.25</v>
+        <v>53.39</v>
       </c>
       <c r="E141" s="9">
-        <v>-13.48</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="8">
-        <v>64.17</v>
+        <v>55.12</v>
       </c>
       <c r="D142" s="8">
-        <v>63.42</v>
+        <v>53.53</v>
       </c>
       <c r="E142" s="9">
-        <v>-0.75</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="8">
-        <v>51.23</v>
+        <v>50.9</v>
       </c>
       <c r="D143" s="8">
-        <v>46.86</v>
+        <v>50.7</v>
       </c>
       <c r="E143" s="9">
-        <v>-4.37</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="8">
-        <v>61.52</v>
+        <v>37.55</v>
       </c>
       <c r="D144" s="8">
-        <v>63.9</v>
-      </c>
-      <c r="E144" s="10">
-        <v>2.38</v>
+        <v>35.87</v>
+      </c>
+      <c r="E144" s="9">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="8">
-        <v>53.52</v>
+        <v>48.3</v>
       </c>
       <c r="D145" s="8">
-        <v>55.6</v>
-      </c>
-      <c r="E145" s="10">
-        <v>2.08</v>
+        <v>45.62</v>
+      </c>
+      <c r="E145" s="9">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="8">
-        <v>40.38</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D146" s="8">
-        <v>40.35</v>
+        <v>61.77</v>
       </c>
       <c r="E146" s="9">
-        <v>-0.03</v>
+        <v>-9.33</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="8">
-        <v>61.26</v>
+        <v>51.5</v>
       </c>
       <c r="D147" s="8">
-        <v>53.44</v>
+        <v>47.33</v>
       </c>
       <c r="E147" s="9">
-        <v>-7.82</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="8">
-        <v>57.91</v>
+        <v>38.28</v>
       </c>
       <c r="D148" s="8">
-        <v>55.12</v>
+        <v>37.49</v>
       </c>
       <c r="E148" s="9">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C149" s="8">
-        <v>51.55</v>
-      </c>
-      <c r="D149" s="8">
-        <v>50.9</v>
-      </c>
-      <c r="E149" s="9">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C150" s="8">
-        <v>47.13</v>
-      </c>
-      <c r="D150" s="8">
-        <v>37.55</v>
-      </c>
-      <c r="E150" s="9">
-        <v>-9.58</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C151" s="8">
-        <v>50.27</v>
-      </c>
-      <c r="D151" s="8">
-        <v>48.3</v>
-      </c>
-      <c r="E151" s="9">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C152" s="8">
-        <v>66.17</v>
-      </c>
-      <c r="D152" s="8">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="E152" s="10">
-        <v>4.93</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C153" s="8">
-        <v>49.16</v>
-      </c>
-      <c r="D153" s="8">
-        <v>51.5</v>
-      </c>
-      <c r="E153" s="10">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C154" s="8">
-        <v>37.64</v>
-      </c>
-      <c r="D154" s="8">
-        <v>38.28</v>
-      </c>
-      <c r="E154" s="10">
-        <v>0.64</v>
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6009,28 +5889,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6038,22 +5918,22 @@
         <v>78</v>
       </c>
       <c r="B2" s="13">
-        <v>51.24</v>
+        <v>47.24</v>
       </c>
       <c r="C2" s="14">
         <v>20</v>
       </c>
       <c r="D2" s="13">
-        <v>50</v>
+        <v>46.8</v>
       </c>
       <c r="E2" s="13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F2" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2" s="13">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
@@ -6179,10 +6059,10 @@
         <v>49</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>48</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>46</v>
@@ -6193,34 +6073,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.7504000000000001</v>
+        <v>0.6013000000000001</v>
       </c>
       <c r="B2" s="16">
-        <v>0.3643</v>
+        <v>0.3357</v>
       </c>
       <c r="C2" s="16">
-        <v>0.3517</v>
+        <v>0.3116</v>
       </c>
       <c r="D2" s="16">
-        <v>0.2992</v>
+        <v>0.3085</v>
       </c>
       <c r="E2" s="16">
-        <v>0.2379</v>
+        <v>0.2414</v>
       </c>
       <c r="F2" s="16">
-        <v>0.2242</v>
+        <v>0.2289</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1826</v>
+        <v>0.1955</v>
       </c>
       <c r="H2" s="16">
-        <v>0.1796</v>
+        <v>0.1913</v>
       </c>
       <c r="I2" s="16">
-        <v>0.1544</v>
+        <v>0.157</v>
       </c>
       <c r="J2" s="16">
-        <v>0.1441</v>
+        <v>0.1454</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6234,13 +6114,13 @@
         <v>40</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>57</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>53</v>
@@ -6257,34 +6137,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.1338</v>
+        <v>0.1394</v>
       </c>
       <c r="B4" s="16">
-        <v>0.1276</v>
+        <v>0.134</v>
       </c>
       <c r="C4" s="16">
-        <v>0.1262</v>
+        <v>0.1242</v>
       </c>
       <c r="D4" s="16">
-        <v>0.1132</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="E4" s="16">
-        <v>0.0861</v>
+        <v>0.08470000000000001</v>
       </c>
       <c r="F4" s="16">
-        <v>0.0819</v>
+        <v>0.083</v>
       </c>
       <c r="G4" s="16">
-        <v>0.0572</v>
+        <v>0.0581</v>
       </c>
       <c r="H4" s="16">
-        <v>0.0481</v>
+        <v>0.0423</v>
       </c>
       <c r="I4" s="16">
-        <v>-0.007900000000000001</v>
+        <v>-0.0021</v>
       </c>
       <c r="J4" s="16">
-        <v>-0.0201</v>
+        <v>-0.0182</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="119">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,49 +289,55 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.1% → -1.4%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.1%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.4% → -3.8%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.4%</t>
   </si>
   <si>
+    <t>-3.8%</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>69.6 → 73.0</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>69.6</t>
+  </si>
+  <si>
+    <t>73.0</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.4 → 58.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.4</t>
-  </si>
-  <si>
-    <t>58.5</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.7% → -2.2%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.7%</t>
-  </si>
-  <si>
-    <t>-2.2%</t>
+    <t>58.0 → 45.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>58.0</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -383,7 +389,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,14 +423,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -436,8 +442,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -464,19 +477,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -546,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -555,14 +574,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -571,7 +591,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1075,10 +1095,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>28851.8</v>
+        <v>28841.5</v>
       </c>
       <c r="E2">
-        <v>-0.11</v>
+        <v>-0.04</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1087,43 +1107,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-2.69</v>
+        <v>-2.72</v>
       </c>
       <c r="I2">
-        <v>21.38</v>
+        <v>21.34</v>
       </c>
       <c r="J2">
-        <v>-1.54</v>
+        <v>-0.89</v>
       </c>
       <c r="K2">
-        <v>2.03</v>
+        <v>0.34</v>
       </c>
       <c r="L2">
-        <v>11.43</v>
+        <v>10.59</v>
       </c>
       <c r="M2">
-        <v>13.28</v>
+        <v>13.65</v>
       </c>
       <c r="N2">
-        <v>23.74</v>
+        <v>23.51</v>
       </c>
       <c r="O2">
         <v>81</v>
       </c>
       <c r="Q2">
-        <v>29010.73</v>
+        <v>28958.77</v>
       </c>
       <c r="R2">
-        <v>29235.5</v>
+        <v>29219.13</v>
       </c>
       <c r="S2">
-        <v>27889.26</v>
+        <v>27934.42</v>
       </c>
       <c r="T2">
-        <v>27108.65</v>
+        <v>27118.96</v>
       </c>
       <c r="U2">
-        <v>6.43</v>
+        <v>6.35</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1138,31 +1158,31 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>53.45</v>
+        <v>53.18</v>
       </c>
       <c r="AA2">
-        <v>314.24</v>
+        <v>274.08</v>
       </c>
       <c r="AB2">
-        <v>453</v>
+        <v>417.21</v>
       </c>
       <c r="AC2">
-        <v>-138.75</v>
+        <v>-143.14</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>2.7</v>
+        <v>1.35</v>
       </c>
       <c r="AF2">
-        <v>337.17</v>
+        <v>331.79</v>
       </c>
       <c r="AH2">
-        <v>29660.41</v>
+        <v>29678.66</v>
       </c>
       <c r="AI2">
-        <v>28810.59</v>
+        <v>28759.59</v>
       </c>
       <c r="AJ2">
         <v>28374.42</v>
@@ -1171,7 +1191,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>29.31</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1185,10 +1205,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9809.15</v>
+        <v>9690.65</v>
       </c>
       <c r="E3">
-        <v>-0.06</v>
+        <v>-1.21</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1197,43 +1217,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-6.61</v>
+        <v>-7.74</v>
       </c>
       <c r="I3">
-        <v>14.44</v>
+        <v>13.05</v>
       </c>
       <c r="J3">
-        <v>0.27</v>
+        <v>-1.59</v>
       </c>
       <c r="K3">
-        <v>-0.16</v>
+        <v>-1.73</v>
       </c>
       <c r="L3">
-        <v>-4.23</v>
+        <v>-5.2</v>
       </c>
       <c r="M3">
-        <v>10.6</v>
+        <v>9.41</v>
       </c>
       <c r="N3">
-        <v>12.56</v>
+        <v>12.04</v>
       </c>
       <c r="O3">
         <v>56</v>
       </c>
       <c r="Q3">
-        <v>9842.879999999999</v>
+        <v>9811.51</v>
       </c>
       <c r="R3">
-        <v>9881.92</v>
+        <v>9866.290000000001</v>
       </c>
       <c r="S3">
-        <v>9870.58</v>
+        <v>9863.280000000001</v>
       </c>
       <c r="T3">
-        <v>9735.559999999999</v>
+        <v>9737.620000000001</v>
       </c>
       <c r="U3">
-        <v>0.76</v>
+        <v>-0.48</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1245,43 +1265,43 @@
         <v>79</v>
       </c>
       <c r="Y3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z3">
-        <v>44.36</v>
+        <v>35.26</v>
       </c>
       <c r="AA3">
-        <v>-20.09</v>
+        <v>-30.48</v>
       </c>
       <c r="AB3">
-        <v>-16.97</v>
+        <v>-19.67</v>
       </c>
       <c r="AC3">
-        <v>-3.12</v>
+        <v>-10.81</v>
       </c>
       <c r="AD3">
-        <v>46.58</v>
+        <v>26.69</v>
       </c>
       <c r="AE3">
-        <v>49.55</v>
+        <v>40.72</v>
       </c>
       <c r="AF3">
-        <v>83.5</v>
+        <v>87.2</v>
       </c>
       <c r="AH3">
-        <v>10044.88</v>
+        <v>10039.85</v>
       </c>
       <c r="AI3">
-        <v>9718.959999999999</v>
+        <v>9692.73</v>
       </c>
       <c r="AJ3">
-        <v>10016.11</v>
+        <v>9988.549999999999</v>
       </c>
       <c r="AK3" t="s">
         <v>82</v>
       </c>
       <c r="AL3">
-        <v>28.09</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1295,10 +1315,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11904.2</v>
+        <v>11802.7</v>
       </c>
       <c r="E4">
-        <v>-0.14</v>
+        <v>-0.85</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1307,43 +1327,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-5.81</v>
+        <v>-6.62</v>
       </c>
       <c r="I4">
-        <v>15.19</v>
+        <v>14.21</v>
       </c>
       <c r="J4">
-        <v>-1.35</v>
+        <v>-1.72</v>
       </c>
       <c r="K4">
-        <v>-1.49</v>
+        <v>-2.31</v>
       </c>
       <c r="L4">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="M4">
-        <v>-3.18</v>
+        <v>-3.72</v>
       </c>
       <c r="N4">
-        <v>11.95</v>
+        <v>11.32</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q4">
-        <v>11979.44</v>
+        <v>11938.07</v>
       </c>
       <c r="R4">
-        <v>12095.18</v>
+        <v>12072.38</v>
       </c>
       <c r="S4">
-        <v>11858.13</v>
+        <v>11861.75</v>
       </c>
       <c r="T4">
-        <v>11687.22</v>
+        <v>11684.97</v>
       </c>
       <c r="U4">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1358,40 +1378,40 @@
         <v>3</v>
       </c>
       <c r="Z4">
-        <v>44.97</v>
+        <v>39.38</v>
       </c>
       <c r="AA4">
-        <v>28.64</v>
+        <v>10.04</v>
       </c>
       <c r="AB4">
-        <v>68.52</v>
+        <v>56.83</v>
       </c>
       <c r="AC4">
-        <v>-39.88</v>
+        <v>-46.79</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>6.2</v>
+        <v>2.99</v>
       </c>
       <c r="AF4">
-        <v>101.59</v>
+        <v>101.58</v>
       </c>
       <c r="AH4">
-        <v>12305.62</v>
+        <v>12305.78</v>
       </c>
       <c r="AI4">
-        <v>11884.73</v>
+        <v>11838.97</v>
       </c>
       <c r="AJ4">
-        <v>11869.84</v>
+        <v>12145.9</v>
       </c>
       <c r="AK4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL4">
-        <v>17.65</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1405,10 +1425,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38003.65</v>
+        <v>37949.25</v>
       </c>
       <c r="E5">
-        <v>-0.26</v>
+        <v>-0.14</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1417,43 +1437,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-8.5</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="I5">
-        <v>14.82</v>
+        <v>14.66</v>
       </c>
       <c r="J5">
-        <v>-0.39</v>
+        <v>-1.01</v>
       </c>
       <c r="K5">
-        <v>-0.8100000000000001</v>
+        <v>-2.01</v>
       </c>
       <c r="L5">
-        <v>-5.59</v>
+        <v>-5.57</v>
       </c>
       <c r="M5">
-        <v>9.06</v>
+        <v>9.42</v>
       </c>
       <c r="N5">
-        <v>13.44</v>
+        <v>13.34</v>
       </c>
       <c r="O5">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q5">
-        <v>38170.84</v>
+        <v>38093.52</v>
       </c>
       <c r="R5">
-        <v>38500</v>
+        <v>38450.61</v>
       </c>
       <c r="S5">
-        <v>39047.55</v>
+        <v>38995.57</v>
       </c>
       <c r="T5">
-        <v>37445.25</v>
+        <v>37456.04</v>
       </c>
       <c r="U5">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="V5" t="s">
         <v>80</v>
@@ -1468,40 +1488,40 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>32.08</v>
+        <v>31.05</v>
       </c>
       <c r="AA5">
-        <v>-275.4</v>
+        <v>-282.82</v>
       </c>
       <c r="AB5">
-        <v>-252.62</v>
+        <v>-258.66</v>
       </c>
       <c r="AC5">
-        <v>-22.79</v>
+        <v>-24.16</v>
       </c>
       <c r="AD5">
-        <v>18</v>
+        <v>10.4</v>
       </c>
       <c r="AE5">
-        <v>34.13</v>
+        <v>21.3</v>
       </c>
       <c r="AF5">
-        <v>341.93</v>
+        <v>341.8</v>
       </c>
       <c r="AH5">
-        <v>39107.42</v>
+        <v>39068.95</v>
       </c>
       <c r="AI5">
-        <v>37892.58</v>
+        <v>37832.27</v>
       </c>
       <c r="AJ5">
-        <v>39069.1</v>
+        <v>38865.56</v>
       </c>
       <c r="AK5" t="s">
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>22.04</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1515,10 +1535,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>46815</v>
+        <v>46025.55</v>
       </c>
       <c r="E6">
-        <v>-0.46</v>
+        <v>-1.69</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1527,43 +1547,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-18.02</v>
+        <v>-19.4</v>
       </c>
       <c r="I6">
-        <v>2.8</v>
+        <v>1.07</v>
       </c>
       <c r="J6">
-        <v>-2.19</v>
+        <v>-3.16</v>
       </c>
       <c r="K6">
-        <v>-5.69</v>
+        <v>-6.3</v>
       </c>
       <c r="L6">
-        <v>-2.97</v>
+        <v>-5.32</v>
       </c>
       <c r="M6">
-        <v>-17.38</v>
+        <v>-18.25</v>
       </c>
       <c r="N6">
-        <v>3.65</v>
+        <v>3.09</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>47266.62</v>
+        <v>46966.17</v>
       </c>
       <c r="R6">
-        <v>48354.39</v>
+        <v>48157.39</v>
       </c>
       <c r="S6">
-        <v>48821.32</v>
+        <v>48750.66</v>
       </c>
       <c r="T6">
-        <v>50792.51</v>
+        <v>50745.45</v>
       </c>
       <c r="U6">
-        <v>-7.83</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="V6" t="s">
         <v>80</v>
@@ -1578,40 +1598,40 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>30.61</v>
+        <v>25.16</v>
       </c>
       <c r="AA6">
-        <v>-524.15</v>
+        <v>-617.3099999999999</v>
       </c>
       <c r="AB6">
-        <v>-374.98</v>
+        <v>-423.45</v>
       </c>
       <c r="AC6">
-        <v>-149.17</v>
+        <v>-193.87</v>
       </c>
       <c r="AD6">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>10.24</v>
+        <v>4.76</v>
       </c>
       <c r="AF6">
-        <v>557.1</v>
+        <v>573.86</v>
       </c>
       <c r="AH6">
-        <v>50239.78</v>
+        <v>50154.02</v>
       </c>
       <c r="AI6">
-        <v>46469</v>
+        <v>46160.75</v>
       </c>
       <c r="AJ6">
-        <v>48541.81</v>
+        <v>48094.23</v>
       </c>
       <c r="AK6" t="s">
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>49.48</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1625,10 +1645,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26286.5</v>
+        <v>26293.65</v>
       </c>
       <c r="E7">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1637,43 +1657,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-7.65</v>
+        <v>-7.62</v>
       </c>
       <c r="I7">
-        <v>11.75</v>
+        <v>11.78</v>
       </c>
       <c r="J7">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="K7">
-        <v>0.13</v>
+        <v>-1.13</v>
       </c>
       <c r="L7">
-        <v>5.11</v>
+        <v>5.76</v>
       </c>
       <c r="M7">
-        <v>-0.76</v>
+        <v>-1.05</v>
       </c>
       <c r="N7">
-        <v>8.07</v>
+        <v>7.79</v>
       </c>
       <c r="O7">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="Q7">
-        <v>26271.87</v>
+        <v>26298.9</v>
       </c>
       <c r="R7">
-        <v>26402.7</v>
+        <v>26368.16</v>
       </c>
       <c r="S7">
-        <v>26596.18</v>
+        <v>26593.43</v>
       </c>
       <c r="T7">
-        <v>26668.38</v>
+        <v>26663.66</v>
       </c>
       <c r="U7">
-        <v>-1.43</v>
+        <v>-1.39</v>
       </c>
       <c r="V7" t="s">
         <v>80</v>
@@ -1688,31 +1708,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>46.15</v>
+        <v>46.42</v>
       </c>
       <c r="AA7">
-        <v>-96.94</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="AB7">
-        <v>-97.7</v>
+        <v>-96.15000000000001</v>
       </c>
       <c r="AC7">
-        <v>0.76</v>
+        <v>6.19</v>
       </c>
       <c r="AD7">
-        <v>84.55</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="AE7">
-        <v>72.45</v>
+        <v>78.84</v>
       </c>
       <c r="AF7">
-        <v>256.9</v>
+        <v>255.79</v>
       </c>
       <c r="AH7">
-        <v>26959.5</v>
+        <v>26854.22</v>
       </c>
       <c r="AI7">
-        <v>25845.89</v>
+        <v>25882.09</v>
       </c>
       <c r="AJ7">
         <v>26900.75</v>
@@ -1721,7 +1741,7 @@
         <v>82</v>
       </c>
       <c r="AL7">
-        <v>24.98</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1735,10 +1755,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31281.7</v>
+        <v>31191.45</v>
       </c>
       <c r="E8">
-        <v>3.51</v>
+        <v>-0.29</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1747,43 +1767,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-20.78</v>
+        <v>-21.01</v>
       </c>
       <c r="I8">
-        <v>21.39</v>
+        <v>21.04</v>
       </c>
       <c r="J8">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="K8">
-        <v>0.28</v>
+        <v>1.57</v>
       </c>
       <c r="L8">
-        <v>4.78</v>
+        <v>0.24</v>
       </c>
       <c r="M8">
-        <v>-12.35</v>
+        <v>-12.69</v>
       </c>
       <c r="N8">
-        <v>-1.72</v>
+        <v>-2.04</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>30638.08</v>
+        <v>30756.99</v>
       </c>
       <c r="R8">
-        <v>31066.18</v>
+        <v>31039.99</v>
       </c>
       <c r="S8">
-        <v>29423.19</v>
+        <v>29498.48</v>
       </c>
       <c r="T8">
-        <v>32313.85</v>
+        <v>32294.22</v>
       </c>
       <c r="U8">
-        <v>-3.19</v>
+        <v>-3.41</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1798,34 +1818,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>58.52</v>
+        <v>57.41</v>
       </c>
       <c r="AA8">
-        <v>232.68</v>
+        <v>250.95</v>
       </c>
       <c r="AB8">
-        <v>369.76</v>
+        <v>346</v>
       </c>
       <c r="AC8">
-        <v>-137.08</v>
+        <v>-95.05</v>
       </c>
       <c r="AD8">
-        <v>18.01</v>
+        <v>39</v>
       </c>
       <c r="AE8">
-        <v>14.6</v>
+        <v>22.27</v>
       </c>
       <c r="AF8">
-        <v>617.55</v>
+        <v>619.67</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32133.81</v>
+        <v>32065.44</v>
       </c>
       <c r="AI8">
-        <v>29998.56</v>
+        <v>30014.55</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1834,7 +1854,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>21.66</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1848,10 +1868,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16558.45</v>
+        <v>16582.95</v>
       </c>
       <c r="E9">
-        <v>-0</v>
+        <v>0.15</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1860,28 +1880,28 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-0.62</v>
+        <v>-0.48</v>
       </c>
       <c r="I9">
-        <v>5.72</v>
+        <v>5.87</v>
       </c>
       <c r="J9">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="K9">
-        <v>2.62</v>
+        <v>1.56</v>
       </c>
       <c r="N9">
-        <v>30.17</v>
+        <v>29.76</v>
       </c>
       <c r="Q9">
-        <v>16555.13</v>
+        <v>16569.46</v>
       </c>
       <c r="R9">
-        <v>16566.65</v>
+        <v>16569.72</v>
       </c>
       <c r="S9">
-        <v>16204.57</v>
+        <v>16215.81</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1893,31 +1913,31 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>61.33</v>
+        <v>62.87</v>
       </c>
       <c r="AA9">
-        <v>103.17</v>
+        <v>99.23</v>
       </c>
       <c r="AB9">
-        <v>127.12</v>
+        <v>121.54</v>
       </c>
       <c r="AC9">
-        <v>-23.95</v>
+        <v>-22.31</v>
       </c>
       <c r="AD9">
-        <v>26.1</v>
+        <v>30.2</v>
       </c>
       <c r="AE9">
-        <v>26.25</v>
+        <v>28.2</v>
       </c>
       <c r="AF9">
-        <v>116.87</v>
+        <v>123.69</v>
       </c>
       <c r="AH9">
-        <v>16672.06</v>
+        <v>16673.15</v>
       </c>
       <c r="AI9">
-        <v>16461.23</v>
+        <v>16466.3</v>
       </c>
       <c r="AJ9">
         <v>16247.63</v>
@@ -1926,7 +1946,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>18.82</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1940,10 +1960,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9242.700000000001</v>
+        <v>9179.4</v>
       </c>
       <c r="E10">
-        <v>0.05</v>
+        <v>-0.68</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1952,43 +1972,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-5.36</v>
+        <v>-6</v>
       </c>
       <c r="I10">
-        <v>7.96</v>
+        <v>7.22</v>
       </c>
       <c r="J10">
-        <v>-1.14</v>
+        <v>-1.75</v>
       </c>
       <c r="K10">
-        <v>-1.1</v>
+        <v>-2.44</v>
       </c>
       <c r="L10">
+        <v>-0.51</v>
+      </c>
+      <c r="M10">
         <v>0.06</v>
       </c>
-      <c r="M10">
-        <v>0.91</v>
-      </c>
       <c r="N10">
-        <v>14.79</v>
+        <v>14.28</v>
       </c>
       <c r="O10">
         <v>32</v>
       </c>
       <c r="Q10">
-        <v>9302.66</v>
+        <v>9270.02</v>
       </c>
       <c r="R10">
-        <v>9386.02</v>
+        <v>9369.6</v>
       </c>
       <c r="S10">
-        <v>9396.93</v>
+        <v>9390.280000000001</v>
       </c>
       <c r="T10">
-        <v>9352.629999999999</v>
+        <v>9351.559999999999</v>
       </c>
       <c r="U10">
-        <v>-1.18</v>
+        <v>-1.84</v>
       </c>
       <c r="V10" t="s">
         <v>80</v>
@@ -2003,40 +2023,40 @@
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>38.2</v>
+        <v>33.96</v>
       </c>
       <c r="AA10">
-        <v>-30.9</v>
+        <v>-40.67</v>
       </c>
       <c r="AB10">
-        <v>-12.81</v>
+        <v>-18.38</v>
       </c>
       <c r="AC10">
-        <v>-18.09</v>
+        <v>-22.29</v>
       </c>
       <c r="AD10">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>16.22</v>
+        <v>7.78</v>
       </c>
       <c r="AF10">
-        <v>81.44</v>
+        <v>81.77</v>
       </c>
       <c r="AH10">
-        <v>9539.049999999999</v>
+        <v>9537.379999999999</v>
       </c>
       <c r="AI10">
-        <v>9232.99</v>
+        <v>9201.83</v>
       </c>
       <c r="AJ10">
-        <v>9229.360000000001</v>
+        <v>9431.969999999999</v>
       </c>
       <c r="AK10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL10">
-        <v>35.52</v>
+        <v>39.36</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2050,10 +2070,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1602.9</v>
+        <v>1557.35</v>
       </c>
       <c r="E11">
-        <v>0.39</v>
+        <v>-2.84</v>
       </c>
       <c r="F11">
         <v>1653.95</v>
@@ -2062,43 +2082,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-3.09</v>
+        <v>-5.84</v>
       </c>
       <c r="I11">
-        <v>27.89</v>
+        <v>24.25</v>
       </c>
       <c r="J11">
-        <v>-1.14</v>
+        <v>-2.87</v>
       </c>
       <c r="K11">
-        <v>1.1</v>
+        <v>-3.79</v>
       </c>
       <c r="L11">
-        <v>12.28</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M11">
-        <v>-2.17</v>
+        <v>-4.95</v>
       </c>
       <c r="N11">
-        <v>-0.01</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="O11">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="Q11">
-        <v>1604.78</v>
+        <v>1595.59</v>
       </c>
       <c r="R11">
-        <v>1588.07</v>
+        <v>1587.5</v>
       </c>
       <c r="S11">
-        <v>1544.37</v>
+        <v>1545.21</v>
       </c>
       <c r="T11">
-        <v>1446.32</v>
+        <v>1446.66</v>
       </c>
       <c r="U11">
-        <v>10.83</v>
+        <v>7.65</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2113,31 +2133,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>57.97</v>
+        <v>45.23</v>
       </c>
       <c r="AA11">
-        <v>19.48</v>
+        <v>14.79</v>
       </c>
       <c r="AB11">
-        <v>21.01</v>
+        <v>19.76</v>
       </c>
       <c r="AC11">
-        <v>-1.53</v>
+        <v>-4.97</v>
       </c>
       <c r="AD11">
-        <v>40.65</v>
+        <v>19.47</v>
       </c>
       <c r="AE11">
-        <v>49.44</v>
+        <v>36.48</v>
       </c>
       <c r="AF11">
-        <v>29.72</v>
+        <v>32.85</v>
       </c>
       <c r="AH11">
-        <v>1631.64</v>
+        <v>1632.41</v>
       </c>
       <c r="AI11">
-        <v>1544.5</v>
+        <v>1542.6</v>
       </c>
       <c r="AJ11">
         <v>1523.72</v>
@@ -2146,7 +2166,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>40.84</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2160,10 +2180,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13525.35</v>
+        <v>13193.9</v>
       </c>
       <c r="E12">
-        <v>0.75</v>
+        <v>-2.45</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2172,43 +2192,43 @@
         <v>9154.799999999999</v>
       </c>
       <c r="H12">
-        <v>-1.41</v>
+        <v>-3.82</v>
       </c>
       <c r="I12">
-        <v>47.74</v>
+        <v>44.12</v>
       </c>
       <c r="J12">
-        <v>3.56</v>
+        <v>-1.4</v>
       </c>
       <c r="K12">
-        <v>6.48</v>
+        <v>3.73</v>
       </c>
       <c r="L12">
-        <v>0.14</v>
+        <v>-2.68</v>
       </c>
       <c r="M12">
-        <v>42.41</v>
+        <v>38.98</v>
       </c>
       <c r="N12">
-        <v>19.19</v>
+        <v>18.22</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13449.2</v>
+        <v>13411.69</v>
       </c>
       <c r="R12">
-        <v>13176.53</v>
+        <v>13190.5</v>
       </c>
       <c r="S12">
-        <v>12811.38</v>
+        <v>12814.84</v>
       </c>
       <c r="T12">
-        <v>12065.65</v>
+        <v>12079.48</v>
       </c>
       <c r="U12">
-        <v>12.1</v>
+        <v>9.23</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2223,31 +2243,31 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>67.39</v>
+        <v>53.42</v>
       </c>
       <c r="AA12">
-        <v>178.14</v>
+        <v>158.78</v>
       </c>
       <c r="AB12">
-        <v>141.01</v>
+        <v>144.56</v>
       </c>
       <c r="AC12">
-        <v>37.13</v>
+        <v>14.21</v>
       </c>
       <c r="AD12">
-        <v>81.68000000000001</v>
+        <v>48.34</v>
       </c>
       <c r="AE12">
-        <v>82.65000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="AF12">
-        <v>195.08</v>
+        <v>205.34</v>
       </c>
       <c r="AH12">
-        <v>13548.34</v>
+        <v>13541.26</v>
       </c>
       <c r="AI12">
-        <v>12804.73</v>
+        <v>12839.74</v>
       </c>
       <c r="AJ12">
         <v>12921.88</v>
@@ -2256,7 +2276,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>38.1</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2270,10 +2290,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9689.25</v>
+        <v>9704.4</v>
       </c>
       <c r="E13">
-        <v>-0.13</v>
+        <v>0.16</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2282,43 +2302,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-10</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="I13">
-        <v>5.29</v>
+        <v>5.45</v>
       </c>
       <c r="J13">
-        <v>-0.55</v>
+        <v>-0.79</v>
       </c>
       <c r="K13">
-        <v>-2.06</v>
+        <v>-2.39</v>
       </c>
       <c r="L13">
-        <v>-4.55</v>
+        <v>-3.75</v>
       </c>
       <c r="M13">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="N13">
-        <v>21.78</v>
+        <v>21.63</v>
       </c>
       <c r="O13">
         <v>19</v>
       </c>
       <c r="Q13">
-        <v>9739.57</v>
+        <v>9724.08</v>
       </c>
       <c r="R13">
-        <v>9834.049999999999</v>
+        <v>9819</v>
       </c>
       <c r="S13">
-        <v>9916.02</v>
+        <v>9906.540000000001</v>
       </c>
       <c r="T13">
-        <v>10038.85</v>
+        <v>10038.01</v>
       </c>
       <c r="U13">
-        <v>-3.48</v>
+        <v>-3.32</v>
       </c>
       <c r="V13" t="s">
         <v>80</v>
@@ -2333,40 +2353,40 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>31.91</v>
+        <v>34.32</v>
       </c>
       <c r="AA13">
-        <v>-62.02</v>
+        <v>-62.87</v>
       </c>
       <c r="AB13">
-        <v>-51.43</v>
+        <v>-53.72</v>
       </c>
       <c r="AC13">
-        <v>-10.59</v>
+        <v>-9.15</v>
       </c>
       <c r="AD13">
-        <v>5.33</v>
+        <v>6.1</v>
       </c>
       <c r="AE13">
-        <v>22.28</v>
+        <v>11.97</v>
       </c>
       <c r="AF13">
-        <v>87.62</v>
+        <v>89.31</v>
       </c>
       <c r="AH13">
-        <v>10015.19</v>
+        <v>9989.92</v>
       </c>
       <c r="AI13">
-        <v>9652.9</v>
+        <v>9648.07</v>
       </c>
       <c r="AJ13">
-        <v>9947.219999999999</v>
+        <v>9916.76</v>
       </c>
       <c r="AK13" t="s">
         <v>82</v>
       </c>
       <c r="AL13">
-        <v>33.24</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2380,10 +2400,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8604.299999999999</v>
+        <v>8609.549999999999</v>
       </c>
       <c r="E14">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2392,43 +2412,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-12.91</v>
+        <v>-12.86</v>
       </c>
       <c r="I14">
-        <v>27.36</v>
+        <v>27.43</v>
       </c>
       <c r="J14">
-        <v>-0.14</v>
+        <v>0.82</v>
       </c>
       <c r="K14">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="L14">
-        <v>7.48</v>
+        <v>6.96</v>
       </c>
       <c r="M14">
-        <v>21.13</v>
+        <v>21.65</v>
       </c>
       <c r="N14">
-        <v>30.02</v>
+        <v>29.82</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8601</v>
+        <v>8614.959999999999</v>
       </c>
       <c r="R14">
-        <v>8641.469999999999</v>
+        <v>8647.610000000001</v>
       </c>
       <c r="S14">
-        <v>8514.57</v>
+        <v>8512.43</v>
       </c>
       <c r="T14">
-        <v>8595.09</v>
+        <v>8596.379999999999</v>
       </c>
       <c r="U14">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2443,31 +2463,31 @@
         <v>2</v>
       </c>
       <c r="Z14">
-        <v>51.65</v>
+        <v>52.01</v>
       </c>
       <c r="AA14">
-        <v>34.12</v>
+        <v>30.95</v>
       </c>
       <c r="AB14">
-        <v>49.62</v>
+        <v>45.88</v>
       </c>
       <c r="AC14">
-        <v>-15.5</v>
+        <v>-14.93</v>
       </c>
       <c r="AD14">
-        <v>23.56</v>
+        <v>18.39</v>
       </c>
       <c r="AE14">
-        <v>21.9</v>
+        <v>21.78</v>
       </c>
       <c r="AF14">
-        <v>120.39</v>
+        <v>123.06</v>
       </c>
       <c r="AH14">
-        <v>8833.02</v>
+        <v>8825.67</v>
       </c>
       <c r="AI14">
-        <v>8449.91</v>
+        <v>8469.540000000001</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
@@ -2476,7 +2496,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>18.49</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2490,13 +2510,13 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26991.85</v>
+        <v>27186.45</v>
       </c>
       <c r="E15">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="F15">
-        <v>26991.85</v>
+        <v>27186.45</v>
       </c>
       <c r="G15">
         <v>21454.25</v>
@@ -2505,40 +2525,40 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>25.81</v>
+        <v>26.72</v>
       </c>
       <c r="J15">
-        <v>2.4</v>
+        <v>3.22</v>
       </c>
       <c r="K15">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="L15">
-        <v>11.47</v>
+        <v>13.25</v>
       </c>
       <c r="M15">
-        <v>22.86</v>
+        <v>22.58</v>
       </c>
       <c r="N15">
-        <v>13.69</v>
+        <v>13.64</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26674.04</v>
+        <v>26843.47</v>
       </c>
       <c r="R15">
-        <v>26566.13</v>
+        <v>26592.31</v>
       </c>
       <c r="S15">
-        <v>26001.5</v>
+        <v>26056.03</v>
       </c>
       <c r="T15">
-        <v>23697.27</v>
+        <v>23722.36</v>
       </c>
       <c r="U15">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2553,43 +2573,43 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>69.63</v>
+        <v>72.98</v>
       </c>
       <c r="AA15">
-        <v>205.91</v>
+        <v>237.63</v>
       </c>
       <c r="AB15">
-        <v>205.72</v>
+        <v>212.1</v>
       </c>
       <c r="AC15">
-        <v>0.19</v>
+        <v>25.52</v>
       </c>
       <c r="AD15">
-        <v>79.26000000000001</v>
+        <v>95.08</v>
       </c>
       <c r="AE15">
-        <v>57.07</v>
+        <v>78.13</v>
       </c>
       <c r="AF15">
-        <v>287.29</v>
+        <v>300.72</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>26927.79</v>
+        <v>27047.23</v>
       </c>
       <c r="AI15">
-        <v>26204.46</v>
+        <v>26137.38</v>
       </c>
       <c r="AJ15">
-        <v>26036.32</v>
+        <v>26048.62</v>
       </c>
       <c r="AK15" t="s">
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>28.39</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2603,10 +2623,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>908.85</v>
+        <v>904.15</v>
       </c>
       <c r="E16">
-        <v>-0.08</v>
+        <v>-0.52</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2615,43 +2635,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-6.17</v>
+        <v>-6.66</v>
       </c>
       <c r="I16">
-        <v>39.58</v>
+        <v>38.85</v>
       </c>
       <c r="J16">
-        <v>0.1</v>
+        <v>-1.41</v>
       </c>
       <c r="K16">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="L16">
-        <v>18.31</v>
+        <v>16.91</v>
       </c>
       <c r="M16">
-        <v>-0.55</v>
+        <v>-1.44</v>
       </c>
       <c r="N16">
-        <v>18.8</v>
+        <v>18.51</v>
       </c>
       <c r="O16">
         <v>74</v>
       </c>
       <c r="Q16">
-        <v>912.7</v>
+        <v>910.11</v>
       </c>
       <c r="R16">
-        <v>901.29</v>
+        <v>900.85</v>
       </c>
       <c r="S16">
-        <v>892.9299999999999</v>
+        <v>894.77</v>
       </c>
       <c r="T16">
-        <v>832.47</v>
+        <v>832.26</v>
       </c>
       <c r="U16">
-        <v>9.17</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2666,31 +2686,31 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>54.73</v>
+        <v>51.82</v>
       </c>
       <c r="AA16">
-        <v>5.55</v>
+        <v>4.91</v>
       </c>
       <c r="AB16">
-        <v>5.63</v>
+        <v>5.49</v>
       </c>
       <c r="AC16">
-        <v>-0.08</v>
+        <v>-0.58</v>
       </c>
       <c r="AD16">
-        <v>58.3</v>
+        <v>45.18</v>
       </c>
       <c r="AE16">
-        <v>73.45</v>
+        <v>59.13</v>
       </c>
       <c r="AF16">
-        <v>15.71</v>
+        <v>16.05</v>
       </c>
       <c r="AH16">
-        <v>921.6</v>
+        <v>920.45</v>
       </c>
       <c r="AI16">
-        <v>880.99</v>
+        <v>881.25</v>
       </c>
       <c r="AJ16">
         <v>869.13</v>
@@ -2699,7 +2719,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>30.78</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2713,10 +2733,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30900.2</v>
+        <v>30836.2</v>
       </c>
       <c r="E17">
-        <v>0.49</v>
+        <v>-0.21</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2725,46 +2745,46 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-9.390000000000001</v>
+        <v>-9.57</v>
       </c>
       <c r="I17">
-        <v>8.94</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="J17">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K17">
-        <v>-0.91</v>
+        <v>-1.38</v>
       </c>
       <c r="L17">
-        <v>4.68</v>
+        <v>3.97</v>
       </c>
       <c r="M17">
-        <v>-5.73</v>
+        <v>-6.03</v>
       </c>
       <c r="N17">
-        <v>5.33</v>
+        <v>4.98</v>
       </c>
       <c r="O17">
         <v>26</v>
       </c>
       <c r="Q17">
-        <v>30881.37</v>
+        <v>30877.1</v>
       </c>
       <c r="R17">
-        <v>31112.77</v>
+        <v>31065.87</v>
       </c>
       <c r="S17">
-        <v>31086.19</v>
+        <v>31091.66</v>
       </c>
       <c r="T17">
-        <v>31692.41</v>
+        <v>31681.45</v>
       </c>
       <c r="U17">
-        <v>-2.5</v>
+        <v>-2.67</v>
       </c>
       <c r="V17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W17" t="b">
         <v>0</v>
@@ -2773,34 +2793,34 @@
         <v>80</v>
       </c>
       <c r="Y17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>45.78</v>
+        <v>43.96</v>
       </c>
       <c r="AA17">
-        <v>-86.84999999999999</v>
+        <v>-88.94</v>
       </c>
       <c r="AB17">
-        <v>-50.61</v>
+        <v>-58.28</v>
       </c>
       <c r="AC17">
-        <v>-36.23</v>
+        <v>-30.66</v>
       </c>
       <c r="AD17">
-        <v>50.95</v>
+        <v>54.77</v>
       </c>
       <c r="AE17">
-        <v>46.67</v>
+        <v>50.11</v>
       </c>
       <c r="AF17">
-        <v>251.98</v>
+        <v>252.05</v>
       </c>
       <c r="AH17">
-        <v>31735.98</v>
+        <v>31616.39</v>
       </c>
       <c r="AI17">
-        <v>30489.57</v>
+        <v>30515.34</v>
       </c>
       <c r="AJ17">
         <v>30549.87</v>
@@ -2809,7 +2829,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>28.12</v>
+        <v>28.87</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2823,13 +2843,13 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16798.5</v>
+        <v>16941.5</v>
       </c>
       <c r="E18">
-        <v>0.54</v>
+        <v>0.85</v>
       </c>
       <c r="F18">
-        <v>16798.5</v>
+        <v>16941.5</v>
       </c>
       <c r="G18">
         <v>15403.15</v>
@@ -2838,25 +2858,25 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>9.06</v>
+        <v>9.99</v>
       </c>
       <c r="J18">
-        <v>2.02</v>
+        <v>3.19</v>
       </c>
       <c r="K18">
-        <v>0.59</v>
+        <v>1.11</v>
       </c>
       <c r="N18">
-        <v>44.17</v>
+        <v>47.82</v>
       </c>
       <c r="Q18">
-        <v>16621.66</v>
+        <v>16726.36</v>
       </c>
       <c r="R18">
-        <v>16604.29</v>
+        <v>16612.19</v>
       </c>
       <c r="S18">
-        <v>16421.77</v>
+        <v>16447.22</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2868,40 +2888,40 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>64.84</v>
+        <v>69.66</v>
       </c>
       <c r="AA18">
-        <v>58.03</v>
+        <v>81.41</v>
       </c>
       <c r="AB18">
-        <v>52.82</v>
+        <v>58.54</v>
       </c>
       <c r="AC18">
-        <v>5.21</v>
+        <v>22.87</v>
       </c>
       <c r="AD18">
-        <v>82.52</v>
+        <v>97.75</v>
       </c>
       <c r="AE18">
-        <v>62.69</v>
+        <v>82.75</v>
       </c>
       <c r="AF18">
-        <v>165.78</v>
+        <v>175.63</v>
       </c>
       <c r="AH18">
-        <v>16863.75</v>
+        <v>16902.45</v>
       </c>
       <c r="AI18">
-        <v>16344.82</v>
+        <v>16321.94</v>
       </c>
       <c r="AJ18">
-        <v>16248.5</v>
+        <v>16262.99</v>
       </c>
       <c r="AK18" t="s">
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>25.15</v>
+        <v>28.73</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2915,10 +2935,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9751.65</v>
+        <v>9718.4</v>
       </c>
       <c r="E19">
-        <v>-0.52</v>
+        <v>-0.34</v>
       </c>
       <c r="F19">
         <v>9968.25</v>
@@ -2927,28 +2947,28 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-2.17</v>
+        <v>-2.51</v>
       </c>
       <c r="I19">
-        <v>8.41</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="J19">
-        <v>-0.51</v>
+        <v>-0.22</v>
       </c>
       <c r="K19">
-        <v>6.13</v>
+        <v>4.15</v>
       </c>
       <c r="N19">
-        <v>46.66</v>
+        <v>42.33</v>
       </c>
       <c r="Q19">
-        <v>9760.389999999999</v>
+        <v>9756.15</v>
       </c>
       <c r="R19">
-        <v>9709.92</v>
+        <v>9723.93</v>
       </c>
       <c r="S19">
-        <v>9538.35</v>
+        <v>9540.969999999999</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2960,31 +2980,31 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>56.15</v>
+        <v>53.93</v>
       </c>
       <c r="AA19">
-        <v>93.06</v>
+        <v>83.53</v>
       </c>
       <c r="AB19">
-        <v>104.28</v>
+        <v>100.13</v>
       </c>
       <c r="AC19">
-        <v>-11.22</v>
+        <v>-16.6</v>
       </c>
       <c r="AD19">
         <v>6.54</v>
       </c>
       <c r="AE19">
-        <v>8.609999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AF19">
-        <v>134.65</v>
+        <v>135.72</v>
       </c>
       <c r="AH19">
-        <v>10010.35</v>
+        <v>9995.77</v>
       </c>
       <c r="AI19">
-        <v>9409.49</v>
+        <v>9452.09</v>
       </c>
       <c r="AJ19">
         <v>9466.209999999999</v>
@@ -2993,7 +3013,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>20.47</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3007,10 +3027,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11067.7</v>
+        <v>11103.8</v>
       </c>
       <c r="E20">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3019,28 +3039,28 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-2.65</v>
+        <v>-2.33</v>
       </c>
       <c r="I20">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="J20">
-        <v>-0.99</v>
+        <v>-0.83</v>
       </c>
       <c r="K20">
-        <v>-0.54</v>
+        <v>-1.28</v>
       </c>
       <c r="N20">
-        <v>2.41</v>
+        <v>3.85</v>
       </c>
       <c r="Q20">
-        <v>11137.92</v>
+        <v>11119.28</v>
       </c>
       <c r="R20">
-        <v>11218.74</v>
+        <v>11206.06</v>
       </c>
       <c r="S20">
-        <v>11182.14</v>
+        <v>11180.82</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3052,31 +3072,31 @@
         <v>1</v>
       </c>
       <c r="Z20">
-        <v>39.19</v>
+        <v>43.05</v>
       </c>
       <c r="AA20">
-        <v>-19.95</v>
+        <v>-23.19</v>
       </c>
       <c r="AB20">
-        <v>1.21</v>
+        <v>-3.67</v>
       </c>
       <c r="AC20">
-        <v>-21.16</v>
+        <v>-19.51</v>
       </c>
       <c r="AD20">
-        <v>1.43</v>
+        <v>10.13</v>
       </c>
       <c r="AE20">
-        <v>10.28</v>
+        <v>7.73</v>
       </c>
       <c r="AF20">
-        <v>115.69</v>
+        <v>117.09</v>
       </c>
       <c r="AH20">
-        <v>11368.98</v>
+        <v>11349.68</v>
       </c>
       <c r="AI20">
-        <v>11068.5</v>
+        <v>11062.43</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3085,7 +3105,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>18.12</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3099,10 +3119,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27737.2</v>
+        <v>28005.75</v>
       </c>
       <c r="E21">
-        <v>-0.08</v>
+        <v>0.97</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3111,43 +3131,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-4.97</v>
+        <v>-4.05</v>
       </c>
       <c r="I21">
-        <v>14.88</v>
+        <v>15.99</v>
       </c>
       <c r="J21">
-        <v>1.05</v>
+        <v>1.83</v>
       </c>
       <c r="K21">
-        <v>0.8100000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="L21">
-        <v>6.4</v>
+        <v>7.67</v>
       </c>
       <c r="M21">
-        <v>2.96</v>
+        <v>3.81</v>
       </c>
       <c r="N21">
-        <v>8.130000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="O21">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="Q21">
-        <v>27635.57</v>
+        <v>27736.36</v>
       </c>
       <c r="R21">
-        <v>27519.8</v>
+        <v>27517.83</v>
       </c>
       <c r="S21">
-        <v>27898.19</v>
+        <v>27900.46</v>
       </c>
       <c r="T21">
-        <v>27638.23</v>
+        <v>27638.59</v>
       </c>
       <c r="U21">
-        <v>0.36</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="s">
         <v>80</v>
@@ -3162,31 +3182,31 @@
         <v>2</v>
       </c>
       <c r="Z21">
-        <v>53.3</v>
+        <v>60.16</v>
       </c>
       <c r="AA21">
-        <v>-61.57</v>
+        <v>-22.19</v>
       </c>
       <c r="AB21">
-        <v>-116.33</v>
+        <v>-97.5</v>
       </c>
       <c r="AC21">
-        <v>54.76</v>
+        <v>75.31</v>
       </c>
       <c r="AD21">
         <v>98.61</v>
       </c>
       <c r="AE21">
-        <v>95.94</v>
+        <v>97.28</v>
       </c>
       <c r="AF21">
-        <v>310.06</v>
+        <v>312.68</v>
       </c>
       <c r="AH21">
-        <v>27987.25</v>
+        <v>27976.2</v>
       </c>
       <c r="AI21">
-        <v>27052.35</v>
+        <v>27059.46</v>
       </c>
       <c r="AJ21">
         <v>28265.67</v>
@@ -3195,7 +3215,7 @@
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>29.41</v>
+        <v>32.21</v>
       </c>
     </row>
   </sheetData>
@@ -3336,7 +3356,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3395,2302 +3415,2390 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2.03</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>-0.16</v>
+      </c>
+      <c r="D11" s="8">
+        <v>-1.73</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8">
+        <v>-1.49</v>
+      </c>
+      <c r="D12" s="8">
+        <v>-2.31</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="D13" s="8">
+        <v>-2.01</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8">
+        <v>-5.69</v>
+      </c>
+      <c r="D14" s="8">
+        <v>-6.3</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.13</v>
+      </c>
+      <c r="D15" s="8">
+        <v>-1.13</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.28</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="8">
+        <v>2.62</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1.56</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-1.1</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-2.44</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="8">
+        <v>1.1</v>
+      </c>
+      <c r="D19" s="8">
+        <v>-3.79</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-4.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="8">
+        <v>6.48</v>
+      </c>
+      <c r="D20" s="8">
+        <v>3.73</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-2.06</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-2.39</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="8">
+        <v>3.32</v>
+      </c>
+      <c r="D22" s="8">
+        <v>2.9</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2.45</v>
+      </c>
+      <c r="D23" s="8">
+        <v>2.46</v>
+      </c>
+      <c r="E23" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="8">
+        <v>1.04</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.3</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-0.91</v>
+      </c>
+      <c r="D25" s="8">
+        <v>-1.38</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.59</v>
+      </c>
+      <c r="D26" s="8">
+        <v>1.11</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="8">
+        <v>6.13</v>
+      </c>
+      <c r="D27" s="8">
+        <v>4.15</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="8">
+        <v>-0.54</v>
+      </c>
+      <c r="D28" s="8">
+        <v>-1.28</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D29" s="8">
+        <v>1.76</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="7">
-        <v>6.58</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2.03</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="8">
+        <v>-1.54</v>
+      </c>
+      <c r="D30" s="8">
+        <v>-0.89</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="D31" s="8">
+        <v>-1.59</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="8">
+        <v>-1.35</v>
+      </c>
+      <c r="D32" s="8">
+        <v>-1.72</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="8">
+        <v>-0.39</v>
+      </c>
+      <c r="D33" s="8">
+        <v>-1.01</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="8">
+        <v>-2.19</v>
+      </c>
+      <c r="D34" s="8">
+        <v>-3.16</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.32</v>
+      </c>
+      <c r="D35" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="E35" s="10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2.45</v>
+      </c>
+      <c r="D36" s="8">
+        <v>1.94</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="8">
+        <v>0.28</v>
+      </c>
+      <c r="D37" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="E37" s="10">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="8">
+        <v>-1.14</v>
+      </c>
+      <c r="D38" s="8">
+        <v>-1.75</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-1.14</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-2.87</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="8">
+        <v>3.56</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-1.4</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-4.96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="8">
+        <v>-0.55</v>
+      </c>
+      <c r="D41" s="8">
+        <v>-0.79</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-0.14</v>
+      </c>
+      <c r="D42" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="D43" s="8">
+        <v>3.22</v>
+      </c>
+      <c r="E43" s="10">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="8">
+        <v>-1.41</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="8">
+        <v>2.02</v>
+      </c>
+      <c r="D46" s="8">
+        <v>3.19</v>
+      </c>
+      <c r="E46" s="10">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="8">
+        <v>-0.51</v>
+      </c>
+      <c r="D47" s="8">
+        <v>-0.22</v>
+      </c>
+      <c r="E47" s="10">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-0.99</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-0.83</v>
+      </c>
+      <c r="E48" s="10">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="D49" s="8">
+        <v>1.83</v>
+      </c>
+      <c r="E49" s="10">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="8">
+        <v>13.28</v>
+      </c>
+      <c r="D50" s="8">
+        <v>13.65</v>
+      </c>
+      <c r="E50" s="10">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="8">
+        <v>10.6</v>
+      </c>
+      <c r="D51" s="8">
+        <v>9.41</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="8">
+        <v>-3.18</v>
+      </c>
+      <c r="D52" s="8">
+        <v>-3.72</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="8">
+        <v>9.06</v>
+      </c>
+      <c r="D53" s="8">
+        <v>9.42</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="8">
+        <v>-17.38</v>
+      </c>
+      <c r="D54" s="8">
+        <v>-18.25</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="8">
+        <v>-0.76</v>
+      </c>
+      <c r="D55" s="8">
+        <v>-1.05</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="8">
+        <v>-12.35</v>
+      </c>
+      <c r="D56" s="8">
+        <v>-12.69</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.91</v>
+      </c>
+      <c r="D57" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="8">
+        <v>-2.17</v>
+      </c>
+      <c r="D58" s="8">
+        <v>-4.95</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="8">
+        <v>42.41</v>
+      </c>
+      <c r="D59" s="8">
+        <v>38.98</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="8">
+        <v>1.27</v>
+      </c>
+      <c r="D60" s="8">
+        <v>1.91</v>
+      </c>
+      <c r="E60" s="10">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="8">
+        <v>21.13</v>
+      </c>
+      <c r="D61" s="8">
+        <v>21.65</v>
+      </c>
+      <c r="E61" s="10">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="8">
+        <v>22.86</v>
+      </c>
+      <c r="D62" s="8">
+        <v>22.58</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="8">
+        <v>-0.55</v>
+      </c>
+      <c r="D63" s="8">
+        <v>-1.44</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C64" s="8">
+        <v>-5.73</v>
+      </c>
+      <c r="D64" s="8">
+        <v>-6.03</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="8">
+        <v>2.96</v>
+      </c>
+      <c r="D65" s="8">
+        <v>3.81</v>
+      </c>
+      <c r="E65" s="10">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="8">
+        <v>11.43</v>
+      </c>
+      <c r="D66" s="8">
+        <v>10.59</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="8">
+        <v>-4.23</v>
+      </c>
+      <c r="D67" s="8">
+        <v>-5.2</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="8">
+        <v>7.4</v>
+      </c>
+      <c r="D68" s="8">
+        <v>5.7</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="8">
+        <v>-5.59</v>
+      </c>
+      <c r="D69" s="8">
+        <v>-5.57</v>
+      </c>
+      <c r="E69" s="10">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="8">
+        <v>-2.97</v>
+      </c>
+      <c r="D70" s="8">
+        <v>-5.32</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="8">
+        <v>5.11</v>
+      </c>
+      <c r="D71" s="8">
+        <v>5.76</v>
+      </c>
+      <c r="E71" s="10">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="8">
+        <v>4.78</v>
+      </c>
+      <c r="D72" s="8">
+        <v>0.24</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-4.54</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="8">
+        <v>0.06</v>
+      </c>
+      <c r="D73" s="8">
+        <v>-0.51</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="8">
+        <v>12.28</v>
+      </c>
+      <c r="D74" s="8">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-3.32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="8">
+        <v>0.14</v>
+      </c>
+      <c r="D75" s="8">
+        <v>-2.68</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="8">
         <v>-4.55</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="D76" s="8">
+        <v>-3.75</v>
+      </c>
+      <c r="E76" s="10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="8">
+        <v>7.48</v>
+      </c>
+      <c r="D77" s="8">
+        <v>6.96</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="8">
+        <v>11.47</v>
+      </c>
+      <c r="D78" s="8">
+        <v>13.25</v>
+      </c>
+      <c r="E78" s="10">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="8">
+        <v>18.31</v>
+      </c>
+      <c r="D79" s="8">
+        <v>16.91</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="8">
+        <v>4.68</v>
+      </c>
+      <c r="D80" s="8">
+        <v>3.97</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="8">
+        <v>6.4</v>
+      </c>
+      <c r="D81" s="8">
+        <v>7.67</v>
+      </c>
+      <c r="E81" s="10">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="8">
+        <v>-2.69</v>
+      </c>
+      <c r="D82" s="8">
+        <v>-2.72</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B83" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="8">
+        <v>-6.61</v>
+      </c>
+      <c r="D83" s="8">
+        <v>-7.74</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="8">
+        <v>-5.81</v>
+      </c>
+      <c r="D84" s="8">
+        <v>-6.62</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="8">
+        <v>-8.5</v>
+      </c>
+      <c r="D85" s="8">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="8">
+        <v>-18.02</v>
+      </c>
+      <c r="D86" s="8">
+        <v>-19.4</v>
+      </c>
+      <c r="E86" s="9">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="8">
+        <v>-7.65</v>
+      </c>
+      <c r="D87" s="8">
+        <v>-7.62</v>
+      </c>
+      <c r="E87" s="10">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="8">
+        <v>-20.78</v>
+      </c>
+      <c r="D88" s="8">
+        <v>-21.01</v>
+      </c>
+      <c r="E88" s="9">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="8">
+        <v>-0.62</v>
+      </c>
+      <c r="D89" s="8">
+        <v>-0.48</v>
+      </c>
+      <c r="E89" s="10">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="8">
+        <v>-5.36</v>
+      </c>
+      <c r="D90" s="8">
+        <v>-6</v>
+      </c>
+      <c r="E90" s="9">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="8">
+        <v>-3.09</v>
+      </c>
+      <c r="D91" s="8">
+        <v>-5.84</v>
+      </c>
+      <c r="E91" s="9">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="8">
+        <v>-1.41</v>
+      </c>
+      <c r="D92" s="8">
+        <v>-3.82</v>
+      </c>
+      <c r="E92" s="9">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="8">
+        <v>-10</v>
+      </c>
+      <c r="D93" s="8">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="E93" s="10">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="8">
+        <v>-12.91</v>
+      </c>
+      <c r="D94" s="8">
+        <v>-12.86</v>
+      </c>
+      <c r="E94" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="8">
+        <v>-6.17</v>
+      </c>
+      <c r="D95" s="8">
+        <v>-6.66</v>
+      </c>
+      <c r="E95" s="9">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="8">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="D96" s="8">
+        <v>-9.57</v>
+      </c>
+      <c r="E96" s="9">
         <v>-0.18</v>
       </c>
-      <c r="D10" s="7">
-        <v>-0.16</v>
-      </c>
-      <c r="E10" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="8">
+        <v>-2.17</v>
+      </c>
+      <c r="D97" s="8">
+        <v>-2.51</v>
+      </c>
+      <c r="E97" s="9">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="8">
+        <v>-2.65</v>
+      </c>
+      <c r="D98" s="8">
+        <v>-2.33</v>
+      </c>
+      <c r="E98" s="10">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="8">
+        <v>-4.97</v>
+      </c>
+      <c r="D99" s="8">
+        <v>-4.05</v>
+      </c>
+      <c r="E99" s="10">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="8">
+        <v>28851.8</v>
+      </c>
+      <c r="D100" s="8">
+        <v>28841.5</v>
+      </c>
+      <c r="E100" s="9">
+        <v>-10.3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="8">
+        <v>9809.15</v>
+      </c>
+      <c r="D101" s="8">
+        <v>9690.65</v>
+      </c>
+      <c r="E101" s="9">
+        <v>-118.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1.85</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-3.34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B102" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="8">
+        <v>11904.2</v>
+      </c>
+      <c r="D102" s="8">
+        <v>11802.7</v>
+      </c>
+      <c r="E102" s="9">
+        <v>-101.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-2.99</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E12" s="9">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B103" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="8">
+        <v>38003.65</v>
+      </c>
+      <c r="D103" s="8">
+        <v>37949.25</v>
+      </c>
+      <c r="E103" s="9">
+        <v>-54.4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-3.52</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-5.69</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B104" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="8">
+        <v>46815</v>
+      </c>
+      <c r="D104" s="8">
+        <v>46025.55</v>
+      </c>
+      <c r="E104" s="9">
+        <v>-789.45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-2.31</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0.13</v>
-      </c>
-      <c r="E14" s="9">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B105" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="8">
+        <v>26286.5</v>
+      </c>
+      <c r="D105" s="8">
+        <v>26293.65</v>
+      </c>
+      <c r="E105" s="10">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-2.9</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.28</v>
-      </c>
-      <c r="E15" s="9">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B106" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="8">
+        <v>31281.7</v>
+      </c>
+      <c r="D106" s="8">
+        <v>31191.45</v>
+      </c>
+      <c r="E106" s="9">
+        <v>-90.25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="7">
-        <v>3.14</v>
-      </c>
-      <c r="D16" s="7">
-        <v>2.62</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B107" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="8">
+        <v>16558.45</v>
+      </c>
+      <c r="D107" s="8">
+        <v>16582.95</v>
+      </c>
+      <c r="E107" s="10">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-1.1</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B108" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="8">
+        <v>9242.700000000001</v>
+      </c>
+      <c r="D108" s="8">
+        <v>9179.4</v>
+      </c>
+      <c r="E108" s="9">
+        <v>-63.3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="7">
-        <v>4.95</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.1</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B109" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" s="8">
+        <v>1602.9</v>
+      </c>
+      <c r="D109" s="8">
+        <v>1557.35</v>
+      </c>
+      <c r="E109" s="9">
+        <v>-45.55</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7">
-        <v>7.95</v>
-      </c>
-      <c r="D19" s="7">
-        <v>6.48</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B110" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="8">
+        <v>13525.35</v>
+      </c>
+      <c r="D110" s="8">
+        <v>13193.9</v>
+      </c>
+      <c r="E110" s="9">
+        <v>-331.45</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-2.38</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.06</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B111" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="8">
+        <v>9689.25</v>
+      </c>
+      <c r="D111" s="8">
+        <v>9704.4</v>
+      </c>
+      <c r="E111" s="10">
+        <v>15.15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="7">
-        <v>2.46</v>
-      </c>
-      <c r="D21" s="7">
-        <v>3.32</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B112" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" s="8">
+        <v>8604.299999999999</v>
+      </c>
+      <c r="D112" s="8">
+        <v>8609.549999999999</v>
+      </c>
+      <c r="E112" s="10">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7">
-        <v>1.8</v>
-      </c>
-      <c r="D22" s="7">
-        <v>2.45</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B113" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="8">
+        <v>26991.85</v>
+      </c>
+      <c r="D113" s="8">
+        <v>27186.45</v>
+      </c>
+      <c r="E113" s="10">
+        <v>194.6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-0.99</v>
-      </c>
-      <c r="D23" s="7">
-        <v>1.04</v>
-      </c>
-      <c r="E23" s="9">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B114" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="8">
+        <v>908.85</v>
+      </c>
+      <c r="D114" s="8">
+        <v>904.15</v>
+      </c>
+      <c r="E114" s="9">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-2.19</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-0.91</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B115" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" s="8">
+        <v>30900.2</v>
+      </c>
+      <c r="D115" s="8">
+        <v>30836.2</v>
+      </c>
+      <c r="E115" s="9">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D25" s="7">
-        <v>0.59</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B116" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" s="8">
+        <v>16798.5</v>
+      </c>
+      <c r="D116" s="8">
+        <v>16941.5</v>
+      </c>
+      <c r="E116" s="10">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>6.3</v>
-      </c>
-      <c r="D26" s="7">
-        <v>6.13</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B117" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="8">
+        <v>9751.65</v>
+      </c>
+      <c r="D117" s="8">
+        <v>9718.4</v>
+      </c>
+      <c r="E117" s="9">
+        <v>-33.25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-0.14</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-0.54</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B118" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="8">
+        <v>11067.7</v>
+      </c>
+      <c r="D118" s="8">
+        <v>11103.8</v>
+      </c>
+      <c r="E118" s="10">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-2.63</v>
-      </c>
-      <c r="D28" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B119" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="8">
+        <v>27737.2</v>
+      </c>
+      <c r="D119" s="8">
+        <v>28005.75</v>
+      </c>
+      <c r="E119" s="10">
+        <v>268.55</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120" s="8">
+        <v>44</v>
+      </c>
+      <c r="D120" s="8">
         <v>38</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-1.43</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-1.54</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="E120" s="9">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" s="8">
+        <v>38</v>
+      </c>
+      <c r="D121" s="8">
+        <v>50</v>
+      </c>
+      <c r="E121" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="8">
+        <v>50</v>
+      </c>
+      <c r="D122" s="8">
+        <v>62</v>
+      </c>
+      <c r="E122" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123" s="8">
+        <v>68</v>
+      </c>
+      <c r="D123" s="8">
+        <v>44</v>
+      </c>
+      <c r="E123" s="9">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" s="8">
+        <v>62</v>
+      </c>
+      <c r="D124" s="8">
+        <v>68</v>
+      </c>
+      <c r="E124" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C125" s="8">
+        <v>53.45</v>
+      </c>
+      <c r="D125" s="8">
+        <v>53.18</v>
+      </c>
+      <c r="E125" s="9">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="D30" s="7">
+      <c r="B126" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C126" s="8">
+        <v>44.36</v>
+      </c>
+      <c r="D126" s="8">
+        <v>35.26</v>
+      </c>
+      <c r="E126" s="9">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C127" s="8">
+        <v>44.97</v>
+      </c>
+      <c r="D127" s="8">
+        <v>39.38</v>
+      </c>
+      <c r="E127" s="9">
+        <v>-5.59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C128" s="8">
+        <v>32.08</v>
+      </c>
+      <c r="D128" s="8">
+        <v>31.05</v>
+      </c>
+      <c r="E128" s="9">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C129" s="8">
+        <v>30.61</v>
+      </c>
+      <c r="D129" s="8">
+        <v>25.16</v>
+      </c>
+      <c r="E129" s="9">
+        <v>-5.45</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C130" s="8">
+        <v>46.15</v>
+      </c>
+      <c r="D130" s="8">
+        <v>46.42</v>
+      </c>
+      <c r="E130" s="10">
         <v>0.27</v>
       </c>
-      <c r="E30" s="8">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-1.21</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-1.35</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-0.13</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-0.39</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-1.74</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-2.19</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="7">
-        <v>0.29</v>
-      </c>
-      <c r="D34" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-1.47</v>
-      </c>
-      <c r="D35" s="7">
-        <v>2.45</v>
-      </c>
-      <c r="E35" s="9">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B131" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C131" s="8">
+        <v>58.52</v>
+      </c>
+      <c r="D131" s="8">
+        <v>57.41</v>
+      </c>
+      <c r="E131" s="9">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C132" s="8">
+        <v>61.33</v>
+      </c>
+      <c r="D132" s="8">
+        <v>62.87</v>
+      </c>
+      <c r="E132" s="10">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-1.19</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-1.14</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B133" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C133" s="8">
+        <v>38.2</v>
+      </c>
+      <c r="D133" s="8">
+        <v>33.96</v>
+      </c>
+      <c r="E133" s="9">
+        <v>-4.24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-1.52</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-1.14</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B134" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C134" s="8">
+        <v>57.97</v>
+      </c>
+      <c r="D134" s="8">
+        <v>45.23</v>
+      </c>
+      <c r="E134" s="9">
+        <v>-12.74</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="7">
-        <v>2.79</v>
-      </c>
-      <c r="D38" s="7">
-        <v>3.56</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B135" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C135" s="8">
+        <v>67.39</v>
+      </c>
+      <c r="D135" s="8">
+        <v>53.42</v>
+      </c>
+      <c r="E135" s="9">
+        <v>-13.97</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-0.43</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-0.55</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B136" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C136" s="8">
+        <v>31.91</v>
+      </c>
+      <c r="D136" s="8">
+        <v>34.32</v>
+      </c>
+      <c r="E136" s="10">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-0.33</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-0.14</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B137" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C137" s="8">
+        <v>51.65</v>
+      </c>
+      <c r="D137" s="8">
+        <v>52.01</v>
+      </c>
+      <c r="E137" s="10">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="7">
-        <v>1.64</v>
-      </c>
-      <c r="D41" s="7">
-        <v>2.4</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B138" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C138" s="8">
+        <v>69.63</v>
+      </c>
+      <c r="D138" s="8">
+        <v>72.98</v>
+      </c>
+      <c r="E138" s="10">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="7">
-        <v>0.18</v>
-      </c>
-      <c r="D42" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B139" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C139" s="8">
+        <v>54.73</v>
+      </c>
+      <c r="D139" s="8">
+        <v>51.82</v>
+      </c>
+      <c r="E139" s="9">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="D43" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B140" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C140" s="8">
+        <v>45.78</v>
+      </c>
+      <c r="D140" s="8">
+        <v>43.96</v>
+      </c>
+      <c r="E140" s="9">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="7">
-        <v>1.47</v>
-      </c>
-      <c r="D44" s="7">
-        <v>2.02</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
+      <c r="B141" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141" s="8">
+        <v>64.84</v>
+      </c>
+      <c r="D141" s="8">
+        <v>69.66</v>
+      </c>
+      <c r="E141" s="10">
+        <v>4.82</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="7">
-        <v>0.01</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-0.51</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="B142" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C142" s="8">
+        <v>56.15</v>
+      </c>
+      <c r="D142" s="8">
+        <v>53.93</v>
+      </c>
+      <c r="E142" s="9">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-1.05</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-0.99</v>
-      </c>
-      <c r="E46" s="9">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="B143" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C143" s="8">
+        <v>39.19</v>
+      </c>
+      <c r="D143" s="8">
+        <v>43.05</v>
+      </c>
+      <c r="E143" s="10">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="7">
-        <v>1.13</v>
-      </c>
-      <c r="D47" s="7">
-        <v>1.05</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="7">
-        <v>13.46</v>
-      </c>
-      <c r="D48" s="7">
-        <v>13.28</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="7">
-        <v>10.92</v>
-      </c>
-      <c r="D49" s="7">
-        <v>10.6</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-2.2</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-3.18</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="7">
-        <v>9.59</v>
-      </c>
-      <c r="D51" s="7">
-        <v>9.06</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-15.85</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-17.38</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-1.17</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-0.76</v>
-      </c>
-      <c r="E53" s="9">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-13.05</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-12.35</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1.15</v>
-      </c>
-      <c r="D55" s="7">
-        <v>0.91</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="7">
-        <v>-4.48</v>
-      </c>
-      <c r="D56" s="7">
-        <v>-2.17</v>
-      </c>
-      <c r="E56" s="9">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="7">
-        <v>41.95</v>
-      </c>
-      <c r="D57" s="7">
-        <v>42.41</v>
-      </c>
-      <c r="E57" s="9">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="7">
-        <v>1.45</v>
-      </c>
-      <c r="D58" s="7">
-        <v>1.27</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="7">
-        <v>20.57</v>
-      </c>
-      <c r="D59" s="7">
-        <v>21.13</v>
-      </c>
-      <c r="E59" s="9">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="7">
-        <v>21.67</v>
-      </c>
-      <c r="D60" s="7">
-        <v>22.86</v>
-      </c>
-      <c r="E60" s="9">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="7">
-        <v>0.59</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-0.55</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-5.72</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-5.73</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="7">
-        <v>2.67</v>
-      </c>
-      <c r="D63" s="7">
-        <v>2.96</v>
-      </c>
-      <c r="E63" s="9">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="7">
-        <v>9.66</v>
-      </c>
-      <c r="D64" s="7">
-        <v>11.43</v>
-      </c>
-      <c r="E64" s="9">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-4.66</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-4.23</v>
-      </c>
-      <c r="E65" s="9">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66" s="7">
-        <v>5.86</v>
-      </c>
-      <c r="D66" s="7">
-        <v>7.4</v>
-      </c>
-      <c r="E66" s="9">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-6.79</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-5.59</v>
-      </c>
-      <c r="E67" s="9">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" s="7">
-        <v>-4.76</v>
-      </c>
-      <c r="D68" s="7">
-        <v>-2.97</v>
-      </c>
-      <c r="E68" s="9">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="7">
-        <v>3.65</v>
-      </c>
-      <c r="D69" s="7">
-        <v>5.11</v>
-      </c>
-      <c r="E69" s="9">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="7">
-        <v>3.92</v>
-      </c>
-      <c r="D70" s="7">
-        <v>4.78</v>
-      </c>
-      <c r="E70" s="9">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="7">
-        <v>-1.23</v>
-      </c>
-      <c r="D71" s="7">
-        <v>0.06</v>
-      </c>
-      <c r="E71" s="9">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="7">
-        <v>13.38</v>
-      </c>
-      <c r="D72" s="7">
-        <v>12.28</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-0.12</v>
-      </c>
-      <c r="D73" s="7">
-        <v>0.14</v>
-      </c>
-      <c r="E73" s="9">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-5.14</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-4.55</v>
-      </c>
-      <c r="E74" s="9">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="7">
-        <v>5.29</v>
-      </c>
-      <c r="D75" s="7">
-        <v>7.48</v>
-      </c>
-      <c r="E75" s="9">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="7">
-        <v>10.28</v>
-      </c>
-      <c r="D76" s="7">
-        <v>11.47</v>
-      </c>
-      <c r="E76" s="9">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="7">
-        <v>16.24</v>
-      </c>
-      <c r="D77" s="7">
-        <v>18.31</v>
-      </c>
-      <c r="E77" s="9">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="7">
-        <v>3.59</v>
-      </c>
-      <c r="D78" s="7">
-        <v>4.68</v>
-      </c>
-      <c r="E78" s="9">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="7">
-        <v>5.44</v>
-      </c>
-      <c r="D79" s="7">
-        <v>6.4</v>
-      </c>
-      <c r="E79" s="9">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-2.58</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-2.69</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-6.55</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-6.61</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-5.68</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-5.81</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-8.26</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-8.5</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="7">
-        <v>-17.64</v>
-      </c>
-      <c r="D84" s="7">
-        <v>-18.02</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="7">
-        <v>-7.67</v>
-      </c>
-      <c r="D85" s="7">
-        <v>-7.65</v>
-      </c>
-      <c r="E85" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="7">
-        <v>-23.47</v>
-      </c>
-      <c r="D86" s="7">
-        <v>-20.78</v>
-      </c>
-      <c r="E86" s="9">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="7">
-        <v>-5.41</v>
-      </c>
-      <c r="D87" s="7">
-        <v>-5.36</v>
-      </c>
-      <c r="E87" s="9">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="7">
-        <v>-3.46</v>
-      </c>
-      <c r="D88" s="7">
-        <v>-3.09</v>
-      </c>
-      <c r="E88" s="9">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C89" s="7">
-        <v>-2.14</v>
-      </c>
-      <c r="D89" s="7">
-        <v>-1.41</v>
-      </c>
-      <c r="E89" s="9">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="7">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="D90" s="7">
-        <v>-10</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="7">
-        <v>-13.08</v>
-      </c>
-      <c r="D91" s="7">
-        <v>-12.91</v>
-      </c>
-      <c r="E91" s="9">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C92" s="7">
-        <v>-6.1</v>
-      </c>
-      <c r="D92" s="7">
-        <v>-6.17</v>
-      </c>
-      <c r="E92" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" s="7">
-        <v>-9.83</v>
-      </c>
-      <c r="D93" s="7">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="E93" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="D94" s="7">
-        <v>0</v>
-      </c>
-      <c r="E94" s="9">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="7">
-        <v>-1.66</v>
-      </c>
-      <c r="D95" s="7">
-        <v>-2.17</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" s="7">
-        <v>-2.71</v>
-      </c>
-      <c r="D96" s="7">
-        <v>-2.65</v>
-      </c>
-      <c r="E96" s="9">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C97" s="7">
-        <v>-4.9</v>
-      </c>
-      <c r="D97" s="7">
-        <v>-4.97</v>
-      </c>
-      <c r="E97" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98" s="7">
-        <v>28883.5</v>
-      </c>
-      <c r="D98" s="7">
-        <v>28851.8</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-31.7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C99" s="7">
-        <v>9814.75</v>
-      </c>
-      <c r="D99" s="7">
-        <v>9809.15</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C100" s="7">
-        <v>11921.2</v>
-      </c>
-      <c r="D100" s="7">
-        <v>11904.2</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-17</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C101" s="7">
-        <v>38103.95</v>
-      </c>
-      <c r="D101" s="7">
-        <v>38003.65</v>
-      </c>
-      <c r="E101" s="8">
-        <v>-100.3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C102" s="7">
-        <v>47030.45</v>
-      </c>
-      <c r="D102" s="7">
-        <v>46815</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-215.45</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C103" s="7">
-        <v>26280.65</v>
-      </c>
-      <c r="D103" s="7">
-        <v>26286.5</v>
-      </c>
-      <c r="E103" s="9">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C104" s="7">
-        <v>30221.15</v>
-      </c>
-      <c r="D104" s="7">
-        <v>31281.7</v>
-      </c>
-      <c r="E104" s="9">
-        <v>1060.55</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C105" s="7">
-        <v>16558.8</v>
-      </c>
-      <c r="D105" s="7">
-        <v>16558.45</v>
-      </c>
-      <c r="E105" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="7">
-        <v>9237.799999999999</v>
-      </c>
-      <c r="D106" s="7">
-        <v>9242.700000000001</v>
-      </c>
-      <c r="E106" s="9">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C107" s="7">
-        <v>1596.7</v>
-      </c>
-      <c r="D107" s="7">
-        <v>1602.9</v>
-      </c>
-      <c r="E107" s="9">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C108" s="7">
-        <v>13425.2</v>
-      </c>
-      <c r="D108" s="7">
-        <v>13525.35</v>
-      </c>
-      <c r="E108" s="9">
-        <v>100.15</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C109" s="7">
-        <v>9701.549999999999</v>
-      </c>
-      <c r="D109" s="7">
-        <v>9689.25</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-12.3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C110" s="7">
-        <v>8587.799999999999</v>
-      </c>
-      <c r="D110" s="7">
-        <v>8604.299999999999</v>
-      </c>
-      <c r="E110" s="9">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C111" s="7">
-        <v>26848.75</v>
-      </c>
-      <c r="D111" s="7">
-        <v>26991.85</v>
-      </c>
-      <c r="E111" s="9">
-        <v>143.1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C112" s="7">
-        <v>909.6</v>
-      </c>
-      <c r="D112" s="7">
-        <v>908.85</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
-      <c r="A113" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" s="7">
-        <v>30750.1</v>
-      </c>
-      <c r="D113" s="7">
-        <v>30900.2</v>
-      </c>
-      <c r="E113" s="9">
-        <v>150.1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="A114" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C114" s="7">
-        <v>16707.7</v>
-      </c>
-      <c r="D114" s="7">
-        <v>16798.5</v>
-      </c>
-      <c r="E114" s="9">
-        <v>90.8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="A115" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C115" s="7">
-        <v>9802.35</v>
-      </c>
-      <c r="D115" s="7">
-        <v>9751.65</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-50.7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="A116" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C116" s="7">
-        <v>11060.65</v>
-      </c>
-      <c r="D116" s="7">
-        <v>11067.7</v>
-      </c>
-      <c r="E116" s="9">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="A117" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C117" s="7">
-        <v>27758.55</v>
-      </c>
-      <c r="D117" s="7">
-        <v>27737.2</v>
-      </c>
-      <c r="E117" s="8">
-        <v>-21.35</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="A118" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C118" s="7">
-        <v>50</v>
-      </c>
-      <c r="D118" s="7">
-        <v>44</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="A119" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C119" s="7">
-        <v>44</v>
-      </c>
-      <c r="D119" s="7">
-        <v>50</v>
-      </c>
-      <c r="E119" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="A120" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B120" s="6" t="s">
+      <c r="B144" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C120" s="7">
-        <v>54.23</v>
-      </c>
-      <c r="D120" s="7">
-        <v>53.45</v>
-      </c>
-      <c r="E120" s="8">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="A121" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C121" s="7">
-        <v>44.87</v>
-      </c>
-      <c r="D121" s="7">
-        <v>44.36</v>
-      </c>
-      <c r="E121" s="8">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="A122" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C122" s="7">
-        <v>45.99</v>
-      </c>
-      <c r="D122" s="7">
-        <v>44.97</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="A123" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C123" s="7">
-        <v>34.02</v>
-      </c>
-      <c r="D123" s="7">
-        <v>32.08</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="A124" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C124" s="7">
-        <v>32.39</v>
-      </c>
-      <c r="D124" s="7">
-        <v>30.61</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="A125" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C125" s="7">
-        <v>45.94</v>
-      </c>
-      <c r="D125" s="7">
-        <v>46.15</v>
-      </c>
-      <c r="E125" s="9">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="A126" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C126" s="7">
-        <v>47.38</v>
-      </c>
-      <c r="D126" s="7">
-        <v>58.52</v>
-      </c>
-      <c r="E126" s="9">
-        <v>11.14</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="A127" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C127" s="7">
-        <v>61.36</v>
-      </c>
-      <c r="D127" s="7">
-        <v>61.33</v>
-      </c>
-      <c r="E127" s="8">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="A128" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C128" s="7">
-        <v>37.64</v>
-      </c>
-      <c r="D128" s="7">
-        <v>38.2</v>
-      </c>
-      <c r="E128" s="9">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
-      <c r="A129" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C129" s="7">
-        <v>56.42</v>
-      </c>
-      <c r="D129" s="7">
-        <v>57.97</v>
-      </c>
-      <c r="E129" s="9">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
-      <c r="A130" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C130" s="7">
-        <v>64.81</v>
-      </c>
-      <c r="D130" s="7">
-        <v>67.39</v>
-      </c>
-      <c r="E130" s="9">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
-      <c r="A131" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C131" s="7">
-        <v>32.82</v>
-      </c>
-      <c r="D131" s="7">
-        <v>31.91</v>
-      </c>
-      <c r="E131" s="8">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
-      <c r="A132" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C132" s="7">
-        <v>50.59</v>
-      </c>
-      <c r="D132" s="7">
-        <v>51.65</v>
-      </c>
-      <c r="E132" s="9">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
-      <c r="A133" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C133" s="7">
-        <v>66.83</v>
-      </c>
-      <c r="D133" s="7">
-        <v>69.63</v>
-      </c>
-      <c r="E133" s="9">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
-      <c r="A134" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C134" s="7">
-        <v>55.19</v>
-      </c>
-      <c r="D134" s="7">
-        <v>54.73</v>
-      </c>
-      <c r="E134" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
-      <c r="A135" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C135" s="7">
-        <v>40.41</v>
-      </c>
-      <c r="D135" s="7">
-        <v>45.78</v>
-      </c>
-      <c r="E135" s="9">
-        <v>5.37</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
-      <c r="A136" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C136" s="7">
-        <v>61.22</v>
-      </c>
-      <c r="D136" s="7">
-        <v>64.84</v>
-      </c>
-      <c r="E136" s="9">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
-      <c r="A137" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C137" s="7">
-        <v>59.62</v>
-      </c>
-      <c r="D137" s="7">
-        <v>56.15</v>
-      </c>
-      <c r="E137" s="8">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
-      <c r="A138" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C138" s="7">
-        <v>38.43</v>
-      </c>
-      <c r="D138" s="7">
-        <v>39.19</v>
-      </c>
-      <c r="E138" s="9">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
-      <c r="A139" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C139" s="7">
-        <v>53.99</v>
-      </c>
-      <c r="D139" s="7">
+      <c r="C144" s="8">
         <v>53.3</v>
       </c>
-      <c r="E139" s="8">
-        <v>-0.6899999999999999</v>
+      <c r="D144" s="8">
+        <v>60.16</v>
+      </c>
+      <c r="E144" s="10">
+        <v>6.86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5710,60 +5818,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>116</v>
       </c>
+      <c r="H1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="12">
-        <v>51.24</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="13">
+        <v>47.24</v>
+      </c>
+      <c r="C2" s="14">
         <v>20</v>
       </c>
-      <c r="D2" s="12">
-        <v>50.1</v>
-      </c>
-      <c r="E2" s="12">
-        <v>50</v>
-      </c>
-      <c r="F2" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="G2" s="12">
-        <v>4.5</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="13">
+        <v>48.3</v>
+      </c>
+      <c r="E2" s="13">
+        <v>40</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.2</v>
+      </c>
+      <c r="G2" s="13">
+        <v>3.6</v>
+      </c>
+      <c r="H2" s="13">
         <v>53.1</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>40</v>
       </c>
     </row>
@@ -5865,131 +5973,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="15">
-        <v>0.4666</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.4417</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.3017</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.3002</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.2374</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.2178</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.1919</v>
-      </c>
-      <c r="H2" s="15">
-        <v>0.188</v>
-      </c>
-      <c r="I2" s="15">
-        <v>0.1479</v>
-      </c>
-      <c r="J2" s="15">
-        <v>0.1369</v>
+      <c r="A2" s="16">
+        <v>0.4782</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.4233</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.2982</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.2976</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.2351</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.2163</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.1851</v>
+      </c>
+      <c r="H2" s="16">
+        <v>0.1822</v>
+      </c>
+      <c r="I2" s="16">
+        <v>0.1428</v>
+      </c>
+      <c r="J2" s="16">
+        <v>0.1364</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="15">
-        <v>0.1344</v>
-      </c>
-      <c r="B4" s="15">
-        <v>0.1256</v>
-      </c>
-      <c r="C4" s="15">
-        <v>0.1195</v>
-      </c>
-      <c r="D4" s="15">
-        <v>0.08130000000000001</v>
-      </c>
-      <c r="E4" s="15">
-        <v>0.08070000000000001</v>
-      </c>
-      <c r="F4" s="15">
-        <v>0.0533</v>
-      </c>
-      <c r="G4" s="15">
-        <v>0.0365</v>
-      </c>
-      <c r="H4" s="15">
-        <v>0.0241</v>
-      </c>
-      <c r="I4" s="15">
-        <v>-0.0001</v>
-      </c>
-      <c r="J4" s="15">
-        <v>-0.0172</v>
+      <c r="A4" s="16">
+        <v>0.1334</v>
+      </c>
+      <c r="B4" s="16">
+        <v>0.1204</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.1132</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0.08259999999999999</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0.0779</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0.0498</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.0385</v>
+      </c>
+      <c r="H4" s="16">
+        <v>0.0309</v>
+      </c>
+      <c r="I4" s="16">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="J4" s="16">
+        <v>-0.0204</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="134">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,55 +289,100 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.4% → -3.8%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.4%</t>
-  </si>
-  <si>
-    <t>-3.8%</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>69.6 → 73.0</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>69.6</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.3% → -2.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.3%</t>
+  </si>
+  <si>
+    <t>-2.0%</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.2 → 32.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.2</t>
+  </si>
+  <si>
+    <t>32.3</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>73.0 → 58.9</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
   </si>
   <si>
     <t>73.0</t>
   </si>
   <si>
+    <t>58.9</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>58.0 → 45.2</t>
+    <t>53.2 → 44.9</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>58.0</t>
-  </si>
-  <si>
-    <t>45.2</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>53.2</t>
+  </si>
+  <si>
+    <t>44.9</t>
+  </si>
+  <si>
+    <t>62.9 → 47.7</t>
+  </si>
+  <si>
+    <t>62.9</t>
+  </si>
+  <si>
+    <t>47.7</t>
+  </si>
+  <si>
+    <t>52.0 → 45.0</t>
+  </si>
+  <si>
+    <t>52.0</t>
+  </si>
+  <si>
+    <t>45.0</t>
+  </si>
+  <si>
+    <t>51.8 → 44.8</t>
+  </si>
+  <si>
+    <t>51.8</t>
+  </si>
+  <si>
+    <t>44.8</t>
+  </si>
+  <si>
+    <t>53.9 → 49.5</t>
+  </si>
+  <si>
+    <t>53.9</t>
+  </si>
+  <si>
+    <t>49.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -389,7 +434,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,14 +468,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -442,15 +487,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,25 +515,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,11 +610,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -591,7 +623,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1095,10 +1127,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>28841.5</v>
+        <v>28491.05</v>
       </c>
       <c r="E2">
-        <v>-0.04</v>
+        <v>-1.22</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1107,43 +1139,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-2.72</v>
+        <v>-3.9</v>
       </c>
       <c r="I2">
-        <v>21.34</v>
+        <v>19.86</v>
       </c>
       <c r="J2">
-        <v>-0.89</v>
+        <v>-2.48</v>
       </c>
       <c r="K2">
-        <v>0.34</v>
+        <v>-2.32</v>
       </c>
       <c r="L2">
-        <v>10.59</v>
+        <v>9.19</v>
       </c>
       <c r="M2">
-        <v>13.65</v>
+        <v>12.48</v>
       </c>
       <c r="N2">
-        <v>23.51</v>
+        <v>23.19</v>
       </c>
       <c r="O2">
         <v>81</v>
       </c>
       <c r="Q2">
-        <v>28958.77</v>
+        <v>28813.6</v>
       </c>
       <c r="R2">
-        <v>29219.13</v>
+        <v>29191.62</v>
       </c>
       <c r="S2">
-        <v>27934.42</v>
+        <v>27970.17</v>
       </c>
       <c r="T2">
-        <v>27118.96</v>
+        <v>27127.12</v>
       </c>
       <c r="U2">
-        <v>6.35</v>
+        <v>5.03</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1158,31 +1190,31 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>53.18</v>
+        <v>44.91</v>
       </c>
       <c r="AA2">
-        <v>274.08</v>
+        <v>211.53</v>
       </c>
       <c r="AB2">
-        <v>417.21</v>
+        <v>376.08</v>
       </c>
       <c r="AC2">
-        <v>-143.14</v>
+        <v>-164.55</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>331.79</v>
+        <v>368.54</v>
       </c>
       <c r="AH2">
-        <v>29678.66</v>
+        <v>29751.01</v>
       </c>
       <c r="AI2">
-        <v>28759.59</v>
+        <v>28632.22</v>
       </c>
       <c r="AJ2">
         <v>28374.42</v>
@@ -1191,7 +1223,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>29.81</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1205,10 +1237,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9690.65</v>
+        <v>9704.200000000001</v>
       </c>
       <c r="E3">
-        <v>-1.21</v>
+        <v>0.14</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1217,43 +1249,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-7.74</v>
+        <v>-7.61</v>
       </c>
       <c r="I3">
-        <v>13.05</v>
+        <v>13.21</v>
       </c>
       <c r="J3">
-        <v>-1.59</v>
+        <v>-1.64</v>
       </c>
       <c r="K3">
-        <v>-1.73</v>
+        <v>-2.99</v>
       </c>
       <c r="L3">
-        <v>-5.2</v>
+        <v>-4.9</v>
       </c>
       <c r="M3">
-        <v>9.41</v>
+        <v>10.76</v>
       </c>
       <c r="N3">
-        <v>12.04</v>
+        <v>12.19</v>
       </c>
       <c r="O3">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Q3">
-        <v>9811.51</v>
+        <v>9779.08</v>
       </c>
       <c r="R3">
-        <v>9866.290000000001</v>
+        <v>9855.059999999999</v>
       </c>
       <c r="S3">
-        <v>9863.280000000001</v>
+        <v>9854.879999999999</v>
       </c>
       <c r="T3">
-        <v>9737.620000000001</v>
+        <v>9739.66</v>
       </c>
       <c r="U3">
-        <v>-0.48</v>
+        <v>-0.36</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1268,40 +1300,40 @@
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>35.26</v>
+        <v>36.85</v>
       </c>
       <c r="AA3">
-        <v>-30.48</v>
+        <v>-37.2</v>
       </c>
       <c r="AB3">
-        <v>-19.67</v>
+        <v>-23.17</v>
       </c>
       <c r="AC3">
-        <v>-10.81</v>
+        <v>-14.02</v>
       </c>
       <c r="AD3">
-        <v>26.69</v>
+        <v>19.41</v>
       </c>
       <c r="AE3">
-        <v>40.72</v>
+        <v>30.89</v>
       </c>
       <c r="AF3">
-        <v>87.2</v>
+        <v>87.23</v>
       </c>
       <c r="AH3">
-        <v>10039.85</v>
+        <v>10040.27</v>
       </c>
       <c r="AI3">
-        <v>9692.73</v>
+        <v>9669.85</v>
       </c>
       <c r="AJ3">
-        <v>9988.549999999999</v>
+        <v>9972.129999999999</v>
       </c>
       <c r="AK3" t="s">
         <v>82</v>
       </c>
       <c r="AL3">
-        <v>30.83</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1315,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11802.7</v>
+        <v>11782.3</v>
       </c>
       <c r="E4">
-        <v>-0.85</v>
+        <v>-0.17</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1327,43 +1359,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-6.62</v>
+        <v>-6.78</v>
       </c>
       <c r="I4">
-        <v>14.21</v>
+        <v>14.01</v>
       </c>
       <c r="J4">
-        <v>-1.72</v>
+        <v>-2.58</v>
       </c>
       <c r="K4">
-        <v>-2.31</v>
+        <v>-3.89</v>
       </c>
       <c r="L4">
-        <v>5.7</v>
+        <v>5.81</v>
       </c>
       <c r="M4">
-        <v>-3.72</v>
+        <v>-3.39</v>
       </c>
       <c r="N4">
-        <v>11.32</v>
+        <v>11.13</v>
       </c>
       <c r="O4">
         <v>38</v>
       </c>
       <c r="Q4">
-        <v>11938.07</v>
+        <v>11875.72</v>
       </c>
       <c r="R4">
-        <v>12072.38</v>
+        <v>12051.02</v>
       </c>
       <c r="S4">
-        <v>11861.75</v>
+        <v>11865.24</v>
       </c>
       <c r="T4">
-        <v>11684.97</v>
+        <v>11682.76</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1378,40 +1410,40 @@
         <v>3</v>
       </c>
       <c r="Z4">
-        <v>39.38</v>
+        <v>38.35</v>
       </c>
       <c r="AA4">
-        <v>10.04</v>
+        <v>-6.28</v>
       </c>
       <c r="AB4">
-        <v>56.83</v>
+        <v>44.21</v>
       </c>
       <c r="AC4">
-        <v>-46.79</v>
+        <v>-50.48</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>101.58</v>
+        <v>104.6</v>
       </c>
       <c r="AH4">
-        <v>12305.78</v>
+        <v>12308.57</v>
       </c>
       <c r="AI4">
-        <v>11838.97</v>
+        <v>11793.48</v>
       </c>
       <c r="AJ4">
-        <v>12145.9</v>
+        <v>12108.84</v>
       </c>
       <c r="AK4" t="s">
         <v>82</v>
       </c>
       <c r="AL4">
-        <v>19.9</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1425,10 +1457,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>37949.25</v>
+        <v>37806.1</v>
       </c>
       <c r="E5">
-        <v>-0.14</v>
+        <v>-0.38</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1437,43 +1469,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-8.630000000000001</v>
+        <v>-8.98</v>
       </c>
       <c r="I5">
-        <v>14.66</v>
+        <v>14.22</v>
       </c>
       <c r="J5">
-        <v>-1.01</v>
+        <v>-1.32</v>
       </c>
       <c r="K5">
-        <v>-2.01</v>
+        <v>-2.9</v>
       </c>
       <c r="L5">
-        <v>-5.57</v>
+        <v>-5.95</v>
       </c>
       <c r="M5">
-        <v>9.42</v>
+        <v>9.56</v>
       </c>
       <c r="N5">
-        <v>13.34</v>
+        <v>13.18</v>
       </c>
       <c r="O5">
         <v>50</v>
       </c>
       <c r="Q5">
-        <v>38093.52</v>
+        <v>37992.57</v>
       </c>
       <c r="R5">
-        <v>38450.61</v>
+        <v>38400.08</v>
       </c>
       <c r="S5">
-        <v>38995.57</v>
+        <v>38936.21</v>
       </c>
       <c r="T5">
-        <v>37456.04</v>
+        <v>37465.46</v>
       </c>
       <c r="U5">
-        <v>1.32</v>
+        <v>0.91</v>
       </c>
       <c r="V5" t="s">
         <v>80</v>
@@ -1488,40 +1520,40 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>31.05</v>
+        <v>28.46</v>
       </c>
       <c r="AA5">
-        <v>-282.82</v>
+        <v>-296.83</v>
       </c>
       <c r="AB5">
-        <v>-258.66</v>
+        <v>-266.29</v>
       </c>
       <c r="AC5">
-        <v>-24.16</v>
+        <v>-30.53</v>
       </c>
       <c r="AD5">
-        <v>10.4</v>
+        <v>2.35</v>
       </c>
       <c r="AE5">
-        <v>21.3</v>
+        <v>10.25</v>
       </c>
       <c r="AF5">
-        <v>341.8</v>
+        <v>338.28</v>
       </c>
       <c r="AH5">
-        <v>39068.95</v>
+        <v>39056.47</v>
       </c>
       <c r="AI5">
-        <v>37832.27</v>
+        <v>37743.7</v>
       </c>
       <c r="AJ5">
-        <v>38865.56</v>
+        <v>38783.5</v>
       </c>
       <c r="AK5" t="s">
         <v>82</v>
       </c>
       <c r="AL5">
-        <v>24.58</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1535,10 +1567,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>46025.55</v>
+        <v>46457.15</v>
       </c>
       <c r="E6">
-        <v>-1.69</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1547,43 +1579,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-19.4</v>
+        <v>-18.64</v>
       </c>
       <c r="I6">
-        <v>1.07</v>
+        <v>2.02</v>
       </c>
       <c r="J6">
-        <v>-3.16</v>
+        <v>-2.62</v>
       </c>
       <c r="K6">
-        <v>-6.3</v>
+        <v>-7.02</v>
       </c>
       <c r="L6">
-        <v>-5.32</v>
+        <v>-3.46</v>
       </c>
       <c r="M6">
-        <v>-18.25</v>
+        <v>-16.65</v>
       </c>
       <c r="N6">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>46966.17</v>
+        <v>46716.21</v>
       </c>
       <c r="R6">
-        <v>48157.39</v>
+        <v>48003.89</v>
       </c>
       <c r="S6">
-        <v>48750.66</v>
+        <v>48692.7</v>
       </c>
       <c r="T6">
-        <v>50745.45</v>
+        <v>50701.06</v>
       </c>
       <c r="U6">
-        <v>-9.300000000000001</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="V6" t="s">
         <v>80</v>
@@ -1598,31 +1630,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>25.16</v>
+        <v>32.26</v>
       </c>
       <c r="AA6">
-        <v>-617.3099999999999</v>
+        <v>-648.84</v>
       </c>
       <c r="AB6">
-        <v>-423.45</v>
+        <v>-468.53</v>
       </c>
       <c r="AC6">
-        <v>-193.87</v>
+        <v>-180.32</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>11.14</v>
       </c>
       <c r="AE6">
-        <v>4.76</v>
+        <v>4.54</v>
       </c>
       <c r="AF6">
-        <v>573.86</v>
+        <v>574.98</v>
       </c>
       <c r="AH6">
-        <v>50154.02</v>
+        <v>50028.97</v>
       </c>
       <c r="AI6">
-        <v>46160.75</v>
+        <v>45978.81</v>
       </c>
       <c r="AJ6">
         <v>48094.23</v>
@@ -1631,7 +1663,7 @@
         <v>82</v>
       </c>
       <c r="AL6">
-        <v>52.65</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1645,10 +1677,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26293.65</v>
+        <v>26003.9</v>
       </c>
       <c r="E7">
-        <v>0.03</v>
+        <v>-1.1</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1657,43 +1689,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-7.62</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="I7">
-        <v>11.78</v>
+        <v>10.55</v>
       </c>
       <c r="J7">
-        <v>0.52</v>
+        <v>-0.93</v>
       </c>
       <c r="K7">
-        <v>-1.13</v>
+        <v>-3.63</v>
       </c>
       <c r="L7">
-        <v>5.76</v>
+        <v>4.2</v>
       </c>
       <c r="M7">
-        <v>-1.05</v>
+        <v>-1.19</v>
       </c>
       <c r="N7">
-        <v>7.79</v>
+        <v>7.59</v>
       </c>
       <c r="O7">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="Q7">
-        <v>26298.9</v>
+        <v>26250.29</v>
       </c>
       <c r="R7">
-        <v>26368.16</v>
+        <v>26326.12</v>
       </c>
       <c r="S7">
-        <v>26593.43</v>
+        <v>26581.8</v>
       </c>
       <c r="T7">
-        <v>26663.66</v>
+        <v>26657.15</v>
       </c>
       <c r="U7">
-        <v>-1.39</v>
+        <v>-2.45</v>
       </c>
       <c r="V7" t="s">
         <v>80</v>
@@ -1708,40 +1740,40 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>46.42</v>
+        <v>38.12</v>
       </c>
       <c r="AA7">
-        <v>-89.95999999999999</v>
+        <v>-106.58</v>
       </c>
       <c r="AB7">
-        <v>-96.15000000000001</v>
+        <v>-98.23999999999999</v>
       </c>
       <c r="AC7">
-        <v>6.19</v>
+        <v>-8.34</v>
       </c>
       <c r="AD7">
-        <v>77.76000000000001</v>
+        <v>58</v>
       </c>
       <c r="AE7">
-        <v>78.84</v>
+        <v>73.44</v>
       </c>
       <c r="AF7">
-        <v>255.79</v>
+        <v>265.89</v>
       </c>
       <c r="AH7">
-        <v>26854.22</v>
+        <v>26783.22</v>
       </c>
       <c r="AI7">
-        <v>25882.09</v>
+        <v>25869.01</v>
       </c>
       <c r="AJ7">
-        <v>26900.75</v>
+        <v>26843.86</v>
       </c>
       <c r="AK7" t="s">
         <v>82</v>
       </c>
       <c r="AL7">
-        <v>24.12</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1755,10 +1787,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31191.45</v>
+        <v>31496.7</v>
       </c>
       <c r="E8">
-        <v>-0.29</v>
+        <v>0.98</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1767,43 +1799,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-21.01</v>
+        <v>-20.24</v>
       </c>
       <c r="I8">
-        <v>21.04</v>
+        <v>22.22</v>
       </c>
       <c r="J8">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="K8">
-        <v>1.57</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L8">
-        <v>0.24</v>
+        <v>7.19</v>
       </c>
       <c r="M8">
-        <v>-12.69</v>
+        <v>-11.13</v>
       </c>
       <c r="N8">
-        <v>-2.04</v>
+        <v>-1.58</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>30756.99</v>
+        <v>30901.97</v>
       </c>
       <c r="R8">
-        <v>31039.99</v>
+        <v>31042.12</v>
       </c>
       <c r="S8">
-        <v>29498.48</v>
+        <v>29575.84</v>
       </c>
       <c r="T8">
-        <v>32294.22</v>
+        <v>32273.26</v>
       </c>
       <c r="U8">
-        <v>-3.41</v>
+        <v>-2.41</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1818,34 +1850,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>57.41</v>
+        <v>60.17</v>
       </c>
       <c r="AA8">
-        <v>250.95</v>
+        <v>286.75</v>
       </c>
       <c r="AB8">
-        <v>346</v>
+        <v>334.15</v>
       </c>
       <c r="AC8">
-        <v>-95.05</v>
+        <v>-47.39</v>
       </c>
       <c r="AD8">
-        <v>39</v>
+        <v>66.28</v>
       </c>
       <c r="AE8">
-        <v>22.27</v>
+        <v>41.09</v>
       </c>
       <c r="AF8">
-        <v>619.67</v>
+        <v>625.0599999999999</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32065.44</v>
+        <v>32071.35</v>
       </c>
       <c r="AI8">
-        <v>30014.55</v>
+        <v>30012.89</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1854,7 +1886,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>20.97</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1868,10 +1900,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16582.95</v>
+        <v>16402.5</v>
       </c>
       <c r="E9">
-        <v>0.15</v>
+        <v>-1.09</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1880,28 +1912,28 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-0.48</v>
+        <v>-1.56</v>
       </c>
       <c r="I9">
-        <v>5.87</v>
+        <v>4.72</v>
       </c>
       <c r="J9">
-        <v>0.43</v>
+        <v>-1.07</v>
       </c>
       <c r="K9">
-        <v>1.56</v>
+        <v>-0.72</v>
       </c>
       <c r="N9">
-        <v>29.76</v>
+        <v>23.12</v>
       </c>
       <c r="Q9">
-        <v>16569.46</v>
+        <v>16534.06</v>
       </c>
       <c r="R9">
-        <v>16569.72</v>
+        <v>16565.05</v>
       </c>
       <c r="S9">
-        <v>16215.81</v>
+        <v>16221.32</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1913,31 +1945,31 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>62.87</v>
+        <v>47.73</v>
       </c>
       <c r="AA9">
-        <v>99.23</v>
+        <v>80.62</v>
       </c>
       <c r="AB9">
-        <v>121.54</v>
+        <v>113.36</v>
       </c>
       <c r="AC9">
-        <v>-22.31</v>
+        <v>-32.74</v>
       </c>
       <c r="AD9">
-        <v>30.2</v>
+        <v>22.48</v>
       </c>
       <c r="AE9">
-        <v>28.2</v>
+        <v>26.26</v>
       </c>
       <c r="AF9">
-        <v>123.69</v>
+        <v>132.94</v>
       </c>
       <c r="AH9">
-        <v>16673.15</v>
+        <v>16688.94</v>
       </c>
       <c r="AI9">
-        <v>16466.3</v>
+        <v>16441.15</v>
       </c>
       <c r="AJ9">
         <v>16247.63</v>
@@ -1946,7 +1978,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>19.57</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1960,10 +1992,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9179.4</v>
+        <v>9209.25</v>
       </c>
       <c r="E10">
-        <v>-0.68</v>
+        <v>0.33</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1972,43 +2004,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-6</v>
+        <v>-5.7</v>
       </c>
       <c r="I10">
-        <v>7.22</v>
+        <v>7.57</v>
       </c>
       <c r="J10">
-        <v>-1.75</v>
+        <v>-2.04</v>
       </c>
       <c r="K10">
-        <v>-2.44</v>
+        <v>-3.14</v>
       </c>
       <c r="L10">
-        <v>-0.51</v>
+        <v>-0.11</v>
       </c>
       <c r="M10">
-        <v>0.06</v>
+        <v>1.13</v>
       </c>
       <c r="N10">
-        <v>14.28</v>
+        <v>14.27</v>
       </c>
       <c r="O10">
         <v>32</v>
       </c>
       <c r="Q10">
-        <v>9270.02</v>
+        <v>9231.6</v>
       </c>
       <c r="R10">
-        <v>9369.6</v>
+        <v>9359.09</v>
       </c>
       <c r="S10">
-        <v>9390.280000000001</v>
+        <v>9383.450000000001</v>
       </c>
       <c r="T10">
-        <v>9351.559999999999</v>
+        <v>9350.5</v>
       </c>
       <c r="U10">
-        <v>-1.84</v>
+        <v>-1.51</v>
       </c>
       <c r="V10" t="s">
         <v>80</v>
@@ -2023,31 +2055,31 @@
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>33.96</v>
+        <v>37.48</v>
       </c>
       <c r="AA10">
-        <v>-40.67</v>
+        <v>-45.48</v>
       </c>
       <c r="AB10">
-        <v>-18.38</v>
+        <v>-23.8</v>
       </c>
       <c r="AC10">
-        <v>-22.29</v>
+        <v>-21.68</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AE10">
-        <v>7.78</v>
+        <v>3.98</v>
       </c>
       <c r="AF10">
-        <v>81.77</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="AH10">
-        <v>9537.379999999999</v>
+        <v>9539.559999999999</v>
       </c>
       <c r="AI10">
-        <v>9201.83</v>
+        <v>9178.610000000001</v>
       </c>
       <c r="AJ10">
         <v>9431.969999999999</v>
@@ -2056,7 +2088,7 @@
         <v>82</v>
       </c>
       <c r="AL10">
-        <v>39.36</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2070,55 +2102,55 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1557.35</v>
+        <v>1561.45</v>
       </c>
       <c r="E11">
-        <v>-2.84</v>
+        <v>0.26</v>
       </c>
       <c r="F11">
-        <v>1653.95</v>
+        <v>1632.5</v>
       </c>
       <c r="G11">
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-5.84</v>
+        <v>-4.35</v>
       </c>
       <c r="I11">
-        <v>24.25</v>
+        <v>24.58</v>
       </c>
       <c r="J11">
-        <v>-2.87</v>
+        <v>-3.02</v>
       </c>
       <c r="K11">
-        <v>-3.79</v>
+        <v>-0.46</v>
       </c>
       <c r="L11">
-        <v>8.960000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M11">
-        <v>-4.95</v>
+        <v>-5.59</v>
       </c>
       <c r="N11">
-        <v>-0.5600000000000001</v>
+        <v>-0.62</v>
       </c>
       <c r="O11">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="Q11">
-        <v>1595.59</v>
+        <v>1585.88</v>
       </c>
       <c r="R11">
-        <v>1587.5</v>
+        <v>1585.55</v>
       </c>
       <c r="S11">
-        <v>1545.21</v>
+        <v>1545.7</v>
       </c>
       <c r="T11">
-        <v>1446.66</v>
+        <v>1447.1</v>
       </c>
       <c r="U11">
-        <v>7.65</v>
+        <v>7.9</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2133,31 +2165,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>45.23</v>
+        <v>46.37</v>
       </c>
       <c r="AA11">
-        <v>14.79</v>
+        <v>11.28</v>
       </c>
       <c r="AB11">
-        <v>19.76</v>
+        <v>18.07</v>
       </c>
       <c r="AC11">
-        <v>-4.97</v>
+        <v>-6.79</v>
       </c>
       <c r="AD11">
-        <v>19.47</v>
+        <v>13.79</v>
       </c>
       <c r="AE11">
-        <v>36.48</v>
+        <v>24.64</v>
       </c>
       <c r="AF11">
-        <v>32.85</v>
+        <v>32.21</v>
       </c>
       <c r="AH11">
-        <v>1632.41</v>
+        <v>1631.46</v>
       </c>
       <c r="AI11">
-        <v>1542.6</v>
+        <v>1539.64</v>
       </c>
       <c r="AJ11">
         <v>1523.72</v>
@@ -2166,7 +2198,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>42.01</v>
+        <v>43.03</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2180,10 +2212,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13193.9</v>
+        <v>13189.85</v>
       </c>
       <c r="E12">
-        <v>-2.45</v>
+        <v>-0.03</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2192,43 +2224,43 @@
         <v>9154.799999999999</v>
       </c>
       <c r="H12">
-        <v>-3.82</v>
+        <v>-3.85</v>
       </c>
       <c r="I12">
-        <v>44.12</v>
+        <v>44.08</v>
       </c>
       <c r="J12">
-        <v>-1.4</v>
+        <v>-1.36</v>
       </c>
       <c r="K12">
-        <v>3.73</v>
+        <v>2.13</v>
       </c>
       <c r="L12">
-        <v>-2.68</v>
+        <v>-2.55</v>
       </c>
       <c r="M12">
-        <v>38.98</v>
+        <v>40.68</v>
       </c>
       <c r="N12">
-        <v>18.22</v>
+        <v>18.64</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13411.69</v>
+        <v>13375.2</v>
       </c>
       <c r="R12">
-        <v>13190.5</v>
+        <v>13198.38</v>
       </c>
       <c r="S12">
-        <v>12814.84</v>
+        <v>12816.81</v>
       </c>
       <c r="T12">
-        <v>12079.48</v>
+        <v>12093.01</v>
       </c>
       <c r="U12">
-        <v>9.23</v>
+        <v>9.07</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2243,31 +2275,31 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>53.42</v>
+        <v>53.28</v>
       </c>
       <c r="AA12">
-        <v>158.78</v>
+        <v>141.47</v>
       </c>
       <c r="AB12">
-        <v>144.56</v>
+        <v>143.94</v>
       </c>
       <c r="AC12">
-        <v>14.21</v>
+        <v>-2.47</v>
       </c>
       <c r="AD12">
-        <v>48.34</v>
+        <v>26.65</v>
       </c>
       <c r="AE12">
-        <v>70.88</v>
+        <v>52.22</v>
       </c>
       <c r="AF12">
-        <v>205.34</v>
+        <v>207.98</v>
       </c>
       <c r="AH12">
-        <v>13541.26</v>
+        <v>13541.17</v>
       </c>
       <c r="AI12">
-        <v>12839.74</v>
+        <v>12855.59</v>
       </c>
       <c r="AJ12">
         <v>12921.88</v>
@@ -2276,7 +2308,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>34.84</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2290,10 +2322,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9704.4</v>
+        <v>9659.5</v>
       </c>
       <c r="E13">
-        <v>0.16</v>
+        <v>-0.46</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2302,43 +2334,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-9.859999999999999</v>
+        <v>-10.28</v>
       </c>
       <c r="I13">
-        <v>5.45</v>
+        <v>4.97</v>
       </c>
       <c r="J13">
-        <v>-0.79</v>
+        <v>-1.41</v>
       </c>
       <c r="K13">
-        <v>-2.39</v>
+        <v>-3.46</v>
       </c>
       <c r="L13">
-        <v>-3.75</v>
+        <v>-4.26</v>
       </c>
       <c r="M13">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="N13">
-        <v>21.63</v>
+        <v>21.54</v>
       </c>
       <c r="O13">
         <v>19</v>
       </c>
       <c r="Q13">
-        <v>9724.08</v>
+        <v>9696.51</v>
       </c>
       <c r="R13">
-        <v>9819</v>
+        <v>9805.08</v>
       </c>
       <c r="S13">
-        <v>9906.540000000001</v>
+        <v>9894.799999999999</v>
       </c>
       <c r="T13">
-        <v>10038.01</v>
+        <v>10036.8</v>
       </c>
       <c r="U13">
-        <v>-3.32</v>
+        <v>-3.76</v>
       </c>
       <c r="V13" t="s">
         <v>80</v>
@@ -2353,31 +2385,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>34.32</v>
+        <v>30.83</v>
       </c>
       <c r="AA13">
-        <v>-62.87</v>
+        <v>-66.40000000000001</v>
       </c>
       <c r="AB13">
-        <v>-53.72</v>
+        <v>-56.25</v>
       </c>
       <c r="AC13">
-        <v>-9.15</v>
+        <v>-10.15</v>
       </c>
       <c r="AD13">
         <v>6.1</v>
       </c>
       <c r="AE13">
-        <v>11.97</v>
+        <v>5.85</v>
       </c>
       <c r="AF13">
-        <v>89.31</v>
+        <v>88.52</v>
       </c>
       <c r="AH13">
-        <v>9989.92</v>
+        <v>9980.51</v>
       </c>
       <c r="AI13">
-        <v>9648.07</v>
+        <v>9629.639999999999</v>
       </c>
       <c r="AJ13">
         <v>9916.76</v>
@@ -2386,7 +2418,7 @@
         <v>82</v>
       </c>
       <c r="AL13">
-        <v>35.57</v>
+        <v>37.59</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2400,10 +2432,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8609.549999999999</v>
+        <v>8505.75</v>
       </c>
       <c r="E14">
-        <v>0.06</v>
+        <v>-1.21</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2412,43 +2444,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-12.86</v>
+        <v>-13.91</v>
       </c>
       <c r="I14">
-        <v>27.43</v>
+        <v>25.9</v>
       </c>
       <c r="J14">
-        <v>0.82</v>
+        <v>-1.14</v>
       </c>
       <c r="K14">
-        <v>2.9</v>
+        <v>0.22</v>
       </c>
       <c r="L14">
-        <v>6.96</v>
+        <v>3.91</v>
       </c>
       <c r="M14">
-        <v>21.65</v>
+        <v>21.54</v>
       </c>
       <c r="N14">
-        <v>29.82</v>
+        <v>29.29</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8614.959999999999</v>
+        <v>8595.379999999999</v>
       </c>
       <c r="R14">
-        <v>8647.610000000001</v>
+        <v>8648.9</v>
       </c>
       <c r="S14">
-        <v>8512.43</v>
+        <v>8507.26</v>
       </c>
       <c r="T14">
-        <v>8596.379999999999</v>
+        <v>8597.209999999999</v>
       </c>
       <c r="U14">
-        <v>0.15</v>
+        <v>-1.06</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2460,34 +2492,34 @@
         <v>80</v>
       </c>
       <c r="Y14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z14">
-        <v>52.01</v>
+        <v>45.02</v>
       </c>
       <c r="AA14">
-        <v>30.95</v>
+        <v>19.84</v>
       </c>
       <c r="AB14">
-        <v>45.88</v>
+        <v>40.67</v>
       </c>
       <c r="AC14">
-        <v>-14.93</v>
+        <v>-20.83</v>
       </c>
       <c r="AD14">
-        <v>18.39</v>
+        <v>13.72</v>
       </c>
       <c r="AE14">
-        <v>21.78</v>
+        <v>18.56</v>
       </c>
       <c r="AF14">
-        <v>123.06</v>
+        <v>124.72</v>
       </c>
       <c r="AH14">
-        <v>8825.67</v>
+        <v>8822.15</v>
       </c>
       <c r="AI14">
-        <v>8469.540000000001</v>
+        <v>8475.65</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
@@ -2496,7 +2528,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>19.05</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2510,10 +2542,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>27186.45</v>
+        <v>26792.65</v>
       </c>
       <c r="E15">
-        <v>0.72</v>
+        <v>-1.45</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2522,43 +2554,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>-1.45</v>
       </c>
       <c r="I15">
-        <v>26.72</v>
+        <v>24.88</v>
       </c>
       <c r="J15">
-        <v>3.22</v>
+        <v>0.86</v>
       </c>
       <c r="K15">
-        <v>2.46</v>
+        <v>0.49</v>
       </c>
       <c r="L15">
-        <v>13.25</v>
+        <v>11.23</v>
       </c>
       <c r="M15">
-        <v>22.58</v>
+        <v>20.34</v>
       </c>
       <c r="N15">
-        <v>13.64</v>
+        <v>13.35</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26843.47</v>
+        <v>26889.2</v>
       </c>
       <c r="R15">
-        <v>26592.31</v>
+        <v>26602.07</v>
       </c>
       <c r="S15">
-        <v>26056.03</v>
+        <v>26096.62</v>
       </c>
       <c r="T15">
-        <v>23722.36</v>
+        <v>23744.42</v>
       </c>
       <c r="U15">
-        <v>14.6</v>
+        <v>12.84</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2573,34 +2605,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>72.98</v>
+        <v>58.85</v>
       </c>
       <c r="AA15">
-        <v>237.63</v>
+        <v>228.35</v>
       </c>
       <c r="AB15">
-        <v>212.1</v>
+        <v>215.35</v>
       </c>
       <c r="AC15">
-        <v>25.52</v>
+        <v>13</v>
       </c>
       <c r="AD15">
-        <v>95.08</v>
+        <v>75.78</v>
       </c>
       <c r="AE15">
-        <v>78.13</v>
+        <v>83.38</v>
       </c>
       <c r="AF15">
-        <v>300.72</v>
+        <v>315.18</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27047.23</v>
+        <v>27065.75</v>
       </c>
       <c r="AI15">
-        <v>26137.38</v>
+        <v>26138.38</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
@@ -2609,7 +2641,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>31.96</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2623,10 +2655,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>904.15</v>
+        <v>891.3</v>
       </c>
       <c r="E16">
-        <v>-0.52</v>
+        <v>-1.42</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2635,43 +2667,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-6.66</v>
+        <v>-7.99</v>
       </c>
       <c r="I16">
-        <v>38.85</v>
+        <v>36.88</v>
       </c>
       <c r="J16">
-        <v>-1.41</v>
+        <v>-2.89</v>
       </c>
       <c r="K16">
-        <v>0.3</v>
+        <v>-2.38</v>
       </c>
       <c r="L16">
-        <v>16.91</v>
+        <v>16.88</v>
       </c>
       <c r="M16">
-        <v>-1.44</v>
+        <v>-2.02</v>
       </c>
       <c r="N16">
-        <v>18.51</v>
+        <v>16.9</v>
       </c>
       <c r="O16">
         <v>74</v>
       </c>
       <c r="Q16">
-        <v>910.11</v>
+        <v>904.8099999999999</v>
       </c>
       <c r="R16">
         <v>900.85</v>
       </c>
       <c r="S16">
-        <v>894.77</v>
+        <v>896.29</v>
       </c>
       <c r="T16">
-        <v>832.26</v>
+        <v>832</v>
       </c>
       <c r="U16">
-        <v>8.640000000000001</v>
+        <v>7.13</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2686,31 +2718,31 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>51.82</v>
+        <v>44.8</v>
       </c>
       <c r="AA16">
-        <v>4.91</v>
+        <v>3.32</v>
       </c>
       <c r="AB16">
-        <v>5.49</v>
+        <v>5.06</v>
       </c>
       <c r="AC16">
-        <v>-0.58</v>
+        <v>-1.73</v>
       </c>
       <c r="AD16">
-        <v>45.18</v>
+        <v>26.08</v>
       </c>
       <c r="AE16">
-        <v>59.13</v>
+        <v>43.19</v>
       </c>
       <c r="AF16">
-        <v>16.05</v>
+        <v>16.39</v>
       </c>
       <c r="AH16">
         <v>920.45</v>
       </c>
       <c r="AI16">
-        <v>881.25</v>
+        <v>881.26</v>
       </c>
       <c r="AJ16">
         <v>869.13</v>
@@ -2719,7 +2751,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>28.33</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2733,10 +2765,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30836.2</v>
+        <v>30756.6</v>
       </c>
       <c r="E17">
-        <v>-0.21</v>
+        <v>-0.26</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2745,43 +2777,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-9.57</v>
+        <v>-9.81</v>
       </c>
       <c r="I17">
-        <v>8.720000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="J17">
-        <v>-0.07000000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="K17">
-        <v>-1.38</v>
+        <v>-3.2</v>
       </c>
       <c r="L17">
-        <v>3.97</v>
+        <v>4.06</v>
       </c>
       <c r="M17">
-        <v>-6.03</v>
+        <v>-5.45</v>
       </c>
       <c r="N17">
-        <v>4.98</v>
+        <v>5.04</v>
       </c>
       <c r="O17">
         <v>26</v>
       </c>
       <c r="Q17">
-        <v>30877.1</v>
+        <v>30828.5</v>
       </c>
       <c r="R17">
-        <v>31065.87</v>
+        <v>31023.27</v>
       </c>
       <c r="S17">
-        <v>31091.66</v>
+        <v>31093</v>
       </c>
       <c r="T17">
-        <v>31681.45</v>
+        <v>31669.48</v>
       </c>
       <c r="U17">
-        <v>-2.67</v>
+        <v>-2.88</v>
       </c>
       <c r="V17" t="s">
         <v>80</v>
@@ -2796,31 +2828,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>43.96</v>
+        <v>41.74</v>
       </c>
       <c r="AA17">
-        <v>-88.94</v>
+        <v>-95.92</v>
       </c>
       <c r="AB17">
-        <v>-58.28</v>
+        <v>-65.81</v>
       </c>
       <c r="AC17">
-        <v>-30.66</v>
+        <v>-30.11</v>
       </c>
       <c r="AD17">
-        <v>54.77</v>
+        <v>62.33</v>
       </c>
       <c r="AE17">
-        <v>50.11</v>
+        <v>56.02</v>
       </c>
       <c r="AF17">
-        <v>252.05</v>
+        <v>250.65</v>
       </c>
       <c r="AH17">
-        <v>31616.39</v>
+        <v>31526.84</v>
       </c>
       <c r="AI17">
-        <v>30515.34</v>
+        <v>30519.7</v>
       </c>
       <c r="AJ17">
         <v>30549.87</v>
@@ -2829,7 +2861,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>28.87</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2843,10 +2875,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16941.5</v>
+        <v>16669.85</v>
       </c>
       <c r="E18">
-        <v>0.85</v>
+        <v>-1.6</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2855,28 +2887,28 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="I18">
-        <v>9.99</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="J18">
-        <v>3.19</v>
+        <v>0.44</v>
       </c>
       <c r="K18">
-        <v>1.11</v>
+        <v>-0.68</v>
       </c>
       <c r="N18">
-        <v>47.82</v>
+        <v>36.76</v>
       </c>
       <c r="Q18">
-        <v>16726.36</v>
+        <v>16740.84</v>
       </c>
       <c r="R18">
-        <v>16612.19</v>
+        <v>16608.35</v>
       </c>
       <c r="S18">
-        <v>16447.22</v>
+        <v>16463.96</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2888,31 +2920,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>69.66</v>
+        <v>54.42</v>
       </c>
       <c r="AA18">
-        <v>81.41</v>
+        <v>77.13</v>
       </c>
       <c r="AB18">
-        <v>58.54</v>
+        <v>62.26</v>
       </c>
       <c r="AC18">
-        <v>22.87</v>
+        <v>14.88</v>
       </c>
       <c r="AD18">
-        <v>97.75</v>
+        <v>78.86</v>
       </c>
       <c r="AE18">
-        <v>82.75</v>
+        <v>86.38</v>
       </c>
       <c r="AF18">
-        <v>175.63</v>
+        <v>186.27</v>
       </c>
       <c r="AH18">
-        <v>16902.45</v>
+        <v>16893.09</v>
       </c>
       <c r="AI18">
-        <v>16321.94</v>
+        <v>16323.61</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2921,7 +2953,7 @@
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>28.73</v>
+        <v>30.97</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2935,10 +2967,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9718.4</v>
+        <v>9647.65</v>
       </c>
       <c r="E19">
-        <v>-0.34</v>
+        <v>-0.73</v>
       </c>
       <c r="F19">
         <v>9968.25</v>
@@ -2947,28 +2979,28 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-2.51</v>
+        <v>-3.22</v>
       </c>
       <c r="I19">
-        <v>8.039999999999999</v>
+        <v>7.25</v>
       </c>
       <c r="J19">
-        <v>-0.22</v>
+        <v>-1.19</v>
       </c>
       <c r="K19">
-        <v>4.15</v>
+        <v>2.22</v>
       </c>
       <c r="N19">
-        <v>42.33</v>
+        <v>37.12</v>
       </c>
       <c r="Q19">
-        <v>9756.15</v>
+        <v>9733.01</v>
       </c>
       <c r="R19">
-        <v>9723.93</v>
+        <v>9735.309999999999</v>
       </c>
       <c r="S19">
-        <v>9540.969999999999</v>
+        <v>9539.35</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2980,31 +3012,31 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>53.93</v>
+        <v>49.46</v>
       </c>
       <c r="AA19">
-        <v>83.53</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="AB19">
-        <v>100.13</v>
+        <v>94</v>
       </c>
       <c r="AC19">
-        <v>-16.6</v>
+        <v>-24.53</v>
       </c>
       <c r="AD19">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>7.4</v>
+        <v>4.36</v>
       </c>
       <c r="AF19">
-        <v>135.72</v>
+        <v>135.14</v>
       </c>
       <c r="AH19">
-        <v>9995.77</v>
+        <v>9970.120000000001</v>
       </c>
       <c r="AI19">
-        <v>9452.09</v>
+        <v>9500.5</v>
       </c>
       <c r="AJ19">
         <v>9466.209999999999</v>
@@ -3013,7 +3045,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>21.34</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3027,10 +3059,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11103.8</v>
+        <v>11142.3</v>
       </c>
       <c r="E20">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3039,28 +3071,28 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-2.33</v>
+        <v>-1.99</v>
       </c>
       <c r="I20">
-        <v>0.96</v>
+        <v>1.31</v>
       </c>
       <c r="J20">
-        <v>-0.83</v>
+        <v>-0.65</v>
       </c>
       <c r="K20">
-        <v>-1.28</v>
+        <v>-1.89</v>
       </c>
       <c r="N20">
-        <v>3.85</v>
+        <v>5.43</v>
       </c>
       <c r="Q20">
-        <v>11119.28</v>
+        <v>11104.76</v>
       </c>
       <c r="R20">
-        <v>11206.06</v>
+        <v>11201.86</v>
       </c>
       <c r="S20">
-        <v>11180.82</v>
+        <v>11178.2</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3072,31 +3104,31 @@
         <v>1</v>
       </c>
       <c r="Z20">
-        <v>43.05</v>
+        <v>46.92</v>
       </c>
       <c r="AA20">
-        <v>-23.19</v>
+        <v>-22.38</v>
       </c>
       <c r="AB20">
-        <v>-3.67</v>
+        <v>-7.41</v>
       </c>
       <c r="AC20">
-        <v>-19.51</v>
+        <v>-14.97</v>
       </c>
       <c r="AD20">
-        <v>10.13</v>
+        <v>29.61</v>
       </c>
       <c r="AE20">
-        <v>7.73</v>
+        <v>13.72</v>
       </c>
       <c r="AF20">
-        <v>117.09</v>
+        <v>118.59</v>
       </c>
       <c r="AH20">
-        <v>11349.68</v>
+        <v>11347.88</v>
       </c>
       <c r="AI20">
-        <v>11062.43</v>
+        <v>11055.83</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3105,7 +3137,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>22.1</v>
+        <v>22.62</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3119,10 +3151,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>28005.75</v>
+        <v>27762.1</v>
       </c>
       <c r="E21">
-        <v>0.97</v>
+        <v>-0.87</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3131,43 +3163,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-4.05</v>
+        <v>-4.89</v>
       </c>
       <c r="I21">
-        <v>15.99</v>
+        <v>14.98</v>
       </c>
       <c r="J21">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="K21">
-        <v>1.76</v>
+        <v>-1.01</v>
       </c>
       <c r="L21">
-        <v>7.67</v>
+        <v>5.99</v>
       </c>
       <c r="M21">
-        <v>3.81</v>
+        <v>4.01</v>
       </c>
       <c r="N21">
-        <v>8.26</v>
+        <v>7.97</v>
       </c>
       <c r="O21">
         <v>68</v>
       </c>
       <c r="Q21">
-        <v>27736.36</v>
+        <v>27799.29</v>
       </c>
       <c r="R21">
-        <v>27517.83</v>
+        <v>27512.92</v>
       </c>
       <c r="S21">
-        <v>27900.46</v>
+        <v>27896.14</v>
       </c>
       <c r="T21">
-        <v>27638.59</v>
+        <v>27637.67</v>
       </c>
       <c r="U21">
-        <v>1.33</v>
+        <v>0.45</v>
       </c>
       <c r="V21" t="s">
         <v>80</v>
@@ -3182,31 +3214,31 @@
         <v>2</v>
       </c>
       <c r="Z21">
-        <v>60.16</v>
+        <v>52.61</v>
       </c>
       <c r="AA21">
-        <v>-22.19</v>
+        <v>-10.52</v>
       </c>
       <c r="AB21">
-        <v>-97.5</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="AC21">
-        <v>75.31</v>
+        <v>69.58</v>
       </c>
       <c r="AD21">
-        <v>98.61</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="AE21">
-        <v>97.28</v>
+        <v>94.91</v>
       </c>
       <c r="AF21">
-        <v>312.68</v>
+        <v>315.51</v>
       </c>
       <c r="AH21">
-        <v>27976.2</v>
+        <v>27957.72</v>
       </c>
       <c r="AI21">
-        <v>27059.46</v>
+        <v>27068.11</v>
       </c>
       <c r="AJ21">
         <v>28265.67</v>
@@ -3215,7 +3247,7 @@
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>32.21</v>
+        <v>34.49</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3388,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3396,7 +3428,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3415,48 +3447,48 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>104</v>
@@ -3465,138 +3497,150 @@
         <v>105</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>80</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="E8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="8">
-        <v>2.03</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.34</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-0.16</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-1.73</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-1.49</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-2.31</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-2.01</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1.2</v>
+      <c r="B13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="8">
-        <v>-5.69</v>
+        <v>0.34</v>
       </c>
       <c r="D14" s="8">
-        <v>-6.3</v>
+        <v>-2.32</v>
       </c>
       <c r="E14" s="9">
-        <v>-0.61</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="8">
-        <v>0.13</v>
+        <v>-1.73</v>
       </c>
       <c r="D15" s="8">
-        <v>-1.13</v>
+        <v>-2.99</v>
       </c>
       <c r="E15" s="9">
         <v>-1.26</v>
@@ -3604,1872 +3648,1872 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="8">
-        <v>0.28</v>
+        <v>-2.31</v>
       </c>
       <c r="D16" s="8">
-        <v>1.57</v>
-      </c>
-      <c r="E16" s="10">
-        <v>1.29</v>
+        <v>-3.89</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="8">
-        <v>2.62</v>
+        <v>-2.01</v>
       </c>
       <c r="D17" s="8">
-        <v>1.56</v>
+        <v>-2.9</v>
       </c>
       <c r="E17" s="9">
-        <v>-1.06</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="8">
-        <v>-1.1</v>
+        <v>-6.3</v>
       </c>
       <c r="D18" s="8">
-        <v>-2.44</v>
+        <v>-7.02</v>
       </c>
       <c r="E18" s="9">
-        <v>-1.34</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="8">
-        <v>1.1</v>
+        <v>-1.13</v>
       </c>
       <c r="D19" s="8">
-        <v>-3.79</v>
+        <v>-3.63</v>
       </c>
       <c r="E19" s="9">
-        <v>-4.89</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="8">
-        <v>6.48</v>
+        <v>1.57</v>
       </c>
       <c r="D20" s="8">
-        <v>3.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E20" s="9">
-        <v>-2.75</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="8">
-        <v>-2.06</v>
+        <v>1.56</v>
       </c>
       <c r="D21" s="8">
-        <v>-2.39</v>
+        <v>-0.72</v>
       </c>
       <c r="E21" s="9">
-        <v>-0.33</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="8">
-        <v>3.32</v>
+        <v>-2.44</v>
       </c>
       <c r="D22" s="8">
-        <v>2.9</v>
+        <v>-3.14</v>
       </c>
       <c r="E22" s="9">
-        <v>-0.42</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="8">
-        <v>2.45</v>
+        <v>-3.79</v>
       </c>
       <c r="D23" s="8">
-        <v>2.46</v>
+        <v>-0.46</v>
       </c>
       <c r="E23" s="10">
-        <v>0.01</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="8">
-        <v>1.04</v>
+        <v>3.73</v>
       </c>
       <c r="D24" s="8">
-        <v>0.3</v>
+        <v>2.13</v>
       </c>
       <c r="E24" s="9">
-        <v>-0.74</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.91</v>
+        <v>-2.39</v>
       </c>
       <c r="D25" s="8">
-        <v>-1.38</v>
+        <v>-3.46</v>
       </c>
       <c r="E25" s="9">
-        <v>-0.47</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="8">
-        <v>0.59</v>
+        <v>2.9</v>
       </c>
       <c r="D26" s="8">
-        <v>1.11</v>
-      </c>
-      <c r="E26" s="10">
-        <v>0.52</v>
+        <v>0.22</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="8">
-        <v>6.13</v>
+        <v>2.46</v>
       </c>
       <c r="D27" s="8">
-        <v>4.15</v>
+        <v>0.49</v>
       </c>
       <c r="E27" s="9">
-        <v>-1.98</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.54</v>
+        <v>0.3</v>
       </c>
       <c r="D28" s="8">
-        <v>-1.28</v>
+        <v>-2.38</v>
       </c>
       <c r="E28" s="9">
-        <v>-0.74</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="8">
-        <v>0.8100000000000001</v>
+        <v>-1.38</v>
       </c>
       <c r="D29" s="8">
-        <v>1.76</v>
-      </c>
-      <c r="E29" s="10">
-        <v>0.95</v>
+        <v>-3.2</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" s="8">
-        <v>-1.54</v>
+        <v>1.11</v>
       </c>
       <c r="D30" s="8">
-        <v>-0.89</v>
-      </c>
-      <c r="E30" s="10">
-        <v>0.65</v>
+        <v>-0.68</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="8">
-        <v>0.27</v>
+        <v>4.15</v>
       </c>
       <c r="D31" s="8">
-        <v>-1.59</v>
+        <v>2.22</v>
       </c>
       <c r="E31" s="9">
-        <v>-1.86</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32" s="8">
-        <v>-1.35</v>
+        <v>-1.28</v>
       </c>
       <c r="D32" s="8">
-        <v>-1.72</v>
+        <v>-1.89</v>
       </c>
       <c r="E32" s="9">
-        <v>-0.37</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33" s="8">
-        <v>-0.39</v>
+        <v>1.76</v>
       </c>
       <c r="D33" s="8">
         <v>-1.01</v>
       </c>
       <c r="E33" s="9">
-        <v>-0.62</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="8">
-        <v>-2.19</v>
+        <v>-0.89</v>
       </c>
       <c r="D34" s="8">
-        <v>-3.16</v>
+        <v>-2.48</v>
       </c>
       <c r="E34" s="9">
-        <v>-0.97</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="8">
-        <v>0.32</v>
+        <v>-1.59</v>
       </c>
       <c r="D35" s="8">
-        <v>0.52</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0.2</v>
+        <v>-1.64</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="8">
-        <v>2.45</v>
+        <v>-1.72</v>
       </c>
       <c r="D36" s="8">
-        <v>1.94</v>
+        <v>-2.58</v>
       </c>
       <c r="E36" s="9">
-        <v>-0.51</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="8">
-        <v>0.28</v>
+        <v>-1.01</v>
       </c>
       <c r="D37" s="8">
-        <v>0.43</v>
-      </c>
-      <c r="E37" s="10">
-        <v>0.15</v>
+        <v>-1.32</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="8">
-        <v>-1.14</v>
+        <v>-3.16</v>
       </c>
       <c r="D38" s="8">
-        <v>-1.75</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.61</v>
+        <v>-2.62</v>
+      </c>
+      <c r="E38" s="10">
+        <v>0.54</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="8">
-        <v>-1.14</v>
+        <v>0.52</v>
       </c>
       <c r="D39" s="8">
-        <v>-2.87</v>
+        <v>-0.93</v>
       </c>
       <c r="E39" s="9">
-        <v>-1.73</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="8">
-        <v>3.56</v>
+        <v>1.94</v>
       </c>
       <c r="D40" s="8">
-        <v>-1.4</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-4.96</v>
+        <v>2.36</v>
+      </c>
+      <c r="E40" s="10">
+        <v>0.42</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="8">
-        <v>-0.55</v>
+        <v>0.43</v>
       </c>
       <c r="D41" s="8">
-        <v>-0.79</v>
+        <v>-1.07</v>
       </c>
       <c r="E41" s="9">
-        <v>-0.24</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="8">
-        <v>-0.14</v>
+        <v>-1.75</v>
       </c>
       <c r="D42" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0.96</v>
+        <v>-2.04</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="8">
-        <v>2.4</v>
+        <v>-2.87</v>
       </c>
       <c r="D43" s="8">
-        <v>3.22</v>
-      </c>
-      <c r="E43" s="10">
-        <v>0.82</v>
+        <v>-3.02</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="8">
-        <v>0.1</v>
+        <v>-1.4</v>
       </c>
       <c r="D44" s="8">
-        <v>-1.41</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.51</v>
+        <v>-1.36</v>
+      </c>
+      <c r="E44" s="10">
+        <v>0.04</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="8">
-        <v>0.03</v>
+        <v>-0.79</v>
       </c>
       <c r="D45" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="E45" s="9">
-        <v>-0.1</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="8">
-        <v>2.02</v>
+        <v>0.82</v>
       </c>
       <c r="D46" s="8">
-        <v>3.19</v>
-      </c>
-      <c r="E46" s="10">
-        <v>1.17</v>
+        <v>-1.14</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="8">
-        <v>-0.51</v>
+        <v>3.22</v>
       </c>
       <c r="D47" s="8">
-        <v>-0.22</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0.29</v>
+        <v>0.86</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>-0.99</v>
+        <v>-1.41</v>
       </c>
       <c r="D48" s="8">
-        <v>-0.83</v>
-      </c>
-      <c r="E48" s="10">
-        <v>0.16</v>
+        <v>-2.89</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="8">
-        <v>1.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D49" s="8">
-        <v>1.83</v>
-      </c>
-      <c r="E49" s="10">
-        <v>0.78</v>
+        <v>-0.78</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="8">
-        <v>13.28</v>
+        <v>3.19</v>
       </c>
       <c r="D50" s="8">
-        <v>13.65</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0.37</v>
+        <v>0.44</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C51" s="8">
-        <v>10.6</v>
+        <v>-0.22</v>
       </c>
       <c r="D51" s="8">
-        <v>9.41</v>
+        <v>-1.19</v>
       </c>
       <c r="E51" s="9">
-        <v>-1.19</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C52" s="8">
-        <v>-3.18</v>
+        <v>-0.83</v>
       </c>
       <c r="D52" s="8">
-        <v>-3.72</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.54</v>
+        <v>-0.65</v>
+      </c>
+      <c r="E52" s="10">
+        <v>0.18</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C53" s="8">
-        <v>9.06</v>
+        <v>1.83</v>
       </c>
       <c r="D53" s="8">
-        <v>9.42</v>
-      </c>
-      <c r="E53" s="10">
-        <v>0.36</v>
+        <v>1.15</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="8">
-        <v>-17.38</v>
+        <v>13.65</v>
       </c>
       <c r="D54" s="8">
-        <v>-18.25</v>
+        <v>12.48</v>
       </c>
       <c r="E54" s="9">
-        <v>-0.87</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="8">
-        <v>-0.76</v>
+        <v>9.41</v>
       </c>
       <c r="D55" s="8">
-        <v>-1.05</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.29</v>
+        <v>10.76</v>
+      </c>
+      <c r="E55" s="10">
+        <v>1.35</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="8">
-        <v>-12.35</v>
+        <v>-3.72</v>
       </c>
       <c r="D56" s="8">
-        <v>-12.69</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-0.34</v>
+        <v>-3.39</v>
+      </c>
+      <c r="E56" s="10">
+        <v>0.33</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="8">
-        <v>0.91</v>
+        <v>9.42</v>
       </c>
       <c r="D57" s="8">
-        <v>0.06</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.85</v>
+        <v>9.56</v>
+      </c>
+      <c r="E57" s="10">
+        <v>0.14</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="8">
-        <v>-2.17</v>
+        <v>-18.25</v>
       </c>
       <c r="D58" s="8">
-        <v>-4.95</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-2.78</v>
+        <v>-16.65</v>
+      </c>
+      <c r="E58" s="10">
+        <v>1.6</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="8">
-        <v>42.41</v>
+        <v>-1.05</v>
       </c>
       <c r="D59" s="8">
-        <v>38.98</v>
+        <v>-1.19</v>
       </c>
       <c r="E59" s="9">
-        <v>-3.43</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="8">
-        <v>1.27</v>
+        <v>-12.69</v>
       </c>
       <c r="D60" s="8">
-        <v>1.91</v>
+        <v>-11.13</v>
       </c>
       <c r="E60" s="10">
-        <v>0.64</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="8">
-        <v>21.13</v>
+        <v>0.06</v>
       </c>
       <c r="D61" s="8">
-        <v>21.65</v>
+        <v>1.13</v>
       </c>
       <c r="E61" s="10">
-        <v>0.52</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="8">
-        <v>22.86</v>
+        <v>-4.95</v>
       </c>
       <c r="D62" s="8">
-        <v>22.58</v>
+        <v>-5.59</v>
       </c>
       <c r="E62" s="9">
-        <v>-0.28</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="8">
-        <v>-0.55</v>
+        <v>38.98</v>
       </c>
       <c r="D63" s="8">
-        <v>-1.44</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-0.89</v>
+        <v>40.68</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1.7</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="8">
-        <v>-5.73</v>
+        <v>1.91</v>
       </c>
       <c r="D64" s="8">
-        <v>-6.03</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-0.3</v>
+        <v>1.99</v>
+      </c>
+      <c r="E64" s="10">
+        <v>0.08</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="8">
-        <v>2.96</v>
+        <v>21.65</v>
       </c>
       <c r="D65" s="8">
-        <v>3.81</v>
-      </c>
-      <c r="E65" s="10">
-        <v>0.85</v>
+        <v>21.54</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="8">
-        <v>11.43</v>
+        <v>22.58</v>
       </c>
       <c r="D66" s="8">
-        <v>10.59</v>
+        <v>20.34</v>
       </c>
       <c r="E66" s="9">
-        <v>-0.84</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67" s="8">
-        <v>-4.23</v>
+        <v>-1.44</v>
       </c>
       <c r="D67" s="8">
-        <v>-5.2</v>
+        <v>-2.02</v>
       </c>
       <c r="E67" s="9">
-        <v>-0.97</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68" s="8">
-        <v>7.4</v>
+        <v>-6.03</v>
       </c>
       <c r="D68" s="8">
-        <v>5.7</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-1.7</v>
+        <v>-5.45</v>
+      </c>
+      <c r="E68" s="10">
+        <v>0.58</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C69" s="8">
-        <v>-5.59</v>
+        <v>3.81</v>
       </c>
       <c r="D69" s="8">
-        <v>-5.57</v>
+        <v>4.01</v>
       </c>
       <c r="E69" s="10">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="8">
-        <v>-2.97</v>
+        <v>10.59</v>
       </c>
       <c r="D70" s="8">
-        <v>-5.32</v>
+        <v>9.19</v>
       </c>
       <c r="E70" s="9">
-        <v>-2.35</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="8">
-        <v>5.11</v>
+        <v>-5.2</v>
       </c>
       <c r="D71" s="8">
-        <v>5.76</v>
+        <v>-4.9</v>
       </c>
       <c r="E71" s="10">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="8">
-        <v>4.78</v>
+        <v>5.7</v>
       </c>
       <c r="D72" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-4.54</v>
+        <v>5.81</v>
+      </c>
+      <c r="E72" s="10">
+        <v>0.11</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="8">
-        <v>0.06</v>
+        <v>-5.57</v>
       </c>
       <c r="D73" s="8">
-        <v>-0.51</v>
+        <v>-5.95</v>
       </c>
       <c r="E73" s="9">
-        <v>-0.57</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="8">
-        <v>12.28</v>
+        <v>-5.32</v>
       </c>
       <c r="D74" s="8">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-3.32</v>
+        <v>-3.46</v>
+      </c>
+      <c r="E74" s="10">
+        <v>1.86</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="8">
-        <v>0.14</v>
+        <v>5.76</v>
       </c>
       <c r="D75" s="8">
-        <v>-2.68</v>
+        <v>4.2</v>
       </c>
       <c r="E75" s="9">
-        <v>-2.82</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="8">
-        <v>-4.55</v>
+        <v>0.24</v>
       </c>
       <c r="D76" s="8">
-        <v>-3.75</v>
+        <v>7.19</v>
       </c>
       <c r="E76" s="10">
-        <v>0.8</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="8">
-        <v>7.48</v>
+        <v>-0.51</v>
       </c>
       <c r="D77" s="8">
-        <v>6.96</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-0.52</v>
+        <v>-0.11</v>
+      </c>
+      <c r="E77" s="10">
+        <v>0.4</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="8">
-        <v>11.47</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D78" s="8">
-        <v>13.25</v>
+        <v>9.9</v>
       </c>
       <c r="E78" s="10">
-        <v>1.78</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="8">
-        <v>18.31</v>
+        <v>-2.68</v>
       </c>
       <c r="D79" s="8">
-        <v>16.91</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-1.4</v>
+        <v>-2.55</v>
+      </c>
+      <c r="E79" s="10">
+        <v>0.13</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="8">
-        <v>4.68</v>
+        <v>-3.75</v>
       </c>
       <c r="D80" s="8">
-        <v>3.97</v>
+        <v>-4.26</v>
       </c>
       <c r="E80" s="9">
-        <v>-0.71</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="8">
-        <v>6.4</v>
+        <v>6.96</v>
       </c>
       <c r="D81" s="8">
-        <v>7.67</v>
-      </c>
-      <c r="E81" s="10">
-        <v>1.27</v>
+        <v>3.91</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-3.05</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C82" s="8">
-        <v>-2.69</v>
+        <v>13.25</v>
       </c>
       <c r="D82" s="8">
-        <v>-2.72</v>
+        <v>11.23</v>
       </c>
       <c r="E82" s="9">
-        <v>-0.03</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C83" s="8">
-        <v>-6.61</v>
+        <v>16.91</v>
       </c>
       <c r="D83" s="8">
-        <v>-7.74</v>
+        <v>16.88</v>
       </c>
       <c r="E83" s="9">
-        <v>-1.13</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C84" s="8">
-        <v>-5.81</v>
+        <v>3.97</v>
       </c>
       <c r="D84" s="8">
-        <v>-6.62</v>
-      </c>
-      <c r="E84" s="9">
-        <v>-0.8100000000000001</v>
+        <v>4.06</v>
+      </c>
+      <c r="E84" s="10">
+        <v>0.09</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="7" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C85" s="8">
-        <v>-8.5</v>
+        <v>7.67</v>
       </c>
       <c r="D85" s="8">
-        <v>-8.630000000000001</v>
+        <v>5.99</v>
       </c>
       <c r="E85" s="9">
-        <v>-0.13</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="8">
-        <v>-18.02</v>
+        <v>-2.72</v>
       </c>
       <c r="D86" s="8">
-        <v>-19.4</v>
+        <v>-3.9</v>
       </c>
       <c r="E86" s="9">
-        <v>-1.38</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="8">
-        <v>-7.65</v>
+        <v>-7.74</v>
       </c>
       <c r="D87" s="8">
-        <v>-7.62</v>
+        <v>-7.61</v>
       </c>
       <c r="E87" s="10">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="8">
-        <v>-20.78</v>
+        <v>-6.62</v>
       </c>
       <c r="D88" s="8">
-        <v>-21.01</v>
+        <v>-6.78</v>
       </c>
       <c r="E88" s="9">
-        <v>-0.23</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="8">
-        <v>-0.62</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="D89" s="8">
-        <v>-0.48</v>
-      </c>
-      <c r="E89" s="10">
-        <v>0.14</v>
+        <v>-8.98</v>
+      </c>
+      <c r="E89" s="9">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="8">
-        <v>-5.36</v>
+        <v>-19.4</v>
       </c>
       <c r="D90" s="8">
-        <v>-6</v>
-      </c>
-      <c r="E90" s="9">
-        <v>-0.64</v>
+        <v>-18.64</v>
+      </c>
+      <c r="E90" s="10">
+        <v>0.76</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="8">
-        <v>-3.09</v>
+        <v>-7.62</v>
       </c>
       <c r="D91" s="8">
-        <v>-5.84</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="E91" s="9">
-        <v>-2.75</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="8">
-        <v>-1.41</v>
+        <v>-21.01</v>
       </c>
       <c r="D92" s="8">
-        <v>-3.82</v>
-      </c>
-      <c r="E92" s="9">
-        <v>-2.41</v>
+        <v>-20.24</v>
+      </c>
+      <c r="E92" s="10">
+        <v>0.77</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="8">
-        <v>-10</v>
+        <v>-0.48</v>
       </c>
       <c r="D93" s="8">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="E93" s="10">
-        <v>0.14</v>
+        <v>-1.56</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="8">
-        <v>-12.91</v>
+        <v>-6</v>
       </c>
       <c r="D94" s="8">
-        <v>-12.86</v>
+        <v>-5.7</v>
       </c>
       <c r="E94" s="10">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="8">
-        <v>-6.17</v>
+        <v>-5.84</v>
       </c>
       <c r="D95" s="8">
-        <v>-6.66</v>
-      </c>
-      <c r="E95" s="9">
-        <v>-0.49</v>
+        <v>-4.35</v>
+      </c>
+      <c r="E95" s="10">
+        <v>1.49</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="8">
-        <v>-9.390000000000001</v>
+        <v>-3.82</v>
       </c>
       <c r="D96" s="8">
-        <v>-9.57</v>
+        <v>-3.85</v>
       </c>
       <c r="E96" s="9">
-        <v>-0.18</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="8">
-        <v>-2.17</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D97" s="8">
-        <v>-2.51</v>
+        <v>-10.28</v>
       </c>
       <c r="E97" s="9">
-        <v>-0.34</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="8">
-        <v>-2.65</v>
+        <v>-12.86</v>
       </c>
       <c r="D98" s="8">
-        <v>-2.33</v>
-      </c>
-      <c r="E98" s="10">
-        <v>0.32</v>
+        <v>-13.91</v>
+      </c>
+      <c r="E98" s="9">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="8">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="D99" s="8">
-        <v>-4.05</v>
-      </c>
-      <c r="E99" s="10">
-        <v>0.92</v>
+        <v>-1.45</v>
+      </c>
+      <c r="E99" s="9">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C100" s="8">
-        <v>28851.8</v>
+        <v>-6.66</v>
       </c>
       <c r="D100" s="8">
-        <v>28841.5</v>
+        <v>-7.99</v>
       </c>
       <c r="E100" s="9">
-        <v>-10.3</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C101" s="8">
-        <v>9809.15</v>
+        <v>-9.57</v>
       </c>
       <c r="D101" s="8">
-        <v>9690.65</v>
+        <v>-9.81</v>
       </c>
       <c r="E101" s="9">
-        <v>-118.5</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C102" s="8">
-        <v>11904.2</v>
+        <v>0</v>
       </c>
       <c r="D102" s="8">
-        <v>11802.7</v>
+        <v>-1.6</v>
       </c>
       <c r="E102" s="9">
-        <v>-101.5</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="7" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C103" s="8">
-        <v>38003.65</v>
+        <v>-2.51</v>
       </c>
       <c r="D103" s="8">
-        <v>37949.25</v>
+        <v>-3.22</v>
       </c>
       <c r="E103" s="9">
-        <v>-54.4</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="7" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C104" s="8">
-        <v>46815</v>
+        <v>-2.33</v>
       </c>
       <c r="D104" s="8">
-        <v>46025.55</v>
-      </c>
-      <c r="E104" s="9">
-        <v>-789.45</v>
+        <v>-1.99</v>
+      </c>
+      <c r="E104" s="10">
+        <v>0.34</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105" s="8">
-        <v>26286.5</v>
+        <v>-4.05</v>
       </c>
       <c r="D105" s="8">
-        <v>26293.65</v>
-      </c>
-      <c r="E105" s="10">
-        <v>7.15</v>
+        <v>-4.89</v>
+      </c>
+      <c r="E105" s="9">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="8">
-        <v>31281.7</v>
+        <v>28841.5</v>
       </c>
       <c r="D106" s="8">
-        <v>31191.45</v>
+        <v>28491.05</v>
       </c>
       <c r="E106" s="9">
-        <v>-90.25</v>
+        <v>-350.45</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="8">
-        <v>16558.45</v>
+        <v>9690.65</v>
       </c>
       <c r="D107" s="8">
-        <v>16582.95</v>
+        <v>9704.200000000001</v>
       </c>
       <c r="E107" s="10">
-        <v>24.5</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="8">
-        <v>9242.700000000001</v>
+        <v>11802.7</v>
       </c>
       <c r="D108" s="8">
-        <v>9179.4</v>
+        <v>11782.3</v>
       </c>
       <c r="E108" s="9">
-        <v>-63.3</v>
+        <v>-20.4</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="8">
-        <v>1602.9</v>
+        <v>37949.25</v>
       </c>
       <c r="D109" s="8">
-        <v>1557.35</v>
+        <v>37806.1</v>
       </c>
       <c r="E109" s="9">
-        <v>-45.55</v>
+        <v>-143.15</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="8">
-        <v>13525.35</v>
+        <v>46025.55</v>
       </c>
       <c r="D110" s="8">
-        <v>13193.9</v>
-      </c>
-      <c r="E110" s="9">
-        <v>-331.45</v>
+        <v>46457.15</v>
+      </c>
+      <c r="E110" s="10">
+        <v>431.6</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="8">
-        <v>9689.25</v>
+        <v>26293.65</v>
       </c>
       <c r="D111" s="8">
-        <v>9704.4</v>
-      </c>
-      <c r="E111" s="10">
-        <v>15.15</v>
+        <v>26003.9</v>
+      </c>
+      <c r="E111" s="9">
+        <v>-289.75</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="8">
-        <v>8604.299999999999</v>
+        <v>31191.45</v>
       </c>
       <c r="D112" s="8">
-        <v>8609.549999999999</v>
+        <v>31496.7</v>
       </c>
       <c r="E112" s="10">
-        <v>5.25</v>
+        <v>305.25</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="8">
-        <v>26991.85</v>
+        <v>16582.95</v>
       </c>
       <c r="D113" s="8">
-        <v>27186.45</v>
-      </c>
-      <c r="E113" s="10">
-        <v>194.6</v>
+        <v>16402.5</v>
+      </c>
+      <c r="E113" s="9">
+        <v>-180.45</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="8">
-        <v>908.85</v>
+        <v>9179.4</v>
       </c>
       <c r="D114" s="8">
-        <v>904.15</v>
-      </c>
-      <c r="E114" s="9">
-        <v>-4.7</v>
+        <v>9209.25</v>
+      </c>
+      <c r="E114" s="10">
+        <v>29.85</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="8">
-        <v>30900.2</v>
+        <v>1557.35</v>
       </c>
       <c r="D115" s="8">
-        <v>30836.2</v>
-      </c>
-      <c r="E115" s="9">
-        <v>-64</v>
+        <v>1561.45</v>
+      </c>
+      <c r="E115" s="10">
+        <v>4.1</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="8">
-        <v>16798.5</v>
+        <v>13193.9</v>
       </c>
       <c r="D116" s="8">
-        <v>16941.5</v>
-      </c>
-      <c r="E116" s="10">
-        <v>143</v>
+        <v>13189.85</v>
+      </c>
+      <c r="E116" s="9">
+        <v>-4.05</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="8">
-        <v>9751.65</v>
+        <v>9704.4</v>
       </c>
       <c r="D117" s="8">
-        <v>9718.4</v>
+        <v>9659.5</v>
       </c>
       <c r="E117" s="9">
-        <v>-33.25</v>
+        <v>-44.9</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="8">
-        <v>11067.7</v>
+        <v>8609.549999999999</v>
       </c>
       <c r="D118" s="8">
-        <v>11103.8</v>
-      </c>
-      <c r="E118" s="10">
-        <v>36.1</v>
+        <v>8505.75</v>
+      </c>
+      <c r="E118" s="9">
+        <v>-103.8</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="8">
-        <v>27737.2</v>
+        <v>27186.45</v>
       </c>
       <c r="D119" s="8">
-        <v>28005.75</v>
-      </c>
-      <c r="E119" s="10">
-        <v>268.55</v>
+        <v>26792.65</v>
+      </c>
+      <c r="E119" s="9">
+        <v>-393.8</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C120" s="8">
-        <v>44</v>
+        <v>904.15</v>
       </c>
       <c r="D120" s="8">
-        <v>38</v>
+        <v>891.3</v>
       </c>
       <c r="E120" s="9">
-        <v>-6</v>
+        <v>-12.85</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C121" s="8">
-        <v>38</v>
+        <v>30836.2</v>
       </c>
       <c r="D121" s="8">
-        <v>50</v>
-      </c>
-      <c r="E121" s="10">
-        <v>12</v>
+        <v>30756.6</v>
+      </c>
+      <c r="E121" s="9">
+        <v>-79.59999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C122" s="8">
-        <v>50</v>
+        <v>16941.5</v>
       </c>
       <c r="D122" s="8">
-        <v>62</v>
-      </c>
-      <c r="E122" s="10">
-        <v>12</v>
+        <v>16669.85</v>
+      </c>
+      <c r="E122" s="9">
+        <v>-271.65</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C123" s="8">
-        <v>68</v>
+        <v>9718.4</v>
       </c>
       <c r="D123" s="8">
-        <v>44</v>
+        <v>9647.65</v>
       </c>
       <c r="E123" s="9">
-        <v>-24</v>
+        <v>-70.75</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C124" s="8">
-        <v>62</v>
+        <v>11103.8</v>
       </c>
       <c r="D124" s="8">
-        <v>68</v>
+        <v>11142.3</v>
       </c>
       <c r="E124" s="10">
-        <v>6</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C125" s="8">
-        <v>53.45</v>
+        <v>28005.75</v>
       </c>
       <c r="D125" s="8">
-        <v>53.18</v>
+        <v>27762.1</v>
       </c>
       <c r="E125" s="9">
-        <v>-0.27</v>
+        <v>-243.65</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -5477,328 +5521,396 @@
         <v>39</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C126" s="8">
-        <v>44.36</v>
+        <v>56</v>
       </c>
       <c r="D126" s="8">
-        <v>35.26</v>
-      </c>
-      <c r="E126" s="9">
-        <v>-9.1</v>
+        <v>62</v>
+      </c>
+      <c r="E126" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C127" s="8">
-        <v>44.97</v>
+        <v>62</v>
       </c>
       <c r="D127" s="8">
-        <v>39.38</v>
+        <v>44</v>
       </c>
       <c r="E127" s="9">
-        <v>-5.59</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C128" s="8">
-        <v>32.08</v>
+        <v>44</v>
       </c>
       <c r="D128" s="8">
-        <v>31.05</v>
-      </c>
-      <c r="E128" s="9">
-        <v>-1.03</v>
+        <v>56</v>
+      </c>
+      <c r="E128" s="10">
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C129" s="8">
-        <v>30.61</v>
+        <v>53.18</v>
       </c>
       <c r="D129" s="8">
-        <v>25.16</v>
+        <v>44.91</v>
       </c>
       <c r="E129" s="9">
-        <v>-5.45</v>
+        <v>-8.27</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C130" s="8">
-        <v>46.15</v>
+        <v>35.26</v>
       </c>
       <c r="D130" s="8">
-        <v>46.42</v>
+        <v>36.85</v>
       </c>
       <c r="E130" s="10">
-        <v>0.27</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C131" s="8">
-        <v>58.52</v>
+        <v>39.38</v>
       </c>
       <c r="D131" s="8">
-        <v>57.41</v>
+        <v>38.35</v>
       </c>
       <c r="E131" s="9">
-        <v>-1.11</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="8">
-        <v>61.33</v>
+        <v>31.05</v>
       </c>
       <c r="D132" s="8">
-        <v>62.87</v>
-      </c>
-      <c r="E132" s="10">
-        <v>1.54</v>
+        <v>28.46</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="8">
-        <v>38.2</v>
+        <v>25.16</v>
       </c>
       <c r="D133" s="8">
-        <v>33.96</v>
-      </c>
-      <c r="E133" s="9">
-        <v>-4.24</v>
+        <v>32.26</v>
+      </c>
+      <c r="E133" s="10">
+        <v>7.1</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="8">
-        <v>57.97</v>
+        <v>46.42</v>
       </c>
       <c r="D134" s="8">
-        <v>45.23</v>
+        <v>38.12</v>
       </c>
       <c r="E134" s="9">
-        <v>-12.74</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="8">
-        <v>67.39</v>
+        <v>57.41</v>
       </c>
       <c r="D135" s="8">
-        <v>53.42</v>
-      </c>
-      <c r="E135" s="9">
-        <v>-13.97</v>
+        <v>60.17</v>
+      </c>
+      <c r="E135" s="10">
+        <v>2.76</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="8">
-        <v>31.91</v>
+        <v>62.87</v>
       </c>
       <c r="D136" s="8">
-        <v>34.32</v>
-      </c>
-      <c r="E136" s="10">
-        <v>2.41</v>
+        <v>47.73</v>
+      </c>
+      <c r="E136" s="9">
+        <v>-15.14</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="8">
-        <v>51.65</v>
+        <v>33.96</v>
       </c>
       <c r="D137" s="8">
-        <v>52.01</v>
+        <v>37.48</v>
       </c>
       <c r="E137" s="10">
-        <v>0.36</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="8">
-        <v>69.63</v>
+        <v>45.23</v>
       </c>
       <c r="D138" s="8">
-        <v>72.98</v>
+        <v>46.37</v>
       </c>
       <c r="E138" s="10">
-        <v>3.35</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="8">
-        <v>54.73</v>
+        <v>53.42</v>
       </c>
       <c r="D139" s="8">
-        <v>51.82</v>
+        <v>53.28</v>
       </c>
       <c r="E139" s="9">
-        <v>-2.91</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="8">
-        <v>45.78</v>
+        <v>34.32</v>
       </c>
       <c r="D140" s="8">
-        <v>43.96</v>
+        <v>30.83</v>
       </c>
       <c r="E140" s="9">
-        <v>-1.82</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="8">
-        <v>64.84</v>
+        <v>52.01</v>
       </c>
       <c r="D141" s="8">
-        <v>69.66</v>
-      </c>
-      <c r="E141" s="10">
-        <v>4.82</v>
+        <v>45.02</v>
+      </c>
+      <c r="E141" s="9">
+        <v>-6.99</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="8">
-        <v>56.15</v>
+        <v>72.98</v>
       </c>
       <c r="D142" s="8">
-        <v>53.93</v>
+        <v>58.85</v>
       </c>
       <c r="E142" s="9">
-        <v>-2.22</v>
+        <v>-14.13</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="8">
-        <v>39.19</v>
+        <v>51.82</v>
       </c>
       <c r="D143" s="8">
-        <v>43.05</v>
-      </c>
-      <c r="E143" s="10">
-        <v>3.86</v>
+        <v>44.8</v>
+      </c>
+      <c r="E143" s="9">
+        <v>-7.02</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="8">
-        <v>53.3</v>
+        <v>43.96</v>
       </c>
       <c r="D144" s="8">
+        <v>41.74</v>
+      </c>
+      <c r="E144" s="9">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C145" s="8">
+        <v>69.66</v>
+      </c>
+      <c r="D145" s="8">
+        <v>54.42</v>
+      </c>
+      <c r="E145" s="9">
+        <v>-15.24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C146" s="8">
+        <v>53.93</v>
+      </c>
+      <c r="D146" s="8">
+        <v>49.46</v>
+      </c>
+      <c r="E146" s="9">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C147" s="8">
+        <v>43.05</v>
+      </c>
+      <c r="D147" s="8">
+        <v>46.92</v>
+      </c>
+      <c r="E147" s="10">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C148" s="8">
         <v>60.16</v>
       </c>
-      <c r="E144" s="10">
-        <v>6.86</v>
+      <c r="D148" s="8">
+        <v>52.61</v>
+      </c>
+      <c r="E148" s="9">
+        <v>-7.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5822,28 +5934,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5857,13 +5969,13 @@
         <v>20</v>
       </c>
       <c r="D2" s="13">
-        <v>48.3</v>
+        <v>44.4</v>
       </c>
       <c r="E2" s="13">
         <v>40</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="G2" s="13">
         <v>3.6</v>
@@ -5974,28 +6086,28 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>54</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>55</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>49</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>48</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>46</v>
@@ -6006,34 +6118,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.4782</v>
+        <v>0.3712</v>
       </c>
       <c r="B2" s="16">
-        <v>0.4233</v>
+        <v>0.3676</v>
       </c>
       <c r="C2" s="16">
-        <v>0.2982</v>
+        <v>0.2929</v>
       </c>
       <c r="D2" s="16">
-        <v>0.2976</v>
+        <v>0.2319</v>
       </c>
       <c r="E2" s="16">
-        <v>0.2351</v>
+        <v>0.2312</v>
       </c>
       <c r="F2" s="16">
-        <v>0.2163</v>
+        <v>0.2154</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1851</v>
+        <v>0.1864</v>
       </c>
       <c r="H2" s="16">
-        <v>0.1822</v>
+        <v>0.169</v>
       </c>
       <c r="I2" s="16">
-        <v>0.1428</v>
+        <v>0.1427</v>
       </c>
       <c r="J2" s="16">
-        <v>0.1364</v>
+        <v>0.1335</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6053,10 +6165,10 @@
         <v>43</v>
       </c>
       <c r="F3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>56</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>42</v>
@@ -6070,34 +6182,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.1334</v>
+        <v>0.1318</v>
       </c>
       <c r="B4" s="16">
-        <v>0.1204</v>
+        <v>0.1219</v>
       </c>
       <c r="C4" s="16">
-        <v>0.1132</v>
+        <v>0.1113</v>
       </c>
       <c r="D4" s="16">
-        <v>0.08259999999999999</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="E4" s="16">
-        <v>0.0779</v>
+        <v>0.0759</v>
       </c>
       <c r="F4" s="16">
-        <v>0.0498</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="G4" s="16">
-        <v>0.0385</v>
+        <v>0.0504</v>
       </c>
       <c r="H4" s="16">
-        <v>0.0309</v>
+        <v>0.0322</v>
       </c>
       <c r="I4" s="16">
-        <v>-0.005600000000000001</v>
+        <v>-0.0062</v>
       </c>
       <c r="J4" s="16">
-        <v>-0.0204</v>
+        <v>-0.0158</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="122">
   <si>
     <t>Symbol</t>
   </si>
@@ -265,12 +265,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -289,100 +289,64 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.3% → -2.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.3%</t>
-  </si>
-  <si>
-    <t>-2.0%</t>
-  </si>
-  <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>25.2 → 32.3</t>
+    <t>28.5 → 37.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>25.2</t>
-  </si>
-  <si>
-    <t>32.3</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>73.0 → 58.9</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>73.0</t>
-  </si>
-  <si>
-    <t>58.9</t>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>37.2</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.2 → 44.9</t>
+    <t>46.9 → 50.4</t>
+  </si>
+  <si>
+    <t>46.9</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.6% → -2.4%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.6%</t>
+  </si>
+  <si>
+    <t>-2.4%</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>53.2</t>
-  </si>
-  <si>
-    <t>44.9</t>
-  </si>
-  <si>
-    <t>62.9 → 47.7</t>
-  </si>
-  <si>
-    <t>62.9</t>
-  </si>
-  <si>
-    <t>47.7</t>
-  </si>
-  <si>
-    <t>52.0 → 45.0</t>
-  </si>
-  <si>
-    <t>52.0</t>
-  </si>
-  <si>
-    <t>45.0</t>
-  </si>
-  <si>
-    <t>51.8 → 44.8</t>
-  </si>
-  <si>
-    <t>51.8</t>
-  </si>
-  <si>
-    <t>44.8</t>
-  </si>
-  <si>
-    <t>53.9 → 49.5</t>
-  </si>
-  <si>
-    <t>53.9</t>
-  </si>
-  <si>
-    <t>49.5</t>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>52.6 → 48.4</t>
+  </si>
+  <si>
+    <t>52.6</t>
+  </si>
+  <si>
+    <t>48.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1127,10 +1091,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>28491.05</v>
+        <v>27981.95</v>
       </c>
       <c r="E2">
-        <v>-1.22</v>
+        <v>-1.79</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1139,43 +1103,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-3.9</v>
+        <v>-5.62</v>
       </c>
       <c r="I2">
-        <v>19.86</v>
+        <v>17.72</v>
       </c>
       <c r="J2">
-        <v>-2.48</v>
+        <v>-3.51</v>
       </c>
       <c r="K2">
-        <v>-2.32</v>
+        <v>-3.65</v>
       </c>
       <c r="L2">
-        <v>9.19</v>
+        <v>7.03</v>
       </c>
       <c r="M2">
-        <v>12.48</v>
+        <v>10.06</v>
       </c>
       <c r="N2">
-        <v>23.19</v>
+        <v>22.8</v>
       </c>
       <c r="O2">
         <v>81</v>
       </c>
       <c r="Q2">
-        <v>28813.6</v>
+        <v>28609.96</v>
       </c>
       <c r="R2">
-        <v>29191.62</v>
+        <v>29120.14</v>
       </c>
       <c r="S2">
-        <v>27970.17</v>
+        <v>27999.88</v>
       </c>
       <c r="T2">
-        <v>27127.12</v>
+        <v>27131.28</v>
       </c>
       <c r="U2">
-        <v>5.03</v>
+        <v>3.14</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1190,16 +1154,16 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>44.91</v>
+        <v>36.13</v>
       </c>
       <c r="AA2">
-        <v>211.53</v>
+        <v>119.5</v>
       </c>
       <c r="AB2">
-        <v>376.08</v>
+        <v>324.76</v>
       </c>
       <c r="AC2">
-        <v>-164.55</v>
+        <v>-205.26</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1208,22 +1172,22 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>368.54</v>
+        <v>410.03</v>
       </c>
       <c r="AH2">
-        <v>29751.01</v>
+        <v>29887.79</v>
       </c>
       <c r="AI2">
-        <v>28632.22</v>
+        <v>28352.48</v>
       </c>
       <c r="AJ2">
-        <v>28374.42</v>
+        <v>29113.69</v>
       </c>
       <c r="AK2" t="s">
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>33.68</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1237,10 +1201,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9704.200000000001</v>
+        <v>9756.9</v>
       </c>
       <c r="E3">
-        <v>0.14</v>
+        <v>0.54</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1249,91 +1213,91 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-7.61</v>
+        <v>-7.11</v>
       </c>
       <c r="I3">
-        <v>13.21</v>
+        <v>13.83</v>
       </c>
       <c r="J3">
-        <v>-1.64</v>
+        <v>-1.21</v>
       </c>
       <c r="K3">
-        <v>-2.99</v>
+        <v>-1.73</v>
       </c>
       <c r="L3">
-        <v>-4.9</v>
+        <v>-4.17</v>
       </c>
       <c r="M3">
-        <v>10.76</v>
+        <v>10.9</v>
       </c>
       <c r="N3">
-        <v>12.19</v>
+        <v>12.08</v>
       </c>
       <c r="O3">
         <v>62</v>
       </c>
       <c r="Q3">
-        <v>9779.08</v>
+        <v>9755.129999999999</v>
       </c>
       <c r="R3">
-        <v>9855.059999999999</v>
+        <v>9842.709999999999</v>
       </c>
       <c r="S3">
-        <v>9854.879999999999</v>
+        <v>9850.870000000001</v>
       </c>
       <c r="T3">
-        <v>9739.66</v>
+        <v>9741.700000000001</v>
       </c>
       <c r="U3">
-        <v>-0.36</v>
+        <v>0.16</v>
       </c>
       <c r="V3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
       </c>
       <c r="X3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y3">
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>36.85</v>
+        <v>42.76</v>
       </c>
       <c r="AA3">
-        <v>-37.2</v>
+        <v>-37.83</v>
       </c>
       <c r="AB3">
-        <v>-23.17</v>
+        <v>-26.11</v>
       </c>
       <c r="AC3">
-        <v>-14.02</v>
+        <v>-11.72</v>
       </c>
       <c r="AD3">
-        <v>19.41</v>
+        <v>19.46</v>
       </c>
       <c r="AE3">
-        <v>30.89</v>
+        <v>21.85</v>
       </c>
       <c r="AF3">
-        <v>87.23</v>
+        <v>92.08</v>
       </c>
       <c r="AH3">
-        <v>10040.27</v>
+        <v>10018.83</v>
       </c>
       <c r="AI3">
-        <v>9669.85</v>
+        <v>9666.58</v>
       </c>
       <c r="AJ3">
-        <v>9972.129999999999</v>
+        <v>9955.58</v>
       </c>
       <c r="AK3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL3">
-        <v>33.38</v>
+        <v>36.97</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1347,10 +1311,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11782.3</v>
+        <v>11703.6</v>
       </c>
       <c r="E4">
-        <v>-0.17</v>
+        <v>-0.67</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1359,43 +1323,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-6.78</v>
+        <v>-7.4</v>
       </c>
       <c r="I4">
-        <v>14.01</v>
+        <v>13.25</v>
       </c>
       <c r="J4">
-        <v>-2.58</v>
+        <v>-2.21</v>
       </c>
       <c r="K4">
-        <v>-3.89</v>
+        <v>-4.14</v>
       </c>
       <c r="L4">
-        <v>5.81</v>
+        <v>4.63</v>
       </c>
       <c r="M4">
-        <v>-3.39</v>
+        <v>-4.17</v>
       </c>
       <c r="N4">
-        <v>11.13</v>
+        <v>10.82</v>
       </c>
       <c r="O4">
         <v>38</v>
       </c>
       <c r="Q4">
-        <v>11875.72</v>
+        <v>11822.8</v>
       </c>
       <c r="R4">
-        <v>12051.02</v>
+        <v>12025.07</v>
       </c>
       <c r="S4">
-        <v>11865.24</v>
+        <v>11869.11</v>
       </c>
       <c r="T4">
-        <v>11682.76</v>
+        <v>11679.68</v>
       </c>
       <c r="U4">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1410,16 +1374,16 @@
         <v>3</v>
       </c>
       <c r="Z4">
-        <v>38.35</v>
+        <v>34.59</v>
       </c>
       <c r="AA4">
-        <v>-6.28</v>
+        <v>-25.27</v>
       </c>
       <c r="AB4">
-        <v>44.21</v>
+        <v>30.31</v>
       </c>
       <c r="AC4">
-        <v>-50.48</v>
+        <v>-55.58</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1428,22 +1392,22 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>104.6</v>
+        <v>111.24</v>
       </c>
       <c r="AH4">
-        <v>12308.57</v>
+        <v>12312.64</v>
       </c>
       <c r="AI4">
-        <v>11793.48</v>
+        <v>11737.5</v>
       </c>
       <c r="AJ4">
-        <v>12108.84</v>
+        <v>11977.93</v>
       </c>
       <c r="AK4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL4">
-        <v>23.66</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1457,10 +1421,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>37806.1</v>
+        <v>38028.4</v>
       </c>
       <c r="E5">
-        <v>-0.38</v>
+        <v>0.59</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1469,43 +1433,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-8.98</v>
+        <v>-8.44</v>
       </c>
       <c r="I5">
-        <v>14.22</v>
+        <v>14.9</v>
       </c>
       <c r="J5">
-        <v>-1.32</v>
+        <v>-0.19</v>
       </c>
       <c r="K5">
-        <v>-2.9</v>
+        <v>-2.03</v>
       </c>
       <c r="L5">
-        <v>-5.95</v>
+        <v>-5.98</v>
       </c>
       <c r="M5">
-        <v>9.56</v>
+        <v>10.25</v>
       </c>
       <c r="N5">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q5">
-        <v>37992.57</v>
+        <v>37978.27</v>
       </c>
       <c r="R5">
-        <v>38400.08</v>
+        <v>38360</v>
       </c>
       <c r="S5">
-        <v>38936.21</v>
+        <v>38891.41</v>
       </c>
       <c r="T5">
-        <v>37465.46</v>
+        <v>37475.26</v>
       </c>
       <c r="U5">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="V5" t="s">
         <v>80</v>
@@ -1520,40 +1484,40 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>28.46</v>
+        <v>37.23</v>
       </c>
       <c r="AA5">
-        <v>-296.83</v>
+        <v>-286.68</v>
       </c>
       <c r="AB5">
-        <v>-266.29</v>
+        <v>-270.37</v>
       </c>
       <c r="AC5">
-        <v>-30.53</v>
+        <v>-16.31</v>
       </c>
       <c r="AD5">
-        <v>2.35</v>
+        <v>23.1</v>
       </c>
       <c r="AE5">
-        <v>10.25</v>
+        <v>11.95</v>
       </c>
       <c r="AF5">
-        <v>338.28</v>
+        <v>351.99</v>
       </c>
       <c r="AH5">
-        <v>39056.47</v>
+        <v>39003.62</v>
       </c>
       <c r="AI5">
-        <v>37743.7</v>
+        <v>37716.39</v>
       </c>
       <c r="AJ5">
         <v>38783.5</v>
       </c>
       <c r="AK5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL5">
-        <v>26.89</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1567,10 +1531,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>46457.15</v>
+        <v>46240.55</v>
       </c>
       <c r="E6">
-        <v>0.9399999999999999</v>
+        <v>-0.47</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1579,43 +1543,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-18.64</v>
+        <v>-19.02</v>
       </c>
       <c r="I6">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="J6">
-        <v>-2.62</v>
+        <v>-2.14</v>
       </c>
       <c r="K6">
-        <v>-7.02</v>
+        <v>-6.64</v>
       </c>
       <c r="L6">
-        <v>-3.46</v>
+        <v>-4.1</v>
       </c>
       <c r="M6">
-        <v>-16.65</v>
+        <v>-16.96</v>
       </c>
       <c r="N6">
-        <v>3.22</v>
+        <v>2.79</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>46716.21</v>
+        <v>46513.74</v>
       </c>
       <c r="R6">
-        <v>48003.89</v>
+        <v>47846.74</v>
       </c>
       <c r="S6">
-        <v>48692.7</v>
+        <v>48636.33</v>
       </c>
       <c r="T6">
-        <v>50701.06</v>
+        <v>50654.65</v>
       </c>
       <c r="U6">
-        <v>-8.369999999999999</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="V6" t="s">
         <v>80</v>
@@ -1630,40 +1594,40 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>32.26</v>
+        <v>30.69</v>
       </c>
       <c r="AA6">
-        <v>-648.84</v>
+        <v>-683.4299999999999</v>
       </c>
       <c r="AB6">
-        <v>-468.53</v>
+        <v>-511.51</v>
       </c>
       <c r="AC6">
-        <v>-180.32</v>
+        <v>-171.92</v>
       </c>
       <c r="AD6">
-        <v>11.14</v>
+        <v>21.05</v>
       </c>
       <c r="AE6">
-        <v>4.54</v>
+        <v>10.73</v>
       </c>
       <c r="AF6">
-        <v>574.98</v>
+        <v>575.09</v>
       </c>
       <c r="AH6">
-        <v>50028.97</v>
+        <v>49908.51</v>
       </c>
       <c r="AI6">
-        <v>45978.81</v>
+        <v>45784.98</v>
       </c>
       <c r="AJ6">
-        <v>48094.23</v>
+        <v>47812.65</v>
       </c>
       <c r="AK6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL6">
-        <v>55.39</v>
+        <v>58.31</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1677,10 +1641,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26003.9</v>
+        <v>25813.05</v>
       </c>
       <c r="E7">
-        <v>-1.1</v>
+        <v>-0.73</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1689,43 +1653,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-8.640000000000001</v>
+        <v>-9.31</v>
       </c>
       <c r="I7">
-        <v>10.55</v>
+        <v>9.74</v>
       </c>
       <c r="J7">
-        <v>-0.93</v>
+        <v>-2.17</v>
       </c>
       <c r="K7">
-        <v>-3.63</v>
+        <v>-3.84</v>
       </c>
       <c r="L7">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="M7">
-        <v>-1.19</v>
+        <v>-1.88</v>
       </c>
       <c r="N7">
-        <v>7.59</v>
+        <v>7.26</v>
       </c>
       <c r="O7">
         <v>44</v>
       </c>
       <c r="Q7">
-        <v>26250.29</v>
+        <v>26135.55</v>
       </c>
       <c r="R7">
-        <v>26326.12</v>
+        <v>26274.57</v>
       </c>
       <c r="S7">
-        <v>26581.8</v>
+        <v>26571.47</v>
       </c>
       <c r="T7">
-        <v>26657.15</v>
+        <v>26649.82</v>
       </c>
       <c r="U7">
-        <v>-2.45</v>
+        <v>-3.14</v>
       </c>
       <c r="V7" t="s">
         <v>80</v>
@@ -1740,40 +1704,40 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>38.12</v>
+        <v>33.84</v>
       </c>
       <c r="AA7">
-        <v>-106.58</v>
+        <v>-133.61</v>
       </c>
       <c r="AB7">
-        <v>-98.23999999999999</v>
+        <v>-105.31</v>
       </c>
       <c r="AC7">
-        <v>-8.34</v>
+        <v>-28.3</v>
       </c>
       <c r="AD7">
-        <v>58</v>
+        <v>32.13</v>
       </c>
       <c r="AE7">
-        <v>73.44</v>
+        <v>55.96</v>
       </c>
       <c r="AF7">
-        <v>265.89</v>
+        <v>270.68</v>
       </c>
       <c r="AH7">
-        <v>26783.22</v>
+        <v>26718.12</v>
       </c>
       <c r="AI7">
-        <v>25869.01</v>
+        <v>25831.03</v>
       </c>
       <c r="AJ7">
-        <v>26843.86</v>
+        <v>26568.68</v>
       </c>
       <c r="AK7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL7">
-        <v>25.48</v>
+        <v>28.82</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1787,10 +1751,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31496.7</v>
+        <v>31102.9</v>
       </c>
       <c r="E8">
-        <v>0.98</v>
+        <v>-1.25</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1799,43 +1763,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-20.24</v>
+        <v>-21.23</v>
       </c>
       <c r="I8">
-        <v>22.22</v>
+        <v>20.7</v>
       </c>
       <c r="J8">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="K8">
-        <v>-0.6899999999999999</v>
+        <v>-1.12</v>
       </c>
       <c r="L8">
-        <v>7.19</v>
+        <v>6.15</v>
       </c>
       <c r="M8">
-        <v>-11.13</v>
+        <v>-14.27</v>
       </c>
       <c r="N8">
-        <v>-1.58</v>
+        <v>-2.15</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>30901.97</v>
+        <v>31058.78</v>
       </c>
       <c r="R8">
-        <v>31042.12</v>
+        <v>31027.06</v>
       </c>
       <c r="S8">
-        <v>29575.84</v>
+        <v>29657.66</v>
       </c>
       <c r="T8">
-        <v>32273.26</v>
+        <v>32248.19</v>
       </c>
       <c r="U8">
-        <v>-2.41</v>
+        <v>-3.55</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1850,43 +1814,43 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>60.17</v>
+        <v>55.2</v>
       </c>
       <c r="AA8">
-        <v>286.75</v>
+        <v>280.13</v>
       </c>
       <c r="AB8">
-        <v>334.15</v>
+        <v>323.34</v>
       </c>
       <c r="AC8">
-        <v>-47.39</v>
+        <v>-43.22</v>
       </c>
       <c r="AD8">
-        <v>66.28</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="AE8">
-        <v>41.09</v>
+        <v>57.37</v>
       </c>
       <c r="AF8">
-        <v>625.0599999999999</v>
+        <v>639.6</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32071.35</v>
+        <v>32042.72</v>
       </c>
       <c r="AI8">
-        <v>30012.89</v>
+        <v>30011.4</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
       </c>
       <c r="AK8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL8">
-        <v>21.84</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1900,10 +1864,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16402.5</v>
+        <v>16269.35</v>
       </c>
       <c r="E9">
-        <v>-1.09</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1912,28 +1876,28 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-1.56</v>
+        <v>-2.36</v>
       </c>
       <c r="I9">
-        <v>4.72</v>
+        <v>3.87</v>
       </c>
       <c r="J9">
-        <v>-1.07</v>
+        <v>-1.8</v>
       </c>
       <c r="K9">
-        <v>-0.72</v>
+        <v>-1.37</v>
       </c>
       <c r="N9">
-        <v>23.12</v>
+        <v>18.43</v>
       </c>
       <c r="Q9">
-        <v>16534.06</v>
+        <v>16474.41</v>
       </c>
       <c r="R9">
-        <v>16565.05</v>
+        <v>16548.93</v>
       </c>
       <c r="S9">
-        <v>16221.32</v>
+        <v>16227.59</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1945,40 +1909,40 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>47.73</v>
+        <v>40.07</v>
       </c>
       <c r="AA9">
-        <v>80.62</v>
+        <v>54.5</v>
       </c>
       <c r="AB9">
-        <v>113.36</v>
+        <v>101.58</v>
       </c>
       <c r="AC9">
-        <v>-32.74</v>
+        <v>-47.09</v>
       </c>
       <c r="AD9">
-        <v>22.48</v>
+        <v>13.29</v>
       </c>
       <c r="AE9">
-        <v>26.26</v>
+        <v>21.99</v>
       </c>
       <c r="AF9">
-        <v>132.94</v>
+        <v>143.03</v>
       </c>
       <c r="AH9">
-        <v>16688.94</v>
+        <v>16729.26</v>
       </c>
       <c r="AI9">
-        <v>16441.15</v>
+        <v>16368.61</v>
       </c>
       <c r="AJ9">
         <v>16247.63</v>
       </c>
       <c r="AK9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL9">
-        <v>21.28</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1992,10 +1956,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9209.25</v>
+        <v>9212.049999999999</v>
       </c>
       <c r="E10">
-        <v>0.33</v>
+        <v>0.03</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -2004,43 +1968,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-5.7</v>
+        <v>-5.67</v>
       </c>
       <c r="I10">
-        <v>7.57</v>
+        <v>7.61</v>
       </c>
       <c r="J10">
-        <v>-2.04</v>
+        <v>-0.83</v>
       </c>
       <c r="K10">
-        <v>-3.14</v>
+        <v>-2.2</v>
       </c>
       <c r="L10">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="M10">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
-        <v>14.27</v>
+        <v>14.05</v>
       </c>
       <c r="O10">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q10">
-        <v>9231.6</v>
+        <v>9216.24</v>
       </c>
       <c r="R10">
-        <v>9359.09</v>
+        <v>9347.049999999999</v>
       </c>
       <c r="S10">
-        <v>9383.450000000001</v>
+        <v>9378.48</v>
       </c>
       <c r="T10">
-        <v>9350.5</v>
+        <v>9349.08</v>
       </c>
       <c r="U10">
-        <v>-1.51</v>
+        <v>-1.47</v>
       </c>
       <c r="V10" t="s">
         <v>80</v>
@@ -2055,40 +2019,40 @@
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>37.48</v>
+        <v>37.82</v>
       </c>
       <c r="AA10">
-        <v>-45.48</v>
+        <v>-48.51</v>
       </c>
       <c r="AB10">
-        <v>-23.8</v>
+        <v>-28.74</v>
       </c>
       <c r="AC10">
-        <v>-21.68</v>
+        <v>-19.77</v>
       </c>
       <c r="AD10">
-        <v>8.119999999999999</v>
+        <v>14.16</v>
       </c>
       <c r="AE10">
-        <v>3.98</v>
+        <v>7.88</v>
       </c>
       <c r="AF10">
-        <v>80.56999999999999</v>
+        <v>81.87</v>
       </c>
       <c r="AH10">
-        <v>9539.559999999999</v>
+        <v>9533.24</v>
       </c>
       <c r="AI10">
-        <v>9178.610000000001</v>
+        <v>9160.860000000001</v>
       </c>
       <c r="AJ10">
-        <v>9431.969999999999</v>
+        <v>9408.6</v>
       </c>
       <c r="AK10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL10">
-        <v>41.2</v>
+        <v>44.21</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2102,10 +2066,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1561.45</v>
+        <v>1534.1</v>
       </c>
       <c r="E11">
-        <v>0.26</v>
+        <v>-1.75</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2114,43 +2078,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-4.35</v>
+        <v>-6.03</v>
       </c>
       <c r="I11">
-        <v>24.58</v>
+        <v>22.4</v>
       </c>
       <c r="J11">
-        <v>-3.02</v>
+        <v>-4.77</v>
       </c>
       <c r="K11">
-        <v>-0.46</v>
+        <v>-4.15</v>
       </c>
       <c r="L11">
-        <v>9.9</v>
+        <v>5.66</v>
       </c>
       <c r="M11">
-        <v>-5.59</v>
+        <v>-5.67</v>
       </c>
       <c r="N11">
-        <v>-0.62</v>
+        <v>-1.03</v>
       </c>
       <c r="O11">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="Q11">
-        <v>1585.88</v>
+        <v>1570.5</v>
       </c>
       <c r="R11">
-        <v>1585.55</v>
+        <v>1583.5</v>
       </c>
       <c r="S11">
-        <v>1545.7</v>
+        <v>1546.09</v>
       </c>
       <c r="T11">
-        <v>1447.1</v>
+        <v>1447.4</v>
       </c>
       <c r="U11">
-        <v>7.9</v>
+        <v>5.99</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2165,40 +2129,40 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>46.37</v>
+        <v>40.33</v>
       </c>
       <c r="AA11">
-        <v>11.28</v>
+        <v>6.22</v>
       </c>
       <c r="AB11">
-        <v>18.07</v>
+        <v>15.7</v>
       </c>
       <c r="AC11">
-        <v>-6.79</v>
+        <v>-9.48</v>
       </c>
       <c r="AD11">
-        <v>13.79</v>
+        <v>1.87</v>
       </c>
       <c r="AE11">
-        <v>24.64</v>
+        <v>11.71</v>
       </c>
       <c r="AF11">
-        <v>32.21</v>
+        <v>32.15</v>
       </c>
       <c r="AH11">
-        <v>1631.46</v>
+        <v>1634.73</v>
       </c>
       <c r="AI11">
-        <v>1539.64</v>
+        <v>1532.27</v>
       </c>
       <c r="AJ11">
         <v>1523.72</v>
       </c>
       <c r="AK11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL11">
-        <v>43.03</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2212,10 +2176,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13189.85</v>
+        <v>13157.35</v>
       </c>
       <c r="E12">
-        <v>-0.03</v>
+        <v>-0.25</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2224,43 +2188,43 @@
         <v>9154.799999999999</v>
       </c>
       <c r="H12">
-        <v>-3.85</v>
+        <v>-4.09</v>
       </c>
       <c r="I12">
-        <v>44.08</v>
+        <v>43.72</v>
       </c>
       <c r="J12">
-        <v>-1.36</v>
+        <v>-2.84</v>
       </c>
       <c r="K12">
-        <v>2.13</v>
+        <v>0.96</v>
       </c>
       <c r="L12">
-        <v>-2.55</v>
+        <v>-2.07</v>
       </c>
       <c r="M12">
-        <v>40.68</v>
+        <v>39.43</v>
       </c>
       <c r="N12">
-        <v>18.64</v>
+        <v>18.41</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13375.2</v>
+        <v>13298.33</v>
       </c>
       <c r="R12">
-        <v>13198.38</v>
+        <v>13193.43</v>
       </c>
       <c r="S12">
-        <v>12816.81</v>
+        <v>12826.58</v>
       </c>
       <c r="T12">
-        <v>12093.01</v>
+        <v>12106</v>
       </c>
       <c r="U12">
-        <v>9.07</v>
+        <v>8.68</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2275,40 +2239,40 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>53.28</v>
+        <v>52.05</v>
       </c>
       <c r="AA12">
-        <v>141.47</v>
+        <v>123.71</v>
       </c>
       <c r="AB12">
-        <v>143.94</v>
+        <v>139.9</v>
       </c>
       <c r="AC12">
-        <v>-2.47</v>
+        <v>-16.19</v>
       </c>
       <c r="AD12">
-        <v>26.65</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>52.22</v>
+        <v>25</v>
       </c>
       <c r="AF12">
-        <v>207.98</v>
+        <v>204.55</v>
       </c>
       <c r="AH12">
-        <v>13541.17</v>
+        <v>13535.55</v>
       </c>
       <c r="AI12">
-        <v>12855.59</v>
+        <v>12851.31</v>
       </c>
       <c r="AJ12">
         <v>12921.88</v>
       </c>
       <c r="AK12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL12">
-        <v>30.81</v>
+        <v>27.94</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2322,10 +2286,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9659.5</v>
+        <v>9695.950000000001</v>
       </c>
       <c r="E13">
-        <v>-0.46</v>
+        <v>0.38</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2334,43 +2298,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-10.28</v>
+        <v>-9.94</v>
       </c>
       <c r="I13">
-        <v>4.97</v>
+        <v>5.36</v>
       </c>
       <c r="J13">
-        <v>-1.41</v>
+        <v>-0.33</v>
       </c>
       <c r="K13">
-        <v>-3.46</v>
+        <v>-2.43</v>
       </c>
       <c r="L13">
-        <v>-4.26</v>
+        <v>-4.21</v>
       </c>
       <c r="M13">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="N13">
-        <v>21.54</v>
+        <v>21.51</v>
       </c>
       <c r="O13">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q13">
-        <v>9696.51</v>
+        <v>9690.129999999999</v>
       </c>
       <c r="R13">
-        <v>9805.08</v>
+        <v>9792.299999999999</v>
       </c>
       <c r="S13">
-        <v>9894.799999999999</v>
+        <v>9885.959999999999</v>
       </c>
       <c r="T13">
-        <v>10036.8</v>
+        <v>10035.34</v>
       </c>
       <c r="U13">
-        <v>-3.76</v>
+        <v>-3.38</v>
       </c>
       <c r="V13" t="s">
         <v>80</v>
@@ -2385,40 +2349,40 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>30.83</v>
+        <v>36.48</v>
       </c>
       <c r="AA13">
-        <v>-66.40000000000001</v>
+        <v>-65.5</v>
       </c>
       <c r="AB13">
-        <v>-56.25</v>
+        <v>-58.1</v>
       </c>
       <c r="AC13">
-        <v>-10.15</v>
+        <v>-7.4</v>
       </c>
       <c r="AD13">
-        <v>6.1</v>
+        <v>22.19</v>
       </c>
       <c r="AE13">
-        <v>5.85</v>
+        <v>11.46</v>
       </c>
       <c r="AF13">
-        <v>88.52</v>
+        <v>91.62</v>
       </c>
       <c r="AH13">
-        <v>9980.51</v>
+        <v>9959.889999999999</v>
       </c>
       <c r="AI13">
-        <v>9629.639999999999</v>
+        <v>9624.709999999999</v>
       </c>
       <c r="AJ13">
-        <v>9916.76</v>
+        <v>9905.1</v>
       </c>
       <c r="AK13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL13">
-        <v>37.59</v>
+        <v>40.88</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2432,10 +2396,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8505.75</v>
+        <v>8511.700000000001</v>
       </c>
       <c r="E14">
-        <v>-1.21</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2444,43 +2408,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-13.91</v>
+        <v>-13.85</v>
       </c>
       <c r="I14">
-        <v>25.9</v>
+        <v>25.99</v>
       </c>
       <c r="J14">
-        <v>-1.14</v>
+        <v>-1.82</v>
       </c>
       <c r="K14">
-        <v>0.22</v>
+        <v>0.38</v>
       </c>
       <c r="L14">
-        <v>3.91</v>
+        <v>3.56</v>
       </c>
       <c r="M14">
-        <v>21.54</v>
+        <v>21.94</v>
       </c>
       <c r="N14">
-        <v>29.29</v>
+        <v>29.42</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8595.379999999999</v>
+        <v>8563.82</v>
       </c>
       <c r="R14">
-        <v>8648.9</v>
+        <v>8647.42</v>
       </c>
       <c r="S14">
-        <v>8507.26</v>
+        <v>8505.68</v>
       </c>
       <c r="T14">
-        <v>8597.209999999999</v>
+        <v>8598.219999999999</v>
       </c>
       <c r="U14">
-        <v>-1.06</v>
+        <v>-1.01</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2495,40 +2459,40 @@
         <v>1</v>
       </c>
       <c r="Z14">
-        <v>45.02</v>
+        <v>45.47</v>
       </c>
       <c r="AA14">
-        <v>19.84</v>
+        <v>11.38</v>
       </c>
       <c r="AB14">
-        <v>40.67</v>
+        <v>34.82</v>
       </c>
       <c r="AC14">
-        <v>-20.83</v>
+        <v>-23.43</v>
       </c>
       <c r="AD14">
-        <v>13.72</v>
+        <v>8.1</v>
       </c>
       <c r="AE14">
-        <v>18.56</v>
+        <v>13.4</v>
       </c>
       <c r="AF14">
-        <v>124.72</v>
+        <v>125.78</v>
       </c>
       <c r="AH14">
-        <v>8822.15</v>
+        <v>8824.99</v>
       </c>
       <c r="AI14">
-        <v>8475.65</v>
+        <v>8469.85</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
       </c>
       <c r="AK14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL14">
-        <v>19.54</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2542,10 +2506,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26792.65</v>
+        <v>26780.7</v>
       </c>
       <c r="E15">
-        <v>-1.45</v>
+        <v>-0.04</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2554,43 +2518,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-1.45</v>
+        <v>-1.49</v>
       </c>
       <c r="I15">
-        <v>24.88</v>
+        <v>24.83</v>
       </c>
       <c r="J15">
-        <v>0.86</v>
+        <v>0.58</v>
       </c>
       <c r="K15">
-        <v>0.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L15">
-        <v>11.23</v>
+        <v>10.76</v>
       </c>
       <c r="M15">
-        <v>20.34</v>
+        <v>19.76</v>
       </c>
       <c r="N15">
-        <v>13.35</v>
+        <v>13.12</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26889.2</v>
+        <v>26920.08</v>
       </c>
       <c r="R15">
-        <v>26602.07</v>
+        <v>26612.92</v>
       </c>
       <c r="S15">
-        <v>26096.62</v>
+        <v>26132.44</v>
       </c>
       <c r="T15">
-        <v>23744.42</v>
+        <v>23766.48</v>
       </c>
       <c r="U15">
-        <v>12.84</v>
+        <v>12.68</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2605,43 +2569,43 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>58.85</v>
+        <v>58.48</v>
       </c>
       <c r="AA15">
-        <v>228.35</v>
+        <v>217.53</v>
       </c>
       <c r="AB15">
-        <v>215.35</v>
+        <v>215.79</v>
       </c>
       <c r="AC15">
-        <v>13</v>
+        <v>1.75</v>
       </c>
       <c r="AD15">
-        <v>75.78</v>
+        <v>50.93</v>
       </c>
       <c r="AE15">
-        <v>83.38</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="AF15">
-        <v>315.18</v>
+        <v>307.44</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27065.75</v>
+        <v>27082.93</v>
       </c>
       <c r="AI15">
-        <v>26138.38</v>
+        <v>26142.91</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
       </c>
       <c r="AK15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL15">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2655,10 +2619,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>891.3</v>
+        <v>893.15</v>
       </c>
       <c r="E16">
-        <v>-1.42</v>
+        <v>0.21</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2667,43 +2631,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-7.99</v>
+        <v>-7.79</v>
       </c>
       <c r="I16">
-        <v>36.88</v>
+        <v>37.17</v>
       </c>
       <c r="J16">
-        <v>-2.89</v>
+        <v>-1.87</v>
       </c>
       <c r="K16">
-        <v>-2.38</v>
+        <v>0.22</v>
       </c>
       <c r="L16">
-        <v>16.88</v>
+        <v>16.81</v>
       </c>
       <c r="M16">
-        <v>-2.02</v>
+        <v>-2.54</v>
       </c>
       <c r="N16">
-        <v>16.9</v>
+        <v>16.66</v>
       </c>
       <c r="O16">
         <v>74</v>
       </c>
       <c r="Q16">
-        <v>904.8099999999999</v>
+        <v>901.41</v>
       </c>
       <c r="R16">
-        <v>900.85</v>
+        <v>900.58</v>
       </c>
       <c r="S16">
-        <v>896.29</v>
+        <v>898.04</v>
       </c>
       <c r="T16">
-        <v>832</v>
+        <v>831.75</v>
       </c>
       <c r="U16">
-        <v>7.13</v>
+        <v>7.38</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2718,40 +2682,40 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>44.8</v>
+        <v>45.93</v>
       </c>
       <c r="AA16">
-        <v>3.32</v>
+        <v>2.19</v>
       </c>
       <c r="AB16">
-        <v>5.06</v>
+        <v>4.48</v>
       </c>
       <c r="AC16">
-        <v>-1.73</v>
+        <v>-2.29</v>
       </c>
       <c r="AD16">
-        <v>26.08</v>
+        <v>10.85</v>
       </c>
       <c r="AE16">
-        <v>43.19</v>
+        <v>27.37</v>
       </c>
       <c r="AF16">
-        <v>16.39</v>
+        <v>17.08</v>
       </c>
       <c r="AH16">
         <v>920.45</v>
       </c>
       <c r="AI16">
-        <v>881.26</v>
+        <v>880.7</v>
       </c>
       <c r="AJ16">
         <v>869.13</v>
       </c>
       <c r="AK16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL16">
-        <v>27.45</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2765,10 +2729,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30756.6</v>
+        <v>30525.25</v>
       </c>
       <c r="E17">
-        <v>-0.26</v>
+        <v>-0.75</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2777,43 +2741,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-9.81</v>
+        <v>-10.49</v>
       </c>
       <c r="I17">
-        <v>8.44</v>
+        <v>7.62</v>
       </c>
       <c r="J17">
-        <v>-0.78</v>
+        <v>-1.21</v>
       </c>
       <c r="K17">
-        <v>-3.2</v>
+        <v>-3.43</v>
       </c>
       <c r="L17">
-        <v>4.06</v>
+        <v>3.17</v>
       </c>
       <c r="M17">
-        <v>-5.45</v>
+        <v>-6.57</v>
       </c>
       <c r="N17">
-        <v>5.04</v>
+        <v>4.69</v>
       </c>
       <c r="O17">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q17">
-        <v>30828.5</v>
+        <v>30753.67</v>
       </c>
       <c r="R17">
-        <v>31023.27</v>
+        <v>30971.55</v>
       </c>
       <c r="S17">
-        <v>31093</v>
+        <v>31097.16</v>
       </c>
       <c r="T17">
-        <v>31669.48</v>
+        <v>31655.74</v>
       </c>
       <c r="U17">
-        <v>-2.88</v>
+        <v>-3.57</v>
       </c>
       <c r="V17" t="s">
         <v>80</v>
@@ -2828,40 +2792,40 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>41.74</v>
+        <v>36.03</v>
       </c>
       <c r="AA17">
-        <v>-95.92</v>
+        <v>-118.74</v>
       </c>
       <c r="AB17">
-        <v>-65.81</v>
+        <v>-76.39</v>
       </c>
       <c r="AC17">
-        <v>-30.11</v>
+        <v>-42.35</v>
       </c>
       <c r="AD17">
-        <v>62.33</v>
+        <v>38.86</v>
       </c>
       <c r="AE17">
-        <v>56.02</v>
+        <v>51.99</v>
       </c>
       <c r="AF17">
-        <v>250.65</v>
+        <v>258.86</v>
       </c>
       <c r="AH17">
-        <v>31526.84</v>
+        <v>31455.24</v>
       </c>
       <c r="AI17">
-        <v>30519.7</v>
+        <v>30487.85</v>
       </c>
       <c r="AJ17">
-        <v>30549.87</v>
+        <v>31236.31</v>
       </c>
       <c r="AK17" t="s">
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>30.15</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2875,10 +2839,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16669.85</v>
+        <v>16629.1</v>
       </c>
       <c r="E18">
-        <v>-1.6</v>
+        <v>-0.24</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2887,28 +2851,28 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-1.6</v>
+        <v>-1.84</v>
       </c>
       <c r="I18">
-        <v>8.220000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="J18">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="K18">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="N18">
-        <v>36.76</v>
+        <v>34.77</v>
       </c>
       <c r="Q18">
-        <v>16740.84</v>
+        <v>16749.33</v>
       </c>
       <c r="R18">
-        <v>16608.35</v>
+        <v>16604.31</v>
       </c>
       <c r="S18">
-        <v>16463.96</v>
+        <v>16478.17</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2920,40 +2884,40 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>54.42</v>
+        <v>52.56</v>
       </c>
       <c r="AA18">
-        <v>77.13</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AB18">
-        <v>62.26</v>
+        <v>63.74</v>
       </c>
       <c r="AC18">
-        <v>14.88</v>
+        <v>5.92</v>
       </c>
       <c r="AD18">
-        <v>78.86</v>
+        <v>55.15</v>
       </c>
       <c r="AE18">
-        <v>86.38</v>
+        <v>77.25</v>
       </c>
       <c r="AF18">
-        <v>186.27</v>
+        <v>181.7</v>
       </c>
       <c r="AH18">
-        <v>16893.09</v>
+        <v>16885.25</v>
       </c>
       <c r="AI18">
-        <v>16323.61</v>
+        <v>16323.37</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
       </c>
       <c r="AK18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL18">
-        <v>30.97</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2967,10 +2931,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9647.65</v>
+        <v>9621.35</v>
       </c>
       <c r="E19">
-        <v>-0.73</v>
+        <v>-0.27</v>
       </c>
       <c r="F19">
         <v>9968.25</v>
@@ -2979,28 +2943,28 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-3.22</v>
+        <v>-3.48</v>
       </c>
       <c r="I19">
-        <v>7.25</v>
+        <v>6.96</v>
       </c>
       <c r="J19">
-        <v>-1.19</v>
+        <v>-1.27</v>
       </c>
       <c r="K19">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="N19">
-        <v>37.12</v>
+        <v>34.94</v>
       </c>
       <c r="Q19">
-        <v>9733.01</v>
+        <v>9708.280000000001</v>
       </c>
       <c r="R19">
-        <v>9735.309999999999</v>
+        <v>9746.57</v>
       </c>
       <c r="S19">
-        <v>9539.35</v>
+        <v>9538.719999999999</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -3012,40 +2976,40 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>49.46</v>
+        <v>47.87</v>
       </c>
       <c r="AA19">
-        <v>69.45999999999999</v>
+        <v>55.55</v>
       </c>
       <c r="AB19">
-        <v>94</v>
+        <v>86.31</v>
       </c>
       <c r="AC19">
-        <v>-24.53</v>
+        <v>-30.75</v>
       </c>
       <c r="AD19">
         <v>0</v>
       </c>
       <c r="AE19">
-        <v>4.36</v>
+        <v>2.18</v>
       </c>
       <c r="AF19">
-        <v>135.14</v>
+        <v>136.19</v>
       </c>
       <c r="AH19">
-        <v>9970.120000000001</v>
+        <v>9928.57</v>
       </c>
       <c r="AI19">
-        <v>9500.5</v>
+        <v>9564.57</v>
       </c>
       <c r="AJ19">
         <v>9466.209999999999</v>
       </c>
       <c r="AK19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL19">
-        <v>22.37</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3059,10 +3023,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11142.3</v>
+        <v>11178.85</v>
       </c>
       <c r="E20">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3071,28 +3035,28 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-1.99</v>
+        <v>-1.67</v>
       </c>
       <c r="I20">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="J20">
-        <v>-0.65</v>
+        <v>0.26</v>
       </c>
       <c r="K20">
-        <v>-1.89</v>
+        <v>-0.42</v>
       </c>
       <c r="N20">
-        <v>5.43</v>
+        <v>6.91</v>
       </c>
       <c r="Q20">
-        <v>11104.76</v>
+        <v>11110.66</v>
       </c>
       <c r="R20">
-        <v>11201.86</v>
+        <v>11200</v>
       </c>
       <c r="S20">
-        <v>11178.2</v>
+        <v>11178.35</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3104,40 +3068,40 @@
         <v>1</v>
       </c>
       <c r="Z20">
-        <v>46.92</v>
+        <v>50.37</v>
       </c>
       <c r="AA20">
-        <v>-22.38</v>
+        <v>-18.58</v>
       </c>
       <c r="AB20">
-        <v>-7.41</v>
+        <v>-9.65</v>
       </c>
       <c r="AC20">
-        <v>-14.97</v>
+        <v>-8.93</v>
       </c>
       <c r="AD20">
-        <v>29.61</v>
+        <v>58.63</v>
       </c>
       <c r="AE20">
-        <v>13.72</v>
+        <v>32.79</v>
       </c>
       <c r="AF20">
-        <v>118.59</v>
+        <v>121.32</v>
       </c>
       <c r="AH20">
-        <v>11347.88</v>
+        <v>11346.21</v>
       </c>
       <c r="AI20">
-        <v>11055.83</v>
+        <v>11053.78</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
       </c>
       <c r="AK20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL20">
-        <v>22.62</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3151,10 +3115,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27762.1</v>
+        <v>27606.8</v>
       </c>
       <c r="E21">
-        <v>-0.87</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3163,43 +3127,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-4.89</v>
+        <v>-5.42</v>
       </c>
       <c r="I21">
-        <v>14.98</v>
+        <v>14.34</v>
       </c>
       <c r="J21">
-        <v>1.15</v>
+        <v>-0.45</v>
       </c>
       <c r="K21">
-        <v>-1.01</v>
+        <v>-0.91</v>
       </c>
       <c r="L21">
-        <v>5.99</v>
+        <v>5.21</v>
       </c>
       <c r="M21">
-        <v>4.01</v>
+        <v>3.41</v>
       </c>
       <c r="N21">
-        <v>7.97</v>
+        <v>7.68</v>
       </c>
       <c r="O21">
         <v>68</v>
       </c>
       <c r="Q21">
-        <v>27799.29</v>
+        <v>27774.08</v>
       </c>
       <c r="R21">
-        <v>27512.92</v>
+        <v>27506.04</v>
       </c>
       <c r="S21">
-        <v>27896.14</v>
+        <v>27893.03</v>
       </c>
       <c r="T21">
-        <v>27637.67</v>
+        <v>27635.47</v>
       </c>
       <c r="U21">
-        <v>0.45</v>
+        <v>-0.1</v>
       </c>
       <c r="V21" t="s">
         <v>80</v>
@@ -3211,43 +3175,43 @@
         <v>80</v>
       </c>
       <c r="Y21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z21">
-        <v>52.61</v>
+        <v>48.44</v>
       </c>
       <c r="AA21">
-        <v>-10.52</v>
+        <v>-13.65</v>
       </c>
       <c r="AB21">
-        <v>-80.09999999999999</v>
+        <v>-66.81</v>
       </c>
       <c r="AC21">
-        <v>69.58</v>
+        <v>53.16</v>
       </c>
       <c r="AD21">
-        <v>87.51000000000001</v>
+        <v>71.67</v>
       </c>
       <c r="AE21">
-        <v>94.91</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="AF21">
-        <v>315.51</v>
+        <v>311.62</v>
       </c>
       <c r="AH21">
-        <v>27957.72</v>
+        <v>27939.91</v>
       </c>
       <c r="AI21">
-        <v>27068.11</v>
+        <v>27072.18</v>
       </c>
       <c r="AJ21">
         <v>28265.67</v>
       </c>
       <c r="AK21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL21">
-        <v>34.49</v>
+        <v>32.98</v>
       </c>
     </row>
   </sheetData>
@@ -3428,7 +3392,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3448,7 +3412,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>94</v>
@@ -3457,2068 +3421,2062 @@
         <v>95</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="E6" s="6" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="E8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>120</v>
-      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="A12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8">
+        <v>-2.32</v>
+      </c>
+      <c r="D12" s="8">
+        <v>-3.65</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.33</v>
+      </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>125</v>
+      <c r="A13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8">
+        <v>-2.99</v>
+      </c>
+      <c r="D13" s="8">
+        <v>-1.73</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="8">
-        <v>0.34</v>
+        <v>-3.89</v>
       </c>
       <c r="D14" s="8">
-        <v>-2.32</v>
+        <v>-4.14</v>
       </c>
       <c r="E14" s="9">
-        <v>-2.66</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="8">
-        <v>-1.73</v>
+        <v>-2.9</v>
       </c>
       <c r="D15" s="8">
-        <v>-2.99</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-1.26</v>
+        <v>-2.03</v>
+      </c>
+      <c r="E15" s="10">
+        <v>0.87</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="8">
-        <v>-2.31</v>
+        <v>-7.02</v>
       </c>
       <c r="D16" s="8">
-        <v>-3.89</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-1.58</v>
+        <v>-6.64</v>
+      </c>
+      <c r="E16" s="10">
+        <v>0.38</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="8">
-        <v>-2.01</v>
+        <v>-3.63</v>
       </c>
       <c r="D17" s="8">
-        <v>-2.9</v>
+        <v>-3.84</v>
       </c>
       <c r="E17" s="9">
-        <v>-0.89</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="8">
-        <v>-6.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D18" s="8">
-        <v>-7.02</v>
+        <v>-1.12</v>
       </c>
       <c r="E18" s="9">
-        <v>-0.72</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="8">
-        <v>-1.13</v>
+        <v>-0.72</v>
       </c>
       <c r="D19" s="8">
-        <v>-3.63</v>
+        <v>-1.37</v>
       </c>
       <c r="E19" s="9">
-        <v>-2.5</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="8">
-        <v>1.57</v>
+        <v>-3.14</v>
       </c>
       <c r="D20" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-2.26</v>
+        <v>-2.2</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="8">
-        <v>1.56</v>
+        <v>-0.46</v>
       </c>
       <c r="D21" s="8">
-        <v>-0.72</v>
+        <v>-4.15</v>
       </c>
       <c r="E21" s="9">
-        <v>-2.28</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="8">
-        <v>-2.44</v>
+        <v>2.13</v>
       </c>
       <c r="D22" s="8">
-        <v>-3.14</v>
+        <v>0.96</v>
       </c>
       <c r="E22" s="9">
-        <v>-0.7</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="8">
-        <v>-3.79</v>
+        <v>-3.46</v>
       </c>
       <c r="D23" s="8">
-        <v>-0.46</v>
+        <v>-2.43</v>
       </c>
       <c r="E23" s="10">
-        <v>3.33</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="8">
-        <v>3.73</v>
+        <v>0.22</v>
       </c>
       <c r="D24" s="8">
-        <v>2.13</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-1.6</v>
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="8">
-        <v>-2.39</v>
+        <v>0.49</v>
       </c>
       <c r="D25" s="8">
-        <v>-3.46</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-1.07</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E25" s="10">
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="8">
-        <v>2.9</v>
+        <v>-2.38</v>
       </c>
       <c r="D26" s="8">
         <v>0.22</v>
       </c>
-      <c r="E26" s="9">
-        <v>-2.68</v>
+      <c r="E26" s="10">
+        <v>2.6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="8">
-        <v>2.46</v>
+        <v>-3.2</v>
       </c>
       <c r="D27" s="8">
-        <v>0.49</v>
+        <v>-3.43</v>
       </c>
       <c r="E27" s="9">
-        <v>-1.97</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="8">
-        <v>0.3</v>
+        <v>-0.68</v>
       </c>
       <c r="D28" s="8">
-        <v>-2.38</v>
+        <v>-0.7</v>
       </c>
       <c r="E28" s="9">
-        <v>-2.68</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="8">
-        <v>-1.38</v>
+        <v>2.22</v>
       </c>
       <c r="D29" s="8">
-        <v>-3.2</v>
+        <v>2.14</v>
       </c>
       <c r="E29" s="9">
-        <v>-1.82</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="8">
-        <v>1.11</v>
+        <v>-1.89</v>
       </c>
       <c r="D30" s="8">
-        <v>-0.68</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-1.79</v>
+        <v>-0.42</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1.47</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="8">
-        <v>4.15</v>
+        <v>-1.01</v>
       </c>
       <c r="D31" s="8">
-        <v>2.22</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-1.93</v>
+        <v>-0.91</v>
+      </c>
+      <c r="E31" s="10">
+        <v>0.1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="8">
-        <v>-1.28</v>
+        <v>-2.48</v>
       </c>
       <c r="D32" s="8">
-        <v>-1.89</v>
+        <v>-3.51</v>
       </c>
       <c r="E32" s="9">
-        <v>-0.61</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="8">
-        <v>1.76</v>
+        <v>-1.64</v>
       </c>
       <c r="D33" s="8">
-        <v>-1.01</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-2.77</v>
+        <v>-1.21</v>
+      </c>
+      <c r="E33" s="10">
+        <v>0.43</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="8">
-        <v>-0.89</v>
+        <v>-2.58</v>
       </c>
       <c r="D34" s="8">
-        <v>-2.48</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-1.59</v>
+        <v>-2.21</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0.37</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="8">
-        <v>-1.59</v>
+        <v>-1.32</v>
       </c>
       <c r="D35" s="8">
-        <v>-1.64</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.05</v>
+        <v>-0.19</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1.13</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="8">
-        <v>-1.72</v>
+        <v>-2.62</v>
       </c>
       <c r="D36" s="8">
-        <v>-2.58</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-0.86</v>
+        <v>-2.14</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.48</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="8">
-        <v>-1.01</v>
+        <v>-0.93</v>
       </c>
       <c r="D37" s="8">
-        <v>-1.32</v>
+        <v>-2.17</v>
       </c>
       <c r="E37" s="9">
-        <v>-0.31</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="8">
-        <v>-3.16</v>
+        <v>2.36</v>
       </c>
       <c r="D38" s="8">
-        <v>-2.62</v>
+        <v>2.59</v>
       </c>
       <c r="E38" s="10">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="8">
-        <v>0.52</v>
+        <v>-1.07</v>
       </c>
       <c r="D39" s="8">
-        <v>-0.93</v>
+        <v>-1.8</v>
       </c>
       <c r="E39" s="9">
-        <v>-1.45</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="8">
-        <v>1.94</v>
+        <v>-2.04</v>
       </c>
       <c r="D40" s="8">
-        <v>2.36</v>
+        <v>-0.83</v>
       </c>
       <c r="E40" s="10">
-        <v>0.42</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="8">
-        <v>0.43</v>
+        <v>-3.02</v>
       </c>
       <c r="D41" s="8">
-        <v>-1.07</v>
+        <v>-4.77</v>
       </c>
       <c r="E41" s="9">
-        <v>-1.5</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="8">
-        <v>-1.75</v>
+        <v>-1.36</v>
       </c>
       <c r="D42" s="8">
-        <v>-2.04</v>
+        <v>-2.84</v>
       </c>
       <c r="E42" s="9">
-        <v>-0.29</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="8">
-        <v>-2.87</v>
+        <v>-1.41</v>
       </c>
       <c r="D43" s="8">
-        <v>-3.02</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.15</v>
+        <v>-0.33</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1.08</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="8">
-        <v>-1.4</v>
+        <v>-1.14</v>
       </c>
       <c r="D44" s="8">
-        <v>-1.36</v>
-      </c>
-      <c r="E44" s="10">
-        <v>0.04</v>
+        <v>-1.82</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="8">
-        <v>-0.79</v>
+        <v>0.86</v>
       </c>
       <c r="D45" s="8">
-        <v>-1.41</v>
+        <v>0.58</v>
       </c>
       <c r="E45" s="9">
-        <v>-0.62</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="8">
-        <v>0.82</v>
+        <v>-2.89</v>
       </c>
       <c r="D46" s="8">
-        <v>-1.14</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-1.96</v>
+        <v>-1.87</v>
+      </c>
+      <c r="E46" s="10">
+        <v>1.02</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="8">
-        <v>3.22</v>
+        <v>-0.78</v>
       </c>
       <c r="D47" s="8">
-        <v>0.86</v>
+        <v>-1.21</v>
       </c>
       <c r="E47" s="9">
-        <v>-2.36</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>-1.41</v>
+        <v>0.44</v>
       </c>
       <c r="D48" s="8">
-        <v>-2.89</v>
+        <v>0.26</v>
       </c>
       <c r="E48" s="9">
-        <v>-1.48</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-1.19</v>
       </c>
       <c r="D49" s="8">
-        <v>-0.78</v>
+        <v>-1.27</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.71</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="8">
-        <v>3.19</v>
+        <v>-0.65</v>
       </c>
       <c r="D50" s="8">
-        <v>0.44</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-2.75</v>
+        <v>0.26</v>
+      </c>
+      <c r="E50" s="10">
+        <v>0.91</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="8">
-        <v>-0.22</v>
+        <v>1.15</v>
       </c>
       <c r="D51" s="8">
-        <v>-1.19</v>
+        <v>-0.45</v>
       </c>
       <c r="E51" s="9">
-        <v>-0.97</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" s="8">
-        <v>-0.83</v>
+        <v>12.48</v>
       </c>
       <c r="D52" s="8">
-        <v>-0.65</v>
-      </c>
-      <c r="E52" s="10">
-        <v>0.18</v>
+        <v>10.06</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C53" s="8">
-        <v>1.83</v>
+        <v>10.76</v>
       </c>
       <c r="D53" s="8">
-        <v>1.15</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-0.68</v>
+        <v>10.9</v>
+      </c>
+      <c r="E53" s="10">
+        <v>0.14</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="8">
-        <v>13.65</v>
+        <v>-3.39</v>
       </c>
       <c r="D54" s="8">
-        <v>12.48</v>
+        <v>-4.17</v>
       </c>
       <c r="E54" s="9">
-        <v>-1.17</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="8">
-        <v>9.41</v>
+        <v>9.56</v>
       </c>
       <c r="D55" s="8">
-        <v>10.76</v>
+        <v>10.25</v>
       </c>
       <c r="E55" s="10">
-        <v>1.35</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="8">
-        <v>-3.72</v>
+        <v>-16.65</v>
       </c>
       <c r="D56" s="8">
-        <v>-3.39</v>
-      </c>
-      <c r="E56" s="10">
-        <v>0.33</v>
+        <v>-16.96</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="8">
-        <v>9.42</v>
+        <v>-1.19</v>
       </c>
       <c r="D57" s="8">
-        <v>9.56</v>
-      </c>
-      <c r="E57" s="10">
-        <v>0.14</v>
+        <v>-1.88</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="8">
-        <v>-18.25</v>
+        <v>-11.13</v>
       </c>
       <c r="D58" s="8">
-        <v>-16.65</v>
-      </c>
-      <c r="E58" s="10">
-        <v>1.6</v>
+        <v>-14.27</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-3.14</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="8">
-        <v>-1.05</v>
+        <v>1.13</v>
       </c>
       <c r="D59" s="8">
-        <v>-1.19</v>
+        <v>1.12</v>
       </c>
       <c r="E59" s="9">
-        <v>-0.14</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="8">
-        <v>-12.69</v>
+        <v>-5.59</v>
       </c>
       <c r="D60" s="8">
-        <v>-11.13</v>
-      </c>
-      <c r="E60" s="10">
-        <v>1.56</v>
+        <v>-5.67</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="8">
-        <v>0.06</v>
+        <v>40.68</v>
       </c>
       <c r="D61" s="8">
-        <v>1.13</v>
-      </c>
-      <c r="E61" s="10">
-        <v>1.07</v>
+        <v>39.43</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="8">
-        <v>-4.95</v>
+        <v>1.99</v>
       </c>
       <c r="D62" s="8">
-        <v>-5.59</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-0.64</v>
+        <v>2.42</v>
+      </c>
+      <c r="E62" s="10">
+        <v>0.43</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="8">
-        <v>38.98</v>
+        <v>21.54</v>
       </c>
       <c r="D63" s="8">
-        <v>40.68</v>
+        <v>21.94</v>
       </c>
       <c r="E63" s="10">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="8">
-        <v>1.91</v>
+        <v>20.34</v>
       </c>
       <c r="D64" s="8">
-        <v>1.99</v>
-      </c>
-      <c r="E64" s="10">
-        <v>0.08</v>
+        <v>19.76</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="8">
-        <v>21.65</v>
+        <v>-2.02</v>
       </c>
       <c r="D65" s="8">
-        <v>21.54</v>
+        <v>-2.54</v>
       </c>
       <c r="E65" s="9">
-        <v>-0.11</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B66" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="8">
-        <v>22.58</v>
+        <v>-5.45</v>
       </c>
       <c r="D66" s="8">
-        <v>20.34</v>
+        <v>-6.57</v>
       </c>
       <c r="E66" s="9">
-        <v>-2.24</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="8">
-        <v>-1.44</v>
+        <v>4.01</v>
       </c>
       <c r="D67" s="8">
-        <v>-2.02</v>
+        <v>3.41</v>
       </c>
       <c r="E67" s="9">
-        <v>-0.58</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" s="8">
-        <v>-6.03</v>
+        <v>9.19</v>
       </c>
       <c r="D68" s="8">
-        <v>-5.45</v>
-      </c>
-      <c r="E68" s="10">
-        <v>0.58</v>
+        <v>7.03</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C69" s="8">
-        <v>3.81</v>
+        <v>-4.9</v>
       </c>
       <c r="D69" s="8">
-        <v>4.01</v>
+        <v>-4.17</v>
       </c>
       <c r="E69" s="10">
-        <v>0.2</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="8">
-        <v>10.59</v>
+        <v>5.81</v>
       </c>
       <c r="D70" s="8">
-        <v>9.19</v>
+        <v>4.63</v>
       </c>
       <c r="E70" s="9">
-        <v>-1.4</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="8">
-        <v>-5.2</v>
+        <v>-5.95</v>
       </c>
       <c r="D71" s="8">
-        <v>-4.9</v>
-      </c>
-      <c r="E71" s="10">
-        <v>0.3</v>
+        <v>-5.98</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="8">
-        <v>5.7</v>
+        <v>-3.46</v>
       </c>
       <c r="D72" s="8">
-        <v>5.81</v>
-      </c>
-      <c r="E72" s="10">
-        <v>0.11</v>
+        <v>-4.1</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="8">
-        <v>-5.57</v>
+        <v>4.2</v>
       </c>
       <c r="D73" s="8">
-        <v>-5.95</v>
+        <v>3.12</v>
       </c>
       <c r="E73" s="9">
-        <v>-0.38</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="8">
-        <v>-5.32</v>
+        <v>7.19</v>
       </c>
       <c r="D74" s="8">
-        <v>-3.46</v>
-      </c>
-      <c r="E74" s="10">
-        <v>1.86</v>
+        <v>6.15</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="8">
-        <v>5.76</v>
+        <v>-0.11</v>
       </c>
       <c r="D75" s="8">
-        <v>4.2</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-1.56</v>
+        <v>0.03</v>
+      </c>
+      <c r="E75" s="10">
+        <v>0.14</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="8">
-        <v>0.24</v>
+        <v>9.9</v>
       </c>
       <c r="D76" s="8">
-        <v>7.19</v>
-      </c>
-      <c r="E76" s="10">
-        <v>6.95</v>
+        <v>5.66</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-4.24</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="8">
-        <v>-0.51</v>
+        <v>-2.55</v>
       </c>
       <c r="D77" s="8">
-        <v>-0.11</v>
+        <v>-2.07</v>
       </c>
       <c r="E77" s="10">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="8">
-        <v>8.960000000000001</v>
+        <v>-4.26</v>
       </c>
       <c r="D78" s="8">
-        <v>9.9</v>
+        <v>-4.21</v>
       </c>
       <c r="E78" s="10">
-        <v>0.9399999999999999</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="8">
-        <v>-2.68</v>
+        <v>3.91</v>
       </c>
       <c r="D79" s="8">
-        <v>-2.55</v>
-      </c>
-      <c r="E79" s="10">
-        <v>0.13</v>
+        <v>3.56</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="8">
-        <v>-3.75</v>
+        <v>11.23</v>
       </c>
       <c r="D80" s="8">
-        <v>-4.26</v>
+        <v>10.76</v>
       </c>
       <c r="E80" s="9">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="8">
-        <v>6.96</v>
+        <v>16.88</v>
       </c>
       <c r="D81" s="8">
-        <v>3.91</v>
+        <v>16.81</v>
       </c>
       <c r="E81" s="9">
-        <v>-3.05</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="8">
-        <v>13.25</v>
+        <v>4.06</v>
       </c>
       <c r="D82" s="8">
-        <v>11.23</v>
+        <v>3.17</v>
       </c>
       <c r="E82" s="9">
-        <v>-2.02</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="8">
-        <v>16.91</v>
+        <v>5.99</v>
       </c>
       <c r="D83" s="8">
-        <v>16.88</v>
+        <v>5.21</v>
       </c>
       <c r="E83" s="9">
-        <v>-0.03</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C84" s="8">
-        <v>3.97</v>
+        <v>-3.9</v>
       </c>
       <c r="D84" s="8">
-        <v>4.06</v>
-      </c>
-      <c r="E84" s="10">
-        <v>0.09</v>
+        <v>-5.62</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C85" s="8">
-        <v>7.67</v>
+        <v>-7.61</v>
       </c>
       <c r="D85" s="8">
-        <v>5.99</v>
-      </c>
-      <c r="E85" s="9">
-        <v>-1.68</v>
+        <v>-7.11</v>
+      </c>
+      <c r="E85" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="8">
-        <v>-2.72</v>
+        <v>-6.78</v>
       </c>
       <c r="D86" s="8">
-        <v>-3.9</v>
+        <v>-7.4</v>
       </c>
       <c r="E86" s="9">
-        <v>-1.18</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="8">
-        <v>-7.74</v>
+        <v>-8.98</v>
       </c>
       <c r="D87" s="8">
-        <v>-7.61</v>
+        <v>-8.44</v>
       </c>
       <c r="E87" s="10">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="8">
-        <v>-6.62</v>
+        <v>-18.64</v>
       </c>
       <c r="D88" s="8">
-        <v>-6.78</v>
+        <v>-19.02</v>
       </c>
       <c r="E88" s="9">
-        <v>-0.16</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="8">
-        <v>-8.630000000000001</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="D89" s="8">
-        <v>-8.98</v>
+        <v>-9.31</v>
       </c>
       <c r="E89" s="9">
-        <v>-0.35</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="8">
-        <v>-19.4</v>
+        <v>-20.24</v>
       </c>
       <c r="D90" s="8">
-        <v>-18.64</v>
-      </c>
-      <c r="E90" s="10">
-        <v>0.76</v>
+        <v>-21.23</v>
+      </c>
+      <c r="E90" s="9">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="8">
-        <v>-7.62</v>
+        <v>-1.56</v>
       </c>
       <c r="D91" s="8">
-        <v>-8.640000000000001</v>
+        <v>-2.36</v>
       </c>
       <c r="E91" s="9">
-        <v>-1.02</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="8">
-        <v>-21.01</v>
+        <v>-5.7</v>
       </c>
       <c r="D92" s="8">
-        <v>-20.24</v>
+        <v>-5.67</v>
       </c>
       <c r="E92" s="10">
-        <v>0.77</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="8">
-        <v>-0.48</v>
+        <v>-4.35</v>
       </c>
       <c r="D93" s="8">
-        <v>-1.56</v>
+        <v>-6.03</v>
       </c>
       <c r="E93" s="9">
-        <v>-1.08</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="8">
-        <v>-6</v>
+        <v>-3.85</v>
       </c>
       <c r="D94" s="8">
-        <v>-5.7</v>
-      </c>
-      <c r="E94" s="10">
-        <v>0.3</v>
+        <v>-4.09</v>
+      </c>
+      <c r="E94" s="9">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="8">
-        <v>-5.84</v>
+        <v>-10.28</v>
       </c>
       <c r="D95" s="8">
-        <v>-4.35</v>
+        <v>-9.94</v>
       </c>
       <c r="E95" s="10">
-        <v>1.49</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="8">
-        <v>-3.82</v>
+        <v>-13.91</v>
       </c>
       <c r="D96" s="8">
-        <v>-3.85</v>
-      </c>
-      <c r="E96" s="9">
-        <v>-0.03</v>
+        <v>-13.85</v>
+      </c>
+      <c r="E96" s="10">
+        <v>0.06</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="8">
-        <v>-9.859999999999999</v>
+        <v>-1.45</v>
       </c>
       <c r="D97" s="8">
-        <v>-10.28</v>
+        <v>-1.49</v>
       </c>
       <c r="E97" s="9">
-        <v>-0.42</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="8">
-        <v>-12.86</v>
+        <v>-7.99</v>
       </c>
       <c r="D98" s="8">
-        <v>-13.91</v>
-      </c>
-      <c r="E98" s="9">
-        <v>-1.05</v>
+        <v>-7.79</v>
+      </c>
+      <c r="E98" s="10">
+        <v>0.2</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="8">
-        <v>0</v>
+        <v>-9.81</v>
       </c>
       <c r="D99" s="8">
-        <v>-1.45</v>
+        <v>-10.49</v>
       </c>
       <c r="E99" s="9">
-        <v>-1.45</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="8">
-        <v>-6.66</v>
+        <v>-1.6</v>
       </c>
       <c r="D100" s="8">
-        <v>-7.99</v>
+        <v>-1.84</v>
       </c>
       <c r="E100" s="9">
-        <v>-1.33</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="8">
-        <v>-9.57</v>
+        <v>-3.22</v>
       </c>
       <c r="D101" s="8">
-        <v>-9.81</v>
+        <v>-3.48</v>
       </c>
       <c r="E101" s="9">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="8">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="D102" s="8">
-        <v>-1.6</v>
-      </c>
-      <c r="E102" s="9">
-        <v>-1.6</v>
+        <v>-1.67</v>
+      </c>
+      <c r="E102" s="10">
+        <v>0.32</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="8">
-        <v>-2.51</v>
+        <v>-4.89</v>
       </c>
       <c r="D103" s="8">
-        <v>-3.22</v>
+        <v>-5.42</v>
       </c>
       <c r="E103" s="9">
-        <v>-0.71</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C104" s="8">
-        <v>-2.33</v>
+        <v>28491.05</v>
       </c>
       <c r="D104" s="8">
-        <v>-1.99</v>
-      </c>
-      <c r="E104" s="10">
-        <v>0.34</v>
+        <v>27981.95</v>
+      </c>
+      <c r="E104" s="9">
+        <v>-509.1</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C105" s="8">
-        <v>-4.05</v>
+        <v>9704.200000000001</v>
       </c>
       <c r="D105" s="8">
-        <v>-4.89</v>
-      </c>
-      <c r="E105" s="9">
-        <v>-0.84</v>
+        <v>9756.9</v>
+      </c>
+      <c r="E105" s="10">
+        <v>52.7</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="8">
-        <v>28841.5</v>
+        <v>11782.3</v>
       </c>
       <c r="D106" s="8">
-        <v>28491.05</v>
+        <v>11703.6</v>
       </c>
       <c r="E106" s="9">
-        <v>-350.45</v>
+        <v>-78.7</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="8">
-        <v>9690.65</v>
+        <v>37806.1</v>
       </c>
       <c r="D107" s="8">
-        <v>9704.200000000001</v>
+        <v>38028.4</v>
       </c>
       <c r="E107" s="10">
-        <v>13.55</v>
+        <v>222.3</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="8">
-        <v>11802.7</v>
+        <v>46457.15</v>
       </c>
       <c r="D108" s="8">
-        <v>11782.3</v>
+        <v>46240.55</v>
       </c>
       <c r="E108" s="9">
-        <v>-20.4</v>
+        <v>-216.6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="8">
-        <v>37949.25</v>
+        <v>26003.9</v>
       </c>
       <c r="D109" s="8">
-        <v>37806.1</v>
+        <v>25813.05</v>
       </c>
       <c r="E109" s="9">
-        <v>-143.15</v>
+        <v>-190.85</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="8">
-        <v>46025.55</v>
+        <v>31496.7</v>
       </c>
       <c r="D110" s="8">
-        <v>46457.15</v>
-      </c>
-      <c r="E110" s="10">
-        <v>431.6</v>
+        <v>31102.9</v>
+      </c>
+      <c r="E110" s="9">
+        <v>-393.8</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="8">
-        <v>26293.65</v>
+        <v>16402.5</v>
       </c>
       <c r="D111" s="8">
-        <v>26003.9</v>
+        <v>16269.35</v>
       </c>
       <c r="E111" s="9">
-        <v>-289.75</v>
+        <v>-133.15</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="8">
-        <v>31191.45</v>
+        <v>9209.25</v>
       </c>
       <c r="D112" s="8">
-        <v>31496.7</v>
+        <v>9212.049999999999</v>
       </c>
       <c r="E112" s="10">
-        <v>305.25</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="8">
-        <v>16582.95</v>
+        <v>1561.45</v>
       </c>
       <c r="D113" s="8">
-        <v>16402.5</v>
+        <v>1534.1</v>
       </c>
       <c r="E113" s="9">
-        <v>-180.45</v>
+        <v>-27.35</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="8">
-        <v>9179.4</v>
+        <v>13189.85</v>
       </c>
       <c r="D114" s="8">
-        <v>9209.25</v>
-      </c>
-      <c r="E114" s="10">
-        <v>29.85</v>
+        <v>13157.35</v>
+      </c>
+      <c r="E114" s="9">
+        <v>-32.5</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="8">
-        <v>1557.35</v>
+        <v>9659.5</v>
       </c>
       <c r="D115" s="8">
-        <v>1561.45</v>
+        <v>9695.950000000001</v>
       </c>
       <c r="E115" s="10">
-        <v>4.1</v>
+        <v>36.45</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="8">
-        <v>13193.9</v>
+        <v>8505.75</v>
       </c>
       <c r="D116" s="8">
-        <v>13189.85</v>
-      </c>
-      <c r="E116" s="9">
-        <v>-4.05</v>
+        <v>8511.700000000001</v>
+      </c>
+      <c r="E116" s="10">
+        <v>5.95</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="8">
-        <v>9704.4</v>
+        <v>26792.65</v>
       </c>
       <c r="D117" s="8">
-        <v>9659.5</v>
+        <v>26780.7</v>
       </c>
       <c r="E117" s="9">
-        <v>-44.9</v>
+        <v>-11.95</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="8">
-        <v>8609.549999999999</v>
+        <v>891.3</v>
       </c>
       <c r="D118" s="8">
-        <v>8505.75</v>
-      </c>
-      <c r="E118" s="9">
-        <v>-103.8</v>
+        <v>893.15</v>
+      </c>
+      <c r="E118" s="10">
+        <v>1.85</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="8">
-        <v>27186.45</v>
+        <v>30756.6</v>
       </c>
       <c r="D119" s="8">
-        <v>26792.65</v>
+        <v>30525.25</v>
       </c>
       <c r="E119" s="9">
-        <v>-393.8</v>
+        <v>-231.35</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="8">
-        <v>904.15</v>
+        <v>16669.85</v>
       </c>
       <c r="D120" s="8">
-        <v>891.3</v>
+        <v>16629.1</v>
       </c>
       <c r="E120" s="9">
-        <v>-12.85</v>
+        <v>-40.75</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="8">
-        <v>30836.2</v>
+        <v>9647.65</v>
       </c>
       <c r="D121" s="8">
-        <v>30756.6</v>
+        <v>9621.35</v>
       </c>
       <c r="E121" s="9">
-        <v>-79.59999999999999</v>
+        <v>-26.3</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="8">
-        <v>16941.5</v>
+        <v>11142.3</v>
       </c>
       <c r="D122" s="8">
-        <v>16669.85</v>
-      </c>
-      <c r="E122" s="9">
-        <v>-271.65</v>
+        <v>11178.85</v>
+      </c>
+      <c r="E122" s="10">
+        <v>36.55</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="8">
-        <v>9718.4</v>
+        <v>27762.1</v>
       </c>
       <c r="D123" s="8">
-        <v>9647.65</v>
+        <v>27606.8</v>
       </c>
       <c r="E123" s="9">
-        <v>-70.75</v>
+        <v>-155.3</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" s="8">
+        <v>50</v>
+      </c>
+      <c r="D124" s="8">
         <v>56</v>
       </c>
-      <c r="B124" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C124" s="8">
-        <v>11103.8</v>
-      </c>
-      <c r="D124" s="8">
-        <v>11142.3</v>
-      </c>
       <c r="E124" s="10">
-        <v>38.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C125" s="8">
-        <v>28005.75</v>
+        <v>32</v>
       </c>
       <c r="D125" s="8">
-        <v>27762.1</v>
-      </c>
-      <c r="E125" s="9">
-        <v>-243.65</v>
+        <v>50</v>
+      </c>
+      <c r="E125" s="10">
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>14</v>
@@ -5527,44 +5485,44 @@
         <v>56</v>
       </c>
       <c r="D126" s="8">
-        <v>62</v>
-      </c>
-      <c r="E126" s="10">
-        <v>6</v>
+        <v>32</v>
+      </c>
+      <c r="E126" s="9">
+        <v>-24</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="8">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D127" s="8">
-        <v>44</v>
-      </c>
-      <c r="E127" s="9">
-        <v>-18</v>
+        <v>26</v>
+      </c>
+      <c r="E127" s="10">
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="8">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D128" s="8">
-        <v>56</v>
-      </c>
-      <c r="E128" s="10">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="E128" s="9">
+        <v>-7</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5575,13 +5533,13 @@
         <v>25</v>
       </c>
       <c r="C129" s="8">
-        <v>53.18</v>
+        <v>44.91</v>
       </c>
       <c r="D129" s="8">
-        <v>44.91</v>
+        <v>36.13</v>
       </c>
       <c r="E129" s="9">
-        <v>-8.27</v>
+        <v>-8.779999999999999</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -5592,13 +5550,13 @@
         <v>25</v>
       </c>
       <c r="C130" s="8">
-        <v>35.26</v>
+        <v>36.85</v>
       </c>
       <c r="D130" s="8">
-        <v>36.85</v>
+        <v>42.76</v>
       </c>
       <c r="E130" s="10">
-        <v>1.59</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5609,13 +5567,13 @@
         <v>25</v>
       </c>
       <c r="C131" s="8">
-        <v>39.38</v>
+        <v>38.35</v>
       </c>
       <c r="D131" s="8">
-        <v>38.35</v>
+        <v>34.59</v>
       </c>
       <c r="E131" s="9">
-        <v>-1.03</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5626,13 +5584,13 @@
         <v>25</v>
       </c>
       <c r="C132" s="8">
-        <v>31.05</v>
+        <v>28.46</v>
       </c>
       <c r="D132" s="8">
-        <v>28.46</v>
-      </c>
-      <c r="E132" s="9">
-        <v>-2.59</v>
+        <v>37.23</v>
+      </c>
+      <c r="E132" s="10">
+        <v>8.77</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -5643,13 +5601,13 @@
         <v>25</v>
       </c>
       <c r="C133" s="8">
-        <v>25.16</v>
+        <v>32.26</v>
       </c>
       <c r="D133" s="8">
-        <v>32.26</v>
-      </c>
-      <c r="E133" s="10">
-        <v>7.1</v>
+        <v>30.69</v>
+      </c>
+      <c r="E133" s="9">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -5660,13 +5618,13 @@
         <v>25</v>
       </c>
       <c r="C134" s="8">
-        <v>46.42</v>
+        <v>38.12</v>
       </c>
       <c r="D134" s="8">
-        <v>38.12</v>
+        <v>33.84</v>
       </c>
       <c r="E134" s="9">
-        <v>-8.300000000000001</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -5677,13 +5635,13 @@
         <v>25</v>
       </c>
       <c r="C135" s="8">
-        <v>57.41</v>
+        <v>60.17</v>
       </c>
       <c r="D135" s="8">
-        <v>60.17</v>
-      </c>
-      <c r="E135" s="10">
-        <v>2.76</v>
+        <v>55.2</v>
+      </c>
+      <c r="E135" s="9">
+        <v>-4.97</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -5694,13 +5652,13 @@
         <v>25</v>
       </c>
       <c r="C136" s="8">
-        <v>62.87</v>
+        <v>47.73</v>
       </c>
       <c r="D136" s="8">
-        <v>47.73</v>
+        <v>40.07</v>
       </c>
       <c r="E136" s="9">
-        <v>-15.14</v>
+        <v>-7.66</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -5711,13 +5669,13 @@
         <v>25</v>
       </c>
       <c r="C137" s="8">
-        <v>33.96</v>
+        <v>37.48</v>
       </c>
       <c r="D137" s="8">
-        <v>37.48</v>
+        <v>37.82</v>
       </c>
       <c r="E137" s="10">
-        <v>3.52</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -5728,13 +5686,13 @@
         <v>25</v>
       </c>
       <c r="C138" s="8">
-        <v>45.23</v>
+        <v>46.37</v>
       </c>
       <c r="D138" s="8">
-        <v>46.37</v>
-      </c>
-      <c r="E138" s="10">
-        <v>1.14</v>
+        <v>40.33</v>
+      </c>
+      <c r="E138" s="9">
+        <v>-6.04</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -5745,13 +5703,13 @@
         <v>25</v>
       </c>
       <c r="C139" s="8">
-        <v>53.42</v>
+        <v>53.28</v>
       </c>
       <c r="D139" s="8">
-        <v>53.28</v>
+        <v>52.05</v>
       </c>
       <c r="E139" s="9">
-        <v>-0.14</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -5762,13 +5720,13 @@
         <v>25</v>
       </c>
       <c r="C140" s="8">
-        <v>34.32</v>
+        <v>30.83</v>
       </c>
       <c r="D140" s="8">
-        <v>30.83</v>
-      </c>
-      <c r="E140" s="9">
-        <v>-3.49</v>
+        <v>36.48</v>
+      </c>
+      <c r="E140" s="10">
+        <v>5.65</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -5779,13 +5737,13 @@
         <v>25</v>
       </c>
       <c r="C141" s="8">
-        <v>52.01</v>
+        <v>45.02</v>
       </c>
       <c r="D141" s="8">
-        <v>45.02</v>
-      </c>
-      <c r="E141" s="9">
-        <v>-6.99</v>
+        <v>45.47</v>
+      </c>
+      <c r="E141" s="10">
+        <v>0.45</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -5796,13 +5754,13 @@
         <v>25</v>
       </c>
       <c r="C142" s="8">
-        <v>72.98</v>
+        <v>58.85</v>
       </c>
       <c r="D142" s="8">
-        <v>58.85</v>
+        <v>58.48</v>
       </c>
       <c r="E142" s="9">
-        <v>-14.13</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -5813,13 +5771,13 @@
         <v>25</v>
       </c>
       <c r="C143" s="8">
-        <v>51.82</v>
+        <v>44.8</v>
       </c>
       <c r="D143" s="8">
-        <v>44.8</v>
-      </c>
-      <c r="E143" s="9">
-        <v>-7.02</v>
+        <v>45.93</v>
+      </c>
+      <c r="E143" s="10">
+        <v>1.13</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -5830,13 +5788,13 @@
         <v>25</v>
       </c>
       <c r="C144" s="8">
-        <v>43.96</v>
+        <v>41.74</v>
       </c>
       <c r="D144" s="8">
-        <v>41.74</v>
+        <v>36.03</v>
       </c>
       <c r="E144" s="9">
-        <v>-2.22</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -5847,13 +5805,13 @@
         <v>25</v>
       </c>
       <c r="C145" s="8">
-        <v>69.66</v>
+        <v>54.42</v>
       </c>
       <c r="D145" s="8">
-        <v>54.42</v>
+        <v>52.56</v>
       </c>
       <c r="E145" s="9">
-        <v>-15.24</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -5864,13 +5822,13 @@
         <v>25</v>
       </c>
       <c r="C146" s="8">
-        <v>53.93</v>
+        <v>49.46</v>
       </c>
       <c r="D146" s="8">
-        <v>49.46</v>
+        <v>47.87</v>
       </c>
       <c r="E146" s="9">
-        <v>-4.47</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -5881,13 +5839,13 @@
         <v>25</v>
       </c>
       <c r="C147" s="8">
-        <v>43.05</v>
+        <v>46.92</v>
       </c>
       <c r="D147" s="8">
-        <v>46.92</v>
+        <v>50.37</v>
       </c>
       <c r="E147" s="10">
-        <v>3.87</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -5898,19 +5856,19 @@
         <v>25</v>
       </c>
       <c r="C148" s="8">
-        <v>60.16</v>
+        <v>52.61</v>
       </c>
       <c r="D148" s="8">
-        <v>52.61</v>
+        <v>48.44</v>
       </c>
       <c r="E148" s="9">
-        <v>-7.55</v>
+        <v>-4.17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5934,28 +5892,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5969,22 +5927,22 @@
         <v>20</v>
       </c>
       <c r="D2" s="13">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="E2" s="13">
         <v>40</v>
       </c>
       <c r="F2" s="13">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="G2" s="13">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
       </c>
       <c r="I2" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -6098,10 +6056,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>49</v>
       </c>
       <c r="G1" s="15" t="s">
         <v>48</v>
@@ -6113,44 +6071,44 @@
         <v>46</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.3712</v>
+        <v>0.3494</v>
       </c>
       <c r="B2" s="16">
-        <v>0.3676</v>
+        <v>0.3477</v>
       </c>
       <c r="C2" s="16">
-        <v>0.2929</v>
+        <v>0.2942</v>
       </c>
       <c r="D2" s="16">
-        <v>0.2319</v>
+        <v>0.228</v>
       </c>
       <c r="E2" s="16">
-        <v>0.2312</v>
+        <v>0.2151</v>
       </c>
       <c r="F2" s="16">
-        <v>0.2154</v>
+        <v>0.1843</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1864</v>
+        <v>0.1841</v>
       </c>
       <c r="H2" s="16">
-        <v>0.169</v>
+        <v>0.1666</v>
       </c>
       <c r="I2" s="16">
-        <v>0.1427</v>
+        <v>0.1405</v>
       </c>
       <c r="J2" s="16">
-        <v>0.1335</v>
+        <v>0.1319</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="15" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>39</v>
@@ -6182,34 +6140,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.1318</v>
+        <v>0.1312</v>
       </c>
       <c r="B4" s="16">
-        <v>0.1219</v>
+        <v>0.1208</v>
       </c>
       <c r="C4" s="16">
-        <v>0.1113</v>
+        <v>0.1082</v>
       </c>
       <c r="D4" s="16">
-        <v>0.07969999999999999</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="E4" s="16">
-        <v>0.0759</v>
+        <v>0.0726</v>
       </c>
       <c r="F4" s="16">
-        <v>0.05429999999999999</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="G4" s="16">
-        <v>0.0504</v>
+        <v>0.0469</v>
       </c>
       <c r="H4" s="16">
-        <v>0.0322</v>
+        <v>0.0279</v>
       </c>
       <c r="I4" s="16">
-        <v>-0.0062</v>
+        <v>-0.0103</v>
       </c>
       <c r="J4" s="16">
-        <v>-0.0158</v>
+        <v>-0.0215</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="125">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,64 +289,73 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.5 → 37.2</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.9 → 57.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>37.2</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>46.9 → 50.4</t>
-  </si>
-  <si>
-    <t>46.9</t>
+    <t>45.9</t>
+  </si>
+  <si>
+    <t>57.6</t>
+  </si>
+  <si>
+    <t>47.9 → 51.1</t>
+  </si>
+  <si>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>48.4 → 52.1</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>52.1</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.8% → -2.3%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
+  </si>
+  <si>
+    <t>-2.3%</t>
+  </si>
+  <si>
+    <t>52.6 → 49.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.6</t>
+  </si>
+  <si>
+    <t>49.1</t>
+  </si>
+  <si>
+    <t>50.4 → 49.0</t>
   </si>
   <si>
     <t>50.4</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.6% → -2.4%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.6%</t>
-  </si>
-  <si>
-    <t>-2.4%</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>52.6 → 48.4</t>
-  </si>
-  <si>
-    <t>52.6</t>
-  </si>
-  <si>
-    <t>48.4</t>
+    <t>49.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1091,10 +1100,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>27981.95</v>
+        <v>27837.4</v>
       </c>
       <c r="E2">
-        <v>-1.79</v>
+        <v>-0.52</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1103,43 +1112,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-5.62</v>
+        <v>-6.11</v>
       </c>
       <c r="I2">
-        <v>17.72</v>
+        <v>17.11</v>
       </c>
       <c r="J2">
-        <v>-3.51</v>
+        <v>-3.62</v>
       </c>
       <c r="K2">
-        <v>-3.65</v>
+        <v>-5.35</v>
       </c>
       <c r="L2">
-        <v>7.03</v>
+        <v>6.39</v>
       </c>
       <c r="M2">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="N2">
-        <v>22.8</v>
+        <v>22.42</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Q2">
-        <v>28609.96</v>
+        <v>28400.74</v>
       </c>
       <c r="R2">
-        <v>29120.14</v>
+        <v>29056.34</v>
       </c>
       <c r="S2">
-        <v>27999.88</v>
+        <v>28028.94</v>
       </c>
       <c r="T2">
-        <v>27131.28</v>
+        <v>27133.05</v>
       </c>
       <c r="U2">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1154,16 +1163,16 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>36.13</v>
+        <v>34.09</v>
       </c>
       <c r="AA2">
-        <v>119.5</v>
+        <v>34.5</v>
       </c>
       <c r="AB2">
-        <v>324.76</v>
+        <v>266.71</v>
       </c>
       <c r="AC2">
-        <v>-205.26</v>
+        <v>-232.21</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1172,13 +1181,13 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>410.03</v>
+        <v>402.16</v>
       </c>
       <c r="AH2">
-        <v>29887.79</v>
+        <v>30014.74</v>
       </c>
       <c r="AI2">
-        <v>28352.48</v>
+        <v>28097.93</v>
       </c>
       <c r="AJ2">
         <v>29113.69</v>
@@ -1187,7 +1196,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>39.35</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1201,10 +1210,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9756.9</v>
+        <v>9750.6</v>
       </c>
       <c r="E3">
-        <v>0.54</v>
+        <v>-0.06</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1213,43 +1222,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-7.11</v>
+        <v>-7.17</v>
       </c>
       <c r="I3">
-        <v>13.83</v>
+        <v>13.75</v>
       </c>
       <c r="J3">
-        <v>-1.21</v>
+        <v>-0.65</v>
       </c>
       <c r="K3">
-        <v>-1.73</v>
+        <v>-2.53</v>
       </c>
       <c r="L3">
-        <v>-4.17</v>
+        <v>-3.49</v>
       </c>
       <c r="M3">
-        <v>10.9</v>
+        <v>12.37</v>
       </c>
       <c r="N3">
-        <v>12.08</v>
+        <v>11.77</v>
       </c>
       <c r="O3">
         <v>62</v>
       </c>
       <c r="Q3">
-        <v>9755.129999999999</v>
+        <v>9742.299999999999</v>
       </c>
       <c r="R3">
-        <v>9842.709999999999</v>
+        <v>9832.389999999999</v>
       </c>
       <c r="S3">
-        <v>9850.870000000001</v>
+        <v>9846.98</v>
       </c>
       <c r="T3">
-        <v>9741.700000000001</v>
+        <v>9743.629999999999</v>
       </c>
       <c r="U3">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V3" t="s">
         <v>80</v>
@@ -1264,31 +1273,31 @@
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>42.76</v>
+        <v>42.25</v>
       </c>
       <c r="AA3">
-        <v>-37.83</v>
+        <v>-38.4</v>
       </c>
       <c r="AB3">
-        <v>-26.11</v>
+        <v>-28.56</v>
       </c>
       <c r="AC3">
-        <v>-11.72</v>
+        <v>-9.83</v>
       </c>
       <c r="AD3">
-        <v>19.46</v>
+        <v>34.41</v>
       </c>
       <c r="AE3">
-        <v>21.85</v>
+        <v>24.43</v>
       </c>
       <c r="AF3">
-        <v>92.08</v>
+        <v>93.42</v>
       </c>
       <c r="AH3">
-        <v>10018.83</v>
+        <v>10004.45</v>
       </c>
       <c r="AI3">
-        <v>9666.58</v>
+        <v>9660.32</v>
       </c>
       <c r="AJ3">
         <v>9955.58</v>
@@ -1297,7 +1306,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>36.97</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1311,10 +1320,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11703.6</v>
+        <v>11644.8</v>
       </c>
       <c r="E4">
-        <v>-0.67</v>
+        <v>-0.5</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1323,43 +1332,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-7.4</v>
+        <v>-7.87</v>
       </c>
       <c r="I4">
-        <v>13.25</v>
+        <v>12.68</v>
       </c>
       <c r="J4">
-        <v>-2.21</v>
+        <v>-2.32</v>
       </c>
       <c r="K4">
-        <v>-4.14</v>
+        <v>-4.73</v>
       </c>
       <c r="L4">
-        <v>4.63</v>
+        <v>4.03</v>
       </c>
       <c r="M4">
-        <v>-4.17</v>
+        <v>-4.29</v>
       </c>
       <c r="N4">
-        <v>10.82</v>
+        <v>10.65</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="Q4">
-        <v>11822.8</v>
+        <v>11767.52</v>
       </c>
       <c r="R4">
-        <v>12025.07</v>
+        <v>11998.73</v>
       </c>
       <c r="S4">
-        <v>11869.11</v>
+        <v>11871.83</v>
       </c>
       <c r="T4">
-        <v>11679.68</v>
+        <v>11675.95</v>
       </c>
       <c r="U4">
-        <v>0.2</v>
+        <v>-0.27</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1371,19 +1380,19 @@
         <v>79</v>
       </c>
       <c r="Y4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z4">
-        <v>34.59</v>
+        <v>32.05</v>
       </c>
       <c r="AA4">
-        <v>-25.27</v>
+        <v>-44.55</v>
       </c>
       <c r="AB4">
-        <v>30.31</v>
+        <v>15.34</v>
       </c>
       <c r="AC4">
-        <v>-55.58</v>
+        <v>-59.89</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1392,13 +1401,13 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>111.24</v>
+        <v>110.39</v>
       </c>
       <c r="AH4">
-        <v>12312.64</v>
+        <v>12323.84</v>
       </c>
       <c r="AI4">
-        <v>11737.5</v>
+        <v>11673.62</v>
       </c>
       <c r="AJ4">
         <v>11977.93</v>
@@ -1407,7 +1416,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>28.96</v>
+        <v>32.47</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1421,10 +1430,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38028.4</v>
+        <v>38140.8</v>
       </c>
       <c r="E5">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1433,43 +1442,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-8.44</v>
+        <v>-8.17</v>
       </c>
       <c r="I5">
-        <v>14.9</v>
+        <v>15.23</v>
       </c>
       <c r="J5">
-        <v>-0.19</v>
+        <v>0.1</v>
       </c>
       <c r="K5">
-        <v>-2.03</v>
+        <v>-1.78</v>
       </c>
       <c r="L5">
-        <v>-5.98</v>
+        <v>-5.47</v>
       </c>
       <c r="M5">
-        <v>10.25</v>
+        <v>12.32</v>
       </c>
       <c r="N5">
-        <v>13.19</v>
+        <v>12.75</v>
       </c>
       <c r="O5">
         <v>56</v>
       </c>
       <c r="Q5">
-        <v>37978.27</v>
+        <v>37985.64</v>
       </c>
       <c r="R5">
-        <v>38360</v>
+        <v>38333.29</v>
       </c>
       <c r="S5">
-        <v>38891.41</v>
+        <v>38856.06</v>
       </c>
       <c r="T5">
-        <v>37475.26</v>
+        <v>37484.52</v>
       </c>
       <c r="U5">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="s">
         <v>80</v>
@@ -1484,31 +1493,31 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>37.23</v>
+        <v>41.16</v>
       </c>
       <c r="AA5">
-        <v>-286.68</v>
+        <v>-266.5</v>
       </c>
       <c r="AB5">
-        <v>-270.37</v>
+        <v>-269.6</v>
       </c>
       <c r="AC5">
-        <v>-16.31</v>
+        <v>3.09</v>
       </c>
       <c r="AD5">
-        <v>23.1</v>
+        <v>56.44</v>
       </c>
       <c r="AE5">
-        <v>11.95</v>
+        <v>27.3</v>
       </c>
       <c r="AF5">
-        <v>351.99</v>
+        <v>347.13</v>
       </c>
       <c r="AH5">
-        <v>39003.62</v>
+        <v>38966.11</v>
       </c>
       <c r="AI5">
-        <v>37716.39</v>
+        <v>37700.47</v>
       </c>
       <c r="AJ5">
         <v>38783.5</v>
@@ -1517,7 +1526,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>25.9</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1531,10 +1540,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>46240.55</v>
+        <v>45955.65</v>
       </c>
       <c r="E6">
-        <v>-0.47</v>
+        <v>-0.62</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1543,43 +1552,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-19.02</v>
+        <v>-19.52</v>
       </c>
       <c r="I6">
-        <v>1.54</v>
+        <v>0.92</v>
       </c>
       <c r="J6">
-        <v>-2.14</v>
+        <v>-2.29</v>
       </c>
       <c r="K6">
-        <v>-6.64</v>
+        <v>-6.94</v>
       </c>
       <c r="L6">
-        <v>-4.1</v>
+        <v>-4.86</v>
       </c>
       <c r="M6">
-        <v>-16.96</v>
+        <v>-18.21</v>
       </c>
       <c r="N6">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>46513.74</v>
+        <v>46298.78</v>
       </c>
       <c r="R6">
-        <v>47846.74</v>
+        <v>47676.03</v>
       </c>
       <c r="S6">
-        <v>48636.33</v>
+        <v>48573.74</v>
       </c>
       <c r="T6">
-        <v>50654.65</v>
+        <v>50606.78</v>
       </c>
       <c r="U6">
-        <v>-8.710000000000001</v>
+        <v>-9.19</v>
       </c>
       <c r="V6" t="s">
         <v>80</v>
@@ -1594,40 +1603,40 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>30.69</v>
+        <v>28.7</v>
       </c>
       <c r="AA6">
-        <v>-683.4299999999999</v>
+        <v>-725.47</v>
       </c>
       <c r="AB6">
-        <v>-511.51</v>
+        <v>-554.3</v>
       </c>
       <c r="AC6">
-        <v>-171.92</v>
+        <v>-171.17</v>
       </c>
       <c r="AD6">
-        <v>21.05</v>
+        <v>29.64</v>
       </c>
       <c r="AE6">
-        <v>10.73</v>
+        <v>20.61</v>
       </c>
       <c r="AF6">
-        <v>575.09</v>
+        <v>564.66</v>
       </c>
       <c r="AH6">
-        <v>49908.51</v>
+        <v>49771.9</v>
       </c>
       <c r="AI6">
-        <v>45784.98</v>
+        <v>45580.16</v>
       </c>
       <c r="AJ6">
-        <v>47812.65</v>
+        <v>47766.9</v>
       </c>
       <c r="AK6" t="s">
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>58.31</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1641,10 +1650,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25813.05</v>
+        <v>25923.05</v>
       </c>
       <c r="E7">
-        <v>-0.73</v>
+        <v>0.43</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1653,43 +1662,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-9.31</v>
+        <v>-8.92</v>
       </c>
       <c r="I7">
-        <v>9.74</v>
+        <v>10.21</v>
       </c>
       <c r="J7">
-        <v>-2.17</v>
+        <v>-1.36</v>
       </c>
       <c r="K7">
-        <v>-3.84</v>
+        <v>-3.43</v>
       </c>
       <c r="L7">
-        <v>3.12</v>
+        <v>3.46</v>
       </c>
       <c r="M7">
-        <v>-1.88</v>
+        <v>-0.11</v>
       </c>
       <c r="N7">
-        <v>7.26</v>
+        <v>7.41</v>
       </c>
       <c r="O7">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q7">
-        <v>26135.55</v>
+        <v>26064.03</v>
       </c>
       <c r="R7">
-        <v>26274.57</v>
+        <v>26227.55</v>
       </c>
       <c r="S7">
-        <v>26571.47</v>
+        <v>26555.21</v>
       </c>
       <c r="T7">
-        <v>26649.82</v>
+        <v>26642.75</v>
       </c>
       <c r="U7">
-        <v>-3.14</v>
+        <v>-2.7</v>
       </c>
       <c r="V7" t="s">
         <v>80</v>
@@ -1704,31 +1713,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>33.84</v>
+        <v>38.15</v>
       </c>
       <c r="AA7">
-        <v>-133.61</v>
+        <v>-144.49</v>
       </c>
       <c r="AB7">
-        <v>-105.31</v>
+        <v>-113.15</v>
       </c>
       <c r="AC7">
-        <v>-28.3</v>
+        <v>-31.34</v>
       </c>
       <c r="AD7">
-        <v>32.13</v>
+        <v>15.01</v>
       </c>
       <c r="AE7">
-        <v>55.96</v>
+        <v>35.04</v>
       </c>
       <c r="AF7">
-        <v>270.68</v>
+        <v>271.85</v>
       </c>
       <c r="AH7">
-        <v>26718.12</v>
+        <v>26602.28</v>
       </c>
       <c r="AI7">
-        <v>25831.03</v>
+        <v>25852.82</v>
       </c>
       <c r="AJ7">
         <v>26568.68</v>
@@ -1737,7 +1746,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>28.82</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1751,10 +1760,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31102.9</v>
+        <v>30838.85</v>
       </c>
       <c r="E8">
-        <v>-1.25</v>
+        <v>-0.85</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1763,43 +1772,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-21.23</v>
+        <v>-21.9</v>
       </c>
       <c r="I8">
-        <v>20.7</v>
+        <v>19.67</v>
       </c>
       <c r="J8">
-        <v>2.59</v>
+        <v>2.04</v>
       </c>
       <c r="K8">
-        <v>-1.12</v>
+        <v>-1.8</v>
       </c>
       <c r="L8">
-        <v>6.15</v>
+        <v>6.3</v>
       </c>
       <c r="M8">
-        <v>-14.27</v>
+        <v>-14.49</v>
       </c>
       <c r="N8">
-        <v>-2.15</v>
+        <v>-2.44</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>31058.78</v>
+        <v>31182.32</v>
       </c>
       <c r="R8">
-        <v>31027.06</v>
+        <v>31008.82</v>
       </c>
       <c r="S8">
-        <v>29657.66</v>
+        <v>29723.1</v>
       </c>
       <c r="T8">
-        <v>32248.19</v>
+        <v>32218.11</v>
       </c>
       <c r="U8">
-        <v>-3.55</v>
+        <v>-4.28</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1814,34 +1823,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>55.2</v>
+        <v>52.09</v>
       </c>
       <c r="AA8">
-        <v>280.13</v>
+        <v>250.68</v>
       </c>
       <c r="AB8">
-        <v>323.34</v>
+        <v>308.81</v>
       </c>
       <c r="AC8">
-        <v>-43.22</v>
+        <v>-58.13</v>
       </c>
       <c r="AD8">
-        <v>66.81999999999999</v>
+        <v>56.37</v>
       </c>
       <c r="AE8">
-        <v>57.37</v>
+        <v>63.15</v>
       </c>
       <c r="AF8">
-        <v>639.6</v>
+        <v>634.2</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32042.72</v>
+        <v>32024.23</v>
       </c>
       <c r="AI8">
-        <v>30011.4</v>
+        <v>29993.41</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1850,7 +1859,7 @@
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>21.04</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1864,10 +1873,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16269.35</v>
+        <v>16271.8</v>
       </c>
       <c r="E9">
-        <v>-0.8100000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1876,28 +1885,28 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-2.36</v>
+        <v>-2.34</v>
       </c>
       <c r="I9">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="J9">
-        <v>-1.8</v>
+        <v>-1.73</v>
       </c>
       <c r="K9">
-        <v>-1.37</v>
+        <v>-1.93</v>
       </c>
       <c r="N9">
-        <v>18.43</v>
+        <v>18.27</v>
       </c>
       <c r="Q9">
-        <v>16474.41</v>
+        <v>16417.01</v>
       </c>
       <c r="R9">
-        <v>16548.93</v>
+        <v>16533.04</v>
       </c>
       <c r="S9">
-        <v>16227.59</v>
+        <v>16235.32</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1909,31 +1918,31 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>40.07</v>
+        <v>40.26</v>
       </c>
       <c r="AA9">
-        <v>54.5</v>
+        <v>33.6</v>
       </c>
       <c r="AB9">
-        <v>101.58</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="AC9">
-        <v>-47.09</v>
+        <v>-54.38</v>
       </c>
       <c r="AD9">
-        <v>13.29</v>
+        <v>0.25</v>
       </c>
       <c r="AE9">
-        <v>21.99</v>
+        <v>12.01</v>
       </c>
       <c r="AF9">
-        <v>143.03</v>
+        <v>139.42</v>
       </c>
       <c r="AH9">
-        <v>16729.26</v>
+        <v>16750.46</v>
       </c>
       <c r="AI9">
-        <v>16368.61</v>
+        <v>16315.62</v>
       </c>
       <c r="AJ9">
         <v>16247.63</v>
@@ -1942,7 +1951,7 @@
         <v>82</v>
       </c>
       <c r="AL9">
-        <v>26.09</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1956,10 +1965,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9212.049999999999</v>
+        <v>9204.200000000001</v>
       </c>
       <c r="E10">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1968,43 +1977,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-5.67</v>
+        <v>-5.75</v>
       </c>
       <c r="I10">
-        <v>7.61</v>
+        <v>7.51</v>
       </c>
       <c r="J10">
-        <v>-0.83</v>
+        <v>-0.36</v>
       </c>
       <c r="K10">
-        <v>-2.2</v>
+        <v>-2.63</v>
       </c>
       <c r="L10">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="M10">
-        <v>1.12</v>
+        <v>2.62</v>
       </c>
       <c r="N10">
-        <v>14.05</v>
+        <v>13.76</v>
       </c>
       <c r="O10">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Q10">
-        <v>9216.24</v>
+        <v>9209.52</v>
       </c>
       <c r="R10">
-        <v>9347.049999999999</v>
+        <v>9334.6</v>
       </c>
       <c r="S10">
-        <v>9378.48</v>
+        <v>9373.299999999999</v>
       </c>
       <c r="T10">
-        <v>9349.08</v>
+        <v>9347.309999999999</v>
       </c>
       <c r="U10">
-        <v>-1.47</v>
+        <v>-1.53</v>
       </c>
       <c r="V10" t="s">
         <v>80</v>
@@ -2019,31 +2028,31 @@
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>37.82</v>
+        <v>37.21</v>
       </c>
       <c r="AA10">
-        <v>-48.51</v>
+        <v>-50.96</v>
       </c>
       <c r="AB10">
-        <v>-28.74</v>
+        <v>-33.19</v>
       </c>
       <c r="AC10">
-        <v>-19.77</v>
+        <v>-17.77</v>
       </c>
       <c r="AD10">
-        <v>14.16</v>
+        <v>20.41</v>
       </c>
       <c r="AE10">
-        <v>7.88</v>
+        <v>14.23</v>
       </c>
       <c r="AF10">
-        <v>81.87</v>
+        <v>79.37</v>
       </c>
       <c r="AH10">
-        <v>9533.24</v>
+        <v>9524.16</v>
       </c>
       <c r="AI10">
-        <v>9160.860000000001</v>
+        <v>9145.040000000001</v>
       </c>
       <c r="AJ10">
         <v>9408.6</v>
@@ -2052,7 +2061,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>44.21</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2066,10 +2075,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1534.1</v>
+        <v>1560.75</v>
       </c>
       <c r="E11">
-        <v>-1.75</v>
+        <v>1.74</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2078,43 +2087,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-6.03</v>
+        <v>-4.4</v>
       </c>
       <c r="I11">
-        <v>22.4</v>
+        <v>24.53</v>
       </c>
       <c r="J11">
-        <v>-4.77</v>
+        <v>-2.25</v>
       </c>
       <c r="K11">
-        <v>-4.15</v>
+        <v>-0.91</v>
       </c>
       <c r="L11">
-        <v>5.66</v>
+        <v>3.88</v>
       </c>
       <c r="M11">
-        <v>-5.67</v>
+        <v>-3.3</v>
       </c>
       <c r="N11">
-        <v>-1.03</v>
+        <v>-0.98</v>
       </c>
       <c r="O11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q11">
-        <v>1570.5</v>
+        <v>1563.31</v>
       </c>
       <c r="R11">
-        <v>1583.5</v>
+        <v>1583.36</v>
       </c>
       <c r="S11">
-        <v>1546.09</v>
+        <v>1546.92</v>
       </c>
       <c r="T11">
-        <v>1447.4</v>
+        <v>1447.77</v>
       </c>
       <c r="U11">
-        <v>5.99</v>
+        <v>7.8</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2129,31 +2138,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>40.33</v>
+        <v>47.51</v>
       </c>
       <c r="AA11">
-        <v>6.22</v>
+        <v>4.31</v>
       </c>
       <c r="AB11">
-        <v>15.7</v>
+        <v>13.42</v>
       </c>
       <c r="AC11">
-        <v>-9.48</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="AD11">
-        <v>1.87</v>
+        <v>11.35</v>
       </c>
       <c r="AE11">
-        <v>11.71</v>
+        <v>9</v>
       </c>
       <c r="AF11">
-        <v>32.15</v>
+        <v>32.05</v>
       </c>
       <c r="AH11">
-        <v>1634.73</v>
+        <v>1634.83</v>
       </c>
       <c r="AI11">
-        <v>1532.27</v>
+        <v>1531.9</v>
       </c>
       <c r="AJ11">
         <v>1523.72</v>
@@ -2162,7 +2171,7 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>45.26</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2176,10 +2185,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13157.35</v>
+        <v>13176.05</v>
       </c>
       <c r="E12">
-        <v>-0.25</v>
+        <v>0.14</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2188,43 +2197,43 @@
         <v>9154.799999999999</v>
       </c>
       <c r="H12">
-        <v>-4.09</v>
+        <v>-3.95</v>
       </c>
       <c r="I12">
-        <v>43.72</v>
+        <v>43.93</v>
       </c>
       <c r="J12">
-        <v>-2.84</v>
+        <v>-1.86</v>
       </c>
       <c r="K12">
-        <v>0.96</v>
+        <v>-0.61</v>
       </c>
       <c r="L12">
-        <v>-2.07</v>
+        <v>-0.34</v>
       </c>
       <c r="M12">
-        <v>39.43</v>
+        <v>41.98</v>
       </c>
       <c r="N12">
-        <v>18.41</v>
+        <v>18.17</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13298.33</v>
+        <v>13248.5</v>
       </c>
       <c r="R12">
-        <v>13193.43</v>
+        <v>13195.05</v>
       </c>
       <c r="S12">
-        <v>12826.58</v>
+        <v>12837.72</v>
       </c>
       <c r="T12">
-        <v>12106</v>
+        <v>12119.17</v>
       </c>
       <c r="U12">
-        <v>8.68</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2239,31 +2248,31 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>52.05</v>
+        <v>52.73</v>
       </c>
       <c r="AA12">
-        <v>123.71</v>
+        <v>109.88</v>
       </c>
       <c r="AB12">
-        <v>139.9</v>
+        <v>133.89</v>
       </c>
       <c r="AC12">
-        <v>-16.19</v>
+        <v>-24.02</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12">
-        <v>25</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AF12">
-        <v>204.55</v>
+        <v>208.44</v>
       </c>
       <c r="AH12">
-        <v>13535.55</v>
+        <v>13536.48</v>
       </c>
       <c r="AI12">
-        <v>12851.31</v>
+        <v>12853.62</v>
       </c>
       <c r="AJ12">
         <v>12921.88</v>
@@ -2272,7 +2281,7 @@
         <v>82</v>
       </c>
       <c r="AL12">
-        <v>27.94</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2286,10 +2295,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9695.950000000001</v>
+        <v>9706.65</v>
       </c>
       <c r="E13">
-        <v>0.38</v>
+        <v>0.11</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2298,43 +2307,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-9.94</v>
+        <v>-9.84</v>
       </c>
       <c r="I13">
-        <v>5.36</v>
+        <v>5.48</v>
       </c>
       <c r="J13">
-        <v>-0.33</v>
+        <v>0.05</v>
       </c>
       <c r="K13">
-        <v>-2.43</v>
+        <v>-2.46</v>
       </c>
       <c r="L13">
-        <v>-4.21</v>
+        <v>-3.71</v>
       </c>
       <c r="M13">
-        <v>2.42</v>
+        <v>4.28</v>
       </c>
       <c r="N13">
-        <v>21.51</v>
+        <v>21.14</v>
       </c>
       <c r="O13">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q13">
-        <v>9690.129999999999</v>
+        <v>9691.15</v>
       </c>
       <c r="R13">
-        <v>9792.299999999999</v>
+        <v>9780.76</v>
       </c>
       <c r="S13">
-        <v>9885.959999999999</v>
+        <v>9878.309999999999</v>
       </c>
       <c r="T13">
-        <v>10035.34</v>
+        <v>10033.89</v>
       </c>
       <c r="U13">
-        <v>-3.38</v>
+        <v>-3.26</v>
       </c>
       <c r="V13" t="s">
         <v>80</v>
@@ -2349,31 +2358,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>36.48</v>
+        <v>38.08</v>
       </c>
       <c r="AA13">
-        <v>-65.5</v>
+        <v>-63.2</v>
       </c>
       <c r="AB13">
-        <v>-58.1</v>
+        <v>-59.12</v>
       </c>
       <c r="AC13">
-        <v>-7.4</v>
+        <v>-4.08</v>
       </c>
       <c r="AD13">
-        <v>22.19</v>
+        <v>36.72</v>
       </c>
       <c r="AE13">
-        <v>11.46</v>
+        <v>21.67</v>
       </c>
       <c r="AF13">
-        <v>91.62</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="AH13">
-        <v>9959.889999999999</v>
+        <v>9937.73</v>
       </c>
       <c r="AI13">
-        <v>9624.709999999999</v>
+        <v>9623.790000000001</v>
       </c>
       <c r="AJ13">
         <v>9905.1</v>
@@ -2382,7 +2391,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>40.88</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2396,10 +2405,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8511.700000000001</v>
+        <v>8552.6</v>
       </c>
       <c r="E14">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2408,43 +2417,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-13.85</v>
+        <v>-13.43</v>
       </c>
       <c r="I14">
-        <v>25.99</v>
+        <v>26.59</v>
       </c>
       <c r="J14">
-        <v>-1.82</v>
+        <v>-0.41</v>
       </c>
       <c r="K14">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="L14">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="M14">
-        <v>21.94</v>
+        <v>24.86</v>
       </c>
       <c r="N14">
-        <v>29.42</v>
+        <v>29.36</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8563.82</v>
+        <v>8556.780000000001</v>
       </c>
       <c r="R14">
-        <v>8647.42</v>
+        <v>8638.59</v>
       </c>
       <c r="S14">
-        <v>8505.68</v>
+        <v>8504.17</v>
       </c>
       <c r="T14">
-        <v>8598.219999999999</v>
+        <v>8599.190000000001</v>
       </c>
       <c r="U14">
-        <v>-1.01</v>
+        <v>-0.54</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2459,31 +2468,31 @@
         <v>1</v>
       </c>
       <c r="Z14">
-        <v>45.47</v>
+        <v>48.6</v>
       </c>
       <c r="AA14">
-        <v>11.38</v>
+        <v>7.89</v>
       </c>
       <c r="AB14">
-        <v>34.82</v>
+        <v>29.43</v>
       </c>
       <c r="AC14">
-        <v>-23.43</v>
+        <v>-21.54</v>
       </c>
       <c r="AD14">
-        <v>8.1</v>
+        <v>9.44</v>
       </c>
       <c r="AE14">
-        <v>13.4</v>
+        <v>10.42</v>
       </c>
       <c r="AF14">
-        <v>125.78</v>
+        <v>127.29</v>
       </c>
       <c r="AH14">
-        <v>8824.99</v>
+        <v>8816.6</v>
       </c>
       <c r="AI14">
-        <v>8469.85</v>
+        <v>8460.58</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
@@ -2492,7 +2501,7 @@
         <v>82</v>
       </c>
       <c r="AL14">
-        <v>21.07</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2506,10 +2515,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26780.7</v>
+        <v>26658.65</v>
       </c>
       <c r="E15">
-        <v>-0.04</v>
+        <v>-0.46</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2518,43 +2527,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-1.49</v>
+        <v>-1.94</v>
       </c>
       <c r="I15">
-        <v>24.83</v>
+        <v>24.26</v>
       </c>
       <c r="J15">
-        <v>0.58</v>
+        <v>-0.71</v>
       </c>
       <c r="K15">
-        <v>0.6899999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="L15">
-        <v>10.76</v>
+        <v>9.94</v>
       </c>
       <c r="M15">
-        <v>19.76</v>
+        <v>21.23</v>
       </c>
       <c r="N15">
-        <v>13.12</v>
+        <v>12.98</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26920.08</v>
+        <v>26882.06</v>
       </c>
       <c r="R15">
-        <v>26612.92</v>
+        <v>26617.62</v>
       </c>
       <c r="S15">
-        <v>26132.44</v>
+        <v>26165.23</v>
       </c>
       <c r="T15">
-        <v>23766.48</v>
+        <v>23786.8</v>
       </c>
       <c r="U15">
-        <v>12.68</v>
+        <v>12.07</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2569,34 +2578,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>58.48</v>
+        <v>54.7</v>
       </c>
       <c r="AA15">
-        <v>217.53</v>
+        <v>196.84</v>
       </c>
       <c r="AB15">
-        <v>215.79</v>
+        <v>212</v>
       </c>
       <c r="AC15">
-        <v>1.75</v>
+        <v>-15.16</v>
       </c>
       <c r="AD15">
-        <v>50.93</v>
+        <v>19.6</v>
       </c>
       <c r="AE15">
-        <v>73.93000000000001</v>
+        <v>48.77</v>
       </c>
       <c r="AF15">
-        <v>307.44</v>
+        <v>300.22</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27082.93</v>
+        <v>27087.48</v>
       </c>
       <c r="AI15">
-        <v>26142.91</v>
+        <v>26147.75</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
@@ -2605,7 +2614,7 @@
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>34.5</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2619,10 +2628,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>893.15</v>
+        <v>916.15</v>
       </c>
       <c r="E16">
-        <v>0.21</v>
+        <v>2.58</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2631,43 +2640,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-7.79</v>
+        <v>-5.42</v>
       </c>
       <c r="I16">
-        <v>37.17</v>
+        <v>40.7</v>
       </c>
       <c r="J16">
-        <v>-1.87</v>
+        <v>0.72</v>
       </c>
       <c r="K16">
-        <v>0.22</v>
+        <v>1.94</v>
       </c>
       <c r="L16">
-        <v>16.81</v>
+        <v>19.15</v>
       </c>
       <c r="M16">
-        <v>-2.54</v>
+        <v>2.25</v>
       </c>
       <c r="N16">
-        <v>16.66</v>
+        <v>17</v>
       </c>
       <c r="O16">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q16">
-        <v>901.41</v>
+        <v>902.72</v>
       </c>
       <c r="R16">
-        <v>900.58</v>
+        <v>902.04</v>
       </c>
       <c r="S16">
-        <v>898.04</v>
+        <v>899.89</v>
       </c>
       <c r="T16">
-        <v>831.75</v>
+        <v>831.64</v>
       </c>
       <c r="U16">
-        <v>7.38</v>
+        <v>10.16</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2682,31 +2691,31 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>45.93</v>
+        <v>57.61</v>
       </c>
       <c r="AA16">
-        <v>2.19</v>
+        <v>3.11</v>
       </c>
       <c r="AB16">
-        <v>4.48</v>
+        <v>4.21</v>
       </c>
       <c r="AC16">
-        <v>-2.29</v>
+        <v>-1.1</v>
       </c>
       <c r="AD16">
-        <v>10.85</v>
+        <v>30.66</v>
       </c>
       <c r="AE16">
-        <v>27.37</v>
+        <v>22.53</v>
       </c>
       <c r="AF16">
-        <v>17.08</v>
+        <v>17.8</v>
       </c>
       <c r="AH16">
-        <v>920.45</v>
+        <v>921.98</v>
       </c>
       <c r="AI16">
-        <v>880.7</v>
+        <v>882.11</v>
       </c>
       <c r="AJ16">
         <v>869.13</v>
@@ -2715,7 +2724,7 @@
         <v>82</v>
       </c>
       <c r="AL16">
-        <v>29.54</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2729,10 +2738,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30525.25</v>
+        <v>30575.05</v>
       </c>
       <c r="E17">
-        <v>-0.75</v>
+        <v>0.16</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2741,43 +2750,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-10.49</v>
+        <v>-10.34</v>
       </c>
       <c r="I17">
-        <v>7.62</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>-1.21</v>
+        <v>-0.57</v>
       </c>
       <c r="K17">
-        <v>-3.43</v>
+        <v>-3.12</v>
       </c>
       <c r="L17">
-        <v>3.17</v>
+        <v>3.58</v>
       </c>
       <c r="M17">
-        <v>-6.57</v>
+        <v>-5.37</v>
       </c>
       <c r="N17">
-        <v>4.69</v>
+        <v>4.74</v>
       </c>
       <c r="O17">
         <v>19</v>
       </c>
       <c r="Q17">
-        <v>30753.67</v>
+        <v>30718.66</v>
       </c>
       <c r="R17">
-        <v>30971.55</v>
+        <v>30925.07</v>
       </c>
       <c r="S17">
-        <v>31097.16</v>
+        <v>31094.26</v>
       </c>
       <c r="T17">
-        <v>31655.74</v>
+        <v>31641.11</v>
       </c>
       <c r="U17">
-        <v>-3.57</v>
+        <v>-3.37</v>
       </c>
       <c r="V17" t="s">
         <v>80</v>
@@ -2792,31 +2801,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>36.03</v>
+        <v>38</v>
       </c>
       <c r="AA17">
-        <v>-118.74</v>
+        <v>-131.3</v>
       </c>
       <c r="AB17">
-        <v>-76.39</v>
+        <v>-87.37</v>
       </c>
       <c r="AC17">
-        <v>-42.35</v>
+        <v>-43.93</v>
       </c>
       <c r="AD17">
-        <v>38.86</v>
+        <v>23.47</v>
       </c>
       <c r="AE17">
-        <v>51.99</v>
+        <v>41.55</v>
       </c>
       <c r="AF17">
-        <v>258.86</v>
+        <v>255.41</v>
       </c>
       <c r="AH17">
-        <v>31455.24</v>
+        <v>31370.2</v>
       </c>
       <c r="AI17">
-        <v>30487.85</v>
+        <v>30479.94</v>
       </c>
       <c r="AJ17">
         <v>31236.31</v>
@@ -2825,7 +2834,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>33.6</v>
+        <v>31.54</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2839,10 +2848,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16629.1</v>
+        <v>16552.2</v>
       </c>
       <c r="E18">
-        <v>-0.24</v>
+        <v>-0.46</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2851,28 +2860,28 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-1.84</v>
+        <v>-2.3</v>
       </c>
       <c r="I18">
-        <v>7.96</v>
+        <v>7.46</v>
       </c>
       <c r="J18">
-        <v>0.26</v>
+        <v>-0.93</v>
       </c>
       <c r="K18">
-        <v>-0.7</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N18">
-        <v>34.77</v>
+        <v>31.57</v>
       </c>
       <c r="Q18">
-        <v>16749.33</v>
+        <v>16718.23</v>
       </c>
       <c r="R18">
-        <v>16604.31</v>
+        <v>16596.07</v>
       </c>
       <c r="S18">
-        <v>16478.17</v>
+        <v>16490.14</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2884,31 +2893,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>52.56</v>
+        <v>49.15</v>
       </c>
       <c r="AA18">
-        <v>69.65000000000001</v>
+        <v>56.86</v>
       </c>
       <c r="AB18">
-        <v>63.74</v>
+        <v>62.36</v>
       </c>
       <c r="AC18">
-        <v>5.92</v>
+        <v>-5.5</v>
       </c>
       <c r="AD18">
-        <v>55.15</v>
+        <v>26.71</v>
       </c>
       <c r="AE18">
-        <v>77.25</v>
+        <v>53.58</v>
       </c>
       <c r="AF18">
-        <v>181.7</v>
+        <v>178.16</v>
       </c>
       <c r="AH18">
-        <v>16885.25</v>
+        <v>16872.74</v>
       </c>
       <c r="AI18">
-        <v>16323.37</v>
+        <v>16319.41</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2917,7 +2926,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>30.2</v>
+        <v>28.81</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2931,10 +2940,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9621.35</v>
+        <v>9670.9</v>
       </c>
       <c r="E19">
-        <v>-0.27</v>
+        <v>0.52</v>
       </c>
       <c r="F19">
         <v>9968.25</v>
@@ -2943,28 +2952,28 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-3.48</v>
+        <v>-2.98</v>
       </c>
       <c r="I19">
-        <v>6.96</v>
+        <v>7.51</v>
       </c>
       <c r="J19">
-        <v>-1.27</v>
+        <v>-1.34</v>
       </c>
       <c r="K19">
-        <v>2.14</v>
+        <v>2.92</v>
       </c>
       <c r="N19">
-        <v>34.94</v>
+        <v>37.53</v>
       </c>
       <c r="Q19">
-        <v>9708.280000000001</v>
+        <v>9681.99</v>
       </c>
       <c r="R19">
-        <v>9746.57</v>
+        <v>9746.809999999999</v>
       </c>
       <c r="S19">
-        <v>9538.719999999999</v>
+        <v>9542.889999999999</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2976,31 +2985,31 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>47.87</v>
+        <v>51.06</v>
       </c>
       <c r="AA19">
-        <v>55.55</v>
+        <v>47.98</v>
       </c>
       <c r="AB19">
-        <v>86.31</v>
+        <v>78.64</v>
       </c>
       <c r="AC19">
-        <v>-30.75</v>
+        <v>-30.67</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AE19">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="AF19">
-        <v>136.19</v>
+        <v>134.34</v>
       </c>
       <c r="AH19">
-        <v>9928.57</v>
+        <v>9928.379999999999</v>
       </c>
       <c r="AI19">
-        <v>9564.57</v>
+        <v>9565.24</v>
       </c>
       <c r="AJ19">
         <v>9466.209999999999</v>
@@ -3009,7 +3018,7 @@
         <v>82</v>
       </c>
       <c r="AL19">
-        <v>25.32</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3023,10 +3032,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11178.85</v>
+        <v>11164.65</v>
       </c>
       <c r="E20">
-        <v>0.33</v>
+        <v>-0.13</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3035,28 +3044,28 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-1.67</v>
+        <v>-1.8</v>
       </c>
       <c r="I20">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="J20">
-        <v>0.26</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K20">
-        <v>-0.42</v>
+        <v>-0.46</v>
       </c>
       <c r="N20">
-        <v>6.91</v>
+        <v>6.23</v>
       </c>
       <c r="Q20">
-        <v>11110.66</v>
+        <v>11131.46</v>
       </c>
       <c r="R20">
-        <v>11200</v>
+        <v>11193.02</v>
       </c>
       <c r="S20">
-        <v>11178.35</v>
+        <v>11176.81</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3068,31 +3077,31 @@
         <v>1</v>
       </c>
       <c r="Z20">
-        <v>50.37</v>
+        <v>49.04</v>
       </c>
       <c r="AA20">
-        <v>-18.58</v>
+        <v>-16.53</v>
       </c>
       <c r="AB20">
-        <v>-9.65</v>
+        <v>-11.02</v>
       </c>
       <c r="AC20">
-        <v>-8.93</v>
+        <v>-5.5</v>
       </c>
       <c r="AD20">
-        <v>58.63</v>
+        <v>76.97</v>
       </c>
       <c r="AE20">
-        <v>32.79</v>
+        <v>55.07</v>
       </c>
       <c r="AF20">
-        <v>121.32</v>
+        <v>118.28</v>
       </c>
       <c r="AH20">
-        <v>11346.21</v>
+        <v>11331.38</v>
       </c>
       <c r="AI20">
-        <v>11053.78</v>
+        <v>11054.65</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3101,7 +3110,7 @@
         <v>82</v>
       </c>
       <c r="AL20">
-        <v>21.39</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3115,10 +3124,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27606.8</v>
+        <v>27747.85</v>
       </c>
       <c r="E21">
-        <v>-0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3127,43 +3136,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-5.42</v>
+        <v>-4.93</v>
       </c>
       <c r="I21">
-        <v>14.34</v>
+        <v>14.92</v>
       </c>
       <c r="J21">
-        <v>-0.45</v>
+        <v>-0.04</v>
       </c>
       <c r="K21">
-        <v>-0.91</v>
+        <v>0.01</v>
       </c>
       <c r="L21">
-        <v>5.21</v>
+        <v>5.51</v>
       </c>
       <c r="M21">
-        <v>3.41</v>
+        <v>5.34</v>
       </c>
       <c r="N21">
-        <v>7.68</v>
+        <v>7.84</v>
       </c>
       <c r="O21">
         <v>68</v>
       </c>
       <c r="Q21">
-        <v>27774.08</v>
+        <v>27771.94</v>
       </c>
       <c r="R21">
-        <v>27506.04</v>
+        <v>27509.44</v>
       </c>
       <c r="S21">
-        <v>27893.03</v>
+        <v>27882.45</v>
       </c>
       <c r="T21">
-        <v>27635.47</v>
+        <v>27633.57</v>
       </c>
       <c r="U21">
-        <v>-0.1</v>
+        <v>0.41</v>
       </c>
       <c r="V21" t="s">
         <v>80</v>
@@ -3175,34 +3184,34 @@
         <v>80</v>
       </c>
       <c r="Y21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z21">
-        <v>48.44</v>
+        <v>52.15</v>
       </c>
       <c r="AA21">
-        <v>-13.65</v>
+        <v>-4.69</v>
       </c>
       <c r="AB21">
-        <v>-66.81</v>
+        <v>-54.39</v>
       </c>
       <c r="AC21">
-        <v>53.16</v>
+        <v>49.7</v>
       </c>
       <c r="AD21">
-        <v>71.67</v>
+        <v>59.89</v>
       </c>
       <c r="AE21">
-        <v>85.93000000000001</v>
+        <v>73.02</v>
       </c>
       <c r="AF21">
-        <v>311.62</v>
+        <v>314.79</v>
       </c>
       <c r="AH21">
-        <v>27939.91</v>
+        <v>27950.05</v>
       </c>
       <c r="AI21">
-        <v>27072.18</v>
+        <v>27068.83</v>
       </c>
       <c r="AJ21">
         <v>28265.67</v>
@@ -3211,7 +3220,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>32.98</v>
+        <v>34.75</v>
       </c>
     </row>
   </sheetData>
@@ -3352,7 +3361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3392,7 +3401,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3412,107 +3421,107 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="E8" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -3524,16 +3533,16 @@
         <v>0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3544,13 +3553,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="8">
-        <v>-2.32</v>
+        <v>-3.65</v>
       </c>
       <c r="D12" s="8">
-        <v>-3.65</v>
+        <v>-5.35</v>
       </c>
       <c r="E12" s="9">
-        <v>-1.33</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3561,13 +3570,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="8">
-        <v>-2.99</v>
+        <v>-1.73</v>
       </c>
       <c r="D13" s="8">
-        <v>-1.73</v>
-      </c>
-      <c r="E13" s="10">
-        <v>1.26</v>
+        <v>-2.53</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3578,13 +3587,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="8">
-        <v>-3.89</v>
+        <v>-4.14</v>
       </c>
       <c r="D14" s="8">
-        <v>-4.14</v>
+        <v>-4.73</v>
       </c>
       <c r="E14" s="9">
-        <v>-0.25</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3595,13 +3604,13 @@
         <v>10</v>
       </c>
       <c r="C15" s="8">
-        <v>-2.9</v>
+        <v>-2.03</v>
       </c>
       <c r="D15" s="8">
-        <v>-2.03</v>
+        <v>-1.78</v>
       </c>
       <c r="E15" s="10">
-        <v>0.87</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3612,13 +3621,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="8">
-        <v>-7.02</v>
+        <v>-6.64</v>
       </c>
       <c r="D16" s="8">
-        <v>-6.64</v>
-      </c>
-      <c r="E16" s="10">
-        <v>0.38</v>
+        <v>-6.94</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3629,13 +3638,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="8">
-        <v>-3.63</v>
+        <v>-3.84</v>
       </c>
       <c r="D17" s="8">
-        <v>-3.84</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.21</v>
+        <v>-3.43</v>
+      </c>
+      <c r="E17" s="10">
+        <v>0.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3646,13 +3655,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-1.12</v>
       </c>
       <c r="D18" s="8">
-        <v>-1.12</v>
+        <v>-1.8</v>
       </c>
       <c r="E18" s="9">
-        <v>-0.43</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3663,13 +3672,13 @@
         <v>10</v>
       </c>
       <c r="C19" s="8">
-        <v>-0.72</v>
+        <v>-1.37</v>
       </c>
       <c r="D19" s="8">
-        <v>-1.37</v>
+        <v>-1.93</v>
       </c>
       <c r="E19" s="9">
-        <v>-0.65</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3680,13 +3689,13 @@
         <v>10</v>
       </c>
       <c r="C20" s="8">
-        <v>-3.14</v>
+        <v>-2.2</v>
       </c>
       <c r="D20" s="8">
-        <v>-2.2</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0.9399999999999999</v>
+        <v>-2.63</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3697,13 +3706,13 @@
         <v>10</v>
       </c>
       <c r="C21" s="8">
-        <v>-0.46</v>
+        <v>-4.15</v>
       </c>
       <c r="D21" s="8">
-        <v>-4.15</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-3.69</v>
+        <v>-0.91</v>
+      </c>
+      <c r="E21" s="10">
+        <v>3.24</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3714,13 +3723,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="8">
-        <v>2.13</v>
+        <v>0.96</v>
       </c>
       <c r="D22" s="8">
-        <v>0.96</v>
+        <v>-0.61</v>
       </c>
       <c r="E22" s="9">
-        <v>-1.17</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3731,13 +3740,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="8">
-        <v>-3.46</v>
+        <v>-2.43</v>
       </c>
       <c r="D23" s="8">
-        <v>-2.43</v>
-      </c>
-      <c r="E23" s="10">
-        <v>1.03</v>
+        <v>-2.46</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3748,13 +3757,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="8">
-        <v>0.22</v>
+        <v>0.38</v>
       </c>
       <c r="D24" s="8">
-        <v>0.38</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0.16</v>
+        <v>0.13</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3765,13 +3774,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="8">
-        <v>0.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D25" s="8">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E25" s="10">
-        <v>0.2</v>
+        <v>0.36</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3782,13 +3791,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="8">
-        <v>-2.38</v>
+        <v>0.22</v>
       </c>
       <c r="D26" s="8">
-        <v>0.22</v>
+        <v>1.94</v>
       </c>
       <c r="E26" s="10">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3799,13 +3808,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="8">
-        <v>-3.2</v>
+        <v>-3.43</v>
       </c>
       <c r="D27" s="8">
-        <v>-3.43</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.23</v>
+        <v>-3.12</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0.31</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3816,13 +3825,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="D28" s="8">
-        <v>-0.7</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E28" s="9">
-        <v>-0.02</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3833,13 +3842,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="8">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="D29" s="8">
-        <v>2.14</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.08</v>
+        <v>2.92</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0.78</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3850,13 +3859,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="8">
-        <v>-1.89</v>
+        <v>-0.42</v>
       </c>
       <c r="D30" s="8">
-        <v>-0.42</v>
-      </c>
-      <c r="E30" s="10">
-        <v>1.47</v>
+        <v>-0.46</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3867,13 +3876,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="8">
-        <v>-1.01</v>
+        <v>-0.91</v>
       </c>
       <c r="D31" s="8">
-        <v>-0.91</v>
+        <v>0.01</v>
       </c>
       <c r="E31" s="10">
-        <v>0.1</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3884,13 +3893,13 @@
         <v>9</v>
       </c>
       <c r="C32" s="8">
-        <v>-2.48</v>
+        <v>-3.51</v>
       </c>
       <c r="D32" s="8">
-        <v>-3.51</v>
+        <v>-3.62</v>
       </c>
       <c r="E32" s="9">
-        <v>-1.03</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3901,13 +3910,13 @@
         <v>9</v>
       </c>
       <c r="C33" s="8">
-        <v>-1.64</v>
+        <v>-1.21</v>
       </c>
       <c r="D33" s="8">
-        <v>-1.21</v>
+        <v>-0.65</v>
       </c>
       <c r="E33" s="10">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3918,13 +3927,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="8">
-        <v>-2.58</v>
+        <v>-2.21</v>
       </c>
       <c r="D34" s="8">
-        <v>-2.21</v>
-      </c>
-      <c r="E34" s="10">
-        <v>0.37</v>
+        <v>-2.32</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3935,13 +3944,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="8">
-        <v>-1.32</v>
+        <v>-0.19</v>
       </c>
       <c r="D35" s="8">
-        <v>-0.19</v>
+        <v>0.1</v>
       </c>
       <c r="E35" s="10">
-        <v>1.13</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3952,13 +3961,13 @@
         <v>9</v>
       </c>
       <c r="C36" s="8">
-        <v>-2.62</v>
+        <v>-2.14</v>
       </c>
       <c r="D36" s="8">
-        <v>-2.14</v>
-      </c>
-      <c r="E36" s="10">
-        <v>0.48</v>
+        <v>-2.29</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3969,13 +3978,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="8">
-        <v>-0.93</v>
+        <v>-2.17</v>
       </c>
       <c r="D37" s="8">
-        <v>-2.17</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1.24</v>
+        <v>-1.36</v>
+      </c>
+      <c r="E37" s="10">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3986,13 +3995,13 @@
         <v>9</v>
       </c>
       <c r="C38" s="8">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="D38" s="8">
-        <v>2.59</v>
-      </c>
-      <c r="E38" s="10">
-        <v>0.23</v>
+        <v>2.04</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4003,13 +4012,13 @@
         <v>9</v>
       </c>
       <c r="C39" s="8">
-        <v>-1.07</v>
+        <v>-1.8</v>
       </c>
       <c r="D39" s="8">
-        <v>-1.8</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.73</v>
+        <v>-1.73</v>
+      </c>
+      <c r="E39" s="10">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -4020,13 +4029,13 @@
         <v>9</v>
       </c>
       <c r="C40" s="8">
-        <v>-2.04</v>
+        <v>-0.83</v>
       </c>
       <c r="D40" s="8">
-        <v>-0.83</v>
+        <v>-0.36</v>
       </c>
       <c r="E40" s="10">
-        <v>1.21</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -4037,13 +4046,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="8">
-        <v>-3.02</v>
+        <v>-4.77</v>
       </c>
       <c r="D41" s="8">
-        <v>-4.77</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-1.75</v>
+        <v>-2.25</v>
+      </c>
+      <c r="E41" s="10">
+        <v>2.52</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -4054,13 +4063,13 @@
         <v>9</v>
       </c>
       <c r="C42" s="8">
-        <v>-1.36</v>
+        <v>-2.84</v>
       </c>
       <c r="D42" s="8">
-        <v>-2.84</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.48</v>
+        <v>-1.86</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0.98</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -4071,13 +4080,13 @@
         <v>9</v>
       </c>
       <c r="C43" s="8">
-        <v>-1.41</v>
+        <v>-0.33</v>
       </c>
       <c r="D43" s="8">
-        <v>-0.33</v>
+        <v>0.05</v>
       </c>
       <c r="E43" s="10">
-        <v>1.08</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -4088,13 +4097,13 @@
         <v>9</v>
       </c>
       <c r="C44" s="8">
-        <v>-1.14</v>
+        <v>-1.82</v>
       </c>
       <c r="D44" s="8">
-        <v>-1.82</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.68</v>
+        <v>-0.41</v>
+      </c>
+      <c r="E44" s="10">
+        <v>1.41</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4105,13 +4114,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="8">
-        <v>0.86</v>
+        <v>0.58</v>
       </c>
       <c r="D45" s="8">
-        <v>0.58</v>
+        <v>-0.71</v>
       </c>
       <c r="E45" s="9">
-        <v>-0.28</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -4122,13 +4131,13 @@
         <v>9</v>
       </c>
       <c r="C46" s="8">
-        <v>-2.89</v>
+        <v>-1.87</v>
       </c>
       <c r="D46" s="8">
-        <v>-1.87</v>
+        <v>0.72</v>
       </c>
       <c r="E46" s="10">
-        <v>1.02</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -4139,13 +4148,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="8">
-        <v>-0.78</v>
+        <v>-1.21</v>
       </c>
       <c r="D47" s="8">
-        <v>-1.21</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.43</v>
+        <v>-0.57</v>
+      </c>
+      <c r="E47" s="10">
+        <v>0.64</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4156,13 +4165,13 @@
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="D48" s="8">
-        <v>0.26</v>
+        <v>-0.93</v>
       </c>
       <c r="E48" s="9">
-        <v>-0.18</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4173,13 +4182,13 @@
         <v>9</v>
       </c>
       <c r="C49" s="8">
-        <v>-1.19</v>
+        <v>-1.27</v>
       </c>
       <c r="D49" s="8">
-        <v>-1.27</v>
+        <v>-1.34</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4190,13 +4199,13 @@
         <v>9</v>
       </c>
       <c r="C50" s="8">
-        <v>-0.65</v>
+        <v>0.26</v>
       </c>
       <c r="D50" s="8">
-        <v>0.26</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E50" s="10">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4207,13 +4216,13 @@
         <v>9</v>
       </c>
       <c r="C51" s="8">
-        <v>1.15</v>
+        <v>-0.45</v>
       </c>
       <c r="D51" s="8">
-        <v>-0.45</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-1.6</v>
+        <v>-0.04</v>
+      </c>
+      <c r="E51" s="10">
+        <v>0.41</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -4224,13 +4233,13 @@
         <v>12</v>
       </c>
       <c r="C52" s="8">
-        <v>12.48</v>
+        <v>10.06</v>
       </c>
       <c r="D52" s="8">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="E52" s="9">
-        <v>-2.42</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4241,13 +4250,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="8">
-        <v>10.76</v>
+        <v>10.9</v>
       </c>
       <c r="D53" s="8">
-        <v>10.9</v>
+        <v>12.37</v>
       </c>
       <c r="E53" s="10">
-        <v>0.14</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -4258,13 +4267,13 @@
         <v>12</v>
       </c>
       <c r="C54" s="8">
-        <v>-3.39</v>
+        <v>-4.17</v>
       </c>
       <c r="D54" s="8">
-        <v>-4.17</v>
+        <v>-4.29</v>
       </c>
       <c r="E54" s="9">
-        <v>-0.78</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -4275,13 +4284,13 @@
         <v>12</v>
       </c>
       <c r="C55" s="8">
-        <v>9.56</v>
+        <v>10.25</v>
       </c>
       <c r="D55" s="8">
-        <v>10.25</v>
+        <v>12.32</v>
       </c>
       <c r="E55" s="10">
-        <v>0.6899999999999999</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -4292,13 +4301,13 @@
         <v>12</v>
       </c>
       <c r="C56" s="8">
-        <v>-16.65</v>
+        <v>-16.96</v>
       </c>
       <c r="D56" s="8">
-        <v>-16.96</v>
+        <v>-18.21</v>
       </c>
       <c r="E56" s="9">
-        <v>-0.31</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -4309,13 +4318,13 @@
         <v>12</v>
       </c>
       <c r="C57" s="8">
-        <v>-1.19</v>
+        <v>-1.88</v>
       </c>
       <c r="D57" s="8">
-        <v>-1.88</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.6899999999999999</v>
+        <v>-0.11</v>
+      </c>
+      <c r="E57" s="10">
+        <v>1.77</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -4326,13 +4335,13 @@
         <v>12</v>
       </c>
       <c r="C58" s="8">
-        <v>-11.13</v>
+        <v>-14.27</v>
       </c>
       <c r="D58" s="8">
-        <v>-14.27</v>
+        <v>-14.49</v>
       </c>
       <c r="E58" s="9">
-        <v>-3.14</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -4343,13 +4352,13 @@
         <v>12</v>
       </c>
       <c r="C59" s="8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="D59" s="8">
-        <v>1.12</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-0.01</v>
+        <v>2.62</v>
+      </c>
+      <c r="E59" s="10">
+        <v>1.5</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -4360,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="C60" s="8">
-        <v>-5.59</v>
+        <v>-5.67</v>
       </c>
       <c r="D60" s="8">
-        <v>-5.67</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-0.08</v>
+        <v>-3.3</v>
+      </c>
+      <c r="E60" s="10">
+        <v>2.37</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -4377,13 +4386,13 @@
         <v>12</v>
       </c>
       <c r="C61" s="8">
-        <v>40.68</v>
+        <v>39.43</v>
       </c>
       <c r="D61" s="8">
-        <v>39.43</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-1.25</v>
+        <v>41.98</v>
+      </c>
+      <c r="E61" s="10">
+        <v>2.55</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -4394,13 +4403,13 @@
         <v>12</v>
       </c>
       <c r="C62" s="8">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="D62" s="8">
-        <v>2.42</v>
+        <v>4.28</v>
       </c>
       <c r="E62" s="10">
-        <v>0.43</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -4411,13 +4420,13 @@
         <v>12</v>
       </c>
       <c r="C63" s="8">
-        <v>21.54</v>
+        <v>21.94</v>
       </c>
       <c r="D63" s="8">
-        <v>21.94</v>
+        <v>24.86</v>
       </c>
       <c r="E63" s="10">
-        <v>0.4</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -4428,13 +4437,13 @@
         <v>12</v>
       </c>
       <c r="C64" s="8">
-        <v>20.34</v>
+        <v>19.76</v>
       </c>
       <c r="D64" s="8">
-        <v>19.76</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-0.58</v>
+        <v>21.23</v>
+      </c>
+      <c r="E64" s="10">
+        <v>1.47</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4445,13 +4454,13 @@
         <v>12</v>
       </c>
       <c r="C65" s="8">
-        <v>-2.02</v>
+        <v>-2.54</v>
       </c>
       <c r="D65" s="8">
-        <v>-2.54</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-0.52</v>
+        <v>2.25</v>
+      </c>
+      <c r="E65" s="10">
+        <v>4.79</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4462,13 +4471,13 @@
         <v>12</v>
       </c>
       <c r="C66" s="8">
-        <v>-5.45</v>
+        <v>-6.57</v>
       </c>
       <c r="D66" s="8">
-        <v>-6.57</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-1.12</v>
+        <v>-5.37</v>
+      </c>
+      <c r="E66" s="10">
+        <v>1.2</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4479,13 +4488,13 @@
         <v>12</v>
       </c>
       <c r="C67" s="8">
-        <v>4.01</v>
+        <v>3.41</v>
       </c>
       <c r="D67" s="8">
-        <v>3.41</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-0.6</v>
+        <v>5.34</v>
+      </c>
+      <c r="E67" s="10">
+        <v>1.93</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4496,13 +4505,13 @@
         <v>11</v>
       </c>
       <c r="C68" s="8">
-        <v>9.19</v>
+        <v>7.03</v>
       </c>
       <c r="D68" s="8">
-        <v>7.03</v>
+        <v>6.39</v>
       </c>
       <c r="E68" s="9">
-        <v>-2.16</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4513,13 +4522,13 @@
         <v>11</v>
       </c>
       <c r="C69" s="8">
-        <v>-4.9</v>
+        <v>-4.17</v>
       </c>
       <c r="D69" s="8">
-        <v>-4.17</v>
+        <v>-3.49</v>
       </c>
       <c r="E69" s="10">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4530,13 +4539,13 @@
         <v>11</v>
       </c>
       <c r="C70" s="8">
-        <v>5.81</v>
+        <v>4.63</v>
       </c>
       <c r="D70" s="8">
-        <v>4.63</v>
+        <v>4.03</v>
       </c>
       <c r="E70" s="9">
-        <v>-1.18</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4547,13 +4556,13 @@
         <v>11</v>
       </c>
       <c r="C71" s="8">
-        <v>-5.95</v>
+        <v>-5.98</v>
       </c>
       <c r="D71" s="8">
-        <v>-5.98</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-0.03</v>
+        <v>-5.47</v>
+      </c>
+      <c r="E71" s="10">
+        <v>0.51</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4564,13 +4573,13 @@
         <v>11</v>
       </c>
       <c r="C72" s="8">
-        <v>-3.46</v>
+        <v>-4.1</v>
       </c>
       <c r="D72" s="8">
-        <v>-4.1</v>
+        <v>-4.86</v>
       </c>
       <c r="E72" s="9">
-        <v>-0.64</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4581,13 +4590,13 @@
         <v>11</v>
       </c>
       <c r="C73" s="8">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="D73" s="8">
-        <v>3.12</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-1.08</v>
+        <v>3.46</v>
+      </c>
+      <c r="E73" s="10">
+        <v>0.34</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4598,13 +4607,13 @@
         <v>11</v>
       </c>
       <c r="C74" s="8">
-        <v>7.19</v>
+        <v>6.15</v>
       </c>
       <c r="D74" s="8">
-        <v>6.15</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-1.04</v>
+        <v>6.3</v>
+      </c>
+      <c r="E74" s="10">
+        <v>0.15</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4615,13 +4624,13 @@
         <v>11</v>
       </c>
       <c r="C75" s="8">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="D75" s="8">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="E75" s="10">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4632,13 +4641,13 @@
         <v>11</v>
       </c>
       <c r="C76" s="8">
-        <v>9.9</v>
+        <v>5.66</v>
       </c>
       <c r="D76" s="8">
-        <v>5.66</v>
+        <v>3.88</v>
       </c>
       <c r="E76" s="9">
-        <v>-4.24</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4649,13 +4658,13 @@
         <v>11</v>
       </c>
       <c r="C77" s="8">
-        <v>-2.55</v>
+        <v>-2.07</v>
       </c>
       <c r="D77" s="8">
-        <v>-2.07</v>
+        <v>-0.34</v>
       </c>
       <c r="E77" s="10">
-        <v>0.48</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4666,13 +4675,13 @@
         <v>11</v>
       </c>
       <c r="C78" s="8">
-        <v>-4.26</v>
+        <v>-4.21</v>
       </c>
       <c r="D78" s="8">
-        <v>-4.21</v>
+        <v>-3.71</v>
       </c>
       <c r="E78" s="10">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4683,13 +4692,13 @@
         <v>11</v>
       </c>
       <c r="C79" s="8">
-        <v>3.91</v>
+        <v>3.56</v>
       </c>
       <c r="D79" s="8">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="E79" s="9">
-        <v>-0.35</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4700,13 +4709,13 @@
         <v>11</v>
       </c>
       <c r="C80" s="8">
-        <v>11.23</v>
+        <v>10.76</v>
       </c>
       <c r="D80" s="8">
-        <v>10.76</v>
+        <v>9.94</v>
       </c>
       <c r="E80" s="9">
-        <v>-0.47</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4717,13 +4726,13 @@
         <v>11</v>
       </c>
       <c r="C81" s="8">
-        <v>16.88</v>
+        <v>16.81</v>
       </c>
       <c r="D81" s="8">
-        <v>16.81</v>
-      </c>
-      <c r="E81" s="9">
-        <v>-0.07000000000000001</v>
+        <v>19.15</v>
+      </c>
+      <c r="E81" s="10">
+        <v>2.34</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4734,13 +4743,13 @@
         <v>11</v>
       </c>
       <c r="C82" s="8">
-        <v>4.06</v>
+        <v>3.17</v>
       </c>
       <c r="D82" s="8">
-        <v>3.17</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-0.89</v>
+        <v>3.58</v>
+      </c>
+      <c r="E82" s="10">
+        <v>0.41</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4751,13 +4760,13 @@
         <v>11</v>
       </c>
       <c r="C83" s="8">
-        <v>5.99</v>
+        <v>5.21</v>
       </c>
       <c r="D83" s="8">
-        <v>5.21</v>
-      </c>
-      <c r="E83" s="9">
-        <v>-0.78</v>
+        <v>5.51</v>
+      </c>
+      <c r="E83" s="10">
+        <v>0.3</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4768,13 +4777,13 @@
         <v>7</v>
       </c>
       <c r="C84" s="8">
-        <v>-3.9</v>
+        <v>-5.62</v>
       </c>
       <c r="D84" s="8">
-        <v>-5.62</v>
+        <v>-6.11</v>
       </c>
       <c r="E84" s="9">
-        <v>-1.72</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4785,13 +4794,13 @@
         <v>7</v>
       </c>
       <c r="C85" s="8">
-        <v>-7.61</v>
+        <v>-7.11</v>
       </c>
       <c r="D85" s="8">
-        <v>-7.11</v>
-      </c>
-      <c r="E85" s="10">
-        <v>0.5</v>
+        <v>-7.17</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4802,13 +4811,13 @@
         <v>7</v>
       </c>
       <c r="C86" s="8">
-        <v>-6.78</v>
+        <v>-7.4</v>
       </c>
       <c r="D86" s="8">
-        <v>-7.4</v>
+        <v>-7.87</v>
       </c>
       <c r="E86" s="9">
-        <v>-0.62</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4819,13 +4828,13 @@
         <v>7</v>
       </c>
       <c r="C87" s="8">
-        <v>-8.98</v>
+        <v>-8.44</v>
       </c>
       <c r="D87" s="8">
-        <v>-8.44</v>
+        <v>-8.17</v>
       </c>
       <c r="E87" s="10">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4836,13 +4845,13 @@
         <v>7</v>
       </c>
       <c r="C88" s="8">
-        <v>-18.64</v>
+        <v>-19.02</v>
       </c>
       <c r="D88" s="8">
-        <v>-19.02</v>
+        <v>-19.52</v>
       </c>
       <c r="E88" s="9">
-        <v>-0.38</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4853,13 +4862,13 @@
         <v>7</v>
       </c>
       <c r="C89" s="8">
-        <v>-8.640000000000001</v>
+        <v>-9.31</v>
       </c>
       <c r="D89" s="8">
-        <v>-9.31</v>
-      </c>
-      <c r="E89" s="9">
-        <v>-0.67</v>
+        <v>-8.92</v>
+      </c>
+      <c r="E89" s="10">
+        <v>0.39</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4870,13 +4879,13 @@
         <v>7</v>
       </c>
       <c r="C90" s="8">
-        <v>-20.24</v>
+        <v>-21.23</v>
       </c>
       <c r="D90" s="8">
-        <v>-21.23</v>
+        <v>-21.9</v>
       </c>
       <c r="E90" s="9">
-        <v>-0.99</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4887,13 +4896,13 @@
         <v>7</v>
       </c>
       <c r="C91" s="8">
-        <v>-1.56</v>
+        <v>-2.36</v>
       </c>
       <c r="D91" s="8">
-        <v>-2.36</v>
-      </c>
-      <c r="E91" s="9">
-        <v>-0.8</v>
+        <v>-2.34</v>
+      </c>
+      <c r="E91" s="10">
+        <v>0.02</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4904,13 +4913,13 @@
         <v>7</v>
       </c>
       <c r="C92" s="8">
-        <v>-5.7</v>
+        <v>-5.67</v>
       </c>
       <c r="D92" s="8">
-        <v>-5.67</v>
-      </c>
-      <c r="E92" s="10">
-        <v>0.03</v>
+        <v>-5.75</v>
+      </c>
+      <c r="E92" s="9">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4921,13 +4930,13 @@
         <v>7</v>
       </c>
       <c r="C93" s="8">
-        <v>-4.35</v>
+        <v>-6.03</v>
       </c>
       <c r="D93" s="8">
-        <v>-6.03</v>
-      </c>
-      <c r="E93" s="9">
-        <v>-1.68</v>
+        <v>-4.4</v>
+      </c>
+      <c r="E93" s="10">
+        <v>1.63</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4938,13 +4947,13 @@
         <v>7</v>
       </c>
       <c r="C94" s="8">
-        <v>-3.85</v>
+        <v>-4.09</v>
       </c>
       <c r="D94" s="8">
-        <v>-4.09</v>
-      </c>
-      <c r="E94" s="9">
-        <v>-0.24</v>
+        <v>-3.95</v>
+      </c>
+      <c r="E94" s="10">
+        <v>0.14</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4955,13 +4964,13 @@
         <v>7</v>
       </c>
       <c r="C95" s="8">
-        <v>-10.28</v>
+        <v>-9.94</v>
       </c>
       <c r="D95" s="8">
-        <v>-9.94</v>
+        <v>-9.84</v>
       </c>
       <c r="E95" s="10">
-        <v>0.34</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4972,13 +4981,13 @@
         <v>7</v>
       </c>
       <c r="C96" s="8">
-        <v>-13.91</v>
+        <v>-13.85</v>
       </c>
       <c r="D96" s="8">
-        <v>-13.85</v>
+        <v>-13.43</v>
       </c>
       <c r="E96" s="10">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4989,13 +4998,13 @@
         <v>7</v>
       </c>
       <c r="C97" s="8">
-        <v>-1.45</v>
+        <v>-1.49</v>
       </c>
       <c r="D97" s="8">
-        <v>-1.49</v>
+        <v>-1.94</v>
       </c>
       <c r="E97" s="9">
-        <v>-0.04</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -5006,13 +5015,13 @@
         <v>7</v>
       </c>
       <c r="C98" s="8">
-        <v>-7.99</v>
+        <v>-7.79</v>
       </c>
       <c r="D98" s="8">
-        <v>-7.79</v>
+        <v>-5.42</v>
       </c>
       <c r="E98" s="10">
-        <v>0.2</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -5023,13 +5032,13 @@
         <v>7</v>
       </c>
       <c r="C99" s="8">
-        <v>-9.81</v>
+        <v>-10.49</v>
       </c>
       <c r="D99" s="8">
-        <v>-10.49</v>
-      </c>
-      <c r="E99" s="9">
-        <v>-0.68</v>
+        <v>-10.34</v>
+      </c>
+      <c r="E99" s="10">
+        <v>0.15</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -5040,13 +5049,13 @@
         <v>7</v>
       </c>
       <c r="C100" s="8">
-        <v>-1.6</v>
+        <v>-1.84</v>
       </c>
       <c r="D100" s="8">
-        <v>-1.84</v>
+        <v>-2.3</v>
       </c>
       <c r="E100" s="9">
-        <v>-0.24</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5057,13 +5066,13 @@
         <v>7</v>
       </c>
       <c r="C101" s="8">
-        <v>-3.22</v>
+        <v>-3.48</v>
       </c>
       <c r="D101" s="8">
-        <v>-3.48</v>
-      </c>
-      <c r="E101" s="9">
-        <v>-0.26</v>
+        <v>-2.98</v>
+      </c>
+      <c r="E101" s="10">
+        <v>0.5</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5074,13 +5083,13 @@
         <v>7</v>
       </c>
       <c r="C102" s="8">
-        <v>-1.99</v>
+        <v>-1.67</v>
       </c>
       <c r="D102" s="8">
-        <v>-1.67</v>
-      </c>
-      <c r="E102" s="10">
-        <v>0.32</v>
+        <v>-1.8</v>
+      </c>
+      <c r="E102" s="9">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5091,13 +5100,13 @@
         <v>7</v>
       </c>
       <c r="C103" s="8">
-        <v>-4.89</v>
+        <v>-5.42</v>
       </c>
       <c r="D103" s="8">
-        <v>-5.42</v>
-      </c>
-      <c r="E103" s="9">
-        <v>-0.53</v>
+        <v>-4.93</v>
+      </c>
+      <c r="E103" s="10">
+        <v>0.49</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5108,13 +5117,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="8">
-        <v>28491.05</v>
+        <v>27981.95</v>
       </c>
       <c r="D104" s="8">
-        <v>27981.95</v>
+        <v>27837.4</v>
       </c>
       <c r="E104" s="9">
-        <v>-509.1</v>
+        <v>-144.55</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5125,13 +5134,13 @@
         <v>3</v>
       </c>
       <c r="C105" s="8">
-        <v>9704.200000000001</v>
+        <v>9756.9</v>
       </c>
       <c r="D105" s="8">
-        <v>9756.9</v>
-      </c>
-      <c r="E105" s="10">
-        <v>52.7</v>
+        <v>9750.6</v>
+      </c>
+      <c r="E105" s="9">
+        <v>-6.3</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5142,13 +5151,13 @@
         <v>3</v>
       </c>
       <c r="C106" s="8">
-        <v>11782.3</v>
+        <v>11703.6</v>
       </c>
       <c r="D106" s="8">
-        <v>11703.6</v>
+        <v>11644.8</v>
       </c>
       <c r="E106" s="9">
-        <v>-78.7</v>
+        <v>-58.8</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5159,13 +5168,13 @@
         <v>3</v>
       </c>
       <c r="C107" s="8">
-        <v>37806.1</v>
+        <v>38028.4</v>
       </c>
       <c r="D107" s="8">
-        <v>38028.4</v>
+        <v>38140.8</v>
       </c>
       <c r="E107" s="10">
-        <v>222.3</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5176,13 +5185,13 @@
         <v>3</v>
       </c>
       <c r="C108" s="8">
-        <v>46457.15</v>
+        <v>46240.55</v>
       </c>
       <c r="D108" s="8">
-        <v>46240.55</v>
+        <v>45955.65</v>
       </c>
       <c r="E108" s="9">
-        <v>-216.6</v>
+        <v>-284.9</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5193,13 +5202,13 @@
         <v>3</v>
       </c>
       <c r="C109" s="8">
-        <v>26003.9</v>
+        <v>25813.05</v>
       </c>
       <c r="D109" s="8">
-        <v>25813.05</v>
-      </c>
-      <c r="E109" s="9">
-        <v>-190.85</v>
+        <v>25923.05</v>
+      </c>
+      <c r="E109" s="10">
+        <v>110</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5210,13 +5219,13 @@
         <v>3</v>
       </c>
       <c r="C110" s="8">
-        <v>31496.7</v>
+        <v>31102.9</v>
       </c>
       <c r="D110" s="8">
-        <v>31102.9</v>
+        <v>30838.85</v>
       </c>
       <c r="E110" s="9">
-        <v>-393.8</v>
+        <v>-264.05</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5227,13 +5236,13 @@
         <v>3</v>
       </c>
       <c r="C111" s="8">
-        <v>16402.5</v>
+        <v>16269.35</v>
       </c>
       <c r="D111" s="8">
-        <v>16269.35</v>
-      </c>
-      <c r="E111" s="9">
-        <v>-133.15</v>
+        <v>16271.8</v>
+      </c>
+      <c r="E111" s="10">
+        <v>2.45</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5244,13 +5253,13 @@
         <v>3</v>
       </c>
       <c r="C112" s="8">
-        <v>9209.25</v>
+        <v>9212.049999999999</v>
       </c>
       <c r="D112" s="8">
-        <v>9212.049999999999</v>
-      </c>
-      <c r="E112" s="10">
-        <v>2.8</v>
+        <v>9204.200000000001</v>
+      </c>
+      <c r="E112" s="9">
+        <v>-7.85</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5261,13 +5270,13 @@
         <v>3</v>
       </c>
       <c r="C113" s="8">
-        <v>1561.45</v>
+        <v>1534.1</v>
       </c>
       <c r="D113" s="8">
-        <v>1534.1</v>
-      </c>
-      <c r="E113" s="9">
-        <v>-27.35</v>
+        <v>1560.75</v>
+      </c>
+      <c r="E113" s="10">
+        <v>26.65</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5278,13 +5287,13 @@
         <v>3</v>
       </c>
       <c r="C114" s="8">
-        <v>13189.85</v>
+        <v>13157.35</v>
       </c>
       <c r="D114" s="8">
-        <v>13157.35</v>
-      </c>
-      <c r="E114" s="9">
-        <v>-32.5</v>
+        <v>13176.05</v>
+      </c>
+      <c r="E114" s="10">
+        <v>18.7</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5295,13 +5304,13 @@
         <v>3</v>
       </c>
       <c r="C115" s="8">
-        <v>9659.5</v>
+        <v>9695.950000000001</v>
       </c>
       <c r="D115" s="8">
-        <v>9695.950000000001</v>
+        <v>9706.65</v>
       </c>
       <c r="E115" s="10">
-        <v>36.45</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5312,13 +5321,13 @@
         <v>3</v>
       </c>
       <c r="C116" s="8">
-        <v>8505.75</v>
+        <v>8511.700000000001</v>
       </c>
       <c r="D116" s="8">
-        <v>8511.700000000001</v>
+        <v>8552.6</v>
       </c>
       <c r="E116" s="10">
-        <v>5.95</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5329,13 +5338,13 @@
         <v>3</v>
       </c>
       <c r="C117" s="8">
-        <v>26792.65</v>
+        <v>26780.7</v>
       </c>
       <c r="D117" s="8">
-        <v>26780.7</v>
+        <v>26658.65</v>
       </c>
       <c r="E117" s="9">
-        <v>-11.95</v>
+        <v>-122.05</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5346,13 +5355,13 @@
         <v>3</v>
       </c>
       <c r="C118" s="8">
-        <v>891.3</v>
+        <v>893.15</v>
       </c>
       <c r="D118" s="8">
-        <v>893.15</v>
+        <v>916.15</v>
       </c>
       <c r="E118" s="10">
-        <v>1.85</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5363,13 +5372,13 @@
         <v>3</v>
       </c>
       <c r="C119" s="8">
-        <v>30756.6</v>
+        <v>30525.25</v>
       </c>
       <c r="D119" s="8">
-        <v>30525.25</v>
-      </c>
-      <c r="E119" s="9">
-        <v>-231.35</v>
+        <v>30575.05</v>
+      </c>
+      <c r="E119" s="10">
+        <v>49.8</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5380,13 +5389,13 @@
         <v>3</v>
       </c>
       <c r="C120" s="8">
-        <v>16669.85</v>
+        <v>16629.1</v>
       </c>
       <c r="D120" s="8">
-        <v>16629.1</v>
+        <v>16552.2</v>
       </c>
       <c r="E120" s="9">
-        <v>-40.75</v>
+        <v>-76.90000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5397,13 +5406,13 @@
         <v>3</v>
       </c>
       <c r="C121" s="8">
-        <v>9647.65</v>
+        <v>9621.35</v>
       </c>
       <c r="D121" s="8">
-        <v>9621.35</v>
-      </c>
-      <c r="E121" s="9">
-        <v>-26.3</v>
+        <v>9670.9</v>
+      </c>
+      <c r="E121" s="10">
+        <v>49.55</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5414,13 +5423,13 @@
         <v>3</v>
       </c>
       <c r="C122" s="8">
-        <v>11142.3</v>
+        <v>11178.85</v>
       </c>
       <c r="D122" s="8">
-        <v>11178.85</v>
-      </c>
-      <c r="E122" s="10">
-        <v>36.55</v>
+        <v>11164.65</v>
+      </c>
+      <c r="E122" s="9">
+        <v>-14.2</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5431,438 +5440,472 @@
         <v>3</v>
       </c>
       <c r="C123" s="8">
-        <v>27762.1</v>
+        <v>27606.8</v>
       </c>
       <c r="D123" s="8">
-        <v>27606.8</v>
-      </c>
-      <c r="E123" s="9">
-        <v>-155.3</v>
+        <v>27747.85</v>
+      </c>
+      <c r="E123" s="10">
+        <v>141.05</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C124" s="8">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D124" s="8">
-        <v>56</v>
-      </c>
-      <c r="E124" s="10">
-        <v>6</v>
+        <v>74</v>
+      </c>
+      <c r="E124" s="9">
+        <v>-7</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C125" s="8">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D125" s="8">
-        <v>50</v>
-      </c>
-      <c r="E125" s="10">
-        <v>18</v>
+        <v>26</v>
+      </c>
+      <c r="E125" s="9">
+        <v>-12</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="8">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D126" s="8">
-        <v>32</v>
-      </c>
-      <c r="E126" s="9">
-        <v>-24</v>
+        <v>50</v>
+      </c>
+      <c r="E126" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="8">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D127" s="8">
-        <v>26</v>
-      </c>
-      <c r="E127" s="10">
-        <v>7</v>
+        <v>44</v>
+      </c>
+      <c r="E127" s="9">
+        <v>-6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="8">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D128" s="8">
-        <v>19</v>
-      </c>
-      <c r="E128" s="9">
-        <v>-7</v>
+        <v>38</v>
+      </c>
+      <c r="E128" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C129" s="8">
-        <v>44.91</v>
+        <v>26</v>
       </c>
       <c r="D129" s="8">
-        <v>36.13</v>
-      </c>
-      <c r="E129" s="9">
-        <v>-8.779999999999999</v>
+        <v>32</v>
+      </c>
+      <c r="E129" s="10">
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C130" s="8">
-        <v>36.85</v>
+        <v>74</v>
       </c>
       <c r="D130" s="8">
-        <v>42.76</v>
+        <v>81</v>
       </c>
       <c r="E130" s="10">
-        <v>5.91</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C131" s="8">
-        <v>38.35</v>
+        <v>36.13</v>
       </c>
       <c r="D131" s="8">
-        <v>34.59</v>
+        <v>34.09</v>
       </c>
       <c r="E131" s="9">
-        <v>-3.76</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="8">
-        <v>28.46</v>
+        <v>42.76</v>
       </c>
       <c r="D132" s="8">
-        <v>37.23</v>
-      </c>
-      <c r="E132" s="10">
-        <v>8.77</v>
+        <v>42.25</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="8">
-        <v>32.26</v>
+        <v>34.59</v>
       </c>
       <c r="D133" s="8">
-        <v>30.69</v>
+        <v>32.05</v>
       </c>
       <c r="E133" s="9">
-        <v>-1.57</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="8">
-        <v>38.12</v>
+        <v>37.23</v>
       </c>
       <c r="D134" s="8">
-        <v>33.84</v>
-      </c>
-      <c r="E134" s="9">
-        <v>-4.28</v>
+        <v>41.16</v>
+      </c>
+      <c r="E134" s="10">
+        <v>3.93</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="8">
-        <v>60.17</v>
+        <v>30.69</v>
       </c>
       <c r="D135" s="8">
-        <v>55.2</v>
+        <v>28.7</v>
       </c>
       <c r="E135" s="9">
-        <v>-4.97</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="8">
-        <v>47.73</v>
+        <v>33.84</v>
       </c>
       <c r="D136" s="8">
-        <v>40.07</v>
-      </c>
-      <c r="E136" s="9">
-        <v>-7.66</v>
+        <v>38.15</v>
+      </c>
+      <c r="E136" s="10">
+        <v>4.31</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="8">
-        <v>37.48</v>
+        <v>55.2</v>
       </c>
       <c r="D137" s="8">
-        <v>37.82</v>
-      </c>
-      <c r="E137" s="10">
-        <v>0.34</v>
+        <v>52.09</v>
+      </c>
+      <c r="E137" s="9">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="8">
-        <v>46.37</v>
+        <v>40.07</v>
       </c>
       <c r="D138" s="8">
-        <v>40.33</v>
-      </c>
-      <c r="E138" s="9">
-        <v>-6.04</v>
+        <v>40.26</v>
+      </c>
+      <c r="E138" s="10">
+        <v>0.19</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="8">
-        <v>53.28</v>
+        <v>37.82</v>
       </c>
       <c r="D139" s="8">
-        <v>52.05</v>
+        <v>37.21</v>
       </c>
       <c r="E139" s="9">
-        <v>-1.23</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="8">
-        <v>30.83</v>
+        <v>40.33</v>
       </c>
       <c r="D140" s="8">
-        <v>36.48</v>
+        <v>47.51</v>
       </c>
       <c r="E140" s="10">
-        <v>5.65</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="8">
-        <v>45.02</v>
+        <v>52.05</v>
       </c>
       <c r="D141" s="8">
-        <v>45.47</v>
+        <v>52.73</v>
       </c>
       <c r="E141" s="10">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="8">
-        <v>58.85</v>
+        <v>36.48</v>
       </c>
       <c r="D142" s="8">
-        <v>58.48</v>
-      </c>
-      <c r="E142" s="9">
-        <v>-0.37</v>
+        <v>38.08</v>
+      </c>
+      <c r="E142" s="10">
+        <v>1.6</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="8">
-        <v>44.8</v>
+        <v>45.47</v>
       </c>
       <c r="D143" s="8">
-        <v>45.93</v>
+        <v>48.6</v>
       </c>
       <c r="E143" s="10">
-        <v>1.13</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="8">
-        <v>41.74</v>
+        <v>58.48</v>
       </c>
       <c r="D144" s="8">
-        <v>36.03</v>
+        <v>54.7</v>
       </c>
       <c r="E144" s="9">
-        <v>-5.71</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="8">
-        <v>54.42</v>
+        <v>45.93</v>
       </c>
       <c r="D145" s="8">
-        <v>52.56</v>
-      </c>
-      <c r="E145" s="9">
-        <v>-1.86</v>
+        <v>57.61</v>
+      </c>
+      <c r="E145" s="10">
+        <v>11.68</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="8">
-        <v>49.46</v>
+        <v>36.03</v>
       </c>
       <c r="D146" s="8">
-        <v>47.87</v>
-      </c>
-      <c r="E146" s="9">
-        <v>-1.59</v>
+        <v>38</v>
+      </c>
+      <c r="E146" s="10">
+        <v>1.97</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="8">
-        <v>46.92</v>
+        <v>52.56</v>
       </c>
       <c r="D147" s="8">
-        <v>50.37</v>
-      </c>
-      <c r="E147" s="10">
-        <v>3.45</v>
+        <v>49.15</v>
+      </c>
+      <c r="E147" s="9">
+        <v>-3.41</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="8">
-        <v>52.61</v>
+        <v>47.87</v>
       </c>
       <c r="D148" s="8">
+        <v>51.06</v>
+      </c>
+      <c r="E148" s="10">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C149" s="8">
+        <v>50.37</v>
+      </c>
+      <c r="D149" s="8">
+        <v>49.04</v>
+      </c>
+      <c r="E149" s="9">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C150" s="8">
         <v>48.44</v>
       </c>
-      <c r="E148" s="9">
-        <v>-4.17</v>
+      <c r="D150" s="8">
+        <v>52.15</v>
+      </c>
+      <c r="E150" s="10">
+        <v>3.71</v>
       </c>
     </row>
   </sheetData>
@@ -5892,28 +5935,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5927,7 +5970,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="13">
-        <v>43.1</v>
+        <v>44.2</v>
       </c>
       <c r="E2" s="13">
         <v>40</v>
@@ -5936,7 +5979,7 @@
         <v>-1.7</v>
       </c>
       <c r="G2" s="13">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
@@ -6071,44 +6114,44 @@
         <v>46</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.3494</v>
+        <v>0.3753</v>
       </c>
       <c r="B2" s="16">
-        <v>0.3477</v>
+        <v>0.3157</v>
       </c>
       <c r="C2" s="16">
-        <v>0.2942</v>
+        <v>0.2936</v>
       </c>
       <c r="D2" s="16">
-        <v>0.228</v>
+        <v>0.2242</v>
       </c>
       <c r="E2" s="16">
-        <v>0.2151</v>
+        <v>0.2114</v>
       </c>
       <c r="F2" s="16">
-        <v>0.1843</v>
+        <v>0.1827</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1841</v>
+        <v>0.1817</v>
       </c>
       <c r="H2" s="16">
-        <v>0.1666</v>
+        <v>0.17</v>
       </c>
       <c r="I2" s="16">
-        <v>0.1405</v>
+        <v>0.1376</v>
       </c>
       <c r="J2" s="16">
-        <v>0.1319</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="15" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>39</v>
@@ -6140,34 +6183,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.1312</v>
+        <v>0.1275</v>
       </c>
       <c r="B4" s="16">
-        <v>0.1208</v>
+        <v>0.1177</v>
       </c>
       <c r="C4" s="16">
-        <v>0.1082</v>
+        <v>0.1065</v>
       </c>
       <c r="D4" s="16">
-        <v>0.07679999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="E4" s="16">
-        <v>0.0726</v>
+        <v>0.0741</v>
       </c>
       <c r="F4" s="16">
-        <v>0.06909999999999999</v>
+        <v>0.0623</v>
       </c>
       <c r="G4" s="16">
-        <v>0.0469</v>
+        <v>0.0474</v>
       </c>
       <c r="H4" s="16">
-        <v>0.0279</v>
+        <v>0.027</v>
       </c>
       <c r="I4" s="16">
-        <v>-0.0103</v>
+        <v>-0.0098</v>
       </c>
       <c r="J4" s="16">
-        <v>-0.0215</v>
+        <v>-0.0244</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="116">
   <si>
     <t>Symbol</t>
   </si>
@@ -292,70 +292,43 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.9 → 57.6</t>
+    <t>49.0 → 51.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>45.9</t>
-  </si>
-  <si>
-    <t>57.6</t>
-  </si>
-  <si>
-    <t>47.9 → 51.1</t>
-  </si>
-  <si>
-    <t>47.9</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>48.4 → 52.1</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>52.1</t>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>51.3</t>
   </si>
   <si>
     <t>Left 52W High Zone</t>
   </si>
   <si>
-    <t>-1.8% → -2.3%</t>
+    <t>-1.9% → -2.6%</t>
   </si>
   <si>
     <t>⚪ NEUTRAL</t>
   </si>
   <si>
-    <t>-1.8%</t>
-  </si>
-  <si>
-    <t>-2.3%</t>
-  </si>
-  <si>
-    <t>52.6 → 49.1</t>
+    <t>-1.9%</t>
+  </si>
+  <si>
+    <t>-2.6%</t>
+  </si>
+  <si>
+    <t>54.7 → 49.6</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.6</t>
-  </si>
-  <si>
-    <t>49.1</t>
-  </si>
-  <si>
-    <t>50.4 → 49.0</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>49.0</t>
+    <t>54.7</t>
+  </si>
+  <si>
+    <t>49.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -582,8 +555,8 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1100,10 +1073,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>27837.4</v>
+        <v>27710.9</v>
       </c>
       <c r="E2">
-        <v>-0.52</v>
+        <v>-0.45</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1112,43 +1085,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-6.11</v>
+        <v>-6.53</v>
       </c>
       <c r="I2">
-        <v>17.11</v>
+        <v>16.58</v>
       </c>
       <c r="J2">
-        <v>-3.62</v>
+        <v>-3.95</v>
       </c>
       <c r="K2">
-        <v>-5.35</v>
+        <v>-4.82</v>
       </c>
       <c r="L2">
-        <v>6.39</v>
+        <v>7.9</v>
       </c>
       <c r="M2">
-        <v>9.94</v>
+        <v>10.04</v>
       </c>
       <c r="N2">
-        <v>22.42</v>
+        <v>22.24</v>
       </c>
       <c r="O2">
         <v>74</v>
       </c>
       <c r="Q2">
-        <v>28400.74</v>
+        <v>28172.56</v>
       </c>
       <c r="R2">
-        <v>29056.34</v>
+        <v>28959.49</v>
       </c>
       <c r="S2">
-        <v>28028.94</v>
+        <v>28043.61</v>
       </c>
       <c r="T2">
-        <v>27133.05</v>
+        <v>27134.69</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1163,16 +1136,16 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>34.09</v>
+        <v>32.37</v>
       </c>
       <c r="AA2">
-        <v>34.5</v>
+        <v>-42.58</v>
       </c>
       <c r="AB2">
-        <v>266.71</v>
+        <v>204.85</v>
       </c>
       <c r="AC2">
-        <v>-232.21</v>
+        <v>-247.43</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1181,22 +1154,22 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>402.16</v>
+        <v>388.5</v>
       </c>
       <c r="AH2">
-        <v>30014.74</v>
+        <v>30048.74</v>
       </c>
       <c r="AI2">
-        <v>28097.93</v>
+        <v>27870.23</v>
       </c>
       <c r="AJ2">
-        <v>29113.69</v>
+        <v>28944.71</v>
       </c>
       <c r="AK2" t="s">
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>44.26</v>
+        <v>48.77</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1210,10 +1183,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9750.6</v>
+        <v>9803.85</v>
       </c>
       <c r="E3">
-        <v>-0.06</v>
+        <v>0.55</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1222,43 +1195,43 @@
         <v>8571.799999999999</v>
       </c>
       <c r="H3">
-        <v>-7.17</v>
+        <v>-6.66</v>
       </c>
       <c r="I3">
-        <v>13.75</v>
+        <v>14.37</v>
       </c>
       <c r="J3">
-        <v>-0.65</v>
+        <v>-0.05</v>
       </c>
       <c r="K3">
-        <v>-2.53</v>
+        <v>-1.54</v>
       </c>
       <c r="L3">
-        <v>-3.49</v>
+        <v>-1.39</v>
       </c>
       <c r="M3">
-        <v>12.37</v>
+        <v>13.86</v>
       </c>
       <c r="N3">
-        <v>11.77</v>
+        <v>11.83</v>
       </c>
       <c r="O3">
         <v>62</v>
       </c>
       <c r="Q3">
-        <v>9742.299999999999</v>
+        <v>9741.24</v>
       </c>
       <c r="R3">
-        <v>9832.389999999999</v>
+        <v>9823</v>
       </c>
       <c r="S3">
-        <v>9846.98</v>
+        <v>9845.959999999999</v>
       </c>
       <c r="T3">
-        <v>9743.629999999999</v>
+        <v>9745.83</v>
       </c>
       <c r="U3">
-        <v>0.07000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="V3" t="s">
         <v>80</v>
@@ -1273,31 +1246,31 @@
         <v>2</v>
       </c>
       <c r="Z3">
-        <v>42.25</v>
+        <v>47.9</v>
       </c>
       <c r="AA3">
-        <v>-38.4</v>
+        <v>-34.15</v>
       </c>
       <c r="AB3">
-        <v>-28.56</v>
+        <v>-29.68</v>
       </c>
       <c r="AC3">
-        <v>-9.83</v>
+        <v>-4.47</v>
       </c>
       <c r="AD3">
-        <v>34.41</v>
+        <v>58.03</v>
       </c>
       <c r="AE3">
-        <v>24.43</v>
+        <v>37.3</v>
       </c>
       <c r="AF3">
-        <v>93.42</v>
+        <v>94.59</v>
       </c>
       <c r="AH3">
-        <v>10004.45</v>
+        <v>9978.129999999999</v>
       </c>
       <c r="AI3">
-        <v>9660.32</v>
+        <v>9667.860000000001</v>
       </c>
       <c r="AJ3">
         <v>9955.58</v>
@@ -1306,7 +1279,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>35.67</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1320,10 +1293,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11644.8</v>
+        <v>11597.7</v>
       </c>
       <c r="E4">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1332,43 +1305,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-7.87</v>
+        <v>-8.24</v>
       </c>
       <c r="I4">
-        <v>12.68</v>
+        <v>12.22</v>
       </c>
       <c r="J4">
-        <v>-2.32</v>
+        <v>-2.57</v>
       </c>
       <c r="K4">
-        <v>-4.73</v>
+        <v>-4.72</v>
       </c>
       <c r="L4">
-        <v>4.03</v>
+        <v>4.64</v>
       </c>
       <c r="M4">
-        <v>-4.29</v>
+        <v>-3.86</v>
       </c>
       <c r="N4">
-        <v>10.65</v>
+        <v>10.58</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q4">
-        <v>11767.52</v>
+        <v>11706.22</v>
       </c>
       <c r="R4">
-        <v>11998.73</v>
+        <v>11968.74</v>
       </c>
       <c r="S4">
-        <v>11871.83</v>
+        <v>11871.92</v>
       </c>
       <c r="T4">
-        <v>11675.95</v>
+        <v>11672.15</v>
       </c>
       <c r="U4">
-        <v>-0.27</v>
+        <v>-0.64</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1383,16 +1356,16 @@
         <v>2</v>
       </c>
       <c r="Z4">
-        <v>32.05</v>
+        <v>30.15</v>
       </c>
       <c r="AA4">
-        <v>-44.55</v>
+        <v>-62.9</v>
       </c>
       <c r="AB4">
-        <v>15.34</v>
+        <v>-0.31</v>
       </c>
       <c r="AC4">
-        <v>-59.89</v>
+        <v>-62.59</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1401,22 +1374,22 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>110.39</v>
+        <v>106.79</v>
       </c>
       <c r="AH4">
-        <v>12323.84</v>
+        <v>12325.76</v>
       </c>
       <c r="AI4">
-        <v>11673.62</v>
+        <v>11611.73</v>
       </c>
       <c r="AJ4">
-        <v>11977.93</v>
+        <v>11946.85</v>
       </c>
       <c r="AK4" t="s">
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>32.47</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1430,10 +1403,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38140.8</v>
+        <v>38067.85</v>
       </c>
       <c r="E5">
-        <v>0.3</v>
+        <v>-0.19</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1442,43 +1415,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-8.17</v>
+        <v>-8.35</v>
       </c>
       <c r="I5">
-        <v>15.23</v>
+        <v>15.01</v>
       </c>
       <c r="J5">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="K5">
-        <v>-1.78</v>
+        <v>-1.57</v>
       </c>
       <c r="L5">
-        <v>-5.47</v>
+        <v>-4.08</v>
       </c>
       <c r="M5">
-        <v>12.32</v>
+        <v>13.02</v>
       </c>
       <c r="N5">
-        <v>12.75</v>
+        <v>12.64</v>
       </c>
       <c r="O5">
         <v>56</v>
       </c>
       <c r="Q5">
-        <v>37985.64</v>
+        <v>37998.48</v>
       </c>
       <c r="R5">
-        <v>38333.29</v>
+        <v>38299.19</v>
       </c>
       <c r="S5">
-        <v>38856.06</v>
+        <v>38824.67</v>
       </c>
       <c r="T5">
-        <v>37484.52</v>
+        <v>37493.92</v>
       </c>
       <c r="U5">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="s">
         <v>80</v>
@@ -1493,31 +1466,31 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>41.16</v>
+        <v>39.43</v>
       </c>
       <c r="AA5">
-        <v>-266.5</v>
+        <v>-253.47</v>
       </c>
       <c r="AB5">
-        <v>-269.6</v>
+        <v>-266.37</v>
       </c>
       <c r="AC5">
-        <v>3.09</v>
+        <v>12.9</v>
       </c>
       <c r="AD5">
-        <v>56.44</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="AE5">
-        <v>27.3</v>
+        <v>54.93</v>
       </c>
       <c r="AF5">
-        <v>347.13</v>
+        <v>334.69</v>
       </c>
       <c r="AH5">
-        <v>38966.11</v>
+        <v>38910.63</v>
       </c>
       <c r="AI5">
-        <v>37700.47</v>
+        <v>37687.75</v>
       </c>
       <c r="AJ5">
         <v>38783.5</v>
@@ -1526,7 +1499,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>23.77</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1540,10 +1513,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>45955.65</v>
+        <v>45892.75</v>
       </c>
       <c r="E6">
-        <v>-0.62</v>
+        <v>-0.14</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1552,22 +1525,22 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-19.52</v>
+        <v>-19.63</v>
       </c>
       <c r="I6">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="J6">
-        <v>-2.29</v>
+        <v>-1.97</v>
       </c>
       <c r="K6">
-        <v>-6.94</v>
+        <v>-7.04</v>
       </c>
       <c r="L6">
-        <v>-4.86</v>
+        <v>-4.59</v>
       </c>
       <c r="M6">
-        <v>-18.21</v>
+        <v>-17.48</v>
       </c>
       <c r="N6">
         <v>2.7</v>
@@ -1576,19 +1549,19 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>46298.78</v>
+        <v>46114.33</v>
       </c>
       <c r="R6">
-        <v>47676.03</v>
+        <v>47498.91</v>
       </c>
       <c r="S6">
-        <v>48573.74</v>
+        <v>48503.21</v>
       </c>
       <c r="T6">
-        <v>50606.78</v>
+        <v>50560.03</v>
       </c>
       <c r="U6">
-        <v>-9.19</v>
+        <v>-9.23</v>
       </c>
       <c r="V6" t="s">
         <v>80</v>
@@ -1603,40 +1576,40 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>28.7</v>
+        <v>28.27</v>
       </c>
       <c r="AA6">
-        <v>-725.47</v>
+        <v>-755.15</v>
       </c>
       <c r="AB6">
-        <v>-554.3</v>
+        <v>-594.47</v>
       </c>
       <c r="AC6">
-        <v>-171.17</v>
+        <v>-160.68</v>
       </c>
       <c r="AD6">
-        <v>29.64</v>
+        <v>26.04</v>
       </c>
       <c r="AE6">
-        <v>20.61</v>
+        <v>25.58</v>
       </c>
       <c r="AF6">
-        <v>564.66</v>
+        <v>548</v>
       </c>
       <c r="AH6">
-        <v>49771.9</v>
+        <v>49567.37</v>
       </c>
       <c r="AI6">
-        <v>45580.16</v>
+        <v>45430.44</v>
       </c>
       <c r="AJ6">
-        <v>47766.9</v>
+        <v>47612.83</v>
       </c>
       <c r="AK6" t="s">
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>60.89</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1650,10 +1623,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25923.05</v>
+        <v>26051</v>
       </c>
       <c r="E7">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1662,43 +1635,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-8.92</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="I7">
-        <v>10.21</v>
+        <v>10.75</v>
       </c>
       <c r="J7">
-        <v>-1.36</v>
+        <v>-0.9</v>
       </c>
       <c r="K7">
-        <v>-3.43</v>
+        <v>-3.02</v>
       </c>
       <c r="L7">
-        <v>3.46</v>
+        <v>5.02</v>
       </c>
       <c r="M7">
-        <v>-0.11</v>
+        <v>1.6</v>
       </c>
       <c r="N7">
-        <v>7.41</v>
+        <v>7.59</v>
       </c>
       <c r="O7">
         <v>50</v>
       </c>
       <c r="Q7">
-        <v>26064.03</v>
+        <v>26016.93</v>
       </c>
       <c r="R7">
-        <v>26227.55</v>
+        <v>26206.8</v>
       </c>
       <c r="S7">
-        <v>26555.21</v>
+        <v>26540.82</v>
       </c>
       <c r="T7">
-        <v>26642.75</v>
+        <v>26636.02</v>
       </c>
       <c r="U7">
-        <v>-2.7</v>
+        <v>-2.2</v>
       </c>
       <c r="V7" t="s">
         <v>80</v>
@@ -1713,31 +1686,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>38.15</v>
+        <v>42.83</v>
       </c>
       <c r="AA7">
-        <v>-144.49</v>
+        <v>-141.16</v>
       </c>
       <c r="AB7">
-        <v>-113.15</v>
+        <v>-118.75</v>
       </c>
       <c r="AC7">
-        <v>-31.34</v>
+        <v>-22.41</v>
       </c>
       <c r="AD7">
-        <v>15.01</v>
+        <v>29.06</v>
       </c>
       <c r="AE7">
-        <v>35.04</v>
+        <v>25.4</v>
       </c>
       <c r="AF7">
-        <v>271.85</v>
+        <v>270.36</v>
       </c>
       <c r="AH7">
-        <v>26602.28</v>
+        <v>26571.76</v>
       </c>
       <c r="AI7">
-        <v>25852.82</v>
+        <v>25841.84</v>
       </c>
       <c r="AJ7">
         <v>26568.68</v>
@@ -1746,7 +1719,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>26.8</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1760,10 +1733,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>30838.85</v>
+        <v>30695.1</v>
       </c>
       <c r="E8">
-        <v>-0.85</v>
+        <v>-0.47</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1772,43 +1745,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-21.9</v>
+        <v>-22.27</v>
       </c>
       <c r="I8">
-        <v>19.67</v>
+        <v>19.11</v>
       </c>
       <c r="J8">
-        <v>2.04</v>
+        <v>-1.88</v>
       </c>
       <c r="K8">
-        <v>-1.8</v>
+        <v>-1.63</v>
       </c>
       <c r="L8">
-        <v>6.3</v>
+        <v>7.12</v>
       </c>
       <c r="M8">
-        <v>-14.49</v>
+        <v>-13.51</v>
       </c>
       <c r="N8">
-        <v>-2.44</v>
+        <v>-2.82</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>31182.32</v>
+        <v>31065</v>
       </c>
       <c r="R8">
-        <v>31008.82</v>
+        <v>30966.19</v>
       </c>
       <c r="S8">
-        <v>29723.1</v>
+        <v>29790.39</v>
       </c>
       <c r="T8">
-        <v>32218.11</v>
+        <v>32188.19</v>
       </c>
       <c r="U8">
-        <v>-4.28</v>
+        <v>-4.64</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1823,34 +1796,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>52.09</v>
+        <v>50.42</v>
       </c>
       <c r="AA8">
-        <v>250.68</v>
+        <v>213.28</v>
       </c>
       <c r="AB8">
-        <v>308.81</v>
+        <v>289.7</v>
       </c>
       <c r="AC8">
-        <v>-58.13</v>
+        <v>-76.42</v>
       </c>
       <c r="AD8">
-        <v>56.37</v>
+        <v>37.03</v>
       </c>
       <c r="AE8">
-        <v>63.15</v>
+        <v>53.4</v>
       </c>
       <c r="AF8">
-        <v>634.2</v>
+        <v>632.22</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>32024.23</v>
+        <v>31957.64</v>
       </c>
       <c r="AI8">
-        <v>29993.41</v>
+        <v>29974.73</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1859,7 +1832,7 @@
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>19.91</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1873,10 +1846,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16271.8</v>
+        <v>16221.4</v>
       </c>
       <c r="E9">
-        <v>0.02</v>
+        <v>-0.31</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1885,28 +1858,28 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-2.34</v>
+        <v>-2.65</v>
       </c>
       <c r="I9">
-        <v>3.89</v>
+        <v>3.56</v>
       </c>
       <c r="J9">
-        <v>-1.73</v>
+        <v>-2.04</v>
       </c>
       <c r="K9">
-        <v>-1.93</v>
+        <v>-2.22</v>
       </c>
       <c r="N9">
-        <v>18.27</v>
+        <v>16.45</v>
       </c>
       <c r="Q9">
-        <v>16417.01</v>
+        <v>16349.6</v>
       </c>
       <c r="R9">
-        <v>16533.04</v>
+        <v>16510.99</v>
       </c>
       <c r="S9">
-        <v>16235.32</v>
+        <v>16241.25</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1918,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>40.26</v>
+        <v>37.61</v>
       </c>
       <c r="AA9">
-        <v>33.6</v>
+        <v>12.83</v>
       </c>
       <c r="AB9">
-        <v>87.98999999999999</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="AC9">
-        <v>-54.38</v>
+        <v>-60.12</v>
       </c>
       <c r="AD9">
         <v>0.25</v>
       </c>
       <c r="AE9">
-        <v>12.01</v>
+        <v>4.59</v>
       </c>
       <c r="AF9">
-        <v>139.42</v>
+        <v>135.3</v>
       </c>
       <c r="AH9">
-        <v>16750.46</v>
+        <v>16760.28</v>
       </c>
       <c r="AI9">
-        <v>16315.62</v>
+        <v>16261.7</v>
       </c>
       <c r="AJ9">
-        <v>16247.63</v>
+        <v>16636.88</v>
       </c>
       <c r="AK9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL9">
-        <v>28.46</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1965,10 +1938,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9204.200000000001</v>
+        <v>9197.799999999999</v>
       </c>
       <c r="E10">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1977,43 +1950,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-5.75</v>
+        <v>-5.82</v>
       </c>
       <c r="I10">
-        <v>7.51</v>
+        <v>7.44</v>
       </c>
       <c r="J10">
-        <v>-0.36</v>
+        <v>-0.49</v>
       </c>
       <c r="K10">
-        <v>-2.63</v>
+        <v>-2.7</v>
       </c>
       <c r="L10">
-        <v>0.24</v>
+        <v>1.21</v>
       </c>
       <c r="M10">
-        <v>2.62</v>
+        <v>3.29</v>
       </c>
       <c r="N10">
-        <v>13.76</v>
+        <v>13.72</v>
       </c>
       <c r="O10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q10">
-        <v>9209.52</v>
+        <v>9200.540000000001</v>
       </c>
       <c r="R10">
-        <v>9334.6</v>
+        <v>9319.280000000001</v>
       </c>
       <c r="S10">
-        <v>9373.299999999999</v>
+        <v>9368.049999999999</v>
       </c>
       <c r="T10">
-        <v>9347.309999999999</v>
+        <v>9345.290000000001</v>
       </c>
       <c r="U10">
-        <v>-1.53</v>
+        <v>-1.58</v>
       </c>
       <c r="V10" t="s">
         <v>80</v>
@@ -2028,31 +2001,31 @@
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>37.21</v>
+        <v>36.7</v>
       </c>
       <c r="AA10">
-        <v>-50.96</v>
+        <v>-52.8</v>
       </c>
       <c r="AB10">
-        <v>-33.19</v>
+        <v>-37.11</v>
       </c>
       <c r="AC10">
-        <v>-17.77</v>
+        <v>-15.69</v>
       </c>
       <c r="AD10">
-        <v>20.41</v>
+        <v>18.91</v>
       </c>
       <c r="AE10">
-        <v>14.23</v>
+        <v>17.83</v>
       </c>
       <c r="AF10">
-        <v>79.37</v>
+        <v>77.61</v>
       </c>
       <c r="AH10">
-        <v>9524.16</v>
+        <v>9500.48</v>
       </c>
       <c r="AI10">
-        <v>9145.040000000001</v>
+        <v>9138.08</v>
       </c>
       <c r="AJ10">
         <v>9408.6</v>
@@ -2061,7 +2034,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>43.64</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2075,10 +2048,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1560.75</v>
+        <v>1565.45</v>
       </c>
       <c r="E11">
-        <v>1.74</v>
+        <v>0.3</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2087,43 +2060,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-4.4</v>
+        <v>-4.11</v>
       </c>
       <c r="I11">
-        <v>24.53</v>
+        <v>24.9</v>
       </c>
       <c r="J11">
-        <v>-2.25</v>
+        <v>-2.34</v>
       </c>
       <c r="K11">
-        <v>-0.91</v>
+        <v>0.13</v>
       </c>
       <c r="L11">
-        <v>3.88</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-3.3</v>
+        <v>-2.55</v>
       </c>
       <c r="N11">
-        <v>-0.98</v>
+        <v>-1.18</v>
       </c>
       <c r="O11">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q11">
-        <v>1563.31</v>
+        <v>1555.82</v>
       </c>
       <c r="R11">
-        <v>1583.36</v>
+        <v>1583.89</v>
       </c>
       <c r="S11">
-        <v>1546.92</v>
+        <v>1548.03</v>
       </c>
       <c r="T11">
-        <v>1447.77</v>
+        <v>1448.2</v>
       </c>
       <c r="U11">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2138,31 +2111,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>47.51</v>
+        <v>48.68</v>
       </c>
       <c r="AA11">
-        <v>4.31</v>
+        <v>3.14</v>
       </c>
       <c r="AB11">
-        <v>13.42</v>
+        <v>11.36</v>
       </c>
       <c r="AC11">
-        <v>-9.109999999999999</v>
+        <v>-8.23</v>
       </c>
       <c r="AD11">
-        <v>11.35</v>
+        <v>20.5</v>
       </c>
       <c r="AE11">
-        <v>9</v>
+        <v>11.24</v>
       </c>
       <c r="AF11">
-        <v>32.05</v>
+        <v>30.8</v>
       </c>
       <c r="AH11">
-        <v>1634.83</v>
+        <v>1634.34</v>
       </c>
       <c r="AI11">
-        <v>1531.9</v>
+        <v>1533.44</v>
       </c>
       <c r="AJ11">
         <v>1523.72</v>
@@ -2171,7 +2144,7 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>45.27</v>
+        <v>44.62</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2185,10 +2158,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13176.05</v>
+        <v>13317.45</v>
       </c>
       <c r="E12">
-        <v>0.14</v>
+        <v>1.07</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2197,43 +2170,43 @@
         <v>9154.799999999999</v>
       </c>
       <c r="H12">
-        <v>-3.95</v>
+        <v>-2.92</v>
       </c>
       <c r="I12">
-        <v>43.93</v>
+        <v>45.47</v>
       </c>
       <c r="J12">
-        <v>-1.86</v>
+        <v>-1.54</v>
       </c>
       <c r="K12">
-        <v>-0.61</v>
+        <v>1.32</v>
       </c>
       <c r="L12">
-        <v>-0.34</v>
+        <v>3.13</v>
       </c>
       <c r="M12">
-        <v>41.98</v>
+        <v>44.59</v>
       </c>
       <c r="N12">
-        <v>18.17</v>
+        <v>18.35</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13248.5</v>
+        <v>13206.92</v>
       </c>
       <c r="R12">
-        <v>13195.05</v>
+        <v>13201.43</v>
       </c>
       <c r="S12">
-        <v>12837.72</v>
+        <v>12855.16</v>
       </c>
       <c r="T12">
-        <v>12119.17</v>
+        <v>12132.81</v>
       </c>
       <c r="U12">
-        <v>8.720000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2248,31 +2221,31 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>52.73</v>
+        <v>57.58</v>
       </c>
       <c r="AA12">
-        <v>109.88</v>
+        <v>109.07</v>
       </c>
       <c r="AB12">
-        <v>133.89</v>
+        <v>128.93</v>
       </c>
       <c r="AC12">
-        <v>-24.02</v>
+        <v>-19.86</v>
       </c>
       <c r="AD12">
-        <v>1.19</v>
+        <v>10.97</v>
       </c>
       <c r="AE12">
-        <v>9.279999999999999</v>
+        <v>4.05</v>
       </c>
       <c r="AF12">
-        <v>208.44</v>
+        <v>210.53</v>
       </c>
       <c r="AH12">
-        <v>13536.48</v>
+        <v>13547.2</v>
       </c>
       <c r="AI12">
-        <v>12853.62</v>
+        <v>12855.67</v>
       </c>
       <c r="AJ12">
         <v>12921.88</v>
@@ -2281,7 +2254,7 @@
         <v>82</v>
       </c>
       <c r="AL12">
-        <v>26.15</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2295,10 +2268,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9706.65</v>
+        <v>9710.15</v>
       </c>
       <c r="E13">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2307,43 +2280,43 @@
         <v>9202.450000000001</v>
       </c>
       <c r="H13">
-        <v>-9.84</v>
+        <v>-9.81</v>
       </c>
       <c r="I13">
-        <v>5.48</v>
+        <v>5.52</v>
       </c>
       <c r="J13">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="K13">
-        <v>-2.46</v>
+        <v>-2.29</v>
       </c>
       <c r="L13">
-        <v>-3.71</v>
+        <v>-3.3</v>
       </c>
       <c r="M13">
-        <v>4.28</v>
+        <v>5.29</v>
       </c>
       <c r="N13">
-        <v>21.14</v>
+        <v>21.29</v>
       </c>
       <c r="O13">
         <v>32</v>
       </c>
       <c r="Q13">
-        <v>9691.15</v>
+        <v>9695.33</v>
       </c>
       <c r="R13">
-        <v>9780.76</v>
+        <v>9770.15</v>
       </c>
       <c r="S13">
-        <v>9878.309999999999</v>
+        <v>9873.43</v>
       </c>
       <c r="T13">
-        <v>10033.89</v>
+        <v>10032.66</v>
       </c>
       <c r="U13">
-        <v>-3.26</v>
+        <v>-3.21</v>
       </c>
       <c r="V13" t="s">
         <v>80</v>
@@ -2358,31 +2331,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>38.08</v>
+        <v>38.62</v>
       </c>
       <c r="AA13">
-        <v>-63.2</v>
+        <v>-60.39</v>
       </c>
       <c r="AB13">
-        <v>-59.12</v>
+        <v>-59.38</v>
       </c>
       <c r="AC13">
-        <v>-4.08</v>
+        <v>-1.02</v>
       </c>
       <c r="AD13">
-        <v>36.72</v>
+        <v>62.79</v>
       </c>
       <c r="AE13">
-        <v>21.67</v>
+        <v>40.57</v>
       </c>
       <c r="AF13">
-        <v>89.76000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AH13">
-        <v>9937.73</v>
+        <v>9915.049999999999</v>
       </c>
       <c r="AI13">
-        <v>9623.790000000001</v>
+        <v>9625.26</v>
       </c>
       <c r="AJ13">
         <v>9905.1</v>
@@ -2391,7 +2364,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>39.64</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2405,10 +2378,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8552.6</v>
+        <v>8514.85</v>
       </c>
       <c r="E14">
-        <v>0.48</v>
+        <v>-0.44</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2417,43 +2390,43 @@
         <v>6756.05</v>
       </c>
       <c r="H14">
-        <v>-13.43</v>
+        <v>-13.82</v>
       </c>
       <c r="I14">
-        <v>26.59</v>
+        <v>26.03</v>
       </c>
       <c r="J14">
-        <v>-0.41</v>
+        <v>-1.04</v>
       </c>
       <c r="K14">
-        <v>0.13</v>
+        <v>-2.46</v>
       </c>
       <c r="L14">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="M14">
-        <v>24.86</v>
+        <v>25.61</v>
       </c>
       <c r="N14">
-        <v>29.36</v>
+        <v>29.33</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8556.780000000001</v>
+        <v>8538.889999999999</v>
       </c>
       <c r="R14">
-        <v>8638.59</v>
+        <v>8625.02</v>
       </c>
       <c r="S14">
-        <v>8504.17</v>
+        <v>8501.74</v>
       </c>
       <c r="T14">
-        <v>8599.190000000001</v>
+        <v>8600.25</v>
       </c>
       <c r="U14">
-        <v>-0.54</v>
+        <v>-0.99</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2468,31 +2441,31 @@
         <v>1</v>
       </c>
       <c r="Z14">
-        <v>48.6</v>
+        <v>45.98</v>
       </c>
       <c r="AA14">
-        <v>7.89</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>29.43</v>
+        <v>23.96</v>
       </c>
       <c r="AC14">
-        <v>-21.54</v>
+        <v>-21.9</v>
       </c>
       <c r="AD14">
-        <v>9.44</v>
+        <v>12.29</v>
       </c>
       <c r="AE14">
-        <v>10.42</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AF14">
-        <v>127.29</v>
+        <v>124.55</v>
       </c>
       <c r="AH14">
-        <v>8816.6</v>
+        <v>8796.92</v>
       </c>
       <c r="AI14">
-        <v>8460.58</v>
+        <v>8453.120000000001</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
@@ -2501,7 +2474,7 @@
         <v>82</v>
       </c>
       <c r="AL14">
-        <v>18.55</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2515,10 +2488,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26658.65</v>
+        <v>26478.1</v>
       </c>
       <c r="E15">
-        <v>-0.46</v>
+        <v>-0.68</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2527,43 +2500,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-1.94</v>
+        <v>-2.61</v>
       </c>
       <c r="I15">
-        <v>24.26</v>
+        <v>23.42</v>
       </c>
       <c r="J15">
-        <v>-0.71</v>
+        <v>-1.9</v>
       </c>
       <c r="K15">
-        <v>0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="L15">
-        <v>9.94</v>
+        <v>9.65</v>
       </c>
       <c r="M15">
-        <v>21.23</v>
+        <v>21.41</v>
       </c>
       <c r="N15">
-        <v>12.98</v>
+        <v>12.84</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26882.06</v>
+        <v>26779.31</v>
       </c>
       <c r="R15">
-        <v>26617.62</v>
+        <v>26614.43</v>
       </c>
       <c r="S15">
-        <v>26165.23</v>
+        <v>26195.4</v>
       </c>
       <c r="T15">
-        <v>23786.8</v>
+        <v>23805.76</v>
       </c>
       <c r="U15">
-        <v>12.07</v>
+        <v>11.23</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2578,34 +2551,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>54.7</v>
+        <v>49.59</v>
       </c>
       <c r="AA15">
-        <v>196.84</v>
+        <v>163.98</v>
       </c>
       <c r="AB15">
-        <v>212</v>
+        <v>202.4</v>
       </c>
       <c r="AC15">
-        <v>-15.16</v>
+        <v>-38.41</v>
       </c>
       <c r="AD15">
-        <v>19.6</v>
+        <v>10.48</v>
       </c>
       <c r="AE15">
-        <v>48.77</v>
+        <v>27</v>
       </c>
       <c r="AF15">
-        <v>300.22</v>
+        <v>295.46</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27087.48</v>
+        <v>27087.31</v>
       </c>
       <c r="AI15">
-        <v>26147.75</v>
+        <v>26141.55</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
@@ -2614,7 +2587,7 @@
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>34.87</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2628,10 +2601,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>916.15</v>
+        <v>907.9</v>
       </c>
       <c r="E16">
-        <v>2.58</v>
+        <v>-0.9</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2640,43 +2613,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-5.42</v>
+        <v>-6.27</v>
       </c>
       <c r="I16">
-        <v>40.7</v>
+        <v>39.43</v>
       </c>
       <c r="J16">
-        <v>0.72</v>
+        <v>-0.1</v>
       </c>
       <c r="K16">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="L16">
-        <v>19.15</v>
+        <v>21.18</v>
       </c>
       <c r="M16">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="N16">
-        <v>17</v>
+        <v>16.09</v>
       </c>
       <c r="O16">
         <v>81</v>
       </c>
       <c r="Q16">
-        <v>902.72</v>
+        <v>902.53</v>
       </c>
       <c r="R16">
-        <v>902.04</v>
+        <v>903.14</v>
       </c>
       <c r="S16">
-        <v>899.89</v>
+        <v>901.52</v>
       </c>
       <c r="T16">
-        <v>831.64</v>
+        <v>831.47</v>
       </c>
       <c r="U16">
-        <v>10.16</v>
+        <v>9.19</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2691,31 +2664,31 @@
         <v>3</v>
       </c>
       <c r="Z16">
-        <v>57.61</v>
+        <v>53.17</v>
       </c>
       <c r="AA16">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="AB16">
-        <v>4.21</v>
+        <v>3.99</v>
       </c>
       <c r="AC16">
-        <v>-1.1</v>
+        <v>-0.85</v>
       </c>
       <c r="AD16">
-        <v>30.66</v>
+        <v>49.07</v>
       </c>
       <c r="AE16">
-        <v>22.53</v>
+        <v>30.19</v>
       </c>
       <c r="AF16">
-        <v>17.8</v>
+        <v>17.86</v>
       </c>
       <c r="AH16">
-        <v>921.98</v>
+        <v>921.71</v>
       </c>
       <c r="AI16">
-        <v>882.11</v>
+        <v>884.5700000000001</v>
       </c>
       <c r="AJ16">
         <v>869.13</v>
@@ -2724,7 +2697,7 @@
         <v>82</v>
       </c>
       <c r="AL16">
-        <v>26.54</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2738,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30575.05</v>
+        <v>30575.55</v>
       </c>
       <c r="E17">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2756,37 +2729,37 @@
         <v>7.8</v>
       </c>
       <c r="J17">
-        <v>-0.57</v>
+        <v>-1.05</v>
       </c>
       <c r="K17">
-        <v>-3.12</v>
+        <v>-2.95</v>
       </c>
       <c r="L17">
-        <v>3.58</v>
+        <v>4.36</v>
       </c>
       <c r="M17">
-        <v>-5.37</v>
+        <v>-4.11</v>
       </c>
       <c r="N17">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="O17">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q17">
-        <v>30718.66</v>
+        <v>30653.73</v>
       </c>
       <c r="R17">
-        <v>30925.07</v>
+        <v>30890.59</v>
       </c>
       <c r="S17">
-        <v>31094.26</v>
+        <v>31091.82</v>
       </c>
       <c r="T17">
-        <v>31641.11</v>
+        <v>31626.43</v>
       </c>
       <c r="U17">
-        <v>-3.37</v>
+        <v>-3.32</v>
       </c>
       <c r="V17" t="s">
         <v>80</v>
@@ -2801,31 +2774,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>38</v>
+        <v>38.02</v>
       </c>
       <c r="AA17">
-        <v>-131.3</v>
+        <v>-139.6</v>
       </c>
       <c r="AB17">
-        <v>-87.37</v>
+        <v>-97.81999999999999</v>
       </c>
       <c r="AC17">
-        <v>-43.93</v>
+        <v>-41.78</v>
       </c>
       <c r="AD17">
-        <v>23.47</v>
+        <v>12.78</v>
       </c>
       <c r="AE17">
-        <v>41.55</v>
+        <v>25.04</v>
       </c>
       <c r="AF17">
-        <v>255.41</v>
+        <v>249.88</v>
       </c>
       <c r="AH17">
-        <v>31370.2</v>
+        <v>31331.61</v>
       </c>
       <c r="AI17">
-        <v>30479.94</v>
+        <v>30449.57</v>
       </c>
       <c r="AJ17">
         <v>31236.31</v>
@@ -2834,7 +2807,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>31.54</v>
+        <v>29.39</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2848,10 +2821,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16552.2</v>
+        <v>16408.05</v>
       </c>
       <c r="E18">
-        <v>-0.46</v>
+        <v>-0.87</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2860,28 +2833,28 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-2.3</v>
+        <v>-3.15</v>
       </c>
       <c r="I18">
-        <v>7.46</v>
+        <v>6.52</v>
       </c>
       <c r="J18">
-        <v>-0.93</v>
+        <v>-2.32</v>
       </c>
       <c r="K18">
-        <v>-0.9399999999999999</v>
+        <v>-1.85</v>
       </c>
       <c r="N18">
-        <v>31.57</v>
+        <v>26.25</v>
       </c>
       <c r="Q18">
-        <v>16718.23</v>
+        <v>16640.14</v>
       </c>
       <c r="R18">
-        <v>16596.07</v>
+        <v>16581.03</v>
       </c>
       <c r="S18">
-        <v>16490.14</v>
+        <v>16499.03</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2893,31 +2866,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>49.15</v>
+        <v>43.46</v>
       </c>
       <c r="AA18">
-        <v>56.86</v>
+        <v>34.69</v>
       </c>
       <c r="AB18">
-        <v>62.36</v>
+        <v>56.83</v>
       </c>
       <c r="AC18">
-        <v>-5.5</v>
+        <v>-22.13</v>
       </c>
       <c r="AD18">
-        <v>26.71</v>
+        <v>14.51</v>
       </c>
       <c r="AE18">
-        <v>53.58</v>
+        <v>32.13</v>
       </c>
       <c r="AF18">
-        <v>178.16</v>
+        <v>177.77</v>
       </c>
       <c r="AH18">
-        <v>16872.74</v>
+        <v>16864.5</v>
       </c>
       <c r="AI18">
-        <v>16319.41</v>
+        <v>16297.57</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2926,7 +2899,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>28.81</v>
+        <v>26.27</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2940,10 +2913,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9670.9</v>
+        <v>9708.85</v>
       </c>
       <c r="E19">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="F19">
         <v>9968.25</v>
@@ -2952,28 +2925,28 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-2.98</v>
+        <v>-2.6</v>
       </c>
       <c r="I19">
-        <v>7.51</v>
+        <v>7.93</v>
       </c>
       <c r="J19">
-        <v>-1.34</v>
+        <v>-0.44</v>
       </c>
       <c r="K19">
-        <v>2.92</v>
+        <v>0.44</v>
       </c>
       <c r="N19">
-        <v>37.53</v>
+        <v>39.36</v>
       </c>
       <c r="Q19">
-        <v>9681.99</v>
+        <v>9673.43</v>
       </c>
       <c r="R19">
-        <v>9746.809999999999</v>
+        <v>9745.65</v>
       </c>
       <c r="S19">
-        <v>9542.889999999999</v>
+        <v>9549.15</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2985,31 +2958,31 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>51.06</v>
+        <v>53.41</v>
       </c>
       <c r="AA19">
-        <v>47.98</v>
+        <v>44.52</v>
       </c>
       <c r="AB19">
-        <v>78.64</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="AC19">
-        <v>-30.67</v>
+        <v>-27.3</v>
       </c>
       <c r="AD19">
-        <v>4.58</v>
+        <v>12.54</v>
       </c>
       <c r="AE19">
-        <v>1.53</v>
+        <v>5.71</v>
       </c>
       <c r="AF19">
-        <v>134.34</v>
+        <v>135.77</v>
       </c>
       <c r="AH19">
-        <v>9928.379999999999</v>
+        <v>9927.91</v>
       </c>
       <c r="AI19">
-        <v>9565.24</v>
+        <v>9563.379999999999</v>
       </c>
       <c r="AJ19">
         <v>9466.209999999999</v>
@@ -3018,7 +2991,7 @@
         <v>82</v>
       </c>
       <c r="AL19">
-        <v>23.53</v>
+        <v>21.55</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3032,10 +3005,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11164.65</v>
+        <v>11187.65</v>
       </c>
       <c r="E20">
-        <v>-0.13</v>
+        <v>0.21</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3044,28 +3017,28 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="I20">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="J20">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="K20">
-        <v>-0.46</v>
+        <v>-1.03</v>
       </c>
       <c r="N20">
-        <v>6.23</v>
+        <v>7.11</v>
       </c>
       <c r="Q20">
-        <v>11131.46</v>
+        <v>11155.45</v>
       </c>
       <c r="R20">
-        <v>11193.02</v>
+        <v>11186.79</v>
       </c>
       <c r="S20">
-        <v>11176.81</v>
+        <v>11177.7</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3077,31 +3050,31 @@
         <v>1</v>
       </c>
       <c r="Z20">
-        <v>49.04</v>
+        <v>51.29</v>
       </c>
       <c r="AA20">
-        <v>-16.53</v>
+        <v>-12.89</v>
       </c>
       <c r="AB20">
-        <v>-11.02</v>
+        <v>-11.4</v>
       </c>
       <c r="AC20">
-        <v>-5.5</v>
+        <v>-1.49</v>
       </c>
       <c r="AD20">
-        <v>76.97</v>
+        <v>90.27</v>
       </c>
       <c r="AE20">
-        <v>55.07</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="AF20">
-        <v>118.28</v>
+        <v>115.99</v>
       </c>
       <c r="AH20">
-        <v>11331.38</v>
+        <v>11313.27</v>
       </c>
       <c r="AI20">
-        <v>11054.65</v>
+        <v>11060.31</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3110,7 +3083,7 @@
         <v>82</v>
       </c>
       <c r="AL20">
-        <v>18.54</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3124,10 +3097,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27747.85</v>
+        <v>27824.5</v>
       </c>
       <c r="E21">
-        <v>0.51</v>
+        <v>0.28</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3136,43 +3109,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-4.93</v>
+        <v>-4.67</v>
       </c>
       <c r="I21">
-        <v>14.92</v>
+        <v>15.24</v>
       </c>
       <c r="J21">
-        <v>-0.04</v>
+        <v>0.31</v>
       </c>
       <c r="K21">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="L21">
-        <v>5.51</v>
+        <v>6.52</v>
       </c>
       <c r="M21">
-        <v>5.34</v>
+        <v>6.71</v>
       </c>
       <c r="N21">
-        <v>7.84</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O21">
         <v>68</v>
       </c>
       <c r="Q21">
-        <v>27771.94</v>
+        <v>27789.4</v>
       </c>
       <c r="R21">
-        <v>27509.44</v>
+        <v>27531.05</v>
       </c>
       <c r="S21">
-        <v>27882.45</v>
+        <v>27872.49</v>
       </c>
       <c r="T21">
-        <v>27633.57</v>
+        <v>27631.94</v>
       </c>
       <c r="U21">
-        <v>0.41</v>
+        <v>0.7</v>
       </c>
       <c r="V21" t="s">
         <v>80</v>
@@ -3187,31 +3160,31 @@
         <v>2</v>
       </c>
       <c r="Z21">
-        <v>52.15</v>
+        <v>54.09</v>
       </c>
       <c r="AA21">
-        <v>-4.69</v>
+        <v>8.49</v>
       </c>
       <c r="AB21">
-        <v>-54.39</v>
+        <v>-41.81</v>
       </c>
       <c r="AC21">
-        <v>49.7</v>
+        <v>50.31</v>
       </c>
       <c r="AD21">
-        <v>59.89</v>
+        <v>62.05</v>
       </c>
       <c r="AE21">
-        <v>73.02</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="AF21">
-        <v>314.79</v>
+        <v>306.48</v>
       </c>
       <c r="AH21">
-        <v>27950.05</v>
+        <v>27989.51</v>
       </c>
       <c r="AI21">
-        <v>27068.83</v>
+        <v>27072.59</v>
       </c>
       <c r="AJ21">
         <v>28265.67</v>
@@ -3220,7 +3193,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>34.75</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3361,7 +3334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3401,7 +3374,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3420,2033 +3393,2024 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>111</v>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8">
+        <v>-5.35</v>
+      </c>
+      <c r="D9" s="8">
+        <v>-4.82</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>-2.53</v>
+      </c>
+      <c r="D10" s="8">
+        <v>-1.54</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>116</v>
+      <c r="A11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8">
+        <v>-4.73</v>
+      </c>
+      <c r="D11" s="8">
+        <v>-4.72</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="8">
-        <v>-3.65</v>
+        <v>-1.78</v>
       </c>
       <c r="D12" s="8">
-        <v>-5.35</v>
+        <v>-1.57</v>
       </c>
       <c r="E12" s="9">
-        <v>-1.7</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="8">
-        <v>-1.73</v>
+        <v>-6.94</v>
       </c>
       <c r="D13" s="8">
-        <v>-2.53</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-0.8</v>
+        <v>-7.04</v>
+      </c>
+      <c r="E13" s="10">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="8">
-        <v>-4.14</v>
+        <v>-3.43</v>
       </c>
       <c r="D14" s="8">
-        <v>-4.73</v>
+        <v>-3.02</v>
       </c>
       <c r="E14" s="9">
-        <v>-0.59</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="8">
-        <v>-2.03</v>
+        <v>-1.8</v>
       </c>
       <c r="D15" s="8">
-        <v>-1.78</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0.25</v>
+        <v>-1.63</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="8">
-        <v>-6.64</v>
+        <v>-1.93</v>
       </c>
       <c r="D16" s="8">
-        <v>-6.94</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.3</v>
+        <v>-2.22</v>
+      </c>
+      <c r="E16" s="10">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="8">
-        <v>-3.84</v>
+        <v>-2.63</v>
       </c>
       <c r="D17" s="8">
-        <v>-3.43</v>
+        <v>-2.7</v>
       </c>
       <c r="E17" s="10">
-        <v>0.41</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="8">
-        <v>-1.12</v>
+        <v>-0.91</v>
       </c>
       <c r="D18" s="8">
-        <v>-1.8</v>
+        <v>0.13</v>
       </c>
       <c r="E18" s="9">
-        <v>-0.68</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="8">
-        <v>-1.37</v>
+        <v>-0.61</v>
       </c>
       <c r="D19" s="8">
-        <v>-1.93</v>
+        <v>1.32</v>
       </c>
       <c r="E19" s="9">
-        <v>-0.5600000000000001</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="8">
-        <v>-2.2</v>
+        <v>-2.46</v>
       </c>
       <c r="D20" s="8">
-        <v>-2.63</v>
+        <v>-2.29</v>
       </c>
       <c r="E20" s="9">
-        <v>-0.43</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="8">
-        <v>-4.15</v>
+        <v>0.13</v>
       </c>
       <c r="D21" s="8">
-        <v>-0.91</v>
+        <v>-2.46</v>
       </c>
       <c r="E21" s="10">
-        <v>3.24</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="8">
-        <v>0.96</v>
+        <v>0.36</v>
       </c>
       <c r="D22" s="8">
-        <v>-0.61</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.57</v>
+        <v>-0.33</v>
+      </c>
+      <c r="E22" s="10">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="8">
-        <v>-2.43</v>
+        <v>1.94</v>
       </c>
       <c r="D23" s="8">
-        <v>-2.46</v>
+        <v>2.37</v>
       </c>
       <c r="E23" s="9">
-        <v>-0.03</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="8">
-        <v>0.38</v>
+        <v>-3.12</v>
       </c>
       <c r="D24" s="8">
-        <v>0.13</v>
+        <v>-2.95</v>
       </c>
       <c r="E24" s="9">
-        <v>-0.25</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="8">
-        <v>0.6899999999999999</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D25" s="8">
-        <v>0.36</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.33</v>
+        <v>-1.85</v>
+      </c>
+      <c r="E25" s="10">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="8">
-        <v>0.22</v>
+        <v>2.92</v>
       </c>
       <c r="D26" s="8">
-        <v>1.94</v>
+        <v>0.44</v>
       </c>
       <c r="E26" s="10">
-        <v>1.72</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="8">
-        <v>-3.43</v>
+        <v>-0.46</v>
       </c>
       <c r="D27" s="8">
-        <v>-3.12</v>
+        <v>-1.03</v>
       </c>
       <c r="E27" s="10">
-        <v>0.31</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="8">
-        <v>-0.7</v>
+        <v>0.01</v>
       </c>
       <c r="D28" s="8">
-        <v>-0.9399999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="E28" s="9">
-        <v>-0.24</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="8">
-        <v>2.14</v>
+        <v>-3.62</v>
       </c>
       <c r="D29" s="8">
-        <v>2.92</v>
+        <v>-3.95</v>
       </c>
       <c r="E29" s="10">
-        <v>0.78</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="8">
-        <v>-0.42</v>
+        <v>-0.65</v>
       </c>
       <c r="D30" s="8">
-        <v>-0.46</v>
+        <v>-0.05</v>
       </c>
       <c r="E30" s="9">
-        <v>-0.04</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="8">
-        <v>-0.91</v>
+        <v>-2.32</v>
       </c>
       <c r="D31" s="8">
-        <v>0.01</v>
+        <v>-2.57</v>
       </c>
       <c r="E31" s="10">
-        <v>0.92</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="8">
-        <v>-3.51</v>
+        <v>0.1</v>
       </c>
       <c r="D32" s="8">
-        <v>-3.62</v>
+        <v>0.17</v>
       </c>
       <c r="E32" s="9">
-        <v>-0.11</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="8">
-        <v>-1.21</v>
+        <v>-2.29</v>
       </c>
       <c r="D33" s="8">
-        <v>-0.65</v>
-      </c>
-      <c r="E33" s="10">
-        <v>0.5600000000000001</v>
+        <v>-1.97</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.32</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="8">
-        <v>-2.21</v>
+        <v>-1.36</v>
       </c>
       <c r="D34" s="8">
-        <v>-2.32</v>
+        <v>-0.9</v>
       </c>
       <c r="E34" s="9">
-        <v>-0.11</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="8">
-        <v>-0.19</v>
+        <v>2.04</v>
       </c>
       <c r="D35" s="8">
-        <v>0.1</v>
+        <v>-1.88</v>
       </c>
       <c r="E35" s="10">
-        <v>0.29</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="8">
-        <v>-2.14</v>
+        <v>-1.73</v>
       </c>
       <c r="D36" s="8">
-        <v>-2.29</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-0.15</v>
+        <v>-2.04</v>
+      </c>
+      <c r="E36" s="10">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="8">
-        <v>-2.17</v>
+        <v>-0.36</v>
       </c>
       <c r="D37" s="8">
-        <v>-1.36</v>
+        <v>-0.49</v>
       </c>
       <c r="E37" s="10">
-        <v>0.8100000000000001</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="8">
-        <v>2.59</v>
+        <v>-2.25</v>
       </c>
       <c r="D38" s="8">
-        <v>2.04</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.55</v>
+        <v>-2.34</v>
+      </c>
+      <c r="E38" s="10">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="8">
-        <v>-1.8</v>
+        <v>-1.86</v>
       </c>
       <c r="D39" s="8">
-        <v>-1.73</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.07000000000000001</v>
+        <v>-1.54</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.32</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="8">
-        <v>-0.83</v>
+        <v>0.05</v>
       </c>
       <c r="D40" s="8">
-        <v>-0.36</v>
-      </c>
-      <c r="E40" s="10">
-        <v>0.47</v>
+        <v>0.22</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.17</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="8">
-        <v>-4.77</v>
+        <v>-0.41</v>
       </c>
       <c r="D41" s="8">
-        <v>-2.25</v>
+        <v>-1.04</v>
       </c>
       <c r="E41" s="10">
-        <v>2.52</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="8">
-        <v>-2.84</v>
+        <v>-0.71</v>
       </c>
       <c r="D42" s="8">
-        <v>-1.86</v>
+        <v>-1.9</v>
       </c>
       <c r="E42" s="10">
-        <v>0.98</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="8">
-        <v>-0.33</v>
+        <v>0.72</v>
       </c>
       <c r="D43" s="8">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E43" s="10">
-        <v>0.38</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="8">
-        <v>-1.82</v>
+        <v>-0.57</v>
       </c>
       <c r="D44" s="8">
-        <v>-0.41</v>
+        <v>-1.05</v>
       </c>
       <c r="E44" s="10">
-        <v>1.41</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="8">
-        <v>0.58</v>
+        <v>-0.93</v>
       </c>
       <c r="D45" s="8">
-        <v>-0.71</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.29</v>
+        <v>-2.32</v>
+      </c>
+      <c r="E45" s="10">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="8">
-        <v>-1.87</v>
+        <v>-1.34</v>
       </c>
       <c r="D46" s="8">
-        <v>0.72</v>
-      </c>
-      <c r="E46" s="10">
-        <v>2.59</v>
+        <v>-0.44</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.9</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="8">
-        <v>-1.21</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D47" s="8">
-        <v>-0.57</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0.64</v>
+        <v>1.08</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.14</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="D48" s="8">
-        <v>-0.93</v>
+        <v>0.31</v>
       </c>
       <c r="E48" s="9">
-        <v>-1.19</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" s="8">
-        <v>-1.27</v>
+        <v>9.94</v>
       </c>
       <c r="D49" s="8">
-        <v>-1.34</v>
+        <v>10.04</v>
       </c>
       <c r="E49" s="9">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="8">
-        <v>0.26</v>
+        <v>12.37</v>
       </c>
       <c r="D50" s="8">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0.68</v>
+        <v>13.86</v>
+      </c>
+      <c r="E50" s="9">
+        <v>1.49</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="8">
-        <v>-0.45</v>
+        <v>-4.29</v>
       </c>
       <c r="D51" s="8">
-        <v>-0.04</v>
-      </c>
-      <c r="E51" s="10">
-        <v>0.41</v>
+        <v>-3.86</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.43</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="8">
-        <v>10.06</v>
+        <v>12.32</v>
       </c>
       <c r="D52" s="8">
-        <v>9.94</v>
+        <v>13.02</v>
       </c>
       <c r="E52" s="9">
-        <v>-0.12</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="8">
-        <v>10.9</v>
+        <v>-18.21</v>
       </c>
       <c r="D53" s="8">
-        <v>12.37</v>
-      </c>
-      <c r="E53" s="10">
-        <v>1.47</v>
+        <v>-17.48</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.73</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="8">
-        <v>-4.17</v>
+        <v>-0.11</v>
       </c>
       <c r="D54" s="8">
-        <v>-4.29</v>
+        <v>1.6</v>
       </c>
       <c r="E54" s="9">
-        <v>-0.12</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="8">
-        <v>10.25</v>
+        <v>-14.49</v>
       </c>
       <c r="D55" s="8">
-        <v>12.32</v>
-      </c>
-      <c r="E55" s="10">
-        <v>2.07</v>
+        <v>-13.51</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.98</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="8">
-        <v>-16.96</v>
+        <v>2.62</v>
       </c>
       <c r="D56" s="8">
-        <v>-18.21</v>
+        <v>3.29</v>
       </c>
       <c r="E56" s="9">
-        <v>-1.25</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="8">
-        <v>-1.88</v>
+        <v>-3.3</v>
       </c>
       <c r="D57" s="8">
-        <v>-0.11</v>
-      </c>
-      <c r="E57" s="10">
-        <v>1.77</v>
+        <v>-2.55</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0.75</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="8">
-        <v>-14.27</v>
+        <v>41.98</v>
       </c>
       <c r="D58" s="8">
-        <v>-14.49</v>
+        <v>44.59</v>
       </c>
       <c r="E58" s="9">
-        <v>-0.22</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="8">
-        <v>1.12</v>
+        <v>4.28</v>
       </c>
       <c r="D59" s="8">
-        <v>2.62</v>
-      </c>
-      <c r="E59" s="10">
-        <v>1.5</v>
+        <v>5.29</v>
+      </c>
+      <c r="E59" s="9">
+        <v>1.01</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="8">
-        <v>-5.67</v>
+        <v>24.86</v>
       </c>
       <c r="D60" s="8">
-        <v>-3.3</v>
-      </c>
-      <c r="E60" s="10">
-        <v>2.37</v>
+        <v>25.61</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0.75</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="8">
-        <v>39.43</v>
+        <v>21.23</v>
       </c>
       <c r="D61" s="8">
-        <v>41.98</v>
-      </c>
-      <c r="E61" s="10">
-        <v>2.55</v>
+        <v>21.41</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.18</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="8">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="D62" s="8">
-        <v>4.28</v>
-      </c>
-      <c r="E62" s="10">
-        <v>1.86</v>
+        <v>2.88</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0.63</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="8">
-        <v>21.94</v>
+        <v>-5.37</v>
       </c>
       <c r="D63" s="8">
-        <v>24.86</v>
-      </c>
-      <c r="E63" s="10">
-        <v>2.92</v>
+        <v>-4.11</v>
+      </c>
+      <c r="E63" s="9">
+        <v>1.26</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="8">
-        <v>19.76</v>
+        <v>5.34</v>
       </c>
       <c r="D64" s="8">
-        <v>21.23</v>
-      </c>
-      <c r="E64" s="10">
-        <v>1.47</v>
+        <v>6.71</v>
+      </c>
+      <c r="E64" s="9">
+        <v>1.37</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" s="8">
-        <v>-2.54</v>
+        <v>6.39</v>
       </c>
       <c r="D65" s="8">
-        <v>2.25</v>
-      </c>
-      <c r="E65" s="10">
-        <v>4.79</v>
+        <v>7.9</v>
+      </c>
+      <c r="E65" s="9">
+        <v>1.51</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" s="8">
-        <v>-6.57</v>
+        <v>-3.49</v>
       </c>
       <c r="D66" s="8">
-        <v>-5.37</v>
-      </c>
-      <c r="E66" s="10">
-        <v>1.2</v>
+        <v>-1.39</v>
+      </c>
+      <c r="E66" s="9">
+        <v>2.1</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="8">
-        <v>3.41</v>
+        <v>4.03</v>
       </c>
       <c r="D67" s="8">
-        <v>5.34</v>
-      </c>
-      <c r="E67" s="10">
-        <v>1.93</v>
+        <v>4.64</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0.61</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="8">
-        <v>7.03</v>
+        <v>-5.47</v>
       </c>
       <c r="D68" s="8">
-        <v>6.39</v>
+        <v>-4.08</v>
       </c>
       <c r="E68" s="9">
-        <v>-0.64</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="8">
-        <v>-4.17</v>
+        <v>-4.86</v>
       </c>
       <c r="D69" s="8">
-        <v>-3.49</v>
-      </c>
-      <c r="E69" s="10">
-        <v>0.68</v>
+        <v>-4.59</v>
+      </c>
+      <c r="E69" s="9">
+        <v>0.27</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="8">
-        <v>4.63</v>
+        <v>3.46</v>
       </c>
       <c r="D70" s="8">
-        <v>4.03</v>
+        <v>5.02</v>
       </c>
       <c r="E70" s="9">
-        <v>-0.6</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="8">
-        <v>-5.98</v>
+        <v>6.3</v>
       </c>
       <c r="D71" s="8">
-        <v>-5.47</v>
-      </c>
-      <c r="E71" s="10">
-        <v>0.51</v>
+        <v>7.12</v>
+      </c>
+      <c r="E71" s="9">
+        <v>0.82</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="8">
-        <v>-4.1</v>
+        <v>0.24</v>
       </c>
       <c r="D72" s="8">
-        <v>-4.86</v>
+        <v>1.21</v>
       </c>
       <c r="E72" s="9">
-        <v>-0.76</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="8">
-        <v>3.12</v>
+        <v>3.88</v>
       </c>
       <c r="D73" s="8">
-        <v>3.46</v>
-      </c>
-      <c r="E73" s="10">
-        <v>0.34</v>
+        <v>6</v>
+      </c>
+      <c r="E73" s="9">
+        <v>2.12</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="8">
-        <v>6.15</v>
+        <v>-0.34</v>
       </c>
       <c r="D74" s="8">
-        <v>6.3</v>
-      </c>
-      <c r="E74" s="10">
-        <v>0.15</v>
+        <v>3.13</v>
+      </c>
+      <c r="E74" s="9">
+        <v>3.47</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="8">
-        <v>0.03</v>
+        <v>-3.71</v>
       </c>
       <c r="D75" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="E75" s="10">
-        <v>0.21</v>
+        <v>-3.3</v>
+      </c>
+      <c r="E75" s="9">
+        <v>0.41</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="8">
-        <v>5.66</v>
+        <v>3.55</v>
       </c>
       <c r="D76" s="8">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="E76" s="9">
-        <v>-1.78</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="8">
-        <v>-2.07</v>
+        <v>9.94</v>
       </c>
       <c r="D77" s="8">
-        <v>-0.34</v>
+        <v>9.65</v>
       </c>
       <c r="E77" s="10">
-        <v>1.73</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="8">
-        <v>-4.21</v>
+        <v>19.15</v>
       </c>
       <c r="D78" s="8">
-        <v>-3.71</v>
-      </c>
-      <c r="E78" s="10">
-        <v>0.5</v>
+        <v>21.18</v>
+      </c>
+      <c r="E78" s="9">
+        <v>2.03</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="8">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="D79" s="8">
-        <v>3.55</v>
+        <v>4.36</v>
       </c>
       <c r="E79" s="9">
-        <v>-0.01</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="8">
-        <v>10.76</v>
+        <v>5.51</v>
       </c>
       <c r="D80" s="8">
-        <v>9.94</v>
+        <v>6.52</v>
       </c>
       <c r="E80" s="9">
-        <v>-0.82</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C81" s="8">
-        <v>16.81</v>
+        <v>-6.11</v>
       </c>
       <c r="D81" s="8">
-        <v>19.15</v>
+        <v>-6.53</v>
       </c>
       <c r="E81" s="10">
-        <v>2.34</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C82" s="8">
-        <v>3.17</v>
+        <v>-7.17</v>
       </c>
       <c r="D82" s="8">
-        <v>3.58</v>
-      </c>
-      <c r="E82" s="10">
-        <v>0.41</v>
+        <v>-6.66</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0.51</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C83" s="8">
-        <v>5.21</v>
+        <v>-7.87</v>
       </c>
       <c r="D83" s="8">
-        <v>5.51</v>
+        <v>-8.24</v>
       </c>
       <c r="E83" s="10">
-        <v>0.3</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="8">
-        <v>-5.62</v>
+        <v>-8.17</v>
       </c>
       <c r="D84" s="8">
-        <v>-6.11</v>
-      </c>
-      <c r="E84" s="9">
-        <v>-0.49</v>
+        <v>-8.35</v>
+      </c>
+      <c r="E84" s="10">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="8">
-        <v>-7.11</v>
+        <v>-19.52</v>
       </c>
       <c r="D85" s="8">
-        <v>-7.17</v>
-      </c>
-      <c r="E85" s="9">
-        <v>-0.06</v>
+        <v>-19.63</v>
+      </c>
+      <c r="E85" s="10">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="8">
-        <v>-7.4</v>
+        <v>-8.92</v>
       </c>
       <c r="D86" s="8">
-        <v>-7.87</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="E86" s="9">
-        <v>-0.47</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="8">
-        <v>-8.44</v>
+        <v>-21.9</v>
       </c>
       <c r="D87" s="8">
-        <v>-8.17</v>
+        <v>-22.27</v>
       </c>
       <c r="E87" s="10">
-        <v>0.27</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="8">
-        <v>-19.02</v>
+        <v>-2.34</v>
       </c>
       <c r="D88" s="8">
-        <v>-19.52</v>
-      </c>
-      <c r="E88" s="9">
-        <v>-0.5</v>
+        <v>-2.65</v>
+      </c>
+      <c r="E88" s="10">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="8">
-        <v>-9.31</v>
+        <v>-5.75</v>
       </c>
       <c r="D89" s="8">
-        <v>-8.92</v>
+        <v>-5.82</v>
       </c>
       <c r="E89" s="10">
-        <v>0.39</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="8">
-        <v>-21.23</v>
+        <v>-4.4</v>
       </c>
       <c r="D90" s="8">
-        <v>-21.9</v>
+        <v>-4.11</v>
       </c>
       <c r="E90" s="9">
-        <v>-0.67</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="8">
-        <v>-2.36</v>
+        <v>-3.95</v>
       </c>
       <c r="D91" s="8">
-        <v>-2.34</v>
-      </c>
-      <c r="E91" s="10">
-        <v>0.02</v>
+        <v>-2.92</v>
+      </c>
+      <c r="E91" s="9">
+        <v>1.03</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="8">
-        <v>-5.67</v>
+        <v>-9.84</v>
       </c>
       <c r="D92" s="8">
-        <v>-5.75</v>
+        <v>-9.81</v>
       </c>
       <c r="E92" s="9">
-        <v>-0.08</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="8">
-        <v>-6.03</v>
+        <v>-13.43</v>
       </c>
       <c r="D93" s="8">
-        <v>-4.4</v>
+        <v>-13.82</v>
       </c>
       <c r="E93" s="10">
-        <v>1.63</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="8">
-        <v>-4.09</v>
+        <v>-1.94</v>
       </c>
       <c r="D94" s="8">
-        <v>-3.95</v>
+        <v>-2.61</v>
       </c>
       <c r="E94" s="10">
-        <v>0.14</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="8">
-        <v>-9.94</v>
+        <v>-5.42</v>
       </c>
       <c r="D95" s="8">
-        <v>-9.84</v>
+        <v>-6.27</v>
       </c>
       <c r="E95" s="10">
-        <v>0.1</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="8">
-        <v>-13.85</v>
+        <v>-2.3</v>
       </c>
       <c r="D96" s="8">
-        <v>-13.43</v>
+        <v>-3.15</v>
       </c>
       <c r="E96" s="10">
-        <v>0.42</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="8">
-        <v>-1.49</v>
+        <v>-2.98</v>
       </c>
       <c r="D97" s="8">
-        <v>-1.94</v>
+        <v>-2.6</v>
       </c>
       <c r="E97" s="9">
-        <v>-0.45</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="8">
-        <v>-7.79</v>
+        <v>-1.8</v>
       </c>
       <c r="D98" s="8">
-        <v>-5.42</v>
-      </c>
-      <c r="E98" s="10">
-        <v>2.37</v>
+        <v>-1.6</v>
+      </c>
+      <c r="E98" s="9">
+        <v>0.2</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="8">
-        <v>-10.49</v>
+        <v>-4.93</v>
       </c>
       <c r="D99" s="8">
-        <v>-10.34</v>
-      </c>
-      <c r="E99" s="10">
-        <v>0.15</v>
+        <v>-4.67</v>
+      </c>
+      <c r="E99" s="9">
+        <v>0.26</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="7" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C100" s="8">
-        <v>-1.84</v>
+        <v>27837.4</v>
       </c>
       <c r="D100" s="8">
-        <v>-2.3</v>
-      </c>
-      <c r="E100" s="9">
-        <v>-0.46</v>
+        <v>27710.9</v>
+      </c>
+      <c r="E100" s="10">
+        <v>-126.5</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="7" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C101" s="8">
-        <v>-3.48</v>
+        <v>9750.6</v>
       </c>
       <c r="D101" s="8">
-        <v>-2.98</v>
-      </c>
-      <c r="E101" s="10">
-        <v>0.5</v>
+        <v>9803.85</v>
+      </c>
+      <c r="E101" s="9">
+        <v>53.25</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="7" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C102" s="8">
-        <v>-1.67</v>
+        <v>11644.8</v>
       </c>
       <c r="D102" s="8">
-        <v>-1.8</v>
-      </c>
-      <c r="E102" s="9">
-        <v>-0.13</v>
+        <v>11597.7</v>
+      </c>
+      <c r="E102" s="10">
+        <v>-47.1</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="7" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C103" s="8">
-        <v>-5.42</v>
+        <v>38140.8</v>
       </c>
       <c r="D103" s="8">
-        <v>-4.93</v>
+        <v>38067.85</v>
       </c>
       <c r="E103" s="10">
-        <v>0.49</v>
+        <v>-72.95</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C104" s="8">
-        <v>27981.95</v>
+        <v>45955.65</v>
       </c>
       <c r="D104" s="8">
-        <v>27837.4</v>
-      </c>
-      <c r="E104" s="9">
-        <v>-144.55</v>
+        <v>45892.75</v>
+      </c>
+      <c r="E104" s="10">
+        <v>-62.9</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="8">
-        <v>9756.9</v>
+        <v>25923.05</v>
       </c>
       <c r="D105" s="8">
-        <v>9750.6</v>
+        <v>26051</v>
       </c>
       <c r="E105" s="9">
-        <v>-6.3</v>
+        <v>127.95</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="8">
-        <v>11703.6</v>
+        <v>30838.85</v>
       </c>
       <c r="D106" s="8">
-        <v>11644.8</v>
-      </c>
-      <c r="E106" s="9">
-        <v>-58.8</v>
+        <v>30695.1</v>
+      </c>
+      <c r="E106" s="10">
+        <v>-143.75</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="8">
-        <v>38028.4</v>
+        <v>16271.8</v>
       </c>
       <c r="D107" s="8">
-        <v>38140.8</v>
+        <v>16221.4</v>
       </c>
       <c r="E107" s="10">
-        <v>112.4</v>
+        <v>-50.4</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="8">
-        <v>46240.55</v>
+        <v>9204.200000000001</v>
       </c>
       <c r="D108" s="8">
-        <v>45955.65</v>
-      </c>
-      <c r="E108" s="9">
-        <v>-284.9</v>
+        <v>9197.799999999999</v>
+      </c>
+      <c r="E108" s="10">
+        <v>-6.4</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="8">
-        <v>25813.05</v>
+        <v>1560.75</v>
       </c>
       <c r="D109" s="8">
-        <v>25923.05</v>
-      </c>
-      <c r="E109" s="10">
-        <v>110</v>
+        <v>1565.45</v>
+      </c>
+      <c r="E109" s="9">
+        <v>4.7</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="8">
-        <v>31102.9</v>
+        <v>13176.05</v>
       </c>
       <c r="D110" s="8">
-        <v>30838.85</v>
+        <v>13317.45</v>
       </c>
       <c r="E110" s="9">
-        <v>-264.05</v>
+        <v>141.4</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="8">
-        <v>16269.35</v>
+        <v>9706.65</v>
       </c>
       <c r="D111" s="8">
-        <v>16271.8</v>
-      </c>
-      <c r="E111" s="10">
-        <v>2.45</v>
+        <v>9710.15</v>
+      </c>
+      <c r="E111" s="9">
+        <v>3.5</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="8">
-        <v>9212.049999999999</v>
+        <v>8552.6</v>
       </c>
       <c r="D112" s="8">
-        <v>9204.200000000001</v>
-      </c>
-      <c r="E112" s="9">
-        <v>-7.85</v>
+        <v>8514.85</v>
+      </c>
+      <c r="E112" s="10">
+        <v>-37.75</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="8">
-        <v>1534.1</v>
+        <v>26658.65</v>
       </c>
       <c r="D113" s="8">
-        <v>1560.75</v>
+        <v>26478.1</v>
       </c>
       <c r="E113" s="10">
-        <v>26.65</v>
+        <v>-180.55</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="8">
-        <v>13157.35</v>
+        <v>916.15</v>
       </c>
       <c r="D114" s="8">
-        <v>13176.05</v>
+        <v>907.9</v>
       </c>
       <c r="E114" s="10">
-        <v>18.7</v>
+        <v>-8.25</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="8">
-        <v>9695.950000000001</v>
+        <v>30575.05</v>
       </c>
       <c r="D115" s="8">
-        <v>9706.65</v>
-      </c>
-      <c r="E115" s="10">
-        <v>10.7</v>
+        <v>30575.55</v>
+      </c>
+      <c r="E115" s="9">
+        <v>0.5</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="8">
-        <v>8511.700000000001</v>
+        <v>16552.2</v>
       </c>
       <c r="D116" s="8">
-        <v>8552.6</v>
+        <v>16408.05</v>
       </c>
       <c r="E116" s="10">
-        <v>40.9</v>
+        <v>-144.15</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="8">
-        <v>26780.7</v>
+        <v>9670.9</v>
       </c>
       <c r="D117" s="8">
-        <v>26658.65</v>
+        <v>9708.85</v>
       </c>
       <c r="E117" s="9">
-        <v>-122.05</v>
+        <v>37.95</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="8">
-        <v>893.15</v>
+        <v>11164.65</v>
       </c>
       <c r="D118" s="8">
-        <v>916.15</v>
-      </c>
-      <c r="E118" s="10">
+        <v>11187.65</v>
+      </c>
+      <c r="E118" s="9">
         <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="8">
-        <v>30525.25</v>
+        <v>27747.85</v>
       </c>
       <c r="D119" s="8">
-        <v>30575.05</v>
-      </c>
-      <c r="E119" s="10">
-        <v>49.8</v>
+        <v>27824.5</v>
+      </c>
+      <c r="E119" s="9">
+        <v>76.65000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C120" s="8">
-        <v>16629.1</v>
+        <v>26</v>
       </c>
       <c r="D120" s="8">
-        <v>16552.2</v>
-      </c>
-      <c r="E120" s="9">
-        <v>-76.90000000000001</v>
+        <v>19</v>
+      </c>
+      <c r="E120" s="10">
+        <v>-7</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C121" s="8">
-        <v>9621.35</v>
+        <v>44</v>
       </c>
       <c r="D121" s="8">
-        <v>9670.9</v>
+        <v>38</v>
       </c>
       <c r="E121" s="10">
-        <v>49.55</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C122" s="8">
-        <v>11178.85</v>
+        <v>38</v>
       </c>
       <c r="D122" s="8">
-        <v>11164.65</v>
+        <v>44</v>
       </c>
       <c r="E122" s="9">
-        <v>-14.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C123" s="8">
-        <v>27606.8</v>
+        <v>19</v>
       </c>
       <c r="D123" s="8">
-        <v>27747.85</v>
-      </c>
-      <c r="E123" s="10">
-        <v>141.05</v>
+        <v>26</v>
+      </c>
+      <c r="E123" s="9">
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5454,464 +5418,345 @@
         <v>38</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C124" s="8">
-        <v>81</v>
+        <v>34.09</v>
       </c>
       <c r="D124" s="8">
-        <v>74</v>
-      </c>
-      <c r="E124" s="9">
-        <v>-7</v>
+        <v>32.37</v>
+      </c>
+      <c r="E124" s="10">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C125" s="8">
-        <v>38</v>
+        <v>42.25</v>
       </c>
       <c r="D125" s="8">
-        <v>26</v>
+        <v>47.9</v>
       </c>
       <c r="E125" s="9">
-        <v>-12</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C126" s="8">
-        <v>44</v>
+        <v>32.05</v>
       </c>
       <c r="D126" s="8">
-        <v>50</v>
+        <v>30.15</v>
       </c>
       <c r="E126" s="10">
-        <v>6</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C127" s="8">
-        <v>50</v>
+        <v>41.16</v>
       </c>
       <c r="D127" s="8">
-        <v>44</v>
-      </c>
-      <c r="E127" s="9">
-        <v>-6</v>
+        <v>39.43</v>
+      </c>
+      <c r="E127" s="10">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C128" s="8">
-        <v>32</v>
+        <v>28.7</v>
       </c>
       <c r="D128" s="8">
-        <v>38</v>
+        <v>28.27</v>
       </c>
       <c r="E128" s="10">
-        <v>6</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C129" s="8">
-        <v>26</v>
+        <v>38.15</v>
       </c>
       <c r="D129" s="8">
-        <v>32</v>
-      </c>
-      <c r="E129" s="10">
-        <v>6</v>
+        <v>42.83</v>
+      </c>
+      <c r="E129" s="9">
+        <v>4.68</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C130" s="8">
-        <v>74</v>
+        <v>52.09</v>
       </c>
       <c r="D130" s="8">
-        <v>81</v>
+        <v>50.42</v>
       </c>
       <c r="E130" s="10">
-        <v>7</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C131" s="8">
-        <v>36.13</v>
+        <v>40.26</v>
       </c>
       <c r="D131" s="8">
-        <v>34.09</v>
-      </c>
-      <c r="E131" s="9">
-        <v>-2.04</v>
+        <v>37.61</v>
+      </c>
+      <c r="E131" s="10">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="8">
-        <v>42.76</v>
+        <v>37.21</v>
       </c>
       <c r="D132" s="8">
-        <v>42.25</v>
-      </c>
-      <c r="E132" s="9">
+        <v>36.7</v>
+      </c>
+      <c r="E132" s="10">
         <v>-0.51</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="8">
-        <v>34.59</v>
+        <v>47.51</v>
       </c>
       <c r="D133" s="8">
-        <v>32.05</v>
+        <v>48.68</v>
       </c>
       <c r="E133" s="9">
-        <v>-2.54</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="8">
-        <v>37.23</v>
+        <v>52.73</v>
       </c>
       <c r="D134" s="8">
-        <v>41.16</v>
-      </c>
-      <c r="E134" s="10">
-        <v>3.93</v>
+        <v>57.58</v>
+      </c>
+      <c r="E134" s="9">
+        <v>4.85</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="8">
-        <v>30.69</v>
+        <v>38.08</v>
       </c>
       <c r="D135" s="8">
-        <v>28.7</v>
+        <v>38.62</v>
       </c>
       <c r="E135" s="9">
-        <v>-1.99</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="8">
-        <v>33.84</v>
+        <v>48.6</v>
       </c>
       <c r="D136" s="8">
-        <v>38.15</v>
+        <v>45.98</v>
       </c>
       <c r="E136" s="10">
-        <v>4.31</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="8">
-        <v>55.2</v>
+        <v>54.7</v>
       </c>
       <c r="D137" s="8">
-        <v>52.09</v>
-      </c>
-      <c r="E137" s="9">
-        <v>-3.11</v>
+        <v>49.59</v>
+      </c>
+      <c r="E137" s="10">
+        <v>-5.11</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="8">
-        <v>40.07</v>
+        <v>57.61</v>
       </c>
       <c r="D138" s="8">
-        <v>40.26</v>
+        <v>53.17</v>
       </c>
       <c r="E138" s="10">
-        <v>0.19</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="8">
-        <v>37.82</v>
+        <v>38</v>
       </c>
       <c r="D139" s="8">
-        <v>37.21</v>
+        <v>38.02</v>
       </c>
       <c r="E139" s="9">
-        <v>-0.61</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="8">
-        <v>40.33</v>
+        <v>49.15</v>
       </c>
       <c r="D140" s="8">
-        <v>47.51</v>
+        <v>43.46</v>
       </c>
       <c r="E140" s="10">
-        <v>7.18</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="8">
-        <v>52.05</v>
+        <v>51.06</v>
       </c>
       <c r="D141" s="8">
-        <v>52.73</v>
-      </c>
-      <c r="E141" s="10">
-        <v>0.68</v>
+        <v>53.41</v>
+      </c>
+      <c r="E141" s="9">
+        <v>2.35</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="8">
-        <v>36.48</v>
+        <v>49.04</v>
       </c>
       <c r="D142" s="8">
-        <v>38.08</v>
-      </c>
-      <c r="E142" s="10">
-        <v>1.6</v>
+        <v>51.29</v>
+      </c>
+      <c r="E142" s="9">
+        <v>2.25</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="8">
-        <v>45.47</v>
+        <v>52.15</v>
       </c>
       <c r="D143" s="8">
-        <v>48.6</v>
-      </c>
-      <c r="E143" s="10">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C144" s="8">
-        <v>58.48</v>
-      </c>
-      <c r="D144" s="8">
-        <v>54.7</v>
-      </c>
-      <c r="E144" s="9">
-        <v>-3.78</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C145" s="8">
-        <v>45.93</v>
-      </c>
-      <c r="D145" s="8">
-        <v>57.61</v>
-      </c>
-      <c r="E145" s="10">
-        <v>11.68</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C146" s="8">
-        <v>36.03</v>
-      </c>
-      <c r="D146" s="8">
-        <v>38</v>
-      </c>
-      <c r="E146" s="10">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C147" s="8">
-        <v>52.56</v>
-      </c>
-      <c r="D147" s="8">
-        <v>49.15</v>
-      </c>
-      <c r="E147" s="9">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C148" s="8">
-        <v>47.87</v>
-      </c>
-      <c r="D148" s="8">
-        <v>51.06</v>
-      </c>
-      <c r="E148" s="10">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C149" s="8">
-        <v>50.37</v>
-      </c>
-      <c r="D149" s="8">
-        <v>49.04</v>
-      </c>
-      <c r="E149" s="9">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C150" s="8">
-        <v>48.44</v>
-      </c>
-      <c r="D150" s="8">
-        <v>52.15</v>
-      </c>
-      <c r="E150" s="10">
-        <v>3.71</v>
+        <v>54.09</v>
+      </c>
+      <c r="E143" s="9">
+        <v>1.94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5935,28 +5780,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5970,16 +5815,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="13">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="E2" s="13">
         <v>40</v>
       </c>
       <c r="F2" s="13">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="G2" s="13">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
@@ -6090,10 +5935,10 @@
         <v>55</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>50</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>38</v>
@@ -6102,10 +5947,10 @@
         <v>49</v>
       </c>
       <c r="F1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>48</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>52</v>
@@ -6119,34 +5964,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.3753</v>
+        <v>0.3936</v>
       </c>
       <c r="B2" s="16">
-        <v>0.3157</v>
+        <v>0.2933</v>
       </c>
       <c r="C2" s="16">
-        <v>0.2936</v>
+        <v>0.2625</v>
       </c>
       <c r="D2" s="16">
-        <v>0.2242</v>
+        <v>0.2224</v>
       </c>
       <c r="E2" s="16">
-        <v>0.2114</v>
+        <v>0.2129</v>
       </c>
       <c r="F2" s="16">
-        <v>0.1827</v>
+        <v>0.1835</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1817</v>
+        <v>0.1645</v>
       </c>
       <c r="H2" s="16">
-        <v>0.17</v>
+        <v>0.1609</v>
       </c>
       <c r="I2" s="16">
-        <v>0.1376</v>
+        <v>0.1372</v>
       </c>
       <c r="J2" s="16">
-        <v>0.1298</v>
+        <v>0.1284</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6183,34 +6028,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.1275</v>
+        <v>0.1264</v>
       </c>
       <c r="B4" s="16">
-        <v>0.1177</v>
+        <v>0.1183</v>
       </c>
       <c r="C4" s="16">
-        <v>0.1065</v>
+        <v>0.1058</v>
       </c>
       <c r="D4" s="16">
-        <v>0.0784</v>
+        <v>0.0803</v>
       </c>
       <c r="E4" s="16">
-        <v>0.0741</v>
+        <v>0.0759</v>
       </c>
       <c r="F4" s="16">
-        <v>0.0623</v>
+        <v>0.0711</v>
       </c>
       <c r="G4" s="16">
-        <v>0.0474</v>
+        <v>0.047</v>
       </c>
       <c r="H4" s="16">
         <v>0.027</v>
       </c>
       <c r="I4" s="16">
-        <v>-0.0098</v>
+        <v>-0.0118</v>
       </c>
       <c r="J4" s="16">
-        <v>-0.0244</v>
+        <v>-0.0282</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="129">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,46 +289,85 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.6% → -1.9%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.6%</t>
+  </si>
+  <si>
+    <t>-1.9%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.0 → 51.3</t>
+    <t>49.6 → 54.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.0</t>
+    <t>49.6</t>
+  </si>
+  <si>
+    <t>54.6</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.6% → -2.2%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.6%</t>
+  </si>
+  <si>
+    <t>-2.2%</t>
+  </si>
+  <si>
+    <t>50.4 → 43.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>43.2</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>53.2 → 46.0</t>
+  </si>
+  <si>
+    <t>53.2</t>
+  </si>
+  <si>
+    <t>46.0</t>
+  </si>
+  <si>
+    <t>51.3 → 44.9</t>
   </si>
   <si>
     <t>51.3</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.9% → -2.6%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.9%</t>
-  </si>
-  <si>
-    <t>-2.6%</t>
-  </si>
-  <si>
-    <t>54.7 → 49.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.7</t>
-  </si>
-  <si>
-    <t>49.6</t>
+    <t>44.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -555,8 +594,8 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1073,10 +1112,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>27710.9</v>
+        <v>27698.75</v>
       </c>
       <c r="E2">
-        <v>-0.45</v>
+        <v>-0.04</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1085,43 +1124,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-6.53</v>
+        <v>-6.57</v>
       </c>
       <c r="I2">
-        <v>16.58</v>
+        <v>16.53</v>
       </c>
       <c r="J2">
-        <v>-3.95</v>
+        <v>-3.96</v>
       </c>
       <c r="K2">
-        <v>-4.82</v>
+        <v>-6.57</v>
       </c>
       <c r="L2">
-        <v>7.9</v>
+        <v>6.43</v>
       </c>
       <c r="M2">
-        <v>10.04</v>
+        <v>10.97</v>
       </c>
       <c r="N2">
-        <v>22.24</v>
+        <v>22.23</v>
       </c>
       <c r="O2">
         <v>74</v>
       </c>
       <c r="Q2">
-        <v>28172.56</v>
+        <v>27944.01</v>
       </c>
       <c r="R2">
-        <v>28959.49</v>
+        <v>28863.42</v>
       </c>
       <c r="S2">
-        <v>28043.61</v>
+        <v>28069.23</v>
       </c>
       <c r="T2">
-        <v>27134.69</v>
+        <v>27136.98</v>
       </c>
       <c r="U2">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1136,16 +1175,16 @@
         <v>3</v>
       </c>
       <c r="Z2">
-        <v>32.37</v>
+        <v>32.2</v>
       </c>
       <c r="AA2">
-        <v>-42.58</v>
+        <v>-103.45</v>
       </c>
       <c r="AB2">
-        <v>204.85</v>
+        <v>143.19</v>
       </c>
       <c r="AC2">
-        <v>-247.43</v>
+        <v>-246.64</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1154,22 +1193,22 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>388.5</v>
+        <v>377.43</v>
       </c>
       <c r="AH2">
-        <v>30048.74</v>
+        <v>30042.56</v>
       </c>
       <c r="AI2">
-        <v>27870.23</v>
+        <v>27684.28</v>
       </c>
       <c r="AJ2">
-        <v>28944.71</v>
+        <v>28801.09</v>
       </c>
       <c r="AK2" t="s">
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>48.77</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1183,55 +1222,55 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9803.85</v>
+        <v>9702.1</v>
       </c>
       <c r="E3">
-        <v>0.55</v>
+        <v>-1.04</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
       </c>
       <c r="G3">
-        <v>8571.799999999999</v>
+        <v>8693.700000000001</v>
       </c>
       <c r="H3">
-        <v>-6.66</v>
+        <v>-7.63</v>
       </c>
       <c r="I3">
-        <v>14.37</v>
+        <v>11.6</v>
       </c>
       <c r="J3">
-        <v>-0.05</v>
+        <v>0.12</v>
       </c>
       <c r="K3">
-        <v>-1.54</v>
+        <v>-2.9</v>
       </c>
       <c r="L3">
-        <v>-1.39</v>
+        <v>-2.72</v>
       </c>
       <c r="M3">
-        <v>13.86</v>
+        <v>13.19</v>
       </c>
       <c r="N3">
-        <v>11.83</v>
+        <v>11.62</v>
       </c>
       <c r="O3">
         <v>62</v>
       </c>
       <c r="Q3">
-        <v>9741.24</v>
+        <v>9743.530000000001</v>
       </c>
       <c r="R3">
-        <v>9823</v>
+        <v>9807.530000000001</v>
       </c>
       <c r="S3">
-        <v>9845.959999999999</v>
+        <v>9843.610000000001</v>
       </c>
       <c r="T3">
-        <v>9745.83</v>
+        <v>9747.65</v>
       </c>
       <c r="U3">
-        <v>0.6</v>
+        <v>-0.47</v>
       </c>
       <c r="V3" t="s">
         <v>80</v>
@@ -1243,34 +1282,34 @@
         <v>80</v>
       </c>
       <c r="Y3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>47.9</v>
+        <v>39.88</v>
       </c>
       <c r="AA3">
-        <v>-34.15</v>
+        <v>-38.56</v>
       </c>
       <c r="AB3">
-        <v>-29.68</v>
+        <v>-31.46</v>
       </c>
       <c r="AC3">
-        <v>-4.47</v>
+        <v>-7.1</v>
       </c>
       <c r="AD3">
-        <v>58.03</v>
+        <v>51.86</v>
       </c>
       <c r="AE3">
-        <v>37.3</v>
+        <v>48.1</v>
       </c>
       <c r="AF3">
-        <v>94.59</v>
+        <v>97.63</v>
       </c>
       <c r="AH3">
-        <v>9978.129999999999</v>
+        <v>9944.139999999999</v>
       </c>
       <c r="AI3">
-        <v>9667.860000000001</v>
+        <v>9670.92</v>
       </c>
       <c r="AJ3">
         <v>9955.58</v>
@@ -1279,7 +1318,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>34.41</v>
+        <v>34.53</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1293,10 +1332,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11597.7</v>
+        <v>11560.75</v>
       </c>
       <c r="E4">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1305,43 +1344,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-8.24</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="I4">
-        <v>12.22</v>
+        <v>11.87</v>
       </c>
       <c r="J4">
-        <v>-2.57</v>
+        <v>-2.05</v>
       </c>
       <c r="K4">
-        <v>-4.72</v>
+        <v>-5.22</v>
       </c>
       <c r="L4">
-        <v>4.64</v>
+        <v>3.72</v>
       </c>
       <c r="M4">
-        <v>-3.86</v>
+        <v>-4.13</v>
       </c>
       <c r="N4">
-        <v>10.58</v>
+        <v>10.41</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q4">
-        <v>11706.22</v>
+        <v>11657.83</v>
       </c>
       <c r="R4">
-        <v>11968.74</v>
+        <v>11935.31</v>
       </c>
       <c r="S4">
-        <v>11871.92</v>
+        <v>11873.31</v>
       </c>
       <c r="T4">
-        <v>11672.15</v>
+        <v>11668.01</v>
       </c>
       <c r="U4">
-        <v>-0.64</v>
+        <v>-0.92</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1356,16 +1395,16 @@
         <v>2</v>
       </c>
       <c r="Z4">
-        <v>30.15</v>
+        <v>28.71</v>
       </c>
       <c r="AA4">
-        <v>-62.9</v>
+        <v>-79.52</v>
       </c>
       <c r="AB4">
-        <v>-0.31</v>
+        <v>-16.15</v>
       </c>
       <c r="AC4">
-        <v>-62.59</v>
+        <v>-63.37</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1374,22 +1413,22 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>106.79</v>
+        <v>103.58</v>
       </c>
       <c r="AH4">
-        <v>12325.76</v>
+        <v>12314.11</v>
       </c>
       <c r="AI4">
-        <v>11611.73</v>
+        <v>11556.51</v>
       </c>
       <c r="AJ4">
-        <v>11946.85</v>
+        <v>11875.9</v>
       </c>
       <c r="AK4" t="s">
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>35.95</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1403,10 +1442,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>38067.85</v>
+        <v>37973.35</v>
       </c>
       <c r="E5">
-        <v>-0.19</v>
+        <v>-0.25</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1415,43 +1454,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-8.35</v>
+        <v>-8.58</v>
       </c>
       <c r="I5">
-        <v>15.01</v>
+        <v>14.73</v>
       </c>
       <c r="J5">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="K5">
-        <v>-1.57</v>
+        <v>-2</v>
       </c>
       <c r="L5">
-        <v>-4.08</v>
+        <v>-4.48</v>
       </c>
       <c r="M5">
-        <v>13.02</v>
+        <v>12.89</v>
       </c>
       <c r="N5">
-        <v>12.64</v>
+        <v>12.65</v>
       </c>
       <c r="O5">
         <v>56</v>
       </c>
       <c r="Q5">
-        <v>37998.48</v>
+        <v>38003.3</v>
       </c>
       <c r="R5">
-        <v>38299.19</v>
+        <v>38260.45</v>
       </c>
       <c r="S5">
-        <v>38824.67</v>
+        <v>38789.78</v>
       </c>
       <c r="T5">
-        <v>37493.92</v>
+        <v>37502.48</v>
       </c>
       <c r="U5">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="s">
         <v>80</v>
@@ -1466,31 +1505,31 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>39.43</v>
+        <v>37.25</v>
       </c>
       <c r="AA5">
-        <v>-253.47</v>
+        <v>-247.92</v>
       </c>
       <c r="AB5">
-        <v>-266.37</v>
+        <v>-262.68</v>
       </c>
       <c r="AC5">
-        <v>12.9</v>
+        <v>14.76</v>
       </c>
       <c r="AD5">
-        <v>85.23999999999999</v>
+        <v>85.23</v>
       </c>
       <c r="AE5">
-        <v>54.93</v>
+        <v>75.64</v>
       </c>
       <c r="AF5">
-        <v>334.69</v>
+        <v>335.55</v>
       </c>
       <c r="AH5">
-        <v>38910.63</v>
+        <v>38849.91</v>
       </c>
       <c r="AI5">
-        <v>37687.75</v>
+        <v>37670.99</v>
       </c>
       <c r="AJ5">
         <v>38783.5</v>
@@ -1499,7 +1538,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>21.08</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1513,10 +1552,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>45892.75</v>
+        <v>45592.15</v>
       </c>
       <c r="E6">
-        <v>-0.14</v>
+        <v>-0.66</v>
       </c>
       <c r="F6">
         <v>57104.05</v>
@@ -1525,43 +1564,43 @@
         <v>45538.65</v>
       </c>
       <c r="H6">
-        <v>-19.63</v>
+        <v>-20.16</v>
       </c>
       <c r="I6">
-        <v>0.78</v>
+        <v>0.12</v>
       </c>
       <c r="J6">
-        <v>-1.97</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K6">
-        <v>-7.04</v>
+        <v>-7.77</v>
       </c>
       <c r="L6">
-        <v>-4.59</v>
+        <v>-5.89</v>
       </c>
       <c r="M6">
-        <v>-17.48</v>
+        <v>-18.79</v>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>46114.33</v>
+        <v>46027.65</v>
       </c>
       <c r="R6">
-        <v>47498.91</v>
+        <v>47310.33</v>
       </c>
       <c r="S6">
-        <v>48503.21</v>
+        <v>48432.5</v>
       </c>
       <c r="T6">
-        <v>50560.03</v>
+        <v>50510.19</v>
       </c>
       <c r="U6">
-        <v>-9.23</v>
+        <v>-9.74</v>
       </c>
       <c r="V6" t="s">
         <v>80</v>
@@ -1576,40 +1615,40 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>28.27</v>
+        <v>26.23</v>
       </c>
       <c r="AA6">
-        <v>-755.15</v>
+        <v>-793.78</v>
       </c>
       <c r="AB6">
-        <v>-594.47</v>
+        <v>-634.33</v>
       </c>
       <c r="AC6">
-        <v>-160.68</v>
+        <v>-159.45</v>
       </c>
       <c r="AD6">
-        <v>26.04</v>
+        <v>18.71</v>
       </c>
       <c r="AE6">
-        <v>25.58</v>
+        <v>24.8</v>
       </c>
       <c r="AF6">
-        <v>548</v>
+        <v>532.12</v>
       </c>
       <c r="AH6">
-        <v>49567.37</v>
+        <v>49350.49</v>
       </c>
       <c r="AI6">
-        <v>45430.44</v>
+        <v>45270.18</v>
       </c>
       <c r="AJ6">
-        <v>47612.83</v>
+        <v>47325.42</v>
       </c>
       <c r="AK6" t="s">
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>63.24</v>
+        <v>65.72</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1623,10 +1662,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>26051</v>
+        <v>25935.6</v>
       </c>
       <c r="E7">
-        <v>0.49</v>
+        <v>-0.44</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1635,43 +1674,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-8.470000000000001</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="I7">
-        <v>10.75</v>
+        <v>10.26</v>
       </c>
       <c r="J7">
-        <v>-0.9</v>
+        <v>-1.36</v>
       </c>
       <c r="K7">
-        <v>-3.02</v>
+        <v>-2</v>
       </c>
       <c r="L7">
-        <v>5.02</v>
+        <v>3.11</v>
       </c>
       <c r="M7">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="N7">
-        <v>7.59</v>
+        <v>7.46</v>
       </c>
       <c r="O7">
         <v>50</v>
       </c>
       <c r="Q7">
-        <v>26016.93</v>
+        <v>25945.32</v>
       </c>
       <c r="R7">
-        <v>26206.8</v>
+        <v>26176.32</v>
       </c>
       <c r="S7">
-        <v>26540.82</v>
+        <v>26527.57</v>
       </c>
       <c r="T7">
-        <v>26636.02</v>
+        <v>26628.24</v>
       </c>
       <c r="U7">
-        <v>-2.2</v>
+        <v>-2.6</v>
       </c>
       <c r="V7" t="s">
         <v>80</v>
@@ -1686,31 +1725,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>42.83</v>
+        <v>39.9</v>
       </c>
       <c r="AA7">
-        <v>-141.16</v>
+        <v>-146.15</v>
       </c>
       <c r="AB7">
-        <v>-118.75</v>
+        <v>-124.23</v>
       </c>
       <c r="AC7">
-        <v>-22.41</v>
+        <v>-21.92</v>
       </c>
       <c r="AD7">
-        <v>29.06</v>
+        <v>42.3</v>
       </c>
       <c r="AE7">
-        <v>25.4</v>
+        <v>28.79</v>
       </c>
       <c r="AF7">
-        <v>270.36</v>
+        <v>263.2</v>
       </c>
       <c r="AH7">
-        <v>26571.76</v>
+        <v>26523.66</v>
       </c>
       <c r="AI7">
-        <v>25841.84</v>
+        <v>25828.97</v>
       </c>
       <c r="AJ7">
         <v>26568.68</v>
@@ -1719,7 +1758,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>23.92</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1733,10 +1772,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>30695.1</v>
+        <v>29995.2</v>
       </c>
       <c r="E8">
-        <v>-0.47</v>
+        <v>-2.28</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1745,43 +1784,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-22.27</v>
+        <v>-24.04</v>
       </c>
       <c r="I8">
-        <v>19.11</v>
+        <v>16.4</v>
       </c>
       <c r="J8">
-        <v>-1.88</v>
+        <v>-3.84</v>
       </c>
       <c r="K8">
-        <v>-1.63</v>
+        <v>-4.92</v>
       </c>
       <c r="L8">
-        <v>7.12</v>
+        <v>5.19</v>
       </c>
       <c r="M8">
-        <v>-13.51</v>
+        <v>-14.74</v>
       </c>
       <c r="N8">
-        <v>-2.82</v>
+        <v>-3.01</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>31065</v>
+        <v>30825.75</v>
       </c>
       <c r="R8">
-        <v>30966.19</v>
+        <v>30884.38</v>
       </c>
       <c r="S8">
-        <v>29790.39</v>
+        <v>29849.52</v>
       </c>
       <c r="T8">
-        <v>32188.19</v>
+        <v>32156.66</v>
       </c>
       <c r="U8">
-        <v>-4.64</v>
+        <v>-6.72</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1796,34 +1835,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>50.42</v>
+        <v>43.19</v>
       </c>
       <c r="AA8">
-        <v>213.28</v>
+        <v>125.72</v>
       </c>
       <c r="AB8">
-        <v>289.7</v>
+        <v>256.91</v>
       </c>
       <c r="AC8">
-        <v>-76.42</v>
+        <v>-131.19</v>
       </c>
       <c r="AD8">
-        <v>37.03</v>
+        <v>18.87</v>
       </c>
       <c r="AE8">
-        <v>53.4</v>
+        <v>37.42</v>
       </c>
       <c r="AF8">
-        <v>632.22</v>
+        <v>647.62</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>31957.64</v>
+        <v>31914</v>
       </c>
       <c r="AI8">
-        <v>29974.73</v>
+        <v>29854.75</v>
       </c>
       <c r="AJ8">
         <v>29811.25</v>
@@ -1832,7 +1871,7 @@
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>19.54</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1846,10 +1885,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16221.4</v>
+        <v>16187</v>
       </c>
       <c r="E9">
-        <v>-0.31</v>
+        <v>-0.21</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1858,28 +1897,28 @@
         <v>15663.1</v>
       </c>
       <c r="H9">
-        <v>-2.65</v>
+        <v>-2.85</v>
       </c>
       <c r="I9">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="J9">
-        <v>-2.04</v>
+        <v>-2.39</v>
       </c>
       <c r="K9">
-        <v>-2.22</v>
+        <v>-2.85</v>
       </c>
       <c r="N9">
-        <v>16.45</v>
+        <v>14.81</v>
       </c>
       <c r="Q9">
-        <v>16349.6</v>
+        <v>16270.41</v>
       </c>
       <c r="R9">
-        <v>16510.99</v>
+        <v>16487.56</v>
       </c>
       <c r="S9">
-        <v>16241.25</v>
+        <v>16248.56</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1891,40 +1930,40 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>37.61</v>
+        <v>35.88</v>
       </c>
       <c r="AA9">
-        <v>12.83</v>
+        <v>-6.33</v>
       </c>
       <c r="AB9">
-        <v>72.95999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="AC9">
-        <v>-60.12</v>
+        <v>-63.43</v>
       </c>
       <c r="AD9">
         <v>0.25</v>
       </c>
       <c r="AE9">
-        <v>4.59</v>
+        <v>0.25</v>
       </c>
       <c r="AF9">
-        <v>135.3</v>
+        <v>131.87</v>
       </c>
       <c r="AH9">
-        <v>16760.28</v>
+        <v>16766.02</v>
       </c>
       <c r="AI9">
-        <v>16261.7</v>
+        <v>16209.11</v>
       </c>
       <c r="AJ9">
-        <v>16636.88</v>
+        <v>16601.47</v>
       </c>
       <c r="AK9" t="s">
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>31.01</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1938,10 +1977,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9197.799999999999</v>
+        <v>9188.700000000001</v>
       </c>
       <c r="E10">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1950,43 +1989,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-5.82</v>
+        <v>-5.91</v>
       </c>
       <c r="I10">
-        <v>7.44</v>
+        <v>7.33</v>
       </c>
       <c r="J10">
-        <v>-0.49</v>
+        <v>0.1</v>
       </c>
       <c r="K10">
-        <v>-2.7</v>
+        <v>-3.32</v>
       </c>
       <c r="L10">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="M10">
-        <v>3.29</v>
+        <v>3.56</v>
       </c>
       <c r="N10">
-        <v>13.72</v>
+        <v>13.65</v>
       </c>
       <c r="O10">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q10">
-        <v>9200.540000000001</v>
+        <v>9202.4</v>
       </c>
       <c r="R10">
-        <v>9319.280000000001</v>
+        <v>9305.42</v>
       </c>
       <c r="S10">
-        <v>9368.049999999999</v>
+        <v>9364.120000000001</v>
       </c>
       <c r="T10">
-        <v>9345.290000000001</v>
+        <v>9343.139999999999</v>
       </c>
       <c r="U10">
-        <v>-1.58</v>
+        <v>-1.65</v>
       </c>
       <c r="V10" t="s">
         <v>80</v>
@@ -2001,31 +2040,31 @@
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>36.7</v>
+        <v>35.94</v>
       </c>
       <c r="AA10">
-        <v>-52.8</v>
+        <v>-54.37</v>
       </c>
       <c r="AB10">
-        <v>-37.11</v>
+        <v>-40.56</v>
       </c>
       <c r="AC10">
-        <v>-15.69</v>
+        <v>-13.81</v>
       </c>
       <c r="AD10">
-        <v>18.91</v>
+        <v>15.31</v>
       </c>
       <c r="AE10">
-        <v>17.83</v>
+        <v>18.21</v>
       </c>
       <c r="AF10">
-        <v>77.61</v>
+        <v>75.98</v>
       </c>
       <c r="AH10">
-        <v>9500.48</v>
+        <v>9481.75</v>
       </c>
       <c r="AI10">
-        <v>9138.08</v>
+        <v>9129.1</v>
       </c>
       <c r="AJ10">
         <v>9408.6</v>
@@ -2034,7 +2073,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>42.55</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2048,10 +2087,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1565.45</v>
+        <v>1520.65</v>
       </c>
       <c r="E11">
-        <v>0.3</v>
+        <v>-2.86</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2060,43 +2099,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-4.11</v>
+        <v>-6.85</v>
       </c>
       <c r="I11">
-        <v>24.9</v>
+        <v>21.33</v>
       </c>
       <c r="J11">
-        <v>-2.34</v>
+        <v>-2.36</v>
       </c>
       <c r="K11">
-        <v>0.13</v>
+        <v>-2.21</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>3.12</v>
       </c>
       <c r="M11">
-        <v>-2.55</v>
+        <v>-5.67</v>
       </c>
       <c r="N11">
-        <v>-1.18</v>
+        <v>-1.78</v>
       </c>
       <c r="O11">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="Q11">
-        <v>1555.82</v>
+        <v>1548.48</v>
       </c>
       <c r="R11">
-        <v>1583.89</v>
+        <v>1581.95</v>
       </c>
       <c r="S11">
-        <v>1548.03</v>
+        <v>1548.65</v>
       </c>
       <c r="T11">
-        <v>1448.2</v>
+        <v>1448.41</v>
       </c>
       <c r="U11">
-        <v>8.1</v>
+        <v>4.99</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2111,40 +2150,40 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>48.68</v>
+        <v>39.6</v>
       </c>
       <c r="AA11">
-        <v>3.14</v>
+        <v>-1.39</v>
       </c>
       <c r="AB11">
-        <v>11.36</v>
+        <v>8.81</v>
       </c>
       <c r="AC11">
-        <v>-8.23</v>
+        <v>-10.2</v>
       </c>
       <c r="AD11">
         <v>20.5</v>
       </c>
       <c r="AE11">
-        <v>11.24</v>
+        <v>17.45</v>
       </c>
       <c r="AF11">
-        <v>30.8</v>
+        <v>32.25</v>
       </c>
       <c r="AH11">
-        <v>1634.34</v>
+        <v>1638.92</v>
       </c>
       <c r="AI11">
-        <v>1533.44</v>
+        <v>1524.98</v>
       </c>
       <c r="AJ11">
-        <v>1523.72</v>
+        <v>1628.46</v>
       </c>
       <c r="AK11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL11">
-        <v>44.62</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2158,55 +2197,55 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13317.45</v>
+        <v>13152.9</v>
       </c>
       <c r="E12">
-        <v>1.07</v>
+        <v>-1.24</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
       </c>
       <c r="G12">
-        <v>9154.799999999999</v>
+        <v>9305.299999999999</v>
       </c>
       <c r="H12">
-        <v>-2.92</v>
+        <v>-4.12</v>
       </c>
       <c r="I12">
-        <v>45.47</v>
+        <v>41.35</v>
       </c>
       <c r="J12">
-        <v>-1.54</v>
+        <v>-0.31</v>
       </c>
       <c r="K12">
-        <v>1.32</v>
+        <v>-0.28</v>
       </c>
       <c r="L12">
-        <v>3.13</v>
+        <v>1.28</v>
       </c>
       <c r="M12">
-        <v>44.59</v>
+        <v>43.67</v>
       </c>
       <c r="N12">
-        <v>18.35</v>
+        <v>18.17</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13206.92</v>
+        <v>13198.72</v>
       </c>
       <c r="R12">
-        <v>13201.43</v>
+        <v>13197.74</v>
       </c>
       <c r="S12">
-        <v>12855.16</v>
+        <v>12867.32</v>
       </c>
       <c r="T12">
-        <v>12132.81</v>
+        <v>12146.1</v>
       </c>
       <c r="U12">
-        <v>9.76</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2221,31 +2260,31 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>57.58</v>
+        <v>51.02</v>
       </c>
       <c r="AA12">
-        <v>109.07</v>
+        <v>94.06</v>
       </c>
       <c r="AB12">
-        <v>128.93</v>
+        <v>121.96</v>
       </c>
       <c r="AC12">
-        <v>-19.86</v>
+        <v>-27.89</v>
       </c>
       <c r="AD12">
         <v>10.97</v>
       </c>
       <c r="AE12">
-        <v>4.05</v>
+        <v>7.71</v>
       </c>
       <c r="AF12">
-        <v>210.53</v>
+        <v>211.79</v>
       </c>
       <c r="AH12">
-        <v>13547.2</v>
+        <v>13543.95</v>
       </c>
       <c r="AI12">
-        <v>12855.67</v>
+        <v>12851.54</v>
       </c>
       <c r="AJ12">
         <v>12921.88</v>
@@ -2254,7 +2293,7 @@
         <v>82</v>
       </c>
       <c r="AL12">
-        <v>25.27</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2268,55 +2307,55 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9710.15</v>
+        <v>9680.049999999999</v>
       </c>
       <c r="E13">
-        <v>0.04</v>
+        <v>-0.31</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
       </c>
       <c r="G13">
-        <v>9202.450000000001</v>
+        <v>9366.4</v>
       </c>
       <c r="H13">
-        <v>-9.81</v>
+        <v>-10.09</v>
       </c>
       <c r="I13">
-        <v>5.52</v>
+        <v>3.35</v>
       </c>
       <c r="J13">
-        <v>0.22</v>
+        <v>-0.25</v>
       </c>
       <c r="K13">
-        <v>-2.29</v>
+        <v>-2.44</v>
       </c>
       <c r="L13">
-        <v>-3.3</v>
+        <v>-3.61</v>
       </c>
       <c r="M13">
-        <v>5.29</v>
+        <v>5.19</v>
       </c>
       <c r="N13">
         <v>21.29</v>
       </c>
       <c r="O13">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q13">
-        <v>9695.33</v>
+        <v>9690.459999999999</v>
       </c>
       <c r="R13">
-        <v>9770.15</v>
+        <v>9761.620000000001</v>
       </c>
       <c r="S13">
-        <v>9873.43</v>
+        <v>9867.639999999999</v>
       </c>
       <c r="T13">
-        <v>10032.66</v>
+        <v>10031.13</v>
       </c>
       <c r="U13">
-        <v>-3.21</v>
+        <v>-3.5</v>
       </c>
       <c r="V13" t="s">
         <v>80</v>
@@ -2331,31 +2370,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>38.62</v>
+        <v>35.72</v>
       </c>
       <c r="AA13">
-        <v>-60.39</v>
+        <v>-59.91</v>
       </c>
       <c r="AB13">
-        <v>-59.38</v>
+        <v>-59.48</v>
       </c>
       <c r="AC13">
-        <v>-1.02</v>
+        <v>-0.43</v>
       </c>
       <c r="AD13">
-        <v>62.79</v>
+        <v>63.05</v>
       </c>
       <c r="AE13">
-        <v>40.57</v>
+        <v>54.19</v>
       </c>
       <c r="AF13">
-        <v>86.59999999999999</v>
+        <v>86.23</v>
       </c>
       <c r="AH13">
-        <v>9915.049999999999</v>
+        <v>9906.629999999999</v>
       </c>
       <c r="AI13">
-        <v>9625.26</v>
+        <v>9616.6</v>
       </c>
       <c r="AJ13">
         <v>9905.1</v>
@@ -2364,7 +2403,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>38.57</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2378,55 +2417,55 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8514.85</v>
+        <v>8424.65</v>
       </c>
       <c r="E14">
-        <v>-0.44</v>
+        <v>-1.06</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
       </c>
       <c r="G14">
-        <v>6756.05</v>
+        <v>6830.95</v>
       </c>
       <c r="H14">
-        <v>-13.82</v>
+        <v>-14.73</v>
       </c>
       <c r="I14">
-        <v>26.03</v>
+        <v>23.33</v>
       </c>
       <c r="J14">
-        <v>-1.04</v>
+        <v>-2.15</v>
       </c>
       <c r="K14">
-        <v>-2.46</v>
+        <v>-4.11</v>
       </c>
       <c r="L14">
-        <v>3.85</v>
+        <v>-0.85</v>
       </c>
       <c r="M14">
-        <v>25.61</v>
+        <v>24.7</v>
       </c>
       <c r="N14">
-        <v>29.33</v>
+        <v>29.35</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8538.889999999999</v>
+        <v>8501.91</v>
       </c>
       <c r="R14">
-        <v>8625.02</v>
+        <v>8614.26</v>
       </c>
       <c r="S14">
-        <v>8501.74</v>
+        <v>8499.16</v>
       </c>
       <c r="T14">
-        <v>8600.25</v>
+        <v>8600.370000000001</v>
       </c>
       <c r="U14">
-        <v>-0.99</v>
+        <v>-2.04</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2441,31 +2480,31 @@
         <v>1</v>
       </c>
       <c r="Z14">
-        <v>45.98</v>
+        <v>40.37</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>-9.74</v>
       </c>
       <c r="AB14">
-        <v>23.96</v>
+        <v>17.22</v>
       </c>
       <c r="AC14">
-        <v>-21.9</v>
+        <v>-26.96</v>
       </c>
       <c r="AD14">
-        <v>12.29</v>
+        <v>11.36</v>
       </c>
       <c r="AE14">
-        <v>9.949999999999999</v>
+        <v>11.03</v>
       </c>
       <c r="AF14">
-        <v>124.55</v>
+        <v>126.9</v>
       </c>
       <c r="AH14">
-        <v>8796.92</v>
+        <v>8807.83</v>
       </c>
       <c r="AI14">
-        <v>8453.120000000001</v>
+        <v>8420.700000000001</v>
       </c>
       <c r="AJ14">
         <v>8382.120000000001</v>
@@ -2474,7 +2513,7 @@
         <v>82</v>
       </c>
       <c r="AL14">
-        <v>17.21</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2488,10 +2527,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26478.1</v>
+        <v>26675.5</v>
       </c>
       <c r="E15">
-        <v>-0.68</v>
+        <v>0.75</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2500,43 +2539,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-2.61</v>
+        <v>-1.88</v>
       </c>
       <c r="I15">
-        <v>23.42</v>
+        <v>24.34</v>
       </c>
       <c r="J15">
-        <v>-1.9</v>
+        <v>-1.88</v>
       </c>
       <c r="K15">
-        <v>-0.33</v>
+        <v>0.5</v>
       </c>
       <c r="L15">
-        <v>9.65</v>
+        <v>9.82</v>
       </c>
       <c r="M15">
-        <v>21.41</v>
+        <v>22.34</v>
       </c>
       <c r="N15">
-        <v>12.84</v>
+        <v>13.14</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26779.31</v>
+        <v>26677.12</v>
       </c>
       <c r="R15">
-        <v>26614.43</v>
+        <v>26624.23</v>
       </c>
       <c r="S15">
-        <v>26195.4</v>
+        <v>26224.35</v>
       </c>
       <c r="T15">
-        <v>23805.76</v>
+        <v>23825.03</v>
       </c>
       <c r="U15">
-        <v>11.23</v>
+        <v>11.96</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2551,34 +2590,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>49.59</v>
+        <v>54.58</v>
       </c>
       <c r="AA15">
-        <v>163.98</v>
+        <v>152.12</v>
       </c>
       <c r="AB15">
-        <v>202.4</v>
+        <v>192.34</v>
       </c>
       <c r="AC15">
-        <v>-38.41</v>
+        <v>-40.22</v>
       </c>
       <c r="AD15">
-        <v>10.48</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AE15">
-        <v>27</v>
+        <v>13.07</v>
       </c>
       <c r="AF15">
-        <v>295.46</v>
+        <v>293.7</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27087.31</v>
+        <v>27093.45</v>
       </c>
       <c r="AI15">
-        <v>26141.55</v>
+        <v>26155.01</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
@@ -2587,7 +2626,7 @@
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>31.22</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2601,10 +2640,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>907.9</v>
+        <v>892.5</v>
       </c>
       <c r="E16">
-        <v>-0.9</v>
+        <v>-1.7</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2613,82 +2652,82 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-6.27</v>
+        <v>-7.86</v>
       </c>
       <c r="I16">
-        <v>39.43</v>
+        <v>37.07</v>
       </c>
       <c r="J16">
-        <v>-0.1</v>
+        <v>-1.29</v>
       </c>
       <c r="K16">
-        <v>2.37</v>
+        <v>0.74</v>
       </c>
       <c r="L16">
-        <v>21.18</v>
+        <v>17.22</v>
       </c>
       <c r="M16">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="N16">
-        <v>16.09</v>
+        <v>16.22</v>
       </c>
       <c r="O16">
         <v>81</v>
       </c>
       <c r="Q16">
-        <v>902.53</v>
+        <v>900.2</v>
       </c>
       <c r="R16">
-        <v>903.14</v>
+        <v>902.87</v>
       </c>
       <c r="S16">
-        <v>901.52</v>
+        <v>903</v>
       </c>
       <c r="T16">
-        <v>831.47</v>
+        <v>831.23</v>
       </c>
       <c r="U16">
-        <v>9.19</v>
+        <v>7.37</v>
       </c>
       <c r="V16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
       </c>
       <c r="X16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z16">
-        <v>53.17</v>
+        <v>46.05</v>
       </c>
       <c r="AA16">
-        <v>3.14</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>3.99</v>
+        <v>3.58</v>
       </c>
       <c r="AC16">
-        <v>-0.85</v>
+        <v>-1.68</v>
       </c>
       <c r="AD16">
-        <v>49.07</v>
+        <v>49.31</v>
       </c>
       <c r="AE16">
-        <v>30.19</v>
+        <v>43.01</v>
       </c>
       <c r="AF16">
-        <v>17.86</v>
+        <v>17.89</v>
       </c>
       <c r="AH16">
-        <v>921.71</v>
+        <v>921.91</v>
       </c>
       <c r="AI16">
-        <v>884.5700000000001</v>
+        <v>883.8200000000001</v>
       </c>
       <c r="AJ16">
         <v>869.13</v>
@@ -2697,7 +2736,7 @@
         <v>82</v>
       </c>
       <c r="AL16">
-        <v>24.47</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2711,10 +2750,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30575.55</v>
+        <v>30422.7</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2723,43 +2762,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-10.34</v>
+        <v>-10.79</v>
       </c>
       <c r="I17">
-        <v>7.8</v>
+        <v>7.26</v>
       </c>
       <c r="J17">
-        <v>-1.05</v>
+        <v>-1.34</v>
       </c>
       <c r="K17">
-        <v>-2.95</v>
+        <v>-2.69</v>
       </c>
       <c r="L17">
-        <v>4.36</v>
+        <v>3.21</v>
       </c>
       <c r="M17">
-        <v>-4.11</v>
+        <v>-4.24</v>
       </c>
       <c r="N17">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="O17">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q17">
-        <v>30653.73</v>
+        <v>30571.03</v>
       </c>
       <c r="R17">
-        <v>30890.59</v>
+        <v>30846.22</v>
       </c>
       <c r="S17">
-        <v>31091.82</v>
+        <v>31087.78</v>
       </c>
       <c r="T17">
-        <v>31626.43</v>
+        <v>31610.86</v>
       </c>
       <c r="U17">
-        <v>-3.32</v>
+        <v>-3.76</v>
       </c>
       <c r="V17" t="s">
         <v>80</v>
@@ -2774,40 +2813,40 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>38.02</v>
+        <v>34.27</v>
       </c>
       <c r="AA17">
-        <v>-139.6</v>
+        <v>-156.71</v>
       </c>
       <c r="AB17">
-        <v>-97.81999999999999</v>
+        <v>-109.6</v>
       </c>
       <c r="AC17">
-        <v>-41.78</v>
+        <v>-47.11</v>
       </c>
       <c r="AD17">
-        <v>12.78</v>
+        <v>12.3</v>
       </c>
       <c r="AE17">
-        <v>25.04</v>
+        <v>16.18</v>
       </c>
       <c r="AF17">
-        <v>249.88</v>
+        <v>247.07</v>
       </c>
       <c r="AH17">
-        <v>31331.61</v>
+        <v>31288.07</v>
       </c>
       <c r="AI17">
-        <v>30449.57</v>
+        <v>30404.36</v>
       </c>
       <c r="AJ17">
-        <v>31236.31</v>
+        <v>31201.83</v>
       </c>
       <c r="AK17" t="s">
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>29.39</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2821,10 +2860,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16408.05</v>
+        <v>16520.3</v>
       </c>
       <c r="E18">
-        <v>-0.87</v>
+        <v>0.68</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2833,28 +2872,28 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-3.15</v>
+        <v>-2.49</v>
       </c>
       <c r="I18">
-        <v>6.52</v>
+        <v>7.25</v>
       </c>
       <c r="J18">
-        <v>-2.32</v>
+        <v>-2.49</v>
       </c>
       <c r="K18">
-        <v>-1.85</v>
+        <v>-1.13</v>
       </c>
       <c r="N18">
-        <v>26.25</v>
+        <v>28.87</v>
       </c>
       <c r="Q18">
-        <v>16640.14</v>
+        <v>16555.9</v>
       </c>
       <c r="R18">
-        <v>16581.03</v>
+        <v>16574.5</v>
       </c>
       <c r="S18">
-        <v>16499.03</v>
+        <v>16507.17</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2866,31 +2905,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>43.46</v>
+        <v>48.46</v>
       </c>
       <c r="AA18">
-        <v>34.69</v>
+        <v>25.88</v>
       </c>
       <c r="AB18">
-        <v>56.83</v>
+        <v>50.64</v>
       </c>
       <c r="AC18">
-        <v>-22.13</v>
+        <v>-24.75</v>
       </c>
       <c r="AD18">
-        <v>14.51</v>
+        <v>11.26</v>
       </c>
       <c r="AE18">
-        <v>32.13</v>
+        <v>17.49</v>
       </c>
       <c r="AF18">
-        <v>177.77</v>
+        <v>174.73</v>
       </c>
       <c r="AH18">
-        <v>16864.5</v>
+        <v>16857.2</v>
       </c>
       <c r="AI18">
-        <v>16297.57</v>
+        <v>16291.8</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2899,7 +2938,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>26.27</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2913,10 +2952,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9708.85</v>
+        <v>9754.549999999999</v>
       </c>
       <c r="E19">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="F19">
         <v>9968.25</v>
@@ -2925,28 +2964,28 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-2.6</v>
+        <v>-2.14</v>
       </c>
       <c r="I19">
-        <v>7.93</v>
+        <v>8.44</v>
       </c>
       <c r="J19">
-        <v>-0.44</v>
+        <v>0.37</v>
       </c>
       <c r="K19">
-        <v>0.44</v>
+        <v>0.23</v>
       </c>
       <c r="N19">
-        <v>39.36</v>
+        <v>40.52</v>
       </c>
       <c r="Q19">
-        <v>9673.43</v>
+        <v>9680.66</v>
       </c>
       <c r="R19">
-        <v>9745.65</v>
+        <v>9751.59</v>
       </c>
       <c r="S19">
-        <v>9549.15</v>
+        <v>9556.42</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2958,31 +2997,31 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>53.41</v>
+        <v>56.14</v>
       </c>
       <c r="AA19">
-        <v>44.52</v>
+        <v>44.95</v>
       </c>
       <c r="AB19">
-        <v>71.81999999999999</v>
+        <v>66.44</v>
       </c>
       <c r="AC19">
-        <v>-27.3</v>
+        <v>-21.49</v>
       </c>
       <c r="AD19">
-        <v>12.54</v>
+        <v>32.39</v>
       </c>
       <c r="AE19">
-        <v>5.71</v>
+        <v>16.5</v>
       </c>
       <c r="AF19">
-        <v>135.77</v>
+        <v>134.56</v>
       </c>
       <c r="AH19">
-        <v>9927.91</v>
+        <v>9926.35</v>
       </c>
       <c r="AI19">
-        <v>9563.379999999999</v>
+        <v>9576.83</v>
       </c>
       <c r="AJ19">
         <v>9466.209999999999</v>
@@ -2991,7 +3030,7 @@
         <v>82</v>
       </c>
       <c r="AL19">
-        <v>21.55</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3005,10 +3044,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11187.65</v>
+        <v>11118.85</v>
       </c>
       <c r="E20">
-        <v>0.21</v>
+        <v>-0.61</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3017,64 +3056,64 @@
         <v>10998.55</v>
       </c>
       <c r="H20">
-        <v>-1.6</v>
+        <v>-2.2</v>
       </c>
       <c r="I20">
-        <v>1.72</v>
+        <v>1.09</v>
       </c>
       <c r="J20">
-        <v>1.08</v>
+        <v>0.14</v>
       </c>
       <c r="K20">
-        <v>-1.03</v>
+        <v>-1.71</v>
       </c>
       <c r="N20">
-        <v>7.11</v>
+        <v>4.13</v>
       </c>
       <c r="Q20">
-        <v>11155.45</v>
+        <v>11158.46</v>
       </c>
       <c r="R20">
-        <v>11186.79</v>
+        <v>11179.21</v>
       </c>
       <c r="S20">
-        <v>11177.7</v>
+        <v>11179.84</v>
       </c>
       <c r="V20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X20" t="s">
         <v>80</v>
       </c>
       <c r="Y20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>51.29</v>
+        <v>44.9</v>
       </c>
       <c r="AA20">
-        <v>-12.89</v>
+        <v>-15.39</v>
       </c>
       <c r="AB20">
-        <v>-11.4</v>
+        <v>-12.19</v>
       </c>
       <c r="AC20">
-        <v>-1.49</v>
+        <v>-3.19</v>
       </c>
       <c r="AD20">
-        <v>90.27</v>
+        <v>76.61</v>
       </c>
       <c r="AE20">
-        <v>75.29000000000001</v>
+        <v>81.28</v>
       </c>
       <c r="AF20">
-        <v>115.99</v>
+        <v>116.8</v>
       </c>
       <c r="AH20">
-        <v>11313.27</v>
+        <v>11302.71</v>
       </c>
       <c r="AI20">
-        <v>11060.31</v>
+        <v>11055.7</v>
       </c>
       <c r="AJ20">
         <v>10895.17</v>
@@ -3083,7 +3122,7 @@
         <v>82</v>
       </c>
       <c r="AL20">
-        <v>17.03</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3097,10 +3136,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27824.5</v>
+        <v>27745.75</v>
       </c>
       <c r="E21">
-        <v>0.28</v>
+        <v>-0.28</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3109,43 +3148,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-4.67</v>
+        <v>-4.94</v>
       </c>
       <c r="I21">
-        <v>15.24</v>
+        <v>14.91</v>
       </c>
       <c r="J21">
-        <v>0.31</v>
+        <v>-0.93</v>
       </c>
       <c r="K21">
-        <v>0.52</v>
+        <v>1.29</v>
       </c>
       <c r="L21">
-        <v>6.52</v>
+        <v>4.5</v>
       </c>
       <c r="M21">
-        <v>6.71</v>
+        <v>6.48</v>
       </c>
       <c r="N21">
-        <v>8.029999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="O21">
         <v>68</v>
       </c>
       <c r="Q21">
-        <v>27789.4</v>
+        <v>27737.4</v>
       </c>
       <c r="R21">
-        <v>27531.05</v>
+        <v>27541.62</v>
       </c>
       <c r="S21">
-        <v>27872.49</v>
+        <v>27866.4</v>
       </c>
       <c r="T21">
-        <v>27631.94</v>
+        <v>27629.71</v>
       </c>
       <c r="U21">
-        <v>0.7</v>
+        <v>0.42</v>
       </c>
       <c r="V21" t="s">
         <v>80</v>
@@ -3160,31 +3199,31 @@
         <v>2</v>
       </c>
       <c r="Z21">
-        <v>54.09</v>
+        <v>51.77</v>
       </c>
       <c r="AA21">
-        <v>8.49</v>
+        <v>12.45</v>
       </c>
       <c r="AB21">
-        <v>-41.81</v>
+        <v>-30.96</v>
       </c>
       <c r="AC21">
-        <v>50.31</v>
+        <v>43.41</v>
       </c>
       <c r="AD21">
-        <v>62.05</v>
+        <v>66.95</v>
       </c>
       <c r="AE21">
-        <v>64.54000000000001</v>
+        <v>62.96</v>
       </c>
       <c r="AF21">
-        <v>306.48</v>
+        <v>293.64</v>
       </c>
       <c r="AH21">
-        <v>27989.51</v>
+        <v>28010.04</v>
       </c>
       <c r="AI21">
-        <v>27072.59</v>
+        <v>27073.2</v>
       </c>
       <c r="AJ21">
         <v>28265.67</v>
@@ -3193,7 +3232,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>36</v>
+        <v>36.27</v>
       </c>
     </row>
   </sheetData>
@@ -3334,7 +3373,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3374,7 +3413,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3393,2370 +3432,2524 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>102</v>
       </c>
+      <c r="F5" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="8">
-        <v>-5.35</v>
-      </c>
-      <c r="D9" s="8">
-        <v>-4.82</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="8">
-        <v>-2.53</v>
-      </c>
-      <c r="D10" s="8">
-        <v>-1.54</v>
-      </c>
-      <c r="E10" s="9">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="8">
-        <v>-4.73</v>
-      </c>
-      <c r="D11" s="8">
-        <v>-4.72</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-1.78</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-1.57</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-6.94</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-7.04</v>
-      </c>
-      <c r="E13" s="10">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-3.43</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-3.02</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.41</v>
+      <c r="B14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="8">
-        <v>-1.8</v>
+        <v>-4.82</v>
       </c>
       <c r="D15" s="8">
-        <v>-1.63</v>
+        <v>-6.57</v>
       </c>
       <c r="E15" s="9">
-        <v>0.17</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="8">
-        <v>-1.93</v>
+        <v>-1.54</v>
       </c>
       <c r="D16" s="8">
-        <v>-2.22</v>
-      </c>
-      <c r="E16" s="10">
-        <v>-0.29</v>
+        <v>-2.9</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="8">
-        <v>-2.63</v>
+        <v>-4.72</v>
       </c>
       <c r="D17" s="8">
-        <v>-2.7</v>
-      </c>
-      <c r="E17" s="10">
-        <v>-0.07000000000000001</v>
+        <v>-5.22</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="8">
-        <v>-0.91</v>
+        <v>-1.57</v>
       </c>
       <c r="D18" s="8">
-        <v>0.13</v>
+        <v>-2</v>
       </c>
       <c r="E18" s="9">
-        <v>1.04</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="8">
-        <v>-0.61</v>
+        <v>-7.04</v>
       </c>
       <c r="D19" s="8">
-        <v>1.32</v>
+        <v>-7.77</v>
       </c>
       <c r="E19" s="9">
-        <v>1.93</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="8">
-        <v>-2.46</v>
+        <v>-3.02</v>
       </c>
       <c r="D20" s="8">
-        <v>-2.29</v>
-      </c>
-      <c r="E20" s="9">
-        <v>0.17</v>
+        <v>-2</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1.02</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="8">
-        <v>0.13</v>
+        <v>-1.63</v>
       </c>
       <c r="D21" s="8">
-        <v>-2.46</v>
-      </c>
-      <c r="E21" s="10">
-        <v>-2.59</v>
+        <v>-4.92</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-3.29</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="8">
-        <v>0.36</v>
+        <v>-2.22</v>
       </c>
       <c r="D22" s="8">
-        <v>-0.33</v>
-      </c>
-      <c r="E22" s="10">
-        <v>-0.6899999999999999</v>
+        <v>-2.85</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="8">
-        <v>1.94</v>
+        <v>-2.7</v>
       </c>
       <c r="D23" s="8">
-        <v>2.37</v>
+        <v>-3.32</v>
       </c>
       <c r="E23" s="9">
-        <v>0.43</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="8">
-        <v>-3.12</v>
+        <v>0.13</v>
       </c>
       <c r="D24" s="8">
-        <v>-2.95</v>
+        <v>-2.21</v>
       </c>
       <c r="E24" s="9">
-        <v>0.17</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="8">
-        <v>-0.9399999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="D25" s="8">
-        <v>-1.85</v>
-      </c>
-      <c r="E25" s="10">
-        <v>-0.91</v>
+        <v>-0.28</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="8">
-        <v>2.92</v>
+        <v>-2.29</v>
       </c>
       <c r="D26" s="8">
-        <v>0.44</v>
-      </c>
-      <c r="E26" s="10">
-        <v>-2.48</v>
+        <v>-2.44</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="8">
-        <v>-0.46</v>
+        <v>-2.46</v>
       </c>
       <c r="D27" s="8">
-        <v>-1.03</v>
-      </c>
-      <c r="E27" s="10">
-        <v>-0.57</v>
+        <v>-4.11</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="8">
-        <v>0.01</v>
+        <v>-0.33</v>
       </c>
       <c r="D28" s="8">
-        <v>0.52</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.51</v>
+        <v>0.5</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0.83</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="8">
-        <v>-3.62</v>
+        <v>2.37</v>
       </c>
       <c r="D29" s="8">
-        <v>-3.95</v>
-      </c>
-      <c r="E29" s="10">
-        <v>-0.33</v>
+        <v>0.74</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" s="8">
-        <v>-0.65</v>
+        <v>-2.95</v>
       </c>
       <c r="D30" s="8">
-        <v>-0.05</v>
-      </c>
-      <c r="E30" s="9">
-        <v>0.6</v>
+        <v>-2.69</v>
+      </c>
+      <c r="E30" s="10">
+        <v>0.26</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="8">
-        <v>-2.32</v>
+        <v>-1.85</v>
       </c>
       <c r="D31" s="8">
-        <v>-2.57</v>
+        <v>-1.13</v>
       </c>
       <c r="E31" s="10">
-        <v>-0.25</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="7" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32" s="8">
-        <v>0.1</v>
+        <v>0.44</v>
       </c>
       <c r="D32" s="8">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="E32" s="9">
-        <v>0.07000000000000001</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33" s="8">
-        <v>-2.29</v>
+        <v>-1.03</v>
       </c>
       <c r="D33" s="8">
-        <v>-1.97</v>
+        <v>-1.71</v>
       </c>
       <c r="E33" s="9">
-        <v>0.32</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="8">
-        <v>-1.36</v>
+        <v>0.52</v>
       </c>
       <c r="D34" s="8">
-        <v>-0.9</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.46</v>
+        <v>1.29</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0.77</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="8">
-        <v>2.04</v>
+        <v>-3.95</v>
       </c>
       <c r="D35" s="8">
-        <v>-1.88</v>
-      </c>
-      <c r="E35" s="10">
-        <v>-3.92</v>
+        <v>-3.96</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="8">
-        <v>-1.73</v>
+        <v>-0.05</v>
       </c>
       <c r="D36" s="8">
-        <v>-2.04</v>
+        <v>0.12</v>
       </c>
       <c r="E36" s="10">
-        <v>-0.31</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="8">
-        <v>-0.36</v>
+        <v>-2.57</v>
       </c>
       <c r="D37" s="8">
-        <v>-0.49</v>
+        <v>-2.05</v>
       </c>
       <c r="E37" s="10">
-        <v>-0.13</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="8">
-        <v>-2.25</v>
+        <v>0.17</v>
       </c>
       <c r="D38" s="8">
-        <v>-2.34</v>
-      </c>
-      <c r="E38" s="10">
-        <v>-0.09</v>
+        <v>0.06</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="8">
-        <v>-1.86</v>
+        <v>-1.97</v>
       </c>
       <c r="D39" s="8">
-        <v>-1.54</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.32</v>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E39" s="10">
+        <v>1.03</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="8">
-        <v>0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="D40" s="8">
-        <v>0.22</v>
+        <v>-1.36</v>
       </c>
       <c r="E40" s="9">
-        <v>0.17</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="8">
-        <v>-0.41</v>
+        <v>-1.88</v>
       </c>
       <c r="D41" s="8">
-        <v>-1.04</v>
-      </c>
-      <c r="E41" s="10">
-        <v>-0.63</v>
+        <v>-3.84</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="8">
-        <v>-0.71</v>
+        <v>-2.04</v>
       </c>
       <c r="D42" s="8">
-        <v>-1.9</v>
-      </c>
-      <c r="E42" s="10">
-        <v>-1.19</v>
+        <v>-2.39</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="8">
-        <v>0.72</v>
+        <v>-0.49</v>
       </c>
       <c r="D43" s="8">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E43" s="10">
-        <v>-0.82</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="8">
-        <v>-0.57</v>
+        <v>-2.34</v>
       </c>
       <c r="D44" s="8">
-        <v>-1.05</v>
-      </c>
-      <c r="E44" s="10">
-        <v>-0.48</v>
+        <v>-2.36</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="8">
-        <v>-0.93</v>
+        <v>-1.54</v>
       </c>
       <c r="D45" s="8">
-        <v>-2.32</v>
+        <v>-0.31</v>
       </c>
       <c r="E45" s="10">
-        <v>-1.39</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="8">
-        <v>-1.34</v>
+        <v>0.22</v>
       </c>
       <c r="D46" s="8">
-        <v>-0.44</v>
+        <v>-0.25</v>
       </c>
       <c r="E46" s="9">
-        <v>0.9</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="8">
-        <v>0.9399999999999999</v>
+        <v>-1.04</v>
       </c>
       <c r="D47" s="8">
-        <v>1.08</v>
+        <v>-2.15</v>
       </c>
       <c r="E47" s="9">
-        <v>0.14</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="8">
-        <v>-0.04</v>
+        <v>-1.9</v>
       </c>
       <c r="D48" s="8">
-        <v>0.31</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.35</v>
+        <v>-1.88</v>
+      </c>
+      <c r="E48" s="10">
+        <v>0.02</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="8">
-        <v>9.94</v>
+        <v>-0.1</v>
       </c>
       <c r="D49" s="8">
-        <v>10.04</v>
+        <v>-1.29</v>
       </c>
       <c r="E49" s="9">
-        <v>0.1</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="8">
-        <v>12.37</v>
+        <v>-1.05</v>
       </c>
       <c r="D50" s="8">
-        <v>13.86</v>
+        <v>-1.34</v>
       </c>
       <c r="E50" s="9">
-        <v>1.49</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C51" s="8">
-        <v>-4.29</v>
+        <v>-2.32</v>
       </c>
       <c r="D51" s="8">
-        <v>-3.86</v>
+        <v>-2.49</v>
       </c>
       <c r="E51" s="9">
-        <v>0.43</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C52" s="8">
-        <v>12.32</v>
+        <v>-0.44</v>
       </c>
       <c r="D52" s="8">
-        <v>13.02</v>
-      </c>
-      <c r="E52" s="9">
-        <v>0.7</v>
+        <v>0.37</v>
+      </c>
+      <c r="E52" s="10">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C53" s="8">
-        <v>-18.21</v>
+        <v>1.08</v>
       </c>
       <c r="D53" s="8">
-        <v>-17.48</v>
+        <v>0.14</v>
       </c>
       <c r="E53" s="9">
-        <v>0.73</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C54" s="8">
-        <v>-0.11</v>
+        <v>0.31</v>
       </c>
       <c r="D54" s="8">
-        <v>1.6</v>
+        <v>-0.93</v>
       </c>
       <c r="E54" s="9">
-        <v>1.71</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="8">
-        <v>-14.49</v>
+        <v>10.04</v>
       </c>
       <c r="D55" s="8">
-        <v>-13.51</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.98</v>
+        <v>10.97</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.93</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="8">
-        <v>2.62</v>
+        <v>13.86</v>
       </c>
       <c r="D56" s="8">
-        <v>3.29</v>
+        <v>13.19</v>
       </c>
       <c r="E56" s="9">
-        <v>0.67</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="8">
-        <v>-3.3</v>
+        <v>-3.86</v>
       </c>
       <c r="D57" s="8">
-        <v>-2.55</v>
+        <v>-4.13</v>
       </c>
       <c r="E57" s="9">
-        <v>0.75</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="8">
-        <v>41.98</v>
+        <v>13.02</v>
       </c>
       <c r="D58" s="8">
-        <v>44.59</v>
+        <v>12.89</v>
       </c>
       <c r="E58" s="9">
-        <v>2.61</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="8">
-        <v>4.28</v>
+        <v>-17.48</v>
       </c>
       <c r="D59" s="8">
-        <v>5.29</v>
+        <v>-18.79</v>
       </c>
       <c r="E59" s="9">
-        <v>1.01</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="8">
-        <v>24.86</v>
+        <v>1.6</v>
       </c>
       <c r="D60" s="8">
-        <v>25.61</v>
+        <v>1.44</v>
       </c>
       <c r="E60" s="9">
-        <v>0.75</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="8">
-        <v>21.23</v>
+        <v>-13.51</v>
       </c>
       <c r="D61" s="8">
-        <v>21.41</v>
+        <v>-14.74</v>
       </c>
       <c r="E61" s="9">
-        <v>0.18</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="8">
-        <v>2.25</v>
+        <v>3.29</v>
       </c>
       <c r="D62" s="8">
-        <v>2.88</v>
-      </c>
-      <c r="E62" s="9">
-        <v>0.63</v>
+        <v>3.56</v>
+      </c>
+      <c r="E62" s="10">
+        <v>0.27</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="8">
-        <v>-5.37</v>
+        <v>-2.55</v>
       </c>
       <c r="D63" s="8">
-        <v>-4.11</v>
+        <v>-5.67</v>
       </c>
       <c r="E63" s="9">
-        <v>1.26</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="8">
-        <v>5.34</v>
+        <v>44.59</v>
       </c>
       <c r="D64" s="8">
-        <v>6.71</v>
+        <v>43.67</v>
       </c>
       <c r="E64" s="9">
-        <v>1.37</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" s="8">
-        <v>6.39</v>
+        <v>5.29</v>
       </c>
       <c r="D65" s="8">
-        <v>7.9</v>
+        <v>5.19</v>
       </c>
       <c r="E65" s="9">
-        <v>1.51</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="8">
-        <v>-3.49</v>
+        <v>25.61</v>
       </c>
       <c r="D66" s="8">
-        <v>-1.39</v>
+        <v>24.7</v>
       </c>
       <c r="E66" s="9">
-        <v>2.1</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67" s="8">
-        <v>4.03</v>
+        <v>21.41</v>
       </c>
       <c r="D67" s="8">
-        <v>4.64</v>
-      </c>
-      <c r="E67" s="9">
-        <v>0.61</v>
+        <v>22.34</v>
+      </c>
+      <c r="E67" s="10">
+        <v>0.93</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68" s="8">
-        <v>-5.47</v>
+        <v>2.88</v>
       </c>
       <c r="D68" s="8">
-        <v>-4.08</v>
+        <v>2.5</v>
       </c>
       <c r="E68" s="9">
-        <v>1.39</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C69" s="8">
-        <v>-4.86</v>
+        <v>-4.11</v>
       </c>
       <c r="D69" s="8">
-        <v>-4.59</v>
+        <v>-4.24</v>
       </c>
       <c r="E69" s="9">
-        <v>0.27</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C70" s="8">
-        <v>3.46</v>
+        <v>6.71</v>
       </c>
       <c r="D70" s="8">
-        <v>5.02</v>
+        <v>6.48</v>
       </c>
       <c r="E70" s="9">
-        <v>1.56</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="8">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="D71" s="8">
-        <v>7.12</v>
+        <v>6.43</v>
       </c>
       <c r="E71" s="9">
-        <v>0.82</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="8">
-        <v>0.24</v>
+        <v>-1.39</v>
       </c>
       <c r="D72" s="8">
-        <v>1.21</v>
+        <v>-2.72</v>
       </c>
       <c r="E72" s="9">
-        <v>0.97</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="8">
-        <v>3.88</v>
+        <v>4.64</v>
       </c>
       <c r="D73" s="8">
-        <v>6</v>
+        <v>3.72</v>
       </c>
       <c r="E73" s="9">
-        <v>2.12</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="8">
-        <v>-0.34</v>
+        <v>-4.08</v>
       </c>
       <c r="D74" s="8">
-        <v>3.13</v>
+        <v>-4.48</v>
       </c>
       <c r="E74" s="9">
-        <v>3.47</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="8">
-        <v>-3.71</v>
+        <v>-4.59</v>
       </c>
       <c r="D75" s="8">
-        <v>-3.3</v>
+        <v>-5.89</v>
       </c>
       <c r="E75" s="9">
-        <v>0.41</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="8">
-        <v>3.55</v>
+        <v>5.02</v>
       </c>
       <c r="D76" s="8">
-        <v>3.85</v>
+        <v>3.11</v>
       </c>
       <c r="E76" s="9">
-        <v>0.3</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="8">
-        <v>9.94</v>
+        <v>7.12</v>
       </c>
       <c r="D77" s="8">
-        <v>9.65</v>
-      </c>
-      <c r="E77" s="10">
-        <v>-0.29</v>
+        <v>5.19</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="8">
-        <v>19.15</v>
+        <v>1.21</v>
       </c>
       <c r="D78" s="8">
-        <v>21.18</v>
+        <v>0.73</v>
       </c>
       <c r="E78" s="9">
-        <v>2.03</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="8">
-        <v>3.58</v>
+        <v>6</v>
       </c>
       <c r="D79" s="8">
-        <v>4.36</v>
+        <v>3.12</v>
       </c>
       <c r="E79" s="9">
-        <v>0.78</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="8">
-        <v>5.51</v>
+        <v>3.13</v>
       </c>
       <c r="D80" s="8">
-        <v>6.52</v>
+        <v>1.28</v>
       </c>
       <c r="E80" s="9">
-        <v>1.01</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C81" s="8">
-        <v>-6.11</v>
+        <v>-3.3</v>
       </c>
       <c r="D81" s="8">
-        <v>-6.53</v>
-      </c>
-      <c r="E81" s="10">
-        <v>-0.42</v>
+        <v>-3.61</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="7" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C82" s="8">
-        <v>-7.17</v>
+        <v>3.85</v>
       </c>
       <c r="D82" s="8">
-        <v>-6.66</v>
+        <v>-0.85</v>
       </c>
       <c r="E82" s="9">
-        <v>0.51</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C83" s="8">
-        <v>-7.87</v>
+        <v>9.65</v>
       </c>
       <c r="D83" s="8">
-        <v>-8.24</v>
+        <v>9.82</v>
       </c>
       <c r="E83" s="10">
-        <v>-0.37</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C84" s="8">
-        <v>-8.17</v>
+        <v>21.18</v>
       </c>
       <c r="D84" s="8">
-        <v>-8.35</v>
-      </c>
-      <c r="E84" s="10">
-        <v>-0.18</v>
+        <v>17.22</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-3.96</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C85" s="8">
-        <v>-19.52</v>
+        <v>4.36</v>
       </c>
       <c r="D85" s="8">
-        <v>-19.63</v>
-      </c>
-      <c r="E85" s="10">
-        <v>-0.11</v>
+        <v>3.21</v>
+      </c>
+      <c r="E85" s="9">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C86" s="8">
-        <v>-8.92</v>
+        <v>6.52</v>
       </c>
       <c r="D86" s="8">
-        <v>-8.470000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="E86" s="9">
-        <v>0.45</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="8">
-        <v>-21.9</v>
+        <v>-6.53</v>
       </c>
       <c r="D87" s="8">
-        <v>-22.27</v>
-      </c>
-      <c r="E87" s="10">
-        <v>-0.37</v>
+        <v>-6.57</v>
+      </c>
+      <c r="E87" s="9">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="8">
-        <v>-2.34</v>
+        <v>-6.66</v>
       </c>
       <c r="D88" s="8">
-        <v>-2.65</v>
-      </c>
-      <c r="E88" s="10">
-        <v>-0.31</v>
+        <v>-7.63</v>
+      </c>
+      <c r="E88" s="9">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="8">
-        <v>-5.75</v>
+        <v>-8.24</v>
       </c>
       <c r="D89" s="8">
-        <v>-5.82</v>
-      </c>
-      <c r="E89" s="10">
-        <v>-0.07000000000000001</v>
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="E89" s="9">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="8">
-        <v>-4.4</v>
+        <v>-8.35</v>
       </c>
       <c r="D90" s="8">
-        <v>-4.11</v>
+        <v>-8.58</v>
       </c>
       <c r="E90" s="9">
-        <v>0.29</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="8">
-        <v>-3.95</v>
+        <v>-19.63</v>
       </c>
       <c r="D91" s="8">
-        <v>-2.92</v>
+        <v>-20.16</v>
       </c>
       <c r="E91" s="9">
-        <v>1.03</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="8">
-        <v>-9.84</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="D92" s="8">
-        <v>-9.81</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="E92" s="9">
-        <v>0.03</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="8">
-        <v>-13.43</v>
+        <v>-22.27</v>
       </c>
       <c r="D93" s="8">
-        <v>-13.82</v>
-      </c>
-      <c r="E93" s="10">
-        <v>-0.39</v>
+        <v>-24.04</v>
+      </c>
+      <c r="E93" s="9">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="8">
-        <v>-1.94</v>
+        <v>-2.65</v>
       </c>
       <c r="D94" s="8">
-        <v>-2.61</v>
-      </c>
-      <c r="E94" s="10">
-        <v>-0.67</v>
+        <v>-2.85</v>
+      </c>
+      <c r="E94" s="9">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="8">
-        <v>-5.42</v>
+        <v>-5.82</v>
       </c>
       <c r="D95" s="8">
-        <v>-6.27</v>
-      </c>
-      <c r="E95" s="10">
-        <v>-0.85</v>
+        <v>-5.91</v>
+      </c>
+      <c r="E95" s="9">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="8">
-        <v>-2.3</v>
+        <v>-4.11</v>
       </c>
       <c r="D96" s="8">
-        <v>-3.15</v>
-      </c>
-      <c r="E96" s="10">
-        <v>-0.85</v>
+        <v>-6.85</v>
+      </c>
+      <c r="E96" s="9">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="8">
-        <v>-2.98</v>
+        <v>-2.92</v>
       </c>
       <c r="D97" s="8">
-        <v>-2.6</v>
+        <v>-4.12</v>
       </c>
       <c r="E97" s="9">
-        <v>0.38</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="8">
-        <v>-1.8</v>
+        <v>-9.81</v>
       </c>
       <c r="D98" s="8">
-        <v>-1.6</v>
+        <v>-10.09</v>
       </c>
       <c r="E98" s="9">
-        <v>0.2</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="8">
-        <v>-4.93</v>
+        <v>-13.82</v>
       </c>
       <c r="D99" s="8">
-        <v>-4.67</v>
+        <v>-14.73</v>
       </c>
       <c r="E99" s="9">
-        <v>0.26</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="7" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C100" s="8">
-        <v>27837.4</v>
+        <v>-2.61</v>
       </c>
       <c r="D100" s="8">
-        <v>27710.9</v>
+        <v>-1.88</v>
       </c>
       <c r="E100" s="10">
-        <v>-126.5</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C101" s="8">
-        <v>9750.6</v>
+        <v>-6.27</v>
       </c>
       <c r="D101" s="8">
-        <v>9803.85</v>
+        <v>-7.86</v>
       </c>
       <c r="E101" s="9">
-        <v>53.25</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="7" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C102" s="8">
-        <v>11644.8</v>
+        <v>-10.34</v>
       </c>
       <c r="D102" s="8">
-        <v>11597.7</v>
-      </c>
-      <c r="E102" s="10">
-        <v>-47.1</v>
+        <v>-10.79</v>
+      </c>
+      <c r="E102" s="9">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="7" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C103" s="8">
-        <v>38140.8</v>
+        <v>-3.15</v>
       </c>
       <c r="D103" s="8">
-        <v>38067.85</v>
+        <v>-2.49</v>
       </c>
       <c r="E103" s="10">
-        <v>-72.95</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="7" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C104" s="8">
-        <v>45955.65</v>
+        <v>-2.6</v>
       </c>
       <c r="D104" s="8">
-        <v>45892.75</v>
+        <v>-2.14</v>
       </c>
       <c r="E104" s="10">
-        <v>-62.9</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105" s="8">
-        <v>25923.05</v>
+        <v>-1.6</v>
       </c>
       <c r="D105" s="8">
-        <v>26051</v>
+        <v>-2.2</v>
       </c>
       <c r="E105" s="9">
-        <v>127.95</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="7" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C106" s="8">
-        <v>30838.85</v>
+        <v>-4.67</v>
       </c>
       <c r="D106" s="8">
-        <v>30695.1</v>
-      </c>
-      <c r="E106" s="10">
-        <v>-143.75</v>
+        <v>-4.94</v>
+      </c>
+      <c r="E106" s="9">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="8">
-        <v>16271.8</v>
+        <v>27710.9</v>
       </c>
       <c r="D107" s="8">
-        <v>16221.4</v>
-      </c>
-      <c r="E107" s="10">
-        <v>-50.4</v>
+        <v>27698.75</v>
+      </c>
+      <c r="E107" s="9">
+        <v>-12.15</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="8">
-        <v>9204.200000000001</v>
+        <v>9803.85</v>
       </c>
       <c r="D108" s="8">
-        <v>9197.799999999999</v>
-      </c>
-      <c r="E108" s="10">
-        <v>-6.4</v>
+        <v>9702.1</v>
+      </c>
+      <c r="E108" s="9">
+        <v>-101.75</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="8">
-        <v>1560.75</v>
+        <v>11597.7</v>
       </c>
       <c r="D109" s="8">
-        <v>1565.45</v>
+        <v>11560.75</v>
       </c>
       <c r="E109" s="9">
-        <v>4.7</v>
+        <v>-36.95</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="8">
-        <v>13176.05</v>
+        <v>38067.85</v>
       </c>
       <c r="D110" s="8">
-        <v>13317.45</v>
+        <v>37973.35</v>
       </c>
       <c r="E110" s="9">
-        <v>141.4</v>
+        <v>-94.5</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="8">
-        <v>9706.65</v>
+        <v>45892.75</v>
       </c>
       <c r="D111" s="8">
-        <v>9710.15</v>
+        <v>45592.15</v>
       </c>
       <c r="E111" s="9">
-        <v>3.5</v>
+        <v>-300.6</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="8">
-        <v>8552.6</v>
+        <v>26051</v>
       </c>
       <c r="D112" s="8">
-        <v>8514.85</v>
-      </c>
-      <c r="E112" s="10">
-        <v>-37.75</v>
+        <v>25935.6</v>
+      </c>
+      <c r="E112" s="9">
+        <v>-115.4</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="8">
-        <v>26658.65</v>
+        <v>30695.1</v>
       </c>
       <c r="D113" s="8">
-        <v>26478.1</v>
-      </c>
-      <c r="E113" s="10">
-        <v>-180.55</v>
+        <v>29995.2</v>
+      </c>
+      <c r="E113" s="9">
+        <v>-699.9</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="7" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="8">
-        <v>916.15</v>
+        <v>16221.4</v>
       </c>
       <c r="D114" s="8">
-        <v>907.9</v>
-      </c>
-      <c r="E114" s="10">
-        <v>-8.25</v>
+        <v>16187</v>
+      </c>
+      <c r="E114" s="9">
+        <v>-34.4</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="8">
-        <v>30575.05</v>
+        <v>9197.799999999999</v>
       </c>
       <c r="D115" s="8">
-        <v>30575.55</v>
+        <v>9188.700000000001</v>
       </c>
       <c r="E115" s="9">
-        <v>0.5</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="8">
-        <v>16552.2</v>
+        <v>1565.45</v>
       </c>
       <c r="D116" s="8">
-        <v>16408.05</v>
-      </c>
-      <c r="E116" s="10">
-        <v>-144.15</v>
+        <v>1520.65</v>
+      </c>
+      <c r="E116" s="9">
+        <v>-44.8</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="8">
-        <v>9670.9</v>
+        <v>13317.45</v>
       </c>
       <c r="D117" s="8">
-        <v>9708.85</v>
+        <v>13152.9</v>
       </c>
       <c r="E117" s="9">
-        <v>37.95</v>
+        <v>-164.55</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="8">
-        <v>11164.65</v>
+        <v>9710.15</v>
       </c>
       <c r="D118" s="8">
-        <v>11187.65</v>
+        <v>9680.049999999999</v>
       </c>
       <c r="E118" s="9">
-        <v>23</v>
+        <v>-30.1</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="8">
-        <v>27747.85</v>
+        <v>8514.85</v>
       </c>
       <c r="D119" s="8">
-        <v>27824.5</v>
+        <v>8424.65</v>
       </c>
       <c r="E119" s="9">
-        <v>76.65000000000001</v>
+        <v>-90.2</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C120" s="8">
-        <v>26</v>
+        <v>26478.1</v>
       </c>
       <c r="D120" s="8">
-        <v>19</v>
+        <v>26675.5</v>
       </c>
       <c r="E120" s="10">
-        <v>-7</v>
+        <v>197.4</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C121" s="8">
-        <v>44</v>
+        <v>907.9</v>
       </c>
       <c r="D121" s="8">
-        <v>38</v>
-      </c>
-      <c r="E121" s="10">
-        <v>-6</v>
+        <v>892.5</v>
+      </c>
+      <c r="E121" s="9">
+        <v>-15.4</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C122" s="8">
-        <v>38</v>
+        <v>30575.55</v>
       </c>
       <c r="D122" s="8">
-        <v>44</v>
+        <v>30422.7</v>
       </c>
       <c r="E122" s="9">
-        <v>6</v>
+        <v>-152.85</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C123" s="8">
-        <v>19</v>
+        <v>16408.05</v>
       </c>
       <c r="D123" s="8">
-        <v>26</v>
-      </c>
-      <c r="E123" s="9">
-        <v>7</v>
+        <v>16520.3</v>
+      </c>
+      <c r="E123" s="10">
+        <v>112.25</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="7" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C124" s="8">
-        <v>34.09</v>
+        <v>9708.85</v>
       </c>
       <c r="D124" s="8">
-        <v>32.37</v>
+        <v>9754.549999999999</v>
       </c>
       <c r="E124" s="10">
-        <v>-1.72</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C125" s="8">
-        <v>42.25</v>
+        <v>11187.65</v>
       </c>
       <c r="D125" s="8">
-        <v>47.9</v>
+        <v>11118.85</v>
       </c>
       <c r="E125" s="9">
-        <v>5.65</v>
+        <v>-68.8</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="7" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C126" s="8">
-        <v>32.05</v>
+        <v>27824.5</v>
       </c>
       <c r="D126" s="8">
-        <v>30.15</v>
-      </c>
-      <c r="E126" s="10">
-        <v>-1.9</v>
+        <v>27745.75</v>
+      </c>
+      <c r="E126" s="9">
+        <v>-78.75</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C127" s="8">
-        <v>41.16</v>
+        <v>19</v>
       </c>
       <c r="D127" s="8">
-        <v>39.43</v>
+        <v>26</v>
       </c>
       <c r="E127" s="10">
-        <v>-1.73</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C128" s="8">
-        <v>28.7</v>
+        <v>38</v>
       </c>
       <c r="D128" s="8">
-        <v>28.27</v>
+        <v>44</v>
       </c>
       <c r="E128" s="10">
-        <v>-0.43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C129" s="8">
-        <v>38.15</v>
+        <v>44</v>
       </c>
       <c r="D129" s="8">
-        <v>42.83</v>
+        <v>19</v>
       </c>
       <c r="E129" s="9">
-        <v>4.68</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C130" s="8">
-        <v>52.09</v>
+        <v>32</v>
       </c>
       <c r="D130" s="8">
-        <v>50.42</v>
+        <v>38</v>
       </c>
       <c r="E130" s="10">
-        <v>-1.67</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C131" s="8">
-        <v>40.26</v>
+        <v>26</v>
       </c>
       <c r="D131" s="8">
-        <v>37.61</v>
+        <v>32</v>
       </c>
       <c r="E131" s="10">
-        <v>-2.65</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="8">
-        <v>37.21</v>
+        <v>32.37</v>
       </c>
       <c r="D132" s="8">
-        <v>36.7</v>
-      </c>
-      <c r="E132" s="10">
-        <v>-0.51</v>
+        <v>32.2</v>
+      </c>
+      <c r="E132" s="9">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="8">
-        <v>47.51</v>
+        <v>47.9</v>
       </c>
       <c r="D133" s="8">
-        <v>48.68</v>
+        <v>39.88</v>
       </c>
       <c r="E133" s="9">
-        <v>1.17</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="8">
-        <v>52.73</v>
+        <v>30.15</v>
       </c>
       <c r="D134" s="8">
-        <v>57.58</v>
+        <v>28.71</v>
       </c>
       <c r="E134" s="9">
-        <v>4.85</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="8">
-        <v>38.08</v>
+        <v>39.43</v>
       </c>
       <c r="D135" s="8">
-        <v>38.62</v>
+        <v>37.25</v>
       </c>
       <c r="E135" s="9">
-        <v>0.54</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="8">
-        <v>48.6</v>
+        <v>28.27</v>
       </c>
       <c r="D136" s="8">
-        <v>45.98</v>
-      </c>
-      <c r="E136" s="10">
-        <v>-2.62</v>
+        <v>26.23</v>
+      </c>
+      <c r="E136" s="9">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="8">
-        <v>54.7</v>
+        <v>42.83</v>
       </c>
       <c r="D137" s="8">
-        <v>49.59</v>
-      </c>
-      <c r="E137" s="10">
-        <v>-5.11</v>
+        <v>39.9</v>
+      </c>
+      <c r="E137" s="9">
+        <v>-2.93</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="8">
-        <v>57.61</v>
+        <v>50.42</v>
       </c>
       <c r="D138" s="8">
-        <v>53.17</v>
-      </c>
-      <c r="E138" s="10">
-        <v>-4.44</v>
+        <v>43.19</v>
+      </c>
+      <c r="E138" s="9">
+        <v>-7.23</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="8">
-        <v>38</v>
+        <v>37.61</v>
       </c>
       <c r="D139" s="8">
-        <v>38.02</v>
+        <v>35.88</v>
       </c>
       <c r="E139" s="9">
-        <v>0.02</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="7" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="8">
-        <v>49.15</v>
+        <v>36.7</v>
       </c>
       <c r="D140" s="8">
-        <v>43.46</v>
-      </c>
-      <c r="E140" s="10">
-        <v>-5.69</v>
+        <v>35.94</v>
+      </c>
+      <c r="E140" s="9">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="8">
-        <v>51.06</v>
+        <v>48.68</v>
       </c>
       <c r="D141" s="8">
-        <v>53.41</v>
+        <v>39.6</v>
       </c>
       <c r="E141" s="9">
-        <v>2.35</v>
+        <v>-9.08</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="8">
-        <v>49.04</v>
+        <v>57.58</v>
       </c>
       <c r="D142" s="8">
-        <v>51.29</v>
+        <v>51.02</v>
       </c>
       <c r="E142" s="9">
-        <v>2.25</v>
+        <v>-6.56</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="8">
-        <v>52.15</v>
+        <v>38.62</v>
       </c>
       <c r="D143" s="8">
+        <v>35.72</v>
+      </c>
+      <c r="E143" s="9">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C144" s="8">
+        <v>45.98</v>
+      </c>
+      <c r="D144" s="8">
+        <v>40.37</v>
+      </c>
+      <c r="E144" s="9">
+        <v>-5.61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C145" s="8">
+        <v>49.59</v>
+      </c>
+      <c r="D145" s="8">
+        <v>54.58</v>
+      </c>
+      <c r="E145" s="10">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C146" s="8">
+        <v>53.17</v>
+      </c>
+      <c r="D146" s="8">
+        <v>46.05</v>
+      </c>
+      <c r="E146" s="9">
+        <v>-7.12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C147" s="8">
+        <v>38.02</v>
+      </c>
+      <c r="D147" s="8">
+        <v>34.27</v>
+      </c>
+      <c r="E147" s="9">
+        <v>-3.75</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C148" s="8">
+        <v>43.46</v>
+      </c>
+      <c r="D148" s="8">
+        <v>48.46</v>
+      </c>
+      <c r="E148" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C149" s="8">
+        <v>53.41</v>
+      </c>
+      <c r="D149" s="8">
+        <v>56.14</v>
+      </c>
+      <c r="E149" s="10">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C150" s="8">
+        <v>51.29</v>
+      </c>
+      <c r="D150" s="8">
+        <v>44.9</v>
+      </c>
+      <c r="E150" s="9">
+        <v>-6.39</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C151" s="8">
         <v>54.09</v>
       </c>
-      <c r="E143" s="9">
-        <v>1.94</v>
+      <c r="D151" s="8">
+        <v>51.77</v>
+      </c>
+      <c r="E151" s="9">
+        <v>-2.32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5780,28 +5973,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5815,22 +6008,22 @@
         <v>20</v>
       </c>
       <c r="D2" s="13">
-        <v>44</v>
+        <v>41.1</v>
       </c>
       <c r="E2" s="13">
         <v>40</v>
       </c>
       <c r="F2" s="13">
-        <v>-1.8</v>
+        <v>-2.5</v>
       </c>
       <c r="G2" s="13">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="H2" s="13">
         <v>53.1</v>
       </c>
       <c r="I2" s="13">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -5950,10 +6143,10 @@
         <v>48</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>52</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>46</v>
@@ -5964,34 +6157,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="16">
-        <v>0.3936</v>
+        <v>0.4052</v>
       </c>
       <c r="B2" s="16">
-        <v>0.2933</v>
+        <v>0.2935</v>
       </c>
       <c r="C2" s="16">
-        <v>0.2625</v>
+        <v>0.2887</v>
       </c>
       <c r="D2" s="16">
-        <v>0.2224</v>
+        <v>0.2223</v>
       </c>
       <c r="E2" s="16">
         <v>0.2129</v>
       </c>
       <c r="F2" s="16">
-        <v>0.1835</v>
+        <v>0.1817</v>
       </c>
       <c r="G2" s="16">
-        <v>0.1645</v>
+        <v>0.1622</v>
       </c>
       <c r="H2" s="16">
-        <v>0.1609</v>
+        <v>0.1481</v>
       </c>
       <c r="I2" s="16">
-        <v>0.1372</v>
+        <v>0.1365</v>
       </c>
       <c r="J2" s="16">
-        <v>0.1284</v>
+        <v>0.1314</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6011,10 +6204,10 @@
         <v>43</v>
       </c>
       <c r="F3" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>53</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>42</v>
@@ -6028,34 +6221,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="16">
-        <v>0.1264</v>
+        <v>0.1265</v>
       </c>
       <c r="B4" s="16">
-        <v>0.1183</v>
+        <v>0.1162</v>
       </c>
       <c r="C4" s="16">
-        <v>0.1058</v>
+        <v>0.1041</v>
       </c>
       <c r="D4" s="16">
-        <v>0.0803</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="E4" s="16">
-        <v>0.0759</v>
+        <v>0.0746</v>
       </c>
       <c r="F4" s="16">
-        <v>0.0711</v>
+        <v>0.0464</v>
       </c>
       <c r="G4" s="16">
-        <v>0.047</v>
+        <v>0.0413</v>
       </c>
       <c r="H4" s="16">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="I4" s="16">
-        <v>-0.0118</v>
+        <v>-0.0178</v>
       </c>
       <c r="J4" s="16">
-        <v>-0.0282</v>
+        <v>-0.0301</v>
       </c>
     </row>
   </sheetData>
